--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36BFCDF0-9253-4D24-A258-E7CE511C0703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9135497C-9C3F-43AB-A86E-305BF3FC8BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2286,23 +2286,23 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="26" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="190" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="193" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="26" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="190" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="193" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C23" s="100">
         <f>Normalized_FCF!C16</f>
-        <v>110800.86771817462</v>
+        <v>130935.41066403006</v>
       </c>
       <c r="D23" s="1" t="str">
         <f>C12</f>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="C25" s="100">
         <f>C23+C24</f>
-        <v>110800.86771817462</v>
+        <v>130935.41066403006</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="C27" s="100">
         <f>Normalized_FCF!C19</f>
-        <v>110800.86771817462</v>
+        <v>130935.41066403006</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="C28" s="143">
         <f>C27/(Common_Shares/Data!C3)</f>
-        <v>8.3100640401050918E-2</v>
+        <v>9.8201545722829325E-2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="C29" s="123">
         <f>C28/Market_Price</f>
-        <v>3.6130713217848227E-2</v>
+        <v>4.2696324227317103E-2</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="C69" s="201">
         <f>Scenarios!F83</f>
-        <v>-0.25621827775788097</v>
+        <v>-0.31072807723991103</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="C90" s="192">
         <f>Scenarios!C83</f>
-        <v>1.1180447596902363</v>
+        <v>1.5469034555263168</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="C12" s="77">
         <f>C64</f>
-        <v>78938.959999999992</v>
+        <v>105586.28</v>
       </c>
       <c r="E12" s="20"/>
       <c r="G12" s="77">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="C13" s="80">
         <f>SUM(C10:C12)</f>
-        <v>149453.72649438077</v>
+        <v>176101.04649438077</v>
       </c>
       <c r="E13" s="20"/>
       <c r="G13" s="80">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="C14" s="77">
         <f>-C13*C37</f>
-        <v>-36527.455690440976</v>
+        <v>-43040.232744585555</v>
       </c>
       <c r="E14" s="20"/>
       <c r="G14" s="77">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="C16" s="73">
         <f>SUM(C13:C15)</f>
-        <v>110800.86771817462</v>
+        <v>130935.41066403006</v>
       </c>
       <c r="D16" s="70"/>
       <c r="E16" s="104"/>
@@ -6223,7 +6223,7 @@
       </c>
       <c r="C19" s="80">
         <f>SUM(C16:C18)</f>
-        <v>110800.86771817462</v>
+        <v>130935.41066403006</v>
       </c>
       <c r="D19" s="30"/>
       <c r="E19" s="86"/>
@@ -6548,7 +6548,7 @@
       </c>
       <c r="C26" s="101">
         <f>ABS(C12/C$4)</f>
-        <v>4.9016405250673717E-2</v>
+        <v>6.5562808141773163E-2</v>
       </c>
       <c r="D26" s="30"/>
       <c r="E26" s="86"/>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="C27" s="101">
         <f>ABS(C14/C$4)</f>
-        <v>2.2681380282925982E-2</v>
+        <v>2.6725427979947067E-2</v>
       </c>
       <c r="D27" s="30"/>
       <c r="E27" s="86"/>
@@ -6660,7 +6660,7 @@
       <c r="B28" s="45"/>
       <c r="C28" s="102">
         <f>ABS(C16/C$4)</f>
-        <v>6.8800757372536187E-2</v>
+        <v>8.1303112566614544E-2</v>
       </c>
       <c r="D28" s="30"/>
       <c r="E28" s="86"/>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="C34" s="102">
         <f>ABS(C19/C$4)</f>
-        <v>6.8800757372536187E-2</v>
+        <v>8.1303112566614544E-2</v>
       </c>
       <c r="D34" s="99"/>
       <c r="E34" s="86"/>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="C38" s="101">
         <f>C19*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.6130713217848227E-2</v>
+        <v>4.2696324227317096E-2</v>
       </c>
       <c r="D38" s="30"/>
       <c r="E38" s="86"/>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="C63" s="77">
         <f>BS!$G$24*C68</f>
-        <v>79941.959999999992</v>
+        <v>106589.28</v>
       </c>
       <c r="G63" s="77">
         <f>Data!C52</f>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="C64" s="80">
         <f>C62+C63</f>
-        <v>78938.959999999992</v>
+        <v>105586.28</v>
       </c>
       <c r="G64" s="80">
         <f t="shared" ref="G64:Q64" si="35">IF(G4="","",G62+G63)</f>
@@ -8302,7 +8302,7 @@
         <v>185</v>
       </c>
       <c r="C68" s="116">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="E68" s="86" t="s">
         <v>165</v>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C96" s="26">
         <f>C94/(C19*$C$3/Common_Shares)</f>
-        <v>1.4175582694848916</v>
+        <v>1.1995737860632731</v>
       </c>
       <c r="G96" s="227">
         <f t="shared" ref="G96:Q96" si="46">IF(G$4="","",G94/(G19*$C$3/Common_Shares))</f>
@@ -10160,7 +10160,7 @@
     <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="G46:Q47 G50:Q50 G4:Q13 G15:Q16">
+  <conditionalFormatting sqref="G4:Q13 G15:Q16 G46:Q47 G50:Q50">
     <cfRule type="expression" dxfId="2" priority="2">
       <formula>ISBLANK(G4)</formula>
     </cfRule>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="C4" s="152">
         <f>Normalized_FCF!C19</f>
-        <v>110800.86771817462</v>
+        <v>130935.41066403006</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="C6" s="179">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>1108008.6771817461</v>
+        <v>1309354.1066403005</v>
       </c>
       <c r="E6" s="193" t="s">
         <v>254</v>
@@ -11067,7 +11067,7 @@
       </c>
       <c r="C9" s="179">
         <f>C6-C7+C8</f>
-        <v>1314129.1771817461</v>
+        <v>1515474.6066403005</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -11079,7 +11079,7 @@
       <c r="B10" s="195" t="s">
         <v>331</v>
       </c>
-      <c r="C10" s="234">
+      <c r="C10" s="232">
         <f>Exchange_Rate</f>
         <v>1.06</v>
       </c>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="C11" s="154">
         <f>(C9*C3)/Common_Shares*C10</f>
-        <v>1.0447325652679176</v>
+        <v>1.2048021616787687</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -11144,11 +11144,11 @@
       </c>
       <c r="C17" s="185">
         <f>(F51-C7)/Common_Shares*C3</f>
-        <v>2.3224961207390811</v>
+        <v>2.7491697970218909</v>
       </c>
       <c r="D17" t="str">
         <f>IF(ROUND(C17,1)=ROUND(Scenarios!C29,1),"equals Market Price","a Current Projection")</f>
-        <v>equals Market Price</v>
+        <v>a Current Projection</v>
       </c>
       <c r="H17" s="164"/>
     </row>
@@ -11179,7 +11179,7 @@
       </c>
       <c r="C20" s="167">
         <f>C4*(1+D20)</f>
-        <v>129637.0152302643</v>
+        <v>153194.43047691515</v>
       </c>
       <c r="D20" s="183">
         <f>IF($C$16&lt;B20,0,Valuation_Model!$C$15)</f>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="F20" s="169">
         <f t="shared" ref="F20:F50" si="1">C20*E20</f>
-        <v>117851.832027513</v>
+        <v>139267.66406992284</v>
       </c>
       <c r="H20" s="164"/>
     </row>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="C21" s="167">
         <f t="shared" ref="C21:C49" si="2">IF(ROW()-ROW($C$20)&lt;$C$16, $C$20*(1+D21)^(ROW()-ROW($C$20)), 0)</f>
-        <v>151675.30781940921</v>
+        <v>179237.48365799073</v>
       </c>
       <c r="D21" s="183">
         <f>IF($C$16&lt;B21,0,Valuation_Model!$C$15)</f>
@@ -11213,7 +11213,7 @@
       </c>
       <c r="F21" s="169">
         <f t="shared" si="1"/>
-        <v>125351.49406562743</v>
+        <v>148130.1517834634</v>
       </c>
       <c r="H21" s="164"/>
     </row>
@@ -11223,7 +11223,7 @@
       </c>
       <c r="C22" s="167">
         <f t="shared" si="2"/>
-        <v>177460.11014870877</v>
+        <v>209707.85587984911</v>
       </c>
       <c r="D22" s="183">
         <f>IF($C$16&lt;B22,0,Valuation_Model!$C$15)</f>
@@ -11235,7 +11235,7 @@
       </c>
       <c r="F22" s="169">
         <f t="shared" si="1"/>
-        <v>133328.40732434916</v>
+        <v>157556.61598786555</v>
       </c>
       <c r="H22" s="164"/>
     </row>
@@ -11245,7 +11245,7 @@
       </c>
       <c r="C23" s="167">
         <f t="shared" si="2"/>
-        <v>207628.32887398926</v>
+        <v>245358.19137942346</v>
       </c>
       <c r="D23" s="183">
         <f>IF($C$16&lt;B23,0,Valuation_Model!$C$15)</f>
@@ -11257,7 +11257,7 @@
       </c>
       <c r="F23" s="169">
         <f t="shared" si="1"/>
-        <v>141812.94233589864</v>
+        <v>167582.94609618429</v>
       </c>
       <c r="H23" s="164"/>
     </row>
@@ -11267,7 +11267,7 @@
       </c>
       <c r="C24" s="167">
         <f t="shared" si="2"/>
-        <v>242925.1447825674</v>
+        <v>287069.08391392539</v>
       </c>
       <c r="D24" s="183">
         <f>IF($C$16&lt;B24,0,Valuation_Model!$C$15)</f>
@@ -11279,7 +11279,7 @@
       </c>
       <c r="F24" s="169">
         <f t="shared" si="1"/>
-        <v>150837.40230272853</v>
+        <v>178247.31539321411</v>
       </c>
       <c r="H24" s="164"/>
     </row>
@@ -11289,7 +11289,7 @@
       </c>
       <c r="C25" s="167">
         <f t="shared" si="2"/>
-        <v>284222.41939560382</v>
+        <v>335870.82817929267</v>
       </c>
       <c r="D25" s="183">
         <f>IF($C$16&lt;B25,0,Valuation_Model!$C$15)</f>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="F25" s="169">
         <f t="shared" si="1"/>
-        <v>160436.14608562941</v>
+        <v>189590.32637278226</v>
       </c>
       <c r="H25" s="164"/>
     </row>
@@ -11311,7 +11311,7 @@
       </c>
       <c r="C26" s="167">
         <f t="shared" si="2"/>
-        <v>332540.23069285648</v>
+        <v>392968.86896977248</v>
       </c>
       <c r="D26" s="183">
         <f>IF($C$16&lt;B26,0,Valuation_Model!$C$15)</f>
@@ -11323,7 +11323,7 @@
       </c>
       <c r="F26" s="169">
         <f t="shared" si="1"/>
-        <v>170645.71901835126</v>
+        <v>201655.1653237775</v>
       </c>
       <c r="H26" s="164"/>
     </row>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C27" s="167">
         <f t="shared" si="2"/>
-        <v>389072.06991064205</v>
+        <v>459773.5766946337</v>
       </c>
       <c r="D27" s="183">
         <f>IF($C$16&lt;B27,0,Valuation_Model!$C$15)</f>
@@ -11345,7 +11345,7 @@
       </c>
       <c r="F27" s="169">
         <f t="shared" si="1"/>
-        <v>181504.99204679177</v>
+        <v>214487.76675347239</v>
       </c>
       <c r="H27" s="164"/>
     </row>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="C28" s="167">
         <f t="shared" si="2"/>
-        <v>455214.32179545111</v>
+        <v>537935.08473272144</v>
       </c>
       <c r="D28" s="183">
         <f>IF($C$16&lt;B28,0,Valuation_Model!$C$15)</f>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="F28" s="169">
         <f t="shared" si="1"/>
-        <v>193055.30972249666</v>
+        <v>228136.98827414791</v>
       </c>
       <c r="H28" s="164"/>
     </row>
@@ -11377,7 +11377,7 @@
       </c>
       <c r="C29" s="167">
         <f t="shared" si="2"/>
-        <v>532600.75650067779</v>
+        <v>629384.04913728393</v>
       </c>
       <c r="D29" s="183">
         <f>IF($C$16&lt;B29,0,Valuation_Model!$C$15)</f>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="F29" s="169">
         <f t="shared" si="1"/>
-        <v>205340.64761392825</v>
+        <v>242654.79661886633</v>
       </c>
       <c r="H29" s="164"/>
     </row>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="C30" s="167">
         <f t="shared" si="2"/>
-        <v>623142.88510579302</v>
+        <v>736379.3374906223</v>
       </c>
       <c r="D30" s="183">
         <f>IF($C$16&lt;B30,0,Valuation_Model!$C$15)</f>
@@ -11411,7 +11411,7 @@
       </c>
       <c r="F30" s="169">
         <f t="shared" si="1"/>
-        <v>218407.77973481454</v>
+        <v>258096.46549461235</v>
       </c>
       <c r="H30" s="164"/>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="C31" s="167">
         <f t="shared" si="2"/>
-        <v>729077.17557377776</v>
+        <v>861563.82486402802</v>
       </c>
       <c r="D31" s="183">
         <f>IF($C$16&lt;B31,0,Valuation_Model!$C$15)</f>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="F31" s="169">
         <f t="shared" si="1"/>
-        <v>232306.45662703001</v>
+        <v>274520.78602608771</v>
       </c>
       <c r="H31" s="164"/>
     </row>
@@ -11443,7 +11443,7 @@
       </c>
       <c r="C32" s="167">
         <f t="shared" si="2"/>
-        <v>853020.29542131978</v>
+        <v>1008029.6750909126</v>
       </c>
       <c r="D32" s="183">
         <f>IF($C$16&lt;B32,0,Valuation_Model!$C$15)</f>
@@ -11455,7 +11455,7 @@
       </c>
       <c r="F32" s="169">
         <f t="shared" si="1"/>
-        <v>247089.59477602277</v>
+        <v>291990.29059138411</v>
       </c>
       <c r="H32" s="164"/>
     </row>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="C33" s="167">
         <f t="shared" si="2"/>
-        <v>998033.74564294412</v>
+        <v>1179394.7198563677</v>
       </c>
       <c r="D33" s="183">
         <f>IF($C$16&lt;B33,0,Valuation_Model!$C$15)</f>
@@ -11477,7 +11477,7 @@
       </c>
       <c r="F33" s="169">
         <f t="shared" si="1"/>
-        <v>262813.47807995143</v>
+        <v>310571.49090174481</v>
       </c>
       <c r="H33" s="164"/>
     </row>
@@ -11487,7 +11487,7 @@
       </c>
       <c r="C34" s="167">
         <f t="shared" si="2"/>
-        <v>1167699.4824022446</v>
+        <v>1379891.8222319502</v>
       </c>
       <c r="D34" s="183">
         <f>IF($C$16&lt;B34,0,Valuation_Model!$C$15)</f>
@@ -11499,7 +11499,7 @@
       </c>
       <c r="F34" s="169">
         <f t="shared" si="1"/>
-        <v>279537.97213958466</v>
+        <v>330335.13123185589</v>
       </c>
       <c r="H34" s="164"/>
     </row>
@@ -11839,7 +11839,7 @@
       </c>
       <c r="C50" s="167">
         <f>C$20*(1+Terminal_Growth)^$C$16/Equity_Cost</f>
-        <v>1296370.1523026428</v>
+        <v>1531944.3047691514</v>
       </c>
       <c r="D50" s="184">
         <f>Terminal_Growth</f>
@@ -11851,7 +11851,7 @@
       </c>
       <c r="F50" s="169">
         <f t="shared" si="1"/>
-        <v>310340.70750074415</v>
+        <v>366735.28663810535</v>
       </c>
       <c r="H50" s="164"/>
     </row>
@@ -11862,7 +11862,7 @@
       </c>
       <c r="F51" s="182">
         <f>SUM(F20:F50)</f>
-        <v>3130660.8814014615</v>
+        <v>3699559.1875574873</v>
       </c>
       <c r="H51" s="164"/>
     </row>
@@ -11883,11 +11883,11 @@
     <row r="54" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A54" s="177">
         <f>F51</f>
-        <v>3130660.8814014615</v>
+        <v>3699559.1875574873</v>
       </c>
       <c r="B54" s="175">
         <f>C77</f>
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="C54" s="175">
         <f>C76</f>
@@ -11899,11 +11899,11 @@
       </c>
       <c r="E54" s="175">
         <f>C74</f>
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="F54" s="175">
         <f>C73</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="H54" s="164"/>
     </row>
@@ -11913,19 +11913,19 @@
       </c>
       <c r="B55" s="167">
         <f t="dataTable" ref="B55:F60" dt2D="1" dtr="1" r1="C15" r2="C16"/>
-        <v>1018170.3409061425</v>
+        <v>1265889.0635203847</v>
       </c>
       <c r="C55" s="167">
-        <v>1205269.0947300647</v>
+        <v>1424288.5198385399</v>
       </c>
       <c r="D55" s="167">
-        <v>1425472.0251963497</v>
+        <v>1684506.34776532</v>
       </c>
       <c r="E55" s="167">
-        <v>1425472.0251963497</v>
+        <v>1832004.6953997593</v>
       </c>
       <c r="F55" s="167">
-        <v>1550288.8705555289</v>
+        <v>1992709.8154951304</v>
       </c>
       <c r="H55" s="164"/>
     </row>
@@ -11934,19 +11934,19 @@
         <v>10</v>
       </c>
       <c r="B56" s="167">
-        <v>945576.17761718901</v>
+        <v>1227172.8337885675</v>
       </c>
       <c r="C56" s="167">
-        <v>1314099.0994997886</v>
+        <v>1552894.9257318284</v>
       </c>
       <c r="D56" s="167">
-        <v>1917709.6717443373</v>
+        <v>2266192.5720915622</v>
       </c>
       <c r="E56" s="167">
-        <v>1917709.6717443373</v>
+        <v>2785350.8370045479</v>
       </c>
       <c r="F56" s="167">
-        <v>2357034.5720420936</v>
+        <v>3457749.5519229416</v>
       </c>
       <c r="H56" s="164"/>
     </row>
@@ -11955,19 +11955,19 @@
         <v>15</v>
       </c>
       <c r="B57" s="167">
-        <v>875896.25705796923</v>
+        <v>1187424.4666885207</v>
       </c>
       <c r="C57" s="167">
-        <v>1447320.8328407165</v>
+        <v>1710325.4831236375</v>
       </c>
       <c r="D57" s="167">
-        <v>2720804.9813367426</v>
+        <v>3215224.9788710778</v>
       </c>
       <c r="E57" s="167">
-        <v>2720804.9813367426</v>
+        <v>4600091.7489890903</v>
       </c>
       <c r="F57" s="167">
-        <v>3892714.3909071451</v>
+        <v>6724645.5697237672</v>
       </c>
       <c r="H57" s="164"/>
     </row>
@@ -11976,19 +11976,19 @@
         <v>20</v>
       </c>
       <c r="B58" s="167">
-        <v>820809.02702296816</v>
+        <v>1153927.1717173851</v>
       </c>
       <c r="C58" s="167">
-        <v>1582064.2457700146</v>
+        <v>1869554.2370991511</v>
       </c>
       <c r="D58" s="167">
-        <v>3840732.1539905923</v>
+        <v>4538663.3894638224</v>
       </c>
       <c r="E58" s="167">
-        <v>3840732.1539905923</v>
+        <v>7616172.7789579621</v>
       </c>
       <c r="F58" s="167">
-        <v>6444998.7082975544</v>
+        <v>13219833.721733619</v>
       </c>
       <c r="H58" s="164"/>
     </row>
@@ -11997,19 +11997,19 @@
         <v>25</v>
       </c>
       <c r="B59" s="167">
-        <v>780924.47670820646</v>
+        <v>1128179.5010663259</v>
       </c>
       <c r="C59" s="167">
-        <v>1706956.1504230951</v>
+        <v>2017141.2836731707</v>
       </c>
       <c r="D59" s="167">
-        <v>5312017.2579092421</v>
+        <v>6277307.8897528686</v>
       </c>
       <c r="E59" s="167">
-        <v>5312017.2579092421</v>
+        <v>12407939.743817186</v>
       </c>
       <c r="F59" s="167">
-        <v>10499913.531698652</v>
+        <v>25716796.285569325</v>
       </c>
       <c r="H59" s="164"/>
     </row>
@@ -12018,19 +12018,19 @@
         <v>30</v>
       </c>
       <c r="B60" s="167">
-        <v>753430.44986577693</v>
+        <v>1109414.8178270396</v>
       </c>
       <c r="C60" s="167">
-        <v>1817175.2540756224</v>
+        <v>2147389.2131070094</v>
       </c>
       <c r="D60" s="167">
-        <v>7194584.8993992582</v>
+        <v>8501972.4823468253</v>
       </c>
       <c r="E60" s="167">
-        <v>7194584.8993992582</v>
+        <v>19893281.460725758</v>
       </c>
       <c r="F60" s="167">
-        <v>16834199.674724173</v>
+        <v>49514800.605722822</v>
       </c>
       <c r="H60" s="164"/>
     </row>
@@ -12054,7 +12054,7 @@
     <row r="63" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="176">
         <f>B54</f>
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="C63" s="176">
         <f>C54</f>
@@ -12066,11 +12066,11 @@
       </c>
       <c r="E63" s="176">
         <f>E54</f>
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="F63" s="176">
         <f>F54</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="H63" s="164"/>
     </row>
@@ -12080,200 +12080,200 @@
       </c>
       <c r="B64" s="168">
         <f>C11</f>
-        <v>1.0447325652679176</v>
+        <v>1.2048021616787687</v>
       </c>
       <c r="C64" s="168">
         <f>C11</f>
-        <v>1.0447325652679176</v>
+        <v>1.2048021616787687</v>
       </c>
       <c r="D64" s="168">
         <f>C11</f>
-        <v>1.0447325652679176</v>
+        <v>1.2048021616787687</v>
       </c>
       <c r="E64" s="186">
         <f>C11</f>
-        <v>1.0447325652679176</v>
+        <v>1.2048021616787687</v>
       </c>
       <c r="F64" s="168">
         <f>C11</f>
-        <v>1.0447325652679176</v>
+        <v>1.2048021616787687</v>
       </c>
       <c r="H64" s="164"/>
     </row>
     <row r="65" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A65" s="188">
-        <f>A55</f>
+        <f t="shared" ref="A65:A70" si="3">A55</f>
         <v>5</v>
       </c>
       <c r="B65" s="168">
-        <f>(B55-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>0.97331109685649619</v>
+        <f t="shared" ref="B65:F70" si="4">(B55-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
+        <v>1.1702474567177736</v>
       </c>
       <c r="C65" s="168">
-        <f>(C55-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>1.1220545875535779</v>
+        <f t="shared" si="4"/>
+        <v>1.2961750087497632</v>
       </c>
       <c r="D65" s="168">
-        <f>(D55-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>1.2971158953916111</v>
+        <f t="shared" si="4"/>
+        <v>1.50304815609241</v>
       </c>
       <c r="E65" s="168">
-        <f>(E55-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>1.2971158953916111</v>
+        <f t="shared" si="4"/>
+        <v>1.6203093278041427</v>
       </c>
       <c r="F65" s="168">
-        <f>(F55-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>1.3963452750484862</v>
+        <f t="shared" si="4"/>
+        <v>1.7480698823098935</v>
       </c>
       <c r="H65" s="164"/>
     </row>
     <row r="66" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A66" s="188">
-        <f>A56</f>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="B66" s="168">
-        <f>(B56-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>0.91559874425582222</v>
+        <f t="shared" si="4"/>
+        <v>1.1394680579284038</v>
       </c>
       <c r="C66" s="168">
-        <f>(C56-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>1.2085744305305282</v>
+        <f t="shared" si="4"/>
+        <v>1.3984170886546676</v>
       </c>
       <c r="D66" s="168">
-        <f>(D56-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>1.6884447754811513</v>
+        <f t="shared" si="4"/>
+        <v>1.9654886466267114</v>
       </c>
       <c r="E66" s="168">
-        <f>(E56-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>1.6884447754811513</v>
+        <f t="shared" si="4"/>
+        <v>2.3782194156411887</v>
       </c>
       <c r="F66" s="168">
-        <f>(F56-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.0377080275599608</v>
+        <f t="shared" si="4"/>
+        <v>2.9127763271816978</v>
       </c>
       <c r="H66" s="164"/>
     </row>
     <row r="67" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A67" s="188">
-        <f>A57</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="B67" s="168">
-        <f>(B57-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>0.86020321433568381</v>
+        <f t="shared" si="4"/>
+        <v>1.1078681100338603</v>
       </c>
       <c r="C67" s="168">
-        <f>(C57-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>1.3144856952976576</v>
+        <f t="shared" si="4"/>
+        <v>1.523574366136496</v>
       </c>
       <c r="D67" s="168">
-        <f>(D57-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.326905466799527</v>
+        <f t="shared" si="4"/>
+        <v>2.7199693157063427</v>
       </c>
       <c r="E67" s="168">
-        <f>(E57-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.326905466799527</v>
+        <f t="shared" si="4"/>
+        <v>3.8209382603290445</v>
       </c>
       <c r="F67" s="168">
-        <f>(F57-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>3.2585733309495142</v>
+        <f t="shared" si="4"/>
+        <v>5.509958336685604</v>
       </c>
       <c r="H67" s="164"/>
     </row>
     <row r="68" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A68" s="189">
-        <f>A58</f>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="B68" s="168">
-        <f>(B58-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>0.81640887193215061</v>
+        <f t="shared" si="4"/>
+        <v>1.0812377638606006</v>
       </c>
       <c r="C68" s="168">
-        <f>(C58-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>1.4216066951863249</v>
+        <f t="shared" si="4"/>
+        <v>1.650161209723674</v>
       </c>
       <c r="D68" s="168">
-        <f>(D58-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>3.217247457766589</v>
+        <f t="shared" si="4"/>
+        <v>3.7721027206108992</v>
       </c>
       <c r="E68" s="168">
-        <f>(E58-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>3.217247457766589</v>
+        <f t="shared" si="4"/>
+        <v>6.2187223794312834</v>
       </c>
       <c r="F68" s="168">
-        <f>(F58-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>5.2876391096416668</v>
+        <f t="shared" si="4"/>
+        <v>10.673632272074194</v>
       </c>
       <c r="H68" s="164"/>
     </row>
     <row r="69" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A69" s="189">
-        <f>A59</f>
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="B69" s="168">
-        <f>(B59-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>0.7847006583954419</v>
+        <f t="shared" si="4"/>
+        <v>1.0607683682516831</v>
       </c>
       <c r="C69" s="168">
-        <f>(C59-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>1.5208957469743922</v>
+        <f t="shared" si="4"/>
+        <v>1.7674928970835588</v>
       </c>
       <c r="D69" s="168">
-        <f>(D59-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>4.3869189691729762</v>
+        <f t="shared" si="4"/>
+        <v>5.1543249255629151</v>
       </c>
       <c r="E69" s="168">
-        <f>(E59-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>4.3869189691729762</v>
+        <f t="shared" si="4"/>
+        <v>10.028176640312582</v>
       </c>
       <c r="F69" s="168">
-        <f>(F59-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>8.5112959912884296</v>
+        <f t="shared" si="4"/>
+        <v>20.608716268438084</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A70" s="189">
-        <f>A60</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B70" s="168">
-        <f>(B60-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>0.7628429097879289</v>
+        <f t="shared" si="4"/>
+        <v>1.0458504469411907</v>
       </c>
       <c r="C70" s="168">
-        <f>(C60-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>1.6085199234251295</v>
+        <f t="shared" si="4"/>
+        <v>1.8710399880400741</v>
       </c>
       <c r="D70" s="168">
-        <f>(D60-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>5.8835600570774034</v>
+        <f t="shared" si="4"/>
+        <v>6.9229330555990947</v>
       </c>
       <c r="E70" s="168">
-        <f>(E60-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>5.8835600570774034</v>
+        <f t="shared" si="4"/>
+        <v>15.979022561399159</v>
       </c>
       <c r="F70" s="168">
-        <f>(F60-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>13.547052845524112</v>
+        <f t="shared" si="4"/>
+        <v>39.528127338033727</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B72" s="231" t="s">
+      <c r="B72" s="229" t="s">
         <v>236</v>
       </c>
-      <c r="C72" s="231" t="s">
+      <c r="C72" s="229" t="s">
         <v>261</v>
       </c>
-      <c r="D72" s="231" t="s">
+      <c r="D72" s="229" t="s">
         <v>230</v>
       </c>
-      <c r="E72" s="232" t="s">
+      <c r="E72" s="230" t="s">
         <v>231</v>
       </c>
-      <c r="F72" s="232" t="s">
+      <c r="F72" s="230" t="s">
         <v>320</v>
       </c>
     </row>
@@ -12284,19 +12284,19 @@
       </c>
       <c r="C73" s="187">
         <f>Scenarios!C69</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="D73" s="190">
         <f>Scenarios!C68</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E73" s="180">
         <f>INDEX(B$64:F$70, MATCH(D73, A$64:A$70, 0), MATCH(C73, B$63:F$63, 0))</f>
-        <v>2.0377080275599608</v>
-      </c>
-      <c r="F73" s="233">
+        <v>5.509958336685604</v>
+      </c>
+      <c r="F73" s="231">
         <f>E73*Common_Shares/1000000</f>
-        <v>2716.9443763646191</v>
+        <v>7346.6120339071949</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="C74" s="187">
         <f>Scenarios!C51</f>
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="D74" s="190">
         <f>Scenarios!C50</f>
@@ -12314,11 +12314,11 @@
       </c>
       <c r="E74" s="180">
         <f>INDEX(B$64:F$70, MATCH(D74, A$64:A$70, 0), MATCH(C74, B$63:F$63, 0))</f>
-        <v>1.6884447754811513</v>
-      </c>
-      <c r="F74" s="233">
+        <v>2.3782194156411887</v>
+      </c>
+      <c r="F74" s="231">
         <f>E74*Common_Shares/1000000</f>
-        <v>2251.2599820489977</v>
+        <v>3170.9596172248207</v>
       </c>
       <c r="H74" s="164" t="s">
         <v>223</v>
@@ -12339,11 +12339,11 @@
       </c>
       <c r="E75" s="180">
         <f>INDEX(B$64:F$70, MATCH(D75, A$64:A$70, 0), MATCH(C75, B$63:F$63, 0))</f>
-        <v>1.6884447754811513</v>
-      </c>
-      <c r="F75" s="233">
+        <v>1.9654886466267114</v>
+      </c>
+      <c r="F75" s="231">
         <f>E75*Common_Shares/1000000</f>
-        <v>2251.2599820489977</v>
+        <v>2620.651856417056</v>
       </c>
       <c r="H75" s="164" t="s">
         <v>222</v>
@@ -12364,11 +12364,11 @@
       </c>
       <c r="E76" s="180">
         <f>INDEX(B$64:F$70, MATCH(D76, A$64:A$70, 0), MATCH(C76, B$63:F$63, 0))</f>
-        <v>1.2085744305305282</v>
-      </c>
-      <c r="F76" s="233">
+        <v>1.3984170886546676</v>
+      </c>
+      <c r="F76" s="231">
         <f>E76*Common_Shares/1000000</f>
-        <v>1611.4327754697758</v>
+        <v>1864.5563512757383</v>
       </c>
       <c r="H76" s="164" t="s">
         <v>221</v>
@@ -12381,19 +12381,19 @@
       </c>
       <c r="C77" s="187">
         <f>Scenarios!C63</f>
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="D77" s="190">
         <f>Scenarios!C62</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E77" s="180">
         <f>INDEX(B$64:F$70, MATCH(D77, A$64:A$70, 0), MATCH(C77, B$63:F$63, 0))</f>
-        <v>0.91559874425582222</v>
-      </c>
-      <c r="F77" s="233">
+        <v>1.1078681100338603</v>
+      </c>
+      <c r="F77" s="231">
         <f>E77*Common_Shares/1000000</f>
-        <v>1220.7984782742203</v>
+        <v>1477.1576646898322</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.35">
@@ -12493,7 +12493,7 @@
         <f>Normalized_FCF!G19</f>
         <v>191231</v>
       </c>
-      <c r="E7" s="229" t="s">
+      <c r="E7" s="234" t="s">
         <v>301</v>
       </c>
     </row>
@@ -12503,18 +12503,18 @@
       </c>
       <c r="C8" s="158">
         <f>Normalized_FCF!C19</f>
-        <v>110800.86771817462</v>
-      </c>
-      <c r="E8" s="230"/>
+        <v>130935.41066403006</v>
+      </c>
+      <c r="E8" s="235"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="E9" s="230"/>
+      <c r="E9" s="235"/>
     </row>
     <row r="10" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B10" s="208" t="s">
         <v>284</v>
       </c>
-      <c r="E10" s="230"/>
+      <c r="E10" s="235"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="162" t="s">
@@ -12525,19 +12525,19 @@
         <v>5.1065088583959473E-2</v>
       </c>
       <c r="D11" s="207"/>
-      <c r="E11" s="230"/>
+      <c r="E11" s="235"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B12" s="193" t="s">
         <v>281</v>
       </c>
-      <c r="E12" s="230"/>
+      <c r="E12" s="235"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="138" t="s">
         <v>166</v>
       </c>
-      <c r="E13" s="230"/>
+      <c r="E13" s="235"/>
     </row>
     <row r="15" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B15" s="208" t="s">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="C21" s="209">
         <f>Valuation_Model!E76</f>
-        <v>1.2085744305305282</v>
+        <v>1.3984170886546676</v>
       </c>
       <c r="D21" t="str">
         <f>Reporting_currency</f>
@@ -12620,7 +12620,7 @@
       </c>
       <c r="C26" s="209">
         <f>Valuation_Model!C17</f>
-        <v>2.3224961207390811</v>
+        <v>2.7491697970218909</v>
       </c>
       <c r="D26" s="209"/>
       <c r="E26" s="223"/>
@@ -12696,7 +12696,7 @@
         <v>10</v>
       </c>
       <c r="D38" s="212"/>
-      <c r="E38" s="230"/>
+      <c r="E38" s="235"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B39" s="162" t="s">
@@ -12706,7 +12706,7 @@
         <v>0.15</v>
       </c>
       <c r="D39" s="213"/>
-      <c r="E39" s="230"/>
+      <c r="E39" s="235"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="138" t="s">
@@ -12714,13 +12714,13 @@
       </c>
       <c r="C40" s="209">
         <f>Valuation_Model!E75</f>
-        <v>1.6884447754811513</v>
+        <v>1.9654886466267114</v>
       </c>
       <c r="D40" s="209" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E40" s="230"/>
+      <c r="E40" s="235"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="138" t="s">
@@ -12730,7 +12730,7 @@
         <v>0.5</v>
       </c>
       <c r="D41" s="214"/>
-      <c r="E41" s="230"/>
+      <c r="E41" s="235"/>
     </row>
     <row r="43" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B43" s="208" t="s">
@@ -12749,7 +12749,7 @@
         <v>10</v>
       </c>
       <c r="D44" s="212"/>
-      <c r="E44" s="230"/>
+      <c r="E44" s="235"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B45" s="162" t="s">
@@ -12759,7 +12759,7 @@
         <v>0.05</v>
       </c>
       <c r="D45" s="213"/>
-      <c r="E45" s="230"/>
+      <c r="E45" s="235"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B46" s="138" t="s">
@@ -12767,13 +12767,13 @@
       </c>
       <c r="C46" s="209">
         <f>Valuation_Model!E76</f>
-        <v>1.2085744305305282</v>
+        <v>1.3984170886546676</v>
       </c>
       <c r="D46" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E46" s="230"/>
+      <c r="E46" s="235"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B47" s="138" t="s">
@@ -12783,7 +12783,7 @@
         <v>0.25</v>
       </c>
       <c r="D47" s="214"/>
-      <c r="E47" s="230"/>
+      <c r="E47" s="235"/>
     </row>
     <row r="49" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B49" s="208" t="s">
@@ -12801,17 +12801,17 @@
         <v>10</v>
       </c>
       <c r="D50" s="212"/>
-      <c r="E50" s="230"/>
+      <c r="E50" s="235"/>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B51" s="162" t="s">
         <v>263</v>
       </c>
       <c r="C51" s="213">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="D51" s="213"/>
-      <c r="E51" s="230"/>
+      <c r="E51" s="235"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B52" s="138" t="s">
@@ -12819,13 +12819,13 @@
       </c>
       <c r="C52" s="209">
         <f>Valuation_Model!E74</f>
-        <v>1.6884447754811513</v>
+        <v>2.3782194156411887</v>
       </c>
       <c r="D52" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E52" s="230"/>
+      <c r="E52" s="235"/>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B53" s="138" t="s">
@@ -12836,7 +12836,7 @@
         <v>0.25</v>
       </c>
       <c r="D53" s="214"/>
-      <c r="E53" s="230"/>
+      <c r="E53" s="235"/>
     </row>
     <row r="55" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B55" s="138" t="s">
@@ -12844,7 +12844,7 @@
       </c>
       <c r="C55" s="202">
         <f>C40*C41+C46*C47+C52*C53</f>
-        <v>1.5684771892434957</v>
+        <v>1.9269034493873198</v>
       </c>
       <c r="D55" t="str">
         <f>Market_currency</f>
@@ -12871,7 +12871,7 @@
         <v>262</v>
       </c>
       <c r="C59" s="196">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E59" s="138"/>
     </row>
@@ -12893,10 +12893,10 @@
       </c>
       <c r="C62" s="215">
         <f>C59</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D62" s="212"/>
-      <c r="E62" s="229" t="s">
+      <c r="E62" s="234" t="s">
         <v>300</v>
       </c>
     </row>
@@ -12905,10 +12905,10 @@
         <v>263</v>
       </c>
       <c r="C63" s="213">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="D63" s="213"/>
-      <c r="E63" s="230"/>
+      <c r="E63" s="235"/>
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B64" s="138" t="s">
@@ -12916,23 +12916,23 @@
       </c>
       <c r="C64" s="209">
         <f>Valuation_Model!E77</f>
-        <v>0.91559874425582222</v>
+        <v>1.1078681100338603</v>
       </c>
       <c r="D64" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E64" s="230"/>
+      <c r="E64" s="235"/>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B65" s="138" t="s">
         <v>289</v>
       </c>
       <c r="C65" s="214">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D65" s="214"/>
-      <c r="E65" s="230"/>
+      <c r="E65" s="235"/>
     </row>
     <row r="67" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B67" s="208" t="s">
@@ -12948,20 +12948,20 @@
       </c>
       <c r="C68" s="215">
         <f>C59</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D68" s="212"/>
-      <c r="E68" s="229"/>
+      <c r="E68" s="234"/>
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B69" s="162" t="s">
         <v>263</v>
       </c>
       <c r="C69" s="213">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="D69" s="213"/>
-      <c r="E69" s="230"/>
+      <c r="E69" s="235"/>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B70" s="138" t="s">
@@ -12969,23 +12969,23 @@
       </c>
       <c r="C70" s="209">
         <f>Valuation_Model!E73</f>
-        <v>2.0377080275599608</v>
+        <v>5.509958336685604</v>
       </c>
       <c r="D70" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E70" s="230"/>
+      <c r="E70" s="235"/>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B71" s="138" t="s">
         <v>289</v>
       </c>
       <c r="C71" s="214">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D71" s="214"/>
-      <c r="E71" s="230"/>
+      <c r="E71" s="235"/>
     </row>
     <row r="73" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B73" s="138" t="s">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="C73" s="202">
         <f>C64*C65+C70*C71+C55*(1-C65-C71)</f>
-        <v>1.5031893447447282</v>
+        <v>2.2442571711494752</v>
       </c>
       <c r="D73" t="str">
         <f>Market_currency</f>
@@ -13039,7 +13039,7 @@
       <c r="B78" s="138" t="s">
         <v>229</v>
       </c>
-      <c r="C78" s="235">
+      <c r="C78" s="233">
         <f>Normalized_FCF!C94</f>
         <v>0.1178</v>
       </c>
@@ -13073,7 +13073,7 @@
       </c>
       <c r="C82" s="160">
         <f>C73/(1+C77)^F77</f>
-        <v>0.86990124117171774</v>
+        <v>1.2987599370077982</v>
       </c>
       <c r="D82" s="160"/>
     </row>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="C83" s="154">
         <f>C81+C82</f>
-        <v>1.1180447596902363</v>
+        <v>1.5469034555263168</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="F83" s="219">
         <f>(C83/C73-1)</f>
-        <v>-0.25621827775788097</v>
+        <v>-0.31072807723991103</v>
       </c>
       <c r="I83" s="164" t="s">
         <v>242</v>

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA634084-B31E-4ABE-BED2-BD387D2831E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245F0A66-578C-4253-B842-FC739352D178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -1649,10 +1649,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Success Scenario</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Market Price</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1911,6 +1907,10 @@
   </si>
   <si>
     <t>朝云集团</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Snowball Scenario</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3148,20 +3148,20 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3467,10 +3467,10 @@
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="306" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F1" s="307" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -3499,13 +3499,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C5" s="49" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D5" s="50" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -3535,7 +3535,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="49" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D8" s="33"/>
       <c r="E8" s="33"/>
@@ -3555,7 +3555,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B10" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C10" s="300">
         <v>6</v>
@@ -3593,24 +3593,24 @@
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="308" t="s">
+      <c r="B14" s="309" t="s">
         <v>300</v>
       </c>
-      <c r="C14" s="308"/>
-      <c r="D14" s="308"/>
-      <c r="E14" s="308"/>
-      <c r="F14" s="308"/>
+      <c r="C14" s="309"/>
+      <c r="D14" s="309"/>
+      <c r="E14" s="309"/>
+      <c r="F14" s="309"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="46" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C16" s="47"/>
       <c r="D16" s="5"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B17" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C17" s="33" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -3623,7 +3623,7 @@
         <v>61</v>
       </c>
       <c r="C18" s="49" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -3645,7 +3645,7 @@
         <v>1.5453771778827836</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E20" s="302">
         <f>Scenarios!C76</f>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C21" s="301">
         <f ca="1">Scenarios!C87</f>
@@ -3681,22 +3681,22 @@
       <c r="F23" s="37"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="308" t="s">
+      <c r="B25" s="309" t="s">
         <v>244</v>
       </c>
-      <c r="C25" s="308"/>
-      <c r="D25" s="308"/>
-      <c r="E25" s="308"/>
-      <c r="F25" s="308"/>
+      <c r="C25" s="309"/>
+      <c r="D25" s="309"/>
+      <c r="E25" s="309"/>
+      <c r="F25" s="309"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="312" t="s">
+      <c r="B26" s="310" t="s">
         <v>265</v>
       </c>
-      <c r="C26" s="312"/>
-      <c r="D26" s="312"/>
-      <c r="E26" s="312"/>
-      <c r="F26" s="312"/>
+      <c r="C26" s="310"/>
+      <c r="D26" s="310"/>
+      <c r="E26" s="310"/>
+      <c r="F26" s="310"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="249" t="s">
@@ -3708,13 +3708,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="310" t="s">
+      <c r="B29" s="308" t="s">
         <v>246</v>
       </c>
-      <c r="C29" s="310"/>
-      <c r="D29" s="310"/>
-      <c r="E29" s="310"/>
-      <c r="F29" s="310"/>
+      <c r="C29" s="308"/>
+      <c r="D29" s="308"/>
+      <c r="E29" s="308"/>
+      <c r="F29" s="308"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="48" t="s">
@@ -3734,13 +3734,13 @@
       <c r="C31" s="83"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="310" t="s">
+      <c r="B32" s="308" t="s">
         <v>248</v>
       </c>
-      <c r="C32" s="310"/>
-      <c r="D32" s="310"/>
-      <c r="E32" s="310"/>
-      <c r="F32" s="310"/>
+      <c r="C32" s="308"/>
+      <c r="D32" s="308"/>
+      <c r="E32" s="308"/>
+      <c r="F32" s="308"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="48" t="s">
@@ -3769,13 +3769,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="310" t="s">
+      <c r="B36" s="308" t="s">
         <v>251</v>
       </c>
-      <c r="C36" s="310"/>
-      <c r="D36" s="310"/>
-      <c r="E36" s="310"/>
-      <c r="F36" s="310"/>
+      <c r="C36" s="308"/>
+      <c r="D36" s="308"/>
+      <c r="E36" s="308"/>
+      <c r="F36" s="308"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="48" t="s">
@@ -3791,13 +3791,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="310" t="s">
+      <c r="B39" s="308" t="s">
         <v>255</v>
       </c>
-      <c r="C39" s="310"/>
-      <c r="D39" s="310"/>
-      <c r="E39" s="310"/>
-      <c r="F39" s="310"/>
+      <c r="C39" s="308"/>
+      <c r="D39" s="308"/>
+      <c r="E39" s="308"/>
+      <c r="F39" s="308"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="48" t="s">
@@ -3831,13 +3831,13 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B45" s="310" t="s">
+      <c r="B45" s="308" t="s">
         <v>256</v>
       </c>
-      <c r="C45" s="310"/>
-      <c r="D45" s="310"/>
-      <c r="E45" s="310"/>
-      <c r="F45" s="310"/>
+      <c r="C45" s="308"/>
+      <c r="D45" s="308"/>
+      <c r="E45" s="308"/>
+      <c r="F45" s="308"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="48" t="s">
@@ -3853,13 +3853,13 @@
       </c>
     </row>
     <row r="48" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="310" t="s">
+      <c r="B48" s="308" t="s">
         <v>259</v>
       </c>
-      <c r="C48" s="311"/>
-      <c r="D48" s="311"/>
-      <c r="E48" s="311"/>
-      <c r="F48" s="311"/>
+      <c r="C48" s="312"/>
+      <c r="D48" s="312"/>
+      <c r="E48" s="312"/>
+      <c r="F48" s="312"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B49" s="48" t="s">
@@ -3888,13 +3888,13 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="308" t="s">
+      <c r="B52" s="309" t="s">
         <v>281</v>
       </c>
-      <c r="C52" s="308"/>
-      <c r="D52" s="308"/>
-      <c r="E52" s="308"/>
-      <c r="F52" s="308"/>
+      <c r="C52" s="309"/>
+      <c r="D52" s="309"/>
+      <c r="E52" s="309"/>
+      <c r="F52" s="309"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B53" s="48" t="s">
@@ -3933,7 +3933,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="271" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C56" s="101">
         <f>Normalized_FCF!C92</f>
@@ -3942,7 +3942,7 @@
     </row>
     <row r="58" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A58" s="263" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B58" s="37"/>
       <c r="C58" s="37"/>
@@ -3955,22 +3955,22 @@
     </row>
     <row r="60" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="17"/>
-      <c r="B60" s="310" t="s">
-        <v>319</v>
-      </c>
-      <c r="C60" s="310"/>
-      <c r="D60" s="310"/>
-      <c r="E60" s="310"/>
-      <c r="F60" s="310"/>
+      <c r="B60" s="308" t="s">
+        <v>318</v>
+      </c>
+      <c r="C60" s="308"/>
+      <c r="D60" s="308"/>
+      <c r="E60" s="308"/>
+      <c r="F60" s="308"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B61" s="312" t="s">
+      <c r="B61" s="310" t="s">
         <v>272</v>
       </c>
-      <c r="C61" s="312"/>
-      <c r="D61" s="312"/>
-      <c r="E61" s="312"/>
-      <c r="F61" s="312"/>
+      <c r="C61" s="310"/>
+      <c r="D61" s="310"/>
+      <c r="E61" s="310"/>
+      <c r="F61" s="310"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B63" s="249" t="s">
@@ -3979,7 +3979,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B64" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C64" s="282">
         <v>0.08</v>
@@ -3987,26 +3987,26 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B65" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C65" s="282">
         <f>IF(D65="Y",1%,0)</f>
         <v>0.01</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C66" s="282">
         <f>IF(D66="Y",1%,0)</f>
         <v>0.01</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
@@ -4022,22 +4022,22 @@
       <c r="C68" s="133"/>
     </row>
     <row r="69" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="308" t="s">
-        <v>330</v>
-      </c>
-      <c r="C69" s="308"/>
-      <c r="D69" s="308"/>
-      <c r="E69" s="308"/>
-      <c r="F69" s="308"/>
+      <c r="B69" s="309" t="s">
+        <v>329</v>
+      </c>
+      <c r="C69" s="309"/>
+      <c r="D69" s="309"/>
+      <c r="E69" s="309"/>
+      <c r="F69" s="309"/>
     </row>
     <row r="70" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="308" t="s">
+      <c r="B70" s="309" t="s">
         <v>271</v>
       </c>
-      <c r="C70" s="308"/>
-      <c r="D70" s="308"/>
-      <c r="E70" s="308"/>
-      <c r="F70" s="308"/>
+      <c r="C70" s="309"/>
+      <c r="D70" s="309"/>
+      <c r="E70" s="309"/>
+      <c r="F70" s="309"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B71" s="48" t="s">
@@ -4049,7 +4049,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B73" s="48" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C73" s="264">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4074,13 +4074,13 @@
       <c r="A76" s="248"/>
     </row>
     <row r="77" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="308" t="s">
+      <c r="B77" s="309" t="s">
         <v>274</v>
       </c>
-      <c r="C77" s="308"/>
-      <c r="D77" s="308"/>
-      <c r="E77" s="308"/>
-      <c r="F77" s="308"/>
+      <c r="C77" s="309"/>
+      <c r="D77" s="309"/>
+      <c r="E77" s="309"/>
+      <c r="F77" s="309"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
@@ -4107,7 +4107,7 @@
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="48" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C82" s="264">
         <f>C81*C28*Exchange_Rate/Common_Shares</f>
@@ -4151,7 +4151,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="48" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C87" s="264">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="48" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C91" s="264">
         <f>C90*C28*Exchange_Rate/Common_Shares</f>
@@ -4194,17 +4194,17 @@
       </c>
     </row>
     <row r="93" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="308" t="s">
+      <c r="B93" s="309" t="s">
         <v>280</v>
       </c>
-      <c r="C93" s="308"/>
-      <c r="D93" s="308"/>
-      <c r="E93" s="308"/>
-      <c r="F93" s="308"/>
+      <c r="C93" s="309"/>
+      <c r="D93" s="309"/>
+      <c r="E93" s="309"/>
+      <c r="F93" s="309"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="48" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C95" s="264">
         <f>Valuation_Model!C12</f>
@@ -4226,13 +4226,13 @@
       <c r="F97" s="37"/>
     </row>
     <row r="99" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="308" t="s">
+      <c r="B99" s="309" t="s">
         <v>306</v>
       </c>
-      <c r="C99" s="308"/>
-      <c r="D99" s="308"/>
-      <c r="E99" s="308"/>
-      <c r="F99" s="308"/>
+      <c r="C99" s="309"/>
+      <c r="D99" s="309"/>
+      <c r="E99" s="309"/>
+      <c r="F99" s="309"/>
     </row>
     <row r="101" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B101" s="278" t="s">
@@ -4254,7 +4254,7 @@
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B102" s="273" t="str">
         <f>Valuation_Model!B74</f>
-        <v>Success Scenario</v>
+        <v>Snowball Scenario</v>
       </c>
       <c r="C102" s="274">
         <f>Valuation_Model!C74</f>
@@ -4376,7 +4376,7 @@
     </row>
     <row r="110" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A110" s="263" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B110" s="37"/>
       <c r="C110" s="37"/>
@@ -4385,13 +4385,13 @@
       <c r="F110" s="37"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B112" s="309" t="s">
+      <c r="B112" s="311" t="s">
         <v>288</v>
       </c>
-      <c r="C112" s="309"/>
-      <c r="D112" s="309"/>
-      <c r="E112" s="309"/>
-      <c r="F112" s="309"/>
+      <c r="C112" s="311"/>
+      <c r="D112" s="311"/>
+      <c r="E112" s="311"/>
+      <c r="F112" s="311"/>
     </row>
     <row r="113" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B113" s="249" t="s">
@@ -4478,12 +4478,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B93:F93"/>
@@ -4496,6 +4490,12 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -10343,7 +10343,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C92" s="24">
         <f>C89/Market_Price</f>
@@ -13137,7 +13137,7 @@
         <v>148</v>
       </c>
       <c r="D65" s="285" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="66" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -13269,7 +13269,7 @@
     </row>
     <row r="78" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="88" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C78" s="38"/>
       <c r="D78" s="38"/>
@@ -13280,15 +13280,15 @@
     </row>
     <row r="79" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="D79" s="290" t="s">
         <v>337</v>
-      </c>
-      <c r="D79" s="290" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="287" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C80" s="200">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -13305,7 +13305,7 @@
     </row>
     <row r="81" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="287" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C81" s="200">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -13339,7 +13339,7 @@
     </row>
     <row r="83" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B83" s="89" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C83" s="199">
         <f>SUM(C80:C82)</f>
@@ -14722,7 +14722,7 @@
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B74" s="139" t="str">
         <f>Scenarios!B54</f>
-        <v>Success Scenario</v>
+        <v>Snowball Scenario</v>
       </c>
       <c r="C74" s="154">
         <f>Scenarios!C56</f>
@@ -14841,7 +14841,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="168" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C80" s="168" t="s">
         <v>117</v>
@@ -14913,7 +14913,7 @@
       <c r="E2" s="38"/>
       <c r="F2" s="38"/>
       <c r="H2" s="298" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I2" s="299"/>
     </row>
@@ -14967,7 +14967,7 @@
         <v>1000</v>
       </c>
       <c r="E6" s="111" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F6" s="111"/>
       <c r="H6" s="297">
@@ -15146,12 +15146,12 @@
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="172" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="111" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C21" s="173">
         <f>Market_Price</f>
@@ -15164,7 +15164,7 @@
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="111" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C22" s="173">
         <f>Valuation_Model!C12</f>
@@ -15452,7 +15452,7 @@
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="172" t="s">
-        <v>311</v>
+        <v>371</v>
       </c>
       <c r="E54" s="172" t="s">
         <v>161</v>
@@ -15521,7 +15521,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="111" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F60" s="294">
         <v>3</v>
@@ -15529,7 +15529,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="37" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C62" s="38"/>
       <c r="D62" s="38"/>
@@ -15538,10 +15538,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="120" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E63" s="304" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -15553,7 +15553,7 @@
       </c>
       <c r="D64" s="162"/>
       <c r="E64" s="303" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -15565,7 +15565,7 @@
       </c>
       <c r="D65" s="163"/>
       <c r="E65" s="303" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -15581,20 +15581,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="303" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="120" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E68" s="304" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="111" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C69" s="293" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -15604,19 +15604,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="111" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C70" s="293" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="303" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="111" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C71" s="293" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -15626,7 +15626,7 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="111" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C72" s="292" t="str">
         <f>IF(E72&gt;50%,"Y","N")</f>
@@ -15655,7 +15655,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="296" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C76" s="295">
         <f>F60</f>
@@ -15680,12 +15680,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="120" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="160" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C80" s="180">
         <f>Thesis!C115</f>
@@ -15739,12 +15739,12 @@
     </row>
     <row r="85" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="120" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="160" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C86" s="286">
         <f>Market_Price</f>
@@ -15757,7 +15757,7 @@
     </row>
     <row r="87" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="111" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C87" s="284">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245F0A66-578C-4253-B842-FC739352D178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FBA02F2-C2D5-450F-83CC-92E745B8C86A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -24,10 +24,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
     <definedName name="Common_Shares">Thesis!$C$7</definedName>
     <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
-    <definedName name="Exchange_Rate">Thesis!$C$9</definedName>
+    <definedName name="Exchange_Rate">Thesis!$C$17</definedName>
     <definedName name="Market_currency">Thesis!$D$6</definedName>
     <definedName name="Market_Price">Thesis!$C$6</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$8</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$16</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="379">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1913,12 +1913,40 @@
     <t>Snowball Scenario</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>Cash Management Analysis</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monthly Operating Expenses</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Companies typically need cash to cover 1 to 2 months of operating expenses</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Operating Cash Requirement</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1x for stable businesses, 2x for for volatile ones</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Operating Expenses Multiple (months)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Operating Cash Multiple (months)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="16">
+  <numFmts count="17">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="178" formatCode="#,##0.00&quot;x&quot;"/>
@@ -1935,8 +1963,9 @@
     <numFmt numFmtId="189" formatCode="#,##0_);\(#,##0\)"/>
     <numFmt numFmtId="190" formatCode="#,##0.00_);\(#,##0.00\)"/>
     <numFmt numFmtId="191" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="192" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="48" x14ac:knownFonts="1">
+  <fonts count="49" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2299,6 +2328,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -2505,7 +2542,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="316">
+  <cellXfs count="324">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3148,6 +3185,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3172,6 +3212,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="192" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="189" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="192" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3531,90 +3580,90 @@
       <c r="E7" s="35"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B8" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="49" t="s">
-        <v>324</v>
-      </c>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
+      <c r="B8" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C8" s="300">
+        <v>6</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="49"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="51">
-        <v>1.06</v>
-      </c>
-      <c r="D9" s="49" t="str">
-        <f>IF(C8=D6,D6,C8&amp;"/"&amp;D6)</f>
-        <v>CNY/HKD</v>
-      </c>
-      <c r="E9" s="49"/>
+      <c r="B9" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C9" s="34">
+        <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
+        <v>45716</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B10" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C10" s="300">
-        <v>6</v>
-      </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="49"/>
+      <c r="B10" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="36">
+        <f>Thesis!C6*Thesis!C7/1000000</f>
+        <v>3066.66705</v>
+      </c>
+      <c r="D10" s="33" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B11" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="C11" s="34">
-        <f>EOMONTH(EDATE(BS!C1,C10+2),0)</f>
-        <v>45716</v>
-      </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="36">
-        <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>3066.66705</v>
-      </c>
-      <c r="D12" s="33" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E12" s="5"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-    </row>
-    <row r="14" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="309" t="s">
+    <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="310" t="s">
         <v>300</v>
       </c>
-      <c r="C14" s="309"/>
-      <c r="D14" s="309"/>
-      <c r="E14" s="309"/>
-      <c r="F14" s="309"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B16" s="46" t="s">
+      <c r="C12" s="310"/>
+      <c r="D12" s="310"/>
+      <c r="E12" s="310"/>
+      <c r="F12" s="310"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B14" s="46" t="s">
         <v>356</v>
       </c>
-      <c r="C16" s="47"/>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B17" s="2" t="s">
+      <c r="C14" s="47"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B15" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="C17" s="33" t="str">
+      <c r="C15" s="33" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v>Low Growth Asset Play</v>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B16" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="49" t="s">
+        <v>324</v>
+      </c>
+      <c r="D16" s="33"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B17" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="51">
+        <v>1.06</v>
+      </c>
+      <c r="D17" s="33" t="str">
+        <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
+        <v>CNY/HKD</v>
       </c>
       <c r="E17" s="5"/>
     </row>
@@ -3642,7 +3691,7 @@
       </c>
       <c r="C20" s="268">
         <f>C121</f>
-        <v>1.5453771778827836</v>
+        <v>1.7432969171114687</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>359</v>
@@ -3658,7 +3707,7 @@
       </c>
       <c r="C21" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>4.3110984690918341E-2</v>
+        <v>8.8876330035536411E-2</v>
       </c>
       <c r="D21" s="5" t="str">
         <f>Market_currency</f>
@@ -3681,22 +3730,22 @@
       <c r="F23" s="37"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="309" t="s">
+      <c r="B25" s="310" t="s">
         <v>244</v>
       </c>
-      <c r="C25" s="309"/>
-      <c r="D25" s="309"/>
-      <c r="E25" s="309"/>
-      <c r="F25" s="309"/>
+      <c r="C25" s="310"/>
+      <c r="D25" s="310"/>
+      <c r="E25" s="310"/>
+      <c r="F25" s="310"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="310" t="s">
+      <c r="B26" s="311" t="s">
         <v>265</v>
       </c>
-      <c r="C26" s="310"/>
-      <c r="D26" s="310"/>
-      <c r="E26" s="310"/>
-      <c r="F26" s="310"/>
+      <c r="C26" s="311"/>
+      <c r="D26" s="311"/>
+      <c r="E26" s="311"/>
+      <c r="F26" s="311"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="249" t="s">
@@ -3708,13 +3757,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="308" t="s">
+      <c r="B29" s="309" t="s">
         <v>246</v>
       </c>
-      <c r="C29" s="308"/>
-      <c r="D29" s="308"/>
-      <c r="E29" s="308"/>
-      <c r="F29" s="308"/>
+      <c r="C29" s="309"/>
+      <c r="D29" s="309"/>
+      <c r="E29" s="309"/>
+      <c r="F29" s="309"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="48" t="s">
@@ -3734,13 +3783,13 @@
       <c r="C31" s="83"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="308" t="s">
+      <c r="B32" s="309" t="s">
         <v>248</v>
       </c>
-      <c r="C32" s="308"/>
-      <c r="D32" s="308"/>
-      <c r="E32" s="308"/>
-      <c r="F32" s="308"/>
+      <c r="C32" s="309"/>
+      <c r="D32" s="309"/>
+      <c r="E32" s="309"/>
+      <c r="F32" s="309"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="48" t="s">
@@ -3769,13 +3818,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="308" t="s">
+      <c r="B36" s="309" t="s">
         <v>251</v>
       </c>
-      <c r="C36" s="308"/>
-      <c r="D36" s="308"/>
-      <c r="E36" s="308"/>
-      <c r="F36" s="308"/>
+      <c r="C36" s="309"/>
+      <c r="D36" s="309"/>
+      <c r="E36" s="309"/>
+      <c r="F36" s="309"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="48" t="s">
@@ -3791,13 +3840,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="308" t="s">
+      <c r="B39" s="309" t="s">
         <v>255</v>
       </c>
-      <c r="C39" s="308"/>
-      <c r="D39" s="308"/>
-      <c r="E39" s="308"/>
-      <c r="F39" s="308"/>
+      <c r="C39" s="309"/>
+      <c r="D39" s="309"/>
+      <c r="E39" s="309"/>
+      <c r="F39" s="309"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="48" t="s">
@@ -3831,13 +3880,13 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B45" s="308" t="s">
+      <c r="B45" s="309" t="s">
         <v>256</v>
       </c>
-      <c r="C45" s="308"/>
-      <c r="D45" s="308"/>
-      <c r="E45" s="308"/>
-      <c r="F45" s="308"/>
+      <c r="C45" s="309"/>
+      <c r="D45" s="309"/>
+      <c r="E45" s="309"/>
+      <c r="F45" s="309"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="48" t="s">
@@ -3853,13 +3902,13 @@
       </c>
     </row>
     <row r="48" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="308" t="s">
+      <c r="B48" s="309" t="s">
         <v>259</v>
       </c>
-      <c r="C48" s="312"/>
-      <c r="D48" s="312"/>
-      <c r="E48" s="312"/>
-      <c r="F48" s="312"/>
+      <c r="C48" s="313"/>
+      <c r="D48" s="313"/>
+      <c r="E48" s="313"/>
+      <c r="F48" s="313"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B49" s="48" t="s">
@@ -3888,13 +3937,13 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="309" t="s">
+      <c r="B52" s="310" t="s">
         <v>281</v>
       </c>
-      <c r="C52" s="309"/>
-      <c r="D52" s="309"/>
-      <c r="E52" s="309"/>
-      <c r="F52" s="309"/>
+      <c r="C52" s="310"/>
+      <c r="D52" s="310"/>
+      <c r="E52" s="310"/>
+      <c r="F52" s="310"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B53" s="48" t="s">
@@ -3955,22 +4004,22 @@
     </row>
     <row r="60" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="17"/>
-      <c r="B60" s="308" t="s">
+      <c r="B60" s="309" t="s">
         <v>318</v>
       </c>
-      <c r="C60" s="308"/>
-      <c r="D60" s="308"/>
-      <c r="E60" s="308"/>
-      <c r="F60" s="308"/>
+      <c r="C60" s="309"/>
+      <c r="D60" s="309"/>
+      <c r="E60" s="309"/>
+      <c r="F60" s="309"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B61" s="310" t="s">
+      <c r="B61" s="311" t="s">
         <v>272</v>
       </c>
-      <c r="C61" s="310"/>
-      <c r="D61" s="310"/>
-      <c r="E61" s="310"/>
-      <c r="F61" s="310"/>
+      <c r="C61" s="311"/>
+      <c r="D61" s="311"/>
+      <c r="E61" s="311"/>
+      <c r="F61" s="311"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B63" s="249" t="s">
@@ -4022,22 +4071,22 @@
       <c r="C68" s="133"/>
     </row>
     <row r="69" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="309" t="s">
+      <c r="B69" s="310" t="s">
         <v>329</v>
       </c>
-      <c r="C69" s="309"/>
-      <c r="D69" s="309"/>
-      <c r="E69" s="309"/>
-      <c r="F69" s="309"/>
+      <c r="C69" s="310"/>
+      <c r="D69" s="310"/>
+      <c r="E69" s="310"/>
+      <c r="F69" s="310"/>
     </row>
     <row r="70" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="309" t="s">
+      <c r="B70" s="310" t="s">
         <v>271</v>
       </c>
-      <c r="C70" s="309"/>
-      <c r="D70" s="309"/>
-      <c r="E70" s="309"/>
-      <c r="F70" s="309"/>
+      <c r="C70" s="310"/>
+      <c r="D70" s="310"/>
+      <c r="E70" s="310"/>
+      <c r="F70" s="310"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B71" s="48" t="s">
@@ -4074,13 +4123,13 @@
       <c r="A76" s="248"/>
     </row>
     <row r="77" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="309" t="s">
+      <c r="B77" s="310" t="s">
         <v>274</v>
       </c>
-      <c r="C77" s="309"/>
-      <c r="D77" s="309"/>
-      <c r="E77" s="309"/>
-      <c r="F77" s="309"/>
+      <c r="C77" s="310"/>
+      <c r="D77" s="310"/>
+      <c r="E77" s="310"/>
+      <c r="F77" s="310"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
@@ -4142,7 +4191,7 @@
       </c>
       <c r="C86" s="200">
         <f>Valuation_Model!C8</f>
-        <v>1598839.2</v>
+        <v>2029405.1093906919</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4155,7 +4204,7 @@
       </c>
       <c r="C87" s="264">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.2710770051153744</v>
+        <v>1.6133768602934926</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4194,13 +4243,13 @@
       </c>
     </row>
     <row r="93" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="309" t="s">
+      <c r="B93" s="310" t="s">
         <v>280</v>
       </c>
-      <c r="C93" s="309"/>
-      <c r="D93" s="309"/>
-      <c r="E93" s="309"/>
-      <c r="F93" s="309"/>
+      <c r="C93" s="310"/>
+      <c r="D93" s="310"/>
+      <c r="E93" s="310"/>
+      <c r="F93" s="310"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="48" t="s">
@@ -4208,7 +4257,7 @@
       </c>
       <c r="C95" s="264">
         <f>Valuation_Model!C12</f>
-        <v>2.191922234814335</v>
+        <v>2.5342220899924537</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4226,13 +4275,13 @@
       <c r="F97" s="37"/>
     </row>
     <row r="99" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="309" t="s">
+      <c r="B99" s="310" t="s">
         <v>306</v>
       </c>
-      <c r="C99" s="309"/>
-      <c r="D99" s="309"/>
-      <c r="E99" s="309"/>
-      <c r="F99" s="309"/>
+      <c r="C99" s="310"/>
+      <c r="D99" s="310"/>
+      <c r="E99" s="310"/>
+      <c r="F99" s="310"/>
     </row>
     <row r="101" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B101" s="278" t="s">
@@ -4258,15 +4307,15 @@
       </c>
       <c r="C102" s="274">
         <f>Valuation_Model!C74</f>
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="D102" s="275">
         <f>Valuation_Model!D74</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E102" s="276" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>2.75 HKD</v>
+        <v>3.12 HKD</v>
       </c>
       <c r="F102" s="277">
         <f>Valuation_Model!F74</f>
@@ -4280,15 +4329,15 @@
       </c>
       <c r="C103" s="259">
         <f>Valuation_Model!C75</f>
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="D103" s="260">
         <f>Valuation_Model!D75</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E103" s="261" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>2.33 HKD</v>
+        <v>2.71 HKD</v>
       </c>
       <c r="F103" s="262">
         <f>Valuation_Model!F75</f>
@@ -4302,15 +4351,15 @@
       </c>
       <c r="C104" s="259">
         <f>Valuation_Model!C76</f>
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="D104" s="260">
         <f>Valuation_Model!D76</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E104" s="261" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>2.25 HKD</v>
+        <v>2.59 HKD</v>
       </c>
       <c r="F104" s="262">
         <f>Valuation_Model!F76</f>
@@ -4324,15 +4373,15 @@
       </c>
       <c r="C105" s="259">
         <f>Valuation_Model!C77</f>
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="D105" s="260">
         <f>Valuation_Model!D77</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E105" s="261" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>2.13 HKD</v>
+        <v>2.4 HKD</v>
       </c>
       <c r="F105" s="262">
         <f>Valuation_Model!F77</f>
@@ -4346,15 +4395,15 @@
       </c>
       <c r="C106" s="259">
         <f>Valuation_Model!C78</f>
-        <v>-0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="D106" s="260">
         <f>Valuation_Model!D78</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E106" s="261" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>1.92 HKD</v>
+        <v>2.26 HKD</v>
       </c>
       <c r="F106" s="262">
         <f>Valuation_Model!F78</f>
@@ -4367,7 +4416,7 @@
       </c>
       <c r="C108" s="257">
         <f>Scenarios!C60</f>
-        <v>2.2416197633814501</v>
+        <v>2.5836250727686179</v>
       </c>
       <c r="D108" s="252" t="str">
         <f>Market_currency</f>
@@ -4385,13 +4434,13 @@
       <c r="F110" s="37"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B112" s="311" t="s">
+      <c r="B112" s="312" t="s">
         <v>288</v>
       </c>
-      <c r="C112" s="311"/>
-      <c r="D112" s="311"/>
-      <c r="E112" s="311"/>
-      <c r="F112" s="311"/>
+      <c r="C112" s="312"/>
+      <c r="D112" s="312"/>
+      <c r="E112" s="312"/>
+      <c r="F112" s="312"/>
     </row>
     <row r="113" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B113" s="249" t="s">
@@ -4451,7 +4500,7 @@
       </c>
       <c r="C120" s="256">
         <f>Scenarios!C82</f>
-        <v>1.297233659364265</v>
+        <v>1.4951533985929502</v>
       </c>
     </row>
     <row r="121" spans="2:4" x14ac:dyDescent="0.35">
@@ -4460,7 +4509,7 @@
       </c>
       <c r="C121" s="255">
         <f>Scenarios!C83</f>
-        <v>1.5453771778827836</v>
+        <v>1.7432969171114687</v>
       </c>
       <c r="D121" s="48" t="str">
         <f>Reporting_currency</f>
@@ -4473,7 +4522,7 @@
       </c>
       <c r="C122" s="166">
         <f>Scenarios!F83</f>
-        <v>-0.31059798672027894</v>
+        <v>-0.32525158720365399</v>
       </c>
     </row>
   </sheetData>
@@ -4491,7 +4540,7 @@
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B29:F29"/>
@@ -4499,7 +4548,7 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="C8" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
@@ -4530,7 +4579,7 @@
   <sheetData>
     <row r="1" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B1" s="99" t="str">
-        <f>Thesis!C8</f>
+        <f>Thesis!C16</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="115">
@@ -6795,7 +6844,7 @@
     <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3"/>
       <c r="B1" s="99" t="str">
-        <f>Thesis!C8</f>
+        <f>Thesis!C16</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="54" t="s">
@@ -8895,7 +8944,7 @@
         <v>179</v>
       </c>
       <c r="C57" s="206">
-        <f>BS!$C73*C65</f>
+        <f>BS!$C79*C65</f>
         <v>0</v>
       </c>
       <c r="G57" s="206">
@@ -9003,7 +9052,7 @@
         <v>170</v>
       </c>
       <c r="C59" s="206">
-        <f>BS!$C75*C67</f>
+        <f>BS!$C81*C67</f>
         <v>0</v>
       </c>
       <c r="G59" s="206">
@@ -9285,7 +9334,7 @@
         <v>0</v>
       </c>
       <c r="G67" s="24">
-        <f>IFERROR(G59/BS!$C$75,0)</f>
+        <f>IFERROR(G59/BS!$C$81,0)</f>
         <v>0</v>
       </c>
       <c r="H67" s="188"/>
@@ -12178,7 +12227,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:H83"/>
+  <dimension ref="B1:H89"/>
   <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
@@ -12904,11 +12953,11 @@
         <v>204</v>
       </c>
       <c r="G42" s="238">
-        <f>C76</f>
+        <f>C82</f>
         <v>380678</v>
       </c>
       <c r="H42" s="239">
-        <f>D76</f>
+        <f>D82</f>
         <v>227656.8</v>
       </c>
     </row>
@@ -13129,7 +13178,7 @@
       <c r="G64" s="38"/>
       <c r="H64" s="38"/>
     </row>
-    <row r="65" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B65" s="16" t="s">
         <v>200</v>
       </c>
@@ -13140,7 +13189,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="66" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B66" s="116" t="s">
         <v>199</v>
       </c>
@@ -13149,14 +13198,14 @@
         <v>2664732</v>
       </c>
       <c r="D66" s="200">
-        <f>(G4+G15)*60%</f>
-        <v>1598839.2</v>
+        <f>C66+D75</f>
+        <v>2029405.1093906919</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="67" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B67" s="116" t="s">
         <v>189</v>
       </c>
@@ -13166,7 +13215,7 @@
       </c>
       <c r="F67" s="305"/>
     </row>
-    <row r="68" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="116" t="s">
         <v>193</v>
       </c>
@@ -13176,7 +13225,7 @@
       </c>
       <c r="F68" s="305"/>
     </row>
-    <row r="69" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="116" t="s">
         <v>191</v>
       </c>
@@ -13186,7 +13235,7 @@
       </c>
       <c r="F69" s="305"/>
     </row>
-    <row r="70" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="89" t="s">
         <v>200</v>
       </c>
@@ -13196,160 +13245,229 @@
       </c>
       <c r="F70" s="305"/>
     </row>
-    <row r="71" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F71" s="305"/>
     </row>
-    <row r="72" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="16" t="s">
+    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B72" s="317" t="s">
+        <v>372</v>
+      </c>
+      <c r="C72" s="279" t="s">
+        <v>106</v>
+      </c>
+      <c r="D72" s="218" t="s">
+        <v>62</v>
+      </c>
+      <c r="F72" s="305"/>
+    </row>
+    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B73" s="116" t="s">
+        <v>373</v>
+      </c>
+      <c r="C73" s="200">
+        <f>(Normalized_FCF!G25+Normalized_FCF!G35)/12</f>
+        <v>-125869.25</v>
+      </c>
+      <c r="D73" s="200">
+        <f>(Normalized_FCF!C25+Normalized_FCF!C35)/12</f>
+        <v>-127065.37812186161</v>
+      </c>
+      <c r="F73" s="305" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="308" t="s">
+        <v>377</v>
+      </c>
+      <c r="C74" s="318">
+        <f>-$C$66/C73</f>
+        <v>21.170635401418537</v>
+      </c>
+      <c r="D74" s="318">
+        <f>-$C$66/D73</f>
+        <v>20.971345927483078</v>
+      </c>
+      <c r="F74" s="305"/>
+    </row>
+    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B75" s="89" t="s">
+        <v>375</v>
+      </c>
+      <c r="C75" s="319"/>
+      <c r="D75" s="320">
+        <f>MIN(D73*D76,-G5)</f>
+        <v>-635326.89060930803</v>
+      </c>
+      <c r="F75" s="305" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B76" s="321" t="s">
+        <v>378</v>
+      </c>
+      <c r="C76" s="322"/>
+      <c r="D76" s="323">
+        <f>IF(D74&lt;=3,1,IF(D74&gt;10,5,2))</f>
+        <v>5</v>
+      </c>
+      <c r="F76" s="305"/>
+    </row>
+    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F77" s="305"/>
+    </row>
+    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B78" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="C72" s="279" t="s">
+      <c r="C78" s="279" t="s">
         <v>148</v>
       </c>
-      <c r="D72" s="219" t="s">
+      <c r="D78" s="219" t="s">
         <v>37</v>
       </c>
-      <c r="F72" s="305"/>
-    </row>
-    <row r="73" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="116" t="s">
+      <c r="F78" s="305"/>
+    </row>
+    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B79" s="116" t="s">
         <v>190</v>
       </c>
-      <c r="C73" s="21">
+      <c r="C79" s="21">
         <f>G7+G17</f>
         <v>379178</v>
       </c>
-      <c r="D73" s="200">
+      <c r="D79" s="200">
         <f>G7*H7+G17*H17</f>
         <v>227506.8</v>
       </c>
-      <c r="F73" s="305"/>
-    </row>
-    <row r="74" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="116" t="s">
+      <c r="F79" s="305"/>
+    </row>
+    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B80" s="116" t="s">
         <v>194</v>
       </c>
-      <c r="C74" s="21">
+      <c r="C80" s="21">
         <f>G19</f>
         <v>1500</v>
       </c>
-      <c r="D74" s="200">
+      <c r="D80" s="200">
         <f>G19*H19</f>
         <v>150</v>
       </c>
-      <c r="F74" s="305"/>
-    </row>
-    <row r="75" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="116" t="s">
+      <c r="F80" s="305"/>
+    </row>
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B81" s="116" t="s">
         <v>192</v>
       </c>
-      <c r="C75" s="21">
+      <c r="C81" s="21">
         <f>G9+G21</f>
         <v>0</v>
       </c>
-      <c r="D75" s="200">
+      <c r="D81" s="200">
         <f>G9*H9+G21*H21</f>
         <v>0</v>
       </c>
-      <c r="F75" s="305"/>
-    </row>
-    <row r="76" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="89" t="s">
+      <c r="F81" s="305"/>
+    </row>
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B82" s="89" t="s">
         <v>201</v>
       </c>
-      <c r="C76" s="90">
-        <f>SUM(C73:C75)</f>
+      <c r="C82" s="90">
+        <f>SUM(C79:C81)</f>
         <v>380678</v>
       </c>
-      <c r="D76" s="90">
-        <f>SUM(D73:D75)</f>
+      <c r="D82" s="90">
+        <f>SUM(D79:D81)</f>
         <v>227656.8</v>
       </c>
-      <c r="F76" s="305"/>
-    </row>
-    <row r="78" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B78" s="88" t="s">
+      <c r="F82" s="305"/>
+    </row>
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B84" s="88" t="s">
         <v>335</v>
       </c>
-      <c r="C78" s="38"/>
-      <c r="D78" s="38"/>
-      <c r="E78" s="38"/>
-      <c r="F78" s="38"/>
-      <c r="G78" s="38"/>
-      <c r="H78" s="38"/>
-    </row>
-    <row r="79" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B79" s="16" t="s">
+      <c r="C84" s="38"/>
+      <c r="D84" s="38"/>
+      <c r="E84" s="38"/>
+      <c r="F84" s="38"/>
+      <c r="G84" s="38"/>
+      <c r="H84" s="38"/>
+    </row>
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B85" s="16" t="s">
         <v>336</v>
       </c>
-      <c r="D79" s="290" t="s">
+      <c r="D85" s="290" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="80" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="287" t="s">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B86" s="287" t="s">
         <v>333</v>
       </c>
-      <c r="C80" s="200">
+      <c r="C86" s="200">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
         <v>-36038.94</v>
       </c>
-      <c r="D80" s="264">
-        <f>C80*$H$1/Common_Shares</f>
+      <c r="D86" s="264">
+        <f>C86*$H$1/Common_Shares</f>
         <v>-2.7029201621349797E-2</v>
       </c>
-      <c r="E80" s="289" t="str">
+      <c r="E86" s="289" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="81" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B81" s="287" t="s">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B87" s="287" t="s">
         <v>334</v>
       </c>
-      <c r="C81" s="200">
+      <c r="C87" s="200">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>1694769.5520000001</v>
-      </c>
-      <c r="D81" s="264">
-        <f>C81*$H$1/Common_Shares</f>
-        <v>1.2710770051153746</v>
-      </c>
-      <c r="E81" s="289" t="str">
+        <v>2151169.4159541335</v>
+      </c>
+      <c r="D87" s="264">
+        <f>C87*$H$1/Common_Shares</f>
+        <v>1.6133768602934926</v>
+      </c>
+      <c r="E87" s="289" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="82" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B82" s="288" t="s">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B88" s="288" t="s">
         <v>201</v>
       </c>
-      <c r="C82" s="200">
+      <c r="C88" s="200">
         <f>Valuation_Model!C9*Exchange_Rate</f>
         <v>241316.20800000001</v>
       </c>
-      <c r="D82" s="264">
-        <f>C82*$H$1/Common_Shares</f>
+      <c r="D88" s="264">
+        <f>C88*$H$1/Common_Shares</f>
         <v>0.18098713337660832</v>
       </c>
-      <c r="E82" s="289" t="str">
+      <c r="E88" s="289" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="83" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="89" t="s">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B89" s="89" t="s">
         <v>338</v>
       </c>
-      <c r="C83" s="199">
-        <f>SUM(C80:C82)</f>
-        <v>1900046.8200000003</v>
-      </c>
-      <c r="D83" s="291">
-        <f>SUM(D80:D82)</f>
-        <v>1.4250349368706332</v>
-      </c>
-      <c r="E83" s="289" t="str">
+      <c r="C89" s="199">
+        <f>SUM(C86:C88)</f>
+        <v>2356446.6839541337</v>
+      </c>
+      <c r="D89" s="291">
+        <f>SUM(D86:D88)</f>
+        <v>1.767334792048751</v>
+      </c>
+      <c r="E89" s="289" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
@@ -13445,10 +13563,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="313" t="s">
+      <c r="E6" s="314" t="s">
         <v>268</v>
       </c>
-      <c r="F6" s="313"/>
+      <c r="F6" s="314"/>
       <c r="H6" s="132"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -13463,8 +13581,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="313"/>
-      <c r="F7" s="313"/>
+      <c r="E7" s="314"/>
+      <c r="F7" s="314"/>
       <c r="H7" s="132"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -13473,14 +13591,14 @@
       </c>
       <c r="C8" s="216">
         <f>BS!D66</f>
-        <v>1598839.2</v>
+        <v>2029405.1093906919</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="313"/>
-      <c r="F8" s="313"/>
+      <c r="E8" s="314"/>
+      <c r="F8" s="314"/>
       <c r="H8" s="132"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -13495,8 +13613,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="313"/>
-      <c r="F9" s="313"/>
+      <c r="E9" s="314"/>
+      <c r="F9" s="314"/>
       <c r="H9" s="132"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -13505,7 +13623,7 @@
       </c>
       <c r="C10" s="247">
         <f>C6-C7+C8+C9</f>
-        <v>2757135.2312007728</v>
+        <v>3187701.1405914649</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -13522,7 +13640,7 @@
         <v>1.06</v>
       </c>
       <c r="D11" t="str">
-        <f>Thesis!D9</f>
+        <f>Thesis!D17</f>
         <v>CNY/HKD</v>
       </c>
       <c r="H11" s="132"/>
@@ -13533,7 +13651,7 @@
       </c>
       <c r="C12" s="123">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>2.191922234814335</v>
+        <v>2.5342220899924537</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -13586,7 +13704,7 @@
       </c>
       <c r="C18" s="152">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>2.2399508804161896</v>
+        <v>2.5822507355943083</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14329,23 +14447,23 @@
       </c>
       <c r="B55" s="143">
         <f>C78</f>
-        <v>-0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="C55" s="143">
         <f>C77</f>
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="D55" s="143">
         <f>C76</f>
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E55" s="143">
         <f>C75</f>
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="F55" s="143">
         <f>C74</f>
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="H55" s="132"/>
     </row>
@@ -14355,19 +14473,19 @@
       </c>
       <c r="B56" s="135">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>746737.1179868232</v>
+        <v>813998.0738684833</v>
       </c>
       <c r="C56" s="135">
-        <v>886424.49913926551</v>
+        <v>871496.87095878203</v>
       </c>
       <c r="D56" s="135">
-        <v>1031827.4488650651</v>
+        <v>997693.41744385497</v>
       </c>
       <c r="E56" s="135">
+        <v>1067087.3379442464</v>
+      </c>
+      <c r="F56" s="135">
         <v>1141180.0070700764</v>
-      </c>
-      <c r="F56" s="135">
-        <v>1241023.5057988083</v>
       </c>
       <c r="H56" s="132"/>
     </row>
@@ -14376,19 +14494,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="135">
-        <v>619205.68915954977</v>
+        <v>710451.4036227921</v>
       </c>
       <c r="C57" s="135">
-        <v>823223.63554253592</v>
+        <v>798634.3801902358</v>
       </c>
       <c r="D57" s="135">
-        <v>1104595.7140257917</v>
+        <v>1031232.8795580668</v>
       </c>
       <c r="E57" s="135">
+        <v>1185526.119672385</v>
+      </c>
+      <c r="F57" s="135">
         <v>1373739.0076440671</v>
-      </c>
-      <c r="F57" s="135">
-        <v>1669568.2116978904</v>
       </c>
       <c r="H57" s="132"/>
     </row>
@@ -14397,19 +14515,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="135">
-        <v>517406.08920374722</v>
+        <v>620525.66080121871</v>
       </c>
       <c r="C58" s="135">
-        <v>762559.92712337279</v>
+        <v>730167.05966451776</v>
       </c>
       <c r="D58" s="135">
-        <v>1191334.3570014765</v>
+        <v>1069192.8718720812</v>
       </c>
       <c r="E58" s="135">
+        <v>1334485.9141775905</v>
+      </c>
+      <c r="F58" s="135">
         <v>1700976.7421748578</v>
-      </c>
-      <c r="F58" s="135">
-        <v>2368747.2478235997</v>
       </c>
       <c r="H58" s="132"/>
     </row>
@@ -14418,19 +14536,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="135">
-        <v>447966.63338024286</v>
+        <v>555291.14965979522</v>
       </c>
       <c r="C59" s="135">
-        <v>714600.69247380772</v>
+        <v>677070.48216505372</v>
       </c>
       <c r="D59" s="135">
-        <v>1276584.9853845071</v>
+        <v>1104509.6367370933</v>
       </c>
       <c r="E59" s="135">
+        <v>1489646.0395210038</v>
+      </c>
+      <c r="F59" s="135">
         <v>2087002.5214596698</v>
-      </c>
-      <c r="F59" s="135">
-        <v>3343761.7843977446</v>
       </c>
       <c r="H59" s="132"/>
     </row>
@@ -14439,19 +14557,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="135">
-        <v>403133.81548150722</v>
+        <v>511340.00438654691</v>
       </c>
       <c r="C60" s="135">
-        <v>679876.99142326158</v>
+        <v>639278.70176446578</v>
       </c>
       <c r="D60" s="135">
-        <v>1353234.4413870566</v>
+        <v>1134491.4165757273</v>
       </c>
       <c r="E60" s="135">
+        <v>1638061.0106374505</v>
+      </c>
+      <c r="F60" s="135">
         <v>2509531.051273209</v>
-      </c>
-      <c r="F60" s="135">
-        <v>4624670.3995234473</v>
       </c>
       <c r="H60" s="132"/>
     </row>
@@ -14460,19 +14578,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="135">
-        <v>374823.28997660452</v>
+        <v>482786.4623653267</v>
       </c>
       <c r="C61" s="135">
-        <v>655940.54582671018</v>
+        <v>613615.16213570454</v>
       </c>
       <c r="D61" s="135">
-        <v>1418743.5136284102</v>
+        <v>1158628.3509282607</v>
       </c>
       <c r="E61" s="135">
+        <v>1773483.978985162</v>
+      </c>
+      <c r="F61" s="135">
         <v>2954724.9172403435</v>
-      </c>
-      <c r="F61" s="135">
-        <v>6263643.7732896013</v>
       </c>
       <c r="H61" s="132"/>
     </row>
@@ -14496,23 +14614,23 @@
     <row r="64" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B64" s="144">
         <f>B55</f>
-        <v>-0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="C64" s="144">
         <f>C55</f>
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="D64" s="144">
         <f>D55</f>
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E64" s="144">
         <f>E55</f>
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="F64" s="144">
         <f>F55</f>
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="H64" s="132"/>
     </row>
@@ -14522,23 +14640,23 @@
       </c>
       <c r="B65" s="136">
         <f>C12</f>
-        <v>2.191922234814335</v>
+        <v>2.5342220899924537</v>
       </c>
       <c r="C65" s="136">
         <f>C12</f>
-        <v>2.191922234814335</v>
+        <v>2.5342220899924537</v>
       </c>
       <c r="D65" s="136">
         <f>C12</f>
-        <v>2.191922234814335</v>
+        <v>2.5342220899924537</v>
       </c>
       <c r="E65" s="153">
         <f>C12</f>
-        <v>2.191922234814335</v>
+        <v>2.5342220899924537</v>
       </c>
       <c r="F65" s="136">
         <f>C12</f>
-        <v>2.191922234814335</v>
+        <v>2.5342220899924537</v>
       </c>
       <c r="H65" s="132"/>
     </row>
@@ -14549,23 +14667,23 @@
       </c>
       <c r="B66" s="136">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.0186908714631655</v>
+        <v>2.4144631798831471</v>
       </c>
       <c r="C66" s="136">
         <f t="shared" si="4"/>
-        <v>2.1297423255979249</v>
+        <v>2.4601747178559918</v>
       </c>
       <c r="D66" s="136">
         <f t="shared" si="4"/>
-        <v>2.2453376561805194</v>
+        <v>2.5605009597708444</v>
       </c>
       <c r="E66" s="136">
         <f t="shared" si="4"/>
-        <v>2.3322729290865944</v>
+        <v>2.6156691196726358</v>
       </c>
       <c r="F66" s="136">
         <f t="shared" si="4"/>
-        <v>2.4116485006539903</v>
+        <v>2.6745727842647127</v>
       </c>
       <c r="H66" s="132"/>
     </row>
@@ -14576,23 +14694,23 @@
       </c>
       <c r="B67" s="136">
         <f t="shared" si="4"/>
-        <v>1.9173033982189176</v>
+        <v>2.3321435873277712</v>
       </c>
       <c r="C67" s="136">
         <f t="shared" si="4"/>
-        <v>2.0794976453191101</v>
+        <v>2.4022490449357066</v>
       </c>
       <c r="D67" s="136">
         <f t="shared" si="4"/>
-        <v>2.3031884197519523</v>
+        <v>2.5871648288186599</v>
       </c>
       <c r="E67" s="136">
         <f t="shared" si="4"/>
-        <v>2.5171573114323689</v>
+        <v>2.7098279393766536</v>
       </c>
       <c r="F67" s="136">
         <f t="shared" si="4"/>
-        <v>2.7523414992571356</v>
+        <v>2.8594571666104871</v>
       </c>
       <c r="H67" s="132"/>
     </row>
@@ -14603,23 +14721,23 @@
       </c>
       <c r="B68" s="136">
         <f t="shared" si="4"/>
-        <v>1.8363727263703882</v>
+        <v>2.2606526307209904</v>
       </c>
       <c r="C68" s="136">
         <f t="shared" si="4"/>
-        <v>2.0312700031543307</v>
+        <v>2.3478175319216996</v>
       </c>
       <c r="D68" s="136">
         <f t="shared" si="4"/>
-        <v>2.3721456322979693</v>
+        <v>2.6173430189360278</v>
       </c>
       <c r="E68" s="136">
         <f t="shared" si="4"/>
-        <v>2.7773112778651017</v>
+        <v>2.8282509612054145</v>
       </c>
       <c r="F68" s="136">
         <f t="shared" si="4"/>
-        <v>3.3081887634961666</v>
+        <v>3.1196111330432204</v>
       </c>
       <c r="H68" s="132"/>
     </row>
@@ -14630,23 +14748,23 @@
       </c>
       <c r="B69" s="136">
         <f t="shared" si="4"/>
-        <v>1.7811683658912472</v>
+        <v>2.2087912008462367</v>
       </c>
       <c r="C69" s="136">
         <f t="shared" si="4"/>
-        <v>1.9931424163738749</v>
+        <v>2.3056057580860974</v>
       </c>
       <c r="D69" s="136">
         <f t="shared" si="4"/>
-        <v>2.439919873390699</v>
+        <v>2.6454198434941092</v>
       </c>
       <c r="E69" s="136">
         <f t="shared" si="4"/>
-        <v>3.0842017340352208</v>
+        <v>2.9516032454343923</v>
       </c>
       <c r="F69" s="136">
         <f t="shared" si="4"/>
-        <v>4.0833252231805535</v>
+        <v>3.426501589213339</v>
       </c>
       <c r="H69" s="132"/>
     </row>
@@ -14657,23 +14775,23 @@
       </c>
       <c r="B70" s="136">
         <f t="shared" si="4"/>
-        <v>1.7455262801170135</v>
+        <v>2.1738500447216489</v>
       </c>
       <c r="C70" s="136">
         <f t="shared" si="4"/>
-        <v>1.9655370774893581</v>
+        <v>2.2755612964231884</v>
       </c>
       <c r="D70" s="136">
         <f t="shared" si="4"/>
-        <v>2.5008561832956868</v>
+        <v>2.6692553554863836</v>
       </c>
       <c r="E70" s="136">
         <f t="shared" si="4"/>
-        <v>3.4201118732482176</v>
+        <v>3.0695931327232318</v>
       </c>
       <c r="F70" s="136">
         <f t="shared" si="4"/>
-        <v>5.1016474449152103</v>
+        <v>3.7624117284263354</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -14683,23 +14801,23 @@
       </c>
       <c r="B71" s="136">
         <f t="shared" si="4"/>
-        <v>1.7230194151539735</v>
+        <v>2.1511499816522868</v>
       </c>
       <c r="C71" s="136">
         <f t="shared" si="4"/>
-        <v>1.9465076056187838</v>
+        <v>2.2551587849686365</v>
       </c>
       <c r="D71" s="136">
         <f t="shared" si="4"/>
-        <v>2.5529358892176002</v>
+        <v>2.6884442158980408</v>
       </c>
       <c r="E71" s="136">
         <f t="shared" si="4"/>
-        <v>3.7740409524509539</v>
+        <v>3.1772543791020067</v>
       </c>
       <c r="F71" s="136">
         <f t="shared" si="4"/>
-        <v>6.4046311141863441</v>
+        <v>4.1163408076290713</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -14726,15 +14844,15 @@
       </c>
       <c r="C74" s="154">
         <f>Scenarios!C56</f>
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="D74" s="157">
         <f>Scenarios!C55</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E74" s="147">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>2.7523414992571356</v>
+        <v>3.1196111330432204</v>
       </c>
       <c r="F74" s="154">
         <f>Scenarios!C58</f>
@@ -14748,15 +14866,15 @@
       </c>
       <c r="C75" s="154">
         <f>Scenarios!C38</f>
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="D75" s="157">
         <f>Scenarios!C37</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E75" s="147">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>2.3322729290865944</v>
+        <v>2.7098279393766536</v>
       </c>
       <c r="F75" s="154">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -14771,15 +14889,15 @@
       </c>
       <c r="C76" s="154">
         <f>Scenarios!C26</f>
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="D76" s="157">
         <f>Scenarios!C25</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E76" s="147">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>2.2453376561805194</v>
+        <v>2.5871648288186599</v>
       </c>
       <c r="F76" s="154">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -14794,15 +14912,15 @@
       </c>
       <c r="C77" s="154">
         <f>Scenarios!C32</f>
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="D77" s="157">
         <f>Scenarios!C31</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E77" s="147">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>2.1297423255979249</v>
+        <v>2.4022490449357066</v>
       </c>
       <c r="F77" s="154">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -14817,15 +14935,15 @@
       </c>
       <c r="C78" s="154">
         <f>Scenarios!C50</f>
-        <v>-0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="D78" s="157">
         <f>Scenarios!C49</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E78" s="147">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>1.9173033982189176</v>
+        <v>2.2606526307209904</v>
       </c>
       <c r="F78" s="154">
         <f>Scenarios!C52</f>
@@ -14975,7 +15093,7 @@
       </c>
       <c r="I6" s="283">
         <f t="shared" si="0"/>
-        <v>2.35941976338145</v>
+        <v>2.7014250727686178</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -14990,11 +15108,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="315" t="str">
+      <c r="E7" s="316" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
-        <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 朝云集团(6601.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
-      </c>
-      <c r="F7" s="315"/>
+        <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 朝云集团(6601.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
+      </c>
+      <c r="F7" s="316"/>
       <c r="H7" s="297">
         <v>4</v>
       </c>
@@ -15015,8 +15133,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="315"/>
-      <c r="F8" s="315"/>
+      <c r="E8" s="316"/>
+      <c r="F8" s="316"/>
       <c r="H8" s="297">
         <v>5</v>
       </c>
@@ -15037,8 +15155,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="315"/>
-      <c r="F9" s="315"/>
+      <c r="E9" s="316"/>
+      <c r="F9" s="316"/>
       <c r="H9" s="297">
         <v>6</v>
       </c>
@@ -15048,8 +15166,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="315"/>
-      <c r="F10" s="315"/>
+      <c r="E10" s="316"/>
+      <c r="F10" s="316"/>
       <c r="H10" s="297">
         <v>7</v>
       </c>
@@ -15062,8 +15180,8 @@
       <c r="B11" s="172" t="s">
         <v>310</v>
       </c>
-      <c r="E11" s="315"/>
-      <c r="F11" s="315"/>
+      <c r="E11" s="316"/>
+      <c r="F11" s="316"/>
       <c r="H11" s="297">
         <v>8</v>
       </c>
@@ -15081,8 +15199,8 @@
         <v>-1.7248638436905273E-2</v>
       </c>
       <c r="D12" s="171"/>
-      <c r="E12" s="315"/>
-      <c r="F12" s="315"/>
+      <c r="E12" s="316"/>
+      <c r="F12" s="316"/>
       <c r="H12" s="297">
         <v>9</v>
       </c>
@@ -15099,8 +15217,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.283580450424601</v>
       </c>
-      <c r="E13" s="315"/>
-      <c r="F13" s="315"/>
+      <c r="E13" s="316"/>
+      <c r="F13" s="316"/>
       <c r="H13" s="297">
         <v>10</v>
       </c>
@@ -15117,8 +15235,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.18767799077696001</v>
       </c>
-      <c r="E14" s="315"/>
-      <c r="F14" s="315"/>
+      <c r="E14" s="316"/>
+      <c r="F14" s="316"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="37" t="s">
@@ -15139,7 +15257,7 @@
         <v>145</v>
       </c>
       <c r="C18" s="162">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E18" s="111"/>
       <c r="F18" s="111"/>
@@ -15168,7 +15286,7 @@
       </c>
       <c r="C22" s="173">
         <f>Valuation_Model!C12</f>
-        <v>2.191922234814335</v>
+        <v>2.5342220899924537</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -15190,22 +15308,22 @@
       </c>
       <c r="C25" s="179">
         <f>C18</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D25" s="176"/>
-      <c r="E25" s="314"/>
-      <c r="F25" s="314"/>
+      <c r="E25" s="315"/>
+      <c r="F25" s="315"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="130" t="s">
         <v>146</v>
       </c>
       <c r="C26" s="177">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="D26" s="177"/>
-      <c r="E26" s="314"/>
-      <c r="F26" s="314"/>
+      <c r="E26" s="315"/>
+      <c r="F26" s="315"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="111" t="s">
@@ -15213,14 +15331,14 @@
       </c>
       <c r="C27" s="173">
         <f>Valuation_Model!E76</f>
-        <v>2.2453376561805194</v>
+        <v>2.5871648288186599</v>
       </c>
       <c r="D27" s="173" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="314"/>
-      <c r="F27" s="314"/>
+      <c r="E27" s="315"/>
+      <c r="F27" s="315"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="111" t="s">
@@ -15230,8 +15348,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="178"/>
-      <c r="E28" s="314"/>
-      <c r="F28" s="314"/>
+      <c r="E28" s="315"/>
+      <c r="F28" s="315"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="172" t="s">
@@ -15248,22 +15366,22 @@
       </c>
       <c r="C31" s="179">
         <f>C18</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D31" s="176"/>
-      <c r="E31" s="314"/>
-      <c r="F31" s="314"/>
+      <c r="E31" s="315"/>
+      <c r="F31" s="315"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="130" t="s">
         <v>146</v>
       </c>
       <c r="C32" s="177">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="D32" s="177"/>
-      <c r="E32" s="314"/>
-      <c r="F32" s="314"/>
+      <c r="E32" s="315"/>
+      <c r="F32" s="315"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="111" t="s">
@@ -15271,14 +15389,14 @@
       </c>
       <c r="C33" s="173">
         <f>Valuation_Model!E77</f>
-        <v>2.1297423255979249</v>
+        <v>2.4022490449357066</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="314"/>
-      <c r="F33" s="314"/>
+      <c r="E33" s="315"/>
+      <c r="F33" s="315"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="111" t="s">
@@ -15288,8 +15406,8 @@
         <v>0.15</v>
       </c>
       <c r="D34" s="178"/>
-      <c r="E34" s="314"/>
-      <c r="F34" s="314"/>
+      <c r="E34" s="315"/>
+      <c r="F34" s="315"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="172" t="s">
@@ -15306,22 +15424,22 @@
       </c>
       <c r="C37" s="179">
         <f>C18</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D37" s="176"/>
-      <c r="E37" s="314"/>
-      <c r="F37" s="314"/>
+      <c r="E37" s="315"/>
+      <c r="F37" s="315"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="130" t="s">
         <v>146</v>
       </c>
       <c r="C38" s="177">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="D38" s="177"/>
-      <c r="E38" s="314"/>
-      <c r="F38" s="314"/>
+      <c r="E38" s="315"/>
+      <c r="F38" s="315"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="111" t="s">
@@ -15329,14 +15447,14 @@
       </c>
       <c r="C39" s="173">
         <f>Valuation_Model!E75</f>
-        <v>2.3322729290865944</v>
+        <v>2.7098279393766536</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="314"/>
-      <c r="F39" s="314"/>
+      <c r="E39" s="315"/>
+      <c r="F39" s="315"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="111" t="s">
@@ -15347,8 +15465,8 @@
         <v>0.25</v>
       </c>
       <c r="D40" s="178"/>
-      <c r="E40" s="314"/>
-      <c r="F40" s="314"/>
+      <c r="E40" s="315"/>
+      <c r="F40" s="315"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="111" t="s">
@@ -15356,7 +15474,7 @@
       </c>
       <c r="C42" s="167">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>2.2497321748196488</v>
+        <v>2.5900932388757152</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -15382,7 +15500,7 @@
         <v>145</v>
       </c>
       <c r="C46" s="162">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E46" s="111"/>
       <c r="F46" s="111"/>
@@ -15407,22 +15525,22 @@
       </c>
       <c r="C49" s="179">
         <f>C46</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D49" s="176"/>
-      <c r="E49" s="314"/>
-      <c r="F49" s="314"/>
+      <c r="E49" s="315"/>
+      <c r="F49" s="315"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="130" t="s">
         <v>146</v>
       </c>
       <c r="C50" s="177">
-        <v>-0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="D50" s="177"/>
-      <c r="E50" s="314"/>
-      <c r="F50" s="314"/>
+      <c r="E50" s="315"/>
+      <c r="F50" s="315"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="111" t="s">
@@ -15430,14 +15548,14 @@
       </c>
       <c r="C51" s="173">
         <f>Valuation_Model!E78</f>
-        <v>1.9173033982189176</v>
+        <v>2.2606526307209904</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="314"/>
-      <c r="F51" s="314"/>
+      <c r="E51" s="315"/>
+      <c r="F51" s="315"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="111" t="s">
@@ -15447,8 +15565,8 @@
         <v>0.1</v>
       </c>
       <c r="D52" s="178"/>
-      <c r="E52" s="314"/>
-      <c r="F52" s="314"/>
+      <c r="E52" s="315"/>
+      <c r="F52" s="315"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="172" t="s">
@@ -15465,22 +15583,22 @@
       </c>
       <c r="C55" s="179">
         <f>C46</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D55" s="176"/>
-      <c r="E55" s="314"/>
-      <c r="F55" s="314"/>
+      <c r="E55" s="315"/>
+      <c r="F55" s="315"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="130" t="s">
         <v>146</v>
       </c>
       <c r="C56" s="177">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="D56" s="177"/>
-      <c r="E56" s="314"/>
-      <c r="F56" s="314"/>
+      <c r="E56" s="315"/>
+      <c r="F56" s="315"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="111" t="s">
@@ -15488,14 +15606,14 @@
       </c>
       <c r="C57" s="173">
         <f>Valuation_Model!E74</f>
-        <v>2.7523414992571356</v>
+        <v>3.1196111330432204</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="314"/>
-      <c r="F57" s="314"/>
+      <c r="E57" s="315"/>
+      <c r="F57" s="315"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="111" t="s">
@@ -15505,8 +15623,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="178"/>
-      <c r="E58" s="314"/>
-      <c r="F58" s="314"/>
+      <c r="E58" s="315"/>
+      <c r="F58" s="315"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="111" t="s">
@@ -15514,7 +15632,7 @@
       </c>
       <c r="C60" s="167">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>2.2416197633814501</v>
+        <v>2.5836250727686179</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -15574,7 +15692,7 @@
       </c>
       <c r="C66" s="173">
         <f>Valuation_Model!C18</f>
-        <v>2.2399508804161896</v>
+        <v>2.5822507355943083</v>
       </c>
       <c r="D66" s="173" t="str">
         <f>Market_currency</f>
@@ -15633,8 +15751,8 @@
         <v>Y</v>
       </c>
       <c r="E72" s="146" t="str">
-        <f>"Non-FCF Value is "&amp;ROUND(BS!D83/C60*100,0)&amp;"% of Expected Equity Value"</f>
-        <v>Non-FCF Value is 64% of Expected Equity Value</v>
+        <f>"Non-FCF Value is "&amp;ROUND(BS!D89/C60*100,0)&amp;"% of Expected Equity Value"</f>
+        <v>Non-FCF Value is 68% of Expected Equity Value</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -15710,7 +15828,7 @@
       </c>
       <c r="C82" s="128">
         <f>C60/(1+C80)^C76</f>
-        <v>1.297233659364265</v>
+        <v>1.4951533985929502</v>
       </c>
       <c r="D82" s="128"/>
     </row>
@@ -15720,7 +15838,7 @@
       </c>
       <c r="C83" s="123">
         <f>C81+C82</f>
-        <v>1.5453771778827836</v>
+        <v>1.7432969171114687</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -15731,7 +15849,7 @@
       </c>
       <c r="F83" s="281">
         <f>(C83/C60-1)</f>
-        <v>-0.31059798672027894</v>
+        <v>-0.32525158720365399</v>
       </c>
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.35">
@@ -15761,7 +15879,7 @@
       </c>
       <c r="C87" s="284">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>4.3110984690918341E-2</v>
+        <v>8.8876330035536411E-2</v>
       </c>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D58EB9EB-B521-46E7-8312-01E369646102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{384287BB-2682-4CBD-A99A-5604F52C7862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="386">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -118,10 +118,6 @@
   </si>
   <si>
     <t>Total Liabilities</t>
-  </si>
-  <si>
-    <t>Capitalization:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>ST AR</t>
@@ -1532,10 +1528,6 @@
   </si>
   <si>
     <t>Update Required After:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target Buy Price:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3328,20 +3320,20 @@
     <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="5"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3647,22 +3639,22 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C1" s="44">
         <v>45730</v>
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="293" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F1" s="294" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A2" s="254" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -3686,24 +3678,24 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" s="50">
         <v>2.2999999999999998</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -3719,7 +3711,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C8" s="287">
         <v>6</v>
@@ -3729,7 +3721,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -3739,17 +3731,15 @@
       <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B10" s="4" t="s">
-        <v>25</v>
+      <c r="B10" s="4" t="str">
+        <f>"Capitalization ("&amp;Market_currency&amp;"):"</f>
+        <v>Capitalization (HKD):</v>
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
         <v>3066.66705</v>
       </c>
-      <c r="D10" s="32" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
+      <c r="D10" s="32"/>
       <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
@@ -3757,24 +3747,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="330" t="s">
-        <v>292</v>
-      </c>
-      <c r="C12" s="330"/>
-      <c r="D12" s="330"/>
-      <c r="E12" s="330"/>
-      <c r="F12" s="330"/>
+      <c r="B12" s="329" t="s">
+        <v>290</v>
+      </c>
+      <c r="C12" s="329"/>
+      <c r="D12" s="329"/>
+      <c r="E12" s="329"/>
+      <c r="F12" s="329"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -3787,7 +3777,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -3807,16 +3797,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B18" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C19" s="256">
         <v>0.2</v>
@@ -3824,15 +3814,16 @@
       <c r="E19" s="5"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B20" s="2" t="s">
-        <v>288</v>
+      <c r="B20" s="2" t="str">
+        <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
+        <v>Target Buy Price (HKD):</v>
       </c>
       <c r="C20" s="259">
         <f>C123</f>
         <v>1.7432969171114687</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E20" s="289">
         <f>Scenarios!C76</f>
@@ -3841,16 +3832,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C21" s="288">
         <f ca="1">Scenarios!C87</f>
         <v>8.8876330035536411E-2</v>
       </c>
-      <c r="D21" s="5" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
+      <c r="D21" s="5"/>
       <c r="E21" s="5"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -3859,7 +3847,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="254" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -3868,26 +3856,26 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="330" t="s">
-        <v>237</v>
-      </c>
-      <c r="C25" s="330"/>
-      <c r="D25" s="330"/>
-      <c r="E25" s="330"/>
-      <c r="F25" s="330"/>
+      <c r="B25" s="329" t="s">
+        <v>236</v>
+      </c>
+      <c r="C25" s="329"/>
+      <c r="D25" s="329"/>
+      <c r="E25" s="329"/>
+      <c r="F25" s="329"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="331" t="s">
-        <v>257</v>
-      </c>
-      <c r="C26" s="331"/>
-      <c r="D26" s="331"/>
-      <c r="E26" s="331"/>
-      <c r="F26" s="331"/>
+      <c r="B26" s="333" t="s">
+        <v>256</v>
+      </c>
+      <c r="C26" s="333"/>
+      <c r="D26" s="333"/>
+      <c r="E26" s="333"/>
+      <c r="F26" s="333"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="241" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C28" s="111">
         <f>Data!C3</f>
@@ -3895,17 +3883,17 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="329" t="s">
-        <v>239</v>
-      </c>
-      <c r="C29" s="329"/>
-      <c r="D29" s="329"/>
-      <c r="E29" s="329"/>
-      <c r="F29" s="329"/>
+      <c r="B29" s="331" t="s">
+        <v>238</v>
+      </c>
+      <c r="C29" s="331"/>
+      <c r="D29" s="331"/>
+      <c r="E29" s="331"/>
+      <c r="F29" s="331"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C30" s="192">
         <f>Normalized_FCF!C8</f>
@@ -3921,17 +3909,17 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="329" t="s">
-        <v>241</v>
-      </c>
-      <c r="C32" s="329"/>
-      <c r="D32" s="329"/>
-      <c r="E32" s="329"/>
-      <c r="F32" s="329"/>
+      <c r="B32" s="331" t="s">
+        <v>240</v>
+      </c>
+      <c r="C32" s="331"/>
+      <c r="D32" s="331"/>
+      <c r="E32" s="331"/>
+      <c r="F32" s="331"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C33" s="192">
         <f>Normalized_FCF!C9</f>
@@ -3944,7 +3932,7 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="52" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C34" s="192">
         <f>Normalized_FCF!C10</f>
@@ -3956,17 +3944,17 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="329" t="s">
-        <v>244</v>
-      </c>
-      <c r="C36" s="329"/>
-      <c r="D36" s="329"/>
-      <c r="E36" s="329"/>
-      <c r="F36" s="329"/>
+      <c r="B36" s="331" t="s">
+        <v>243</v>
+      </c>
+      <c r="C36" s="331"/>
+      <c r="D36" s="331"/>
+      <c r="E36" s="331"/>
+      <c r="F36" s="331"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C37" s="192">
         <f>Normalized_FCF!C11</f>
@@ -3978,17 +3966,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="329" t="s">
-        <v>248</v>
-      </c>
-      <c r="C39" s="329"/>
-      <c r="D39" s="329"/>
-      <c r="E39" s="329"/>
-      <c r="F39" s="329"/>
+      <c r="B39" s="331" t="s">
+        <v>247</v>
+      </c>
+      <c r="C39" s="331"/>
+      <c r="D39" s="331"/>
+      <c r="E39" s="331"/>
+      <c r="F39" s="331"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C40" s="192">
         <f>Normalized_FCF!C12</f>
@@ -4001,12 +3989,12 @@
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B42" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B43" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C43" s="192">
         <f>Normalized_FCF!C15</f>
@@ -4018,17 +4006,17 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B45" s="329" t="s">
-        <v>249</v>
-      </c>
-      <c r="C45" s="329"/>
-      <c r="D45" s="329"/>
-      <c r="E45" s="329"/>
-      <c r="F45" s="329"/>
+      <c r="B45" s="331" t="s">
+        <v>248</v>
+      </c>
+      <c r="C45" s="331"/>
+      <c r="D45" s="331"/>
+      <c r="E45" s="331"/>
+      <c r="F45" s="331"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="47" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C46" s="192">
         <f>Normalized_FCF!C14</f>
@@ -4040,17 +4028,17 @@
       </c>
     </row>
     <row r="48" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="329" t="s">
-        <v>252</v>
-      </c>
-      <c r="C48" s="333"/>
-      <c r="D48" s="333"/>
-      <c r="E48" s="333"/>
-      <c r="F48" s="333"/>
+      <c r="B48" s="331" t="s">
+        <v>251</v>
+      </c>
+      <c r="C48" s="332"/>
+      <c r="D48" s="332"/>
+      <c r="E48" s="332"/>
+      <c r="F48" s="332"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B49" s="47" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C49" s="1">
         <f>Normalized_FCF!C17</f>
@@ -4063,7 +4051,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B50" s="47" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C50" s="1">
         <f>Normalized_FCF!C18</f>
@@ -4075,17 +4063,17 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="330" t="s">
-        <v>273</v>
-      </c>
-      <c r="C52" s="330"/>
-      <c r="D52" s="330"/>
-      <c r="E52" s="330"/>
-      <c r="F52" s="330"/>
+      <c r="B52" s="329" t="s">
+        <v>272</v>
+      </c>
+      <c r="C52" s="329"/>
+      <c r="D52" s="329"/>
+      <c r="E52" s="329"/>
+      <c r="F52" s="329"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B53" s="47" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C53" s="192">
         <f>Normalized_FCF!G19</f>
@@ -4098,7 +4086,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B54" s="47" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C54" s="192">
         <f>Normalized_FCF!C19</f>
@@ -4111,7 +4099,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B55" s="261" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C120</f>
@@ -4120,7 +4108,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="261" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C56" s="94">
         <f>Normalized_FCF!C92</f>
@@ -4129,7 +4117,7 @@
     </row>
     <row r="58" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A58" s="254" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B58" s="36"/>
       <c r="C58" s="36"/>
@@ -4142,31 +4130,31 @@
     </row>
     <row r="60" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="17"/>
-      <c r="B60" s="329" t="s">
-        <v>309</v>
-      </c>
-      <c r="C60" s="329"/>
-      <c r="D60" s="329"/>
-      <c r="E60" s="329"/>
-      <c r="F60" s="329"/>
+      <c r="B60" s="331" t="s">
+        <v>307</v>
+      </c>
+      <c r="C60" s="331"/>
+      <c r="D60" s="331"/>
+      <c r="E60" s="331"/>
+      <c r="F60" s="331"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B61" s="331" t="s">
-        <v>264</v>
-      </c>
-      <c r="C61" s="331"/>
-      <c r="D61" s="331"/>
-      <c r="E61" s="331"/>
-      <c r="F61" s="331"/>
+      <c r="B61" s="333" t="s">
+        <v>263</v>
+      </c>
+      <c r="C61" s="333"/>
+      <c r="D61" s="333"/>
+      <c r="E61" s="333"/>
+      <c r="F61" s="333"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B63" s="241" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B64" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C64" s="322">
         <v>0.08</v>
@@ -4174,31 +4162,31 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B65" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C65" s="271">
         <f>IF(D65="Y",1%,0)</f>
         <v>0.01</v>
       </c>
       <c r="D65" s="296" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C66" s="271">
         <f>IF(D66="Y",1%,0)</f>
         <v>0.01</v>
       </c>
       <c r="D66" s="296" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="82" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C67" s="271">
         <f>SUM(C64:C66)</f>
@@ -4209,26 +4197,26 @@
       <c r="C68" s="125"/>
     </row>
     <row r="69" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="330" t="s">
-        <v>317</v>
-      </c>
-      <c r="C69" s="330"/>
-      <c r="D69" s="330"/>
-      <c r="E69" s="330"/>
-      <c r="F69" s="330"/>
+      <c r="B69" s="329" t="s">
+        <v>315</v>
+      </c>
+      <c r="C69" s="329"/>
+      <c r="D69" s="329"/>
+      <c r="E69" s="329"/>
+      <c r="F69" s="329"/>
     </row>
     <row r="70" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="330" t="s">
-        <v>263</v>
-      </c>
-      <c r="C70" s="330"/>
-      <c r="D70" s="330"/>
-      <c r="E70" s="330"/>
-      <c r="F70" s="330"/>
+      <c r="B70" s="329" t="s">
+        <v>262</v>
+      </c>
+      <c r="C70" s="329"/>
+      <c r="D70" s="329"/>
+      <c r="E70" s="329"/>
+      <c r="F70" s="329"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B71" s="47" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C71" s="271">
         <v>0</v>
@@ -4236,7 +4224,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B73" s="47" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C73" s="255">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4249,7 +4237,7 @@
     </row>
     <row r="75" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A75" s="254" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B75" s="36"/>
       <c r="C75" s="36"/>
@@ -4261,27 +4249,27 @@
       <c r="A76" s="240"/>
     </row>
     <row r="77" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="330" t="s">
-        <v>266</v>
-      </c>
-      <c r="C77" s="330"/>
-      <c r="D77" s="330"/>
-      <c r="E77" s="330"/>
-      <c r="F77" s="330"/>
+      <c r="B77" s="329" t="s">
+        <v>265</v>
+      </c>
+      <c r="C77" s="329"/>
+      <c r="D77" s="329"/>
+      <c r="E77" s="329"/>
+      <c r="F77" s="329"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B80" s="241" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="47" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C81" s="192">
         <f>Valuation_Model!C7</f>
@@ -4294,7 +4282,7 @@
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="47" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C82" s="255">
         <f>C81*C28*Exchange_Rate/Common_Shares</f>
@@ -4307,12 +4295,12 @@
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B84" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C85" s="192">
         <f>BS!C66</f>
@@ -4325,7 +4313,7 @@
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C86" s="192">
         <f>Valuation_Model!C8</f>
@@ -4338,7 +4326,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C87" s="255">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4351,12 +4339,12 @@
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B89" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="47" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C90" s="192">
         <f>Valuation_Model!C9</f>
@@ -4369,7 +4357,7 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="47" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C91" s="255">
         <f>C90*C28*Exchange_Rate/Common_Shares</f>
@@ -4381,17 +4369,17 @@
       </c>
     </row>
     <row r="93" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="330" t="s">
-        <v>272</v>
-      </c>
-      <c r="C93" s="330"/>
-      <c r="D93" s="330"/>
-      <c r="E93" s="330"/>
-      <c r="F93" s="330"/>
+      <c r="B93" s="329" t="s">
+        <v>271</v>
+      </c>
+      <c r="C93" s="329"/>
+      <c r="D93" s="329"/>
+      <c r="E93" s="329"/>
+      <c r="F93" s="329"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="47" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C95" s="255">
         <f>Valuation_Model!C12</f>
@@ -4404,7 +4392,7 @@
     </row>
     <row r="97" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A97" s="254" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B97" s="36"/>
       <c r="C97" s="36"/>
@@ -4413,29 +4401,29 @@
       <c r="F97" s="36"/>
     </row>
     <row r="99" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="329" t="s">
-        <v>373</v>
-      </c>
-      <c r="C99" s="329"/>
-      <c r="D99" s="329"/>
-      <c r="E99" s="329"/>
-      <c r="F99" s="329"/>
+      <c r="B99" s="331" t="s">
+        <v>371</v>
+      </c>
+      <c r="C99" s="331"/>
+      <c r="D99" s="331"/>
+      <c r="E99" s="331"/>
+      <c r="F99" s="331"/>
     </row>
     <row r="101" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B101" s="267" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C101" s="267" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D101" s="267" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E101" s="267" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F101" s="267" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
@@ -4550,7 +4538,7 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B108" s="242" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C108" s="248">
         <f>Scenarios!C60</f>
@@ -4563,7 +4551,7 @@
     </row>
     <row r="110" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B110" s="334" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C110" s="334"/>
       <c r="D110" s="334"/>
@@ -4572,7 +4560,7 @@
     </row>
     <row r="112" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A112" s="254" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B112" s="36"/>
       <c r="C112" s="36"/>
@@ -4581,22 +4569,22 @@
       <c r="F112" s="36"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B114" s="332" t="s">
-        <v>280</v>
-      </c>
-      <c r="C114" s="332"/>
-      <c r="D114" s="332"/>
-      <c r="E114" s="332"/>
-      <c r="F114" s="332"/>
+      <c r="B114" s="330" t="s">
+        <v>279</v>
+      </c>
+      <c r="C114" s="330"/>
+      <c r="D114" s="330"/>
+      <c r="E114" s="330"/>
+      <c r="F114" s="330"/>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B115" s="241" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="116" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B116" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C116" s="258">
         <f>E20</f>
@@ -4605,7 +4593,7 @@
     </row>
     <row r="117" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B117" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C117" s="257">
         <f>C19</f>
@@ -4614,7 +4602,7 @@
     </row>
     <row r="118" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B118" s="243" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C118" s="244">
         <f>Scenarios!C77</f>
@@ -4627,7 +4615,7 @@
     </row>
     <row r="120" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B120" s="241" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.35">
@@ -4652,7 +4640,7 @@
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B123" s="82" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C123" s="246">
         <f>Scenarios!C83</f>
@@ -4665,7 +4653,7 @@
     </row>
     <row r="124" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B124" s="245" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C124" s="158">
         <f>Scenarios!F83</f>
@@ -4674,6 +4662,12 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B93:F93"/>
@@ -4687,12 +4681,6 @@
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B110:F110"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -4776,7 +4764,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -4792,7 +4780,7 @@
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3" s="109">
         <v>1000</v>
@@ -4826,7 +4814,7 @@
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" s="194">
         <v>897327</v>
@@ -4852,7 +4840,7 @@
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B6" s="40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6" s="194">
         <v>613104</v>
@@ -4878,7 +4866,7 @@
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B7" s="70" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C7" s="195">
         <v>425033</v>
@@ -4898,7 +4886,7 @@
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B8" s="40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8" s="194"/>
       <c r="D8" s="185"/>
@@ -4914,7 +4902,7 @@
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B9" s="40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C9" s="194"/>
       <c r="D9" s="185"/>
@@ -4930,7 +4918,7 @@
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B10" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C10" s="194"/>
       <c r="D10" s="185"/>
@@ -4946,7 +4934,7 @@
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C11" s="194"/>
       <c r="D11" s="185"/>
@@ -4962,7 +4950,7 @@
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B12" s="40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" s="194">
         <v>1003</v>
@@ -4988,7 +4976,7 @@
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B13" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C13" s="194">
         <v>73805</v>
@@ -5008,7 +4996,7 @@
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B14" s="40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C14" s="194">
         <v>44449</v>
@@ -5028,7 +5016,7 @@
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B15" s="43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" s="196">
         <v>172817</v>
@@ -5052,7 +5040,7 @@
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B16" s="28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" s="194">
         <v>2199</v>
@@ -5072,13 +5060,13 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B18" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B19" s="27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C19" s="185">
         <v>35974</v>
@@ -5102,7 +5090,7 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B20" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C20" s="185">
         <v>15312</v>
@@ -5122,7 +5110,7 @@
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B21" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C21" s="185">
         <v>-169280</v>
@@ -5161,13 +5149,13 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C24" s="9"/>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B25" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C25" s="187"/>
       <c r="D25" s="185"/>
@@ -5183,7 +5171,7 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B26" s="26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26" s="187"/>
       <c r="D26" s="185"/>
@@ -5199,7 +5187,7 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B27" s="29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" s="186">
         <v>642877</v>
@@ -5225,7 +5213,7 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="186">
         <v>3027292</v>
@@ -5251,7 +5239,7 @@
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B29" s="26" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C29" s="185"/>
       <c r="D29" s="185"/>
@@ -5267,13 +5255,13 @@
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B31" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C31" s="9"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B32" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C32" s="185"/>
       <c r="D32" s="185"/>
@@ -5289,7 +5277,7 @@
     </row>
     <row r="34" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B34" s="36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -5305,7 +5293,7 @@
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B35" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.35">
@@ -5359,7 +5347,7 @@
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B37" s="40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C37" s="187">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -5408,7 +5396,7 @@
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B38" s="31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C38" s="188">
         <f>IF(C36="","",C36+C37)</f>
@@ -5457,7 +5445,7 @@
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B39" s="40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C39" s="187">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -5506,7 +5494,7 @@
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B40" s="70" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C40" s="189">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -5555,7 +5543,7 @@
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B41" s="70" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C41" s="189">
         <f>IF(C$4="","",C39-C40)</f>
@@ -5604,7 +5592,7 @@
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B42" s="40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C42" s="187">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -5653,7 +5641,7 @@
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B43" s="43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C43" s="190">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -5702,7 +5690,7 @@
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B44" s="43" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C44" s="191">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -5751,7 +5739,7 @@
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B45" s="40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C45" s="192">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -5800,7 +5788,7 @@
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B46" s="40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" s="187">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -5849,7 +5837,7 @@
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B47" s="43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C47" s="190">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -5898,7 +5886,7 @@
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B48" s="28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C48" s="187">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -5947,12 +5935,12 @@
     </row>
     <row r="50" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B50" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B51" s="40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C51" s="187">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
@@ -6001,7 +5989,7 @@
     </row>
     <row r="52" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B52" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C52" s="187">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -6050,12 +6038,12 @@
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B54" s="179" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B55" s="40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C55" s="192">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -6104,7 +6092,7 @@
     </row>
     <row r="56" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B56" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C56" s="192">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -6153,7 +6141,7 @@
     </row>
     <row r="57" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B57" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C57" s="192">
         <f>IF(C$4="","",C11)</f>
@@ -6202,7 +6190,7 @@
     </row>
     <row r="58" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B58" s="40" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C58" s="192">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -6251,13 +6239,13 @@
     </row>
     <row r="60" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B60" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B61" s="27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C61" s="187">
         <f t="shared" ref="C61:M61" si="29">IF(C$4="","",-C19)</f>
@@ -6306,7 +6294,7 @@
     </row>
     <row r="62" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B62" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C62" s="187">
         <f t="shared" ref="C62:M62" si="30">IF(C$4="","",-C20)</f>
@@ -6355,7 +6343,7 @@
     </row>
     <row r="63" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B63" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C63" s="187">
         <f t="shared" ref="C63:M63" si="31">IF(C$4="","",-C21)</f>
@@ -6404,7 +6392,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C64" s="75">
         <f t="shared" ref="C64:M64" si="32">IF(C$4="","",C22)</f>
@@ -6453,7 +6441,7 @@
     </row>
     <row r="66" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B66" s="93" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="2:13" x14ac:dyDescent="0.35">
@@ -6708,7 +6696,7 @@
     </row>
     <row r="73" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B73" s="36" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C73" s="37"/>
       <c r="D73" s="37"/>
@@ -6724,7 +6712,7 @@
     </row>
     <row r="74" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B74" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C74" s="9"/>
     </row>
@@ -6779,7 +6767,7 @@
     </row>
     <row r="76" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B76" s="95" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C76" s="74">
         <f t="shared" ref="C76:H77" si="39">IF(C$4="","",C25)</f>
@@ -6813,7 +6801,7 @@
     </row>
     <row r="77" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B77" s="95" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C77" s="74">
         <f t="shared" si="39"/>
@@ -6847,7 +6835,7 @@
     </row>
     <row r="78" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B78" s="26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C78" s="58">
         <f t="shared" ref="C78:M78" si="40">IF(C$4="","",C27)</f>
@@ -6896,7 +6884,7 @@
     </row>
     <row r="79" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B79" s="26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C79" s="58">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C28)</f>
@@ -6988,7 +6976,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C1" s="102">
         <v>45473</v>
@@ -7004,7 +6992,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="81" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -7015,27 +7003,27 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C3" s="210" t="s">
+        <v>141</v>
+      </c>
+      <c r="D3" s="211" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C3" s="210" t="s">
-        <v>142</v>
-      </c>
-      <c r="D3" s="211" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>191</v>
-      </c>
       <c r="G3" s="210" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H3" s="211" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" s="19">
         <v>180994</v>
@@ -7045,7 +7033,7 @@
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G4" s="19">
         <v>2385307</v>
@@ -7056,7 +7044,7 @@
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" s="19">
         <v>0</v>
@@ -7066,7 +7054,7 @@
       </c>
       <c r="E5" s="25"/>
       <c r="F5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5" s="19">
         <v>0</v>
@@ -7087,7 +7075,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -7098,7 +7086,7 @@
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C7" s="19">
         <v>0</v>
@@ -7108,7 +7096,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G7" s="19">
         <v>253051</v>
@@ -7119,7 +7107,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -7129,7 +7117,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -7140,7 +7128,7 @@
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" s="19">
         <v>0</v>
@@ -7150,7 +7138,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -7185,7 +7173,7 @@
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="82" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C12" s="83">
         <f>SUM(C4:C11)</f>
@@ -7196,7 +7184,7 @@
         <v>192972.19999999998</v>
       </c>
       <c r="F12" s="82" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G12" s="83">
         <f>SUM(G4:G9)</f>
@@ -7214,27 +7202,27 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C14" s="210" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D14" s="211" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G14" s="210" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H14" s="211" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C15" s="19">
         <v>0</v>
@@ -7243,7 +7231,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G15" s="19">
         <v>279425</v>
@@ -7254,7 +7242,7 @@
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" s="19">
         <v>0</v>
@@ -7263,7 +7251,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -7274,7 +7262,7 @@
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C17" s="19">
         <v>0</v>
@@ -7283,7 +7271,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G17" s="19">
         <v>126127</v>
@@ -7294,7 +7282,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -7303,7 +7291,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -7314,7 +7302,7 @@
     </row>
     <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" s="19">
         <v>193915</v>
@@ -7323,7 +7311,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G19" s="19">
         <v>1500</v>
@@ -7343,7 +7331,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -7363,7 +7351,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -7398,7 +7386,7 @@
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="82" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C24" s="83">
         <f>SUM(C15:C23)</f>
@@ -7409,7 +7397,7 @@
         <v>88388.3</v>
       </c>
       <c r="F24" s="82" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G24" s="83">
         <f>SUM(G15:G21)</f>
@@ -7422,19 +7410,19 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C26" s="210" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F26" s="212" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G26" s="213" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H26" s="214" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7445,7 +7433,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="215" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G27" s="87">
         <f>G32-G30</f>
@@ -7464,7 +7452,7 @@
         <v>13416</v>
       </c>
       <c r="F28" s="217" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G28" s="185">
         <v>3990</v>
@@ -7479,7 +7467,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="218" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -7508,14 +7496,14 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="82" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C31" s="83">
         <f>SUM(C27:C30)</f>
         <v>13416</v>
       </c>
       <c r="F31" s="218" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G31" s="219">
         <f>C31+C40</f>
@@ -7532,7 +7520,7 @@
         <v>598515</v>
       </c>
       <c r="F32" s="220" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G32" s="221">
         <f>G35+G40</f>
@@ -7558,24 +7546,24 @@
       <c r="B34" s="85"/>
       <c r="C34" s="86"/>
       <c r="F34" s="224" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G34" s="225" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H34" s="226" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C35" s="210" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F35" s="227" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G35" s="221">
         <f>C12+C24</f>
@@ -7594,7 +7582,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="218" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G36" s="219">
         <f>C4+C15</f>
@@ -7610,7 +7598,7 @@
         <v>20583</v>
       </c>
       <c r="F37" s="218" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G37" s="219">
         <f>C6</f>
@@ -7626,7 +7614,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="218" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G38" s="219">
         <f>C7+C17</f>
@@ -7642,7 +7630,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="218" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G39" s="219">
         <f>C7+C17+C19+C20</f>
@@ -7655,14 +7643,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="82" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C40" s="83">
         <f>SUM(C36:C39)</f>
         <v>20583</v>
       </c>
       <c r="F40" s="227" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G40" s="221">
         <f>G12+G24</f>
@@ -7682,7 +7670,7 @@
         <v>10363</v>
       </c>
       <c r="F41" s="218" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G41" s="219">
         <f>C70</f>
@@ -7701,7 +7689,7 @@
         <v>30946</v>
       </c>
       <c r="F42" s="229" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G42" s="230">
         <f>C82</f>
@@ -7714,7 +7702,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="81" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -7725,21 +7713,21 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C45" s="268" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D45" s="210" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F45" s="297" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C46" s="192">
         <f>G29</f>
@@ -7771,20 +7759,20 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="162" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C49" s="269" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D49" s="225" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="292"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C50" s="98">
         <f>G31/Normalized_FCF!C8</f>
@@ -7798,7 +7786,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C51" s="209"/>
       <c r="D51" s="94">
@@ -7812,19 +7800,19 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="162" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C53" s="269" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D53" s="225" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F53" s="292"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C54" s="94">
         <f>Normalized_FCF!C8/G35</f>
@@ -7838,7 +7826,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C11/G40</f>
@@ -7855,19 +7843,19 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B57" s="162" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C57" s="269" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D57" s="225" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F57" s="292"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C58" s="101"/>
       <c r="D58" s="23">
@@ -7878,7 +7866,7 @@
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B59" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C59" s="101"/>
       <c r="D59" s="94">
@@ -7892,19 +7880,19 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="162" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C61" s="269" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D61" s="225" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F61" s="292"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C62" s="94">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -7915,12 +7903,12 @@
         <v>1.3197490690642218E-3</v>
       </c>
       <c r="F62" s="292" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" s="81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -7931,21 +7919,21 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B65" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C65" s="268" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D65" s="211" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F65" s="297" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B66" s="108" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -7956,12 +7944,12 @@
         <v>2029405.1093906919</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B67" s="108" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -7971,7 +7959,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="108" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -7981,7 +7969,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="108" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -7991,7 +7979,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C70" s="83">
         <f>SUM(C66:C69)</f>
@@ -8004,19 +7992,19 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="295" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C72" s="268" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D72" s="210" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F72" s="292"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C73" s="192">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35)/12</f>
@@ -8029,7 +8017,7 @@
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="298" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C74" s="299">
         <f>-$C$66/C73</f>
@@ -8040,12 +8028,12 @@
         <v>20.971345927483078</v>
       </c>
       <c r="F74" s="292" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="82" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C75" s="304"/>
       <c r="D75" s="303">
@@ -8053,12 +8041,12 @@
         <v>-635326.89060930803</v>
       </c>
       <c r="F75" s="292" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="300" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C76" s="301"/>
       <c r="D76" s="302">
@@ -8066,7 +8054,7 @@
         <v>5</v>
       </c>
       <c r="F76" s="292" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8074,19 +8062,19 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="16" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C78" s="268" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D78" s="211" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F78" s="292"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="108" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -8100,7 +8088,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="108" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -8114,7 +8102,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="108" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -8128,7 +8116,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B82" s="82" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C82" s="83">
         <f>SUM(C79:C81)</f>
@@ -8142,7 +8130,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8153,15 +8141,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D85" s="278" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="275" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C86" s="192">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -8178,7 +8166,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="275" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C87" s="192">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -8195,7 +8183,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B88" s="276" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C88" s="192">
         <f>Valuation_Model!C9*Exchange_Rate</f>
@@ -8212,7 +8200,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="82" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C89" s="191">
         <f>SUM(C86:C88)</f>
@@ -8260,7 +8248,7 @@
         <v>CNY</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
@@ -8313,12 +8301,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="37"/>
@@ -8336,7 +8324,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C3" s="110">
         <f>Data!C3</f>
@@ -8407,7 +8395,7 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5" s="198">
         <f>C25</f>
@@ -8462,7 +8450,7 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6" s="188">
         <f>C4+C5</f>
@@ -8517,7 +8505,7 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="198">
         <f>C35</f>
@@ -8572,7 +8560,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C8" s="199">
         <f>C6+C7</f>
@@ -8629,7 +8617,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9" s="198">
         <f>BS!$G$39*BS!D58</f>
@@ -8684,7 +8672,7 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C10" s="198">
         <f>-C4*C77</f>
@@ -8739,7 +8727,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C11" s="200">
         <f>C62</f>
@@ -8796,7 +8784,7 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C12" s="198">
         <f>C49</f>
@@ -8851,7 +8839,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="10"/>
       <c r="B13" s="71" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C13" s="188">
         <f>SUM(C8:C12)</f>
@@ -8906,7 +8894,7 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C14" s="198">
         <f>-SUM(C8+C11,C12)*C43</f>
@@ -8961,7 +8949,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C15" s="198">
         <f>-C4*C82</f>
@@ -9018,7 +9006,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C16" s="201">
         <f>SUM(C13:C15)</f>
@@ -9075,7 +9063,7 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C17" s="198">
         <f>-C4*C84</f>
@@ -9083,7 +9071,7 @@
       </c>
       <c r="D17" s="59"/>
       <c r="E17" s="312" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="202"/>
@@ -9101,7 +9089,7 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C18" s="198">
         <f>-C4*C85</f>
@@ -9109,7 +9097,7 @@
       </c>
       <c r="D18" s="59"/>
       <c r="E18" s="312" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="203"/>
@@ -9127,7 +9115,7 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C19" s="188">
         <f>SUM(C16:C18)</f>
@@ -9203,12 +9191,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
       <c r="E21" s="67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="37"/>
@@ -9226,7 +9214,7 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="10"/>
       <c r="B22" s="65" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="27"/>
@@ -9247,7 +9235,7 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C23" s="204">
         <f>-C4*C28</f>
@@ -9304,7 +9292,7 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10"/>
       <c r="B24" s="69" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C24" s="198">
         <f>-C4*C29</f>
@@ -9361,7 +9349,7 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10"/>
       <c r="B25" s="71" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C25" s="188">
         <f>C23+C24</f>
@@ -9422,14 +9410,14 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="65" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E27" s="313"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C28" s="64">
         <f>AVERAGE(G28:H28)</f>
@@ -9437,7 +9425,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="311" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -9497,7 +9485,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="311" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -9548,7 +9536,7 @@
     <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10"/>
       <c r="B30" s="71" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C30" s="72">
         <f>ABS(C25/$C$4)</f>
@@ -9607,21 +9595,21 @@
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10"/>
       <c r="B32" s="65" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E32" s="313"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C33" s="205">
         <f>AVERAGE(G33:H33)</f>
         <v>-175999.5</v>
       </c>
       <c r="E33" s="311" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G33" s="198">
         <f>Data!C41</f>
@@ -9671,7 +9659,7 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C34" s="205">
         <f>AVERAGE(G34:J34)</f>
@@ -9679,7 +9667,7 @@
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="311" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="187">
@@ -9730,7 +9718,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="10"/>
       <c r="B35" s="71" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C35" s="188">
         <f>C33+C34</f>
@@ -9791,7 +9779,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10"/>
       <c r="B37" s="65" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E37" s="313"/>
     </row>
@@ -9914,7 +9902,7 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="10"/>
       <c r="B40" s="71" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C40" s="72">
         <f>ABS(C35/$C$4)</f>
@@ -9973,21 +9961,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10"/>
       <c r="B42" s="65" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E42" s="313"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C43" s="307">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="310" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10041,12 +10029,12 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
       <c r="E45" s="67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="37"/>
@@ -10064,14 +10052,14 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="10"/>
       <c r="B46" s="65" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E46" s="313"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C47" s="198">
         <f>-BS!G31*Normalized_FCF!C53</f>
@@ -10126,7 +10114,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C48" s="198">
         <f>BS!$C$66*C52</f>
@@ -10181,7 +10169,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="71" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C49" s="188">
         <f>C47+C48</f>
@@ -10240,24 +10228,24 @@
     <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="10"/>
       <c r="B51" s="73" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E51" s="313"/>
       <c r="G51" s="100" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C52" s="89">
         <f>G52</f>
         <v>2.7696969151119136E-2</v>
       </c>
       <c r="E52" s="310" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G52" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G48/BS!$C$66)</f>
@@ -10277,14 +10265,14 @@
     <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C53" s="84">
         <f>Normalized_FCF!G53</f>
         <v>2.9500867672578604E-2</v>
       </c>
       <c r="E53" s="310" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G53" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -10304,7 +10292,7 @@
     <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="10"/>
       <c r="B54" s="26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C54" s="42">
         <f>-C8/C47</f>
@@ -10363,17 +10351,17 @@
     <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="10"/>
       <c r="B56" s="65" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E56" s="313"/>
       <c r="G56" s="100" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="10"/>
       <c r="B57" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C57" s="198">
         <f>BS!$C79*C65</f>
@@ -10428,7 +10416,7 @@
     <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C58" s="198">
         <f>BS!$C68*C66</f>
@@ -10483,7 +10471,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C59" s="198">
         <f>BS!$C81*C67</f>
@@ -10538,7 +10526,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="10"/>
       <c r="B60" s="31" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C60" s="188">
         <f>SUM(C57:C59)</f>
@@ -10593,13 +10581,13 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="10"/>
       <c r="B61" s="40" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C61" s="308">
         <v>0</v>
       </c>
       <c r="E61" s="311" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G61" s="198">
         <f>Data!C58</f>
@@ -10649,7 +10637,7 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="10"/>
       <c r="B62" s="31" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C62" s="188">
         <f>C60+C61</f>
@@ -10708,17 +10696,17 @@
     <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="10"/>
       <c r="B64" s="99" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E64" s="313"/>
       <c r="G64" s="100" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="10"/>
       <c r="B65" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C65" s="181">
         <f>G65</f>
@@ -10743,7 +10731,7 @@
     <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="10"/>
       <c r="B66" s="108" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C66" s="181">
         <f>G66</f>
@@ -10768,7 +10756,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="10"/>
       <c r="B67" s="108" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C67" s="181">
         <f>G67</f>
@@ -10793,7 +10781,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="10"/>
       <c r="B68" s="31" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C68" s="72">
         <f>C60/BS!C70</f>
@@ -10823,12 +10811,12 @@
     <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A70" s="10"/>
       <c r="B70" s="54" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C70" s="54"/>
       <c r="D70" s="56"/>
       <c r="E70" s="67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F70" s="56"/>
       <c r="G70" s="37"/>
@@ -10846,7 +10834,7 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="10"/>
       <c r="B71" s="73" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C71" s="63"/>
       <c r="D71" s="27"/>
@@ -10867,7 +10855,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="10"/>
       <c r="B72" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C72" s="79">
         <f>ABS(C5/C$4)</f>
@@ -10924,7 +10912,7 @@
     <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="10"/>
       <c r="B73" s="31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C73" s="80">
         <f>ABS(C6/C$4)</f>
@@ -10981,7 +10969,7 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="10"/>
       <c r="B74" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C74" s="79">
         <f>ABS(C7/C$4)</f>
@@ -11038,7 +11026,7 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="10"/>
       <c r="B75" s="29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C75" s="80">
         <f>ABS(C8/C$4)</f>
@@ -11095,7 +11083,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C76" s="79">
         <f>ABS(C9/C$4)</f>
@@ -11152,7 +11140,7 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C77" s="90">
         <f>MAX(AVERAGE(G77:J77),C76)</f>
@@ -11160,7 +11148,7 @@
       </c>
       <c r="D77" s="27"/>
       <c r="E77" s="311" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
@@ -11211,7 +11199,7 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="10"/>
       <c r="B78" s="31" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C78" s="80">
         <f>ABS(C11/C$4)</f>
@@ -11268,7 +11256,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="10"/>
       <c r="B79" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C79" s="79">
         <f>ABS(C12/C$4)</f>
@@ -11325,7 +11313,7 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="10"/>
       <c r="B80" s="71" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C80" s="80">
         <f>C13/C4</f>
@@ -11382,7 +11370,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C81" s="79">
         <f>ABS(C14/C$4)</f>
@@ -11497,7 +11485,7 @@
     <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="10"/>
       <c r="B83" s="41" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C83" s="80">
         <f>ABS(C16/C$4)</f>
@@ -11554,7 +11542,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="10"/>
       <c r="B84" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C84" s="309">
         <v>0</v>
@@ -11580,7 +11568,7 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="10"/>
       <c r="B85" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C85" s="309">
         <v>0</v>
@@ -11604,7 +11592,7 @@
     <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="10"/>
       <c r="B86" s="31" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C86" s="80">
         <f>ABS(C19/C$4)</f>
@@ -11665,7 +11653,7 @@
     <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="10"/>
       <c r="B88" s="65" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E88" s="313"/>
     </row>
@@ -11784,7 +11772,7 @@
     <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C91" s="23">
         <f>C89/(C19*$C$3/Common_Shares)</f>
@@ -11839,7 +11827,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C92" s="23">
         <f>C89/Market_Price</f>
@@ -11898,7 +11886,7 @@
     <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="10"/>
       <c r="B94" s="162" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C94" s="63"/>
       <c r="D94" s="27"/>
@@ -11919,7 +11907,7 @@
     <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="10"/>
       <c r="B95" s="27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C95" s="79">
         <f>C4/G4-1</f>
@@ -11976,7 +11964,7 @@
     <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="10"/>
       <c r="B96" s="71" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C96" s="79">
         <f>C13/G13-1</f>
@@ -12036,12 +12024,12 @@
     <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A98" s="3"/>
       <c r="B98" s="54" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C98" s="54"/>
       <c r="D98" s="56"/>
       <c r="E98" s="67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F98" s="56"/>
       <c r="G98" s="37"/>
@@ -12059,11 +12047,11 @@
     <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="10"/>
       <c r="B99" s="65" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E99" s="313"/>
       <c r="G99" s="100" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -12126,7 +12114,7 @@
     <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="10"/>
       <c r="B101" s="95" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C101" s="207">
         <f>BS!C4</f>
@@ -12183,7 +12171,7 @@
     <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="10"/>
       <c r="B102" s="95" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C102" s="207">
         <f>BS!C6+BS!C7</f>
@@ -12240,7 +12228,7 @@
     <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="10"/>
       <c r="B103" s="26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C103" s="206">
         <f>BS!G30</f>
@@ -12297,7 +12285,7 @@
     <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C104" s="206">
         <f>BS!G27</f>
@@ -12358,14 +12346,14 @@
     <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="10"/>
       <c r="B106" s="93" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C106" s="26"/>
       <c r="D106" s="26"/>
       <c r="E106" s="314"/>
       <c r="F106" s="26"/>
       <c r="G106" s="100" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H106" s="12"/>
       <c r="I106" s="12"/>
@@ -12381,7 +12369,7 @@
     <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="10"/>
       <c r="B107" s="26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C107" s="97">
         <f>C101/C$4</f>
@@ -12438,7 +12426,7 @@
     <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C108" s="97">
         <f>C102/C$4</f>
@@ -12495,7 +12483,7 @@
     <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C109" s="97">
         <f>BS!$G$38/C$4</f>
@@ -12526,7 +12514,7 @@
     <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="10"/>
       <c r="B111" s="93" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C111" s="55"/>
       <c r="D111" s="55"/>
@@ -12580,7 +12568,7 @@
     <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="10"/>
       <c r="B112" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C112" s="23">
         <f>C80</f>
@@ -12634,7 +12622,7 @@
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B113" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C113" s="42">
         <f>C4/C100</f>
@@ -12688,7 +12676,7 @@
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B114" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C114" s="15">
         <f>C100/C104</f>
@@ -12745,7 +12733,7 @@
     <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="10"/>
       <c r="B115" s="71" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C115" s="105">
         <f>C8/C104</f>
@@ -12821,12 +12809,12 @@
     <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A117" s="10"/>
       <c r="B117" s="54" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C117" s="54"/>
       <c r="D117" s="56"/>
       <c r="E117" s="67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F117" s="56"/>
       <c r="G117" s="37"/>
@@ -12844,7 +12832,7 @@
     <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="10"/>
       <c r="B118" s="183" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C118" s="184"/>
       <c r="D118" s="27"/>
@@ -12923,7 +12911,7 @@
     <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="10"/>
       <c r="B120" s="27" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C120" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -13692,32 +13680,32 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="134" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="112" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C3" s="110">
         <f>Normalized_FCF!C3</f>
         <v>1000</v>
       </c>
       <c r="E3" s="112" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H3" s="124"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B4" s="103" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C4" s="113">
         <f>Normalized_FCF!C19</f>
@@ -13728,7 +13716,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="103" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F4" s="138">
         <f>Thesis!C71</f>
@@ -13738,7 +13726,7 @@
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B5" s="234" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C5" s="235">
         <f>Thesis!C67</f>
@@ -13749,7 +13737,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="153" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C6" s="239">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -13760,14 +13748,14 @@
         <v>CNY</v>
       </c>
       <c r="E6" s="335" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F6" s="335"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" s="152" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C7" s="233">
         <f>BS!G31</f>
@@ -13783,7 +13771,7 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B8" s="152" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C8" s="208">
         <f>BS!D66</f>
@@ -13799,7 +13787,7 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B9" s="234" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C9" s="236">
         <f>BS!H42</f>
@@ -13815,7 +13803,7 @@
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B10" s="153" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C10" s="239">
         <f>C6-C7+C8+C9</f>
@@ -13829,7 +13817,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="237" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C11" s="238">
         <f>Exchange_Rate</f>
@@ -13843,7 +13831,7 @@
     </row>
     <row r="12" spans="2:8" ht="13.5" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B12" s="153" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
@@ -13860,7 +13848,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B14" s="36" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -13870,13 +13858,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B15" s="123" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H15" s="124"/>
     </row>
     <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C16" s="166">
         <f>Scenarios!C65</f>
@@ -13886,7 +13874,7 @@
     </row>
     <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C17" s="167">
         <f>Scenarios!C64</f>
@@ -13896,7 +13884,7 @@
     </row>
     <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="157" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
@@ -13913,19 +13901,19 @@
     </row>
     <row r="20" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="132" t="s">
+        <v>112</v>
+      </c>
+      <c r="C20" s="132" t="s">
         <v>113</v>
       </c>
-      <c r="C20" s="132" t="s">
+      <c r="D20" s="132" t="s">
+        <v>123</v>
+      </c>
+      <c r="E20" s="132" t="s">
         <v>114</v>
       </c>
-      <c r="D20" s="132" t="s">
-        <v>124</v>
-      </c>
-      <c r="E20" s="132" t="s">
+      <c r="F20" s="133" t="s">
         <v>115</v>
-      </c>
-      <c r="F20" s="133" t="s">
-        <v>116</v>
       </c>
       <c r="H20" s="124"/>
     </row>
@@ -14591,7 +14579,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B51" s="130" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C51" s="127">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -14614,7 +14602,7 @@
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C52" s="118"/>
       <c r="E52" s="131" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F52" s="141">
         <f>SUM(F21:F51)</f>
@@ -14628,7 +14616,7 @@
     </row>
     <row r="54" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B54" s="123" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C54" s="140"/>
       <c r="D54" s="140"/>
@@ -14799,7 +14787,7 @@
     </row>
     <row r="63" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B63" s="123" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C63" s="118"/>
       <c r="D63" s="118"/>
@@ -15018,19 +15006,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B73" s="176" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C73" s="176" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D73" s="176" t="s">
+        <v>117</v>
+      </c>
+      <c r="E73" s="177" t="s">
         <v>118</v>
       </c>
-      <c r="E73" s="177" t="s">
-        <v>119</v>
-      </c>
       <c r="F73" s="177" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
@@ -15155,20 +15143,20 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="160" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C80" s="160" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="81" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C81" s="160" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="82" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C82" s="160" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="92" spans="3:3" x14ac:dyDescent="0.35">
@@ -15220,20 +15208,20 @@
   <sheetData>
     <row r="2" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="285" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="I2" s="286"/>
     </row>
     <row r="3" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="164" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H3" s="284">
         <v>0</v>
@@ -15245,14 +15233,14 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B4" s="156" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C4" s="124">
         <v>3</v>
       </c>
       <c r="D4" s="124"/>
       <c r="E4" s="160" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F4" s="160"/>
       <c r="H4" s="284">
@@ -15274,14 +15262,14 @@
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B6" s="164" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C6" s="110">
         <f>Valuation_Model!C3</f>
         <v>1000</v>
       </c>
       <c r="E6" s="103" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F6" s="103"/>
       <c r="H6" s="284">
@@ -15294,7 +15282,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="103" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C7" s="118">
         <f>Normalized_FCF!G8</f>
@@ -15319,7 +15307,7 @@
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" s="103" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C8" s="118">
         <f>Normalized_FCF!G19</f>
@@ -15341,7 +15329,7 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B9" s="103" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9" s="208">
         <f>Normalized_FCF!C19</f>
@@ -15374,7 +15362,7 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="164" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E11" s="337"/>
       <c r="F11" s="337"/>
@@ -15388,7 +15376,7 @@
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B12" s="122" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C12" s="163">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
@@ -15407,7 +15395,7 @@
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B13" s="152" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C13" s="163">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
@@ -15425,7 +15413,7 @@
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="103" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C14" s="163">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
@@ -15436,7 +15424,7 @@
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -15445,21 +15433,21 @@
     </row>
     <row r="17" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B17" s="112" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E17" s="164" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C18" s="154">
         <v>10</v>
       </c>
       <c r="E18" s="337" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F18" s="338"/>
     </row>
@@ -15469,14 +15457,14 @@
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="164" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E20" s="338"/>
       <c r="F20" s="338"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C21" s="165">
         <f>Market_Price</f>
@@ -15491,7 +15479,7 @@
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C22" s="165">
         <f>Valuation_Model!C12</f>
@@ -15506,16 +15494,16 @@
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="164" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E24" s="164" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F24" s="164"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C25" s="171">
         <f>C18</f>
@@ -15527,7 +15515,7 @@
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C26" s="169">
         <v>0.02</v>
@@ -15538,7 +15526,7 @@
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C27" s="165">
         <f>Valuation_Model!E76</f>
@@ -15553,7 +15541,7 @@
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C28" s="170">
         <v>0.6</v>
@@ -15564,16 +15552,16 @@
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="164" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E30" s="164" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F30" s="164"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B31" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C31" s="171">
         <f>C18</f>
@@ -15585,7 +15573,7 @@
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C32" s="169">
         <v>-0.06</v>
@@ -15596,7 +15584,7 @@
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C33" s="165">
         <f>Valuation_Model!E77</f>
@@ -15611,7 +15599,7 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C34" s="170">
         <v>0.15</v>
@@ -15622,16 +15610,16 @@
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="164" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E36" s="164" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F36" s="164"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C37" s="171">
         <f>C18</f>
@@ -15643,7 +15631,7 @@
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C38" s="169">
         <v>0.06</v>
@@ -15654,7 +15642,7 @@
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C39" s="165">
         <f>Valuation_Model!E75</f>
@@ -15669,7 +15657,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C40" s="172">
         <f>1-C28-C34</f>
@@ -15681,7 +15669,7 @@
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C42" s="159">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -15694,7 +15682,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B44" s="36" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -15703,12 +15691,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B45" s="112" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C46" s="154">
         <v>15</v>
@@ -15723,16 +15711,16 @@
     </row>
     <row r="48" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B48" s="164" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E48" s="164" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F48" s="164"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C49" s="171">
         <f>C46</f>
@@ -15744,7 +15732,7 @@
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C50" s="169">
         <v>-0.1</v>
@@ -15755,7 +15743,7 @@
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C51" s="165">
         <f>Valuation_Model!E78</f>
@@ -15770,7 +15758,7 @@
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C52" s="170">
         <v>0.1</v>
@@ -15781,16 +15769,16 @@
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="164" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E54" s="164" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F54" s="164"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B55" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C55" s="171">
         <f>C46</f>
@@ -15802,7 +15790,7 @@
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C56" s="169">
         <v>0.1</v>
@@ -15813,7 +15801,7 @@
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C57" s="165">
         <f>Valuation_Model!E74</f>
@@ -15828,7 +15816,7 @@
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C58" s="170">
         <v>0.05</v>
@@ -15839,7 +15827,7 @@
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C60" s="159">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -15850,7 +15838,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="103" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F60" s="324">
         <v>3</v>
@@ -15858,7 +15846,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -15867,39 +15855,39 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="112" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E63" s="291" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B64" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C64" s="171">
         <v>10</v>
       </c>
       <c r="D64" s="154"/>
       <c r="E64" s="290" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B65" s="122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C65" s="155">
         <v>1.8222579123958901E-2</v>
       </c>
       <c r="D65" s="155"/>
       <c r="E65" s="290" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B66" s="103" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C66" s="165">
         <f>Valuation_Model!C18</f>
@@ -15910,20 +15898,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="290" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="112" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E68" s="291" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="103" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C69" s="281" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -15933,19 +15921,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="103" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C70" s="281" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="290" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="103" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C71" s="281" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -15955,7 +15943,7 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C72" s="280" t="str">
         <f>IF(E72&gt;50%,"Y","N")</f>
@@ -15968,7 +15956,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B74" s="36" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -15977,16 +15965,16 @@
     </row>
     <row r="75" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B75" s="112" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E75" s="325" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F75" s="323"/>
     </row>
     <row r="76" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B76" s="283" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C76" s="282">
         <f>F60</f>
@@ -15994,15 +15982,15 @@
       </c>
       <c r="D76" s="138"/>
       <c r="E76" s="326" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F76" s="323" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B77" s="103" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C77" s="178">
         <f>Normalized_FCF!C89</f>
@@ -16013,28 +16001,28 @@
         <v>HKD</v>
       </c>
       <c r="E77" s="327" t="s">
+        <v>365</v>
+      </c>
+      <c r="F77" s="323" t="s">
         <v>367</v>
-      </c>
-      <c r="F77" s="323" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="78" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E78" s="328" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F78" s="323" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="112" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="152" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C80" s="172">
         <f>Thesis!C117</f>
@@ -16043,7 +16031,7 @@
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="103" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C81" s="120">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -16055,7 +16043,7 @@
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="103" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
@@ -16065,7 +16053,7 @@
     </row>
     <row r="83" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B83" s="114" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
@@ -16076,7 +16064,7 @@
         <v>HKD</v>
       </c>
       <c r="E83" s="150" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F83" s="270">
         <f>(C83/C60-1)</f>
@@ -16088,12 +16076,12 @@
     </row>
     <row r="85" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="112" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="152" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C86" s="274">
         <f>Market_Price</f>
@@ -16106,7 +16094,7 @@
     </row>
     <row r="87" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="103" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C87" s="273">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{384287BB-2682-4CBD-A99A-5604F52C7862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCECFB0F-D83B-448B-876D-2F1854D02970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3320,20 +3320,20 @@
     <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="5"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3692,7 +3692,7 @@
         <v>99</v>
       </c>
       <c r="C6" s="50">
-        <v>2.2999999999999998</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>43</v>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>3066.66705</v>
+        <v>3040.0003799999995</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -3747,13 +3747,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="329" t="s">
+      <c r="B12" s="330" t="s">
         <v>290</v>
       </c>
-      <c r="C12" s="329"/>
-      <c r="D12" s="329"/>
-      <c r="E12" s="329"/>
-      <c r="F12" s="329"/>
+      <c r="C12" s="330"/>
+      <c r="D12" s="330"/>
+      <c r="E12" s="330"/>
+      <c r="F12" s="330"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C21" s="288">
         <f ca="1">Scenarios!C87</f>
-        <v>8.8876330035536411E-2</v>
+        <v>9.2203750287490172E-2</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3856,22 +3856,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="329" t="s">
+      <c r="B25" s="330" t="s">
         <v>236</v>
       </c>
-      <c r="C25" s="329"/>
-      <c r="D25" s="329"/>
-      <c r="E25" s="329"/>
-      <c r="F25" s="329"/>
+      <c r="C25" s="330"/>
+      <c r="D25" s="330"/>
+      <c r="E25" s="330"/>
+      <c r="F25" s="330"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="333" t="s">
+      <c r="B26" s="331" t="s">
         <v>256</v>
       </c>
-      <c r="C26" s="333"/>
-      <c r="D26" s="333"/>
-      <c r="E26" s="333"/>
-      <c r="F26" s="333"/>
+      <c r="C26" s="331"/>
+      <c r="D26" s="331"/>
+      <c r="E26" s="331"/>
+      <c r="F26" s="331"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="241" t="s">
@@ -3883,13 +3883,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="331" t="s">
+      <c r="B29" s="329" t="s">
         <v>238</v>
       </c>
-      <c r="C29" s="331"/>
-      <c r="D29" s="331"/>
-      <c r="E29" s="331"/>
-      <c r="F29" s="331"/>
+      <c r="C29" s="329"/>
+      <c r="D29" s="329"/>
+      <c r="E29" s="329"/>
+      <c r="F29" s="329"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3909,13 +3909,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="331" t="s">
+      <c r="B32" s="329" t="s">
         <v>240</v>
       </c>
-      <c r="C32" s="331"/>
-      <c r="D32" s="331"/>
-      <c r="E32" s="331"/>
-      <c r="F32" s="331"/>
+      <c r="C32" s="329"/>
+      <c r="D32" s="329"/>
+      <c r="E32" s="329"/>
+      <c r="F32" s="329"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -3944,13 +3944,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="331" t="s">
+      <c r="B36" s="329" t="s">
         <v>243</v>
       </c>
-      <c r="C36" s="331"/>
-      <c r="D36" s="331"/>
-      <c r="E36" s="331"/>
-      <c r="F36" s="331"/>
+      <c r="C36" s="329"/>
+      <c r="D36" s="329"/>
+      <c r="E36" s="329"/>
+      <c r="F36" s="329"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -3966,13 +3966,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="331" t="s">
+      <c r="B39" s="329" t="s">
         <v>247</v>
       </c>
-      <c r="C39" s="331"/>
-      <c r="D39" s="331"/>
-      <c r="E39" s="331"/>
-      <c r="F39" s="331"/>
+      <c r="C39" s="329"/>
+      <c r="D39" s="329"/>
+      <c r="E39" s="329"/>
+      <c r="F39" s="329"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4006,13 +4006,13 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B45" s="331" t="s">
+      <c r="B45" s="329" t="s">
         <v>248</v>
       </c>
-      <c r="C45" s="331"/>
-      <c r="D45" s="331"/>
-      <c r="E45" s="331"/>
-      <c r="F45" s="331"/>
+      <c r="C45" s="329"/>
+      <c r="D45" s="329"/>
+      <c r="E45" s="329"/>
+      <c r="F45" s="329"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="47" t="s">
@@ -4028,13 +4028,13 @@
       </c>
     </row>
     <row r="48" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="331" t="s">
+      <c r="B48" s="329" t="s">
         <v>251</v>
       </c>
-      <c r="C48" s="332"/>
-      <c r="D48" s="332"/>
-      <c r="E48" s="332"/>
-      <c r="F48" s="332"/>
+      <c r="C48" s="333"/>
+      <c r="D48" s="333"/>
+      <c r="E48" s="333"/>
+      <c r="F48" s="333"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B49" s="47" t="s">
@@ -4063,13 +4063,13 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="329" t="s">
+      <c r="B52" s="330" t="s">
         <v>272</v>
       </c>
-      <c r="C52" s="329"/>
-      <c r="D52" s="329"/>
-      <c r="E52" s="329"/>
-      <c r="F52" s="329"/>
+      <c r="C52" s="330"/>
+      <c r="D52" s="330"/>
+      <c r="E52" s="330"/>
+      <c r="F52" s="330"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B53" s="47" t="s">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C120</f>
-        <v>3.3342925997552272E-2</v>
+        <v>3.3635407804548351E-2</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="C56" s="94">
         <f>Normalized_FCF!C92</f>
-        <v>5.1217391304347833E-2</v>
+        <v>5.1666666666666673E-2</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4130,22 +4130,22 @@
     </row>
     <row r="60" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="17"/>
-      <c r="B60" s="331" t="s">
+      <c r="B60" s="329" t="s">
         <v>307</v>
       </c>
-      <c r="C60" s="331"/>
-      <c r="D60" s="331"/>
-      <c r="E60" s="331"/>
-      <c r="F60" s="331"/>
+      <c r="C60" s="329"/>
+      <c r="D60" s="329"/>
+      <c r="E60" s="329"/>
+      <c r="F60" s="329"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B61" s="333" t="s">
+      <c r="B61" s="331" t="s">
         <v>263</v>
       </c>
-      <c r="C61" s="333"/>
-      <c r="D61" s="333"/>
-      <c r="E61" s="333"/>
-      <c r="F61" s="333"/>
+      <c r="C61" s="331"/>
+      <c r="D61" s="331"/>
+      <c r="E61" s="331"/>
+      <c r="F61" s="331"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B63" s="241" t="s">
@@ -4197,22 +4197,22 @@
       <c r="C68" s="125"/>
     </row>
     <row r="69" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="329" t="s">
+      <c r="B69" s="330" t="s">
         <v>315</v>
       </c>
-      <c r="C69" s="329"/>
-      <c r="D69" s="329"/>
-      <c r="E69" s="329"/>
-      <c r="F69" s="329"/>
+      <c r="C69" s="330"/>
+      <c r="D69" s="330"/>
+      <c r="E69" s="330"/>
+      <c r="F69" s="330"/>
     </row>
     <row r="70" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="329" t="s">
+      <c r="B70" s="330" t="s">
         <v>262</v>
       </c>
-      <c r="C70" s="329"/>
-      <c r="D70" s="329"/>
-      <c r="E70" s="329"/>
-      <c r="F70" s="329"/>
+      <c r="C70" s="330"/>
+      <c r="D70" s="330"/>
+      <c r="E70" s="330"/>
+      <c r="F70" s="330"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B71" s="47" t="s">
@@ -4249,13 +4249,13 @@
       <c r="A76" s="240"/>
     </row>
     <row r="77" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="329" t="s">
+      <c r="B77" s="330" t="s">
         <v>265</v>
       </c>
-      <c r="C77" s="329"/>
-      <c r="D77" s="329"/>
-      <c r="E77" s="329"/>
-      <c r="F77" s="329"/>
+      <c r="C77" s="330"/>
+      <c r="D77" s="330"/>
+      <c r="E77" s="330"/>
+      <c r="F77" s="330"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
@@ -4369,13 +4369,13 @@
       </c>
     </row>
     <row r="93" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="329" t="s">
+      <c r="B93" s="330" t="s">
         <v>271</v>
       </c>
-      <c r="C93" s="329"/>
-      <c r="D93" s="329"/>
-      <c r="E93" s="329"/>
-      <c r="F93" s="329"/>
+      <c r="C93" s="330"/>
+      <c r="D93" s="330"/>
+      <c r="E93" s="330"/>
+      <c r="F93" s="330"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="47" t="s">
@@ -4401,13 +4401,13 @@
       <c r="F97" s="36"/>
     </row>
     <row r="99" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="331" t="s">
+      <c r="B99" s="329" t="s">
         <v>371</v>
       </c>
-      <c r="C99" s="331"/>
-      <c r="D99" s="331"/>
-      <c r="E99" s="331"/>
-      <c r="F99" s="331"/>
+      <c r="C99" s="329"/>
+      <c r="D99" s="329"/>
+      <c r="E99" s="329"/>
+      <c r="F99" s="329"/>
     </row>
     <row r="101" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B101" s="267" t="s">
@@ -4569,13 +4569,13 @@
       <c r="F112" s="36"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B114" s="330" t="s">
+      <c r="B114" s="332" t="s">
         <v>279</v>
       </c>
-      <c r="C114" s="330"/>
-      <c r="D114" s="330"/>
-      <c r="E114" s="330"/>
-      <c r="F114" s="330"/>
+      <c r="C114" s="332"/>
+      <c r="D114" s="332"/>
+      <c r="E114" s="332"/>
+      <c r="F114" s="332"/>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B115" s="241" t="s">
@@ -4662,12 +4662,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B93:F93"/>
@@ -4681,6 +4675,12 @@
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -11831,12 +11831,12 @@
       </c>
       <c r="C92" s="23">
         <f>C89/Market_Price</f>
-        <v>5.1217391304347833E-2</v>
+        <v>5.1666666666666673E-2</v>
       </c>
       <c r="E92" s="313"/>
       <c r="G92" s="23">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G89/Market_Price)</f>
-        <v>5.1217391304347833E-2</v>
+        <v>5.1666666666666673E-2</v>
       </c>
       <c r="H92" s="23">
         <f t="shared" si="38"/>
@@ -12915,30 +12915,30 @@
       </c>
       <c r="C120" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.3342925997552272E-2</v>
+        <v>3.3635407804548351E-2</v>
       </c>
       <c r="D120" s="27"/>
       <c r="E120" s="310"/>
       <c r="F120" s="27"/>
       <c r="G120" s="79">
         <f t="shared" ref="G120" si="49">IF(G$4="","",G119/Market_Price)</f>
-        <v>5.252875430347094E-2</v>
+        <v>5.2989532849992617E-2</v>
       </c>
       <c r="H120" s="79">
         <f t="shared" ref="H120" si="50">IF(H$4="","",H119/Market_Price)</f>
-        <v>1.5735121946153237E-2</v>
+        <v>1.5873149331645811E-2</v>
       </c>
       <c r="I120" s="79">
         <f t="shared" ref="I120" si="51">IF(I$4="","",I119/Market_Price)</f>
-        <v>2.7860950565207272E-2</v>
+        <v>2.8105344868410844E-2</v>
       </c>
       <c r="J120" s="79">
         <f t="shared" ref="J120" si="52">IF(J$4="","",J119/Market_Price)</f>
-        <v>9.7996923343862855E-2</v>
+        <v>9.8856545478458138E-2</v>
       </c>
       <c r="K120" s="79">
         <f t="shared" ref="K120" si="53">IF(K$4="","",K119/Market_Price)</f>
-        <v>7.0139039058707081E-2</v>
+        <v>7.0754293787292241E-2</v>
       </c>
       <c r="L120" s="79" t="str">
         <f t="shared" ref="L120" si="54">IF(L$4="","",L119/Market_Price)</f>
@@ -15228,7 +15228,7 @@
       </c>
       <c r="I3" s="272">
         <f>-Market_Price</f>
-        <v>-2.2999999999999998</v>
+        <v>-2.2799999999999998</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C21" s="165">
         <f>Market_Price</f>
-        <v>2.2999999999999998</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16085,7 +16085,7 @@
       </c>
       <c r="C86" s="274">
         <f>Market_Price</f>
-        <v>2.2999999999999998</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16098,7 +16098,7 @@
       </c>
       <c r="C87" s="273">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>8.8876330035536411E-2</v>
+        <v>9.2203750287490172E-2</v>
       </c>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCECFB0F-D83B-448B-876D-2F1854D02970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{509BF5AE-7406-4FAC-BAB1-8067A4F55478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3320,20 +3320,20 @@
     <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="5"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3692,7 +3692,7 @@
         <v>99</v>
       </c>
       <c r="C6" s="50">
-        <v>2.2799999999999998</v>
+        <v>2.29</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>43</v>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>3040.0003799999995</v>
+        <v>3053.3337150000002</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -3747,13 +3747,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="330" t="s">
+      <c r="B12" s="329" t="s">
         <v>290</v>
       </c>
-      <c r="C12" s="330"/>
-      <c r="D12" s="330"/>
-      <c r="E12" s="330"/>
-      <c r="F12" s="330"/>
+      <c r="C12" s="329"/>
+      <c r="D12" s="329"/>
+      <c r="E12" s="329"/>
+      <c r="F12" s="329"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3787,7 +3787,7 @@
         <v>2</v>
       </c>
       <c r="C17" s="50">
-        <v>1.06</v>
+        <v>1.0725774000000001</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="C20" s="259">
         <f>C123</f>
-        <v>1.7432969171114687</v>
+        <v>1.7610376174468114</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>344</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C21" s="288">
         <f ca="1">Scenarios!C87</f>
-        <v>9.2203750287490172E-2</v>
+        <v>9.4453005765433362E-2</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3856,22 +3856,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="330" t="s">
+      <c r="B25" s="329" t="s">
         <v>236</v>
       </c>
-      <c r="C25" s="330"/>
-      <c r="D25" s="330"/>
-      <c r="E25" s="330"/>
-      <c r="F25" s="330"/>
+      <c r="C25" s="329"/>
+      <c r="D25" s="329"/>
+      <c r="E25" s="329"/>
+      <c r="F25" s="329"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="331" t="s">
+      <c r="B26" s="333" t="s">
         <v>256</v>
       </c>
-      <c r="C26" s="331"/>
-      <c r="D26" s="331"/>
-      <c r="E26" s="331"/>
-      <c r="F26" s="331"/>
+      <c r="C26" s="333"/>
+      <c r="D26" s="333"/>
+      <c r="E26" s="333"/>
+      <c r="F26" s="333"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="241" t="s">
@@ -3883,13 +3883,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="329" t="s">
+      <c r="B29" s="331" t="s">
         <v>238</v>
       </c>
-      <c r="C29" s="329"/>
-      <c r="D29" s="329"/>
-      <c r="E29" s="329"/>
-      <c r="F29" s="329"/>
+      <c r="C29" s="331"/>
+      <c r="D29" s="331"/>
+      <c r="E29" s="331"/>
+      <c r="F29" s="331"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3909,13 +3909,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="329" t="s">
+      <c r="B32" s="331" t="s">
         <v>240</v>
       </c>
-      <c r="C32" s="329"/>
-      <c r="D32" s="329"/>
-      <c r="E32" s="329"/>
-      <c r="F32" s="329"/>
+      <c r="C32" s="331"/>
+      <c r="D32" s="331"/>
+      <c r="E32" s="331"/>
+      <c r="F32" s="331"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -3944,13 +3944,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="329" t="s">
+      <c r="B36" s="331" t="s">
         <v>243</v>
       </c>
-      <c r="C36" s="329"/>
-      <c r="D36" s="329"/>
-      <c r="E36" s="329"/>
-      <c r="F36" s="329"/>
+      <c r="C36" s="331"/>
+      <c r="D36" s="331"/>
+      <c r="E36" s="331"/>
+      <c r="F36" s="331"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -3966,13 +3966,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="329" t="s">
+      <c r="B39" s="331" t="s">
         <v>247</v>
       </c>
-      <c r="C39" s="329"/>
-      <c r="D39" s="329"/>
-      <c r="E39" s="329"/>
-      <c r="F39" s="329"/>
+      <c r="C39" s="331"/>
+      <c r="D39" s="331"/>
+      <c r="E39" s="331"/>
+      <c r="F39" s="331"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4006,13 +4006,13 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B45" s="329" t="s">
+      <c r="B45" s="331" t="s">
         <v>248</v>
       </c>
-      <c r="C45" s="329"/>
-      <c r="D45" s="329"/>
-      <c r="E45" s="329"/>
-      <c r="F45" s="329"/>
+      <c r="C45" s="331"/>
+      <c r="D45" s="331"/>
+      <c r="E45" s="331"/>
+      <c r="F45" s="331"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="47" t="s">
@@ -4028,13 +4028,13 @@
       </c>
     </row>
     <row r="48" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="329" t="s">
+      <c r="B48" s="331" t="s">
         <v>251</v>
       </c>
-      <c r="C48" s="333"/>
-      <c r="D48" s="333"/>
-      <c r="E48" s="333"/>
-      <c r="F48" s="333"/>
+      <c r="C48" s="332"/>
+      <c r="D48" s="332"/>
+      <c r="E48" s="332"/>
+      <c r="F48" s="332"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B49" s="47" t="s">
@@ -4063,13 +4063,13 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="330" t="s">
+      <c r="B52" s="329" t="s">
         <v>272</v>
       </c>
-      <c r="C52" s="330"/>
-      <c r="D52" s="330"/>
-      <c r="E52" s="330"/>
-      <c r="F52" s="330"/>
+      <c r="C52" s="329"/>
+      <c r="D52" s="329"/>
+      <c r="E52" s="329"/>
+      <c r="F52" s="329"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B53" s="47" t="s">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C120</f>
-        <v>3.3635407804548351E-2</v>
+        <v>3.3885885479174496E-2</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="C56" s="94">
         <f>Normalized_FCF!C92</f>
-        <v>5.1666666666666673E-2</v>
+        <v>5.1441048034934496E-2</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4130,22 +4130,22 @@
     </row>
     <row r="60" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="17"/>
-      <c r="B60" s="329" t="s">
+      <c r="B60" s="331" t="s">
         <v>307</v>
       </c>
-      <c r="C60" s="329"/>
-      <c r="D60" s="329"/>
-      <c r="E60" s="329"/>
-      <c r="F60" s="329"/>
+      <c r="C60" s="331"/>
+      <c r="D60" s="331"/>
+      <c r="E60" s="331"/>
+      <c r="F60" s="331"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B61" s="331" t="s">
+      <c r="B61" s="333" t="s">
         <v>263</v>
       </c>
-      <c r="C61" s="331"/>
-      <c r="D61" s="331"/>
-      <c r="E61" s="331"/>
-      <c r="F61" s="331"/>
+      <c r="C61" s="333"/>
+      <c r="D61" s="333"/>
+      <c r="E61" s="333"/>
+      <c r="F61" s="333"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B63" s="241" t="s">
@@ -4197,22 +4197,22 @@
       <c r="C68" s="125"/>
     </row>
     <row r="69" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="330" t="s">
+      <c r="B69" s="329" t="s">
         <v>315</v>
       </c>
-      <c r="C69" s="330"/>
-      <c r="D69" s="330"/>
-      <c r="E69" s="330"/>
-      <c r="F69" s="330"/>
+      <c r="C69" s="329"/>
+      <c r="D69" s="329"/>
+      <c r="E69" s="329"/>
+      <c r="F69" s="329"/>
     </row>
     <row r="70" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="330" t="s">
+      <c r="B70" s="329" t="s">
         <v>262</v>
       </c>
-      <c r="C70" s="330"/>
-      <c r="D70" s="330"/>
-      <c r="E70" s="330"/>
-      <c r="F70" s="330"/>
+      <c r="C70" s="329"/>
+      <c r="D70" s="329"/>
+      <c r="E70" s="329"/>
+      <c r="F70" s="329"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B71" s="47" t="s">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="C73" s="255">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.76688729794370236</v>
+        <v>0.77598677747309586</v>
       </c>
       <c r="D73" s="1" t="str">
         <f>Market_currency</f>
@@ -4249,13 +4249,13 @@
       <c r="A76" s="240"/>
     </row>
     <row r="77" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="330" t="s">
+      <c r="B77" s="329" t="s">
         <v>265</v>
       </c>
-      <c r="C77" s="330"/>
-      <c r="D77" s="330"/>
-      <c r="E77" s="330"/>
-      <c r="F77" s="330"/>
+      <c r="C77" s="329"/>
+      <c r="D77" s="329"/>
+      <c r="E77" s="329"/>
+      <c r="F77" s="329"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="C82" s="255">
         <f>C81*C28*Exchange_Rate/Common_Shares</f>
-        <v>2.7029201621349797E-2</v>
+        <v>2.7349915848210522E-2</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="C87" s="255">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.6133768602934926</v>
+        <v>1.632520337767696</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="C91" s="255">
         <f>C90*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.18098713337660832</v>
+        <v>0.18313463108541114</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Market_currency</f>
@@ -4369,13 +4369,13 @@
       </c>
     </row>
     <row r="93" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="330" t="s">
+      <c r="B93" s="329" t="s">
         <v>271</v>
       </c>
-      <c r="C93" s="330"/>
-      <c r="D93" s="330"/>
-      <c r="E93" s="330"/>
-      <c r="F93" s="330"/>
+      <c r="C93" s="329"/>
+      <c r="D93" s="329"/>
+      <c r="E93" s="329"/>
+      <c r="F93" s="329"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="47" t="s">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="C95" s="255">
         <f>Valuation_Model!C12</f>
-        <v>2.5342220899924537</v>
+        <v>2.5642918304779925</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4401,13 +4401,13 @@
       <c r="F97" s="36"/>
     </row>
     <row r="99" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="329" t="s">
+      <c r="B99" s="331" t="s">
         <v>371</v>
       </c>
-      <c r="C99" s="329"/>
-      <c r="D99" s="329"/>
-      <c r="E99" s="329"/>
-      <c r="F99" s="329"/>
+      <c r="C99" s="331"/>
+      <c r="D99" s="331"/>
+      <c r="E99" s="331"/>
+      <c r="F99" s="331"/>
     </row>
     <row r="101" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B101" s="267" t="s">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E102" s="265" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>3.12 HKD</v>
+        <v>3.16 HKD</v>
       </c>
       <c r="F102" s="266">
         <f>Valuation_Model!F74</f>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="E103" s="252" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>2.71 HKD</v>
+        <v>2.74 HKD</v>
       </c>
       <c r="F103" s="253">
         <f>Valuation_Model!F75</f>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="E104" s="252" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>2.59 HKD</v>
+        <v>2.62 HKD</v>
       </c>
       <c r="F104" s="253">
         <f>Valuation_Model!F76</f>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="E105" s="252" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>2.4 HKD</v>
+        <v>2.43 HKD</v>
       </c>
       <c r="F105" s="253">
         <f>Valuation_Model!F77</f>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="E106" s="252" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>2.26 HKD</v>
+        <v>2.29 HKD</v>
       </c>
       <c r="F106" s="253">
         <f>Valuation_Model!F78</f>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="C108" s="248">
         <f>Scenarios!C60</f>
-        <v>2.5836250727686179</v>
+        <v>2.6142810029480898</v>
       </c>
       <c r="D108" s="243" t="str">
         <f>Market_currency</f>
@@ -4569,13 +4569,13 @@
       <c r="F112" s="36"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B114" s="332" t="s">
+      <c r="B114" s="330" t="s">
         <v>279</v>
       </c>
-      <c r="C114" s="332"/>
-      <c r="D114" s="332"/>
-      <c r="E114" s="332"/>
-      <c r="F114" s="332"/>
+      <c r="C114" s="330"/>
+      <c r="D114" s="330"/>
+      <c r="E114" s="330"/>
+      <c r="F114" s="330"/>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B115" s="241" t="s">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="C122" s="247">
         <f>Scenarios!C82</f>
-        <v>1.4951533985929502</v>
+        <v>1.5128940989282929</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.35">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="C123" s="246">
         <f>Scenarios!C83</f>
-        <v>1.7432969171114687</v>
+        <v>1.7610376174468114</v>
       </c>
       <c r="D123" s="47" t="str">
         <f>Reporting_currency</f>
@@ -4657,11 +4657,17 @@
       </c>
       <c r="C124" s="158">
         <f>Scenarios!F83</f>
-        <v>-0.32525158720365399</v>
+        <v>-0.32637783946679311</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B93:F93"/>
@@ -4675,12 +4681,6 @@
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B110:F110"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -7746,11 +7746,11 @@
       </c>
       <c r="C47" s="151">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>2.4035247895594014</v>
+        <v>2.432043744925632</v>
       </c>
       <c r="D47" s="151">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.77481072514866</v>
+        <v>1.7958696915774193</v>
       </c>
       <c r="F47" s="292"/>
     </row>
@@ -8153,11 +8153,11 @@
       </c>
       <c r="C86" s="192">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-36038.94</v>
+        <v>-36466.559022600006</v>
       </c>
       <c r="D86" s="255">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-2.7029201621349797E-2</v>
+        <v>-2.7349915848210522E-2</v>
       </c>
       <c r="E86" s="277" t="str">
         <f>Market_currency</f>
@@ -8170,11 +8170,11 @@
       </c>
       <c r="C87" s="192">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>2151169.4159541335</v>
+        <v>2176694.055776984</v>
       </c>
       <c r="D87" s="255">
         <f>C87*$H$1/Common_Shares</f>
-        <v>1.6133768602934926</v>
+        <v>1.6325203377676956</v>
       </c>
       <c r="E87" s="277" t="str">
         <f>Market_currency</f>
@@ -8187,11 +8187,11 @@
       </c>
       <c r="C88" s="192">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>241316.20800000001</v>
+        <v>244179.53863632001</v>
       </c>
       <c r="D88" s="255">
         <f>C88*$H$1/Common_Shares</f>
-        <v>0.18098713337660832</v>
+        <v>0.18313463108541111</v>
       </c>
       <c r="E88" s="277" t="str">
         <f>Market_currency</f>
@@ -8204,11 +8204,11 @@
       </c>
       <c r="C89" s="191">
         <f>SUM(C86:C88)</f>
-        <v>2356446.6839541337</v>
+        <v>2384407.0353907039</v>
       </c>
       <c r="D89" s="279">
         <f>SUM(D86:D88)</f>
-        <v>1.767334792048751</v>
+        <v>1.7883050530048963</v>
       </c>
       <c r="E89" s="277" t="str">
         <f>Market_currency</f>
@@ -11831,12 +11831,12 @@
       </c>
       <c r="C92" s="23">
         <f>C89/Market_Price</f>
-        <v>5.1666666666666673E-2</v>
+        <v>5.1441048034934496E-2</v>
       </c>
       <c r="E92" s="313"/>
       <c r="G92" s="23">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G89/Market_Price)</f>
-        <v>5.1666666666666673E-2</v>
+        <v>5.1441048034934496E-2</v>
       </c>
       <c r="H92" s="23">
         <f t="shared" si="38"/>
@@ -12858,30 +12858,30 @@
       </c>
       <c r="C119" s="182">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>7.668872979437022E-2</v>
+        <v>7.759867774730958E-2</v>
       </c>
       <c r="D119" s="27"/>
       <c r="E119" s="310"/>
       <c r="F119" s="27"/>
       <c r="G119" s="182">
         <f t="shared" ref="G119:Q119" si="48">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.12081613489798315</v>
+        <v>0.1222496753272906</v>
       </c>
       <c r="H119" s="182">
         <f t="shared" si="48"/>
-        <v>3.6190780476152443E-2</v>
+        <v>3.6620201157624863E-2</v>
       </c>
       <c r="I119" s="182">
         <f t="shared" si="48"/>
-        <v>6.4080186299976721E-2</v>
+        <v>6.4840527936928918E-2</v>
       </c>
       <c r="J119" s="182">
         <f t="shared" si="48"/>
-        <v>0.22539292369088454</v>
+        <v>0.22806731704789374</v>
       </c>
       <c r="K119" s="182">
         <f t="shared" si="48"/>
-        <v>0.16131978983502629</v>
+        <v>0.16323392523565938</v>
       </c>
       <c r="L119" s="182" t="str">
         <f t="shared" si="48"/>
@@ -12915,30 +12915,30 @@
       </c>
       <c r="C120" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.3635407804548351E-2</v>
+        <v>3.3885885479174496E-2</v>
       </c>
       <c r="D120" s="27"/>
       <c r="E120" s="310"/>
       <c r="F120" s="27"/>
       <c r="G120" s="79">
         <f t="shared" ref="G120" si="49">IF(G$4="","",G119/Market_Price)</f>
-        <v>5.2989532849992617E-2</v>
+        <v>5.3384137697506814E-2</v>
       </c>
       <c r="H120" s="79">
         <f t="shared" ref="H120" si="50">IF(H$4="","",H119/Market_Price)</f>
-        <v>1.5873149331645811E-2</v>
+        <v>1.5991354217303431E-2</v>
       </c>
       <c r="I120" s="79">
         <f t="shared" ref="I120" si="51">IF(I$4="","",I119/Market_Price)</f>
-        <v>2.8105344868410844E-2</v>
+        <v>2.8314641020492977E-2</v>
       </c>
       <c r="J120" s="79">
         <f t="shared" ref="J120" si="52">IF(J$4="","",J119/Market_Price)</f>
-        <v>9.8856545478458138E-2</v>
+        <v>9.959271486807586E-2</v>
       </c>
       <c r="K120" s="79">
         <f t="shared" ref="K120" si="53">IF(K$4="","",K119/Market_Price)</f>
-        <v>7.0754293787292241E-2</v>
+        <v>7.1281190059239899E-2</v>
       </c>
       <c r="L120" s="79" t="str">
         <f t="shared" ref="L120" si="54">IF(L$4="","",L119/Market_Price)</f>
@@ -13821,7 +13821,7 @@
       </c>
       <c r="C11" s="238">
         <f>Exchange_Rate</f>
-        <v>1.06</v>
+        <v>1.0725774000000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -13835,7 +13835,7 @@
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>2.5342220899924537</v>
+        <v>2.5642918304779925</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -13888,7 +13888,7 @@
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>2.5822507355943083</v>
+        <v>2.6128903586149343</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14824,23 +14824,23 @@
       </c>
       <c r="B65" s="128">
         <f>C12</f>
-        <v>2.5342220899924537</v>
+        <v>2.5642918304779925</v>
       </c>
       <c r="C65" s="128">
         <f>C12</f>
-        <v>2.5342220899924537</v>
+        <v>2.5642918304779925</v>
       </c>
       <c r="D65" s="128">
         <f>C12</f>
-        <v>2.5342220899924537</v>
+        <v>2.5642918304779925</v>
       </c>
       <c r="E65" s="145">
         <f>C12</f>
-        <v>2.5342220899924537</v>
+        <v>2.5642918304779925</v>
       </c>
       <c r="F65" s="128">
         <f>C12</f>
-        <v>2.5342220899924537</v>
+        <v>2.5642918304779925</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -14851,23 +14851,23 @@
       </c>
       <c r="B66" s="128">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.4144631798831471</v>
+        <v>2.4431119244101871</v>
       </c>
       <c r="C66" s="128">
         <f t="shared" si="4"/>
-        <v>2.4601747178559918</v>
+        <v>2.489365851343126</v>
       </c>
       <c r="D66" s="128">
         <f t="shared" si="4"/>
-        <v>2.5605009597708444</v>
+        <v>2.5908825114419973</v>
       </c>
       <c r="E66" s="128">
         <f t="shared" si="4"/>
-        <v>2.6156691196726358</v>
+        <v>2.6467052675837404</v>
       </c>
       <c r="F66" s="128">
         <f t="shared" si="4"/>
-        <v>2.6745727842647127</v>
+        <v>2.7063078519409496</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -14878,23 +14878,23 @@
       </c>
       <c r="B67" s="128">
         <f t="shared" si="4"/>
-        <v>2.3321435873277712</v>
+        <v>2.3598155710591455</v>
       </c>
       <c r="C67" s="128">
         <f t="shared" si="4"/>
-        <v>2.4022490449357066</v>
+        <v>2.4307528629902109</v>
       </c>
       <c r="D67" s="128">
         <f t="shared" si="4"/>
-        <v>2.5871648288186599</v>
+        <v>2.6178627598733617</v>
       </c>
       <c r="E67" s="128">
         <f t="shared" si="4"/>
-        <v>2.7098279393766536</v>
+        <v>2.7419813260980841</v>
       </c>
       <c r="F67" s="128">
         <f t="shared" si="4"/>
-        <v>2.8594571666104871</v>
+        <v>2.8933859746928712</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -14905,23 +14905,23 @@
       </c>
       <c r="B68" s="128">
         <f t="shared" si="4"/>
-        <v>2.2606526307209904</v>
+        <v>2.2874763405300755</v>
       </c>
       <c r="C68" s="128">
         <f t="shared" si="4"/>
-        <v>2.3478175319216996</v>
+        <v>2.3756754943990508</v>
       </c>
       <c r="D68" s="128">
         <f t="shared" si="4"/>
-        <v>2.6173430189360278</v>
+        <v>2.6483990284514674</v>
       </c>
       <c r="E68" s="128">
         <f t="shared" si="4"/>
-        <v>2.8282509612054145</v>
+        <v>2.8618094929407589</v>
       </c>
       <c r="F68" s="128">
         <f t="shared" si="4"/>
-        <v>3.1196111330432204</v>
+        <v>3.156626790651464</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -14932,23 +14932,23 @@
       </c>
       <c r="B69" s="128">
         <f t="shared" si="4"/>
-        <v>2.2087912008462367</v>
+        <v>2.2349995503269193</v>
       </c>
       <c r="C69" s="128">
         <f t="shared" si="4"/>
-        <v>2.3056057580860974</v>
+        <v>2.3329628579556752</v>
       </c>
       <c r="D69" s="128">
         <f t="shared" si="4"/>
-        <v>2.6454198434941092</v>
+        <v>2.6768089977767158</v>
       </c>
       <c r="E69" s="128">
         <f t="shared" si="4"/>
-        <v>2.9516032454343923</v>
+        <v>2.9866254102071537</v>
       </c>
       <c r="F69" s="128">
         <f t="shared" si="4"/>
-        <v>3.426501589213339</v>
+        <v>3.4671586468436901</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -14959,23 +14959,23 @@
       </c>
       <c r="B70" s="128">
         <f t="shared" si="4"/>
-        <v>2.1738500447216489</v>
+        <v>2.1996438009032357</v>
       </c>
       <c r="C70" s="128">
         <f t="shared" si="4"/>
-        <v>2.2755612964231884</v>
+        <v>2.3025619045832197</v>
       </c>
       <c r="D70" s="128">
         <f t="shared" si="4"/>
-        <v>2.6692553554863836</v>
+        <v>2.7009273293619445</v>
       </c>
       <c r="E70" s="128">
         <f t="shared" si="4"/>
-        <v>3.0695931327232318</v>
+        <v>3.1060153031642823</v>
       </c>
       <c r="F70" s="128">
         <f t="shared" si="4"/>
-        <v>3.7624117284263354</v>
+        <v>3.8070545183066273</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -14985,23 +14985,23 @@
       </c>
       <c r="B71" s="128">
         <f t="shared" si="4"/>
-        <v>2.1511499816522868</v>
+        <v>2.1766743908779791</v>
       </c>
       <c r="C71" s="128">
         <f t="shared" si="4"/>
-        <v>2.2551587849686365</v>
+        <v>2.2819173077064332</v>
       </c>
       <c r="D71" s="128">
         <f t="shared" si="4"/>
-        <v>2.6884442158980408</v>
+        <v>2.7203438746537354</v>
       </c>
       <c r="E71" s="128">
         <f t="shared" si="4"/>
-        <v>3.1772543791020067</v>
+        <v>3.2149540010149482</v>
       </c>
       <c r="F71" s="128">
         <f t="shared" si="4"/>
-        <v>4.1163408076290713</v>
+        <v>4.1651831329817828</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15036,7 +15036,7 @@
       </c>
       <c r="E74" s="139">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>3.1196111330432204</v>
+        <v>3.156626790651464</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
@@ -15058,7 +15058,7 @@
       </c>
       <c r="E75" s="139">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>2.7098279393766536</v>
+        <v>2.7419813260980841</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -15081,7 +15081,7 @@
       </c>
       <c r="E76" s="139">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>2.5871648288186599</v>
+        <v>2.6178627598733617</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15104,7 +15104,7 @@
       </c>
       <c r="E77" s="139">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>2.4022490449357066</v>
+        <v>2.4307528629902109</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -15127,7 +15127,7 @@
       </c>
       <c r="E78" s="139">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.2606526307209904</v>
+        <v>2.2874763405300755</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
@@ -15228,7 +15228,7 @@
       </c>
       <c r="I3" s="272">
         <f>-Market_Price</f>
-        <v>-2.2799999999999998</v>
+        <v>-2.29</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -15277,7 +15277,7 @@
       </c>
       <c r="I6" s="272">
         <f t="shared" si="0"/>
-        <v>2.7014250727686178</v>
+        <v>2.7320810029480898</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C21" s="165">
         <f>Market_Price</f>
-        <v>2.2799999999999998</v>
+        <v>2.29</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -15483,7 +15483,7 @@
       </c>
       <c r="C22" s="165">
         <f>Valuation_Model!C12</f>
-        <v>2.5342220899924537</v>
+        <v>2.5642918304779925</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="C27" s="165">
         <f>Valuation_Model!E76</f>
-        <v>2.5871648288186599</v>
+        <v>2.6178627598733617</v>
       </c>
       <c r="D27" s="165" t="str">
         <f>Market_currency</f>
@@ -15588,7 +15588,7 @@
       </c>
       <c r="C33" s="165">
         <f>Valuation_Model!E77</f>
-        <v>2.4022490449357066</v>
+        <v>2.4307528629902109</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="C39" s="165">
         <f>Valuation_Model!E75</f>
-        <v>2.7098279393766536</v>
+        <v>2.7419813260980841</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -15673,7 +15673,7 @@
       </c>
       <c r="C42" s="159">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>2.5900932388757152</v>
+        <v>2.6208259168970698</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -15747,7 +15747,7 @@
       </c>
       <c r="C51" s="165">
         <f>Valuation_Model!E78</f>
-        <v>2.2606526307209904</v>
+        <v>2.2874763405300755</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -15805,7 +15805,7 @@
       </c>
       <c r="C57" s="165">
         <f>Valuation_Model!E74</f>
-        <v>3.1196111330432204</v>
+        <v>3.156626790651464</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="C60" s="159">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>2.5836250727686179</v>
+        <v>2.6142810029480898</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -15891,7 +15891,7 @@
       </c>
       <c r="C66" s="165">
         <f>Valuation_Model!C18</f>
-        <v>2.5822507355943083</v>
+        <v>2.6128903586149343</v>
       </c>
       <c r="D66" s="165" t="str">
         <f>Market_currency</f>
@@ -16047,7 +16047,7 @@
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
-        <v>1.4951533985929502</v>
+        <v>1.5128940989282929</v>
       </c>
       <c r="D82" s="120"/>
     </row>
@@ -16057,7 +16057,7 @@
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
-        <v>1.7432969171114687</v>
+        <v>1.7610376174468114</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16068,7 +16068,7 @@
       </c>
       <c r="F83" s="270">
         <f>(C83/C60-1)</f>
-        <v>-0.32525158720365399</v>
+        <v>-0.32637783946679311</v>
       </c>
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.35">
@@ -16085,7 +16085,7 @@
       </c>
       <c r="C86" s="274">
         <f>Market_Price</f>
-        <v>2.2799999999999998</v>
+        <v>2.29</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16098,7 +16098,7 @@
       </c>
       <c r="C87" s="273">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.2203750287490172E-2</v>
+        <v>9.4453005765433362E-2</v>
       </c>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{509BF5AE-7406-4FAC-BAB1-8067A4F55478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6848EF6F-6634-4191-994A-B4D2745ABEB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1986,7 +1986,7 @@
     <numFmt numFmtId="191" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
     <numFmt numFmtId="192" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="58" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2410,13 +2410,7 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF00B050"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <i/>
       <u/>
       <sz val="10"/>
@@ -2632,7 +2626,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="339">
+  <cellXfs count="342">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3234,9 +3228,6 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="187" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3304,21 +3295,27 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="5"/>
+    <xf numFmtId="187" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3645,10 +3642,10 @@
         <v>45730</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="293" t="s">
+      <c r="E1" s="292" t="s">
         <v>354</v>
       </c>
-      <c r="F1" s="294" t="s">
+      <c r="F1" s="293" t="s">
         <v>373</v>
       </c>
     </row>
@@ -3747,13 +3744,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="329" t="s">
+      <c r="B12" s="332" t="s">
         <v>290</v>
       </c>
-      <c r="C12" s="329"/>
-      <c r="D12" s="329"/>
-      <c r="E12" s="329"/>
-      <c r="F12" s="329"/>
+      <c r="C12" s="332"/>
+      <c r="D12" s="332"/>
+      <c r="E12" s="332"/>
+      <c r="F12" s="332"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3787,7 +3784,7 @@
         <v>2</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0725774000000001</v>
+        <v>1.0725773999999999</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -3819,15 +3816,15 @@
         <v>Target Buy Price (HKD):</v>
       </c>
       <c r="C20" s="259">
-        <f>C123</f>
-        <v>1.7610376174468114</v>
+        <f ca="1">C123</f>
+        <v>41.714272051273504</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="E20" s="289">
-        <f>Scenarios!C76</f>
-        <v>3</v>
+      <c r="E20" s="323">
+        <f ca="1">Scenarios!C76</f>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -3836,7 +3833,7 @@
       </c>
       <c r="C21" s="288">
         <f ca="1">Scenarios!C87</f>
-        <v>9.4453005765433362E-2</v>
+        <v>2.2492801309755399</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3856,22 +3853,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="329" t="s">
+      <c r="B25" s="332" t="s">
         <v>236</v>
       </c>
-      <c r="C25" s="329"/>
-      <c r="D25" s="329"/>
-      <c r="E25" s="329"/>
-      <c r="F25" s="329"/>
+      <c r="C25" s="332"/>
+      <c r="D25" s="332"/>
+      <c r="E25" s="332"/>
+      <c r="F25" s="332"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="333" t="s">
+      <c r="B26" s="336" t="s">
         <v>256</v>
       </c>
-      <c r="C26" s="333"/>
-      <c r="D26" s="333"/>
-      <c r="E26" s="333"/>
-      <c r="F26" s="333"/>
+      <c r="C26" s="336"/>
+      <c r="D26" s="336"/>
+      <c r="E26" s="336"/>
+      <c r="F26" s="336"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="241" t="s">
@@ -3883,13 +3880,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="331" t="s">
+      <c r="B29" s="334" t="s">
         <v>238</v>
       </c>
-      <c r="C29" s="331"/>
-      <c r="D29" s="331"/>
-      <c r="E29" s="331"/>
-      <c r="F29" s="331"/>
+      <c r="C29" s="334"/>
+      <c r="D29" s="334"/>
+      <c r="E29" s="334"/>
+      <c r="F29" s="334"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3909,13 +3906,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="331" t="s">
+      <c r="B32" s="334" t="s">
         <v>240</v>
       </c>
-      <c r="C32" s="331"/>
-      <c r="D32" s="331"/>
-      <c r="E32" s="331"/>
-      <c r="F32" s="331"/>
+      <c r="C32" s="334"/>
+      <c r="D32" s="334"/>
+      <c r="E32" s="334"/>
+      <c r="F32" s="334"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -3944,13 +3941,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="331" t="s">
+      <c r="B36" s="334" t="s">
         <v>243</v>
       </c>
-      <c r="C36" s="331"/>
-      <c r="D36" s="331"/>
-      <c r="E36" s="331"/>
-      <c r="F36" s="331"/>
+      <c r="C36" s="334"/>
+      <c r="D36" s="334"/>
+      <c r="E36" s="334"/>
+      <c r="F36" s="334"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -3966,13 +3963,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="331" t="s">
+      <c r="B39" s="334" t="s">
         <v>247</v>
       </c>
-      <c r="C39" s="331"/>
-      <c r="D39" s="331"/>
-      <c r="E39" s="331"/>
-      <c r="F39" s="331"/>
+      <c r="C39" s="334"/>
+      <c r="D39" s="334"/>
+      <c r="E39" s="334"/>
+      <c r="F39" s="334"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4006,13 +4003,13 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B45" s="331" t="s">
+      <c r="B45" s="334" t="s">
         <v>248</v>
       </c>
-      <c r="C45" s="331"/>
-      <c r="D45" s="331"/>
-      <c r="E45" s="331"/>
-      <c r="F45" s="331"/>
+      <c r="C45" s="334"/>
+      <c r="D45" s="334"/>
+      <c r="E45" s="334"/>
+      <c r="F45" s="334"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="47" t="s">
@@ -4028,13 +4025,13 @@
       </c>
     </row>
     <row r="48" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="331" t="s">
+      <c r="B48" s="334" t="s">
         <v>251</v>
       </c>
-      <c r="C48" s="332"/>
-      <c r="D48" s="332"/>
-      <c r="E48" s="332"/>
-      <c r="F48" s="332"/>
+      <c r="C48" s="335"/>
+      <c r="D48" s="335"/>
+      <c r="E48" s="335"/>
+      <c r="F48" s="335"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B49" s="47" t="s">
@@ -4063,13 +4060,13 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="329" t="s">
+      <c r="B52" s="332" t="s">
         <v>272</v>
       </c>
-      <c r="C52" s="329"/>
-      <c r="D52" s="329"/>
-      <c r="E52" s="329"/>
-      <c r="F52" s="329"/>
+      <c r="C52" s="332"/>
+      <c r="D52" s="332"/>
+      <c r="E52" s="332"/>
+      <c r="F52" s="332"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B53" s="47" t="s">
@@ -4103,7 +4100,7 @@
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C120</f>
-        <v>3.3885885479174496E-2</v>
+        <v>3.3885885479174489E-2</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
@@ -4130,22 +4127,22 @@
     </row>
     <row r="60" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="17"/>
-      <c r="B60" s="331" t="s">
+      <c r="B60" s="334" t="s">
         <v>307</v>
       </c>
-      <c r="C60" s="331"/>
-      <c r="D60" s="331"/>
-      <c r="E60" s="331"/>
-      <c r="F60" s="331"/>
+      <c r="C60" s="334"/>
+      <c r="D60" s="334"/>
+      <c r="E60" s="334"/>
+      <c r="F60" s="334"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B61" s="333" t="s">
+      <c r="B61" s="336" t="s">
         <v>263</v>
       </c>
-      <c r="C61" s="333"/>
-      <c r="D61" s="333"/>
-      <c r="E61" s="333"/>
-      <c r="F61" s="333"/>
+      <c r="C61" s="336"/>
+      <c r="D61" s="336"/>
+      <c r="E61" s="336"/>
+      <c r="F61" s="336"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B63" s="241" t="s">
@@ -4156,7 +4153,7 @@
       <c r="B64" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="C64" s="322">
+      <c r="C64" s="321">
         <v>0.08</v>
       </c>
     </row>
@@ -4168,7 +4165,7 @@
         <f>IF(D65="Y",1%,0)</f>
         <v>0.01</v>
       </c>
-      <c r="D65" s="296" t="s">
+      <c r="D65" s="295" t="s">
         <v>311</v>
       </c>
     </row>
@@ -4180,7 +4177,7 @@
         <f>IF(D66="Y",1%,0)</f>
         <v>0.01</v>
       </c>
-      <c r="D66" s="296" t="s">
+      <c r="D66" s="295" t="s">
         <v>311</v>
       </c>
     </row>
@@ -4197,22 +4194,22 @@
       <c r="C68" s="125"/>
     </row>
     <row r="69" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="329" t="s">
+      <c r="B69" s="332" t="s">
         <v>315</v>
       </c>
-      <c r="C69" s="329"/>
-      <c r="D69" s="329"/>
-      <c r="E69" s="329"/>
-      <c r="F69" s="329"/>
+      <c r="C69" s="332"/>
+      <c r="D69" s="332"/>
+      <c r="E69" s="332"/>
+      <c r="F69" s="332"/>
     </row>
     <row r="70" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="329" t="s">
+      <c r="B70" s="332" t="s">
         <v>262</v>
       </c>
-      <c r="C70" s="329"/>
-      <c r="D70" s="329"/>
-      <c r="E70" s="329"/>
-      <c r="F70" s="329"/>
+      <c r="C70" s="332"/>
+      <c r="D70" s="332"/>
+      <c r="E70" s="332"/>
+      <c r="F70" s="332"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B71" s="47" t="s">
@@ -4228,7 +4225,7 @@
       </c>
       <c r="C73" s="255">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.77598677747309586</v>
+        <v>0.77598677747309575</v>
       </c>
       <c r="D73" s="1" t="str">
         <f>Market_currency</f>
@@ -4249,13 +4246,13 @@
       <c r="A76" s="240"/>
     </row>
     <row r="77" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="329" t="s">
+      <c r="B77" s="332" t="s">
         <v>265</v>
       </c>
-      <c r="C77" s="329"/>
-      <c r="D77" s="329"/>
-      <c r="E77" s="329"/>
-      <c r="F77" s="329"/>
+      <c r="C77" s="332"/>
+      <c r="D77" s="332"/>
+      <c r="E77" s="332"/>
+      <c r="F77" s="332"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
@@ -4286,7 +4283,7 @@
       </c>
       <c r="C82" s="255">
         <f>C81*C28*Exchange_Rate/Common_Shares</f>
-        <v>2.7349915848210522E-2</v>
+        <v>2.7349915848210515E-2</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4330,7 +4327,7 @@
       </c>
       <c r="C87" s="255">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.632520337767696</v>
+        <v>1.6325203377676956</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4361,7 +4358,7 @@
       </c>
       <c r="C91" s="255">
         <f>C90*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.18313463108541114</v>
+        <v>0.18313463108541109</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Market_currency</f>
@@ -4369,13 +4366,13 @@
       </c>
     </row>
     <row r="93" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="329" t="s">
+      <c r="B93" s="332" t="s">
         <v>271</v>
       </c>
-      <c r="C93" s="329"/>
-      <c r="D93" s="329"/>
-      <c r="E93" s="329"/>
-      <c r="F93" s="329"/>
+      <c r="C93" s="332"/>
+      <c r="D93" s="332"/>
+      <c r="E93" s="332"/>
+      <c r="F93" s="332"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="47" t="s">
@@ -4383,7 +4380,7 @@
       </c>
       <c r="C95" s="255">
         <f>Valuation_Model!C12</f>
-        <v>2.5642918304779925</v>
+        <v>2.564291830477992</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4401,13 +4398,13 @@
       <c r="F97" s="36"/>
     </row>
     <row r="99" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="331" t="s">
+      <c r="B99" s="334" t="s">
         <v>371</v>
       </c>
-      <c r="C99" s="331"/>
-      <c r="D99" s="331"/>
-      <c r="E99" s="331"/>
-      <c r="F99" s="331"/>
+      <c r="C99" s="334"/>
+      <c r="D99" s="334"/>
+      <c r="E99" s="334"/>
+      <c r="F99" s="334"/>
     </row>
     <row r="101" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B101" s="267" t="s">
@@ -4542,7 +4539,7 @@
       </c>
       <c r="C108" s="248">
         <f>Scenarios!C60</f>
-        <v>2.6142810029480898</v>
+        <v>2.6142810029480894</v>
       </c>
       <c r="D108" s="243" t="str">
         <f>Market_currency</f>
@@ -4550,13 +4547,13 @@
       </c>
     </row>
     <row r="110" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B110" s="334" t="s">
+      <c r="B110" s="337" t="s">
         <v>372</v>
       </c>
-      <c r="C110" s="334"/>
-      <c r="D110" s="334"/>
-      <c r="E110" s="334"/>
-      <c r="F110" s="334"/>
+      <c r="C110" s="337"/>
+      <c r="D110" s="337"/>
+      <c r="E110" s="337"/>
+      <c r="F110" s="337"/>
     </row>
     <row r="112" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A112" s="254" t="s">
@@ -4569,13 +4566,13 @@
       <c r="F112" s="36"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B114" s="330" t="s">
+      <c r="B114" s="333" t="s">
         <v>279</v>
       </c>
-      <c r="C114" s="330"/>
-      <c r="D114" s="330"/>
-      <c r="E114" s="330"/>
-      <c r="F114" s="330"/>
+      <c r="C114" s="333"/>
+      <c r="D114" s="333"/>
+      <c r="E114" s="333"/>
+      <c r="F114" s="333"/>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B115" s="241" t="s">
@@ -4587,7 +4584,7 @@
         <v>280</v>
       </c>
       <c r="C116" s="258">
-        <f>E20</f>
+        <f ca="1">E20</f>
         <v>3</v>
       </c>
     </row>
@@ -4620,22 +4617,22 @@
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B121" s="243" t="str">
-        <f>"PV("&amp;C116&amp;" yrs of Dividends)"</f>
+        <f ca="1">"PV("&amp;C116&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C121" s="247">
-        <f>Scenarios!C81</f>
-        <v>0.24814351851851849</v>
+        <f ca="1">Scenarios!C81</f>
+        <v>1.2217592592592592</v>
       </c>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B122" s="243" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C116&amp;")"</f>
+        <f ca="1">"+ PV(Equity Value realized at year "&amp;C116&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C122" s="247">
-        <f>Scenarios!C82</f>
-        <v>1.5128940989282929</v>
+        <f ca="1">Scenarios!C82</f>
+        <v>40.492512792014246</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.35">
@@ -4643,8 +4640,8 @@
         <v>275</v>
       </c>
       <c r="C123" s="246">
-        <f>Scenarios!C83</f>
-        <v>1.7610376174468114</v>
+        <f ca="1">Scenarios!C83</f>
+        <v>41.714272051273504</v>
       </c>
       <c r="D123" s="47" t="str">
         <f>Reporting_currency</f>
@@ -4656,8 +4653,8 @@
         <v>277</v>
       </c>
       <c r="C124" s="158">
-        <f>Scenarios!F83</f>
-        <v>-0.32637783946679311</v>
+        <f ca="1">Scenarios!F83</f>
+        <v>-0.40383537427352023</v>
       </c>
     </row>
   </sheetData>
@@ -7028,7 +7025,7 @@
       <c r="C4" s="19">
         <v>180994</v>
       </c>
-      <c r="D4" s="305">
+      <c r="D4" s="304">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -7038,7 +7035,7 @@
       <c r="G4" s="19">
         <v>2385307</v>
       </c>
-      <c r="H4" s="305">
+      <c r="H4" s="304">
         <v>0.9</v>
       </c>
     </row>
@@ -7049,7 +7046,7 @@
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="305">
+      <c r="D5" s="304">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -7059,7 +7056,7 @@
       <c r="G5" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="305">
+      <c r="H5" s="304">
         <v>0.7</v>
       </c>
     </row>
@@ -7070,7 +7067,7 @@
       <c r="C6" s="19">
         <v>158110</v>
       </c>
-      <c r="D6" s="305">
+      <c r="D6" s="304">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -7080,7 +7077,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="305">
+      <c r="H6" s="304">
         <v>0.6</v>
       </c>
     </row>
@@ -7091,7 +7088,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="305">
+      <c r="D7" s="304">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -7101,7 +7098,7 @@
       <c r="G7" s="19">
         <v>253051</v>
       </c>
-      <c r="H7" s="305">
+      <c r="H7" s="304">
         <v>0.6</v>
       </c>
     </row>
@@ -7112,7 +7109,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="305">
+      <c r="D8" s="304">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -7122,7 +7119,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="305">
+      <c r="H8" s="304">
         <v>0.6</v>
       </c>
     </row>
@@ -7133,7 +7130,7 @@
       <c r="C9" s="19">
         <v>0</v>
       </c>
-      <c r="D9" s="305">
+      <c r="D9" s="304">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -7143,7 +7140,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="305">
+      <c r="H9" s="304">
         <v>0.6</v>
       </c>
     </row>
@@ -7154,10 +7151,10 @@
       <c r="C10" s="19">
         <v>5912</v>
       </c>
-      <c r="D10" s="305">
+      <c r="D10" s="304">
         <v>0.9</v>
       </c>
-      <c r="H10" s="306"/>
+      <c r="H10" s="305"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
@@ -7166,10 +7163,10 @@
       <c r="C11" s="19">
         <v>0</v>
       </c>
-      <c r="D11" s="305">
+      <c r="D11" s="304">
         <v>0.05</v>
       </c>
-      <c r="H11" s="306"/>
+      <c r="H11" s="305"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="82" t="s">
@@ -7227,7 +7224,7 @@
       <c r="C15" s="19">
         <v>0</v>
       </c>
-      <c r="D15" s="305">
+      <c r="D15" s="304">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -7236,7 +7233,7 @@
       <c r="G15" s="19">
         <v>279425</v>
       </c>
-      <c r="H15" s="305">
+      <c r="H15" s="304">
         <v>0.8</v>
       </c>
     </row>
@@ -7247,7 +7244,7 @@
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="305">
+      <c r="D16" s="304">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -7256,7 +7253,7 @@
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="305">
+      <c r="H16" s="304">
         <v>0.6</v>
       </c>
     </row>
@@ -7267,7 +7264,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="305">
+      <c r="D17" s="304">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -7276,7 +7273,7 @@
       <c r="G17" s="19">
         <v>126127</v>
       </c>
-      <c r="H17" s="305">
+      <c r="H17" s="304">
         <v>0.6</v>
       </c>
     </row>
@@ -7287,7 +7284,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="305">
+      <c r="D18" s="304">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -7296,7 +7293,7 @@
       <c r="G18" s="19">
         <v>0</v>
       </c>
-      <c r="H18" s="305">
+      <c r="H18" s="304">
         <v>0.1</v>
       </c>
     </row>
@@ -7307,7 +7304,7 @@
       <c r="C19" s="19">
         <v>193915</v>
       </c>
-      <c r="D19" s="305">
+      <c r="D19" s="304">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -7316,7 +7313,7 @@
       <c r="G19" s="19">
         <v>1500</v>
       </c>
-      <c r="H19" s="305">
+      <c r="H19" s="304">
         <v>0.1</v>
       </c>
     </row>
@@ -7327,7 +7324,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="305">
+      <c r="D20" s="304">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -7336,7 +7333,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="305">
+      <c r="H20" s="304">
         <v>0.2</v>
       </c>
     </row>
@@ -7347,7 +7344,7 @@
       <c r="C21" s="19">
         <v>9704</v>
       </c>
-      <c r="D21" s="305">
+      <c r="D21" s="304">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -7356,7 +7353,7 @@
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="305">
+      <c r="H21" s="304">
         <v>0.1</v>
       </c>
     </row>
@@ -7367,10 +7364,10 @@
       <c r="C22" s="19">
         <v>76124</v>
       </c>
-      <c r="D22" s="305">
+      <c r="D22" s="304">
         <v>0.9</v>
       </c>
-      <c r="H22" s="306"/>
+      <c r="H22" s="305"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
@@ -7379,10 +7376,10 @@
       <c r="C23" s="19">
         <v>0</v>
       </c>
-      <c r="D23" s="305">
-        <v>0</v>
-      </c>
-      <c r="H23" s="306"/>
+      <c r="D23" s="304">
+        <v>0</v>
+      </c>
+      <c r="H23" s="305"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="82" t="s">
@@ -7721,7 +7718,7 @@
       <c r="D45" s="210" t="s">
         <v>292</v>
       </c>
-      <c r="F45" s="297" t="s">
+      <c r="F45" s="296" t="s">
         <v>63</v>
       </c>
     </row>
@@ -7737,7 +7734,7 @@
         <f>H29</f>
         <v>2232466.6000000006</v>
       </c>
-      <c r="F46" s="292"/>
+      <c r="F46" s="291"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B47" s="1" t="str">
@@ -7746,16 +7743,16 @@
       </c>
       <c r="C47" s="151">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>2.432043744925632</v>
+        <v>2.4320437449256316</v>
       </c>
       <c r="D47" s="151">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.7958696915774193</v>
-      </c>
-      <c r="F47" s="292"/>
+        <v>1.7958696915774188</v>
+      </c>
+      <c r="F47" s="291"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F48" s="292"/>
+      <c r="F48" s="291"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="162" t="s">
@@ -7768,7 +7765,7 @@
         <v>100</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="292"/>
+      <c r="F49" s="291"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="8" t="s">
@@ -7782,7 +7779,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>0.3233257888430302</v>
       </c>
-      <c r="F50" s="292"/>
+      <c r="F50" s="291"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
@@ -7793,10 +7790,10 @@
         <f>G29/G32</f>
         <v>0.82375007799368372</v>
       </c>
-      <c r="F51" s="292"/>
+      <c r="F51" s="291"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F52" s="292"/>
+      <c r="F52" s="291"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="162" t="s">
@@ -7808,7 +7805,7 @@
       <c r="D53" s="225" t="s">
         <v>100</v>
       </c>
-      <c r="F53" s="292"/>
+      <c r="F53" s="291"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
@@ -7822,7 +7819,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>0.16831130083760298</v>
       </c>
-      <c r="F54" s="292"/>
+      <c r="F54" s="291"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
@@ -7836,10 +7833,10 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>0</v>
       </c>
-      <c r="F55" s="292"/>
+      <c r="F55" s="291"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F56" s="292"/>
+      <c r="F56" s="291"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B57" s="162" t="s">
@@ -7851,7 +7848,7 @@
       <c r="D57" s="225" t="s">
         <v>100</v>
       </c>
-      <c r="F57" s="292"/>
+      <c r="F57" s="291"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="2" t="s">
@@ -7873,10 +7870,10 @@
         <f>G39/G32</f>
         <v>5.2835441637701153E-2</v>
       </c>
-      <c r="F59" s="292"/>
+      <c r="F59" s="291"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F60" s="292"/>
+      <c r="F60" s="291"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="162" t="s">
@@ -7888,7 +7885,7 @@
       <c r="D61" s="225" t="s">
         <v>100</v>
       </c>
-      <c r="F61" s="292"/>
+      <c r="F61" s="291"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
@@ -7902,7 +7899,7 @@
         <f>G28/G29</f>
         <v>1.3197490690642218E-3</v>
       </c>
-      <c r="F62" s="292" t="s">
+      <c r="F62" s="291" t="s">
         <v>293</v>
       </c>
     </row>
@@ -7927,7 +7924,7 @@
       <c r="D65" s="211" t="s">
         <v>318</v>
       </c>
-      <c r="F65" s="297" t="s">
+      <c r="F65" s="296" t="s">
         <v>63</v>
       </c>
     </row>
@@ -7955,7 +7952,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="292"/>
+      <c r="F67" s="291"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="108" t="s">
@@ -7965,7 +7962,7 @@
         <f>G18</f>
         <v>0</v>
       </c>
-      <c r="F68" s="292"/>
+      <c r="F68" s="291"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="108" t="s">
@@ -7975,7 +7972,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="292"/>
+      <c r="F69" s="291"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
@@ -7985,13 +7982,13 @@
         <f>SUM(C66:C69)</f>
         <v>2664732</v>
       </c>
-      <c r="F70" s="292"/>
+      <c r="F70" s="291"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F71" s="292"/>
+      <c r="F71" s="291"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="295" t="s">
+      <c r="B72" s="294" t="s">
         <v>357</v>
       </c>
       <c r="C72" s="268" t="s">
@@ -8000,7 +7997,7 @@
       <c r="D72" s="210" t="s">
         <v>61</v>
       </c>
-      <c r="F72" s="292"/>
+      <c r="F72" s="291"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
@@ -8016,18 +8013,18 @@
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="298" t="s">
+      <c r="B74" s="297" t="s">
         <v>361</v>
       </c>
-      <c r="C74" s="299">
+      <c r="C74" s="298">
         <f>-$C$66/C73</f>
         <v>21.170635401418537</v>
       </c>
-      <c r="D74" s="299">
+      <c r="D74" s="298">
         <f>-$C$66/D73</f>
         <v>20.971345927483078</v>
       </c>
-      <c r="F74" s="292" t="s">
+      <c r="F74" s="291" t="s">
         <v>358</v>
       </c>
     </row>
@@ -8035,30 +8032,30 @@
       <c r="B75" s="82" t="s">
         <v>359</v>
       </c>
-      <c r="C75" s="304"/>
-      <c r="D75" s="303">
+      <c r="C75" s="303"/>
+      <c r="D75" s="302">
         <f>MIN(D73*D76,-G5)</f>
         <v>-635326.89060930803</v>
       </c>
-      <c r="F75" s="292" t="s">
+      <c r="F75" s="291" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="300" t="s">
+      <c r="B76" s="299" t="s">
         <v>362</v>
       </c>
-      <c r="C76" s="301"/>
-      <c r="D76" s="302">
+      <c r="C76" s="300"/>
+      <c r="D76" s="301">
         <f>IF(D74&lt;=3,1,IF(D74&gt;10,5,2))</f>
         <v>5</v>
       </c>
-      <c r="F76" s="292" t="s">
+      <c r="F76" s="291" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F77" s="292"/>
+      <c r="F77" s="291"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="16" t="s">
@@ -8070,7 +8067,7 @@
       <c r="D78" s="211" t="s">
         <v>36</v>
       </c>
-      <c r="F78" s="292"/>
+      <c r="F78" s="291"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="108" t="s">
@@ -8084,7 +8081,7 @@
         <f>G7*H7+G17*H17</f>
         <v>227506.8</v>
       </c>
-      <c r="F79" s="292"/>
+      <c r="F79" s="291"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="108" t="s">
@@ -8098,7 +8095,7 @@
         <f>G19*H19</f>
         <v>150</v>
       </c>
-      <c r="F80" s="292"/>
+      <c r="F80" s="291"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="108" t="s">
@@ -8112,7 +8109,7 @@
         <f>G9*H9+G21*H21</f>
         <v>0</v>
       </c>
-      <c r="F81" s="292"/>
+      <c r="F81" s="291"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B82" s="82" t="s">
@@ -8126,7 +8123,7 @@
         <f>SUM(D79:D81)</f>
         <v>227656.8</v>
       </c>
-      <c r="F82" s="292"/>
+      <c r="F82" s="291"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
@@ -8153,11 +8150,11 @@
       </c>
       <c r="C86" s="192">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-36466.559022600006</v>
+        <v>-36466.559022599999</v>
       </c>
       <c r="D86" s="255">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-2.7349915848210522E-2</v>
+        <v>-2.7349915848210515E-2</v>
       </c>
       <c r="E86" s="277" t="str">
         <f>Market_currency</f>
@@ -8170,11 +8167,11 @@
       </c>
       <c r="C87" s="192">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>2176694.055776984</v>
+        <v>2176694.0557769835</v>
       </c>
       <c r="D87" s="255">
         <f>C87*$H$1/Common_Shares</f>
-        <v>1.6325203377676956</v>
+        <v>1.6325203377676951</v>
       </c>
       <c r="E87" s="277" t="str">
         <f>Market_currency</f>
@@ -8187,11 +8184,11 @@
       </c>
       <c r="C88" s="192">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>244179.53863632001</v>
+        <v>244179.53863631998</v>
       </c>
       <c r="D88" s="255">
         <f>C88*$H$1/Common_Shares</f>
-        <v>0.18313463108541111</v>
+        <v>0.18313463108541109</v>
       </c>
       <c r="E88" s="277" t="str">
         <f>Market_currency</f>
@@ -8204,11 +8201,11 @@
       </c>
       <c r="C89" s="191">
         <f>SUM(C86:C88)</f>
-        <v>2384407.0353907039</v>
+        <v>2384407.0353907035</v>
       </c>
       <c r="D89" s="279">
         <f>SUM(D86:D88)</f>
-        <v>1.7883050530048963</v>
+        <v>1.7883050530048958</v>
       </c>
       <c r="E89" s="277" t="str">
         <f>Market_currency</f>
@@ -8331,7 +8328,7 @@
         <v>1000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="313"/>
+      <c r="E3" s="312"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -8345,7 +8342,7 @@
         <v>1583387.2</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="311"/>
+      <c r="E4" s="310"/>
       <c r="F4" s="57"/>
       <c r="G4" s="187">
         <f>Data!C36</f>
@@ -8401,7 +8398,7 @@
         <f>C25</f>
         <v>-1348785.0374623393</v>
       </c>
-      <c r="E5" s="313"/>
+      <c r="E5" s="312"/>
       <c r="G5" s="187">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-1322360</v>
@@ -8456,7 +8453,7 @@
         <f>C4+C5</f>
         <v>234602.16253766068</v>
       </c>
-      <c r="E6" s="313"/>
+      <c r="E6" s="312"/>
       <c r="G6" s="188">
         <f>IF(G4="","",G4+G5)</f>
         <v>293225</v>
@@ -8511,7 +8508,7 @@
         <f>C35</f>
         <v>-175999.5</v>
       </c>
-      <c r="E7" s="313"/>
+      <c r="E7" s="312"/>
       <c r="G7" s="198">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-188071</v>
@@ -8567,7 +8564,7 @@
         <v>58602.662537660683</v>
       </c>
       <c r="D8" s="60"/>
-      <c r="E8" s="319"/>
+      <c r="E8" s="318"/>
       <c r="F8" s="60"/>
       <c r="G8" s="188">
         <f>IF(G$4="","",G6+G7)</f>
@@ -8623,7 +8620,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>35974</v>
       </c>
-      <c r="E9" s="313"/>
+      <c r="E9" s="312"/>
       <c r="G9" s="198">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>35974</v>
@@ -8678,7 +8675,7 @@
         <f>-C4*C77</f>
         <v>-35974</v>
       </c>
-      <c r="E10" s="313"/>
+      <c r="E10" s="312"/>
       <c r="G10" s="198">
         <f>Data!C62</f>
         <v>-15312</v>
@@ -8734,7 +8731,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="173"/>
-      <c r="E11" s="312"/>
+      <c r="E11" s="311"/>
       <c r="F11" s="173"/>
       <c r="G11" s="190">
         <f>G60</f>
@@ -8790,7 +8787,7 @@
         <f>C49</f>
         <v>72802</v>
       </c>
-      <c r="E12" s="313"/>
+      <c r="E12" s="312"/>
       <c r="G12" s="198">
         <f t="shared" ref="G12:Q12" si="6">G49</f>
         <v>72802</v>
@@ -8845,7 +8842,7 @@
         <f>SUM(C8:C12)</f>
         <v>131404.66253766068</v>
       </c>
-      <c r="E13" s="313"/>
+      <c r="E13" s="312"/>
       <c r="G13" s="188">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>198618</v>
@@ -8900,7 +8897,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-32851.165634415171</v>
       </c>
-      <c r="E14" s="313"/>
+      <c r="E14" s="312"/>
       <c r="G14" s="198">
         <f>Data!C46</f>
         <v>-44449</v>
@@ -8956,7 +8953,7 @@
         <v>-2089.6737831682049</v>
       </c>
       <c r="D15" s="61"/>
-      <c r="E15" s="320"/>
+      <c r="E15" s="319"/>
       <c r="F15" s="61"/>
       <c r="G15" s="187">
         <f>Data!C48</f>
@@ -9013,7 +9010,7 @@
         <v>96463.823120077301</v>
       </c>
       <c r="D16" s="62"/>
-      <c r="E16" s="321"/>
+      <c r="E16" s="320"/>
       <c r="F16" s="62"/>
       <c r="G16" s="188">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -9070,7 +9067,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="59"/>
-      <c r="E17" s="312" t="s">
+      <c r="E17" s="311" t="s">
         <v>378</v>
       </c>
       <c r="F17" s="59"/>
@@ -9096,7 +9093,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="59"/>
-      <c r="E18" s="312" t="s">
+      <c r="E18" s="311" t="s">
         <v>379</v>
       </c>
       <c r="F18" s="59"/>
@@ -9122,7 +9119,7 @@
         <v>96463.823120077301</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="310"/>
+      <c r="E19" s="309"/>
       <c r="F19" s="27"/>
       <c r="G19" s="190">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",SUM(G16:G18))</f>
@@ -9218,7 +9215,7 @@
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="310"/>
+      <c r="E22" s="309"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -9242,7 +9239,7 @@
         <v>-902304.82874495955</v>
       </c>
       <c r="D23" s="59"/>
-      <c r="E23" s="312"/>
+      <c r="E23" s="311"/>
       <c r="F23" s="59"/>
       <c r="G23" s="187">
         <f>Data!C37</f>
@@ -9299,7 +9296,7 @@
         <v>-446480.2087173796</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="310"/>
+      <c r="E24" s="309"/>
       <c r="F24" s="27"/>
       <c r="G24" s="187">
         <f>Data!C40</f>
@@ -9356,7 +9353,7 @@
         <v>-1348785.0374623393</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="318"/>
+      <c r="E25" s="317"/>
       <c r="F25" s="9"/>
       <c r="G25" s="188">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -9405,14 +9402,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="10"/>
-      <c r="E26" s="313"/>
+      <c r="E26" s="312"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="65" t="s">
         <v>211</v>
       </c>
-      <c r="E27" s="313"/>
+      <c r="E27" s="312"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
@@ -9424,7 +9421,7 @@
         <v>0.56985734679739708</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="311" t="s">
+      <c r="E28" s="310" t="s">
         <v>380</v>
       </c>
       <c r="F28" s="26"/>
@@ -9484,7 +9481,7 @@
         <v>0.28197790705733861</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="311" t="s">
+      <c r="E29" s="310" t="s">
         <v>380</v>
       </c>
       <c r="F29" s="26"/>
@@ -9542,7 +9539,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.8518352538547358</v>
       </c>
-      <c r="E30" s="313"/>
+      <c r="E30" s="312"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.81850227626525374</v>
@@ -9590,14 +9587,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10"/>
-      <c r="E31" s="313"/>
+      <c r="E31" s="312"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10"/>
       <c r="B32" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="313"/>
+      <c r="E32" s="312"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10"/>
@@ -9608,7 +9605,7 @@
         <f>AVERAGE(G33:H33)</f>
         <v>-175999.5</v>
       </c>
-      <c r="E33" s="311" t="s">
+      <c r="E33" s="310" t="s">
         <v>380</v>
       </c>
       <c r="G33" s="198">
@@ -9666,7 +9663,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="59"/>
-      <c r="E34" s="311" t="s">
+      <c r="E34" s="310" t="s">
         <v>380</v>
       </c>
       <c r="F34" s="59"/>
@@ -9725,7 +9722,7 @@
         <v>-175999.5</v>
       </c>
       <c r="D35" s="59"/>
-      <c r="E35" s="312"/>
+      <c r="E35" s="311"/>
       <c r="F35" s="59"/>
       <c r="G35" s="188">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -9774,14 +9771,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="10"/>
-      <c r="E36" s="313"/>
+      <c r="E36" s="312"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10"/>
       <c r="B37" s="65" t="s">
         <v>212</v>
       </c>
-      <c r="E37" s="313"/>
+      <c r="E37" s="312"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="10"/>
@@ -9794,7 +9791,7 @@
         <v>0.11115379737817763</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="310"/>
+      <c r="E38" s="309"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -9852,7 +9849,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="310"/>
+      <c r="E39" s="309"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -9908,7 +9905,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>0.11115379737817763</v>
       </c>
-      <c r="E40" s="313"/>
+      <c r="E40" s="312"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>0.11641046432097352</v>
@@ -9956,25 +9953,25 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="10"/>
-      <c r="E41" s="313"/>
+      <c r="E41" s="312"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10"/>
       <c r="B42" s="65" t="s">
         <v>213</v>
       </c>
-      <c r="E42" s="313"/>
+      <c r="E42" s="312"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="C43" s="307">
+      <c r="C43" s="306">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="310" t="s">
+      <c r="E43" s="309" t="s">
         <v>381</v>
       </c>
       <c r="F43" s="27"/>
@@ -10054,7 +10051,7 @@
       <c r="B46" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="E46" s="313"/>
+      <c r="E46" s="312"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="10"/>
@@ -10065,7 +10062,7 @@
         <f>-BS!G31*Normalized_FCF!C53</f>
         <v>-1003</v>
       </c>
-      <c r="E47" s="313"/>
+      <c r="E47" s="312"/>
       <c r="G47" s="198">
         <f>Data!C51</f>
         <v>-1003</v>
@@ -10120,7 +10117,7 @@
         <f>BS!$C$66*C52</f>
         <v>73805</v>
       </c>
-      <c r="E48" s="313"/>
+      <c r="E48" s="312"/>
       <c r="G48" s="198">
         <f>Data!C52</f>
         <v>73805</v>
@@ -10175,7 +10172,7 @@
         <f>C47+C48</f>
         <v>72802</v>
       </c>
-      <c r="E49" s="313"/>
+      <c r="E49" s="312"/>
       <c r="G49" s="188">
         <f t="shared" ref="G49:Q49" si="19">IF(G4="","",G47+G48)</f>
         <v>72802</v>
@@ -10223,14 +10220,14 @@
     </row>
     <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="10"/>
-      <c r="E50" s="313"/>
+      <c r="E50" s="312"/>
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="10"/>
       <c r="B51" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="E51" s="313"/>
+      <c r="E51" s="312"/>
       <c r="G51" s="100" t="s">
         <v>224</v>
       </c>
@@ -10244,7 +10241,7 @@
         <f>G52</f>
         <v>2.7696969151119136E-2</v>
       </c>
-      <c r="E52" s="310" t="s">
+      <c r="E52" s="309" t="s">
         <v>382</v>
       </c>
       <c r="G52" s="6">
@@ -10271,7 +10268,7 @@
         <f>Normalized_FCF!G53</f>
         <v>2.9500867672578604E-2</v>
       </c>
-      <c r="E53" s="310" t="s">
+      <c r="E53" s="309" t="s">
         <v>383</v>
       </c>
       <c r="G53" s="23">
@@ -10298,7 +10295,7 @@
         <f>-C8/C47</f>
         <v>58.427380396471271</v>
       </c>
-      <c r="E54" s="313"/>
+      <c r="E54" s="312"/>
       <c r="G54" s="42">
         <f>IF(G4="","",-G8/G47)</f>
         <v>104.839481555334</v>
@@ -10346,14 +10343,14 @@
     </row>
     <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="10"/>
-      <c r="E55" s="313"/>
+      <c r="E55" s="312"/>
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="10"/>
       <c r="B56" s="65" t="s">
         <v>173</v>
       </c>
-      <c r="E56" s="313"/>
+      <c r="E56" s="312"/>
       <c r="G56" s="100" t="s">
         <v>224</v>
       </c>
@@ -10367,7 +10364,7 @@
         <f>BS!$C79*C65</f>
         <v>0</v>
       </c>
-      <c r="E57" s="313"/>
+      <c r="E57" s="312"/>
       <c r="G57" s="198">
         <f>Data!C56</f>
         <v>0</v>
@@ -10422,7 +10419,7 @@
         <f>BS!$C68*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="313"/>
+      <c r="E58" s="312"/>
       <c r="G58" s="198">
         <f>Data!C55</f>
         <v>0</v>
@@ -10477,7 +10474,7 @@
         <f>BS!$C81*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="313"/>
+      <c r="E59" s="312"/>
       <c r="G59" s="198">
         <f>Data!C57</f>
         <v>0</v>
@@ -10532,7 +10529,7 @@
         <f>SUM(C57:C59)</f>
         <v>0</v>
       </c>
-      <c r="E60" s="313"/>
+      <c r="E60" s="312"/>
       <c r="G60" s="188">
         <f t="shared" ref="G60:Q60" si="21">IF(G4="","",SUM(G57:G59))</f>
         <v>0</v>
@@ -10583,10 +10580,10 @@
       <c r="B61" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="C61" s="308">
-        <v>0</v>
-      </c>
-      <c r="E61" s="311" t="s">
+      <c r="C61" s="307">
+        <v>0</v>
+      </c>
+      <c r="E61" s="310" t="s">
         <v>384</v>
       </c>
       <c r="G61" s="198">
@@ -10643,7 +10640,7 @@
         <f>C60+C61</f>
         <v>0</v>
       </c>
-      <c r="E62" s="313"/>
+      <c r="E62" s="312"/>
       <c r="G62" s="188">
         <f t="shared" ref="G62:Q62" si="22">IF(G4="","",G60+G61)</f>
         <v>39310</v>
@@ -10691,14 +10688,14 @@
     </row>
     <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="10"/>
-      <c r="E63" s="313"/>
+      <c r="E63" s="312"/>
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="10"/>
       <c r="B64" s="99" t="s">
         <v>174</v>
       </c>
-      <c r="E64" s="313"/>
+      <c r="E64" s="312"/>
       <c r="G64" s="100" t="s">
         <v>224</v>
       </c>
@@ -10712,7 +10709,7 @@
         <f>G65</f>
         <v>0</v>
       </c>
-      <c r="E65" s="313"/>
+      <c r="E65" s="312"/>
       <c r="G65" s="23">
         <f>IFERROR(G57/BS!$C$67,0)</f>
         <v>0</v>
@@ -10737,7 +10734,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="313"/>
+      <c r="E66" s="312"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$68,0)</f>
         <v>0</v>
@@ -10762,7 +10759,7 @@
         <f>G67</f>
         <v>0</v>
       </c>
-      <c r="E67" s="313"/>
+      <c r="E67" s="312"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$81,0)</f>
         <v>0</v>
@@ -10788,7 +10785,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="9"/>
-      <c r="E68" s="318"/>
+      <c r="E68" s="317"/>
       <c r="F68" s="9"/>
       <c r="G68" s="72">
         <f>G60/BS!C70</f>
@@ -10838,7 +10835,7 @@
       </c>
       <c r="C71" s="63"/>
       <c r="D71" s="27"/>
-      <c r="E71" s="310"/>
+      <c r="E71" s="309"/>
       <c r="F71" s="27"/>
       <c r="G71" s="100"/>
       <c r="H71" s="12"/>
@@ -10862,7 +10859,7 @@
         <v>0.8518352538547358</v>
       </c>
       <c r="D72" s="27"/>
-      <c r="E72" s="310"/>
+      <c r="E72" s="309"/>
       <c r="F72" s="27"/>
       <c r="G72" s="6">
         <f t="shared" ref="G72:Q72" si="23">IF(G$4="","",ABS(G5/G$4))</f>
@@ -10919,7 +10916,7 @@
         <v>0.1481647461452642</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="310"/>
+      <c r="E73" s="309"/>
       <c r="F73" s="27"/>
       <c r="G73" s="66">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G6/G$4))</f>
@@ -10976,7 +10973,7 @@
         <v>0.11115379737817763</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="310"/>
+      <c r="E74" s="309"/>
       <c r="F74" s="27"/>
       <c r="G74" s="6">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G7/G$4))</f>
@@ -11033,7 +11030,7 @@
         <v>3.7010948767086591E-2</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="310"/>
+      <c r="E75" s="309"/>
       <c r="F75" s="27"/>
       <c r="G75" s="66">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G8/G$4))</f>
@@ -11090,7 +11087,7 @@
         <v>2.2719648106287585E-2</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="310"/>
+      <c r="E76" s="309"/>
       <c r="F76" s="27"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",G9/G$4)</f>
@@ -11147,7 +11144,7 @@
         <v>2.2719648106287585E-2</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="311" t="s">
+      <c r="E77" s="310" t="s">
         <v>385</v>
       </c>
       <c r="F77" s="27"/>
@@ -11206,7 +11203,7 @@
         <v>0</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="310"/>
+      <c r="E78" s="309"/>
       <c r="F78" s="27"/>
       <c r="G78" s="66">
         <f t="shared" ref="G78:Q78" si="29">IF(G$4="","",G11/G$4)</f>
@@ -11263,7 +11260,7 @@
         <v>4.5978646284370622E-2</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="310"/>
+      <c r="E79" s="309"/>
       <c r="F79" s="27"/>
       <c r="G79" s="6">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",ABS(G12/G$4))</f>
@@ -11320,7 +11317,7 @@
         <v>8.2989595051457213E-2</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="310"/>
+      <c r="E80" s="309"/>
       <c r="F80" s="27"/>
       <c r="G80" s="66">
         <f>IF(G$4="","",G13/G$4)</f>
@@ -11377,7 +11374,7 @@
         <v>2.0747398762864303E-2</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="310"/>
+      <c r="E81" s="309"/>
       <c r="F81" s="27"/>
       <c r="G81" s="6">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",ABS(G14/G$4))</f>
@@ -11430,12 +11427,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C82" s="309">
+      <c r="C82" s="308">
         <f>MIN(BS!C62,MAX(G82:K82))</f>
         <v>1.3197490690642218E-3</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="310"/>
+      <c r="E82" s="309"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",-G15/G$4)</f>
@@ -11492,7 +11489,7 @@
         <v>6.0922447219528678E-2</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="310"/>
+      <c r="E83" s="309"/>
       <c r="F83" s="27"/>
       <c r="G83" s="66">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",ABS(G16/G$4))</f>
@@ -11544,11 +11541,11 @@
       <c r="B84" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C84" s="309">
+      <c r="C84" s="308">
         <v>0</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="312" t="str">
+      <c r="E84" s="311" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
@@ -11570,10 +11567,10 @@
       <c r="B85" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C85" s="309">
-        <v>0</v>
-      </c>
-      <c r="E85" s="312" t="str">
+      <c r="C85" s="308">
+        <v>0</v>
+      </c>
+      <c r="E85" s="311" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -11599,7 +11596,7 @@
         <v>6.0922447219528678E-2</v>
       </c>
       <c r="D86" s="77"/>
-      <c r="E86" s="310"/>
+      <c r="E86" s="309"/>
       <c r="F86" s="77"/>
       <c r="G86" s="66">
         <f t="shared" ref="G86:Q86" si="35">IF(G$4="","",ABS(G19/G$4))</f>
@@ -11648,14 +11645,14 @@
     </row>
     <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="10"/>
-      <c r="E87" s="313"/>
+      <c r="E87" s="312"/>
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="10"/>
       <c r="B88" s="65" t="s">
         <v>219</v>
       </c>
-      <c r="E88" s="313"/>
+      <c r="E88" s="312"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="10"/>
@@ -11667,7 +11664,7 @@
         <f>G89</f>
         <v>0.1178</v>
       </c>
-      <c r="E89" s="313"/>
+      <c r="E89" s="312"/>
       <c r="G89" s="116">
         <f>Data!C64</f>
         <v>0.1178</v>
@@ -11723,7 +11720,7 @@
         <f>C89*Common_Shares/$C$3</f>
         <v>157066.6863</v>
       </c>
-      <c r="E90" s="313"/>
+      <c r="E90" s="312"/>
       <c r="G90" s="76">
         <f t="shared" ref="G90:Q90" si="36">IF(G$4="","",G89*Common_Shares/$C$3)</f>
         <v>157066.6863</v>
@@ -11778,7 +11775,7 @@
         <f>C89/(C19*$C$3/Common_Shares)</f>
         <v>1.6282444674049961</v>
       </c>
-      <c r="E91" s="313"/>
+      <c r="E91" s="312"/>
       <c r="G91" s="175">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G89/(G19*$C$3/Common_Shares))</f>
         <v>1.0335374501546357</v>
@@ -11833,7 +11830,7 @@
         <f>C89/Market_Price</f>
         <v>5.1441048034934496E-2</v>
       </c>
-      <c r="E92" s="313"/>
+      <c r="E92" s="312"/>
       <c r="G92" s="23">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G89/Market_Price)</f>
         <v>5.1441048034934496E-2</v>
@@ -11881,7 +11878,7 @@
     </row>
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
-      <c r="E93" s="313"/>
+      <c r="E93" s="312"/>
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="10"/>
@@ -11890,7 +11887,7 @@
       </c>
       <c r="C94" s="63"/>
       <c r="D94" s="27"/>
-      <c r="E94" s="310"/>
+      <c r="E94" s="309"/>
       <c r="F94" s="27"/>
       <c r="G94" s="12"/>
       <c r="H94" s="12"/>
@@ -11914,7 +11911,7 @@
         <v>-1.992949922164422E-2</v>
       </c>
       <c r="D95" s="27"/>
-      <c r="E95" s="310"/>
+      <c r="E95" s="309"/>
       <c r="F95" s="27"/>
       <c r="G95" s="6">
         <f t="shared" ref="G95:Q95" si="39">IF(H4="","",G4/H4-1)</f>
@@ -11971,7 +11968,7 @@
         <v>-0.33840506631996758</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="310"/>
+      <c r="E96" s="309"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G13/H13-1)</f>
@@ -12049,7 +12046,7 @@
       <c r="B99" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="E99" s="313"/>
+      <c r="E99" s="312"/>
       <c r="G99" s="100" t="s">
         <v>224</v>
       </c>
@@ -12064,7 +12061,7 @@
         <v>3670169</v>
       </c>
       <c r="D100" s="26"/>
-      <c r="E100" s="314"/>
+      <c r="E100" s="313"/>
       <c r="F100" s="26"/>
       <c r="G100" s="187">
         <f t="shared" ref="G100:Q100" si="41">IF(G$4="","",G104+G103)</f>
@@ -12121,7 +12118,7 @@
         <v>180994</v>
       </c>
       <c r="D101" s="91"/>
-      <c r="E101" s="315"/>
+      <c r="E101" s="314"/>
       <c r="F101" s="91"/>
       <c r="G101" s="189">
         <f>IF(G$4="","",Data!D76)</f>
@@ -12178,7 +12175,7 @@
         <v>158110</v>
       </c>
       <c r="D102" s="91"/>
-      <c r="E102" s="315"/>
+      <c r="E102" s="314"/>
       <c r="F102" s="91"/>
       <c r="G102" s="189">
         <f>IF(G$4="","",Data!D77)</f>
@@ -12235,7 +12232,7 @@
         <v>642877</v>
       </c>
       <c r="D103" s="26"/>
-      <c r="E103" s="314"/>
+      <c r="E103" s="313"/>
       <c r="F103" s="26"/>
       <c r="G103" s="187">
         <f>Data!C78</f>
@@ -12292,7 +12289,7 @@
         <v>3027292</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="314"/>
+      <c r="E104" s="313"/>
       <c r="F104" s="26"/>
       <c r="G104" s="187">
         <f>Data!C79</f>
@@ -12341,7 +12338,7 @@
     </row>
     <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="10"/>
-      <c r="E105" s="313"/>
+      <c r="E105" s="312"/>
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="10"/>
@@ -12350,7 +12347,7 @@
       </c>
       <c r="C106" s="26"/>
       <c r="D106" s="26"/>
-      <c r="E106" s="314"/>
+      <c r="E106" s="313"/>
       <c r="F106" s="26"/>
       <c r="G106" s="100" t="s">
         <v>224</v>
@@ -12376,7 +12373,7 @@
         <v>0.11430811111773545</v>
       </c>
       <c r="D107" s="26"/>
-      <c r="E107" s="314"/>
+      <c r="E107" s="313"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97">
         <f t="shared" ref="G107:Q107" si="42">IF(G$4="","",G101/G$4)</f>
@@ -12433,7 +12430,7 @@
         <v>9.9855550177492911E-2</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="314"/>
+      <c r="E108" s="313"/>
       <c r="F108" s="26"/>
       <c r="G108" s="97">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -12490,7 +12487,7 @@
         <v>0</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="314"/>
+      <c r="E109" s="313"/>
       <c r="F109" s="26"/>
       <c r="G109" s="97">
         <f>BS!$G$38/G$4</f>
@@ -12509,7 +12506,7 @@
     </row>
     <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="10"/>
-      <c r="E110" s="313"/>
+      <c r="E110" s="312"/>
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="10"/>
@@ -12518,7 +12515,7 @@
       </c>
       <c r="C111" s="55"/>
       <c r="D111" s="55"/>
-      <c r="E111" s="316"/>
+      <c r="E111" s="315"/>
       <c r="F111" s="55"/>
       <c r="G111" s="23" t="str">
         <f>IFERROR(IF(#REF!*G113*(1/#REF!)=G115,"","Error"),"")</f>
@@ -12574,7 +12571,7 @@
         <f>C80</f>
         <v>8.2989595051457213E-2</v>
       </c>
-      <c r="E112" s="313"/>
+      <c r="E112" s="312"/>
       <c r="G112" s="23">
         <f t="shared" ref="G112:Q112" si="44">G80</f>
         <v>0.12293874974080596</v>
@@ -12628,7 +12625,7 @@
         <f>C4/C100</f>
         <v>0.43142078743512902</v>
       </c>
-      <c r="E113" s="313"/>
+      <c r="E113" s="312"/>
       <c r="G113" s="42">
         <f t="shared" ref="G113:Q113" si="45">IF(G4="","",G4/G100)</f>
         <v>0.44019362596109335</v>
@@ -12683,7 +12680,7 @@
         <v>1.2123604198075375</v>
       </c>
       <c r="D114" s="11"/>
-      <c r="E114" s="317"/>
+      <c r="E114" s="316"/>
       <c r="F114" s="11"/>
       <c r="G114" s="15">
         <f t="shared" ref="G114:Q114" si="46">IF(G$4="","",G100/G104)</f>
@@ -12740,7 +12737,7 @@
         <v>1.9358113633458775E-2</v>
       </c>
       <c r="D115" s="106"/>
-      <c r="E115" s="316"/>
+      <c r="E115" s="315"/>
       <c r="F115" s="106"/>
       <c r="G115" s="105">
         <f t="shared" ref="G115:Q115" si="47">IF(G$4="","",G8/G104)</f>
@@ -12836,7 +12833,7 @@
       </c>
       <c r="C118" s="184"/>
       <c r="D118" s="27"/>
-      <c r="E118" s="310"/>
+      <c r="E118" s="309"/>
       <c r="F118" s="27"/>
       <c r="G118" s="12"/>
       <c r="H118" s="12"/>
@@ -12858,30 +12855,30 @@
       </c>
       <c r="C119" s="182">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>7.759867774730958E-2</v>
+        <v>7.7598677747309566E-2</v>
       </c>
       <c r="D119" s="27"/>
-      <c r="E119" s="310"/>
+      <c r="E119" s="309"/>
       <c r="F119" s="27"/>
       <c r="G119" s="182">
         <f t="shared" ref="G119:Q119" si="48">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.1222496753272906</v>
+        <v>0.12224967532729059</v>
       </c>
       <c r="H119" s="182">
         <f t="shared" si="48"/>
-        <v>3.6620201157624863E-2</v>
+        <v>3.6620201157624856E-2</v>
       </c>
       <c r="I119" s="182">
         <f t="shared" si="48"/>
-        <v>6.4840527936928918E-2</v>
+        <v>6.4840527936928904E-2</v>
       </c>
       <c r="J119" s="182">
         <f t="shared" si="48"/>
-        <v>0.22806731704789374</v>
+        <v>0.22806731704789368</v>
       </c>
       <c r="K119" s="182">
         <f t="shared" si="48"/>
-        <v>0.16323392523565938</v>
+        <v>0.16323392523565936</v>
       </c>
       <c r="L119" s="182" t="str">
         <f t="shared" si="48"/>
@@ -12915,14 +12912,14 @@
       </c>
       <c r="C120" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.3885885479174496E-2</v>
+        <v>3.3885885479174489E-2</v>
       </c>
       <c r="D120" s="27"/>
-      <c r="E120" s="310"/>
+      <c r="E120" s="309"/>
       <c r="F120" s="27"/>
       <c r="G120" s="79">
         <f t="shared" ref="G120" si="49">IF(G$4="","",G119/Market_Price)</f>
-        <v>5.3384137697506814E-2</v>
+        <v>5.3384137697506807E-2</v>
       </c>
       <c r="H120" s="79">
         <f t="shared" ref="H120" si="50">IF(H$4="","",H119/Market_Price)</f>
@@ -12930,15 +12927,15 @@
       </c>
       <c r="I120" s="79">
         <f t="shared" ref="I120" si="51">IF(I$4="","",I119/Market_Price)</f>
-        <v>2.8314641020492977E-2</v>
+        <v>2.831464102049297E-2</v>
       </c>
       <c r="J120" s="79">
         <f t="shared" ref="J120" si="52">IF(J$4="","",J119/Market_Price)</f>
-        <v>9.959271486807586E-2</v>
+        <v>9.9592714868075846E-2</v>
       </c>
       <c r="K120" s="79">
         <f t="shared" ref="K120" si="53">IF(K$4="","",K119/Market_Price)</f>
-        <v>7.1281190059239899E-2</v>
+        <v>7.1281190059239885E-2</v>
       </c>
       <c r="L120" s="79" t="str">
         <f t="shared" ref="L120" si="54">IF(L$4="","",L119/Market_Price)</f>
@@ -13747,10 +13744,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="335" t="s">
+      <c r="E6" s="338" t="s">
         <v>259</v>
       </c>
-      <c r="F6" s="335"/>
+      <c r="F6" s="338"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -13765,8 +13762,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="335"/>
-      <c r="F7" s="335"/>
+      <c r="E7" s="338"/>
+      <c r="F7" s="338"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -13781,8 +13778,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="335"/>
-      <c r="F8" s="335"/>
+      <c r="E8" s="338"/>
+      <c r="F8" s="338"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -13797,8 +13794,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="335"/>
-      <c r="F9" s="335"/>
+      <c r="E9" s="338"/>
+      <c r="F9" s="338"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -13821,7 +13818,7 @@
       </c>
       <c r="C11" s="238">
         <f>Exchange_Rate</f>
-        <v>1.0725774000000001</v>
+        <v>1.0725773999999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -13835,7 +13832,7 @@
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>2.5642918304779925</v>
+        <v>2.564291830477992</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14824,23 +14821,23 @@
       </c>
       <c r="B65" s="128">
         <f>C12</f>
-        <v>2.5642918304779925</v>
+        <v>2.564291830477992</v>
       </c>
       <c r="C65" s="128">
         <f>C12</f>
-        <v>2.5642918304779925</v>
+        <v>2.564291830477992</v>
       </c>
       <c r="D65" s="128">
         <f>C12</f>
-        <v>2.5642918304779925</v>
+        <v>2.564291830477992</v>
       </c>
       <c r="E65" s="145">
         <f>C12</f>
-        <v>2.5642918304779925</v>
+        <v>2.564291830477992</v>
       </c>
       <c r="F65" s="128">
         <f>C12</f>
-        <v>2.5642918304779925</v>
+        <v>2.564291830477992</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -14851,23 +14848,23 @@
       </c>
       <c r="B66" s="128">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.4431119244101871</v>
+        <v>2.4431119244101862</v>
       </c>
       <c r="C66" s="128">
         <f t="shared" si="4"/>
-        <v>2.489365851343126</v>
+        <v>2.4893658513431256</v>
       </c>
       <c r="D66" s="128">
         <f t="shared" si="4"/>
-        <v>2.5908825114419973</v>
+        <v>2.5908825114419964</v>
       </c>
       <c r="E66" s="128">
         <f t="shared" si="4"/>
-        <v>2.6467052675837404</v>
+        <v>2.6467052675837399</v>
       </c>
       <c r="F66" s="128">
         <f t="shared" si="4"/>
-        <v>2.7063078519409496</v>
+        <v>2.7063078519409491</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -14878,23 +14875,23 @@
       </c>
       <c r="B67" s="128">
         <f t="shared" si="4"/>
-        <v>2.3598155710591455</v>
+        <v>2.3598155710591446</v>
       </c>
       <c r="C67" s="128">
         <f t="shared" si="4"/>
-        <v>2.4307528629902109</v>
+        <v>2.4307528629902104</v>
       </c>
       <c r="D67" s="128">
         <f t="shared" si="4"/>
-        <v>2.6178627598733617</v>
+        <v>2.6178627598733613</v>
       </c>
       <c r="E67" s="128">
         <f t="shared" si="4"/>
-        <v>2.7419813260980841</v>
+        <v>2.7419813260980832</v>
       </c>
       <c r="F67" s="128">
         <f t="shared" si="4"/>
-        <v>2.8933859746928712</v>
+        <v>2.8933859746928707</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -14905,23 +14902,23 @@
       </c>
       <c r="B68" s="128">
         <f t="shared" si="4"/>
-        <v>2.2874763405300755</v>
+        <v>2.2874763405300751</v>
       </c>
       <c r="C68" s="128">
         <f t="shared" si="4"/>
-        <v>2.3756754943990508</v>
+        <v>2.3756754943990503</v>
       </c>
       <c r="D68" s="128">
         <f t="shared" si="4"/>
-        <v>2.6483990284514674</v>
+        <v>2.6483990284514669</v>
       </c>
       <c r="E68" s="128">
         <f t="shared" si="4"/>
-        <v>2.8618094929407589</v>
+        <v>2.8618094929407585</v>
       </c>
       <c r="F68" s="128">
         <f t="shared" si="4"/>
-        <v>3.156626790651464</v>
+        <v>3.1566267906514631</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -14932,23 +14929,23 @@
       </c>
       <c r="B69" s="128">
         <f t="shared" si="4"/>
-        <v>2.2349995503269193</v>
+        <v>2.2349995503269189</v>
       </c>
       <c r="C69" s="128">
         <f t="shared" si="4"/>
-        <v>2.3329628579556752</v>
+        <v>2.3329628579556747</v>
       </c>
       <c r="D69" s="128">
         <f t="shared" si="4"/>
-        <v>2.6768089977767158</v>
+        <v>2.6768089977767149</v>
       </c>
       <c r="E69" s="128">
         <f t="shared" si="4"/>
-        <v>2.9866254102071537</v>
+        <v>2.9866254102071528</v>
       </c>
       <c r="F69" s="128">
         <f t="shared" si="4"/>
-        <v>3.4671586468436901</v>
+        <v>3.4671586468436892</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -14959,23 +14956,23 @@
       </c>
       <c r="B70" s="128">
         <f t="shared" si="4"/>
-        <v>2.1996438009032357</v>
+        <v>2.1996438009032353</v>
       </c>
       <c r="C70" s="128">
         <f t="shared" si="4"/>
-        <v>2.3025619045832197</v>
+        <v>2.3025619045832193</v>
       </c>
       <c r="D70" s="128">
         <f t="shared" si="4"/>
-        <v>2.7009273293619445</v>
+        <v>2.700927329361944</v>
       </c>
       <c r="E70" s="128">
         <f t="shared" si="4"/>
-        <v>3.1060153031642823</v>
+        <v>3.1060153031642814</v>
       </c>
       <c r="F70" s="128">
         <f t="shared" si="4"/>
-        <v>3.8070545183066273</v>
+        <v>3.8070545183066264</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -14985,23 +14982,23 @@
       </c>
       <c r="B71" s="128">
         <f t="shared" si="4"/>
-        <v>2.1766743908779791</v>
+        <v>2.1766743908779786</v>
       </c>
       <c r="C71" s="128">
         <f t="shared" si="4"/>
-        <v>2.2819173077064332</v>
+        <v>2.2819173077064328</v>
       </c>
       <c r="D71" s="128">
         <f t="shared" si="4"/>
-        <v>2.7203438746537354</v>
+        <v>2.7203438746537345</v>
       </c>
       <c r="E71" s="128">
         <f t="shared" si="4"/>
-        <v>3.2149540010149482</v>
+        <v>3.2149540010149473</v>
       </c>
       <c r="F71" s="128">
         <f t="shared" si="4"/>
-        <v>4.1651831329817828</v>
+        <v>4.1651831329817819</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15036,7 +15033,7 @@
       </c>
       <c r="E74" s="139">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>3.156626790651464</v>
+        <v>3.1566267906514631</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
@@ -15058,7 +15055,7 @@
       </c>
       <c r="E75" s="139">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>2.7419813260980841</v>
+        <v>2.7419813260980832</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -15081,7 +15078,7 @@
       </c>
       <c r="E76" s="139">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>2.6178627598733617</v>
+        <v>2.6178627598733613</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15104,7 +15101,7 @@
       </c>
       <c r="E77" s="139">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>2.4307528629902109</v>
+        <v>2.4307528629902104</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -15127,7 +15124,7 @@
       </c>
       <c r="E78" s="139">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.2874763405300755</v>
+        <v>2.2874763405300751</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
@@ -15195,7 +15192,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I90"/>
+  <dimension ref="B2:I92"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -15247,8 +15244,8 @@
         <v>1</v>
       </c>
       <c r="I4" s="272">
-        <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.1178</v>
+        <f t="shared" ref="I4:I13" ca="1" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
+        <v>0.57999999999999996</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -15256,8 +15253,8 @@
         <v>2</v>
       </c>
       <c r="I5" s="272">
-        <f t="shared" si="0"/>
-        <v>0.1178</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>0.57999999999999996</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
@@ -15276,8 +15273,8 @@
         <v>3</v>
       </c>
       <c r="I6" s="272">
-        <f t="shared" si="0"/>
-        <v>2.7320810029480898</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>70.551062104600618</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15292,16 +15289,16 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="337" t="str">
+      <c r="E7" s="340" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 朝云集团(6601.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="337"/>
+      <c r="F7" s="340"/>
       <c r="H7" s="284">
         <v>4</v>
       </c>
       <c r="I7" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -15317,13 +15314,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="337"/>
-      <c r="F8" s="337"/>
+      <c r="E8" s="340"/>
+      <c r="F8" s="340"/>
       <c r="H8" s="284">
         <v>5</v>
       </c>
       <c r="I8" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -15339,24 +15336,24 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="337"/>
-      <c r="F9" s="337"/>
+      <c r="E9" s="340"/>
+      <c r="F9" s="340"/>
       <c r="H9" s="284">
         <v>6</v>
       </c>
       <c r="I9" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="337"/>
-      <c r="F10" s="337"/>
+      <c r="E10" s="340"/>
+      <c r="F10" s="340"/>
       <c r="H10" s="284">
         <v>7</v>
       </c>
       <c r="I10" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -15364,13 +15361,13 @@
       <c r="B11" s="164" t="s">
         <v>299</v>
       </c>
-      <c r="E11" s="337"/>
-      <c r="F11" s="337"/>
+      <c r="E11" s="340"/>
+      <c r="F11" s="340"/>
       <c r="H11" s="284">
         <v>8</v>
       </c>
       <c r="I11" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -15383,13 +15380,13 @@
         <v>-1.7248638436905273E-2</v>
       </c>
       <c r="D12" s="163"/>
-      <c r="E12" s="337"/>
-      <c r="F12" s="337"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
       <c r="H12" s="284">
         <v>9</v>
       </c>
       <c r="I12" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -15401,13 +15398,13 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.283580450424601</v>
       </c>
-      <c r="E13" s="337"/>
-      <c r="F13" s="337"/>
+      <c r="E13" s="340"/>
+      <c r="F13" s="340"/>
       <c r="H13" s="284">
         <v>10</v>
       </c>
       <c r="I13" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -15419,8 +15416,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.18767799077696001</v>
       </c>
-      <c r="E14" s="337"/>
-      <c r="F14" s="337"/>
+      <c r="E14" s="340"/>
+      <c r="F14" s="340"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -15446,21 +15443,21 @@
       <c r="C18" s="154">
         <v>10</v>
       </c>
-      <c r="E18" s="337" t="s">
+      <c r="E18" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="F18" s="338"/>
+      <c r="F18" s="341"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="338"/>
-      <c r="F19" s="338"/>
+      <c r="E19" s="341"/>
+      <c r="F19" s="341"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="164" t="s">
         <v>337</v>
       </c>
-      <c r="E20" s="338"/>
-      <c r="F20" s="338"/>
+      <c r="E20" s="341"/>
+      <c r="F20" s="341"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
@@ -15474,8 +15471,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="338"/>
-      <c r="F21" s="338"/>
+      <c r="E21" s="341"/>
+      <c r="F21" s="341"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
@@ -15483,14 +15480,14 @@
       </c>
       <c r="C22" s="165">
         <f>Valuation_Model!C12</f>
-        <v>2.5642918304779925</v>
+        <v>2.564291830477992</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="338"/>
-      <c r="F22" s="338"/>
+      <c r="E22" s="341"/>
+      <c r="F22" s="341"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="164" t="s">
@@ -15510,8 +15507,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="168"/>
-      <c r="E25" s="336"/>
-      <c r="F25" s="336"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
@@ -15521,8 +15518,8 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="169"/>
-      <c r="E26" s="336"/>
-      <c r="F26" s="336"/>
+      <c r="E26" s="339"/>
+      <c r="F26" s="339"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
@@ -15530,14 +15527,14 @@
       </c>
       <c r="C27" s="165">
         <f>Valuation_Model!E76</f>
-        <v>2.6178627598733617</v>
+        <v>2.6178627598733613</v>
       </c>
       <c r="D27" s="165" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="336"/>
-      <c r="F27" s="336"/>
+      <c r="E27" s="339"/>
+      <c r="F27" s="339"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
@@ -15547,8 +15544,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="170"/>
-      <c r="E28" s="336"/>
-      <c r="F28" s="336"/>
+      <c r="E28" s="339"/>
+      <c r="F28" s="339"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="164" t="s">
@@ -15568,8 +15565,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="168"/>
-      <c r="E31" s="336"/>
-      <c r="F31" s="336"/>
+      <c r="E31" s="339"/>
+      <c r="F31" s="339"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
@@ -15579,8 +15576,8 @@
         <v>-0.06</v>
       </c>
       <c r="D32" s="169"/>
-      <c r="E32" s="336"/>
-      <c r="F32" s="336"/>
+      <c r="E32" s="339"/>
+      <c r="F32" s="339"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
@@ -15588,14 +15585,14 @@
       </c>
       <c r="C33" s="165">
         <f>Valuation_Model!E77</f>
-        <v>2.4307528629902109</v>
+        <v>2.4307528629902104</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="336"/>
-      <c r="F33" s="336"/>
+      <c r="E33" s="339"/>
+      <c r="F33" s="339"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
@@ -15605,8 +15602,8 @@
         <v>0.15</v>
       </c>
       <c r="D34" s="170"/>
-      <c r="E34" s="336"/>
-      <c r="F34" s="336"/>
+      <c r="E34" s="339"/>
+      <c r="F34" s="339"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="164" t="s">
@@ -15626,8 +15623,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="168"/>
-      <c r="E37" s="336"/>
-      <c r="F37" s="336"/>
+      <c r="E37" s="339"/>
+      <c r="F37" s="339"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
@@ -15637,8 +15634,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="169"/>
-      <c r="E38" s="336"/>
-      <c r="F38" s="336"/>
+      <c r="E38" s="339"/>
+      <c r="F38" s="339"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
@@ -15646,14 +15643,14 @@
       </c>
       <c r="C39" s="165">
         <f>Valuation_Model!E75</f>
-        <v>2.7419813260980841</v>
+        <v>2.7419813260980832</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="336"/>
-      <c r="F39" s="336"/>
+      <c r="E39" s="339"/>
+      <c r="F39" s="339"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
@@ -15664,8 +15661,8 @@
         <v>0.25</v>
       </c>
       <c r="D40" s="170"/>
-      <c r="E40" s="336"/>
-      <c r="F40" s="336"/>
+      <c r="E40" s="339"/>
+      <c r="F40" s="339"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
@@ -15673,7 +15670,7 @@
       </c>
       <c r="C42" s="159">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>2.6208259168970698</v>
+        <v>2.6208259168970693</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -15727,8 +15724,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="168"/>
-      <c r="E49" s="336"/>
-      <c r="F49" s="336"/>
+      <c r="E49" s="339"/>
+      <c r="F49" s="339"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
@@ -15738,8 +15735,8 @@
         <v>-0.1</v>
       </c>
       <c r="D50" s="169"/>
-      <c r="E50" s="336"/>
-      <c r="F50" s="336"/>
+      <c r="E50" s="339"/>
+      <c r="F50" s="339"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
@@ -15747,14 +15744,14 @@
       </c>
       <c r="C51" s="165">
         <f>Valuation_Model!E78</f>
-        <v>2.2874763405300755</v>
+        <v>2.2874763405300751</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="336"/>
-      <c r="F51" s="336"/>
+      <c r="E51" s="339"/>
+      <c r="F51" s="339"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
@@ -15764,8 +15761,8 @@
         <v>0.1</v>
       </c>
       <c r="D52" s="170"/>
-      <c r="E52" s="336"/>
-      <c r="F52" s="336"/>
+      <c r="E52" s="339"/>
+      <c r="F52" s="339"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="164" t="s">
@@ -15785,8 +15782,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="168"/>
-      <c r="E55" s="336"/>
-      <c r="F55" s="336"/>
+      <c r="E55" s="339"/>
+      <c r="F55" s="339"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
@@ -15796,8 +15793,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="169"/>
-      <c r="E56" s="336"/>
-      <c r="F56" s="336"/>
+      <c r="E56" s="339"/>
+      <c r="F56" s="339"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
@@ -15805,14 +15802,14 @@
       </c>
       <c r="C57" s="165">
         <f>Valuation_Model!E74</f>
-        <v>3.156626790651464</v>
+        <v>3.1566267906514631</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="336"/>
-      <c r="F57" s="336"/>
+      <c r="E57" s="339"/>
+      <c r="F57" s="339"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
@@ -15822,8 +15819,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="170"/>
-      <c r="E58" s="336"/>
-      <c r="F58" s="336"/>
+      <c r="E58" s="339"/>
+      <c r="F58" s="339"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
@@ -15831,7 +15828,7 @@
       </c>
       <c r="C60" s="159">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>2.6142810029480898</v>
+        <v>2.6142810029480894</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -15840,7 +15837,8 @@
       <c r="E60" s="103" t="s">
         <v>330</v>
       </c>
-      <c r="F60" s="324">
+      <c r="F60" s="322">
+        <f ca="1">Thesis!E20</f>
         <v>3</v>
       </c>
     </row>
@@ -15857,7 +15855,7 @@
       <c r="B63" s="112" t="s">
         <v>338</v>
       </c>
-      <c r="E63" s="291" t="s">
+      <c r="E63" s="290" t="s">
         <v>348</v>
       </c>
     </row>
@@ -15869,7 +15867,7 @@
         <v>10</v>
       </c>
       <c r="D64" s="154"/>
-      <c r="E64" s="290" t="s">
+      <c r="E64" s="289" t="s">
         <v>349</v>
       </c>
     </row>
@@ -15881,7 +15879,7 @@
         <v>1.8222579123958901E-2</v>
       </c>
       <c r="D65" s="155"/>
-      <c r="E65" s="290" t="s">
+      <c r="E65" s="289" t="s">
         <v>350</v>
       </c>
     </row>
@@ -15897,7 +15895,7 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E66" s="290" t="s">
+      <c r="E66" s="289" t="s">
         <v>351</v>
       </c>
     </row>
@@ -15905,7 +15903,7 @@
       <c r="B68" s="112" t="s">
         <v>325</v>
       </c>
-      <c r="E68" s="291" t="s">
+      <c r="E68" s="290" t="s">
         <v>352</v>
       </c>
     </row>
@@ -15927,7 +15925,7 @@
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
-      <c r="E70" s="290" t="s">
+      <c r="E70" s="289" t="s">
         <v>328</v>
       </c>
     </row>
@@ -15939,7 +15937,7 @@
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="290"/>
+      <c r="E71" s="289"/>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
@@ -15963,32 +15961,22 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B75" s="112" t="s">
         <v>130</v>
       </c>
-      <c r="E75" s="325" t="s">
-        <v>364</v>
-      </c>
-      <c r="F75" s="323"/>
-    </row>
-    <row r="76" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    </row>
+    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="283" t="s">
         <v>331</v>
       </c>
       <c r="C76" s="282">
-        <f>F60</f>
+        <f ca="1">F60</f>
         <v>3</v>
       </c>
       <c r="D76" s="138"/>
-      <c r="E76" s="326" t="s">
-        <v>365</v>
-      </c>
-      <c r="F76" s="323" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="77" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B77" s="103" t="s">
         <v>116</v>
       </c>
@@ -16000,20 +15988,6 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E77" s="327" t="s">
-        <v>365</v>
-      </c>
-      <c r="F77" s="323" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="78" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E78" s="328" t="s">
-        <v>365</v>
-      </c>
-      <c r="F78" s="323" t="s">
-        <v>368</v>
-      </c>
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="112" t="s">
@@ -16029,35 +16003,35 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B81" s="103" t="s">
         <v>126</v>
       </c>
       <c r="C81" s="120">
-        <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.24814351851851849</v>
+        <f ca="1">PV(C80, C76, -C77, 0)</f>
+        <v>1.2217592592592592</v>
       </c>
       <c r="D81" s="120"/>
       <c r="E81" s="103"/>
       <c r="F81" s="103"/>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B82" s="103" t="s">
         <v>127</v>
       </c>
       <c r="C82" s="120">
-        <f>C60/(1+C80)^C76</f>
-        <v>1.5128940989282929</v>
+        <f ca="1">C60/(1+C80)^C76</f>
+        <v>40.492512792014246</v>
       </c>
       <c r="D82" s="120"/>
     </row>
-    <row r="83" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="83" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B83" s="114" t="s">
         <v>106</v>
       </c>
       <c r="C83" s="115">
-        <f>C81+C82</f>
-        <v>1.7610376174468114</v>
+        <f ca="1">C81+C82</f>
+        <v>41.714272051273504</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16067,19 +16041,19 @@
         <v>131</v>
       </c>
       <c r="F83" s="270">
-        <f>(C83/C60-1)</f>
-        <v>-0.32637783946679311</v>
-      </c>
-    </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
+        <f ca="1">(C83/C60-1)</f>
+        <v>-0.40383537427352023</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.35">
       <c r="E84" s="124"/>
     </row>
-    <row r="85" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="112" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="152" t="s">
         <v>334</v>
       </c>
@@ -16092,20 +16066,55 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="103" t="s">
         <v>332</v>
       </c>
       <c r="C87" s="273">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.4453005765433362E-2</v>
-      </c>
-    </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
+        <v>2.2492801309755399</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B88" s="103"/>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C90" s="121"/>
+    <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
+      <c r="E89" s="331" t="s">
+        <v>364</v>
+      </c>
+      <c r="F89" s="328"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="327"/>
+    </row>
+    <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E90" s="324" t="s">
+        <v>365</v>
+      </c>
+      <c r="F90" s="329" t="s">
+        <v>366</v>
+      </c>
+      <c r="G90" s="2"/>
+      <c r="H90" s="327"/>
+    </row>
+    <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E91" s="325" t="s">
+        <v>365</v>
+      </c>
+      <c r="F91" s="329" t="s">
+        <v>367</v>
+      </c>
+      <c r="G91" s="2"/>
+      <c r="H91" s="327"/>
+    </row>
+    <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E92" s="326" t="s">
+        <v>365</v>
+      </c>
+      <c r="F92" s="330" t="s">
+        <v>368</v>
+      </c>
+      <c r="G92" s="2"/>
+      <c r="H92" s="327"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6848EF6F-6634-4191-994A-B4D2745ABEB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{483E8EA0-F3D6-460B-B1FC-91887BA3D758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3317,20 +3317,20 @@
     <xf numFmtId="0" fontId="57" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3744,13 +3744,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="332" t="s">
+      <c r="B12" s="333" t="s">
         <v>290</v>
       </c>
-      <c r="C12" s="332"/>
-      <c r="D12" s="332"/>
-      <c r="E12" s="332"/>
-      <c r="F12" s="332"/>
+      <c r="C12" s="333"/>
+      <c r="D12" s="333"/>
+      <c r="E12" s="333"/>
+      <c r="F12" s="333"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3816,15 +3816,14 @@
         <v>Target Buy Price (HKD):</v>
       </c>
       <c r="C20" s="259">
-        <f ca="1">C123</f>
-        <v>41.714272051273504</v>
+        <f>C123</f>
+        <v>1.761037617446811</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>344</v>
       </c>
       <c r="E20" s="323">
-        <f ca="1">Scenarios!C76</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -3833,7 +3832,7 @@
       </c>
       <c r="C21" s="288">
         <f ca="1">Scenarios!C87</f>
-        <v>2.2492801309755399</v>
+        <v>9.445300576543314E-2</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3853,22 +3852,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="332" t="s">
+      <c r="B25" s="333" t="s">
         <v>236</v>
       </c>
-      <c r="C25" s="332"/>
-      <c r="D25" s="332"/>
-      <c r="E25" s="332"/>
-      <c r="F25" s="332"/>
+      <c r="C25" s="333"/>
+      <c r="D25" s="333"/>
+      <c r="E25" s="333"/>
+      <c r="F25" s="333"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="336" t="s">
+      <c r="B26" s="334" t="s">
         <v>256</v>
       </c>
-      <c r="C26" s="336"/>
-      <c r="D26" s="336"/>
-      <c r="E26" s="336"/>
-      <c r="F26" s="336"/>
+      <c r="C26" s="334"/>
+      <c r="D26" s="334"/>
+      <c r="E26" s="334"/>
+      <c r="F26" s="334"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="241" t="s">
@@ -3880,13 +3879,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="334" t="s">
+      <c r="B29" s="332" t="s">
         <v>238</v>
       </c>
-      <c r="C29" s="334"/>
-      <c r="D29" s="334"/>
-      <c r="E29" s="334"/>
-      <c r="F29" s="334"/>
+      <c r="C29" s="332"/>
+      <c r="D29" s="332"/>
+      <c r="E29" s="332"/>
+      <c r="F29" s="332"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3906,13 +3905,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="334" t="s">
+      <c r="B32" s="332" t="s">
         <v>240</v>
       </c>
-      <c r="C32" s="334"/>
-      <c r="D32" s="334"/>
-      <c r="E32" s="334"/>
-      <c r="F32" s="334"/>
+      <c r="C32" s="332"/>
+      <c r="D32" s="332"/>
+      <c r="E32" s="332"/>
+      <c r="F32" s="332"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -3941,13 +3940,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="334" t="s">
+      <c r="B36" s="332" t="s">
         <v>243</v>
       </c>
-      <c r="C36" s="334"/>
-      <c r="D36" s="334"/>
-      <c r="E36" s="334"/>
-      <c r="F36" s="334"/>
+      <c r="C36" s="332"/>
+      <c r="D36" s="332"/>
+      <c r="E36" s="332"/>
+      <c r="F36" s="332"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -3963,13 +3962,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="334" t="s">
+      <c r="B39" s="332" t="s">
         <v>247</v>
       </c>
-      <c r="C39" s="334"/>
-      <c r="D39" s="334"/>
-      <c r="E39" s="334"/>
-      <c r="F39" s="334"/>
+      <c r="C39" s="332"/>
+      <c r="D39" s="332"/>
+      <c r="E39" s="332"/>
+      <c r="F39" s="332"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4003,13 +4002,13 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B45" s="334" t="s">
+      <c r="B45" s="332" t="s">
         <v>248</v>
       </c>
-      <c r="C45" s="334"/>
-      <c r="D45" s="334"/>
-      <c r="E45" s="334"/>
-      <c r="F45" s="334"/>
+      <c r="C45" s="332"/>
+      <c r="D45" s="332"/>
+      <c r="E45" s="332"/>
+      <c r="F45" s="332"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="47" t="s">
@@ -4025,13 +4024,13 @@
       </c>
     </row>
     <row r="48" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="334" t="s">
+      <c r="B48" s="332" t="s">
         <v>251</v>
       </c>
-      <c r="C48" s="335"/>
-      <c r="D48" s="335"/>
-      <c r="E48" s="335"/>
-      <c r="F48" s="335"/>
+      <c r="C48" s="336"/>
+      <c r="D48" s="336"/>
+      <c r="E48" s="336"/>
+      <c r="F48" s="336"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B49" s="47" t="s">
@@ -4060,13 +4059,13 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="332" t="s">
+      <c r="B52" s="333" t="s">
         <v>272</v>
       </c>
-      <c r="C52" s="332"/>
-      <c r="D52" s="332"/>
-      <c r="E52" s="332"/>
-      <c r="F52" s="332"/>
+      <c r="C52" s="333"/>
+      <c r="D52" s="333"/>
+      <c r="E52" s="333"/>
+      <c r="F52" s="333"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B53" s="47" t="s">
@@ -4127,22 +4126,22 @@
     </row>
     <row r="60" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="17"/>
-      <c r="B60" s="334" t="s">
+      <c r="B60" s="332" t="s">
         <v>307</v>
       </c>
-      <c r="C60" s="334"/>
-      <c r="D60" s="334"/>
-      <c r="E60" s="334"/>
-      <c r="F60" s="334"/>
+      <c r="C60" s="332"/>
+      <c r="D60" s="332"/>
+      <c r="E60" s="332"/>
+      <c r="F60" s="332"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B61" s="336" t="s">
+      <c r="B61" s="334" t="s">
         <v>263</v>
       </c>
-      <c r="C61" s="336"/>
-      <c r="D61" s="336"/>
-      <c r="E61" s="336"/>
-      <c r="F61" s="336"/>
+      <c r="C61" s="334"/>
+      <c r="D61" s="334"/>
+      <c r="E61" s="334"/>
+      <c r="F61" s="334"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B63" s="241" t="s">
@@ -4194,22 +4193,22 @@
       <c r="C68" s="125"/>
     </row>
     <row r="69" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="332" t="s">
+      <c r="B69" s="333" t="s">
         <v>315</v>
       </c>
-      <c r="C69" s="332"/>
-      <c r="D69" s="332"/>
-      <c r="E69" s="332"/>
-      <c r="F69" s="332"/>
+      <c r="C69" s="333"/>
+      <c r="D69" s="333"/>
+      <c r="E69" s="333"/>
+      <c r="F69" s="333"/>
     </row>
     <row r="70" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="332" t="s">
+      <c r="B70" s="333" t="s">
         <v>262</v>
       </c>
-      <c r="C70" s="332"/>
-      <c r="D70" s="332"/>
-      <c r="E70" s="332"/>
-      <c r="F70" s="332"/>
+      <c r="C70" s="333"/>
+      <c r="D70" s="333"/>
+      <c r="E70" s="333"/>
+      <c r="F70" s="333"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B71" s="47" t="s">
@@ -4246,13 +4245,13 @@
       <c r="A76" s="240"/>
     </row>
     <row r="77" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="332" t="s">
+      <c r="B77" s="333" t="s">
         <v>265</v>
       </c>
-      <c r="C77" s="332"/>
-      <c r="D77" s="332"/>
-      <c r="E77" s="332"/>
-      <c r="F77" s="332"/>
+      <c r="C77" s="333"/>
+      <c r="D77" s="333"/>
+      <c r="E77" s="333"/>
+      <c r="F77" s="333"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
@@ -4366,13 +4365,13 @@
       </c>
     </row>
     <row r="93" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="332" t="s">
+      <c r="B93" s="333" t="s">
         <v>271</v>
       </c>
-      <c r="C93" s="332"/>
-      <c r="D93" s="332"/>
-      <c r="E93" s="332"/>
-      <c r="F93" s="332"/>
+      <c r="C93" s="333"/>
+      <c r="D93" s="333"/>
+      <c r="E93" s="333"/>
+      <c r="F93" s="333"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="47" t="s">
@@ -4398,13 +4397,13 @@
       <c r="F97" s="36"/>
     </row>
     <row r="99" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="334" t="s">
+      <c r="B99" s="332" t="s">
         <v>371</v>
       </c>
-      <c r="C99" s="334"/>
-      <c r="D99" s="334"/>
-      <c r="E99" s="334"/>
-      <c r="F99" s="334"/>
+      <c r="C99" s="332"/>
+      <c r="D99" s="332"/>
+      <c r="E99" s="332"/>
+      <c r="F99" s="332"/>
     </row>
     <row r="101" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B101" s="267" t="s">
@@ -4566,13 +4565,13 @@
       <c r="F112" s="36"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B114" s="333" t="s">
+      <c r="B114" s="335" t="s">
         <v>279</v>
       </c>
-      <c r="C114" s="333"/>
-      <c r="D114" s="333"/>
-      <c r="E114" s="333"/>
-      <c r="F114" s="333"/>
+      <c r="C114" s="335"/>
+      <c r="D114" s="335"/>
+      <c r="E114" s="335"/>
+      <c r="F114" s="335"/>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B115" s="241" t="s">
@@ -4584,7 +4583,7 @@
         <v>280</v>
       </c>
       <c r="C116" s="258">
-        <f ca="1">E20</f>
+        <f>E20</f>
         <v>3</v>
       </c>
     </row>
@@ -4617,22 +4616,22 @@
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B121" s="243" t="str">
-        <f ca="1">"PV("&amp;C116&amp;" yrs of Dividends)"</f>
+        <f>"PV("&amp;C116&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C121" s="247">
-        <f ca="1">Scenarios!C81</f>
-        <v>1.2217592592592592</v>
+        <f>Scenarios!C81</f>
+        <v>0.24814351851851849</v>
       </c>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B122" s="243" t="str">
-        <f ca="1">"+ PV(Equity Value realized at year "&amp;C116&amp;")"</f>
+        <f>"+ PV(Equity Value realized at year "&amp;C116&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C122" s="247">
-        <f ca="1">Scenarios!C82</f>
-        <v>40.492512792014246</v>
+        <f>Scenarios!C82</f>
+        <v>1.5128940989282924</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.35">
@@ -4640,8 +4639,8 @@
         <v>275</v>
       </c>
       <c r="C123" s="246">
-        <f ca="1">Scenarios!C83</f>
-        <v>41.714272051273504</v>
+        <f>Scenarios!C83</f>
+        <v>1.761037617446811</v>
       </c>
       <c r="D123" s="47" t="str">
         <f>Reporting_currency</f>
@@ -4653,18 +4652,12 @@
         <v>277</v>
       </c>
       <c r="C124" s="158">
-        <f ca="1">Scenarios!F83</f>
-        <v>-0.40383537427352023</v>
+        <f>Scenarios!F83</f>
+        <v>-0.32637783946679311</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B93:F93"/>
@@ -4678,6 +4671,12 @@
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -15244,8 +15243,8 @@
         <v>1</v>
       </c>
       <c r="I4" s="272">
-        <f t="shared" ref="I4:I13" ca="1" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.57999999999999996</v>
+        <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
+        <v>0.1178</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -15253,8 +15252,8 @@
         <v>2</v>
       </c>
       <c r="I5" s="272">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.57999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>0.1178</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
@@ -15273,8 +15272,8 @@
         <v>3</v>
       </c>
       <c r="I6" s="272">
-        <f t="shared" ca="1" si="0"/>
-        <v>70.551062104600618</v>
+        <f t="shared" si="0"/>
+        <v>2.7320810029480893</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15298,7 +15297,7 @@
         <v>4</v>
       </c>
       <c r="I7" s="272" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15320,7 +15319,7 @@
         <v>5</v>
       </c>
       <c r="I8" s="272" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15342,7 +15341,7 @@
         <v>6</v>
       </c>
       <c r="I9" s="272" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15353,7 +15352,7 @@
         <v>7</v>
       </c>
       <c r="I10" s="272" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15367,7 +15366,7 @@
         <v>8</v>
       </c>
       <c r="I11" s="272" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15386,7 +15385,7 @@
         <v>9</v>
       </c>
       <c r="I12" s="272" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15404,7 +15403,7 @@
         <v>10</v>
       </c>
       <c r="I13" s="272" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15838,7 +15837,7 @@
         <v>330</v>
       </c>
       <c r="F60" s="322">
-        <f ca="1">Thesis!E20</f>
+        <f>Thesis!E20</f>
         <v>3</v>
       </c>
     </row>
@@ -15971,7 +15970,7 @@
         <v>331</v>
       </c>
       <c r="C76" s="282">
-        <f ca="1">F60</f>
+        <f>F60</f>
         <v>3</v>
       </c>
       <c r="D76" s="138"/>
@@ -16008,8 +16007,8 @@
         <v>126</v>
       </c>
       <c r="C81" s="120">
-        <f ca="1">PV(C80, C76, -C77, 0)</f>
-        <v>1.2217592592592592</v>
+        <f>PV(C80, C76, -C77, 0)</f>
+        <v>0.24814351851851849</v>
       </c>
       <c r="D81" s="120"/>
       <c r="E81" s="103"/>
@@ -16020,8 +16019,8 @@
         <v>127</v>
       </c>
       <c r="C82" s="120">
-        <f ca="1">C60/(1+C80)^C76</f>
-        <v>40.492512792014246</v>
+        <f>C60/(1+C80)^C76</f>
+        <v>1.5128940989282924</v>
       </c>
       <c r="D82" s="120"/>
     </row>
@@ -16030,8 +16029,8 @@
         <v>106</v>
       </c>
       <c r="C83" s="115">
-        <f ca="1">C81+C82</f>
-        <v>41.714272051273504</v>
+        <f>C81+C82</f>
+        <v>1.761037617446811</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16041,8 +16040,8 @@
         <v>131</v>
       </c>
       <c r="F83" s="270">
-        <f ca="1">(C83/C60-1)</f>
-        <v>-0.40383537427352023</v>
+        <f>(C83/C60-1)</f>
+        <v>-0.32637783946679311</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16072,7 +16071,7 @@
       </c>
       <c r="C87" s="273">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>2.2492801309755399</v>
+        <v>9.445300576543314E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{483E8EA0-F3D6-460B-B1FC-91887BA3D758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D927423-F760-44D0-BFC5-6E7E3A278992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3689,7 +3689,7 @@
         <v>99</v>
       </c>
       <c r="C6" s="50">
-        <v>2.29</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>43</v>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>3053.3337150000002</v>
+        <v>3040.0003799999995</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -3784,7 +3784,7 @@
         <v>2</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0725773999999999</v>
+        <v>1.0726602000000001</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="C20" s="259">
         <f>C123</f>
-        <v>1.761037617446811</v>
+        <v>1.7611544086745501</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>344</v>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="C21" s="288">
         <f ca="1">Scenarios!C87</f>
-        <v>9.445300576543314E-2</v>
+        <v>9.6153062008305534E-2</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C120</f>
-        <v>3.3885885479174489E-2</v>
+        <v>3.4037135153498488E-2</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="C56" s="94">
         <f>Normalized_FCF!C92</f>
-        <v>5.1441048034934496E-2</v>
+        <v>5.1666666666666673E-2</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="C73" s="255">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.77598677747309575</v>
+        <v>0.77604668149976541</v>
       </c>
       <c r="D73" s="1" t="str">
         <f>Market_currency</f>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="C82" s="255">
         <f>C81*C28*Exchange_Rate/Common_Shares</f>
-        <v>2.7349915848210515E-2</v>
+        <v>2.7352027185846606E-2</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C87" s="255">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.6325203377676956</v>
+        <v>1.6326463638092357</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C91" s="255">
         <f>C90*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.18313463108541109</v>
+        <v>0.18314876857092394</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Market_currency</f>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="C95" s="255">
         <f>Valuation_Model!C12</f>
-        <v>2.564291830477992</v>
+        <v>2.5644897866940783</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C108" s="248">
         <f>Scenarios!C60</f>
-        <v>2.6142810029480894</v>
+        <v>2.6144828181896225</v>
       </c>
       <c r="D108" s="243" t="str">
         <f>Market_currency</f>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="C122" s="247">
         <f>Scenarios!C82</f>
-        <v>1.5128940989282924</v>
+        <v>1.5130108901560315</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.35">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="C123" s="246">
         <f>Scenarios!C83</f>
-        <v>1.761037617446811</v>
+        <v>1.7611544086745501</v>
       </c>
       <c r="D123" s="47" t="str">
         <f>Reporting_currency</f>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="C124" s="158">
         <f>Scenarios!F83</f>
-        <v>-0.32637783946679311</v>
+        <v>-0.32638516634274639</v>
       </c>
     </row>
   </sheetData>
@@ -7742,11 +7742,11 @@
       </c>
       <c r="C47" s="151">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>2.4320437449256316</v>
+        <v>2.4322314919563635</v>
       </c>
       <c r="D47" s="151">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.7958696915774188</v>
+        <v>1.7960083277359495</v>
       </c>
       <c r="F47" s="291"/>
     </row>
@@ -8149,11 +8149,11 @@
       </c>
       <c r="C86" s="192">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-36466.559022599999</v>
+        <v>-36469.374139800006</v>
       </c>
       <c r="D86" s="255">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-2.7349915848210515E-2</v>
+        <v>-2.7352027185846606E-2</v>
       </c>
       <c r="E86" s="277" t="str">
         <f>Market_currency</f>
@@ -8166,11 +8166,11 @@
       </c>
       <c r="C87" s="192">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>2176694.0557769835</v>
+        <v>2176862.0905200415</v>
       </c>
       <c r="D87" s="255">
         <f>C87*$H$1/Common_Shares</f>
-        <v>1.6325203377676951</v>
+        <v>1.6326463638092357</v>
       </c>
       <c r="E87" s="277" t="str">
         <f>Market_currency</f>
@@ -8183,11 +8183,11 @@
       </c>
       <c r="C88" s="192">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>244179.53863631998</v>
+        <v>244198.38861935999</v>
       </c>
       <c r="D88" s="255">
         <f>C88*$H$1/Common_Shares</f>
-        <v>0.18313463108541109</v>
+        <v>0.18314876857092394</v>
       </c>
       <c r="E88" s="277" t="str">
         <f>Market_currency</f>
@@ -8200,11 +8200,11 @@
       </c>
       <c r="C89" s="191">
         <f>SUM(C86:C88)</f>
-        <v>2384407.0353907035</v>
+        <v>2384591.1049996014</v>
       </c>
       <c r="D89" s="279">
         <f>SUM(D86:D88)</f>
-        <v>1.7883050530048958</v>
+        <v>1.788443105194313</v>
       </c>
       <c r="E89" s="277" t="str">
         <f>Market_currency</f>
@@ -11827,12 +11827,12 @@
       </c>
       <c r="C92" s="23">
         <f>C89/Market_Price</f>
-        <v>5.1441048034934496E-2</v>
+        <v>5.1666666666666673E-2</v>
       </c>
       <c r="E92" s="312"/>
       <c r="G92" s="23">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G89/Market_Price)</f>
-        <v>5.1441048034934496E-2</v>
+        <v>5.1666666666666673E-2</v>
       </c>
       <c r="H92" s="23">
         <f t="shared" si="38"/>
@@ -12854,30 +12854,30 @@
       </c>
       <c r="C119" s="182">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>7.7598677747309566E-2</v>
+        <v>7.7604668149976533E-2</v>
       </c>
       <c r="D119" s="27"/>
       <c r="E119" s="309"/>
       <c r="F119" s="27"/>
       <c r="G119" s="182">
         <f t="shared" ref="G119:Q119" si="48">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.12224967532729059</v>
+        <v>0.12225911266311093</v>
       </c>
       <c r="H119" s="182">
         <f t="shared" si="48"/>
-        <v>3.6620201157624856E-2</v>
+        <v>3.6623028135571487E-2</v>
       </c>
       <c r="I119" s="182">
         <f t="shared" si="48"/>
-        <v>6.4840527936928904E-2</v>
+        <v>6.484553344582103E-2</v>
       </c>
       <c r="J119" s="182">
         <f t="shared" si="48"/>
-        <v>0.22806731704789368</v>
+        <v>0.22808492321212165</v>
       </c>
       <c r="K119" s="182">
         <f t="shared" si="48"/>
-        <v>0.16323392523565936</v>
+        <v>0.16324652644188423</v>
       </c>
       <c r="L119" s="182" t="str">
         <f t="shared" si="48"/>
@@ -12911,30 +12911,30 @@
       </c>
       <c r="C120" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.3885885479174489E-2</v>
+        <v>3.4037135153498488E-2</v>
       </c>
       <c r="D120" s="27"/>
       <c r="E120" s="309"/>
       <c r="F120" s="27"/>
       <c r="G120" s="79">
         <f t="shared" ref="G120" si="49">IF(G$4="","",G119/Market_Price)</f>
-        <v>5.3384137697506807E-2</v>
+        <v>5.3622417834697782E-2</v>
       </c>
       <c r="H120" s="79">
         <f t="shared" ref="H120" si="50">IF(H$4="","",H119/Market_Price)</f>
-        <v>1.5991354217303431E-2</v>
+        <v>1.6062731638408548E-2</v>
       </c>
       <c r="I120" s="79">
         <f t="shared" ref="I120" si="51">IF(I$4="","",I119/Market_Price)</f>
-        <v>2.831464102049297E-2</v>
+        <v>2.8441023441149578E-2</v>
       </c>
       <c r="J120" s="79">
         <f t="shared" ref="J120" si="52">IF(J$4="","",J119/Market_Price)</f>
-        <v>9.9592714868075846E-2</v>
+        <v>0.10003724702286038</v>
       </c>
       <c r="K120" s="79">
         <f t="shared" ref="K120" si="53">IF(K$4="","",K119/Market_Price)</f>
-        <v>7.1281190059239885E-2</v>
+        <v>7.1599353702580804E-2</v>
       </c>
       <c r="L120" s="79" t="str">
         <f t="shared" ref="L120" si="54">IF(L$4="","",L119/Market_Price)</f>
@@ -13817,7 +13817,7 @@
       </c>
       <c r="C11" s="238">
         <f>Exchange_Rate</f>
-        <v>1.0725773999999999</v>
+        <v>1.0726602000000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -13831,7 +13831,7 @@
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>2.564291830477992</v>
+        <v>2.5644897866940783</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -13884,7 +13884,7 @@
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>2.6128903586149343</v>
+        <v>2.613092066502583</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14820,23 +14820,23 @@
       </c>
       <c r="B65" s="128">
         <f>C12</f>
-        <v>2.564291830477992</v>
+        <v>2.5644897866940783</v>
       </c>
       <c r="C65" s="128">
         <f>C12</f>
-        <v>2.564291830477992</v>
+        <v>2.5644897866940783</v>
       </c>
       <c r="D65" s="128">
         <f>C12</f>
-        <v>2.564291830477992</v>
+        <v>2.5644897866940783</v>
       </c>
       <c r="E65" s="145">
         <f>C12</f>
-        <v>2.564291830477992</v>
+        <v>2.5644897866940783</v>
       </c>
       <c r="F65" s="128">
         <f>C12</f>
-        <v>2.564291830477992</v>
+        <v>2.5644897866940783</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -14847,23 +14847,23 @@
       </c>
       <c r="B66" s="128">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.4431119244101862</v>
+        <v>2.443300525873672</v>
       </c>
       <c r="C66" s="128">
         <f t="shared" si="4"/>
-        <v>2.4893658513431256</v>
+        <v>2.489558023481464</v>
       </c>
       <c r="D66" s="128">
         <f t="shared" si="4"/>
-        <v>2.5908825114419964</v>
+        <v>2.5910825203848922</v>
       </c>
       <c r="E66" s="128">
         <f t="shared" si="4"/>
-        <v>2.6467052675837399</v>
+        <v>2.6469095858885598</v>
       </c>
       <c r="F66" s="128">
         <f t="shared" si="4"/>
-        <v>2.7063078519409491</v>
+        <v>2.7065167713999467</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -14874,23 +14874,23 @@
       </c>
       <c r="B67" s="128">
         <f t="shared" si="4"/>
-        <v>2.3598155710591446</v>
+        <v>2.3599977422752119</v>
       </c>
       <c r="C67" s="128">
         <f t="shared" si="4"/>
-        <v>2.4307528629902104</v>
+        <v>2.4309405103684378</v>
       </c>
       <c r="D67" s="128">
         <f t="shared" si="4"/>
-        <v>2.6178627598733613</v>
+        <v>2.6180648516165936</v>
       </c>
       <c r="E67" s="128">
         <f t="shared" si="4"/>
-        <v>2.7419813260980832</v>
+        <v>2.7421929994503293</v>
       </c>
       <c r="F67" s="128">
         <f t="shared" si="4"/>
-        <v>2.8933859746928707</v>
+        <v>2.8936093360639989</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -14901,23 +14901,23 @@
       </c>
       <c r="B68" s="128">
         <f t="shared" si="4"/>
-        <v>2.2874763405300751</v>
+        <v>2.2876529273582111</v>
       </c>
       <c r="C68" s="128">
         <f t="shared" si="4"/>
-        <v>2.3756754943990503</v>
+        <v>2.3758588899572044</v>
       </c>
       <c r="D68" s="128">
         <f t="shared" si="4"/>
-        <v>2.6483990284514669</v>
+        <v>2.6486034775099276</v>
       </c>
       <c r="E68" s="128">
         <f t="shared" si="4"/>
-        <v>2.8618094929407585</v>
+        <v>2.8620304166950867</v>
       </c>
       <c r="F68" s="128">
         <f t="shared" si="4"/>
-        <v>3.1566267906514631</v>
+        <v>3.1568704734833655</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -14928,23 +14928,23 @@
       </c>
       <c r="B69" s="128">
         <f t="shared" si="4"/>
-        <v>2.2349995503269189</v>
+        <v>2.2351720860924194</v>
       </c>
       <c r="C69" s="128">
         <f t="shared" si="4"/>
-        <v>2.3329628579556747</v>
+        <v>2.3331429562167783</v>
       </c>
       <c r="D69" s="128">
         <f t="shared" si="4"/>
-        <v>2.6768089977767149</v>
+        <v>2.6770156400059997</v>
       </c>
       <c r="E69" s="128">
         <f t="shared" si="4"/>
-        <v>2.9866254102071528</v>
+        <v>2.9868559694040608</v>
       </c>
       <c r="F69" s="128">
         <f t="shared" si="4"/>
-        <v>3.4671586468436892</v>
+        <v>3.467426301873489</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -14955,23 +14955,23 @@
       </c>
       <c r="B70" s="128">
         <f t="shared" si="4"/>
-        <v>2.1996438009032353</v>
+        <v>2.1998136073029557</v>
       </c>
       <c r="C70" s="128">
         <f t="shared" si="4"/>
-        <v>2.3025619045832193</v>
+        <v>2.3027396559750533</v>
       </c>
       <c r="D70" s="128">
         <f t="shared" si="4"/>
-        <v>2.700927329361944</v>
+        <v>2.7011358334595239</v>
       </c>
       <c r="E70" s="128">
         <f t="shared" si="4"/>
-        <v>3.1060153031642814</v>
+        <v>3.1062550789297436</v>
       </c>
       <c r="F70" s="128">
         <f t="shared" si="4"/>
-        <v>3.8070545183066264</v>
+        <v>3.8073484123548478</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -14981,23 +14981,23 @@
       </c>
       <c r="B71" s="128">
         <f t="shared" si="4"/>
-        <v>2.1766743908779786</v>
+        <v>2.1768424241029609</v>
       </c>
       <c r="C71" s="128">
         <f t="shared" si="4"/>
-        <v>2.2819173077064328</v>
+        <v>2.2820934653926552</v>
       </c>
       <c r="D71" s="128">
         <f t="shared" si="4"/>
-        <v>2.7203438746537345</v>
+        <v>2.7205538776547504</v>
       </c>
       <c r="E71" s="128">
         <f t="shared" si="4"/>
-        <v>3.2149540010149473</v>
+        <v>3.2152021865456928</v>
       </c>
       <c r="F71" s="128">
         <f t="shared" si="4"/>
-        <v>4.1651831329817819</v>
+        <v>4.165504673565624</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15032,7 +15032,7 @@
       </c>
       <c r="E74" s="139">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>3.1566267906514631</v>
+        <v>3.1568704734833655</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
@@ -15054,7 +15054,7 @@
       </c>
       <c r="E75" s="139">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>2.7419813260980832</v>
+        <v>2.7421929994503293</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -15077,7 +15077,7 @@
       </c>
       <c r="E76" s="139">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>2.6178627598733613</v>
+        <v>2.6180648516165936</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15100,7 +15100,7 @@
       </c>
       <c r="E77" s="139">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>2.4307528629902104</v>
+        <v>2.4309405103684378</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -15123,7 +15123,7 @@
       </c>
       <c r="E78" s="139">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.2874763405300751</v>
+        <v>2.2876529273582111</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
@@ -15224,7 +15224,7 @@
       </c>
       <c r="I3" s="272">
         <f>-Market_Price</f>
-        <v>-2.29</v>
+        <v>-2.2799999999999998</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -15273,7 +15273,7 @@
       </c>
       <c r="I6" s="272">
         <f t="shared" si="0"/>
-        <v>2.7320810029480893</v>
+        <v>2.7322828181896224</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="C21" s="165">
         <f>Market_Price</f>
-        <v>2.29</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -15479,7 +15479,7 @@
       </c>
       <c r="C22" s="165">
         <f>Valuation_Model!C12</f>
-        <v>2.564291830477992</v>
+        <v>2.5644897866940783</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -15526,7 +15526,7 @@
       </c>
       <c r="C27" s="165">
         <f>Valuation_Model!E76</f>
-        <v>2.6178627598733613</v>
+        <v>2.6180648516165936</v>
       </c>
       <c r="D27" s="165" t="str">
         <f>Market_currency</f>
@@ -15584,7 +15584,7 @@
       </c>
       <c r="C33" s="165">
         <f>Valuation_Model!E77</f>
-        <v>2.4307528629902104</v>
+        <v>2.4309405103684378</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -15642,7 +15642,7 @@
       </c>
       <c r="C39" s="165">
         <f>Valuation_Model!E75</f>
-        <v>2.7419813260980832</v>
+        <v>2.7421929994503293</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -15669,7 +15669,7 @@
       </c>
       <c r="C42" s="159">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>2.6208259168970693</v>
+        <v>2.621028237387804</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -15743,7 +15743,7 @@
       </c>
       <c r="C51" s="165">
         <f>Valuation_Model!E78</f>
-        <v>2.2874763405300751</v>
+        <v>2.2876529273582111</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -15801,7 +15801,7 @@
       </c>
       <c r="C57" s="165">
         <f>Valuation_Model!E74</f>
-        <v>3.1566267906514631</v>
+        <v>3.1568704734833655</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -15827,7 +15827,7 @@
       </c>
       <c r="C60" s="159">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>2.6142810029480894</v>
+        <v>2.6144828181896225</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -15888,7 +15888,7 @@
       </c>
       <c r="C66" s="165">
         <f>Valuation_Model!C18</f>
-        <v>2.6128903586149343</v>
+        <v>2.613092066502583</v>
       </c>
       <c r="D66" s="165" t="str">
         <f>Market_currency</f>
@@ -16020,7 +16020,7 @@
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
-        <v>1.5128940989282924</v>
+        <v>1.5130108901560315</v>
       </c>
       <c r="D82" s="120"/>
     </row>
@@ -16030,7 +16030,7 @@
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
-        <v>1.761037617446811</v>
+        <v>1.7611544086745501</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="F83" s="270">
         <f>(C83/C60-1)</f>
-        <v>-0.32637783946679311</v>
+        <v>-0.32638516634274639</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16058,7 +16058,7 @@
       </c>
       <c r="C86" s="274">
         <f>Market_Price</f>
-        <v>2.29</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16071,7 +16071,7 @@
       </c>
       <c r="C87" s="273">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.445300576543314E-2</v>
+        <v>9.6153062008305534E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D927423-F760-44D0-BFC5-6E7E3A278992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E491A4BF-4D30-458B-A295-ADC7075B401A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="388">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1961,6 +1961,14 @@
   </si>
   <si>
     <t>Historical Average or D&amp;A</t>
+  </si>
+  <si>
+    <t>Investment property income</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Financial assets income</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3317,20 +3325,20 @@
     <xf numFmtId="0" fontId="57" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3744,13 +3752,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="333" t="s">
+      <c r="B12" s="332" t="s">
         <v>290</v>
       </c>
-      <c r="C12" s="333"/>
-      <c r="D12" s="333"/>
-      <c r="E12" s="333"/>
-      <c r="F12" s="333"/>
+      <c r="C12" s="332"/>
+      <c r="D12" s="332"/>
+      <c r="E12" s="332"/>
+      <c r="F12" s="332"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3852,22 +3860,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="333" t="s">
+      <c r="B25" s="332" t="s">
         <v>236</v>
       </c>
-      <c r="C25" s="333"/>
-      <c r="D25" s="333"/>
-      <c r="E25" s="333"/>
-      <c r="F25" s="333"/>
+      <c r="C25" s="332"/>
+      <c r="D25" s="332"/>
+      <c r="E25" s="332"/>
+      <c r="F25" s="332"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="334" t="s">
+      <c r="B26" s="336" t="s">
         <v>256</v>
       </c>
-      <c r="C26" s="334"/>
-      <c r="D26" s="334"/>
-      <c r="E26" s="334"/>
-      <c r="F26" s="334"/>
+      <c r="C26" s="336"/>
+      <c r="D26" s="336"/>
+      <c r="E26" s="336"/>
+      <c r="F26" s="336"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="241" t="s">
@@ -3879,13 +3887,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="332" t="s">
+      <c r="B29" s="334" t="s">
         <v>238</v>
       </c>
-      <c r="C29" s="332"/>
-      <c r="D29" s="332"/>
-      <c r="E29" s="332"/>
-      <c r="F29" s="332"/>
+      <c r="C29" s="334"/>
+      <c r="D29" s="334"/>
+      <c r="E29" s="334"/>
+      <c r="F29" s="334"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3905,13 +3913,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="332" t="s">
+      <c r="B32" s="334" t="s">
         <v>240</v>
       </c>
-      <c r="C32" s="332"/>
-      <c r="D32" s="332"/>
-      <c r="E32" s="332"/>
-      <c r="F32" s="332"/>
+      <c r="C32" s="334"/>
+      <c r="D32" s="334"/>
+      <c r="E32" s="334"/>
+      <c r="F32" s="334"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -3940,13 +3948,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="332" t="s">
+      <c r="B36" s="334" t="s">
         <v>243</v>
       </c>
-      <c r="C36" s="332"/>
-      <c r="D36" s="332"/>
-      <c r="E36" s="332"/>
-      <c r="F36" s="332"/>
+      <c r="C36" s="334"/>
+      <c r="D36" s="334"/>
+      <c r="E36" s="334"/>
+      <c r="F36" s="334"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -3962,13 +3970,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="332" t="s">
+      <c r="B39" s="334" t="s">
         <v>247</v>
       </c>
-      <c r="C39" s="332"/>
-      <c r="D39" s="332"/>
-      <c r="E39" s="332"/>
-      <c r="F39" s="332"/>
+      <c r="C39" s="334"/>
+      <c r="D39" s="334"/>
+      <c r="E39" s="334"/>
+      <c r="F39" s="334"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4002,13 +4010,13 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B45" s="332" t="s">
+      <c r="B45" s="334" t="s">
         <v>248</v>
       </c>
-      <c r="C45" s="332"/>
-      <c r="D45" s="332"/>
-      <c r="E45" s="332"/>
-      <c r="F45" s="332"/>
+      <c r="C45" s="334"/>
+      <c r="D45" s="334"/>
+      <c r="E45" s="334"/>
+      <c r="F45" s="334"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="47" t="s">
@@ -4024,13 +4032,13 @@
       </c>
     </row>
     <row r="48" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="332" t="s">
+      <c r="B48" s="334" t="s">
         <v>251</v>
       </c>
-      <c r="C48" s="336"/>
-      <c r="D48" s="336"/>
-      <c r="E48" s="336"/>
-      <c r="F48" s="336"/>
+      <c r="C48" s="335"/>
+      <c r="D48" s="335"/>
+      <c r="E48" s="335"/>
+      <c r="F48" s="335"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B49" s="47" t="s">
@@ -4059,13 +4067,13 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="333" t="s">
+      <c r="B52" s="332" t="s">
         <v>272</v>
       </c>
-      <c r="C52" s="333"/>
-      <c r="D52" s="333"/>
-      <c r="E52" s="333"/>
-      <c r="F52" s="333"/>
+      <c r="C52" s="332"/>
+      <c r="D52" s="332"/>
+      <c r="E52" s="332"/>
+      <c r="F52" s="332"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B53" s="47" t="s">
@@ -4126,22 +4134,22 @@
     </row>
     <row r="60" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="17"/>
-      <c r="B60" s="332" t="s">
+      <c r="B60" s="334" t="s">
         <v>307</v>
       </c>
-      <c r="C60" s="332"/>
-      <c r="D60" s="332"/>
-      <c r="E60" s="332"/>
-      <c r="F60" s="332"/>
+      <c r="C60" s="334"/>
+      <c r="D60" s="334"/>
+      <c r="E60" s="334"/>
+      <c r="F60" s="334"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B61" s="334" t="s">
+      <c r="B61" s="336" t="s">
         <v>263</v>
       </c>
-      <c r="C61" s="334"/>
-      <c r="D61" s="334"/>
-      <c r="E61" s="334"/>
-      <c r="F61" s="334"/>
+      <c r="C61" s="336"/>
+      <c r="D61" s="336"/>
+      <c r="E61" s="336"/>
+      <c r="F61" s="336"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B63" s="241" t="s">
@@ -4193,22 +4201,22 @@
       <c r="C68" s="125"/>
     </row>
     <row r="69" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="333" t="s">
+      <c r="B69" s="332" t="s">
         <v>315</v>
       </c>
-      <c r="C69" s="333"/>
-      <c r="D69" s="333"/>
-      <c r="E69" s="333"/>
-      <c r="F69" s="333"/>
+      <c r="C69" s="332"/>
+      <c r="D69" s="332"/>
+      <c r="E69" s="332"/>
+      <c r="F69" s="332"/>
     </row>
     <row r="70" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="333" t="s">
+      <c r="B70" s="332" t="s">
         <v>262</v>
       </c>
-      <c r="C70" s="333"/>
-      <c r="D70" s="333"/>
-      <c r="E70" s="333"/>
-      <c r="F70" s="333"/>
+      <c r="C70" s="332"/>
+      <c r="D70" s="332"/>
+      <c r="E70" s="332"/>
+      <c r="F70" s="332"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B71" s="47" t="s">
@@ -4245,13 +4253,13 @@
       <c r="A76" s="240"/>
     </row>
     <row r="77" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="333" t="s">
+      <c r="B77" s="332" t="s">
         <v>265</v>
       </c>
-      <c r="C77" s="333"/>
-      <c r="D77" s="333"/>
-      <c r="E77" s="333"/>
-      <c r="F77" s="333"/>
+      <c r="C77" s="332"/>
+      <c r="D77" s="332"/>
+      <c r="E77" s="332"/>
+      <c r="F77" s="332"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
@@ -4365,13 +4373,13 @@
       </c>
     </row>
     <row r="93" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="333" t="s">
+      <c r="B93" s="332" t="s">
         <v>271</v>
       </c>
-      <c r="C93" s="333"/>
-      <c r="D93" s="333"/>
-      <c r="E93" s="333"/>
-      <c r="F93" s="333"/>
+      <c r="C93" s="332"/>
+      <c r="D93" s="332"/>
+      <c r="E93" s="332"/>
+      <c r="F93" s="332"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="47" t="s">
@@ -4397,13 +4405,13 @@
       <c r="F97" s="36"/>
     </row>
     <row r="99" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="332" t="s">
+      <c r="B99" s="334" t="s">
         <v>371</v>
       </c>
-      <c r="C99" s="332"/>
-      <c r="D99" s="332"/>
-      <c r="E99" s="332"/>
-      <c r="F99" s="332"/>
+      <c r="C99" s="334"/>
+      <c r="D99" s="334"/>
+      <c r="E99" s="334"/>
+      <c r="F99" s="334"/>
     </row>
     <row r="101" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B101" s="267" t="s">
@@ -4565,13 +4573,13 @@
       <c r="F112" s="36"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B114" s="335" t="s">
+      <c r="B114" s="333" t="s">
         <v>279</v>
       </c>
-      <c r="C114" s="335"/>
-      <c r="D114" s="335"/>
-      <c r="E114" s="335"/>
-      <c r="F114" s="335"/>
+      <c r="C114" s="333"/>
+      <c r="D114" s="333"/>
+      <c r="E114" s="333"/>
+      <c r="F114" s="333"/>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B115" s="241" t="s">
@@ -4658,6 +4666,12 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B93:F93"/>
@@ -4671,12 +4685,6 @@
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B110:F110"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -4914,7 +4922,7 @@
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B10" s="40" t="s">
-        <v>172</v>
+        <v>387</v>
       </c>
       <c r="C10" s="194"/>
       <c r="D10" s="185"/>
@@ -4930,7 +4938,7 @@
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="40" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="C11" s="194"/>
       <c r="D11" s="185"/>
@@ -6137,7 +6145,7 @@
     </row>
     <row r="57" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B57" s="40" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="C57" s="192">
         <f>IF(C$4="","",C11)</f>

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E491A4BF-4D30-458B-A295-ADC7075B401A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE8C373-63D7-4E62-94C2-0E3AC03A3F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="388">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1919,6 +1919,31 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>AI Prompt</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I need to categorize the balance sheet items from the provided financial statements into the exact structure below. Follow these steps:
+1.	Identify Line Items: Extract all assets, liabilities, and equity line items from the text. Preserve their exact wording (e.g., ‘Trade Receivables’ vs. ‘Accounts Receivable’).
+2.	Map to Categories: Classify each item into the pre-defined structure below. Use the descriptions to resolve ambiguities.
+3.	Flag Uncertainties: Note items that don’t fit cleanly or require assumptions.
+4.	Format Output: Provide a table with columns: PDF Line Item | Category | Subcategory | Amount. 
+STRUCTURE TO FOLLOW (use exact names):
+•	ST Operating Assets: ST AR, Operating ST Financial Assets, Inventory, Prepayments and Contract Assets, ST DTA, Other ST Assets, Operating ST Assets
+•	LT Operating Assets: LT AR, Operating LT Financial Assets, PP&amp;E &amp; Right of Use Assets, Biological assets, Intangible assets, LT DTA, Other assets &amp; Goodwill
+•	ST Non-Operating Assets: Cash and cash equivalents, Restricted cash, Securities with stable income, Other Securities, Properties with stable income, Other Properties
+•	LT Non-Operating Assets: LT Deposits, Securities with stable income, Other Securities, JV or associate with stable income, Other JV or associate, Properties with stable income, Other Properties
+•	ST Liabilities: ST Borrowing, ST Lease liabilities, ST SH Loan, ST Financial Liabilities, ST Interest-bearing Debt, Other ST liabilities
+•	LT Liabilities: LT Borrowing, LT Lease liabilities, LT SH Loan, LT Financial Liabilities, LT Interest-bearing Debt, Other LT liabilities
+•	Equity: Minority Interest (NCI), Common Equity
+EXAMPLE:
+•	If the PDF says “Property, Plant, and Equipment – $50M”, map to:
+PP&amp;E &amp; Right of Use Assets | LT Operating Assets | PP&amp;E &amp; Right of Use Assets | \$50,000,000
+•	If the PDF says “Marketable Securities – $10M”, map to:
+Other Securities | ST Non-Operating Assets | Other Securities | \$10,000,000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>Not Held</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1961,14 +1986,6 @@
   </si>
   <si>
     <t>Historical Average or D&amp;A</t>
-  </si>
-  <si>
-    <t>Investment property income</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Financial assets income</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3325,20 +3342,20 @@
     <xf numFmtId="0" fontId="57" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3654,7 +3671,7 @@
         <v>354</v>
       </c>
       <c r="F1" s="293" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -3686,10 +3703,10 @@
         <v>353</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -3752,13 +3769,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="332" t="s">
+      <c r="B12" s="333" t="s">
         <v>290</v>
       </c>
-      <c r="C12" s="332"/>
-      <c r="D12" s="332"/>
-      <c r="E12" s="332"/>
-      <c r="F12" s="332"/>
+      <c r="C12" s="333"/>
+      <c r="D12" s="333"/>
+      <c r="E12" s="333"/>
+      <c r="F12" s="333"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3782,7 +3799,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -3805,7 +3822,7 @@
         <v>60</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -3860,22 +3877,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="332" t="s">
+      <c r="B25" s="333" t="s">
         <v>236</v>
       </c>
-      <c r="C25" s="332"/>
-      <c r="D25" s="332"/>
-      <c r="E25" s="332"/>
-      <c r="F25" s="332"/>
+      <c r="C25" s="333"/>
+      <c r="D25" s="333"/>
+      <c r="E25" s="333"/>
+      <c r="F25" s="333"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="336" t="s">
+      <c r="B26" s="334" t="s">
         <v>256</v>
       </c>
-      <c r="C26" s="336"/>
-      <c r="D26" s="336"/>
-      <c r="E26" s="336"/>
-      <c r="F26" s="336"/>
+      <c r="C26" s="334"/>
+      <c r="D26" s="334"/>
+      <c r="E26" s="334"/>
+      <c r="F26" s="334"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="241" t="s">
@@ -3887,13 +3904,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="334" t="s">
+      <c r="B29" s="332" t="s">
         <v>238</v>
       </c>
-      <c r="C29" s="334"/>
-      <c r="D29" s="334"/>
-      <c r="E29" s="334"/>
-      <c r="F29" s="334"/>
+      <c r="C29" s="332"/>
+      <c r="D29" s="332"/>
+      <c r="E29" s="332"/>
+      <c r="F29" s="332"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3913,13 +3930,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="334" t="s">
+      <c r="B32" s="332" t="s">
         <v>240</v>
       </c>
-      <c r="C32" s="334"/>
-      <c r="D32" s="334"/>
-      <c r="E32" s="334"/>
-      <c r="F32" s="334"/>
+      <c r="C32" s="332"/>
+      <c r="D32" s="332"/>
+      <c r="E32" s="332"/>
+      <c r="F32" s="332"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -3948,13 +3965,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="334" t="s">
+      <c r="B36" s="332" t="s">
         <v>243</v>
       </c>
-      <c r="C36" s="334"/>
-      <c r="D36" s="334"/>
-      <c r="E36" s="334"/>
-      <c r="F36" s="334"/>
+      <c r="C36" s="332"/>
+      <c r="D36" s="332"/>
+      <c r="E36" s="332"/>
+      <c r="F36" s="332"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -3970,13 +3987,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="334" t="s">
+      <c r="B39" s="332" t="s">
         <v>247</v>
       </c>
-      <c r="C39" s="334"/>
-      <c r="D39" s="334"/>
-      <c r="E39" s="334"/>
-      <c r="F39" s="334"/>
+      <c r="C39" s="332"/>
+      <c r="D39" s="332"/>
+      <c r="E39" s="332"/>
+      <c r="F39" s="332"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4010,13 +4027,13 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B45" s="334" t="s">
+      <c r="B45" s="332" t="s">
         <v>248</v>
       </c>
-      <c r="C45" s="334"/>
-      <c r="D45" s="334"/>
-      <c r="E45" s="334"/>
-      <c r="F45" s="334"/>
+      <c r="C45" s="332"/>
+      <c r="D45" s="332"/>
+      <c r="E45" s="332"/>
+      <c r="F45" s="332"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="47" t="s">
@@ -4032,13 +4049,13 @@
       </c>
     </row>
     <row r="48" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="334" t="s">
+      <c r="B48" s="332" t="s">
         <v>251</v>
       </c>
-      <c r="C48" s="335"/>
-      <c r="D48" s="335"/>
-      <c r="E48" s="335"/>
-      <c r="F48" s="335"/>
+      <c r="C48" s="336"/>
+      <c r="D48" s="336"/>
+      <c r="E48" s="336"/>
+      <c r="F48" s="336"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B49" s="47" t="s">
@@ -4067,13 +4084,13 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="332" t="s">
+      <c r="B52" s="333" t="s">
         <v>272</v>
       </c>
-      <c r="C52" s="332"/>
-      <c r="D52" s="332"/>
-      <c r="E52" s="332"/>
-      <c r="F52" s="332"/>
+      <c r="C52" s="333"/>
+      <c r="D52" s="333"/>
+      <c r="E52" s="333"/>
+      <c r="F52" s="333"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B53" s="47" t="s">
@@ -4134,22 +4151,22 @@
     </row>
     <row r="60" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="17"/>
-      <c r="B60" s="334" t="s">
+      <c r="B60" s="332" t="s">
         <v>307</v>
       </c>
-      <c r="C60" s="334"/>
-      <c r="D60" s="334"/>
-      <c r="E60" s="334"/>
-      <c r="F60" s="334"/>
+      <c r="C60" s="332"/>
+      <c r="D60" s="332"/>
+      <c r="E60" s="332"/>
+      <c r="F60" s="332"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B61" s="336" t="s">
+      <c r="B61" s="334" t="s">
         <v>263</v>
       </c>
-      <c r="C61" s="336"/>
-      <c r="D61" s="336"/>
-      <c r="E61" s="336"/>
-      <c r="F61" s="336"/>
+      <c r="C61" s="334"/>
+      <c r="D61" s="334"/>
+      <c r="E61" s="334"/>
+      <c r="F61" s="334"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B63" s="241" t="s">
@@ -4201,22 +4218,22 @@
       <c r="C68" s="125"/>
     </row>
     <row r="69" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="332" t="s">
+      <c r="B69" s="333" t="s">
         <v>315</v>
       </c>
-      <c r="C69" s="332"/>
-      <c r="D69" s="332"/>
-      <c r="E69" s="332"/>
-      <c r="F69" s="332"/>
+      <c r="C69" s="333"/>
+      <c r="D69" s="333"/>
+      <c r="E69" s="333"/>
+      <c r="F69" s="333"/>
     </row>
     <row r="70" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="332" t="s">
+      <c r="B70" s="333" t="s">
         <v>262</v>
       </c>
-      <c r="C70" s="332"/>
-      <c r="D70" s="332"/>
-      <c r="E70" s="332"/>
-      <c r="F70" s="332"/>
+      <c r="C70" s="333"/>
+      <c r="D70" s="333"/>
+      <c r="E70" s="333"/>
+      <c r="F70" s="333"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B71" s="47" t="s">
@@ -4253,13 +4270,13 @@
       <c r="A76" s="240"/>
     </row>
     <row r="77" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="332" t="s">
+      <c r="B77" s="333" t="s">
         <v>265</v>
       </c>
-      <c r="C77" s="332"/>
-      <c r="D77" s="332"/>
-      <c r="E77" s="332"/>
-      <c r="F77" s="332"/>
+      <c r="C77" s="333"/>
+      <c r="D77" s="333"/>
+      <c r="E77" s="333"/>
+      <c r="F77" s="333"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
@@ -4373,13 +4390,13 @@
       </c>
     </row>
     <row r="93" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="332" t="s">
+      <c r="B93" s="333" t="s">
         <v>271</v>
       </c>
-      <c r="C93" s="332"/>
-      <c r="D93" s="332"/>
-      <c r="E93" s="332"/>
-      <c r="F93" s="332"/>
+      <c r="C93" s="333"/>
+      <c r="D93" s="333"/>
+      <c r="E93" s="333"/>
+      <c r="F93" s="333"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="47" t="s">
@@ -4405,13 +4422,13 @@
       <c r="F97" s="36"/>
     </row>
     <row r="99" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="334" t="s">
+      <c r="B99" s="332" t="s">
         <v>371</v>
       </c>
-      <c r="C99" s="334"/>
-      <c r="D99" s="334"/>
-      <c r="E99" s="334"/>
-      <c r="F99" s="334"/>
+      <c r="C99" s="332"/>
+      <c r="D99" s="332"/>
+      <c r="E99" s="332"/>
+      <c r="F99" s="332"/>
     </row>
     <row r="101" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B101" s="267" t="s">
@@ -4573,13 +4590,13 @@
       <c r="F112" s="36"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B114" s="333" t="s">
+      <c r="B114" s="335" t="s">
         <v>279</v>
       </c>
-      <c r="C114" s="333"/>
-      <c r="D114" s="333"/>
-      <c r="E114" s="333"/>
-      <c r="F114" s="333"/>
+      <c r="C114" s="335"/>
+      <c r="D114" s="335"/>
+      <c r="E114" s="335"/>
+      <c r="F114" s="335"/>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B115" s="241" t="s">
@@ -4666,12 +4683,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B93:F93"/>
@@ -4685,6 +4696,12 @@
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -4922,7 +4939,7 @@
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B10" s="40" t="s">
-        <v>387</v>
+        <v>172</v>
       </c>
       <c r="C10" s="194"/>
       <c r="D10" s="185"/>
@@ -4938,7 +4955,7 @@
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="40" t="s">
-        <v>386</v>
+        <v>163</v>
       </c>
       <c r="C11" s="194"/>
       <c r="D11" s="185"/>
@@ -6145,7 +6162,7 @@
     </row>
     <row r="57" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B57" s="40" t="s">
-        <v>386</v>
+        <v>163</v>
       </c>
       <c r="C57" s="192">
         <f>IF(C$4="","",C11)</f>
@@ -6966,7 +6983,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:H89"/>
+  <dimension ref="B1:H93"/>
   <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
@@ -8219,7 +8236,38 @@
         <v>HKD</v>
       </c>
     </row>
+    <row r="91" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B91" s="81" t="s">
+        <v>373</v>
+      </c>
+      <c r="C91" s="37"/>
+      <c r="D91" s="37"/>
+      <c r="E91" s="37"/>
+      <c r="F91" s="37"/>
+      <c r="G91" s="37"/>
+      <c r="H91" s="37"/>
+    </row>
+    <row r="92" spans="2:8" ht="212" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B92" s="332" t="s">
+        <v>374</v>
+      </c>
+      <c r="C92" s="332"/>
+      <c r="D92" s="332"/>
+      <c r="E92" s="332"/>
+      <c r="F92" s="332"/>
+      <c r="G92" s="332"/>
+      <c r="H92" s="332"/>
+    </row>
+    <row r="93" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B93" s="1" t="str">
+        <f>"Please find the financial statement text below. The output should use a scaling factor of "&amp;H1</f>
+        <v>Please find the financial statement text below. The output should use a scaling factor of 1000</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B92:H92"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="71" orientation="portrait" r:id="rId1"/>
@@ -9075,7 +9123,7 @@
       </c>
       <c r="D17" s="59"/>
       <c r="E17" s="311" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="202"/>
@@ -9101,7 +9149,7 @@
       </c>
       <c r="D18" s="59"/>
       <c r="E18" s="311" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="203"/>
@@ -9429,7 +9477,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="310" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -9489,7 +9537,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="310" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -9613,7 +9661,7 @@
         <v>-175999.5</v>
       </c>
       <c r="E33" s="310" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G33" s="198">
         <f>Data!C41</f>
@@ -9671,7 +9719,7 @@
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="310" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="187">
@@ -9979,7 +10027,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="309" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10249,7 +10297,7 @@
         <v>2.7696969151119136E-2</v>
       </c>
       <c r="E52" s="309" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="G52" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G48/BS!$C$66)</f>
@@ -10276,7 +10324,7 @@
         <v>2.9500867672578604E-2</v>
       </c>
       <c r="E53" s="309" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G53" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -10591,7 +10639,7 @@
         <v>0</v>
       </c>
       <c r="E61" s="310" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="G61" s="198">
         <f>Data!C58</f>
@@ -11152,7 +11200,7 @@
       </c>
       <c r="D77" s="27"/>
       <c r="E77" s="310" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F77" s="27"/>
       <c r="G77" s="6">

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE8C373-63D7-4E62-94C2-0E3AC03A3F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3732E4CF-5891-4967-9E85-69DD49D34F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3714,7 +3714,7 @@
         <v>99</v>
       </c>
       <c r="C6" s="50">
-        <v>2.2799999999999998</v>
+        <v>2.23</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>43</v>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>3040.0003799999995</v>
+        <v>2973.333705</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -3809,7 +3809,7 @@
         <v>2</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0726602000000001</v>
+        <v>1.07197944</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="C20" s="259">
         <f>C123</f>
-        <v>1.7611544086745501</v>
+        <v>1.7601941816673556</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>344</v>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="C21" s="288">
         <f ca="1">Scenarios!C87</f>
-        <v>9.6153062008305534E-2</v>
+        <v>0.10446582016168726</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C120</f>
-        <v>3.4037135153498488E-2</v>
+        <v>3.4778213731821772E-2</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="C56" s="94">
         <f>Normalized_FCF!C92</f>
-        <v>5.1666666666666673E-2</v>
+        <v>5.282511210762332E-2</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="C73" s="255">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.77604668149976541</v>
+        <v>0.77555416621962558</v>
       </c>
       <c r="D73" s="1" t="str">
         <f>Market_currency</f>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="C82" s="255">
         <f>C81*C28*Exchange_Rate/Common_Shares</f>
-        <v>2.7352027185846606E-2</v>
+        <v>2.7334668318586459E-2</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="C87" s="255">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.6326463638092357</v>
+        <v>1.6316102105720531</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="C91" s="255">
         <f>C90*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.18314876857092394</v>
+        <v>0.18303253385307727</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Market_currency</f>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="C95" s="255">
         <f>Valuation_Model!C12</f>
-        <v>2.5644897866940783</v>
+        <v>2.5628622423261698</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="E102" s="265" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>3.16 HKD</v>
+        <v>3.15 HKD</v>
       </c>
       <c r="F102" s="266">
         <f>Valuation_Model!F74</f>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="C108" s="248">
         <f>Scenarios!C60</f>
-        <v>2.6144828181896225</v>
+        <v>2.6128235459211906</v>
       </c>
       <c r="D108" s="243" t="str">
         <f>Market_currency</f>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="C122" s="247">
         <f>Scenarios!C82</f>
-        <v>1.5130108901560315</v>
+        <v>1.5120506631488371</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.35">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="C123" s="246">
         <f>Scenarios!C83</f>
-        <v>1.7611544086745501</v>
+        <v>1.7601941816673556</v>
       </c>
       <c r="D123" s="47" t="str">
         <f>Reporting_currency</f>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C124" s="158">
         <f>Scenarios!F83</f>
-        <v>-0.32638516634274639</v>
+        <v>-0.32632489307777868</v>
       </c>
     </row>
   </sheetData>
@@ -7767,11 +7767,11 @@
       </c>
       <c r="C47" s="151">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>2.4322314919563635</v>
+        <v>2.4306878848471745</v>
       </c>
       <c r="D47" s="151">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.7960083277359495</v>
+        <v>1.7948684974064664</v>
       </c>
       <c r="F47" s="291"/>
     </row>
@@ -8174,11 +8174,11 @@
       </c>
       <c r="C86" s="192">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-36469.374139800006</v>
+        <v>-36446.228980560001</v>
       </c>
       <c r="D86" s="255">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-2.7352027185846606E-2</v>
+        <v>-2.7334668318586462E-2</v>
       </c>
       <c r="E86" s="277" t="str">
         <f>Market_currency</f>
@@ -8191,11 +8191,11 @@
       </c>
       <c r="C87" s="192">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>2176862.0905200415</v>
+        <v>2175480.5526977726</v>
       </c>
       <c r="D87" s="255">
         <f>C87*$H$1/Common_Shares</f>
-        <v>1.6326463638092357</v>
+        <v>1.6316102105720531</v>
       </c>
       <c r="E87" s="277" t="str">
         <f>Market_currency</f>
@@ -8208,11 +8208,11 @@
       </c>
       <c r="C88" s="192">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>244198.38861935999</v>
+        <v>244043.40897619197</v>
       </c>
       <c r="D88" s="255">
         <f>C88*$H$1/Common_Shares</f>
-        <v>0.18314876857092394</v>
+        <v>0.18303253385307724</v>
       </c>
       <c r="E88" s="277" t="str">
         <f>Market_currency</f>
@@ -8225,11 +8225,11 @@
       </c>
       <c r="C89" s="191">
         <f>SUM(C86:C88)</f>
-        <v>2384591.1049996014</v>
+        <v>2383077.7326934049</v>
       </c>
       <c r="D89" s="279">
         <f>SUM(D86:D88)</f>
-        <v>1.788443105194313</v>
+        <v>1.7873080761065439</v>
       </c>
       <c r="E89" s="277" t="str">
         <f>Market_currency</f>
@@ -11883,12 +11883,12 @@
       </c>
       <c r="C92" s="23">
         <f>C89/Market_Price</f>
-        <v>5.1666666666666673E-2</v>
+        <v>5.282511210762332E-2</v>
       </c>
       <c r="E92" s="312"/>
       <c r="G92" s="23">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G89/Market_Price)</f>
-        <v>5.1666666666666673E-2</v>
+        <v>5.282511210762332E-2</v>
       </c>
       <c r="H92" s="23">
         <f t="shared" si="38"/>
@@ -12910,30 +12910,30 @@
       </c>
       <c r="C119" s="182">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>7.7604668149976533E-2</v>
+        <v>7.7555416621962553E-2</v>
       </c>
       <c r="D119" s="27"/>
       <c r="E119" s="309"/>
       <c r="F119" s="27"/>
       <c r="G119" s="182">
         <f t="shared" ref="G119:Q119" si="48">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.12225911266311093</v>
+        <v>0.12218152134990984</v>
       </c>
       <c r="H119" s="182">
         <f t="shared" si="48"/>
-        <v>3.6623028135571487E-2</v>
+        <v>3.6599785460366824E-2</v>
       </c>
       <c r="I119" s="182">
         <f t="shared" si="48"/>
-        <v>6.484553344582103E-2</v>
+        <v>6.4804379457495009E-2</v>
       </c>
       <c r="J119" s="182">
         <f t="shared" si="48"/>
-        <v>0.22808492321212165</v>
+        <v>0.22794016992275201</v>
       </c>
       <c r="K119" s="182">
         <f t="shared" si="48"/>
-        <v>0.16324652644188423</v>
+        <v>0.16314292261157468</v>
       </c>
       <c r="L119" s="182" t="str">
         <f t="shared" si="48"/>
@@ -12967,30 +12967,30 @@
       </c>
       <c r="C120" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.4037135153498488E-2</v>
+        <v>3.4778213731821772E-2</v>
       </c>
       <c r="D120" s="27"/>
       <c r="E120" s="309"/>
       <c r="F120" s="27"/>
       <c r="G120" s="79">
         <f t="shared" ref="G120" si="49">IF(G$4="","",G119/Market_Price)</f>
-        <v>5.3622417834697782E-2</v>
+        <v>5.4789919887851944E-2</v>
       </c>
       <c r="H120" s="79">
         <f t="shared" ref="H120" si="50">IF(H$4="","",H119/Market_Price)</f>
-        <v>1.6062731638408548E-2</v>
+        <v>1.6412459847698128E-2</v>
       </c>
       <c r="I120" s="79">
         <f t="shared" ref="I120" si="51">IF(I$4="","",I119/Market_Price)</f>
-        <v>2.8441023441149578E-2</v>
+        <v>2.9060259846410318E-2</v>
       </c>
       <c r="J120" s="79">
         <f t="shared" ref="J120" si="52">IF(J$4="","",J119/Market_Price)</f>
-        <v>0.10003724702286038</v>
+        <v>0.1022153228353148</v>
       </c>
       <c r="K120" s="79">
         <f t="shared" ref="K120" si="53">IF(K$4="","",K119/Market_Price)</f>
-        <v>7.1599353702580804E-2</v>
+        <v>7.3158261260795818E-2</v>
       </c>
       <c r="L120" s="79" t="str">
         <f t="shared" ref="L120" si="54">IF(L$4="","",L119/Market_Price)</f>
@@ -13873,7 +13873,7 @@
       </c>
       <c r="C11" s="238">
         <f>Exchange_Rate</f>
-        <v>1.0726602000000001</v>
+        <v>1.07197944</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -13887,7 +13887,7 @@
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>2.5644897866940783</v>
+        <v>2.5628622423261698</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>2.613092066502583</v>
+        <v>2.6114336768697872</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14876,23 +14876,23 @@
       </c>
       <c r="B65" s="128">
         <f>C12</f>
-        <v>2.5644897866940783</v>
+        <v>2.5628622423261698</v>
       </c>
       <c r="C65" s="128">
         <f>C12</f>
-        <v>2.5644897866940783</v>
+        <v>2.5628622423261698</v>
       </c>
       <c r="D65" s="128">
         <f>C12</f>
-        <v>2.5644897866940783</v>
+        <v>2.5628622423261698</v>
       </c>
       <c r="E65" s="145">
         <f>C12</f>
-        <v>2.5644897866940783</v>
+        <v>2.5628622423261698</v>
       </c>
       <c r="F65" s="128">
         <f>C12</f>
-        <v>2.5644897866940783</v>
+        <v>2.5628622423261698</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -14903,23 +14903,23 @@
       </c>
       <c r="B66" s="128">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.443300525873672</v>
+        <v>2.4417498938412781</v>
       </c>
       <c r="C66" s="128">
         <f t="shared" si="4"/>
-        <v>2.489558023481464</v>
+        <v>2.4879780342919093</v>
       </c>
       <c r="D66" s="128">
         <f t="shared" si="4"/>
-        <v>2.5910825203848922</v>
+        <v>2.5894380990326531</v>
       </c>
       <c r="E66" s="128">
         <f t="shared" si="4"/>
-        <v>2.6469095858885598</v>
+        <v>2.6452297340867594</v>
       </c>
       <c r="F66" s="128">
         <f t="shared" si="4"/>
-        <v>2.7065167713999467</v>
+        <v>2.7047990901087995</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -14930,23 +14930,23 @@
       </c>
       <c r="B67" s="128">
         <f t="shared" si="4"/>
-        <v>2.3599977422752119</v>
+        <v>2.358499978059637</v>
       </c>
       <c r="C67" s="128">
         <f t="shared" si="4"/>
-        <v>2.4309405103684378</v>
+        <v>2.4293977225761449</v>
       </c>
       <c r="D67" s="128">
         <f t="shared" si="4"/>
-        <v>2.6180648516165936</v>
+        <v>2.6164033060233232</v>
       </c>
       <c r="E67" s="128">
         <f t="shared" si="4"/>
-        <v>2.7421929994503293</v>
+        <v>2.7404526763673007</v>
       </c>
       <c r="F67" s="128">
         <f t="shared" si="4"/>
-        <v>2.8936093360639989</v>
+        <v>2.8917729171387707</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -14957,23 +14957,23 @@
       </c>
       <c r="B68" s="128">
         <f t="shared" si="4"/>
-        <v>2.2876529273582111</v>
+        <v>2.2862010765234091</v>
       </c>
       <c r="C68" s="128">
         <f t="shared" si="4"/>
-        <v>2.3758588899572044</v>
+        <v>2.3743510595203827</v>
       </c>
       <c r="D68" s="128">
         <f t="shared" si="4"/>
-        <v>2.6486034775099276</v>
+        <v>2.6469225506858041</v>
       </c>
       <c r="E68" s="128">
         <f t="shared" si="4"/>
-        <v>2.8620304166950867</v>
+        <v>2.8602140392192847</v>
       </c>
       <c r="F68" s="128">
         <f t="shared" si="4"/>
-        <v>3.1568704734833655</v>
+        <v>3.1548669768089028</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -14984,23 +14984,23 @@
       </c>
       <c r="B69" s="128">
         <f t="shared" si="4"/>
-        <v>2.2351720860924194</v>
+        <v>2.2337535420378081</v>
       </c>
       <c r="C69" s="128">
         <f t="shared" si="4"/>
-        <v>2.3331429562167783</v>
+        <v>2.3316622352961418</v>
       </c>
       <c r="D69" s="128">
         <f t="shared" si="4"/>
-        <v>2.6770156400059997</v>
+        <v>2.6753166815034928</v>
       </c>
       <c r="E69" s="128">
         <f t="shared" si="4"/>
-        <v>2.9868559694040608</v>
+        <v>2.9849603718329645</v>
       </c>
       <c r="F69" s="128">
         <f t="shared" si="4"/>
-        <v>3.467426301873489</v>
+        <v>3.4652257120415331</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -15011,23 +15011,23 @@
       </c>
       <c r="B70" s="128">
         <f t="shared" si="4"/>
-        <v>2.1998136073029557</v>
+        <v>2.1984175033817812</v>
       </c>
       <c r="C70" s="128">
         <f t="shared" si="4"/>
-        <v>2.3027396559750533</v>
+        <v>2.3012782304013237</v>
       </c>
       <c r="D70" s="128">
         <f t="shared" si="4"/>
-        <v>2.7011358334595239</v>
+        <v>2.6994215671615982</v>
       </c>
       <c r="E70" s="128">
         <f t="shared" si="4"/>
-        <v>3.1062550789297436</v>
+        <v>3.1042837051363166</v>
       </c>
       <c r="F70" s="128">
         <f t="shared" si="4"/>
-        <v>3.8073484123548478</v>
+        <v>3.8049320921583911</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15037,23 +15037,23 @@
       </c>
       <c r="B71" s="128">
         <f t="shared" si="4"/>
-        <v>2.1768424241029609</v>
+        <v>2.175460898761914</v>
       </c>
       <c r="C71" s="128">
         <f t="shared" si="4"/>
-        <v>2.2820934653926552</v>
+        <v>2.2806451428507164</v>
       </c>
       <c r="D71" s="128">
         <f t="shared" si="4"/>
-        <v>2.7205538776547504</v>
+        <v>2.7188272877637929</v>
       </c>
       <c r="E71" s="128">
         <f t="shared" si="4"/>
-        <v>3.2152021865456928</v>
+        <v>3.2131616698559591</v>
       </c>
       <c r="F71" s="128">
         <f t="shared" si="4"/>
-        <v>4.165504673565624</v>
+        <v>4.162861050765434</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15088,7 +15088,7 @@
       </c>
       <c r="E74" s="139">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>3.1568704734833655</v>
+        <v>3.1548669768089028</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="E75" s="139">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>2.7421929994503293</v>
+        <v>2.7404526763673007</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -15133,7 +15133,7 @@
       </c>
       <c r="E76" s="139">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>2.6180648516165936</v>
+        <v>2.6164033060233232</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15156,7 +15156,7 @@
       </c>
       <c r="E77" s="139">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>2.4309405103684378</v>
+        <v>2.4293977225761449</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -15179,7 +15179,7 @@
       </c>
       <c r="E78" s="139">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.2876529273582111</v>
+        <v>2.2862010765234091</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="I3" s="272">
         <f>-Market_Price</f>
-        <v>-2.2799999999999998</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -15329,7 +15329,7 @@
       </c>
       <c r="I6" s="272">
         <f t="shared" si="0"/>
-        <v>2.7322828181896224</v>
+        <v>2.7306235459211905</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15520,7 +15520,7 @@
       </c>
       <c r="C21" s="165">
         <f>Market_Price</f>
-        <v>2.2799999999999998</v>
+        <v>2.23</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -15535,7 +15535,7 @@
       </c>
       <c r="C22" s="165">
         <f>Valuation_Model!C12</f>
-        <v>2.5644897866940783</v>
+        <v>2.5628622423261698</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -15582,7 +15582,7 @@
       </c>
       <c r="C27" s="165">
         <f>Valuation_Model!E76</f>
-        <v>2.6180648516165936</v>
+        <v>2.6164033060233232</v>
       </c>
       <c r="D27" s="165" t="str">
         <f>Market_currency</f>
@@ -15640,7 +15640,7 @@
       </c>
       <c r="C33" s="165">
         <f>Valuation_Model!E77</f>
-        <v>2.4309405103684378</v>
+        <v>2.4293977225761449</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -15698,7 +15698,7 @@
       </c>
       <c r="C39" s="165">
         <f>Valuation_Model!E75</f>
-        <v>2.7421929994503293</v>
+        <v>2.7404526763673007</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C42" s="159">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>2.621028237387804</v>
+        <v>2.619364811092241</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -15799,7 +15799,7 @@
       </c>
       <c r="C51" s="165">
         <f>Valuation_Model!E78</f>
-        <v>2.2876529273582111</v>
+        <v>2.2862010765234091</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -15857,7 +15857,7 @@
       </c>
       <c r="C57" s="165">
         <f>Valuation_Model!E74</f>
-        <v>3.1568704734833655</v>
+        <v>3.1548669768089028</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -15883,7 +15883,7 @@
       </c>
       <c r="C60" s="159">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>2.6144828181896225</v>
+        <v>2.6128235459211906</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -15944,7 +15944,7 @@
       </c>
       <c r="C66" s="165">
         <f>Valuation_Model!C18</f>
-        <v>2.613092066502583</v>
+        <v>2.6114336768697872</v>
       </c>
       <c r="D66" s="165" t="str">
         <f>Market_currency</f>
@@ -16076,7 +16076,7 @@
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
-        <v>1.5130108901560315</v>
+        <v>1.5120506631488371</v>
       </c>
       <c r="D82" s="120"/>
     </row>
@@ -16086,7 +16086,7 @@
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
-        <v>1.7611544086745501</v>
+        <v>1.7601941816673556</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16097,7 +16097,7 @@
       </c>
       <c r="F83" s="270">
         <f>(C83/C60-1)</f>
-        <v>-0.32638516634274639</v>
+        <v>-0.32632489307777868</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="C86" s="274">
         <f>Market_Price</f>
-        <v>2.2799999999999998</v>
+        <v>2.23</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16127,7 +16127,7 @@
       </c>
       <c r="C87" s="273">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.6153062008305534E-2</v>
+        <v>0.10446582016168726</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5D8292-43A9-4E59-8585-02D4475D4B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C39B32-2D22-4A22-B313-62A2B45E9CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="392">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1978,6 +1978,14 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Operating Interest Income</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Non-FCF Value is of the Expected Value, at</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>Not Held</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2026,7 +2034,7 @@
     <numFmt numFmtId="192" formatCode="0.0\x"/>
     <numFmt numFmtId="193" formatCode="0\x"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="58" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2459,13 +2467,6 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color theme="0" tint="-4.9989318521683403E-2"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -3369,15 +3370,17 @@
     <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="193" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3707,7 +3710,7 @@
         <v>348</v>
       </c>
       <c r="F1" s="293" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -3739,10 +3742,10 @@
         <v>347</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -3750,7 +3753,7 @@
         <v>99</v>
       </c>
       <c r="C6" s="50">
-        <v>2.23</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>43</v>
@@ -3795,7 +3798,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>2973.333705</v>
+        <v>2906.6670300000001</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -3835,7 +3838,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -3845,7 +3848,7 @@
         <v>2</v>
       </c>
       <c r="C17" s="50">
-        <v>1.07197944</v>
+        <v>1.0705486499999999</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -3858,7 +3861,7 @@
         <v>60</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -3878,7 +3881,7 @@
       </c>
       <c r="C20" s="259">
         <f>C127</f>
-        <v>1.5748978886562173</v>
+        <v>1.5731270460314282</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>338</v>
@@ -3893,7 +3896,7 @@
       </c>
       <c r="C21" s="288">
         <f ca="1">Scenarios!C87</f>
-        <v>6.1633064159671846E-2</v>
+        <v>6.9675781490122768E-2</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4160,7 +4163,7 @@
       </c>
       <c r="C56" s="192">
         <f>Normalized_FCF!G19</f>
-        <v>79168</v>
+        <v>99280.955148098932</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4186,7 +4189,7 @@
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C121</f>
-        <v>2.0531182016336334E-2</v>
+        <v>2.0974048836286365E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4195,7 +4198,7 @@
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
-        <v>5.282511210762332E-2</v>
+        <v>5.4036697247706419E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4311,7 +4314,7 @@
       </c>
       <c r="C76" s="255">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.57230669870537532</v>
+        <v>0.5715428307888033</v>
       </c>
       <c r="D76" s="1" t="str">
         <f>Market_currency</f>
@@ -4378,7 +4381,7 @@
       </c>
       <c r="C86" s="255">
         <f>C85*C28*Exchange_Rate/Common_Shares</f>
-        <v>2.7334668318586459E-2</v>
+        <v>2.7298184251239466E-2</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -4422,7 +4425,7 @@
       </c>
       <c r="C91" s="255">
         <f>C90*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.5294516186800311</v>
+        <v>1.5274102324371277</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Market_currency</f>
@@ -4453,7 +4456,7 @@
       </c>
       <c r="C95" s="255">
         <f>C94*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.18303253385307727</v>
+        <v>0.18278823707896036</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4475,7 +4478,7 @@
       </c>
       <c r="C99" s="255">
         <f>Valuation_Model!C12</f>
-        <v>2.2574561829198969</v>
+        <v>2.2544431160536518</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4533,7 +4536,7 @@
       </c>
       <c r="E106" s="265" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>2.57 HKD</v>
+        <v>2.56 HKD</v>
       </c>
       <c r="F106" s="266">
         <f>Valuation_Model!F74</f>
@@ -4599,7 +4602,7 @@
       </c>
       <c r="E109" s="252" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>2.17 HKD</v>
+        <v>2.16 HKD</v>
       </c>
       <c r="F109" s="253">
         <f>Valuation_Model!F77</f>
@@ -4634,7 +4637,7 @@
       </c>
       <c r="C112" s="248">
         <f>Scenarios!C60</f>
-        <v>2.2926315515979434</v>
+        <v>2.2895715355423079</v>
       </c>
       <c r="D112" s="243" t="str">
         <f>Market_currency</f>
@@ -4727,7 +4730,7 @@
       </c>
       <c r="C126" s="247">
         <f>Scenarios!C82</f>
-        <v>1.3267543701376987</v>
+        <v>1.3249835275129096</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
@@ -4736,7 +4739,7 @@
       </c>
       <c r="C127" s="246">
         <f>Scenarios!C83</f>
-        <v>1.5748978886562173</v>
+        <v>1.5731270460314282</v>
       </c>
       <c r="D127" s="47" t="str">
         <f>Reporting_currency</f>
@@ -4749,7 +4752,7 @@
       </c>
       <c r="C128" s="158">
         <f>Scenarios!F83</f>
-        <v>-0.31306105965499442</v>
+        <v>-0.31291640308638913</v>
       </c>
     </row>
   </sheetData>
@@ -7840,11 +7843,11 @@
       </c>
       <c r="C47" s="151">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>2.4306878848471745</v>
+        <v>2.4274436025512744</v>
       </c>
       <c r="D47" s="151">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.7948684974064664</v>
+        <v>1.7924728545409609</v>
       </c>
       <c r="F47" s="291"/>
     </row>
@@ -8143,7 +8146,7 @@
         <v>357</v>
       </c>
       <c r="C76" s="300"/>
-      <c r="D76" s="339">
+      <c r="D76" s="337">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,IF(D74&gt;36,12,6),2))</f>
         <v>6</v>
       </c>
@@ -8247,11 +8250,11 @@
       </c>
       <c r="C86" s="192">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-36446.228980560001</v>
+        <v>-36397.583551349999</v>
       </c>
       <c r="D86" s="255">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-2.7334668318586462E-2</v>
+        <v>-2.7298184251239466E-2</v>
       </c>
       <c r="E86" s="277" t="str">
         <f>Market_currency</f>
@@ -8264,11 +8267,11 @@
       </c>
       <c r="C87" s="192">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>2039269.0798153114</v>
+        <v>2036547.231151209</v>
       </c>
       <c r="D87" s="255">
         <f>C87*$H$1/Common_Shares</f>
-        <v>1.5294516186800313</v>
+        <v>1.5274102324371277</v>
       </c>
       <c r="E87" s="277" t="str">
         <f>Market_currency</f>
@@ -8281,11 +8284,11 @@
       </c>
       <c r="C88" s="192">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>244043.40897619197</v>
+        <v>243717.67990331995</v>
       </c>
       <c r="D88" s="255">
         <f>C88*$H$1/Common_Shares</f>
-        <v>0.18303253385307724</v>
+        <v>0.18278823707896033</v>
       </c>
       <c r="E88" s="277" t="str">
         <f>Market_currency</f>
@@ -8298,11 +8301,11 @@
       </c>
       <c r="C89" s="191">
         <f>SUM(C86:C88)</f>
-        <v>2246866.2598109432</v>
+        <v>2243867.3275031787</v>
       </c>
       <c r="D89" s="279">
         <f>SUM(D86:D88)</f>
-        <v>1.685149484214522</v>
+        <v>1.6829002852648487</v>
       </c>
       <c r="E89" s="277" t="str">
         <f>Market_currency</f>
@@ -8886,48 +8889,48 @@
       </c>
       <c r="E12" s="311"/>
       <c r="G12" s="198">
-        <f t="shared" ref="G12:Q12" si="6">G50</f>
-        <v>0</v>
+        <f>G50</f>
+        <v>20112.955148098936</v>
       </c>
       <c r="H12" s="198">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" ref="H12:Q12" si="6">H50</f>
+        <v>12111.846771442135</v>
       </c>
       <c r="I12" s="198">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-1613</v>
       </c>
       <c r="J12" s="198">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-2645</v>
       </c>
       <c r="K12" s="198">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="198">
+        <v>-299</v>
+      </c>
+      <c r="L12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="198">
+        <v/>
+      </c>
+      <c r="M12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="N12" s="198">
+        <v/>
+      </c>
+      <c r="N12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O12" s="198">
+        <v/>
+      </c>
+      <c r="O12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P12" s="198">
+        <v/>
+      </c>
+      <c r="P12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="198">
+        <v/>
+      </c>
+      <c r="Q12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -8942,23 +8945,23 @@
       <c r="E13" s="311"/>
       <c r="G13" s="188">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>125816</v>
+        <v>145928.95514809893</v>
       </c>
       <c r="H13" s="188">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>22698</v>
+        <v>34809.846771442135</v>
       </c>
       <c r="I13" s="188">
         <f t="shared" si="7"/>
-        <v>82217.017999999996</v>
+        <v>80604.017999999996</v>
       </c>
       <c r="J13" s="188">
         <f t="shared" si="7"/>
-        <v>286158.147</v>
+        <v>283513.147</v>
       </c>
       <c r="K13" s="188">
         <f t="shared" si="7"/>
-        <v>203217</v>
+        <v>202918</v>
       </c>
       <c r="L13" s="188" t="str">
         <f t="shared" si="7"/>
@@ -9111,23 +9114,23 @@
       <c r="F16" s="62"/>
       <c r="G16" s="188">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>79168</v>
+        <v>99280.955148098932</v>
       </c>
       <c r="H16" s="188">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>1036</v>
+        <v>13147.846771442135</v>
       </c>
       <c r="I16" s="188">
         <f t="shared" si="8"/>
-        <v>82217.017999999996</v>
+        <v>80604.017999999996</v>
       </c>
       <c r="J16" s="188">
         <f t="shared" si="8"/>
-        <v>286158.147</v>
+        <v>283513.147</v>
       </c>
       <c r="K16" s="188">
         <f t="shared" si="8"/>
-        <v>203217</v>
+        <v>202918</v>
       </c>
       <c r="L16" s="188" t="str">
         <f t="shared" si="8"/>
@@ -9219,23 +9222,23 @@
       <c r="F19" s="27"/>
       <c r="G19" s="190">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>79168</v>
+        <v>99280.955148098932</v>
       </c>
       <c r="H19" s="190">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>1036</v>
+        <v>13147.846771442135</v>
       </c>
       <c r="I19" s="190">
         <f t="shared" si="9"/>
-        <v>82217.017999999996</v>
+        <v>80604.017999999996</v>
       </c>
       <c r="J19" s="190">
         <f t="shared" si="9"/>
-        <v>286158.147</v>
+        <v>283513.147</v>
       </c>
       <c r="K19" s="190">
         <f t="shared" si="9"/>
-        <v>203217</v>
+        <v>202918</v>
       </c>
       <c r="L19" s="190" t="str">
         <f t="shared" si="9"/>
@@ -10073,11 +10076,11 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.42270384388610988</v>
+        <v>0.35483420146557754</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>9.5880474452554747</v>
+        <v>1.4693250239481581</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
@@ -10207,78 +10210,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>71</v>
+        <v>384</v>
       </c>
       <c r="C48" s="198">
         <f>BS!D75*C53</f>
         <v>21115.955148098936</v>
       </c>
       <c r="E48" s="311"/>
-      <c r="G48" s="333"/>
-      <c r="H48" s="333"/>
-      <c r="I48" s="333"/>
-      <c r="J48" s="333"/>
-      <c r="K48" s="333"/>
-      <c r="L48" s="333"/>
-      <c r="M48" s="333"/>
-      <c r="N48" s="333"/>
-      <c r="O48" s="333"/>
-      <c r="P48" s="333"/>
-      <c r="Q48" s="333"/>
+      <c r="G48" s="338">
+        <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
+        <v>21115.955148098936</v>
+      </c>
+      <c r="H48" s="338">
+        <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
+        <v>12974.846771442135</v>
+      </c>
+      <c r="I48" s="338">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="338">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="K48" s="338">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="L48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="M48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="N48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="O48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="P48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="Q48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
-      <c r="B49" s="334" t="s">
+      <c r="B49" s="333" t="s">
         <v>379</v>
       </c>
-      <c r="C49" s="335">
+      <c r="C49" s="334">
         <f>BS!$C$66*C53</f>
         <v>73805</v>
       </c>
-      <c r="D49" s="336"/>
-      <c r="E49" s="337"/>
-      <c r="F49" s="336"/>
-      <c r="G49" s="335">
+      <c r="D49" s="335"/>
+      <c r="E49" s="336"/>
+      <c r="F49" s="335"/>
+      <c r="G49" s="334">
         <f>Data!C52</f>
         <v>73805</v>
       </c>
-      <c r="H49" s="335">
+      <c r="H49" s="334">
         <f>Data!D52</f>
         <v>45350</v>
       </c>
-      <c r="I49" s="335">
+      <c r="I49" s="334">
         <f>Data!E52</f>
         <v>0</v>
       </c>
-      <c r="J49" s="335">
+      <c r="J49" s="334">
         <f>Data!F52</f>
         <v>0</v>
       </c>
-      <c r="K49" s="335">
+      <c r="K49" s="334">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="335" t="str">
+      <c r="L49" s="334" t="str">
         <f>Data!H52</f>
         <v/>
       </c>
-      <c r="M49" s="335" t="str">
+      <c r="M49" s="334" t="str">
         <f>Data!I52</f>
         <v/>
       </c>
-      <c r="N49" s="335" t="str">
+      <c r="N49" s="334" t="str">
         <f>Data!J52</f>
         <v/>
       </c>
-      <c r="O49" s="335" t="str">
+      <c r="O49" s="334" t="str">
         <f>Data!K52</f>
         <v/>
       </c>
-      <c r="P49" s="335" t="str">
+      <c r="P49" s="334" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="335" t="str">
+      <c r="Q49" s="334" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -10293,17 +10329,50 @@
         <v>20112.955148098936</v>
       </c>
       <c r="E50" s="311"/>
-      <c r="G50" s="338"/>
-      <c r="H50" s="338"/>
-      <c r="I50" s="338"/>
-      <c r="J50" s="338"/>
-      <c r="K50" s="338"/>
-      <c r="L50" s="338"/>
-      <c r="M50" s="338"/>
-      <c r="N50" s="338"/>
-      <c r="O50" s="338"/>
-      <c r="P50" s="338"/>
-      <c r="Q50" s="338"/>
+      <c r="G50" s="188">
+        <f>IF(G$4="","",(G47+G48))</f>
+        <v>20112.955148098936</v>
+      </c>
+      <c r="H50" s="188">
+        <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
+        <v>12111.846771442135</v>
+      </c>
+      <c r="I50" s="188">
+        <f t="shared" si="20"/>
+        <v>-1613</v>
+      </c>
+      <c r="J50" s="188">
+        <f t="shared" si="20"/>
+        <v>-2645</v>
+      </c>
+      <c r="K50" s="188">
+        <f t="shared" si="20"/>
+        <v>-299</v>
+      </c>
+      <c r="L50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="M50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="N50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="O50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="P50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="Q50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="10"/>
@@ -10384,47 +10453,47 @@
       </c>
       <c r="E55" s="311"/>
       <c r="G55" s="42">
-        <f t="shared" ref="G55:Q55" si="19">IF(G4="","",-G8/G47)</f>
+        <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>104.839481555334</v>
       </c>
       <c r="H55" s="42">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>2.5399768250289689</v>
       </c>
       <c r="I55" s="42">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>50.859268443893363</v>
       </c>
       <c r="J55" s="42">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>108.1179584120983</v>
       </c>
       <c r="K55" s="42">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>679.65551839464888</v>
       </c>
       <c r="L55" s="42" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="M55" s="42" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="N55" s="42" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="O55" s="42" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P55" s="42" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Q55" s="42" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -10618,47 +10687,47 @@
       </c>
       <c r="E61" s="311"/>
       <c r="G61" s="188">
-        <f t="shared" ref="G61:Q61" si="20">IF(G4="","",SUM(G58:G60))</f>
+        <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
       </c>
       <c r="H61" s="188">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I61" s="188">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="J61" s="188">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K61" s="188">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="L61" s="188" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="M61" s="188" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="N61" s="188" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="O61" s="188" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="P61" s="188" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="Q61" s="188" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -10729,47 +10798,47 @@
       </c>
       <c r="E63" s="311"/>
       <c r="G63" s="188">
-        <f t="shared" ref="G63:Q63" si="21">IF(G4="","",G61+G62)</f>
+        <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>39310</v>
       </c>
       <c r="H63" s="188">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>39794</v>
       </c>
       <c r="I63" s="188">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-74687.603451000003</v>
       </c>
       <c r="J63" s="188">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-273680.96301000001</v>
       </c>
       <c r="K63" s="188">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-202918</v>
       </c>
       <c r="L63" s="188" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M63" s="188" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="N63" s="188" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="O63" s="188" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="P63" s="188" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="Q63" s="188" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
@@ -10949,47 +11018,47 @@
       <c r="E73" s="308"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
-        <f t="shared" ref="G73:Q73" si="22">IF(G$4="","",ABS(G5/G$4))</f>
+        <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
         <v>0.81850227626525374</v>
       </c>
       <c r="H73" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0.88516823144421752</v>
       </c>
       <c r="I73" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0.55491457230760188</v>
       </c>
       <c r="J73" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0.56373982612619067</v>
       </c>
       <c r="K73" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0.56638778894348862</v>
       </c>
       <c r="L73" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="M73" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N73" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="O73" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="P73" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="Q73" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -11006,47 +11075,47 @@
       <c r="E74" s="308"/>
       <c r="F74" s="27"/>
       <c r="G74" s="66">
-        <f t="shared" ref="G74:Q74" si="23">IF(G$4="","",ABS(G6/G$4))</f>
+        <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
         <v>0.18149772373474624</v>
       </c>
       <c r="H74" s="66">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0.11483176855578245</v>
       </c>
       <c r="I74" s="66">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0.44508542769239812</v>
       </c>
       <c r="J74" s="66">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0.43626017387380928</v>
       </c>
       <c r="K74" s="66">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0.43361221105651143</v>
       </c>
       <c r="L74" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="M74" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="N74" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="O74" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="P74" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q74" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -11063,47 +11132,47 @@
       <c r="E75" s="308"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
-        <f t="shared" ref="G75:Q75" si="24">IF(G$4="","",ABS(G7/G$4))</f>
+        <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
         <v>0.11641046432097352</v>
       </c>
       <c r="H75" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0.11331653115706901</v>
       </c>
       <c r="I75" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0.39871532034748752</v>
       </c>
       <c r="J75" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0.2682542237658872</v>
       </c>
       <c r="K75" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0.28671564736786559</v>
       </c>
       <c r="L75" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="M75" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="N75" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="O75" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="P75" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="Q75" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -11120,47 +11189,47 @@
       <c r="E76" s="308"/>
       <c r="F76" s="27"/>
       <c r="G76" s="66">
-        <f t="shared" ref="G76:Q76" si="25">IF(G$4="","",ABS(G8/G$4))</f>
+        <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
         <v>6.5087259413772719E-2</v>
       </c>
       <c r="H76" s="66">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1.5152373987134308E-3</v>
       </c>
       <c r="I76" s="66">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>4.6370107344910601E-2</v>
       </c>
       <c r="J76" s="66">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.16800595010792208</v>
       </c>
       <c r="K76" s="66">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.14689656368864581</v>
       </c>
       <c r="L76" s="66" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="M76" s="66" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="N76" s="66" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="O76" s="66" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="P76" s="66" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Q76" s="66" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
     </row>
@@ -11177,47 +11246,47 @@
       <c r="E77" s="308"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
-        <f t="shared" ref="G77:Q77" si="26">IF(G$4="","",G9/G$4)</f>
+        <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
         <v>2.2266856897037297E-2</v>
       </c>
       <c r="H77" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>2.2193527337177648E-2</v>
       </c>
       <c r="I77" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1.0231878798772523E-4</v>
       </c>
       <c r="J77" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1.0935967015910428E-4</v>
       </c>
       <c r="K77" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L77" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="M77" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="N77" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="O77" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="P77" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="Q77" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -11232,51 +11301,51 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="309" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
-        <f t="shared" ref="G78:Q78" si="27">IF(G$4="","",-G10/G$4)</f>
+        <f t="shared" ref="G78:Q78" si="29">IF(G$4="","",-G10/G$4)</f>
         <v>9.4776814590380575E-3</v>
       </c>
       <c r="H78" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>8.0185920734834829E-3</v>
       </c>
       <c r="I78" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="J78" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="K78" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="L78" s="6" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="M78" s="6" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N78" s="6" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="O78" s="6" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="P78" s="6" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Q78" s="6" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -11293,47 +11362,47 @@
       <c r="E79" s="308"/>
       <c r="F79" s="27"/>
       <c r="G79" s="66">
-        <f t="shared" ref="G79:Q79" si="28">IF(G$4="","",G11/G$4)</f>
+        <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
         <v>0</v>
       </c>
       <c r="H79" s="66">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="I79" s="66">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="J79" s="66">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K79" s="66">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="L79" s="66" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="M79" s="66" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="N79" s="66" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="O79" s="66" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="P79" s="66" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q79" s="66" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -11350,47 +11419,47 @@
       <c r="E80" s="308"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
-        <f t="shared" ref="G80:Q80" si="29">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>0</v>
+        <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
+        <v>1.2449332686363723E-2</v>
       </c>
       <c r="H80" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="31"/>
+        <v>8.3724102169596918E-3</v>
       </c>
       <c r="I80" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="31"/>
+        <v>9.1173366750378854E-4</v>
       </c>
       <c r="J80" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="31"/>
+        <v>1.5539134531893119E-3</v>
       </c>
       <c r="K80" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="31"/>
+        <v>2.1613384974143452E-4</v>
       </c>
       <c r="L80" s="6" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="M80" s="6" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N80" s="6" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="O80" s="6" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="P80" s="6" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="Q80" s="6" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -11407,47 +11476,47 @@
       <c r="E81" s="308"/>
       <c r="F81" s="27"/>
       <c r="G81" s="66">
-        <f t="shared" ref="G81:Q81" si="30">IF(G$4="","",G13/G$4)</f>
-        <v>7.7876434851771953E-2</v>
+        <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
+        <v>9.0325767538135676E-2</v>
       </c>
       <c r="H81" s="66">
-        <f t="shared" si="30"/>
-        <v>1.5690172662407596E-2</v>
+        <f t="shared" si="32"/>
+        <v>2.406258287936729E-2</v>
       </c>
       <c r="I81" s="66">
-        <f t="shared" si="30"/>
-        <v>4.6472426132898322E-2</v>
+        <f t="shared" si="32"/>
+        <v>4.5560692465394535E-2</v>
       </c>
       <c r="J81" s="66">
-        <f t="shared" si="30"/>
-        <v>0.16811530977808117</v>
+        <f t="shared" si="32"/>
+        <v>0.16656139632489186</v>
       </c>
       <c r="K81" s="66">
-        <f t="shared" si="30"/>
-        <v>0.14689656368864581</v>
+        <f t="shared" si="32"/>
+        <v>0.14668042983890439</v>
       </c>
       <c r="L81" s="66" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M81" s="66" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="N81" s="66" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="O81" s="66" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="P81" s="66" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="Q81" s="66" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -11464,47 +11533,47 @@
       <c r="E82" s="308"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
-        <f t="shared" ref="G82:Q82" si="31">IF(G$4="","",ABS(G14/G$4))</f>
+        <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
         <v>2.7512634742214121E-2</v>
       </c>
       <c r="H82" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1.4528168069689861E-2</v>
       </c>
       <c r="I82" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="J82" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K82" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L82" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M82" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="N82" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O82" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="P82" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="Q82" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
     </row>
@@ -11522,47 +11591,47 @@
       <c r="E83" s="308"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
-        <f t="shared" ref="G83:Q83" si="32">IF(G$4="","",-G15/G$4)</f>
+        <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
         <v>1.3611168709786237E-3</v>
       </c>
       <c r="H83" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>4.4586136960317649E-4</v>
       </c>
       <c r="I83" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="J83" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K83" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L83" s="6" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M83" s="6" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N83" s="6" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="O83" s="6" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="P83" s="6" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Q83" s="6" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
     </row>
@@ -11579,47 +11648,47 @@
       <c r="E84" s="308"/>
       <c r="F84" s="27"/>
       <c r="G84" s="66">
-        <f t="shared" ref="G84:Q84" si="33">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>4.9002683238579217E-2</v>
+        <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
+        <v>6.1452015924942933E-2</v>
       </c>
       <c r="H84" s="66">
-        <f t="shared" si="33"/>
-        <v>7.1614322311455941E-4</v>
+        <f t="shared" si="35"/>
+        <v>9.0885534400742506E-3</v>
       </c>
       <c r="I84" s="66">
-        <f t="shared" si="33"/>
-        <v>4.6472426132898322E-2</v>
+        <f t="shared" si="35"/>
+        <v>4.5560692465394535E-2</v>
       </c>
       <c r="J84" s="66">
-        <f t="shared" si="33"/>
-        <v>0.16811530977808117</v>
+        <f t="shared" si="35"/>
+        <v>0.16656139632489186</v>
       </c>
       <c r="K84" s="66">
-        <f t="shared" si="33"/>
-        <v>0.14689656368864581</v>
+        <f t="shared" si="35"/>
+        <v>0.14668042983890439</v>
       </c>
       <c r="L84" s="66" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="M84" s="66" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N84" s="66" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O84" s="66" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="P84" s="66" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q84" s="66" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
     </row>
@@ -11686,47 +11755,47 @@
       <c r="E87" s="308"/>
       <c r="F87" s="77"/>
       <c r="G87" s="66">
-        <f t="shared" ref="G87:Q87" si="34">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>4.9002683238579217E-2</v>
+        <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
+        <v>6.1452015924942933E-2</v>
       </c>
       <c r="H87" s="66">
-        <f t="shared" si="34"/>
-        <v>7.1614322311455941E-4</v>
+        <f t="shared" si="36"/>
+        <v>9.0885534400742506E-3</v>
       </c>
       <c r="I87" s="66">
-        <f t="shared" si="34"/>
-        <v>4.6472426132898322E-2</v>
+        <f t="shared" si="36"/>
+        <v>4.5560692465394535E-2</v>
       </c>
       <c r="J87" s="66">
-        <f t="shared" si="34"/>
-        <v>0.16811530977808117</v>
+        <f t="shared" si="36"/>
+        <v>0.16656139632489186</v>
       </c>
       <c r="K87" s="66">
-        <f t="shared" si="34"/>
-        <v>0.14689656368864581</v>
+        <f t="shared" si="36"/>
+        <v>0.14668042983890439</v>
       </c>
       <c r="L87" s="66" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="M87" s="66" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="N87" s="66" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="O87" s="66" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="P87" s="66" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Q87" s="66" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -11809,47 +11878,47 @@
       </c>
       <c r="E91" s="311"/>
       <c r="G91" s="76">
-        <f t="shared" ref="G91:Q91" si="35">IF(G$4="","",G90*Common_Shares/$C$3)</f>
+        <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
         <v>157066.6863</v>
       </c>
       <c r="H91" s="76">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="I91" s="76">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="J91" s="76">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="K91" s="76">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="L91" s="76" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="M91" s="76" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N91" s="76" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="O91" s="76" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="P91" s="76" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="Q91" s="76" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -11864,47 +11933,47 @@
       </c>
       <c r="E92" s="311"/>
       <c r="G92" s="175">
-        <f t="shared" ref="G92:Q92" si="36">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>1.9839668338217462</v>
+        <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
+        <v>1.5820424578480456</v>
       </c>
       <c r="H92" s="175">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="I92" s="175">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="J92" s="175">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="K92" s="175">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="L92" s="175" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="M92" s="175" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="N92" s="175" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O92" s="175" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="P92" s="175" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="Q92" s="175" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -11915,51 +11984,51 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.282511210762332E-2</v>
+        <v>5.4036697247706419E-2</v>
       </c>
       <c r="E93" s="311"/>
       <c r="G93" s="23">
-        <f t="shared" ref="G93:Q93" si="37">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.282511210762332E-2</v>
+        <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
+        <v>5.4036697247706419E-2</v>
       </c>
       <c r="H93" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="I93" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="J93" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="K93" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="L93" s="23" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="M93" s="23" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N93" s="23" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="O93" s="23" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P93" s="23" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="Q93" s="23" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -12001,47 +12070,47 @@
       <c r="E96" s="308"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
-        <f t="shared" ref="G96:Q96" si="38">IF(H4="","",G4/H4-1)</f>
+        <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
         <v>0.11678595474472542</v>
       </c>
       <c r="H96" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-0.18230094898304672</v>
       </c>
       <c r="I96" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>3.9363653347464389E-2</v>
       </c>
       <c r="J96" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0.2304116952266948</v>
       </c>
       <c r="K96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="L96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="M96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="N96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="O96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="P96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="Q96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -12052,53 +12121,53 @@
       </c>
       <c r="C97" s="79">
         <f>C13/G13-1</f>
-        <v>-0.37435924138615428</v>
+        <v>-0.46058945186119171</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="308"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
-        <f t="shared" ref="G97:Q97" si="39">IF(H5="","",G13/H13-1)</f>
-        <v>4.5430434399506563</v>
+        <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
+        <v>3.1921745908924395</v>
       </c>
       <c r="H97" s="6">
-        <f t="shared" si="39"/>
-        <v>-0.72392576923672913</v>
+        <f t="shared" si="41"/>
+        <v>-0.56813757384350083</v>
       </c>
       <c r="I97" s="6">
-        <f t="shared" si="39"/>
-        <v>-0.71268678224981663</v>
+        <f t="shared" si="41"/>
+        <v>-0.71569566049083433</v>
       </c>
       <c r="J97" s="6">
-        <f t="shared" si="39"/>
-        <v>0.40814079038663098</v>
+        <f t="shared" si="41"/>
+        <v>0.39718086616268633</v>
       </c>
       <c r="K97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="L97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="M97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="N97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="O97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="P97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="Q97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
     </row>
@@ -12151,47 +12220,47 @@
       <c r="E101" s="312"/>
       <c r="F101" s="26"/>
       <c r="G101" s="187">
-        <f t="shared" ref="G101:Q101" si="40">IF(G$4="","",G105+G104)</f>
+        <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
         <v>3670169</v>
       </c>
       <c r="H101" s="187">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>3559477</v>
       </c>
       <c r="I101" s="187">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>3413258</v>
       </c>
       <c r="J101" s="187">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>1603329</v>
       </c>
       <c r="K101" s="187">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>1218998</v>
       </c>
       <c r="L101" s="187" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="M101" s="187" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="N101" s="187" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="O101" s="187" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="P101" s="187" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="Q101" s="187" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
     </row>
@@ -12463,47 +12532,47 @@
       <c r="E108" s="312"/>
       <c r="F108" s="26"/>
       <c r="G108" s="97">
-        <f t="shared" ref="G108:Q108" si="41">IF(G$4="","",G102/G$4)</f>
+        <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
         <v>0</v>
       </c>
       <c r="H108" s="97">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="I108" s="97">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="J108" s="97">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="K108" s="97" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>#VALUE!</v>
       </c>
       <c r="L108" s="97" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="M108" s="97" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="N108" s="97" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="O108" s="97" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="P108" s="97" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="Q108" s="97" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -12520,47 +12589,47 @@
       <c r="E109" s="312"/>
       <c r="F109" s="26"/>
       <c r="G109" s="97">
-        <f t="shared" ref="G109:Q109" si="42">IF(G$4="","",G103/G$4)</f>
+        <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
         <v>0</v>
       </c>
       <c r="H109" s="97">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="I109" s="97">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="J109" s="97">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="K109" s="97" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>#VALUE!</v>
       </c>
       <c r="L109" s="97" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="M109" s="97" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="N109" s="97" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="O109" s="97" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="P109" s="97" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="Q109" s="97" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
     </row>
@@ -12660,47 +12729,47 @@
       </c>
       <c r="E113" s="311"/>
       <c r="G113" s="23">
-        <f t="shared" ref="G113:Q113" si="43">G81</f>
-        <v>7.7876434851771953E-2</v>
+        <f t="shared" ref="G113:Q113" si="45">G81</f>
+        <v>9.0325767538135676E-2</v>
       </c>
       <c r="H113" s="23">
-        <f t="shared" si="43"/>
-        <v>1.5690172662407596E-2</v>
+        <f t="shared" si="45"/>
+        <v>2.406258287936729E-2</v>
       </c>
       <c r="I113" s="23">
-        <f t="shared" si="43"/>
-        <v>4.6472426132898322E-2</v>
+        <f t="shared" si="45"/>
+        <v>4.5560692465394535E-2</v>
       </c>
       <c r="J113" s="23">
-        <f t="shared" si="43"/>
-        <v>0.16811530977808117</v>
+        <f t="shared" si="45"/>
+        <v>0.16656139632489186</v>
       </c>
       <c r="K113" s="23">
-        <f t="shared" si="43"/>
-        <v>0.14689656368864581</v>
+        <f t="shared" si="45"/>
+        <v>0.14668042983890439</v>
       </c>
       <c r="L113" s="23" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="M113" s="23" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="N113" s="23" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="O113" s="23" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="P113" s="23" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="Q113" s="23" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
     </row>
@@ -12714,47 +12783,47 @@
       </c>
       <c r="E114" s="311"/>
       <c r="G114" s="42">
-        <f t="shared" ref="G114:Q114" si="44">IF(G4="","",G4/G101)</f>
+        <f t="shared" ref="G114:Q114" si="46">IF(G4="","",G4/G101)</f>
         <v>0.44019362596109335</v>
       </c>
       <c r="H114" s="42">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0.40641869578030704</v>
       </c>
       <c r="I114" s="42">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0.51831915430946029</v>
       </c>
       <c r="J114" s="42">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>1.0616373807247297</v>
       </c>
       <c r="K114" s="42">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>1.1348681458049972</v>
       </c>
       <c r="L114" s="42" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="M114" s="42" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="N114" s="42" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="O114" s="42" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="P114" s="42" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="Q114" s="42" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
@@ -12770,47 +12839,47 @@
       <c r="E115" s="315"/>
       <c r="F115" s="11"/>
       <c r="G115" s="15">
-        <f t="shared" ref="G115:Q115" si="45">IF(G$4="","",G101/G105)</f>
+        <f t="shared" ref="G115:Q115" si="47">IF(G$4="","",G101/G105)</f>
         <v>1.2123604198075375</v>
       </c>
       <c r="H115" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>1.2601845662770377</v>
       </c>
       <c r="I115" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>1.2478737845300938</v>
       </c>
       <c r="J115" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>6.3996463553848981</v>
       </c>
       <c r="K115" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>87.508829863603736</v>
       </c>
       <c r="L115" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="M115" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="N115" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="O115" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="P115" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="Q115" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
     </row>
@@ -12827,47 +12896,47 @@
       <c r="E116" s="314"/>
       <c r="F116" s="106"/>
       <c r="G116" s="105">
-        <f t="shared" ref="G116:Q116" si="46">IF(G$4="","",G8/G105)</f>
+        <f t="shared" ref="G116:Q116" si="48">IF(G$4="","",G8/G105)</f>
         <v>3.4735334417690791E-2</v>
       </c>
       <c r="H116" s="105">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>7.7604787705588959E-4</v>
       </c>
       <c r="I116" s="105">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>2.9992040973085183E-2</v>
       </c>
       <c r="J116" s="105">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>1.1414498630924346</v>
       </c>
       <c r="K116" s="105">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>14.588442211055277</v>
       </c>
       <c r="L116" s="105" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="M116" s="105" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="N116" s="105" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="O116" s="105" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="P116" s="105" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="Q116" s="105" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
     </row>
@@ -12942,53 +13011,53 @@
       </c>
       <c r="C120" s="182">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>4.5784535896430022E-2</v>
+        <v>4.5723426463104268E-2</v>
       </c>
       <c r="D120" s="27"/>
       <c r="E120" s="308"/>
       <c r="F120" s="27"/>
       <c r="G120" s="182">
-        <f t="shared" ref="G120:Q120" si="47">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.3649843273209591E-2</v>
+        <f t="shared" ref="G120:Q120" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
+        <v>7.9713809414154707E-2</v>
       </c>
       <c r="H120" s="182">
-        <f t="shared" si="47"/>
-        <v>8.3292792076400998E-4</v>
+        <f t="shared" si="49"/>
+        <v>1.055655588911119E-2</v>
       </c>
       <c r="I120" s="182">
-        <f t="shared" si="47"/>
-        <v>6.6101206422931644E-2</v>
+        <f t="shared" si="49"/>
+        <v>6.4717883901121279E-2</v>
       </c>
       <c r="J120" s="182">
-        <f t="shared" si="47"/>
-        <v>0.23006670887103464</v>
+        <f t="shared" si="49"/>
+        <v>0.22763593412908437</v>
       </c>
       <c r="K120" s="182">
-        <f t="shared" si="47"/>
-        <v>0.16338331397094574</v>
+        <f t="shared" si="49"/>
+        <v>0.1629251728548784</v>
       </c>
       <c r="L120" s="182" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="M120" s="182" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="N120" s="182" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="O120" s="182" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="P120" s="182" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="Q120" s="182" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
     </row>
@@ -12999,53 +13068,53 @@
       </c>
       <c r="C121" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.0531182016336334E-2</v>
+        <v>2.0974048836286365E-2</v>
       </c>
       <c r="D121" s="27"/>
       <c r="E121" s="308"/>
       <c r="F121" s="27"/>
       <c r="G121" s="79">
-        <f t="shared" ref="G121" si="48">IF(G$4="","",G120/Market_Price)</f>
-        <v>2.8542530615789055E-2</v>
+        <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
+        <v>3.6565967621171883E-2</v>
       </c>
       <c r="H121" s="79">
-        <f t="shared" ref="H121" si="49">IF(H$4="","",H120/Market_Price)</f>
-        <v>3.7351027836951122E-4</v>
+        <f t="shared" ref="H121" si="51">IF(H$4="","",H120/Market_Price)</f>
+        <v>4.8424568298675178E-3</v>
       </c>
       <c r="I121" s="79">
-        <f t="shared" ref="I121" si="50">IF(I$4="","",I120/Market_Price)</f>
-        <v>2.9641796602211501E-2</v>
+        <f t="shared" ref="I121" si="52">IF(I$4="","",I120/Market_Price)</f>
+        <v>2.9687102706936364E-2</v>
       </c>
       <c r="J121" s="79">
-        <f t="shared" ref="J121" si="51">IF(J$4="","",J120/Market_Price)</f>
-        <v>0.10316892774485859</v>
+        <f t="shared" ref="J121" si="53">IF(J$4="","",J120/Market_Price)</f>
+        <v>0.10442015327022218</v>
       </c>
       <c r="K121" s="79">
-        <f t="shared" ref="K121" si="52">IF(K$4="","",K120/Market_Price)</f>
-        <v>7.3266060076657286E-2</v>
+        <f t="shared" ref="K121" si="54">IF(K$4="","",K120/Market_Price)</f>
+        <v>7.4736317823338713E-2</v>
       </c>
       <c r="L121" s="79" t="str">
-        <f t="shared" ref="L121" si="53">IF(L$4="","",L120/Market_Price)</f>
+        <f t="shared" ref="L121" si="55">IF(L$4="","",L120/Market_Price)</f>
         <v/>
       </c>
       <c r="M121" s="79" t="str">
-        <f t="shared" ref="M121" si="54">IF(M$4="","",M120/Market_Price)</f>
+        <f t="shared" ref="M121" si="56">IF(M$4="","",M120/Market_Price)</f>
         <v/>
       </c>
       <c r="N121" s="79" t="str">
-        <f t="shared" ref="N121" si="55">IF(N$4="","",N120/Market_Price)</f>
+        <f t="shared" ref="N121" si="57">IF(N$4="","",N120/Market_Price)</f>
         <v/>
       </c>
       <c r="O121" s="79" t="str">
-        <f t="shared" ref="O121" si="56">IF(O$4="","",O120/Market_Price)</f>
+        <f t="shared" ref="O121" si="58">IF(O$4="","",O120/Market_Price)</f>
         <v/>
       </c>
       <c r="P121" s="79" t="str">
-        <f t="shared" ref="P121" si="57">IF(P$4="","",P120/Market_Price)</f>
+        <f t="shared" ref="P121" si="59">IF(P$4="","",P120/Market_Price)</f>
         <v/>
       </c>
       <c r="Q121" s="79" t="str">
-        <f t="shared" ref="Q121" si="58">IF(Q$4="","",Q120/Market_Price)</f>
+        <f t="shared" ref="Q121" si="60">IF(Q$4="","",Q120/Market_Price)</f>
         <v/>
       </c>
     </row>
@@ -13905,7 +13974,7 @@
       </c>
       <c r="C11" s="238">
         <f>Exchange_Rate</f>
-        <v>1.07197944</v>
+        <v>1.0705486499999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -13919,7 +13988,7 @@
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>2.2574561829198969</v>
+        <v>2.2544431160536518</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -13972,7 +14041,7 @@
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>2.290148715098975</v>
+        <v>2.2870920129293171</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14908,23 +14977,23 @@
       </c>
       <c r="B65" s="128">
         <f>C12</f>
-        <v>2.2574561829198969</v>
+        <v>2.2544431160536518</v>
       </c>
       <c r="C65" s="128">
         <f>C12</f>
-        <v>2.2574561829198969</v>
+        <v>2.2544431160536518</v>
       </c>
       <c r="D65" s="128">
         <f>C12</f>
-        <v>2.2574561829198969</v>
+        <v>2.2544431160536518</v>
       </c>
       <c r="E65" s="145">
         <f>C12</f>
-        <v>2.2574561829198969</v>
+        <v>2.2544431160536518</v>
       </c>
       <c r="F65" s="128">
         <f>C12</f>
-        <v>2.2574561829198969</v>
+        <v>2.2544431160536518</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -14935,23 +15004,23 @@
       </c>
       <c r="B66" s="128">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.2051459045184889</v>
+        <v>2.2022026571100066</v>
       </c>
       <c r="C66" s="128">
         <f t="shared" si="4"/>
-        <v>2.2051459045184889</v>
+        <v>2.2022026571100066</v>
       </c>
       <c r="D66" s="128">
         <f t="shared" si="4"/>
-        <v>2.2759217928922166</v>
+        <v>2.2728840796483389</v>
       </c>
       <c r="E66" s="128">
         <f t="shared" si="4"/>
-        <v>2.3145363927670646</v>
+        <v>2.3114471399308276</v>
       </c>
       <c r="F66" s="128">
         <f t="shared" si="4"/>
-        <v>2.3347346722005082</v>
+        <v>2.3316184603619323</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -14962,23 +15031,23 @@
       </c>
       <c r="B67" s="128">
         <f t="shared" si="4"/>
-        <v>2.1650496646349171</v>
+        <v>2.162159934390032</v>
       </c>
       <c r="C67" s="128">
         <f t="shared" si="4"/>
-        <v>2.1650496646349171</v>
+        <v>2.162159934390032</v>
       </c>
       <c r="D67" s="128">
         <f t="shared" si="4"/>
-        <v>2.2944044067732943</v>
+        <v>2.2913420244563656</v>
       </c>
       <c r="E67" s="128">
         <f t="shared" si="4"/>
-        <v>2.3798536851861303</v>
+        <v>2.3766772521994795</v>
       </c>
       <c r="F67" s="128">
         <f t="shared" si="4"/>
-        <v>2.4292906780886012</v>
+        <v>2.4260482606693805</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -14989,23 +15058,23 @@
       </c>
       <c r="B68" s="128">
         <f t="shared" si="4"/>
-        <v>2.1238428093649251</v>
+        <v>2.1210080786417205</v>
       </c>
       <c r="C68" s="128">
         <f t="shared" si="4"/>
-        <v>2.1238428093649251</v>
+        <v>2.1210080786417205</v>
       </c>
       <c r="D68" s="128">
         <f t="shared" si="4"/>
-        <v>2.3172817661997365</v>
+        <v>2.3141888490648133</v>
       </c>
       <c r="E68" s="128">
         <f t="shared" si="4"/>
-        <v>2.4697001409243393</v>
+        <v>2.4664037882772836</v>
       </c>
       <c r="F68" s="128">
         <f t="shared" si="4"/>
-        <v>2.5667656572813171</v>
+        <v>2.5633397495654178</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -15016,23 +15085,23 @@
       </c>
       <c r="B69" s="128">
         <f t="shared" si="4"/>
-        <v>2.0888463011524525</v>
+        <v>2.0860582808903976</v>
       </c>
       <c r="C69" s="128">
         <f t="shared" si="4"/>
-        <v>2.0888463011524525</v>
+        <v>2.0860582808903976</v>
       </c>
       <c r="D69" s="128">
         <f t="shared" si="4"/>
-        <v>2.3405901266693476</v>
+        <v>2.3374660994516825</v>
       </c>
       <c r="E69" s="128">
         <f t="shared" si="4"/>
-        <v>2.5721905253925392</v>
+        <v>2.5687573770088101</v>
       </c>
       <c r="F69" s="128">
         <f t="shared" si="4"/>
-        <v>2.7334505685390997</v>
+        <v>2.7298021835113415</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -15043,23 +15112,23 @@
       </c>
       <c r="B70" s="128">
         <f t="shared" si="4"/>
-        <v>2.0615559541065314</v>
+        <v>2.0588043587554337</v>
       </c>
       <c r="C70" s="128">
         <f t="shared" si="4"/>
-        <v>2.0615559541065314</v>
+        <v>2.0588043587554337</v>
       </c>
       <c r="D70" s="128">
         <f t="shared" si="4"/>
-        <v>2.362268195287232</v>
+        <v>2.3591152339663179</v>
       </c>
       <c r="E70" s="128">
         <f t="shared" si="4"/>
-        <v>2.6795973321055397</v>
+        <v>2.6760208259490379</v>
       </c>
       <c r="F70" s="128">
         <f t="shared" si="4"/>
-        <v>2.9200152687468646</v>
+        <v>2.9161178724998149</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15069,23 +15138,23 @@
       </c>
       <c r="B71" s="128">
         <f t="shared" si="4"/>
-        <v>2.0412482427325078</v>
+        <v>2.0385237524445041</v>
       </c>
       <c r="C71" s="128">
         <f t="shared" si="4"/>
-        <v>2.0412482427325078</v>
+        <v>2.0385237524445041</v>
       </c>
       <c r="D71" s="128">
         <f t="shared" si="4"/>
-        <v>2.3813912674048643</v>
+        <v>2.3782127821799142</v>
       </c>
       <c r="E71" s="128">
         <f t="shared" si="4"/>
-        <v>2.786990489515798</v>
+        <v>2.7832706438044896</v>
       </c>
       <c r="F71" s="128">
         <f t="shared" si="4"/>
-        <v>3.120109819274564</v>
+        <v>3.115945353276671</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15120,7 +15189,7 @@
       </c>
       <c r="E74" s="139">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>2.5667656572813171</v>
+        <v>2.5633397495654178</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
@@ -15142,7 +15211,7 @@
       </c>
       <c r="E75" s="139">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>2.3798536851861303</v>
+        <v>2.3766772521994795</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -15165,7 +15234,7 @@
       </c>
       <c r="E76" s="139">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>2.2944044067732943</v>
+        <v>2.2913420244563656</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15188,7 +15257,7 @@
       </c>
       <c r="E77" s="139">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>2.1650496646349171</v>
+        <v>2.162159934390032</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -15211,7 +15280,7 @@
       </c>
       <c r="E78" s="139">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.1238428093649251</v>
+        <v>2.1210080786417205</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
@@ -15312,7 +15381,7 @@
       </c>
       <c r="I3" s="272">
         <f>-Market_Price</f>
-        <v>-2.23</v>
+        <v>-2.1800000000000002</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -15361,7 +15430,7 @@
       </c>
       <c r="I6" s="272">
         <f t="shared" si="0"/>
-        <v>2.4104315515979433</v>
+        <v>2.4073715355423078</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15395,7 +15464,7 @@
       </c>
       <c r="C8" s="118">
         <f>Normalized_FCF!G19</f>
-        <v>79168</v>
+        <v>99280.955148098932</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15501,7 +15570,7 @@
       </c>
       <c r="C14" s="163">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-0.34839983405888664</v>
+        <v>-0.2951485762236955</v>
       </c>
       <c r="E14" s="348"/>
       <c r="F14" s="348"/>
@@ -15552,7 +15621,7 @@
       </c>
       <c r="C21" s="165">
         <f>Market_Price</f>
-        <v>2.23</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -15567,7 +15636,7 @@
       </c>
       <c r="C22" s="165">
         <f>Valuation_Model!C12</f>
-        <v>2.2574561829198969</v>
+        <v>2.2544431160536518</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -15614,7 +15683,7 @@
       </c>
       <c r="C27" s="165">
         <f>Valuation_Model!E76</f>
-        <v>2.2944044067732943</v>
+        <v>2.2913420244563656</v>
       </c>
       <c r="D27" s="165" t="str">
         <f>Market_currency</f>
@@ -15672,7 +15741,7 @@
       </c>
       <c r="C33" s="165">
         <f>Valuation_Model!E77</f>
-        <v>2.1650496646349171</v>
+        <v>2.162159934390032</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -15730,7 +15799,7 @@
       </c>
       <c r="C39" s="165">
         <f>Valuation_Model!E75</f>
-        <v>2.3798536851861303</v>
+        <v>2.3766772521994795</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -15757,7 +15826,7 @@
       </c>
       <c r="C42" s="159">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>2.2963635150557469</v>
+        <v>2.2932985178821941</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -15831,7 +15900,7 @@
       </c>
       <c r="C51" s="165">
         <f>Valuation_Model!E78</f>
-        <v>2.1238428093649251</v>
+        <v>2.1210080786417205</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -15889,7 +15958,7 @@
       </c>
       <c r="C57" s="165">
         <f>Valuation_Model!E74</f>
-        <v>2.5667656572813171</v>
+        <v>2.5633397495654178</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -15915,7 +15984,7 @@
       </c>
       <c r="C60" s="159">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>2.2926315515979434</v>
+        <v>2.2895715355423079</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -15976,7 +16045,7 @@
       </c>
       <c r="C66" s="165">
         <f>Valuation_Model!C18</f>
-        <v>2.290148715098975</v>
+        <v>2.2870920129293171</v>
       </c>
       <c r="D66" s="165" t="str">
         <f>Market_currency</f>
@@ -16031,12 +16100,15 @@
         <v>311</v>
       </c>
       <c r="C72" s="280" t="str">
-        <f>IF(E72&gt;50%,"Y","N")</f>
+        <f>IF(F72&gt;50%,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="E72" s="138" t="str">
-        <f>"Non-FCF Value is "&amp;ROUND(BS!D89/C60*100,0)&amp;"% of the Expected Equity Value"</f>
-        <v>Non-FCF Value is 74% of the Expected Equity Value</v>
+      <c r="E72" s="138" t="s">
+        <v>385</v>
+      </c>
+      <c r="F72" s="339">
+        <f>BS!D89/C60</f>
+        <v>0.7350284798444775</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16108,7 +16180,7 @@
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
-        <v>1.3267543701376987</v>
+        <v>1.3249835275129096</v>
       </c>
       <c r="D82" s="120"/>
     </row>
@@ -16118,7 +16190,7 @@
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
-        <v>1.5748978886562173</v>
+        <v>1.5731270460314282</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16129,7 +16201,7 @@
       </c>
       <c r="F83" s="270">
         <f>(C83/C60-1)</f>
-        <v>-0.31306105965499442</v>
+        <v>-0.31291640308638913</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16146,7 +16218,7 @@
       </c>
       <c r="C86" s="274">
         <f>Market_Price</f>
-        <v>2.23</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16159,7 +16231,7 @@
       </c>
       <c r="C87" s="273">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>6.1633064159671846E-2</v>
+        <v>6.9675781490122768E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C39B32-2D22-4A22-B313-62A2B45E9CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A80A5DCF-4118-4689-8DB1-42FB0FFD3A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2674,7 +2674,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="350">
+  <cellXfs count="348">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3017,7 +3017,6 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3239,9 +3238,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="190" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3381,20 +3377,20 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3706,15 +3702,15 @@
         <v>45730</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="292" t="s">
+      <c r="E1" s="290" t="s">
         <v>348</v>
       </c>
-      <c r="F1" s="293" t="s">
+      <c r="F1" s="291" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A2" s="254" t="s">
+      <c r="A2" s="253" t="s">
         <v>281</v>
       </c>
       <c r="B2" s="36"/>
@@ -3774,7 +3770,7 @@
       <c r="B8" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="C8" s="287">
+      <c r="C8" s="285">
         <v>6</v>
       </c>
       <c r="D8" s="5"/>
@@ -3808,13 +3804,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="339" t="s">
         <v>286</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="339"/>
+      <c r="D12" s="339"/>
+      <c r="E12" s="339"/>
+      <c r="F12" s="339"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3848,7 +3844,7 @@
         <v>2</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0705486499999999</v>
+        <v>1.0705486500000001</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -3869,7 +3865,7 @@
       <c r="B19" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C19" s="256">
+      <c r="C19" s="255">
         <v>0.2</v>
       </c>
       <c r="E19" s="5"/>
@@ -3879,14 +3875,14 @@
         <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
         <v>Target Buy Price (HKD):</v>
       </c>
-      <c r="C20" s="259">
+      <c r="C20" s="258">
         <f>C127</f>
-        <v>1.5731270460314282</v>
+        <v>1.5731270460314284</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="E20" s="322">
+      <c r="E20" s="320">
         <v>3</v>
       </c>
     </row>
@@ -3894,7 +3890,7 @@
       <c r="B21" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="C21" s="288">
+      <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
         <v>6.9675781490122768E-2</v>
       </c>
@@ -3906,7 +3902,7 @@
       <c r="E22" s="5"/>
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A23" s="254" t="s">
+      <c r="A23" s="253" t="s">
         <v>235</v>
       </c>
       <c r="B23" s="36"/>
@@ -3916,25 +3912,25 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="339" t="s">
         <v>236</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="339"/>
+      <c r="D25" s="339"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="344" t="s">
+      <c r="B26" s="340" t="s">
         <v>376</v>
       </c>
-      <c r="C26" s="344"/>
-      <c r="D26" s="344"/>
-      <c r="E26" s="344"/>
-      <c r="F26" s="344"/>
+      <c r="C26" s="340"/>
+      <c r="D26" s="340"/>
+      <c r="E26" s="340"/>
+      <c r="F26" s="340"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B28" s="241" t="s">
+      <c r="B28" s="240" t="s">
         <v>237</v>
       </c>
       <c r="C28" s="111">
@@ -3943,19 +3939,19 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="342" t="s">
+      <c r="B29" s="338" t="s">
         <v>238</v>
       </c>
-      <c r="C29" s="342"/>
-      <c r="D29" s="342"/>
-      <c r="E29" s="342"/>
-      <c r="F29" s="342"/>
+      <c r="C29" s="338"/>
+      <c r="D29" s="338"/>
+      <c r="E29" s="338"/>
+      <c r="F29" s="338"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C30" s="192">
+      <c r="C30" s="191">
         <f>Normalized_FCF!C8</f>
         <v>58602.662537660683</v>
       </c>
@@ -3969,19 +3965,19 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="342" t="s">
+      <c r="B32" s="338" t="s">
         <v>240</v>
       </c>
-      <c r="C32" s="342"/>
-      <c r="D32" s="342"/>
-      <c r="E32" s="342"/>
-      <c r="F32" s="342"/>
+      <c r="C32" s="338"/>
+      <c r="D32" s="338"/>
+      <c r="E32" s="338"/>
+      <c r="F32" s="338"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
         <v>241</v>
       </c>
-      <c r="C33" s="192">
+      <c r="C33" s="191">
         <f>Normalized_FCF!C9</f>
         <v>35974</v>
       </c>
@@ -3994,7 +3990,7 @@
       <c r="B34" s="52" t="s">
         <v>242</v>
       </c>
-      <c r="C34" s="192">
+      <c r="C34" s="191">
         <f>Normalized_FCF!C10</f>
         <v>-35974</v>
       </c>
@@ -4004,19 +4000,19 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="342" t="s">
+      <c r="B36" s="338" t="s">
         <v>243</v>
       </c>
-      <c r="C36" s="342"/>
-      <c r="D36" s="342"/>
-      <c r="E36" s="342"/>
-      <c r="F36" s="342"/>
+      <c r="C36" s="338"/>
+      <c r="D36" s="338"/>
+      <c r="E36" s="338"/>
+      <c r="F36" s="338"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
         <v>244</v>
       </c>
-      <c r="C37" s="192">
+      <c r="C37" s="191">
         <f>Normalized_FCF!C11</f>
         <v>0</v>
       </c>
@@ -4026,19 +4022,19 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="342" t="s">
+      <c r="B39" s="338" t="s">
         <v>247</v>
       </c>
-      <c r="C39" s="342"/>
-      <c r="D39" s="342"/>
-      <c r="E39" s="342"/>
-      <c r="F39" s="342"/>
+      <c r="C39" s="338"/>
+      <c r="D39" s="338"/>
+      <c r="E39" s="338"/>
+      <c r="F39" s="338"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
         <v>377</v>
       </c>
-      <c r="C40" s="332">
+      <c r="C40" s="330">
         <f>Normalized_FCF!C48</f>
         <v>21115.955148098936</v>
       </c>
@@ -4046,14 +4042,14 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E40" s="331"/>
-      <c r="F40" s="331"/>
+      <c r="E40" s="329"/>
+      <c r="F40" s="329"/>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
         <v>378</v>
       </c>
-      <c r="C41" s="332">
+      <c r="C41" s="330">
         <f>Normalized_FCF!C47</f>
         <v>-1003</v>
       </c>
@@ -4061,14 +4057,14 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E41" s="331"/>
-      <c r="F41" s="331"/>
+      <c r="E41" s="329"/>
+      <c r="F41" s="329"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B42" s="47" t="s">
         <v>245</v>
       </c>
-      <c r="C42" s="192">
+      <c r="C42" s="191">
         <f>Normalized_FCF!C12</f>
         <v>20112.955148098936</v>
       </c>
@@ -4086,7 +4082,7 @@
       <c r="B45" s="47" t="s">
         <v>279</v>
       </c>
-      <c r="C45" s="192">
+      <c r="C45" s="191">
         <f>Normalized_FCF!C15</f>
         <v>-2089.6737831682049</v>
       </c>
@@ -4096,19 +4092,19 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="342" t="s">
+      <c r="B47" s="338" t="s">
         <v>248</v>
       </c>
-      <c r="C47" s="342"/>
-      <c r="D47" s="342"/>
-      <c r="E47" s="342"/>
-      <c r="F47" s="342"/>
+      <c r="C47" s="338"/>
+      <c r="D47" s="338"/>
+      <c r="E47" s="338"/>
+      <c r="F47" s="338"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
         <v>246</v>
       </c>
-      <c r="C48" s="192">
+      <c r="C48" s="191">
         <f>Normalized_FCF!C14</f>
         <v>-19678.904421439904</v>
       </c>
@@ -4118,13 +4114,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="342" t="s">
+      <c r="B50" s="338" t="s">
         <v>375</v>
       </c>
-      <c r="C50" s="343"/>
-      <c r="D50" s="343"/>
-      <c r="E50" s="343"/>
-      <c r="F50" s="343"/>
+      <c r="C50" s="342"/>
+      <c r="D50" s="342"/>
+      <c r="E50" s="342"/>
+      <c r="F50" s="342"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4140,28 +4136,28 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="339" t="s">
         <v>380</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="339"/>
+      <c r="D53" s="339"/>
+      <c r="E53" s="339"/>
+      <c r="F53" s="339"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="339" t="s">
         <v>268</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="339"/>
+      <c r="D54" s="339"/>
+      <c r="E54" s="339"/>
+      <c r="F54" s="339"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
         <v>285</v>
       </c>
-      <c r="C56" s="192">
+      <c r="C56" s="191">
         <f>Normalized_FCF!G19</f>
         <v>99280.955148098932</v>
       </c>
@@ -4174,7 +4170,7 @@
       <c r="B57" s="47" t="s">
         <v>255</v>
       </c>
-      <c r="C57" s="192">
+      <c r="C57" s="191">
         <f>Normalized_FCF!C19</f>
         <v>56947.039481151507</v>
       </c>
@@ -4184,7 +4180,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B58" s="261" t="s">
+      <c r="B58" s="260" t="s">
         <v>284</v>
       </c>
       <c r="C58" s="94">
@@ -4193,7 +4189,7 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B59" s="261" t="s">
+      <c r="B59" s="260" t="s">
         <v>339</v>
       </c>
       <c r="C59" s="94">
@@ -4202,7 +4198,7 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A61" s="254" t="s">
+      <c r="A61" s="253" t="s">
         <v>302</v>
       </c>
       <c r="B61" s="36"/>
@@ -4212,29 +4208,29 @@
       <c r="F61" s="36"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A62" s="240"/>
+      <c r="A62" s="239"/>
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="338" t="s">
         <v>303</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="338"/>
+      <c r="D63" s="338"/>
+      <c r="E63" s="338"/>
+      <c r="F63" s="338"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="344" t="s">
+      <c r="B64" s="340" t="s">
         <v>259</v>
       </c>
-      <c r="C64" s="344"/>
-      <c r="D64" s="344"/>
-      <c r="E64" s="344"/>
-      <c r="F64" s="344"/>
+      <c r="C64" s="340"/>
+      <c r="D64" s="340"/>
+      <c r="E64" s="340"/>
+      <c r="F64" s="340"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B66" s="241" t="s">
+      <c r="B66" s="240" t="s">
         <v>237</v>
       </c>
     </row>
@@ -4242,7 +4238,7 @@
       <c r="B67" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C67" s="320">
+      <c r="C67" s="318">
         <v>0.08</v>
       </c>
     </row>
@@ -4250,11 +4246,11 @@
       <c r="B68" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="C68" s="271">
+      <c r="C68" s="269">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
-      <c r="D68" s="295" t="s">
+      <c r="D68" s="293" t="s">
         <v>354</v>
       </c>
     </row>
@@ -4262,11 +4258,11 @@
       <c r="B69" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="C69" s="271">
+      <c r="C69" s="269">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
-      <c r="D69" s="295" t="s">
+      <c r="D69" s="293" t="s">
         <v>354</v>
       </c>
     </row>
@@ -4274,7 +4270,7 @@
       <c r="B70" s="82" t="s">
         <v>254</v>
       </c>
-      <c r="C70" s="271">
+      <c r="C70" s="269">
         <f>SUM(C67:C69)</f>
         <v>0.08</v>
       </c>
@@ -4283,28 +4279,28 @@
       <c r="C71" s="125"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B72" s="340" t="s">
+      <c r="B72" s="339" t="s">
         <v>381</v>
       </c>
-      <c r="C72" s="340"/>
-      <c r="D72" s="340"/>
-      <c r="E72" s="340"/>
-      <c r="F72" s="340"/>
+      <c r="C72" s="339"/>
+      <c r="D72" s="339"/>
+      <c r="E72" s="339"/>
+      <c r="F72" s="339"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="339" t="s">
         <v>382</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="339"/>
+      <c r="D73" s="339"/>
+      <c r="E73" s="339"/>
+      <c r="F73" s="339"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B75" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="C75" s="271">
+      <c r="C75" s="269">
         <v>0</v>
       </c>
     </row>
@@ -4312,9 +4308,9 @@
       <c r="B76" s="47" t="s">
         <v>301</v>
       </c>
-      <c r="C76" s="255">
+      <c r="C76" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.5715428307888033</v>
+        <v>0.57154283078880352</v>
       </c>
       <c r="D76" s="1" t="str">
         <f>Market_currency</f>
@@ -4322,7 +4318,7 @@
       </c>
     </row>
     <row r="78" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A78" s="254" t="s">
+      <c r="A78" s="253" t="s">
         <v>260</v>
       </c>
       <c r="B78" s="36"/>
@@ -4332,16 +4328,16 @@
       <c r="F78" s="36"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A79" s="240"/>
+      <c r="A79" s="239"/>
     </row>
     <row r="80" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="340" t="s">
+      <c r="B80" s="339" t="s">
         <v>261</v>
       </c>
-      <c r="C80" s="340"/>
-      <c r="D80" s="340"/>
-      <c r="E80" s="340"/>
-      <c r="F80" s="340"/>
+      <c r="C80" s="339"/>
+      <c r="D80" s="339"/>
+      <c r="E80" s="339"/>
+      <c r="F80" s="339"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="1" t="s">
@@ -4349,24 +4345,24 @@
       </c>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B83" s="241" t="s">
+      <c r="B83" s="240" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="84" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="340" t="s">
+      <c r="B84" s="339" t="s">
         <v>383</v>
       </c>
-      <c r="C84" s="340"/>
-      <c r="D84" s="340"/>
-      <c r="E84" s="340"/>
-      <c r="F84" s="340"/>
+      <c r="C84" s="339"/>
+      <c r="D84" s="339"/>
+      <c r="E84" s="339"/>
+      <c r="F84" s="339"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="47" t="s">
         <v>264</v>
       </c>
-      <c r="C85" s="192">
+      <c r="C85" s="191">
         <f>Valuation_Model!C7</f>
         <v>33999</v>
       </c>
@@ -4379,9 +4375,9 @@
       <c r="B86" s="47" t="s">
         <v>304</v>
       </c>
-      <c r="C86" s="255">
+      <c r="C86" s="254">
         <f>C85*C28*Exchange_Rate/Common_Shares</f>
-        <v>2.7298184251239466E-2</v>
+        <v>2.7298184251239473E-2</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -4397,7 +4393,7 @@
       <c r="B89" s="47" t="s">
         <v>278</v>
       </c>
-      <c r="C89" s="192">
+      <c r="C89" s="191">
         <f>BS!C66</f>
         <v>2664732</v>
       </c>
@@ -4410,7 +4406,7 @@
       <c r="B90" s="47" t="s">
         <v>280</v>
       </c>
-      <c r="C90" s="192">
+      <c r="C90" s="191">
         <f>Valuation_Model!C8</f>
         <v>1902339.7312688304</v>
       </c>
@@ -4423,9 +4419,9 @@
       <c r="B91" s="47" t="s">
         <v>305</v>
       </c>
-      <c r="C91" s="255">
+      <c r="C91" s="254">
         <f>C90*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.5274102324371277</v>
+        <v>1.5274102324371279</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Market_currency</f>
@@ -4441,7 +4437,7 @@
       <c r="B94" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C94" s="192">
+      <c r="C94" s="191">
         <f>Valuation_Model!C9</f>
         <v>227656.8</v>
       </c>
@@ -4454,9 +4450,9 @@
       <c r="B95" s="47" t="s">
         <v>306</v>
       </c>
-      <c r="C95" s="255">
+      <c r="C95" s="254">
         <f>C94*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.18278823707896036</v>
+        <v>0.18278823707896039</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4464,21 +4460,21 @@
       </c>
     </row>
     <row r="97" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="340" t="s">
+      <c r="B97" s="339" t="s">
         <v>267</v>
       </c>
-      <c r="C97" s="340"/>
-      <c r="D97" s="340"/>
-      <c r="E97" s="340"/>
-      <c r="F97" s="340"/>
+      <c r="C97" s="339"/>
+      <c r="D97" s="339"/>
+      <c r="E97" s="339"/>
+      <c r="F97" s="339"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B99" s="47" t="s">
         <v>300</v>
       </c>
-      <c r="C99" s="255">
+      <c r="C99" s="254">
         <f>Valuation_Model!C12</f>
-        <v>2.2544431160536518</v>
+        <v>2.2544431160536522</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4486,7 +4482,7 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A101" s="254" t="s">
+      <c r="A101" s="253" t="s">
         <v>277</v>
       </c>
       <c r="B101" s="36"/>
@@ -4496,165 +4492,165 @@
       <c r="F101" s="36"/>
     </row>
     <row r="103" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="342" t="s">
+      <c r="B103" s="338" t="s">
         <v>366</v>
       </c>
-      <c r="C103" s="342"/>
-      <c r="D103" s="342"/>
-      <c r="E103" s="342"/>
-      <c r="F103" s="342"/>
+      <c r="C103" s="338"/>
+      <c r="D103" s="338"/>
+      <c r="E103" s="338"/>
+      <c r="F103" s="338"/>
     </row>
     <row r="105" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
-      <c r="B105" s="267" t="s">
+      <c r="B105" s="266" t="s">
         <v>122</v>
       </c>
-      <c r="C105" s="267" t="s">
+      <c r="C105" s="266" t="s">
         <v>137</v>
       </c>
-      <c r="D105" s="267" t="s">
+      <c r="D105" s="266" t="s">
         <v>117</v>
       </c>
-      <c r="E105" s="267" t="s">
+      <c r="E105" s="266" t="s">
         <v>270</v>
       </c>
-      <c r="F105" s="267" t="s">
+      <c r="F105" s="266" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B106" s="262" t="str">
+      <c r="B106" s="261" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C106" s="263">
+      <c r="C106" s="262">
         <f>Valuation_Model!C74</f>
         <v>0.08</v>
       </c>
-      <c r="D106" s="264">
+      <c r="D106" s="263">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E106" s="265" t="str">
+      <c r="E106" s="264" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>2.56 HKD</v>
       </c>
-      <c r="F106" s="266">
+      <c r="F106" s="265">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B107" s="249" t="str">
+      <c r="B107" s="248" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C107" s="250">
+      <c r="C107" s="249">
         <f>Valuation_Model!C75</f>
         <v>0.06</v>
       </c>
-      <c r="D107" s="251">
+      <c r="D107" s="250">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E107" s="252" t="str">
+      <c r="E107" s="251" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>2.38 HKD</v>
       </c>
-      <c r="F107" s="253">
+      <c r="F107" s="252">
         <f>Valuation_Model!F75</f>
         <v>0.21249999999999999</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B108" s="249" t="str">
+      <c r="B108" s="248" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C108" s="250">
+      <c r="C108" s="249">
         <f>Valuation_Model!C76</f>
         <v>0.02</v>
       </c>
-      <c r="D108" s="251">
+      <c r="D108" s="250">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E108" s="252" t="str">
+      <c r="E108" s="251" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>2.29 HKD</v>
       </c>
-      <c r="F108" s="253">
+      <c r="F108" s="252">
         <f>Valuation_Model!F76</f>
         <v>0.51</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B109" s="249" t="str">
+      <c r="B109" s="248" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C109" s="250">
+      <c r="C109" s="249">
         <f>Valuation_Model!C77</f>
         <v>-0.06</v>
       </c>
-      <c r="D109" s="251">
+      <c r="D109" s="250">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E109" s="252" t="str">
+      <c r="E109" s="251" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>2.16 HKD</v>
       </c>
-      <c r="F109" s="253">
+      <c r="F109" s="252">
         <f>Valuation_Model!F77</f>
         <v>0.1275</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B110" s="249" t="str">
+      <c r="B110" s="248" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C110" s="250">
+      <c r="C110" s="249">
         <f>Valuation_Model!C78</f>
         <v>-0.06</v>
       </c>
-      <c r="D110" s="251">
+      <c r="D110" s="250">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E110" s="252" t="str">
+      <c r="E110" s="251" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>2.12 HKD</v>
       </c>
-      <c r="F110" s="253">
+      <c r="F110" s="252">
         <f>Valuation_Model!F78</f>
         <v>0.1</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B112" s="242" t="s">
+      <c r="B112" s="241" t="s">
         <v>269</v>
       </c>
-      <c r="C112" s="248">
+      <c r="C112" s="247">
         <f>Scenarios!C60</f>
-        <v>2.2895715355423079</v>
-      </c>
-      <c r="D112" s="243" t="str">
+        <v>2.2895715355423083</v>
+      </c>
+      <c r="D112" s="242" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B114" s="345" t="s">
+      <c r="B114" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C114" s="345"/>
-      <c r="D114" s="345"/>
-      <c r="E114" s="345"/>
-      <c r="F114" s="345"/>
+      <c r="C114" s="343"/>
+      <c r="D114" s="343"/>
+      <c r="E114" s="343"/>
+      <c r="F114" s="343"/>
     </row>
     <row r="116" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A116" s="254" t="s">
+      <c r="A116" s="253" t="s">
         <v>299</v>
       </c>
       <c r="B116" s="36"/>
@@ -4673,7 +4669,7 @@
       <c r="F118" s="341"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="241" t="s">
+      <c r="B119" s="240" t="s">
         <v>237</v>
       </c>
     </row>
@@ -4681,7 +4677,7 @@
       <c r="B120" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="C120" s="258">
+      <c r="C120" s="257">
         <f>E20</f>
         <v>3</v>
       </c>
@@ -4690,56 +4686,56 @@
       <c r="B121" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C121" s="257">
+      <c r="C121" s="256">
         <f>C19</f>
         <v>0.2</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B122" s="243" t="s">
+      <c r="B122" s="242" t="s">
         <v>272</v>
       </c>
-      <c r="C122" s="244">
+      <c r="C122" s="243">
         <f>Scenarios!C77</f>
         <v>0.1178</v>
       </c>
-      <c r="D122" s="243" t="str">
+      <c r="D122" s="242" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B124" s="241" t="s">
+      <c r="B124" s="240" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B125" s="243" t="str">
+      <c r="B125" s="242" t="str">
         <f>"PV("&amp;C120&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C125" s="247">
+      <c r="C125" s="246">
         <f>Scenarios!C81</f>
         <v>0.24814351851851849</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B126" s="243" t="str">
+      <c r="B126" s="242" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C120&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C126" s="247">
+      <c r="C126" s="246">
         <f>Scenarios!C82</f>
-        <v>1.3249835275129096</v>
+        <v>1.3249835275129098</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B127" s="82" t="s">
         <v>271</v>
       </c>
-      <c r="C127" s="246">
+      <c r="C127" s="245">
         <f>Scenarios!C83</f>
-        <v>1.5731270460314282</v>
+        <v>1.5731270460314284</v>
       </c>
       <c r="D127" s="47" t="str">
         <f>Reporting_currency</f>
@@ -4747,22 +4743,16 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B128" s="245" t="s">
+      <c r="B128" s="244" t="s">
         <v>273</v>
       </c>
-      <c r="C128" s="158">
+      <c r="C128" s="94">
         <f>Scenarios!F83</f>
-        <v>-0.31291640308638913</v>
+        <v>0.31291640308638913</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B97:F97"/>
@@ -4778,6 +4768,12 @@
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -4887,273 +4883,273 @@
       <c r="B4" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="194">
+      <c r="C4" s="193">
         <v>1615585</v>
       </c>
-      <c r="D4" s="185">
+      <c r="D4" s="184">
         <v>1446638</v>
       </c>
-      <c r="E4" s="185">
+      <c r="E4" s="184">
         <v>1769157</v>
       </c>
-      <c r="F4" s="185">
+      <c r="F4" s="184">
         <v>1702154</v>
       </c>
-      <c r="G4" s="185">
+      <c r="G4" s="184">
         <v>1383402</v>
       </c>
-      <c r="H4" s="185"/>
-      <c r="I4" s="185"/>
-      <c r="J4" s="185"/>
-      <c r="K4" s="185"/>
-      <c r="L4" s="185"/>
-      <c r="M4" s="185"/>
+      <c r="H4" s="184"/>
+      <c r="I4" s="184"/>
+      <c r="J4" s="184"/>
+      <c r="K4" s="184"/>
+      <c r="L4" s="184"/>
+      <c r="M4" s="184"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="194">
+      <c r="C5" s="193">
         <v>897327</v>
       </c>
-      <c r="D5" s="185">
+      <c r="D5" s="184">
         <v>845264</v>
       </c>
-      <c r="E5" s="185">
+      <c r="E5" s="184">
         <v>981731</v>
       </c>
-      <c r="F5" s="185">
+      <c r="F5" s="184">
         <v>959572</v>
       </c>
-      <c r="G5" s="185">
+      <c r="G5" s="184">
         <v>783542</v>
       </c>
-      <c r="H5" s="185"/>
-      <c r="I5" s="185"/>
-      <c r="J5" s="185"/>
-      <c r="K5" s="185"/>
-      <c r="L5" s="185"/>
-      <c r="M5" s="185"/>
+      <c r="H5" s="184"/>
+      <c r="I5" s="184"/>
+      <c r="J5" s="184"/>
+      <c r="K5" s="184"/>
+      <c r="L5" s="184"/>
+      <c r="M5" s="184"/>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B6" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="194">
+      <c r="C6" s="193">
         <v>613104</v>
       </c>
-      <c r="D6" s="185">
+      <c r="D6" s="184">
         <v>599182</v>
       </c>
-      <c r="E6" s="185">
+      <c r="E6" s="184">
         <v>705390</v>
       </c>
-      <c r="F6" s="185">
+      <c r="F6" s="184">
         <v>456610</v>
       </c>
-      <c r="G6" s="185">
+      <c r="G6" s="184">
         <v>396643</v>
       </c>
-      <c r="H6" s="185"/>
-      <c r="I6" s="185"/>
-      <c r="J6" s="185"/>
-      <c r="K6" s="185"/>
-      <c r="L6" s="185"/>
-      <c r="M6" s="185"/>
+      <c r="H6" s="184"/>
+      <c r="I6" s="184"/>
+      <c r="J6" s="184"/>
+      <c r="K6" s="184"/>
+      <c r="L6" s="184"/>
+      <c r="M6" s="184"/>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B7" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="195">
+      <c r="C7" s="194">
         <v>425033</v>
       </c>
-      <c r="D7" s="193">
+      <c r="D7" s="192">
         <v>435254</v>
       </c>
-      <c r="E7" s="193"/>
-      <c r="F7" s="193"/>
-      <c r="G7" s="193"/>
-      <c r="H7" s="193"/>
-      <c r="I7" s="193"/>
-      <c r="J7" s="193"/>
-      <c r="K7" s="193"/>
-      <c r="L7" s="193"/>
-      <c r="M7" s="193"/>
+      <c r="E7" s="192"/>
+      <c r="F7" s="192"/>
+      <c r="G7" s="192"/>
+      <c r="H7" s="192"/>
+      <c r="I7" s="192"/>
+      <c r="J7" s="192"/>
+      <c r="K7" s="192"/>
+      <c r="L7" s="192"/>
+      <c r="M7" s="192"/>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B8" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="194"/>
-      <c r="D8" s="185"/>
-      <c r="E8" s="185"/>
-      <c r="F8" s="185"/>
-      <c r="G8" s="185"/>
-      <c r="H8" s="185"/>
-      <c r="I8" s="185"/>
-      <c r="J8" s="185"/>
-      <c r="K8" s="185"/>
-      <c r="L8" s="185"/>
-      <c r="M8" s="185"/>
+      <c r="C8" s="193"/>
+      <c r="D8" s="184"/>
+      <c r="E8" s="184"/>
+      <c r="F8" s="184"/>
+      <c r="G8" s="184"/>
+      <c r="H8" s="184"/>
+      <c r="I8" s="184"/>
+      <c r="J8" s="184"/>
+      <c r="K8" s="184"/>
+      <c r="L8" s="184"/>
+      <c r="M8" s="184"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B9" s="40" t="s">
         <v>164</v>
       </c>
-      <c r="C9" s="194"/>
-      <c r="D9" s="185"/>
-      <c r="E9" s="185"/>
-      <c r="F9" s="185"/>
-      <c r="G9" s="185"/>
-      <c r="H9" s="185"/>
-      <c r="I9" s="185"/>
-      <c r="J9" s="185"/>
-      <c r="K9" s="185"/>
-      <c r="L9" s="185"/>
-      <c r="M9" s="185"/>
+      <c r="C9" s="193"/>
+      <c r="D9" s="184"/>
+      <c r="E9" s="184"/>
+      <c r="F9" s="184"/>
+      <c r="G9" s="184"/>
+      <c r="H9" s="184"/>
+      <c r="I9" s="184"/>
+      <c r="J9" s="184"/>
+      <c r="K9" s="184"/>
+      <c r="L9" s="184"/>
+      <c r="M9" s="184"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B10" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="C10" s="194"/>
-      <c r="D10" s="185"/>
-      <c r="E10" s="185"/>
-      <c r="F10" s="185"/>
-      <c r="G10" s="185"/>
-      <c r="H10" s="185"/>
-      <c r="I10" s="185"/>
-      <c r="J10" s="185"/>
-      <c r="K10" s="185"/>
-      <c r="L10" s="185"/>
-      <c r="M10" s="185"/>
+      <c r="C10" s="193"/>
+      <c r="D10" s="184"/>
+      <c r="E10" s="184"/>
+      <c r="F10" s="184"/>
+      <c r="G10" s="184"/>
+      <c r="H10" s="184"/>
+      <c r="I10" s="184"/>
+      <c r="J10" s="184"/>
+      <c r="K10" s="184"/>
+      <c r="L10" s="184"/>
+      <c r="M10" s="184"/>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="C11" s="194"/>
-      <c r="D11" s="185"/>
-      <c r="E11" s="185"/>
-      <c r="F11" s="185"/>
-      <c r="G11" s="185"/>
-      <c r="H11" s="185"/>
-      <c r="I11" s="185"/>
-      <c r="J11" s="185"/>
-      <c r="K11" s="185"/>
-      <c r="L11" s="185"/>
-      <c r="M11" s="185"/>
+      <c r="C11" s="193"/>
+      <c r="D11" s="184"/>
+      <c r="E11" s="184"/>
+      <c r="F11" s="184"/>
+      <c r="G11" s="184"/>
+      <c r="H11" s="184"/>
+      <c r="I11" s="184"/>
+      <c r="J11" s="184"/>
+      <c r="K11" s="184"/>
+      <c r="L11" s="184"/>
+      <c r="M11" s="184"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B12" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="194">
+      <c r="C12" s="193">
         <v>1003</v>
       </c>
-      <c r="D12" s="185">
+      <c r="D12" s="184">
         <v>863</v>
       </c>
-      <c r="E12" s="185">
+      <c r="E12" s="184">
         <v>1613</v>
       </c>
-      <c r="F12" s="185">
+      <c r="F12" s="184">
         <v>2645</v>
       </c>
-      <c r="G12" s="185">
+      <c r="G12" s="184">
         <v>299</v>
       </c>
-      <c r="H12" s="185"/>
-      <c r="I12" s="185"/>
-      <c r="J12" s="185"/>
-      <c r="K12" s="185"/>
-      <c r="L12" s="185"/>
-      <c r="M12" s="185"/>
+      <c r="H12" s="184"/>
+      <c r="I12" s="184"/>
+      <c r="J12" s="184"/>
+      <c r="K12" s="184"/>
+      <c r="L12" s="184"/>
+      <c r="M12" s="184"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B13" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="194">
+      <c r="C13" s="193">
         <v>73805</v>
       </c>
-      <c r="D13" s="185">
+      <c r="D13" s="184">
         <v>45350</v>
       </c>
-      <c r="E13" s="185"/>
-      <c r="F13" s="185"/>
-      <c r="G13" s="185"/>
-      <c r="H13" s="185"/>
-      <c r="I13" s="185"/>
-      <c r="J13" s="185"/>
-      <c r="K13" s="185"/>
-      <c r="L13" s="185"/>
-      <c r="M13" s="185"/>
+      <c r="E13" s="184"/>
+      <c r="F13" s="184"/>
+      <c r="G13" s="184"/>
+      <c r="H13" s="184"/>
+      <c r="I13" s="184"/>
+      <c r="J13" s="184"/>
+      <c r="K13" s="184"/>
+      <c r="L13" s="184"/>
+      <c r="M13" s="184"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B14" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="194">
+      <c r="C14" s="193">
         <v>44449</v>
       </c>
-      <c r="D14" s="185">
+      <c r="D14" s="184">
         <v>21017</v>
       </c>
-      <c r="E14" s="185"/>
-      <c r="F14" s="185"/>
-      <c r="G14" s="185"/>
-      <c r="H14" s="185"/>
-      <c r="I14" s="185"/>
-      <c r="J14" s="185"/>
-      <c r="K14" s="185"/>
-      <c r="L14" s="185"/>
-      <c r="M14" s="185"/>
+      <c r="E14" s="184"/>
+      <c r="F14" s="184"/>
+      <c r="G14" s="184"/>
+      <c r="H14" s="184"/>
+      <c r="I14" s="184"/>
+      <c r="J14" s="184"/>
+      <c r="K14" s="184"/>
+      <c r="L14" s="184"/>
+      <c r="M14" s="184"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B15" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="196">
+      <c r="C15" s="195">
         <v>172817</v>
       </c>
-      <c r="D15" s="186">
+      <c r="D15" s="185">
         <v>65456</v>
       </c>
-      <c r="E15" s="186">
+      <c r="E15" s="185">
         <v>5735.3965490000001</v>
       </c>
-      <c r="F15" s="186">
+      <c r="F15" s="185">
         <v>9646.0369900000005</v>
       </c>
-      <c r="G15" s="186"/>
-      <c r="H15" s="186"/>
-      <c r="I15" s="186"/>
-      <c r="J15" s="186"/>
-      <c r="K15" s="186"/>
-      <c r="L15" s="186"/>
-      <c r="M15" s="186"/>
+      <c r="G15" s="185"/>
+      <c r="H15" s="185"/>
+      <c r="I15" s="185"/>
+      <c r="J15" s="185"/>
+      <c r="K15" s="185"/>
+      <c r="L15" s="185"/>
+      <c r="M15" s="185"/>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B16" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="194">
+      <c r="C16" s="193">
         <v>2199</v>
       </c>
-      <c r="D16" s="185">
+      <c r="D16" s="184">
         <v>645</v>
       </c>
-      <c r="E16" s="185"/>
-      <c r="F16" s="185"/>
-      <c r="G16" s="185"/>
-      <c r="H16" s="185"/>
-      <c r="I16" s="185"/>
-      <c r="J16" s="185"/>
-      <c r="K16" s="185"/>
-      <c r="L16" s="185"/>
-      <c r="M16" s="185"/>
+      <c r="E16" s="184"/>
+      <c r="F16" s="184"/>
+      <c r="G16" s="184"/>
+      <c r="H16" s="184"/>
+      <c r="I16" s="184"/>
+      <c r="J16" s="184"/>
+      <c r="K16" s="184"/>
+      <c r="L16" s="184"/>
+      <c r="M16" s="184"/>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B18" s="16" t="s">
@@ -5165,65 +5161,65 @@
       <c r="B19" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="185">
+      <c r="C19" s="184">
         <v>35974</v>
       </c>
-      <c r="D19" s="185">
+      <c r="D19" s="184">
         <v>32106</v>
       </c>
-      <c r="E19" s="185">
+      <c r="E19" s="184">
         <v>181.018</v>
       </c>
-      <c r="F19" s="185">
+      <c r="F19" s="184">
         <v>186.14699999999999</v>
       </c>
-      <c r="G19" s="185"/>
-      <c r="H19" s="185"/>
-      <c r="I19" s="185"/>
-      <c r="J19" s="185"/>
-      <c r="K19" s="185"/>
-      <c r="L19" s="185"/>
-      <c r="M19" s="185"/>
+      <c r="G19" s="184"/>
+      <c r="H19" s="184"/>
+      <c r="I19" s="184"/>
+      <c r="J19" s="184"/>
+      <c r="K19" s="184"/>
+      <c r="L19" s="184"/>
+      <c r="M19" s="184"/>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B20" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="185">
+      <c r="C20" s="184">
         <v>15312</v>
       </c>
-      <c r="D20" s="185">
+      <c r="D20" s="184">
         <v>11600</v>
       </c>
-      <c r="E20" s="185"/>
-      <c r="F20" s="185"/>
-      <c r="G20" s="185"/>
-      <c r="H20" s="185"/>
-      <c r="I20" s="185"/>
-      <c r="J20" s="185"/>
-      <c r="K20" s="185"/>
-      <c r="L20" s="185"/>
-      <c r="M20" s="185"/>
+      <c r="E20" s="184"/>
+      <c r="F20" s="184"/>
+      <c r="G20" s="184"/>
+      <c r="H20" s="184"/>
+      <c r="I20" s="184"/>
+      <c r="J20" s="184"/>
+      <c r="K20" s="184"/>
+      <c r="L20" s="184"/>
+      <c r="M20" s="184"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B21" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="185">
+      <c r="C21" s="184">
         <v>-169280</v>
       </c>
-      <c r="D21" s="185">
+      <c r="D21" s="184">
         <v>-50846</v>
       </c>
-      <c r="E21" s="185"/>
-      <c r="F21" s="185"/>
-      <c r="G21" s="185"/>
-      <c r="H21" s="185"/>
-      <c r="I21" s="185"/>
-      <c r="J21" s="185"/>
-      <c r="K21" s="185"/>
-      <c r="L21" s="185"/>
-      <c r="M21" s="185"/>
+      <c r="E21" s="184"/>
+      <c r="F21" s="184"/>
+      <c r="G21" s="184"/>
+      <c r="H21" s="184"/>
+      <c r="I21" s="184"/>
+      <c r="J21" s="184"/>
+      <c r="K21" s="184"/>
+      <c r="L21" s="184"/>
+      <c r="M21" s="184"/>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="24" t="str">
@@ -5254,101 +5250,101 @@
       <c r="B25" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="187"/>
-      <c r="D25" s="185"/>
-      <c r="E25" s="185"/>
-      <c r="F25" s="185"/>
-      <c r="G25" s="185"/>
-      <c r="H25" s="185"/>
-      <c r="I25" s="185"/>
-      <c r="J25" s="185"/>
-      <c r="K25" s="185"/>
-      <c r="L25" s="185"/>
-      <c r="M25" s="185"/>
+      <c r="C25" s="186"/>
+      <c r="D25" s="184"/>
+      <c r="E25" s="184"/>
+      <c r="F25" s="184"/>
+      <c r="G25" s="184"/>
+      <c r="H25" s="184"/>
+      <c r="I25" s="184"/>
+      <c r="J25" s="184"/>
+      <c r="K25" s="184"/>
+      <c r="L25" s="184"/>
+      <c r="M25" s="184"/>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B26" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="187"/>
-      <c r="D26" s="185"/>
-      <c r="E26" s="185"/>
-      <c r="F26" s="185"/>
-      <c r="G26" s="185"/>
-      <c r="H26" s="185"/>
-      <c r="I26" s="185"/>
-      <c r="J26" s="185"/>
-      <c r="K26" s="185"/>
-      <c r="L26" s="185"/>
-      <c r="M26" s="185"/>
+      <c r="C26" s="186"/>
+      <c r="D26" s="184"/>
+      <c r="E26" s="184"/>
+      <c r="F26" s="184"/>
+      <c r="G26" s="184"/>
+      <c r="H26" s="184"/>
+      <c r="I26" s="184"/>
+      <c r="J26" s="184"/>
+      <c r="K26" s="184"/>
+      <c r="L26" s="184"/>
+      <c r="M26" s="184"/>
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B27" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="186">
+      <c r="C27" s="185">
         <v>642877</v>
       </c>
-      <c r="D27" s="186">
+      <c r="D27" s="185">
         <v>734909</v>
       </c>
-      <c r="E27" s="186">
+      <c r="E27" s="185">
         <v>677999</v>
       </c>
-      <c r="F27" s="186">
+      <c r="F27" s="185">
         <v>1352795</v>
       </c>
-      <c r="G27" s="186">
+      <c r="G27" s="185">
         <v>1205068</v>
       </c>
-      <c r="H27" s="186"/>
-      <c r="I27" s="186"/>
-      <c r="J27" s="186"/>
-      <c r="K27" s="186"/>
-      <c r="L27" s="186"/>
-      <c r="M27" s="186"/>
+      <c r="H27" s="185"/>
+      <c r="I27" s="185"/>
+      <c r="J27" s="185"/>
+      <c r="K27" s="185"/>
+      <c r="L27" s="185"/>
+      <c r="M27" s="185"/>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="186">
+      <c r="C28" s="185">
         <v>3027292</v>
       </c>
-      <c r="D28" s="186">
+      <c r="D28" s="185">
         <v>2824568</v>
       </c>
-      <c r="E28" s="186">
+      <c r="E28" s="185">
         <v>2735259</v>
       </c>
-      <c r="F28" s="186">
+      <c r="F28" s="185">
         <v>250534</v>
       </c>
-      <c r="G28" s="186">
+      <c r="G28" s="185">
         <v>13930</v>
       </c>
-      <c r="H28" s="186"/>
-      <c r="I28" s="186"/>
-      <c r="J28" s="186"/>
-      <c r="K28" s="186"/>
-      <c r="L28" s="186"/>
-      <c r="M28" s="186"/>
+      <c r="H28" s="185"/>
+      <c r="I28" s="185"/>
+      <c r="J28" s="185"/>
+      <c r="K28" s="185"/>
+      <c r="L28" s="185"/>
+      <c r="M28" s="185"/>
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B29" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="C29" s="185"/>
-      <c r="D29" s="185"/>
-      <c r="E29" s="185"/>
-      <c r="F29" s="185"/>
-      <c r="G29" s="186"/>
-      <c r="H29" s="186"/>
-      <c r="I29" s="186"/>
-      <c r="J29" s="186"/>
-      <c r="K29" s="186"/>
-      <c r="L29" s="186"/>
-      <c r="M29" s="186"/>
+      <c r="C29" s="184"/>
+      <c r="D29" s="184"/>
+      <c r="E29" s="184"/>
+      <c r="F29" s="184"/>
+      <c r="G29" s="185"/>
+      <c r="H29" s="185"/>
+      <c r="I29" s="185"/>
+      <c r="J29" s="185"/>
+      <c r="K29" s="185"/>
+      <c r="L29" s="185"/>
+      <c r="M29" s="185"/>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B31" s="16" t="s">
@@ -5360,17 +5356,17 @@
       <c r="B32" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="C32" s="185"/>
-      <c r="D32" s="185"/>
-      <c r="E32" s="185"/>
-      <c r="F32" s="185"/>
-      <c r="G32" s="185"/>
-      <c r="H32" s="185"/>
-      <c r="I32" s="185"/>
-      <c r="J32" s="185"/>
-      <c r="K32" s="185"/>
-      <c r="L32" s="185"/>
-      <c r="M32" s="185"/>
+      <c r="C32" s="184"/>
+      <c r="D32" s="184"/>
+      <c r="E32" s="184"/>
+      <c r="F32" s="184"/>
+      <c r="G32" s="184"/>
+      <c r="H32" s="184"/>
+      <c r="I32" s="184"/>
+      <c r="J32" s="184"/>
+      <c r="K32" s="184"/>
+      <c r="L32" s="184"/>
+      <c r="M32" s="184"/>
     </row>
     <row r="34" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B34" s="36" t="s">
@@ -5397,47 +5393,47 @@
       <c r="B36" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C36" s="187">
+      <c r="C36" s="186">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
         <v>1615585</v>
       </c>
-      <c r="D36" s="187">
+      <c r="D36" s="186">
         <f t="shared" si="1"/>
         <v>1446638</v>
       </c>
-      <c r="E36" s="187">
+      <c r="E36" s="186">
         <f t="shared" si="1"/>
         <v>1769157</v>
       </c>
-      <c r="F36" s="187">
+      <c r="F36" s="186">
         <f t="shared" si="1"/>
         <v>1702154</v>
       </c>
-      <c r="G36" s="187">
+      <c r="G36" s="186">
         <f t="shared" si="1"/>
         <v>1383402</v>
       </c>
-      <c r="H36" s="187" t="str">
+      <c r="H36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I36" s="187" t="str">
+      <c r="I36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J36" s="187" t="str">
+      <c r="J36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K36" s="187" t="str">
+      <c r="K36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="L36" s="187" t="str">
+      <c r="L36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="M36" s="187" t="str">
+      <c r="M36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -5446,47 +5442,47 @@
       <c r="B37" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="C37" s="187">
+      <c r="C37" s="186">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
         <v>-897327</v>
       </c>
-      <c r="D37" s="187">
+      <c r="D37" s="186">
         <f t="shared" si="2"/>
         <v>-845264</v>
       </c>
-      <c r="E37" s="187">
+      <c r="E37" s="186">
         <f t="shared" si="2"/>
         <v>-981731</v>
       </c>
-      <c r="F37" s="187">
+      <c r="F37" s="186">
         <f t="shared" si="2"/>
         <v>-959572</v>
       </c>
-      <c r="G37" s="187">
+      <c r="G37" s="186">
         <f t="shared" si="2"/>
         <v>-783542</v>
       </c>
-      <c r="H37" s="187" t="str">
+      <c r="H37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I37" s="187" t="str">
+      <c r="I37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J37" s="187" t="str">
+      <c r="J37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K37" s="187" t="str">
+      <c r="K37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L37" s="187" t="str">
+      <c r="L37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M37" s="187" t="str">
+      <c r="M37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -5495,47 +5491,47 @@
       <c r="B38" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="C38" s="188">
+      <c r="C38" s="187">
         <f>IF(C36="","",C36+C37)</f>
         <v>718258</v>
       </c>
-      <c r="D38" s="188">
+      <c r="D38" s="187">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
         <v>601374</v>
       </c>
-      <c r="E38" s="188">
+      <c r="E38" s="187">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
         <v>787426</v>
       </c>
-      <c r="F38" s="188">
+      <c r="F38" s="187">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
         <v>742582</v>
       </c>
-      <c r="G38" s="188">
+      <c r="G38" s="187">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
         <v>599860</v>
       </c>
-      <c r="H38" s="188" t="str">
+      <c r="H38" s="187" t="str">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
         <v/>
       </c>
-      <c r="I38" s="188" t="str">
+      <c r="I38" s="187" t="str">
         <f t="shared" ref="I38" si="8">IF(I36="","",I36+I37)</f>
         <v/>
       </c>
-      <c r="J38" s="188" t="str">
+      <c r="J38" s="187" t="str">
         <f t="shared" ref="J38" si="9">IF(J36="","",J36+J37)</f>
         <v/>
       </c>
-      <c r="K38" s="188" t="str">
+      <c r="K38" s="187" t="str">
         <f t="shared" ref="K38" si="10">IF(K36="","",K36+K37)</f>
         <v/>
       </c>
-      <c r="L38" s="188" t="str">
+      <c r="L38" s="187" t="str">
         <f t="shared" ref="L38" si="11">IF(L36="","",L36+L37)</f>
         <v/>
       </c>
-      <c r="M38" s="188" t="str">
+      <c r="M38" s="187" t="str">
         <f t="shared" ref="M38" si="12">IF(M36="","",M36+M37)</f>
         <v/>
       </c>
@@ -5544,47 +5540,47 @@
       <c r="B39" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="C39" s="187">
+      <c r="C39" s="186">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
         <v>-613104</v>
       </c>
-      <c r="D39" s="187">
+      <c r="D39" s="186">
         <f t="shared" si="13"/>
         <v>-599182</v>
       </c>
-      <c r="E39" s="187">
+      <c r="E39" s="186">
         <f t="shared" si="13"/>
         <v>-705390</v>
       </c>
-      <c r="F39" s="187">
+      <c r="F39" s="186">
         <f t="shared" si="13"/>
         <v>-456610</v>
       </c>
-      <c r="G39" s="187">
+      <c r="G39" s="186">
         <f t="shared" si="13"/>
         <v>-396643</v>
       </c>
-      <c r="H39" s="187" t="str">
+      <c r="H39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="I39" s="187" t="str">
+      <c r="I39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="J39" s="187" t="str">
+      <c r="J39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="K39" s="187" t="str">
+      <c r="K39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="L39" s="187" t="str">
+      <c r="L39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="M39" s="187" t="str">
+      <c r="M39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -5593,47 +5589,47 @@
       <c r="B40" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="C40" s="189">
+      <c r="C40" s="188">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
         <v>-425033</v>
       </c>
-      <c r="D40" s="189">
+      <c r="D40" s="188">
         <f t="shared" si="14"/>
         <v>-435254</v>
       </c>
-      <c r="E40" s="189">
+      <c r="E40" s="188">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="F40" s="189">
+      <c r="F40" s="188">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G40" s="189">
+      <c r="G40" s="188">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H40" s="189" t="str">
+      <c r="H40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="I40" s="189" t="str">
+      <c r="I40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="J40" s="189" t="str">
+      <c r="J40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="K40" s="189" t="str">
+      <c r="K40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L40" s="189" t="str">
+      <c r="L40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="M40" s="189" t="str">
+      <c r="M40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -5642,47 +5638,47 @@
       <c r="B41" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="C41" s="189">
+      <c r="C41" s="188">
         <f>IF(C$4="","",C39-C40)</f>
         <v>-188071</v>
       </c>
-      <c r="D41" s="189">
+      <c r="D41" s="188">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
         <v>-163928</v>
       </c>
-      <c r="E41" s="189">
+      <c r="E41" s="188">
         <f t="shared" si="15"/>
         <v>-705390</v>
       </c>
-      <c r="F41" s="189">
+      <c r="F41" s="188">
         <f t="shared" si="15"/>
         <v>-456610</v>
       </c>
-      <c r="G41" s="189">
+      <c r="G41" s="188">
         <f t="shared" si="15"/>
         <v>-396643</v>
       </c>
-      <c r="H41" s="189" t="str">
+      <c r="H41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I41" s="189" t="str">
+      <c r="I41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J41" s="189" t="str">
+      <c r="J41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K41" s="189" t="str">
+      <c r="K41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="L41" s="189" t="str">
+      <c r="L41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="M41" s="189" t="str">
+      <c r="M41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -5691,47 +5687,47 @@
       <c r="B42" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="C42" s="187">
+      <c r="C42" s="186">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
         <v>0</v>
       </c>
-      <c r="D42" s="187">
+      <c r="D42" s="186">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="E42" s="187">
+      <c r="E42" s="186">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F42" s="187">
+      <c r="F42" s="186">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="G42" s="187">
+      <c r="G42" s="186">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H42" s="187" t="str">
+      <c r="H42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="I42" s="187" t="str">
+      <c r="I42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="J42" s="187" t="str">
+      <c r="J42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="K42" s="187" t="str">
+      <c r="K42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="L42" s="187" t="str">
+      <c r="L42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="M42" s="187" t="str">
+      <c r="M42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
@@ -5740,47 +5736,47 @@
       <c r="B43" s="43" t="s">
         <v>157</v>
       </c>
-      <c r="C43" s="190">
+      <c r="C43" s="189">
         <f>IF(C$4="","",C38+C39+C42)</f>
         <v>105154</v>
       </c>
-      <c r="D43" s="190">
+      <c r="D43" s="189">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
         <v>2192</v>
       </c>
-      <c r="E43" s="190">
+      <c r="E43" s="189">
         <f t="shared" si="17"/>
         <v>82036</v>
       </c>
-      <c r="F43" s="190">
+      <c r="F43" s="189">
         <f t="shared" si="17"/>
         <v>285972</v>
       </c>
-      <c r="G43" s="190">
+      <c r="G43" s="189">
         <f t="shared" si="17"/>
         <v>203217</v>
       </c>
-      <c r="H43" s="190" t="str">
+      <c r="H43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="I43" s="190" t="str">
+      <c r="I43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="J43" s="190" t="str">
+      <c r="J43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="K43" s="190" t="str">
+      <c r="K43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="L43" s="190" t="str">
+      <c r="L43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="M43" s="190" t="str">
+      <c r="M43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -5789,47 +5785,47 @@
       <c r="B44" s="43" t="s">
         <v>173</v>
       </c>
-      <c r="C44" s="191">
+      <c r="C44" s="190">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
         <v>39310</v>
       </c>
-      <c r="D44" s="191">
+      <c r="D44" s="190">
         <f t="shared" si="18"/>
         <v>39794</v>
       </c>
-      <c r="E44" s="191">
+      <c r="E44" s="190">
         <f t="shared" si="18"/>
         <v>-74687.603451000003</v>
       </c>
-      <c r="F44" s="191">
+      <c r="F44" s="190">
         <f t="shared" si="18"/>
         <v>-273680.96301000001</v>
       </c>
-      <c r="G44" s="191">
+      <c r="G44" s="190">
         <f t="shared" si="18"/>
         <v>-202918</v>
       </c>
-      <c r="H44" s="191" t="str">
+      <c r="H44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="I44" s="191" t="str">
+      <c r="I44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="J44" s="191" t="str">
+      <c r="J44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="K44" s="191" t="str">
+      <c r="K44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L44" s="191" t="str">
+      <c r="L44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="M44" s="191" t="str">
+      <c r="M44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
@@ -5838,47 +5834,47 @@
       <c r="B45" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="C45" s="192">
+      <c r="C45" s="191">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
         <v>72802</v>
       </c>
-      <c r="D45" s="192">
+      <c r="D45" s="191">
         <f t="shared" si="19"/>
         <v>44487</v>
       </c>
-      <c r="E45" s="192">
+      <c r="E45" s="191">
         <f t="shared" si="19"/>
         <v>-1613</v>
       </c>
-      <c r="F45" s="192">
+      <c r="F45" s="191">
         <f t="shared" si="19"/>
         <v>-2645</v>
       </c>
-      <c r="G45" s="192">
+      <c r="G45" s="191">
         <f t="shared" si="19"/>
         <v>-299</v>
       </c>
-      <c r="H45" s="192" t="str">
+      <c r="H45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I45" s="192" t="str">
+      <c r="I45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J45" s="192" t="str">
+      <c r="J45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="K45" s="192" t="str">
+      <c r="K45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="L45" s="192" t="str">
+      <c r="L45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="M45" s="192" t="str">
+      <c r="M45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
@@ -5887,47 +5883,47 @@
       <c r="B46" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="C46" s="187">
+      <c r="C46" s="186">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
         <v>-44449</v>
       </c>
-      <c r="D46" s="187">
+      <c r="D46" s="186">
         <f t="shared" si="20"/>
         <v>-21017</v>
       </c>
-      <c r="E46" s="187">
+      <c r="E46" s="186">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="F46" s="187">
+      <c r="F46" s="186">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="G46" s="187">
+      <c r="G46" s="186">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="H46" s="187" t="str">
+      <c r="H46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="I46" s="187" t="str">
+      <c r="I46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="J46" s="187" t="str">
+      <c r="J46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="K46" s="187" t="str">
+      <c r="K46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="L46" s="187" t="str">
+      <c r="L46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="M46" s="187" t="str">
+      <c r="M46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -5936,47 +5932,47 @@
       <c r="B47" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="190">
+      <c r="C47" s="189">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
         <v>172817</v>
       </c>
-      <c r="D47" s="190">
+      <c r="D47" s="189">
         <f t="shared" si="21"/>
         <v>65456</v>
       </c>
-      <c r="E47" s="190">
+      <c r="E47" s="189">
         <f t="shared" si="21"/>
         <v>5735.3965490000001</v>
       </c>
-      <c r="F47" s="190">
+      <c r="F47" s="189">
         <f t="shared" si="21"/>
         <v>9646.0369900000005</v>
       </c>
-      <c r="G47" s="190">
+      <c r="G47" s="189">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="H47" s="190" t="str">
+      <c r="H47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="I47" s="190" t="str">
+      <c r="I47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="J47" s="190" t="str">
+      <c r="J47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="K47" s="190" t="str">
+      <c r="K47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="L47" s="190" t="str">
+      <c r="L47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="M47" s="190" t="str">
+      <c r="M47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -5985,47 +5981,47 @@
       <c r="B48" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="C48" s="187">
+      <c r="C48" s="186">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
         <v>-2199</v>
       </c>
-      <c r="D48" s="187">
+      <c r="D48" s="186">
         <f t="shared" si="22"/>
         <v>-645</v>
       </c>
-      <c r="E48" s="187">
+      <c r="E48" s="186">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F48" s="187">
+      <c r="F48" s="186">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="G48" s="187">
+      <c r="G48" s="186">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="H48" s="187" t="str">
+      <c r="H48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="I48" s="187" t="str">
+      <c r="I48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="J48" s="187" t="str">
+      <c r="J48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="K48" s="187" t="str">
+      <c r="K48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L48" s="187" t="str">
+      <c r="L48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="M48" s="187" t="str">
+      <c r="M48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -6039,47 +6035,47 @@
       <c r="B51" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="C51" s="187">
+      <c r="C51" s="186">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
         <v>-1003</v>
       </c>
-      <c r="D51" s="187">
+      <c r="D51" s="186">
         <f t="shared" si="23"/>
         <v>-863</v>
       </c>
-      <c r="E51" s="187">
+      <c r="E51" s="186">
         <f t="shared" si="23"/>
         <v>-1613</v>
       </c>
-      <c r="F51" s="187">
+      <c r="F51" s="186">
         <f t="shared" si="23"/>
         <v>-2645</v>
       </c>
-      <c r="G51" s="187">
+      <c r="G51" s="186">
         <f t="shared" si="23"/>
         <v>-299</v>
       </c>
-      <c r="H51" s="187" t="str">
+      <c r="H51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="I51" s="187" t="str">
+      <c r="I51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="J51" s="187" t="str">
+      <c r="J51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="K51" s="187" t="str">
+      <c r="K51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="L51" s="187" t="str">
+      <c r="L51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="M51" s="187" t="str">
+      <c r="M51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -6088,53 +6084,53 @@
       <c r="B52" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="C52" s="187">
+      <c r="C52" s="186">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
         <v>73805</v>
       </c>
-      <c r="D52" s="187">
+      <c r="D52" s="186">
         <f t="shared" si="24"/>
         <v>45350</v>
       </c>
-      <c r="E52" s="187">
+      <c r="E52" s="186">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="F52" s="187">
+      <c r="F52" s="186">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="G52" s="187">
+      <c r="G52" s="186">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="H52" s="187" t="str">
+      <c r="H52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="I52" s="187" t="str">
+      <c r="I52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="J52" s="187" t="str">
+      <c r="J52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="K52" s="187" t="str">
+      <c r="K52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="L52" s="187" t="str">
+      <c r="L52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="M52" s="187" t="str">
+      <c r="M52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B54" s="179" t="s">
+      <c r="B54" s="178" t="s">
         <v>173</v>
       </c>
     </row>
@@ -6142,47 +6138,47 @@
       <c r="B55" s="40" t="s">
         <v>164</v>
       </c>
-      <c r="C55" s="192">
+      <c r="C55" s="191">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
         <v>0</v>
       </c>
-      <c r="D55" s="192">
+      <c r="D55" s="191">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="E55" s="192">
+      <c r="E55" s="191">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="F55" s="192">
+      <c r="F55" s="191">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="G55" s="192">
+      <c r="G55" s="191">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="H55" s="192" t="str">
+      <c r="H55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="I55" s="192" t="str">
+      <c r="I55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="J55" s="192" t="str">
+      <c r="J55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="K55" s="192" t="str">
+      <c r="K55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="L55" s="192" t="str">
+      <c r="L55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="M55" s="192" t="str">
+      <c r="M55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
@@ -6191,47 +6187,47 @@
       <c r="B56" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="C56" s="192">
+      <c r="C56" s="191">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
         <v>0</v>
       </c>
-      <c r="D56" s="192">
+      <c r="D56" s="191">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E56" s="192">
+      <c r="E56" s="191">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="F56" s="192">
+      <c r="F56" s="191">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="G56" s="192">
+      <c r="G56" s="191">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="H56" s="192" t="str">
+      <c r="H56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="I56" s="192" t="str">
+      <c r="I56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="J56" s="192" t="str">
+      <c r="J56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="K56" s="192" t="str">
+      <c r="K56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="L56" s="192" t="str">
+      <c r="L56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="M56" s="192" t="str">
+      <c r="M56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
@@ -6240,47 +6236,47 @@
       <c r="B57" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="C57" s="192">
+      <c r="C57" s="191">
         <f>IF(C$4="","",C11)</f>
         <v>0</v>
       </c>
-      <c r="D57" s="192">
+      <c r="D57" s="191">
         <f t="shared" ref="D57:M57" si="27">IF(D$4="","",D11)</f>
         <v>0</v>
       </c>
-      <c r="E57" s="192">
+      <c r="E57" s="191">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="F57" s="192">
+      <c r="F57" s="191">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="G57" s="192">
+      <c r="G57" s="191">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="H57" s="192" t="str">
+      <c r="H57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="I57" s="192" t="str">
+      <c r="I57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="J57" s="192" t="str">
+      <c r="J57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="K57" s="192" t="str">
+      <c r="K57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="L57" s="192" t="str">
+      <c r="L57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="M57" s="192" t="str">
+      <c r="M57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -6289,47 +6285,47 @@
       <c r="B58" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="C58" s="192">
+      <c r="C58" s="191">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
         <v>39310</v>
       </c>
-      <c r="D58" s="192">
+      <c r="D58" s="191">
         <f t="shared" ref="D58:M58" si="28">IF(D$4="","",D44-D55-D56-D57)</f>
         <v>39794</v>
       </c>
-      <c r="E58" s="192">
+      <c r="E58" s="191">
         <f t="shared" si="28"/>
         <v>-74687.603451000003</v>
       </c>
-      <c r="F58" s="192">
+      <c r="F58" s="191">
         <f t="shared" si="28"/>
         <v>-273680.96301000001</v>
       </c>
-      <c r="G58" s="192">
+      <c r="G58" s="191">
         <f t="shared" si="28"/>
         <v>-202918</v>
       </c>
-      <c r="H58" s="192" t="str">
+      <c r="H58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="I58" s="192" t="str">
+      <c r="I58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="J58" s="192" t="str">
+      <c r="J58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="K58" s="192" t="str">
+      <c r="K58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="L58" s="192" t="str">
+      <c r="L58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="M58" s="192" t="str">
+      <c r="M58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
@@ -6344,47 +6340,47 @@
       <c r="B61" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="C61" s="187">
+      <c r="C61" s="186">
         <f t="shared" ref="C61:M61" si="29">IF(C$4="","",-C19)</f>
         <v>-35974</v>
       </c>
-      <c r="D61" s="187">
+      <c r="D61" s="186">
         <f t="shared" si="29"/>
         <v>-32106</v>
       </c>
-      <c r="E61" s="187">
+      <c r="E61" s="186">
         <f t="shared" si="29"/>
         <v>-181.018</v>
       </c>
-      <c r="F61" s="187">
+      <c r="F61" s="186">
         <f t="shared" si="29"/>
         <v>-186.14699999999999</v>
       </c>
-      <c r="G61" s="187">
+      <c r="G61" s="186">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="H61" s="187" t="str">
+      <c r="H61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="I61" s="187" t="str">
+      <c r="I61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="J61" s="187" t="str">
+      <c r="J61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="K61" s="187" t="str">
+      <c r="K61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="L61" s="187" t="str">
+      <c r="L61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="M61" s="187" t="str">
+      <c r="M61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
@@ -6393,47 +6389,47 @@
       <c r="B62" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="C62" s="187">
+      <c r="C62" s="186">
         <f t="shared" ref="C62:M62" si="30">IF(C$4="","",-C20)</f>
         <v>-15312</v>
       </c>
-      <c r="D62" s="187">
+      <c r="D62" s="186">
         <f t="shared" si="30"/>
         <v>-11600</v>
       </c>
-      <c r="E62" s="187">
+      <c r="E62" s="186">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="F62" s="187">
+      <c r="F62" s="186">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="G62" s="187">
+      <c r="G62" s="186">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="H62" s="187" t="str">
+      <c r="H62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="I62" s="187" t="str">
+      <c r="I62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="J62" s="187" t="str">
+      <c r="J62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="K62" s="187" t="str">
+      <c r="K62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="L62" s="187" t="str">
+      <c r="L62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="M62" s="187" t="str">
+      <c r="M62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
@@ -6442,47 +6438,47 @@
       <c r="B63" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C63" s="187">
+      <c r="C63" s="186">
         <f t="shared" ref="C63:M63" si="31">IF(C$4="","",-C21)</f>
         <v>169280</v>
       </c>
-      <c r="D63" s="187">
+      <c r="D63" s="186">
         <f t="shared" si="31"/>
         <v>50846</v>
       </c>
-      <c r="E63" s="187">
+      <c r="E63" s="186">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="F63" s="187">
+      <c r="F63" s="186">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G63" s="187">
+      <c r="G63" s="186">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="H63" s="187" t="str">
+      <c r="H63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="I63" s="187" t="str">
+      <c r="I63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="J63" s="187" t="str">
+      <c r="J63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="K63" s="187" t="str">
+      <c r="K63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="L63" s="187" t="str">
+      <c r="L63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="M63" s="187" t="str">
+      <c r="M63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
@@ -7102,19 +7098,19 @@
       <c r="B3" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C3" s="210" t="s">
+      <c r="C3" s="209" t="s">
         <v>141</v>
       </c>
-      <c r="D3" s="211" t="s">
+      <c r="D3" s="210" t="s">
         <v>36</v>
       </c>
       <c r="F3" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="G3" s="210" t="s">
+      <c r="G3" s="209" t="s">
         <v>141</v>
       </c>
-      <c r="H3" s="211" t="s">
+      <c r="H3" s="210" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7125,7 +7121,7 @@
       <c r="C4" s="19">
         <v>180994</v>
       </c>
-      <c r="D4" s="303">
+      <c r="D4" s="301">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -7135,7 +7131,7 @@
       <c r="G4" s="19">
         <v>2385307</v>
       </c>
-      <c r="H4" s="303">
+      <c r="H4" s="301">
         <v>0.9</v>
       </c>
     </row>
@@ -7146,7 +7142,7 @@
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="303">
+      <c r="D5" s="301">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -7156,7 +7152,7 @@
       <c r="G5" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="303">
+      <c r="H5" s="301">
         <v>0.7</v>
       </c>
     </row>
@@ -7167,7 +7163,7 @@
       <c r="C6" s="19">
         <v>158110</v>
       </c>
-      <c r="D6" s="303">
+      <c r="D6" s="301">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -7177,7 +7173,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="303">
+      <c r="H6" s="301">
         <v>0.6</v>
       </c>
     </row>
@@ -7188,7 +7184,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="303">
+      <c r="D7" s="301">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -7198,7 +7194,7 @@
       <c r="G7" s="19">
         <v>253051</v>
       </c>
-      <c r="H7" s="303">
+      <c r="H7" s="301">
         <v>0.6</v>
       </c>
     </row>
@@ -7209,7 +7205,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="303">
+      <c r="D8" s="301">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -7219,7 +7215,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="303">
+      <c r="H8" s="301">
         <v>0.6</v>
       </c>
     </row>
@@ -7230,7 +7226,7 @@
       <c r="C9" s="19">
         <v>0</v>
       </c>
-      <c r="D9" s="303">
+      <c r="D9" s="301">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -7240,7 +7236,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="303">
+      <c r="H9" s="301">
         <v>0.6</v>
       </c>
     </row>
@@ -7251,10 +7247,10 @@
       <c r="C10" s="19">
         <v>5912</v>
       </c>
-      <c r="D10" s="303">
+      <c r="D10" s="301">
         <v>0.9</v>
       </c>
-      <c r="H10" s="304"/>
+      <c r="H10" s="302"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
@@ -7263,10 +7259,10 @@
       <c r="C11" s="19">
         <v>0</v>
       </c>
-      <c r="D11" s="303">
+      <c r="D11" s="301">
         <v>0.05</v>
       </c>
-      <c r="H11" s="304"/>
+      <c r="H11" s="302"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="82" t="s">
@@ -7301,19 +7297,19 @@
       <c r="B14" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="C14" s="210" t="s">
+      <c r="C14" s="209" t="s">
         <v>141</v>
       </c>
-      <c r="D14" s="211" t="s">
+      <c r="D14" s="210" t="s">
         <v>36</v>
       </c>
       <c r="F14" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="G14" s="210" t="s">
+      <c r="G14" s="209" t="s">
         <v>141</v>
       </c>
-      <c r="H14" s="211" t="s">
+      <c r="H14" s="210" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7324,7 +7320,7 @@
       <c r="C15" s="19">
         <v>0</v>
       </c>
-      <c r="D15" s="303">
+      <c r="D15" s="301">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -7333,7 +7329,7 @@
       <c r="G15" s="19">
         <v>279425</v>
       </c>
-      <c r="H15" s="303">
+      <c r="H15" s="301">
         <v>0.8</v>
       </c>
     </row>
@@ -7344,7 +7340,7 @@
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="303">
+      <c r="D16" s="301">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -7353,7 +7349,7 @@
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="303">
+      <c r="H16" s="301">
         <v>0.6</v>
       </c>
     </row>
@@ -7364,7 +7360,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="303">
+      <c r="D17" s="301">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -7373,7 +7369,7 @@
       <c r="G17" s="19">
         <v>126127</v>
       </c>
-      <c r="H17" s="303">
+      <c r="H17" s="301">
         <v>0.6</v>
       </c>
     </row>
@@ -7384,7 +7380,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="303">
+      <c r="D18" s="301">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -7393,7 +7389,7 @@
       <c r="G18" s="19">
         <v>0</v>
       </c>
-      <c r="H18" s="303">
+      <c r="H18" s="301">
         <v>0.1</v>
       </c>
     </row>
@@ -7404,7 +7400,7 @@
       <c r="C19" s="19">
         <v>193915</v>
       </c>
-      <c r="D19" s="303">
+      <c r="D19" s="301">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -7413,7 +7409,7 @@
       <c r="G19" s="19">
         <v>1500</v>
       </c>
-      <c r="H19" s="303">
+      <c r="H19" s="301">
         <v>0.1</v>
       </c>
     </row>
@@ -7424,7 +7420,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="303">
+      <c r="D20" s="301">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -7433,7 +7429,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="303">
+      <c r="H20" s="301">
         <v>0.2</v>
       </c>
     </row>
@@ -7444,7 +7440,7 @@
       <c r="C21" s="19">
         <v>9704</v>
       </c>
-      <c r="D21" s="303">
+      <c r="D21" s="301">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -7453,7 +7449,7 @@
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="303">
+      <c r="H21" s="301">
         <v>0.1</v>
       </c>
     </row>
@@ -7464,10 +7460,10 @@
       <c r="C22" s="19">
         <v>76124</v>
       </c>
-      <c r="D22" s="303">
+      <c r="D22" s="301">
         <v>0.9</v>
       </c>
-      <c r="H22" s="304"/>
+      <c r="H22" s="302"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
@@ -7476,10 +7472,10 @@
       <c r="C23" s="19">
         <v>0</v>
       </c>
-      <c r="D23" s="303">
-        <v>0</v>
-      </c>
-      <c r="H23" s="304"/>
+      <c r="D23" s="301">
+        <v>0</v>
+      </c>
+      <c r="H23" s="302"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="82" t="s">
@@ -7509,16 +7505,16 @@
       <c r="B26" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="C26" s="210" t="s">
+      <c r="C26" s="209" t="s">
         <v>141</v>
       </c>
-      <c r="F26" s="212" t="s">
+      <c r="F26" s="211" t="s">
         <v>201</v>
       </c>
-      <c r="G26" s="213" t="s">
+      <c r="G26" s="212" t="s">
         <v>141</v>
       </c>
-      <c r="H26" s="214" t="s">
+      <c r="H26" s="213" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7529,14 +7525,14 @@
       <c r="C27" s="19">
         <v>0</v>
       </c>
-      <c r="F27" s="215" t="s">
+      <c r="F27" s="214" t="s">
         <v>31</v>
       </c>
       <c r="G27" s="87">
         <f>G32-G30</f>
         <v>3027292</v>
       </c>
-      <c r="H27" s="216">
+      <c r="H27" s="215">
         <f>H32-G30</f>
         <v>2236456.6000000006</v>
       </c>
@@ -7548,13 +7544,13 @@
       <c r="C28" s="19">
         <v>13416</v>
       </c>
-      <c r="F28" s="217" t="s">
+      <c r="F28" s="216" t="s">
         <v>251</v>
       </c>
-      <c r="G28" s="185">
+      <c r="G28" s="184">
         <v>3990</v>
       </c>
-      <c r="H28" s="216"/>
+      <c r="H28" s="215"/>
     </row>
     <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="4" t="s">
@@ -7563,14 +7559,14 @@
       <c r="C29" s="19">
         <v>0</v>
       </c>
-      <c r="F29" s="218" t="s">
+      <c r="F29" s="217" t="s">
         <v>80</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
         <v>3023302</v>
       </c>
-      <c r="H29" s="216">
+      <c r="H29" s="215">
         <f>H27-G28</f>
         <v>2232466.6000000006</v>
       </c>
@@ -7582,14 +7578,14 @@
       <c r="C30" s="19">
         <v>0</v>
       </c>
-      <c r="F30" s="215" t="s">
+      <c r="F30" s="214" t="s">
         <v>24</v>
       </c>
       <c r="G30" s="87">
         <f>C33+C42</f>
         <v>642877</v>
       </c>
-      <c r="H30" s="216"/>
+      <c r="H30" s="215"/>
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="82" t="s">
@@ -7599,14 +7595,14 @@
         <f>SUM(C27:C30)</f>
         <v>13416</v>
       </c>
-      <c r="F31" s="218" t="s">
+      <c r="F31" s="217" t="s">
         <v>81</v>
       </c>
-      <c r="G31" s="219">
+      <c r="G31" s="218">
         <f>C31+C40</f>
         <v>33999</v>
       </c>
-      <c r="H31" s="216"/>
+      <c r="H31" s="215"/>
     </row>
     <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="4" t="s">
@@ -7616,14 +7612,14 @@
         <f>C33-C31</f>
         <v>598515</v>
       </c>
-      <c r="F32" s="220" t="s">
+      <c r="F32" s="219" t="s">
         <v>79</v>
       </c>
-      <c r="G32" s="221">
+      <c r="G32" s="220">
         <f>G35+G40</f>
         <v>3670169</v>
       </c>
-      <c r="H32" s="216">
+      <c r="H32" s="215">
         <f>H35+H40</f>
         <v>2879333.6000000006</v>
       </c>
@@ -7635,20 +7631,20 @@
       <c r="C33" s="86">
         <v>611931</v>
       </c>
-      <c r="F33" s="222"/>
+      <c r="F33" s="221"/>
       <c r="G33" s="2"/>
-      <c r="H33" s="223"/>
+      <c r="H33" s="222"/>
     </row>
     <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="85"/>
       <c r="C34" s="86"/>
-      <c r="F34" s="224" t="s">
+      <c r="F34" s="223" t="s">
         <v>207</v>
       </c>
-      <c r="G34" s="225" t="s">
+      <c r="G34" s="224" t="s">
         <v>141</v>
       </c>
-      <c r="H34" s="226" t="s">
+      <c r="H34" s="225" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7656,17 +7652,17 @@
       <c r="B35" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="C35" s="210" t="s">
+      <c r="C35" s="209" t="s">
         <v>141</v>
       </c>
-      <c r="F35" s="227" t="s">
+      <c r="F35" s="226" t="s">
         <v>32</v>
       </c>
-      <c r="G35" s="221">
+      <c r="G35" s="220">
         <f>C12+C24</f>
         <v>624759</v>
       </c>
-      <c r="H35" s="228">
+      <c r="H35" s="227">
         <f>D12+D24</f>
         <v>281360.5</v>
       </c>
@@ -7678,14 +7674,14 @@
       <c r="C36" s="19">
         <v>0</v>
       </c>
-      <c r="F36" s="218" t="s">
+      <c r="F36" s="217" t="s">
         <v>202</v>
       </c>
-      <c r="G36" s="219">
+      <c r="G36" s="218">
         <f>C4+C15</f>
         <v>180994</v>
       </c>
-      <c r="H36" s="223"/>
+      <c r="H36" s="222"/>
     </row>
     <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="4" t="s">
@@ -7694,14 +7690,14 @@
       <c r="C37" s="19">
         <v>20583</v>
       </c>
-      <c r="F37" s="218" t="s">
+      <c r="F37" s="217" t="s">
         <v>203</v>
       </c>
-      <c r="G37" s="219">
+      <c r="G37" s="218">
         <f>C6</f>
         <v>158110</v>
       </c>
-      <c r="H37" s="223"/>
+      <c r="H37" s="222"/>
     </row>
     <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="4" t="s">
@@ -7710,14 +7706,14 @@
       <c r="C38" s="19">
         <v>0</v>
       </c>
-      <c r="F38" s="218" t="s">
+      <c r="F38" s="217" t="s">
         <v>204</v>
       </c>
-      <c r="G38" s="219">
+      <c r="G38" s="218">
         <f>C7+C17</f>
         <v>0</v>
       </c>
-      <c r="H38" s="223"/>
+      <c r="H38" s="222"/>
     </row>
     <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="2" t="s">
@@ -7726,14 +7722,14 @@
       <c r="C39" s="19">
         <v>0</v>
       </c>
-      <c r="F39" s="218" t="s">
+      <c r="F39" s="217" t="s">
         <v>84</v>
       </c>
-      <c r="G39" s="219">
+      <c r="G39" s="218">
         <f>C7+C17+C19+C20</f>
         <v>193915</v>
       </c>
-      <c r="H39" s="216">
+      <c r="H39" s="215">
         <f>C7*D7+C17*D17+C19*D19+C20*D20</f>
         <v>19391.5</v>
       </c>
@@ -7746,14 +7742,14 @@
         <f>SUM(C36:C39)</f>
         <v>20583</v>
       </c>
-      <c r="F40" s="227" t="s">
+      <c r="F40" s="226" t="s">
         <v>143</v>
       </c>
-      <c r="G40" s="221">
+      <c r="G40" s="220">
         <f>G12+G24</f>
         <v>3045410</v>
       </c>
-      <c r="H40" s="228">
+      <c r="H40" s="227">
         <f>H12+H24</f>
         <v>2597973.1000000006</v>
       </c>
@@ -7766,14 +7762,14 @@
         <f>C42-C40</f>
         <v>10363</v>
       </c>
-      <c r="F41" s="218" t="s">
+      <c r="F41" s="217" t="s">
         <v>196</v>
       </c>
-      <c r="G41" s="219">
+      <c r="G41" s="218">
         <f>C70</f>
         <v>2664732</v>
       </c>
-      <c r="H41" s="228">
+      <c r="H41" s="227">
         <f>H40-H42</f>
         <v>2370316.3000000007</v>
       </c>
@@ -7785,14 +7781,14 @@
       <c r="C42" s="86">
         <v>30946</v>
       </c>
-      <c r="F42" s="229" t="s">
+      <c r="F42" s="228" t="s">
         <v>197</v>
       </c>
-      <c r="G42" s="230">
+      <c r="G42" s="229">
         <f>C82</f>
         <v>380678</v>
       </c>
-      <c r="H42" s="231">
+      <c r="H42" s="230">
         <f>D82</f>
         <v>227656.8</v>
       </c>
@@ -7812,13 +7808,13 @@
       <c r="B45" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="C45" s="268" t="s">
+      <c r="C45" s="267" t="s">
         <v>141</v>
       </c>
-      <c r="D45" s="210" t="s">
+      <c r="D45" s="209" t="s">
         <v>288</v>
       </c>
-      <c r="F45" s="296" t="s">
+      <c r="F45" s="294" t="s">
         <v>63</v>
       </c>
     </row>
@@ -7826,15 +7822,15 @@
       <c r="B46" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C46" s="192">
+      <c r="C46" s="191">
         <f>G29</f>
         <v>3023302</v>
       </c>
-      <c r="D46" s="192">
+      <c r="D46" s="191">
         <f>H29</f>
         <v>2232466.6000000006</v>
       </c>
-      <c r="F46" s="291"/>
+      <c r="F46" s="289"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B47" s="1" t="str">
@@ -7843,29 +7839,29 @@
       </c>
       <c r="C47" s="151">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>2.4274436025512744</v>
+        <v>2.4274436025512749</v>
       </c>
       <c r="D47" s="151">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.7924728545409609</v>
-      </c>
-      <c r="F47" s="291"/>
+        <v>1.7924728545409614</v>
+      </c>
+      <c r="F47" s="289"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F48" s="291"/>
+      <c r="F48" s="289"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="162" t="s">
+      <c r="B49" s="161" t="s">
         <v>148</v>
       </c>
-      <c r="C49" s="269" t="s">
+      <c r="C49" s="268" t="s">
         <v>61</v>
       </c>
-      <c r="D49" s="225" t="s">
+      <c r="D49" s="224" t="s">
         <v>100</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="291"/>
+      <c r="F49" s="289"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="8" t="s">
@@ -7879,33 +7875,33 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>0.3233257888430302</v>
       </c>
-      <c r="F50" s="291"/>
+      <c r="F50" s="289"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C51" s="209"/>
+      <c r="C51" s="208"/>
       <c r="D51" s="94">
         <f>G29/G32</f>
         <v>0.82375007799368372</v>
       </c>
-      <c r="F51" s="291"/>
+      <c r="F51" s="289"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F52" s="291"/>
+      <c r="F52" s="289"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="162" t="s">
+      <c r="B53" s="161" t="s">
         <v>147</v>
       </c>
-      <c r="C53" s="269" t="s">
+      <c r="C53" s="268" t="s">
         <v>61</v>
       </c>
-      <c r="D53" s="225" t="s">
+      <c r="D53" s="224" t="s">
         <v>100</v>
       </c>
-      <c r="F53" s="291"/>
+      <c r="F53" s="289"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
@@ -7919,7 +7915,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>0.16831130083760298</v>
       </c>
-      <c r="F54" s="291"/>
+      <c r="F54" s="289"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
@@ -7933,22 +7929,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>0</v>
       </c>
-      <c r="F55" s="291"/>
+      <c r="F55" s="289"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F56" s="291"/>
+      <c r="F56" s="289"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="162" t="s">
+      <c r="B57" s="161" t="s">
         <v>180</v>
       </c>
-      <c r="C57" s="269" t="s">
+      <c r="C57" s="268" t="s">
         <v>61</v>
       </c>
-      <c r="D57" s="225" t="s">
+      <c r="D57" s="224" t="s">
         <v>100</v>
       </c>
-      <c r="F57" s="291"/>
+      <c r="F57" s="289"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="2" t="s">
@@ -7970,22 +7966,22 @@
         <f>G39/G32</f>
         <v>5.2835441637701153E-2</v>
       </c>
-      <c r="F59" s="291"/>
+      <c r="F59" s="289"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F60" s="291"/>
+      <c r="F60" s="289"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="162" t="s">
+      <c r="B61" s="161" t="s">
         <v>291</v>
       </c>
-      <c r="C61" s="269" t="s">
+      <c r="C61" s="268" t="s">
         <v>142</v>
       </c>
-      <c r="D61" s="225" t="s">
+      <c r="D61" s="224" t="s">
         <v>100</v>
       </c>
-      <c r="F61" s="291"/>
+      <c r="F61" s="289"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
@@ -7999,7 +7995,7 @@
         <f>G28/G29</f>
         <v>1.3197490690642218E-3</v>
       </c>
-      <c r="F62" s="291" t="s">
+      <c r="F62" s="289" t="s">
         <v>289</v>
       </c>
     </row>
@@ -8018,13 +8014,13 @@
       <c r="B65" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="C65" s="268" t="s">
+      <c r="C65" s="267" t="s">
         <v>141</v>
       </c>
-      <c r="D65" s="211" t="s">
+      <c r="D65" s="210" t="s">
         <v>312</v>
       </c>
-      <c r="F65" s="296" t="s">
+      <c r="F65" s="294" t="s">
         <v>63</v>
       </c>
     </row>
@@ -8036,7 +8032,7 @@
         <f>G4+G5+G15</f>
         <v>2664732</v>
       </c>
-      <c r="D66" s="192">
+      <c r="D66" s="191">
         <f>C66-D75</f>
         <v>1902339.7312688304</v>
       </c>
@@ -8052,7 +8048,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="291"/>
+      <c r="F67" s="289"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="108" t="s">
@@ -8062,7 +8058,7 @@
         <f>G18</f>
         <v>0</v>
       </c>
-      <c r="F68" s="291"/>
+      <c r="F68" s="289"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="108" t="s">
@@ -8072,7 +8068,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="291"/>
+      <c r="F69" s="289"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
@@ -8082,49 +8078,49 @@
         <f>SUM(C66:C69)</f>
         <v>2664732</v>
       </c>
-      <c r="F70" s="291"/>
+      <c r="F70" s="289"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F71" s="291"/>
+      <c r="F71" s="289"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="294" t="s">
+      <c r="B72" s="292" t="s">
         <v>351</v>
       </c>
-      <c r="C72" s="268" t="s">
+      <c r="C72" s="267" t="s">
         <v>100</v>
       </c>
-      <c r="D72" s="210" t="s">
+      <c r="D72" s="209" t="s">
         <v>61</v>
       </c>
-      <c r="F72" s="291"/>
+      <c r="F72" s="289"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
         <v>350</v>
       </c>
-      <c r="C73" s="192">
+      <c r="C73" s="191">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35)/12</f>
         <v>-125869.25</v>
       </c>
-      <c r="D73" s="192">
+      <c r="D73" s="191">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35)/12</f>
         <v>-127065.37812186161</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="297" t="s">
+      <c r="B74" s="295" t="s">
         <v>356</v>
       </c>
-      <c r="C74" s="298">
+      <c r="C74" s="296">
         <f>-$C$66/C73</f>
         <v>21.170635401418537</v>
       </c>
-      <c r="D74" s="298">
+      <c r="D74" s="296">
         <f>-$C$66/D73</f>
         <v>20.971345927483078</v>
       </c>
-      <c r="F74" s="291" t="s">
+      <c r="F74" s="289" t="s">
         <v>352</v>
       </c>
     </row>
@@ -8132,42 +8128,42 @@
       <c r="B75" s="82" t="s">
         <v>353</v>
       </c>
-      <c r="C75" s="302"/>
-      <c r="D75" s="301">
+      <c r="C75" s="300"/>
+      <c r="D75" s="299">
         <f>MAX(-D73*D76,G5)</f>
         <v>762392.26873116964</v>
       </c>
-      <c r="F75" s="291" t="s">
+      <c r="F75" s="289" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="299" t="s">
+      <c r="B76" s="297" t="s">
         <v>357</v>
       </c>
-      <c r="C76" s="300"/>
-      <c r="D76" s="337">
+      <c r="C76" s="298"/>
+      <c r="D76" s="335">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,IF(D74&gt;36,12,6),2))</f>
         <v>6</v>
       </c>
-      <c r="F76" s="291" t="s">
+      <c r="F76" s="289" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F77" s="291"/>
+      <c r="F77" s="289"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="267" t="s">
         <v>141</v>
       </c>
-      <c r="D78" s="211" t="s">
+      <c r="D78" s="210" t="s">
         <v>36</v>
       </c>
-      <c r="F78" s="291"/>
+      <c r="F78" s="289"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="108" t="s">
@@ -8177,11 +8173,11 @@
         <f>G7+G17</f>
         <v>379178</v>
       </c>
-      <c r="D79" s="192">
+      <c r="D79" s="191">
         <f>G7*H7+G17*H17</f>
         <v>227506.8</v>
       </c>
-      <c r="F79" s="291"/>
+      <c r="F79" s="289"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="108" t="s">
@@ -8191,11 +8187,11 @@
         <f>G19</f>
         <v>1500</v>
       </c>
-      <c r="D80" s="192">
+      <c r="D80" s="191">
         <f>G19*H19</f>
         <v>150</v>
       </c>
-      <c r="F80" s="291"/>
+      <c r="F80" s="289"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="108" t="s">
@@ -8205,11 +8201,11 @@
         <f>G9+G21</f>
         <v>0</v>
       </c>
-      <c r="D81" s="192">
+      <c r="D81" s="191">
         <f>G9*H9+G21*H21</f>
         <v>0</v>
       </c>
-      <c r="F81" s="291"/>
+      <c r="F81" s="289"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B82" s="82" t="s">
@@ -8223,7 +8219,7 @@
         <f>SUM(D79:D81)</f>
         <v>227656.8</v>
       </c>
-      <c r="F82" s="291"/>
+      <c r="F82" s="289"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
@@ -8240,57 +8236,57 @@
       <c r="B85" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="D85" s="278" t="s">
+      <c r="D85" s="276" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B86" s="275" t="s">
+      <c r="B86" s="273" t="s">
         <v>313</v>
       </c>
-      <c r="C86" s="192">
+      <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-36397.583551349999</v>
-      </c>
-      <c r="D86" s="255">
+        <v>-36397.583551350006</v>
+      </c>
+      <c r="D86" s="254">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-2.7298184251239466E-2</v>
-      </c>
-      <c r="E86" s="277" t="str">
+        <v>-2.7298184251239473E-2</v>
+      </c>
+      <c r="E86" s="275" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B87" s="275" t="s">
+      <c r="B87" s="273" t="s">
         <v>314</v>
       </c>
-      <c r="C87" s="192">
+      <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>2036547.231151209</v>
-      </c>
-      <c r="D87" s="255">
+        <v>2036547.2311512092</v>
+      </c>
+      <c r="D87" s="254">
         <f>C87*$H$1/Common_Shares</f>
         <v>1.5274102324371277</v>
       </c>
-      <c r="E87" s="277" t="str">
+      <c r="E87" s="275" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B88" s="276" t="s">
+      <c r="B88" s="274" t="s">
         <v>194</v>
       </c>
-      <c r="C88" s="192">
+      <c r="C88" s="191">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>243717.67990331995</v>
-      </c>
-      <c r="D88" s="255">
+        <v>243717.67990332001</v>
+      </c>
+      <c r="D88" s="254">
         <f>C88*$H$1/Common_Shares</f>
-        <v>0.18278823707896033</v>
-      </c>
-      <c r="E88" s="277" t="str">
+        <v>0.18278823707896039</v>
+      </c>
+      <c r="E88" s="275" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
@@ -8299,15 +8295,15 @@
       <c r="B89" s="82" t="s">
         <v>318</v>
       </c>
-      <c r="C89" s="191">
+      <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
-        <v>2243867.3275031787</v>
-      </c>
-      <c r="D89" s="279">
+        <v>2243867.3275031792</v>
+      </c>
+      <c r="D89" s="277">
         <f>SUM(D86:D88)</f>
         <v>1.6829002852648487</v>
       </c>
-      <c r="E89" s="277" t="str">
+      <c r="E89" s="275" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
@@ -8428,7 +8424,7 @@
         <v>1000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="311"/>
+      <c r="E3" s="309"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -8437,54 +8433,54 @@
       <c r="B4" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="197">
+      <c r="C4" s="196">
         <f>AVERAGE(G4:K4)</f>
         <v>1583387.2</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="309"/>
+      <c r="E4" s="307"/>
       <c r="F4" s="57"/>
-      <c r="G4" s="187">
+      <c r="G4" s="186">
         <f>Data!C36</f>
         <v>1615585</v>
       </c>
-      <c r="H4" s="187">
+      <c r="H4" s="186">
         <f>Data!D36</f>
         <v>1446638</v>
       </c>
-      <c r="I4" s="187">
+      <c r="I4" s="186">
         <f>Data!E36</f>
         <v>1769157</v>
       </c>
-      <c r="J4" s="187">
+      <c r="J4" s="186">
         <f>Data!F36</f>
         <v>1702154</v>
       </c>
-      <c r="K4" s="187">
+      <c r="K4" s="186">
         <f>Data!G36</f>
         <v>1383402</v>
       </c>
-      <c r="L4" s="187" t="str">
+      <c r="L4" s="186" t="str">
         <f>Data!H36</f>
         <v/>
       </c>
-      <c r="M4" s="187" t="str">
+      <c r="M4" s="186" t="str">
         <f>Data!I36</f>
         <v/>
       </c>
-      <c r="N4" s="187" t="str">
+      <c r="N4" s="186" t="str">
         <f>Data!J36</f>
         <v/>
       </c>
-      <c r="O4" s="187" t="str">
+      <c r="O4" s="186" t="str">
         <f>Data!K36</f>
         <v/>
       </c>
-      <c r="P4" s="187" t="str">
+      <c r="P4" s="186" t="str">
         <f>Data!L36</f>
         <v/>
       </c>
-      <c r="Q4" s="187" t="str">
+      <c r="Q4" s="186" t="str">
         <f>Data!M36</f>
         <v/>
       </c>
@@ -8494,52 +8490,52 @@
       <c r="B5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="198">
+      <c r="C5" s="197">
         <f>C25</f>
         <v>-1348785.0374623393</v>
       </c>
-      <c r="E5" s="311"/>
-      <c r="G5" s="187">
+      <c r="E5" s="309"/>
+      <c r="G5" s="186">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-1322360</v>
       </c>
-      <c r="H5" s="187">
+      <c r="H5" s="186">
         <f t="shared" si="1"/>
         <v>-1280518</v>
       </c>
-      <c r="I5" s="187">
+      <c r="I5" s="186">
         <f t="shared" si="1"/>
         <v>-981731</v>
       </c>
-      <c r="J5" s="187">
+      <c r="J5" s="186">
         <f t="shared" si="1"/>
         <v>-959572</v>
       </c>
-      <c r="K5" s="187">
+      <c r="K5" s="186">
         <f t="shared" si="1"/>
         <v>-783542</v>
       </c>
-      <c r="L5" s="187" t="str">
+      <c r="L5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="M5" s="187" t="str">
+      <c r="M5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="N5" s="187" t="str">
+      <c r="N5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="O5" s="187" t="str">
+      <c r="O5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P5" s="187" t="str">
+      <c r="P5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q5" s="187" t="str">
+      <c r="Q5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8549,52 +8545,52 @@
       <c r="B6" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="188">
+      <c r="C6" s="187">
         <f>C4+C5</f>
         <v>234602.16253766068</v>
       </c>
-      <c r="E6" s="311"/>
-      <c r="G6" s="188">
+      <c r="E6" s="309"/>
+      <c r="G6" s="187">
         <f>IF(G4="","",G4+G5)</f>
         <v>293225</v>
       </c>
-      <c r="H6" s="188">
+      <c r="H6" s="187">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
         <v>166120</v>
       </c>
-      <c r="I6" s="188">
+      <c r="I6" s="187">
         <f t="shared" si="2"/>
         <v>787426</v>
       </c>
-      <c r="J6" s="188">
+      <c r="J6" s="187">
         <f t="shared" si="2"/>
         <v>742582</v>
       </c>
-      <c r="K6" s="188">
+      <c r="K6" s="187">
         <f t="shared" si="2"/>
         <v>599860</v>
       </c>
-      <c r="L6" s="188" t="str">
+      <c r="L6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M6" s="188" t="str">
+      <c r="M6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="N6" s="188" t="str">
+      <c r="N6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O6" s="188" t="str">
+      <c r="O6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P6" s="188" t="str">
+      <c r="P6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Q6" s="188" t="str">
+      <c r="Q6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -8604,52 +8600,52 @@
       <c r="B7" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="198">
+      <c r="C7" s="197">
         <f>C35</f>
         <v>-175999.5</v>
       </c>
-      <c r="E7" s="311"/>
-      <c r="G7" s="198">
+      <c r="E7" s="309"/>
+      <c r="G7" s="197">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-188071</v>
       </c>
-      <c r="H7" s="198">
+      <c r="H7" s="197">
         <f t="shared" si="3"/>
         <v>-163928</v>
       </c>
-      <c r="I7" s="198">
+      <c r="I7" s="197">
         <f t="shared" si="3"/>
         <v>-705390</v>
       </c>
-      <c r="J7" s="198">
+      <c r="J7" s="197">
         <f t="shared" si="3"/>
         <v>-456610</v>
       </c>
-      <c r="K7" s="198">
+      <c r="K7" s="197">
         <f t="shared" si="3"/>
         <v>-396643</v>
       </c>
-      <c r="L7" s="198" t="str">
+      <c r="L7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M7" s="198" t="str">
+      <c r="M7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="N7" s="198" t="str">
+      <c r="N7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O7" s="198" t="str">
+      <c r="O7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P7" s="198" t="str">
+      <c r="P7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="Q7" s="198" t="str">
+      <c r="Q7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -8659,54 +8655,54 @@
       <c r="B8" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="C8" s="199">
+      <c r="C8" s="198">
         <f>C6+C7</f>
         <v>58602.662537660683</v>
       </c>
       <c r="D8" s="60"/>
-      <c r="E8" s="317"/>
+      <c r="E8" s="315"/>
       <c r="F8" s="60"/>
-      <c r="G8" s="188">
+      <c r="G8" s="187">
         <f>IF(G$4="","",G6+G7)</f>
         <v>105154</v>
       </c>
-      <c r="H8" s="188">
+      <c r="H8" s="187">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
         <v>2192</v>
       </c>
-      <c r="I8" s="188">
+      <c r="I8" s="187">
         <f t="shared" si="4"/>
         <v>82036</v>
       </c>
-      <c r="J8" s="188">
+      <c r="J8" s="187">
         <f t="shared" si="4"/>
         <v>285972</v>
       </c>
-      <c r="K8" s="188">
+      <c r="K8" s="187">
         <f t="shared" si="4"/>
         <v>203217</v>
       </c>
-      <c r="L8" s="188" t="str">
+      <c r="L8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M8" s="188" t="str">
+      <c r="M8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N8" s="188" t="str">
+      <c r="N8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O8" s="188" t="str">
+      <c r="O8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P8" s="188" t="str">
+      <c r="P8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Q8" s="188" t="str">
+      <c r="Q8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -8716,52 +8712,52 @@
       <c r="B9" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="198">
+      <c r="C9" s="197">
         <f>BS!$G$39*BS!D58</f>
         <v>35974</v>
       </c>
-      <c r="E9" s="311"/>
-      <c r="G9" s="198">
+      <c r="E9" s="309"/>
+      <c r="G9" s="197">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>35974</v>
       </c>
-      <c r="H9" s="198">
+      <c r="H9" s="197">
         <f>IF(Data!D61="","",-Data!D61)</f>
         <v>32106</v>
       </c>
-      <c r="I9" s="198">
+      <c r="I9" s="197">
         <f>IF(Data!E61="","",-Data!E61)</f>
         <v>181.018</v>
       </c>
-      <c r="J9" s="198">
+      <c r="J9" s="197">
         <f>IF(Data!F61="","",-Data!F61)</f>
         <v>186.14699999999999</v>
       </c>
-      <c r="K9" s="198">
+      <c r="K9" s="197">
         <f>IF(Data!G61="","",-Data!G61)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="198" t="str">
+      <c r="L9" s="197" t="str">
         <f>IF(Data!H61="","",-Data!H61)</f>
         <v/>
       </c>
-      <c r="M9" s="198" t="str">
+      <c r="M9" s="197" t="str">
         <f>IF(Data!I61="","",-Data!I61)</f>
         <v/>
       </c>
-      <c r="N9" s="198" t="str">
+      <c r="N9" s="197" t="str">
         <f>IF(Data!J61="","",-Data!J61)</f>
         <v/>
       </c>
-      <c r="O9" s="198" t="str">
+      <c r="O9" s="197" t="str">
         <f>IF(Data!K61="","",-Data!K61)</f>
         <v/>
       </c>
-      <c r="P9" s="198" t="str">
+      <c r="P9" s="197" t="str">
         <f>IF(Data!L61="","",-Data!L61)</f>
         <v/>
       </c>
-      <c r="Q9" s="198" t="str">
+      <c r="Q9" s="197" t="str">
         <f>IF(Data!M61="","",-Data!M61)</f>
         <v/>
       </c>
@@ -8771,52 +8767,52 @@
       <c r="B10" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="198">
+      <c r="C10" s="197">
         <f>-C4*C78</f>
         <v>-35974</v>
       </c>
-      <c r="E10" s="311"/>
-      <c r="G10" s="198">
+      <c r="E10" s="309"/>
+      <c r="G10" s="197">
         <f>Data!C62</f>
         <v>-15312</v>
       </c>
-      <c r="H10" s="198">
+      <c r="H10" s="197">
         <f>Data!D62</f>
         <v>-11600</v>
       </c>
-      <c r="I10" s="198">
+      <c r="I10" s="197">
         <f>Data!E62</f>
         <v>0</v>
       </c>
-      <c r="J10" s="198">
+      <c r="J10" s="197">
         <f>Data!F62</f>
         <v>0</v>
       </c>
-      <c r="K10" s="198">
+      <c r="K10" s="197">
         <f>Data!G62</f>
         <v>0</v>
       </c>
-      <c r="L10" s="198" t="str">
+      <c r="L10" s="197" t="str">
         <f>Data!H62</f>
         <v/>
       </c>
-      <c r="M10" s="198" t="str">
+      <c r="M10" s="197" t="str">
         <f>Data!I62</f>
         <v/>
       </c>
-      <c r="N10" s="198" t="str">
+      <c r="N10" s="197" t="str">
         <f>Data!J62</f>
         <v/>
       </c>
-      <c r="O10" s="198" t="str">
+      <c r="O10" s="197" t="str">
         <f>Data!K62</f>
         <v/>
       </c>
-      <c r="P10" s="198" t="str">
+      <c r="P10" s="197" t="str">
         <f>Data!L62</f>
         <v/>
       </c>
-      <c r="Q10" s="198" t="str">
+      <c r="Q10" s="197" t="str">
         <f>Data!M62</f>
         <v/>
       </c>
@@ -8826,54 +8822,54 @@
       <c r="B11" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="C11" s="200">
+      <c r="C11" s="199">
         <f>C63</f>
         <v>0</v>
       </c>
-      <c r="D11" s="173"/>
-      <c r="E11" s="310"/>
-      <c r="F11" s="173"/>
-      <c r="G11" s="190">
+      <c r="D11" s="172"/>
+      <c r="E11" s="308"/>
+      <c r="F11" s="172"/>
+      <c r="G11" s="189">
         <f>G61</f>
         <v>0</v>
       </c>
-      <c r="H11" s="190">
+      <c r="H11" s="189">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
         <v>0</v>
       </c>
-      <c r="I11" s="190">
+      <c r="I11" s="189">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J11" s="190">
+      <c r="J11" s="189">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K11" s="190">
+      <c r="K11" s="189">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L11" s="190" t="str">
+      <c r="L11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="M11" s="190" t="str">
+      <c r="M11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N11" s="190" t="str">
+      <c r="N11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="O11" s="190" t="str">
+      <c r="O11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="P11" s="190" t="str">
+      <c r="P11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q11" s="190" t="str">
+      <c r="Q11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -8883,52 +8879,52 @@
       <c r="B12" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="198">
+      <c r="C12" s="197">
         <f>C50</f>
         <v>20112.955148098936</v>
       </c>
-      <c r="E12" s="311"/>
-      <c r="G12" s="198">
+      <c r="E12" s="309"/>
+      <c r="G12" s="197">
         <f>G50</f>
         <v>20112.955148098936</v>
       </c>
-      <c r="H12" s="198">
+      <c r="H12" s="197">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
         <v>12111.846771442135</v>
       </c>
-      <c r="I12" s="198">
+      <c r="I12" s="197">
         <f t="shared" si="6"/>
         <v>-1613</v>
       </c>
-      <c r="J12" s="198">
+      <c r="J12" s="197">
         <f t="shared" si="6"/>
         <v>-2645</v>
       </c>
-      <c r="K12" s="198">
+      <c r="K12" s="197">
         <f t="shared" si="6"/>
         <v>-299</v>
       </c>
-      <c r="L12" s="198" t="str">
+      <c r="L12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="M12" s="198" t="str">
+      <c r="M12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="N12" s="198" t="str">
+      <c r="N12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O12" s="198" t="str">
+      <c r="O12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="P12" s="198" t="str">
+      <c r="P12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q12" s="198" t="str">
+      <c r="Q12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -8938,52 +8934,52 @@
       <c r="B13" s="71" t="s">
         <v>169</v>
       </c>
-      <c r="C13" s="188">
+      <c r="C13" s="187">
         <f>SUM(C8:C12)</f>
         <v>78715.617685759615</v>
       </c>
-      <c r="E13" s="311"/>
-      <c r="G13" s="188">
+      <c r="E13" s="309"/>
+      <c r="G13" s="187">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>145928.95514809893</v>
       </c>
-      <c r="H13" s="188">
+      <c r="H13" s="187">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
         <v>34809.846771442135</v>
       </c>
-      <c r="I13" s="188">
+      <c r="I13" s="187">
         <f t="shared" si="7"/>
         <v>80604.017999999996</v>
       </c>
-      <c r="J13" s="188">
+      <c r="J13" s="187">
         <f t="shared" si="7"/>
         <v>283513.147</v>
       </c>
-      <c r="K13" s="188">
+      <c r="K13" s="187">
         <f t="shared" si="7"/>
         <v>202918</v>
       </c>
-      <c r="L13" s="188" t="str">
+      <c r="L13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="M13" s="188" t="str">
+      <c r="M13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N13" s="188" t="str">
+      <c r="N13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="O13" s="188" t="str">
+      <c r="O13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="P13" s="188" t="str">
+      <c r="P13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q13" s="188" t="str">
+      <c r="Q13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -8993,52 +8989,52 @@
       <c r="B14" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="198">
+      <c r="C14" s="197">
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-19678.904421439904</v>
       </c>
-      <c r="E14" s="311"/>
-      <c r="G14" s="198">
+      <c r="E14" s="309"/>
+      <c r="G14" s="197">
         <f>Data!C46</f>
         <v>-44449</v>
       </c>
-      <c r="H14" s="198">
+      <c r="H14" s="197">
         <f>Data!D46</f>
         <v>-21017</v>
       </c>
-      <c r="I14" s="198">
+      <c r="I14" s="197">
         <f>Data!E46</f>
         <v>0</v>
       </c>
-      <c r="J14" s="198">
+      <c r="J14" s="197">
         <f>Data!F46</f>
         <v>0</v>
       </c>
-      <c r="K14" s="198">
+      <c r="K14" s="197">
         <f>Data!G46</f>
         <v>0</v>
       </c>
-      <c r="L14" s="198" t="str">
+      <c r="L14" s="197" t="str">
         <f>Data!H46</f>
         <v/>
       </c>
-      <c r="M14" s="198" t="str">
+      <c r="M14" s="197" t="str">
         <f>Data!I46</f>
         <v/>
       </c>
-      <c r="N14" s="198" t="str">
+      <c r="N14" s="197" t="str">
         <f>Data!J46</f>
         <v/>
       </c>
-      <c r="O14" s="198" t="str">
+      <c r="O14" s="197" t="str">
         <f>Data!K46</f>
         <v/>
       </c>
-      <c r="P14" s="198" t="str">
+      <c r="P14" s="197" t="str">
         <f>Data!L46</f>
         <v/>
       </c>
-      <c r="Q14" s="198" t="str">
+      <c r="Q14" s="197" t="str">
         <f>Data!M46</f>
         <v/>
       </c>
@@ -9048,54 +9044,54 @@
       <c r="B15" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="C15" s="198">
+      <c r="C15" s="197">
         <f>-C4*C83</f>
         <v>-2089.6737831682049</v>
       </c>
       <c r="D15" s="61"/>
-      <c r="E15" s="318"/>
+      <c r="E15" s="316"/>
       <c r="F15" s="61"/>
-      <c r="G15" s="187">
+      <c r="G15" s="186">
         <f>Data!C48</f>
         <v>-2199</v>
       </c>
-      <c r="H15" s="187">
+      <c r="H15" s="186">
         <f>Data!D48</f>
         <v>-645</v>
       </c>
-      <c r="I15" s="187">
+      <c r="I15" s="186">
         <f>Data!E48</f>
         <v>0</v>
       </c>
-      <c r="J15" s="187">
+      <c r="J15" s="186">
         <f>Data!F48</f>
         <v>0</v>
       </c>
-      <c r="K15" s="187">
+      <c r="K15" s="186">
         <f>Data!G48</f>
         <v>0</v>
       </c>
-      <c r="L15" s="187" t="str">
+      <c r="L15" s="186" t="str">
         <f>Data!H48</f>
         <v/>
       </c>
-      <c r="M15" s="187" t="str">
+      <c r="M15" s="186" t="str">
         <f>Data!I48</f>
         <v/>
       </c>
-      <c r="N15" s="187" t="str">
+      <c r="N15" s="186" t="str">
         <f>Data!J48</f>
         <v/>
       </c>
-      <c r="O15" s="187" t="str">
+      <c r="O15" s="186" t="str">
         <f>Data!K48</f>
         <v/>
       </c>
-      <c r="P15" s="187" t="str">
+      <c r="P15" s="186" t="str">
         <f>Data!L48</f>
         <v/>
       </c>
-      <c r="Q15" s="187" t="str">
+      <c r="Q15" s="186" t="str">
         <f>Data!M48</f>
         <v/>
       </c>
@@ -9105,54 +9101,54 @@
       <c r="B16" s="41" t="s">
         <v>159</v>
       </c>
-      <c r="C16" s="201">
+      <c r="C16" s="200">
         <f>SUM(C13:C15)</f>
         <v>56947.039481151507</v>
       </c>
       <c r="D16" s="62"/>
-      <c r="E16" s="319"/>
+      <c r="E16" s="317"/>
       <c r="F16" s="62"/>
-      <c r="G16" s="188">
+      <c r="G16" s="187">
         <f>IF(G$4="","",SUM(G13:G15))</f>
         <v>99280.955148098932</v>
       </c>
-      <c r="H16" s="188">
+      <c r="H16" s="187">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
         <v>13147.846771442135</v>
       </c>
-      <c r="I16" s="188">
+      <c r="I16" s="187">
         <f t="shared" si="8"/>
         <v>80604.017999999996</v>
       </c>
-      <c r="J16" s="188">
+      <c r="J16" s="187">
         <f t="shared" si="8"/>
         <v>283513.147</v>
       </c>
-      <c r="K16" s="188">
+      <c r="K16" s="187">
         <f t="shared" si="8"/>
         <v>202918</v>
       </c>
-      <c r="L16" s="188" t="str">
+      <c r="L16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="M16" s="188" t="str">
+      <c r="M16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="N16" s="188" t="str">
+      <c r="N16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="O16" s="188" t="str">
+      <c r="O16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="P16" s="188" t="str">
+      <c r="P16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="Q16" s="188" t="str">
+      <c r="Q16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -9162,105 +9158,105 @@
       <c r="B17" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="198">
+      <c r="C17" s="197">
         <f>-C4*C85</f>
         <v>0</v>
       </c>
       <c r="D17" s="59"/>
-      <c r="E17" s="310" t="s">
+      <c r="E17" s="308" t="s">
         <v>368</v>
       </c>
       <c r="F17" s="59"/>
-      <c r="G17" s="202"/>
-      <c r="H17" s="202"/>
-      <c r="I17" s="202"/>
-      <c r="J17" s="202"/>
-      <c r="K17" s="202"/>
-      <c r="L17" s="202"/>
-      <c r="M17" s="202"/>
-      <c r="N17" s="202"/>
-      <c r="O17" s="202"/>
-      <c r="P17" s="202"/>
-      <c r="Q17" s="202"/>
+      <c r="G17" s="201"/>
+      <c r="H17" s="201"/>
+      <c r="I17" s="201"/>
+      <c r="J17" s="201"/>
+      <c r="K17" s="201"/>
+      <c r="L17" s="201"/>
+      <c r="M17" s="201"/>
+      <c r="N17" s="201"/>
+      <c r="O17" s="201"/>
+      <c r="P17" s="201"/>
+      <c r="Q17" s="201"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C18" s="198">
+      <c r="C18" s="197">
         <v>0</v>
       </c>
       <c r="D18" s="59"/>
-      <c r="E18" s="310" t="s">
+      <c r="E18" s="308" t="s">
         <v>369</v>
       </c>
       <c r="F18" s="59"/>
-      <c r="G18" s="203"/>
-      <c r="H18" s="203"/>
-      <c r="I18" s="203"/>
-      <c r="J18" s="203"/>
-      <c r="K18" s="203"/>
-      <c r="L18" s="203"/>
-      <c r="M18" s="203"/>
-      <c r="N18" s="203"/>
-      <c r="O18" s="203"/>
-      <c r="P18" s="203"/>
-      <c r="Q18" s="203"/>
+      <c r="G18" s="202"/>
+      <c r="H18" s="202"/>
+      <c r="I18" s="202"/>
+      <c r="J18" s="202"/>
+      <c r="K18" s="202"/>
+      <c r="L18" s="202"/>
+      <c r="M18" s="202"/>
+      <c r="N18" s="202"/>
+      <c r="O18" s="202"/>
+      <c r="P18" s="202"/>
+      <c r="Q18" s="202"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="188">
+      <c r="C19" s="187">
         <f>C16+C17</f>
         <v>56947.039481151507</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="308"/>
+      <c r="E19" s="306"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="190">
+      <c r="G19" s="189">
         <f>IF(G$4="","",G16+G17)</f>
         <v>99280.955148098932</v>
       </c>
-      <c r="H19" s="190">
+      <c r="H19" s="189">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
         <v>13147.846771442135</v>
       </c>
-      <c r="I19" s="190">
+      <c r="I19" s="189">
         <f t="shared" si="9"/>
         <v>80604.017999999996</v>
       </c>
-      <c r="J19" s="190">
+      <c r="J19" s="189">
         <f t="shared" si="9"/>
         <v>283513.147</v>
       </c>
-      <c r="K19" s="190">
+      <c r="K19" s="189">
         <f t="shared" si="9"/>
         <v>202918</v>
       </c>
-      <c r="L19" s="190" t="str">
+      <c r="L19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="M19" s="190" t="str">
+      <c r="M19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="N19" s="190" t="str">
+      <c r="N19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="O19" s="190" t="str">
+      <c r="O19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="P19" s="190" t="str">
+      <c r="P19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="Q19" s="190" t="str">
+      <c r="Q19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -9314,7 +9310,7 @@
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="308"/>
+      <c r="E22" s="306"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -9333,54 +9329,54 @@
       <c r="B23" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="204">
+      <c r="C23" s="203">
         <f>-C4*C28</f>
         <v>-902304.82874495955</v>
       </c>
       <c r="D23" s="59"/>
-      <c r="E23" s="310"/>
+      <c r="E23" s="308"/>
       <c r="F23" s="59"/>
-      <c r="G23" s="187">
+      <c r="G23" s="186">
         <f>Data!C37</f>
         <v>-897327</v>
       </c>
-      <c r="H23" s="187">
+      <c r="H23" s="186">
         <f>Data!D37</f>
         <v>-845264</v>
       </c>
-      <c r="I23" s="187">
+      <c r="I23" s="186">
         <f>Data!E37</f>
         <v>-981731</v>
       </c>
-      <c r="J23" s="187">
+      <c r="J23" s="186">
         <f>Data!F37</f>
         <v>-959572</v>
       </c>
-      <c r="K23" s="187">
+      <c r="K23" s="186">
         <f>Data!G37</f>
         <v>-783542</v>
       </c>
-      <c r="L23" s="187" t="str">
+      <c r="L23" s="186" t="str">
         <f>Data!H37</f>
         <v/>
       </c>
-      <c r="M23" s="187" t="str">
+      <c r="M23" s="186" t="str">
         <f>Data!I37</f>
         <v/>
       </c>
-      <c r="N23" s="187" t="str">
+      <c r="N23" s="186" t="str">
         <f>Data!J37</f>
         <v/>
       </c>
-      <c r="O23" s="187" t="str">
+      <c r="O23" s="186" t="str">
         <f>Data!K37</f>
         <v/>
       </c>
-      <c r="P23" s="187" t="str">
+      <c r="P23" s="186" t="str">
         <f>Data!L37</f>
         <v/>
       </c>
-      <c r="Q23" s="187" t="str">
+      <c r="Q23" s="186" t="str">
         <f>Data!M37</f>
         <v/>
       </c>
@@ -9390,54 +9386,54 @@
       <c r="B24" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="C24" s="198">
+      <c r="C24" s="197">
         <f>-C4*C29</f>
         <v>-446480.2087173796</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="308"/>
+      <c r="E24" s="306"/>
       <c r="F24" s="27"/>
-      <c r="G24" s="187">
+      <c r="G24" s="186">
         <f>Data!C40</f>
         <v>-425033</v>
       </c>
-      <c r="H24" s="187">
+      <c r="H24" s="186">
         <f>Data!D40</f>
         <v>-435254</v>
       </c>
-      <c r="I24" s="187">
+      <c r="I24" s="186">
         <f>Data!E40</f>
         <v>0</v>
       </c>
-      <c r="J24" s="187">
+      <c r="J24" s="186">
         <f>Data!F40</f>
         <v>0</v>
       </c>
-      <c r="K24" s="187">
+      <c r="K24" s="186">
         <f>Data!G40</f>
         <v>0</v>
       </c>
-      <c r="L24" s="187" t="str">
+      <c r="L24" s="186" t="str">
         <f>Data!H40</f>
         <v/>
       </c>
-      <c r="M24" s="187" t="str">
+      <c r="M24" s="186" t="str">
         <f>Data!I40</f>
         <v/>
       </c>
-      <c r="N24" s="187" t="str">
+      <c r="N24" s="186" t="str">
         <f>Data!J40</f>
         <v/>
       </c>
-      <c r="O24" s="187" t="str">
+      <c r="O24" s="186" t="str">
         <f>Data!K40</f>
         <v/>
       </c>
-      <c r="P24" s="187" t="str">
+      <c r="P24" s="186" t="str">
         <f>Data!L40</f>
         <v/>
       </c>
-      <c r="Q24" s="187" t="str">
+      <c r="Q24" s="186" t="str">
         <f>Data!M40</f>
         <v/>
       </c>
@@ -9447,68 +9443,68 @@
       <c r="B25" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="188">
+      <c r="C25" s="187">
         <f>C23+C24</f>
         <v>-1348785.0374623393</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="316"/>
+      <c r="E25" s="314"/>
       <c r="F25" s="9"/>
-      <c r="G25" s="188">
+      <c r="G25" s="187">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
         <v>-1322360</v>
       </c>
-      <c r="H25" s="188">
+      <c r="H25" s="187">
         <f t="shared" si="10"/>
         <v>-1280518</v>
       </c>
-      <c r="I25" s="188">
+      <c r="I25" s="187">
         <f t="shared" si="10"/>
         <v>-981731</v>
       </c>
-      <c r="J25" s="188">
+      <c r="J25" s="187">
         <f t="shared" si="10"/>
         <v>-959572</v>
       </c>
-      <c r="K25" s="188">
+      <c r="K25" s="187">
         <f t="shared" si="10"/>
         <v>-783542</v>
       </c>
-      <c r="L25" s="188" t="str">
+      <c r="L25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="M25" s="188" t="str">
+      <c r="M25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="N25" s="188" t="str">
+      <c r="N25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="O25" s="188" t="str">
+      <c r="O25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="P25" s="188" t="str">
+      <c r="P25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Q25" s="188" t="str">
+      <c r="Q25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="10"/>
-      <c r="E26" s="311"/>
+      <c r="E26" s="309"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="65" t="s">
         <v>211</v>
       </c>
-      <c r="E27" s="311"/>
+      <c r="E27" s="309"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
@@ -9520,7 +9516,7 @@
         <v>0.56985734679739708</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="309" t="s">
+      <c r="E28" s="307" t="s">
         <v>370</v>
       </c>
       <c r="F28" s="26"/>
@@ -9580,7 +9576,7 @@
         <v>0.28197790705733861</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="309" t="s">
+      <c r="E29" s="307" t="s">
         <v>370</v>
       </c>
       <c r="F29" s="26"/>
@@ -9638,7 +9634,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.8518352538547358</v>
       </c>
-      <c r="E30" s="311"/>
+      <c r="E30" s="309"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.81850227626525374</v>
@@ -9686,68 +9682,68 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10"/>
-      <c r="E31" s="311"/>
+      <c r="E31" s="309"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10"/>
       <c r="B32" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="311"/>
+      <c r="E32" s="309"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="C33" s="205">
+      <c r="C33" s="204">
         <f>AVERAGE(G33:H33)</f>
         <v>-175999.5</v>
       </c>
-      <c r="E33" s="309" t="s">
+      <c r="E33" s="307" t="s">
         <v>370</v>
       </c>
-      <c r="G33" s="198">
+      <c r="G33" s="197">
         <f>Data!C41</f>
         <v>-188071</v>
       </c>
-      <c r="H33" s="198">
+      <c r="H33" s="197">
         <f>Data!D41</f>
         <v>-163928</v>
       </c>
-      <c r="I33" s="198">
+      <c r="I33" s="197">
         <f>Data!E41</f>
         <v>-705390</v>
       </c>
-      <c r="J33" s="198">
+      <c r="J33" s="197">
         <f>Data!F41</f>
         <v>-456610</v>
       </c>
-      <c r="K33" s="198">
+      <c r="K33" s="197">
         <f>Data!G41</f>
         <v>-396643</v>
       </c>
-      <c r="L33" s="198" t="str">
+      <c r="L33" s="197" t="str">
         <f>Data!H41</f>
         <v/>
       </c>
-      <c r="M33" s="198" t="str">
+      <c r="M33" s="197" t="str">
         <f>Data!I41</f>
         <v/>
       </c>
-      <c r="N33" s="198" t="str">
+      <c r="N33" s="197" t="str">
         <f>Data!J41</f>
         <v/>
       </c>
-      <c r="O33" s="198" t="str">
+      <c r="O33" s="197" t="str">
         <f>Data!K41</f>
         <v/>
       </c>
-      <c r="P33" s="198" t="str">
+      <c r="P33" s="197" t="str">
         <f>Data!L41</f>
         <v/>
       </c>
-      <c r="Q33" s="198" t="str">
+      <c r="Q33" s="197" t="str">
         <f>Data!M41</f>
         <v/>
       </c>
@@ -9757,56 +9753,56 @@
       <c r="B34" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="205">
+      <c r="C34" s="204">
         <f>AVERAGE(G34:J34)</f>
         <v>0</v>
       </c>
       <c r="D34" s="59"/>
-      <c r="E34" s="309" t="s">
+      <c r="E34" s="307" t="s">
         <v>370</v>
       </c>
       <c r="F34" s="59"/>
-      <c r="G34" s="187">
+      <c r="G34" s="186">
         <f>Data!C42</f>
         <v>0</v>
       </c>
-      <c r="H34" s="187">
+      <c r="H34" s="186">
         <f>Data!D42</f>
         <v>0</v>
       </c>
-      <c r="I34" s="187">
+      <c r="I34" s="186">
         <f>Data!E42</f>
         <v>0</v>
       </c>
-      <c r="J34" s="187">
+      <c r="J34" s="186">
         <f>Data!F42</f>
         <v>0</v>
       </c>
-      <c r="K34" s="187">
+      <c r="K34" s="186">
         <f>Data!G42</f>
         <v>0</v>
       </c>
-      <c r="L34" s="187" t="str">
+      <c r="L34" s="186" t="str">
         <f>Data!H42</f>
         <v/>
       </c>
-      <c r="M34" s="187" t="str">
+      <c r="M34" s="186" t="str">
         <f>Data!I42</f>
         <v/>
       </c>
-      <c r="N34" s="187" t="str">
+      <c r="N34" s="186" t="str">
         <f>Data!J42</f>
         <v/>
       </c>
-      <c r="O34" s="187" t="str">
+      <c r="O34" s="186" t="str">
         <f>Data!K42</f>
         <v/>
       </c>
-      <c r="P34" s="187" t="str">
+      <c r="P34" s="186" t="str">
         <f>Data!L42</f>
         <v/>
       </c>
-      <c r="Q34" s="187" t="str">
+      <c r="Q34" s="186" t="str">
         <f>Data!M42</f>
         <v/>
       </c>
@@ -9816,68 +9812,68 @@
       <c r="B35" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="188">
+      <c r="C35" s="187">
         <f>C33+C34</f>
         <v>-175999.5</v>
       </c>
       <c r="D35" s="59"/>
-      <c r="E35" s="310"/>
+      <c r="E35" s="308"/>
       <c r="F35" s="59"/>
-      <c r="G35" s="188">
+      <c r="G35" s="187">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
         <v>-188071</v>
       </c>
-      <c r="H35" s="188">
+      <c r="H35" s="187">
         <f t="shared" si="14"/>
         <v>-163928</v>
       </c>
-      <c r="I35" s="188">
+      <c r="I35" s="187">
         <f t="shared" si="14"/>
         <v>-705390</v>
       </c>
-      <c r="J35" s="188">
+      <c r="J35" s="187">
         <f t="shared" si="14"/>
         <v>-456610</v>
       </c>
-      <c r="K35" s="188">
+      <c r="K35" s="187">
         <f t="shared" si="14"/>
         <v>-396643</v>
       </c>
-      <c r="L35" s="188" t="str">
+      <c r="L35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="M35" s="188" t="str">
+      <c r="M35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="N35" s="188" t="str">
+      <c r="N35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="O35" s="188" t="str">
+      <c r="O35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="P35" s="188" t="str">
+      <c r="P35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="Q35" s="188" t="str">
+      <c r="Q35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="10"/>
-      <c r="E36" s="311"/>
+      <c r="E36" s="309"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10"/>
       <c r="B37" s="65" t="s">
         <v>212</v>
       </c>
-      <c r="E37" s="311"/>
+      <c r="E37" s="309"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="10"/>
@@ -9890,7 +9886,7 @@
         <v>0.11115379737817763</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="308"/>
+      <c r="E38" s="306"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -9948,7 +9944,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="308"/>
+      <c r="E39" s="306"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -10004,7 +10000,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>0.11115379737817763</v>
       </c>
-      <c r="E40" s="311"/>
+      <c r="E40" s="309"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>0.11641046432097352</v>
@@ -10052,25 +10048,25 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="10"/>
-      <c r="E41" s="311"/>
+      <c r="E41" s="309"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10"/>
       <c r="B42" s="65" t="s">
         <v>213</v>
       </c>
-      <c r="E42" s="311"/>
+      <c r="E42" s="309"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="C43" s="305">
+      <c r="C43" s="303">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="308" t="s">
+      <c r="E43" s="306" t="s">
         <v>371</v>
       </c>
       <c r="F43" s="27"/>
@@ -10150,59 +10146,59 @@
       <c r="B46" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="E46" s="311"/>
+      <c r="E46" s="309"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C47" s="198">
+      <c r="C47" s="197">
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-1003</v>
       </c>
-      <c r="E47" s="311"/>
-      <c r="G47" s="198">
+      <c r="E47" s="309"/>
+      <c r="G47" s="197">
         <f>Data!C51</f>
         <v>-1003</v>
       </c>
-      <c r="H47" s="198">
+      <c r="H47" s="197">
         <f>Data!D51</f>
         <v>-863</v>
       </c>
-      <c r="I47" s="198">
+      <c r="I47" s="197">
         <f>Data!E51</f>
         <v>-1613</v>
       </c>
-      <c r="J47" s="198">
+      <c r="J47" s="197">
         <f>Data!F51</f>
         <v>-2645</v>
       </c>
-      <c r="K47" s="198">
+      <c r="K47" s="197">
         <f>Data!G51</f>
         <v>-299</v>
       </c>
-      <c r="L47" s="198" t="str">
+      <c r="L47" s="197" t="str">
         <f>Data!H51</f>
         <v/>
       </c>
-      <c r="M47" s="198" t="str">
+      <c r="M47" s="197" t="str">
         <f>Data!I51</f>
         <v/>
       </c>
-      <c r="N47" s="198" t="str">
+      <c r="N47" s="197" t="str">
         <f>Data!J51</f>
         <v/>
       </c>
-      <c r="O47" s="198" t="str">
+      <c r="O47" s="197" t="str">
         <f>Data!K51</f>
         <v/>
       </c>
-      <c r="P47" s="198" t="str">
+      <c r="P47" s="197" t="str">
         <f>Data!L51</f>
         <v/>
       </c>
-      <c r="Q47" s="198" t="str">
+      <c r="Q47" s="197" t="str">
         <f>Data!M51</f>
         <v/>
       </c>
@@ -10212,109 +10208,109 @@
       <c r="B48" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="C48" s="198">
+      <c r="C48" s="197">
         <f>BS!D75*C53</f>
         <v>21115.955148098936</v>
       </c>
-      <c r="E48" s="311"/>
-      <c r="G48" s="338">
+      <c r="E48" s="309"/>
+      <c r="G48" s="336">
         <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
         <v>21115.955148098936</v>
       </c>
-      <c r="H48" s="338">
+      <c r="H48" s="336">
         <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
         <v>12974.846771442135</v>
       </c>
-      <c r="I48" s="338">
+      <c r="I48" s="336">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J48" s="338">
+      <c r="J48" s="336">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K48" s="338">
+      <c r="K48" s="336">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="338" t="str">
+      <c r="L48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="M48" s="338" t="str">
+      <c r="M48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="N48" s="338" t="str">
+      <c r="N48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="O48" s="338" t="str">
+      <c r="O48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="P48" s="338" t="str">
+      <c r="P48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="338" t="str">
+      <c r="Q48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
-      <c r="B49" s="333" t="s">
+      <c r="B49" s="331" t="s">
         <v>379</v>
       </c>
-      <c r="C49" s="334">
+      <c r="C49" s="332">
         <f>BS!$C$66*C53</f>
         <v>73805</v>
       </c>
-      <c r="D49" s="335"/>
-      <c r="E49" s="336"/>
-      <c r="F49" s="335"/>
-      <c r="G49" s="334">
+      <c r="D49" s="333"/>
+      <c r="E49" s="334"/>
+      <c r="F49" s="333"/>
+      <c r="G49" s="332">
         <f>Data!C52</f>
         <v>73805</v>
       </c>
-      <c r="H49" s="334">
+      <c r="H49" s="332">
         <f>Data!D52</f>
         <v>45350</v>
       </c>
-      <c r="I49" s="334">
+      <c r="I49" s="332">
         <f>Data!E52</f>
         <v>0</v>
       </c>
-      <c r="J49" s="334">
+      <c r="J49" s="332">
         <f>Data!F52</f>
         <v>0</v>
       </c>
-      <c r="K49" s="334">
+      <c r="K49" s="332">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="334" t="str">
+      <c r="L49" s="332" t="str">
         <f>Data!H52</f>
         <v/>
       </c>
-      <c r="M49" s="334" t="str">
+      <c r="M49" s="332" t="str">
         <f>Data!I52</f>
         <v/>
       </c>
-      <c r="N49" s="334" t="str">
+      <c r="N49" s="332" t="str">
         <f>Data!J52</f>
         <v/>
       </c>
-      <c r="O49" s="334" t="str">
+      <c r="O49" s="332" t="str">
         <f>Data!K52</f>
         <v/>
       </c>
-      <c r="P49" s="334" t="str">
+      <c r="P49" s="332" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="334" t="str">
+      <c r="Q49" s="332" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -10324,66 +10320,66 @@
       <c r="B50" s="71" t="s">
         <v>72</v>
       </c>
-      <c r="C50" s="188">
+      <c r="C50" s="187">
         <f>C47+C48</f>
         <v>20112.955148098936</v>
       </c>
-      <c r="E50" s="311"/>
-      <c r="G50" s="188">
+      <c r="E50" s="309"/>
+      <c r="G50" s="187">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>20112.955148098936</v>
       </c>
-      <c r="H50" s="188">
+      <c r="H50" s="187">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
         <v>12111.846771442135</v>
       </c>
-      <c r="I50" s="188">
+      <c r="I50" s="187">
         <f t="shared" si="20"/>
         <v>-1613</v>
       </c>
-      <c r="J50" s="188">
+      <c r="J50" s="187">
         <f t="shared" si="20"/>
         <v>-2645</v>
       </c>
-      <c r="K50" s="188">
+      <c r="K50" s="187">
         <f t="shared" si="20"/>
         <v>-299</v>
       </c>
-      <c r="L50" s="188" t="str">
+      <c r="L50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="M50" s="188" t="str">
+      <c r="M50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="N50" s="188" t="str">
+      <c r="N50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="O50" s="188" t="str">
+      <c r="O50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="P50" s="188" t="str">
+      <c r="P50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="Q50" s="188" t="str">
+      <c r="Q50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="10"/>
-      <c r="E51" s="311"/>
+      <c r="E51" s="309"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="10"/>
       <c r="B52" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="E52" s="311"/>
+      <c r="E52" s="309"/>
       <c r="G52" s="100" t="s">
         <v>224</v>
       </c>
@@ -10397,23 +10393,23 @@
         <f>G53</f>
         <v>2.7696969151119136E-2</v>
       </c>
-      <c r="E53" s="308" t="s">
+      <c r="E53" s="306" t="s">
         <v>372</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
         <v>2.7696969151119136E-2</v>
       </c>
-      <c r="H53" s="174"/>
-      <c r="I53" s="174"/>
-      <c r="J53" s="174"/>
-      <c r="K53" s="174"/>
-      <c r="L53" s="174"/>
-      <c r="M53" s="174"/>
-      <c r="N53" s="174"/>
-      <c r="O53" s="174"/>
-      <c r="P53" s="174"/>
-      <c r="Q53" s="174"/>
+      <c r="H53" s="173"/>
+      <c r="I53" s="173"/>
+      <c r="J53" s="173"/>
+      <c r="K53" s="173"/>
+      <c r="L53" s="173"/>
+      <c r="M53" s="173"/>
+      <c r="N53" s="173"/>
+      <c r="O53" s="173"/>
+      <c r="P53" s="173"/>
+      <c r="Q53" s="173"/>
     </row>
     <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="10"/>
@@ -10424,23 +10420,23 @@
         <f>G54</f>
         <v>2.9500867672578604E-2</v>
       </c>
-      <c r="E54" s="308" t="s">
+      <c r="E54" s="306" t="s">
         <v>373</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
         <v>2.9500867672578604E-2</v>
       </c>
-      <c r="H54" s="174"/>
-      <c r="I54" s="174"/>
-      <c r="J54" s="174"/>
-      <c r="K54" s="174"/>
-      <c r="L54" s="174"/>
-      <c r="M54" s="174"/>
-      <c r="N54" s="174"/>
-      <c r="O54" s="174"/>
-      <c r="P54" s="174"/>
-      <c r="Q54" s="174"/>
+      <c r="H54" s="173"/>
+      <c r="I54" s="173"/>
+      <c r="J54" s="173"/>
+      <c r="K54" s="173"/>
+      <c r="L54" s="173"/>
+      <c r="M54" s="173"/>
+      <c r="N54" s="173"/>
+      <c r="O54" s="173"/>
+      <c r="P54" s="173"/>
+      <c r="Q54" s="173"/>
     </row>
     <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="10"/>
@@ -10451,7 +10447,7 @@
         <f>-C8/C47</f>
         <v>58.427380396471271</v>
       </c>
-      <c r="E55" s="311"/>
+      <c r="E55" s="309"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>104.839481555334</v>
@@ -10499,14 +10495,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="10"/>
-      <c r="E56" s="311"/>
+      <c r="E56" s="309"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="10"/>
       <c r="B57" s="65" t="s">
         <v>173</v>
       </c>
-      <c r="E57" s="311"/>
+      <c r="E57" s="309"/>
       <c r="G57" s="100" t="s">
         <v>224</v>
       </c>
@@ -10516,52 +10512,52 @@
       <c r="B58" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="C58" s="198">
+      <c r="C58" s="197">
         <f>BS!$C79*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="311"/>
-      <c r="G58" s="198">
+      <c r="E58" s="309"/>
+      <c r="G58" s="197">
         <f>Data!C56</f>
         <v>0</v>
       </c>
-      <c r="H58" s="198">
+      <c r="H58" s="197">
         <f>Data!D56</f>
         <v>0</v>
       </c>
-      <c r="I58" s="198">
+      <c r="I58" s="197">
         <f>Data!E56</f>
         <v>0</v>
       </c>
-      <c r="J58" s="198">
+      <c r="J58" s="197">
         <f>Data!F56</f>
         <v>0</v>
       </c>
-      <c r="K58" s="198">
+      <c r="K58" s="197">
         <f>Data!G56</f>
         <v>0</v>
       </c>
-      <c r="L58" s="198" t="str">
+      <c r="L58" s="197" t="str">
         <f>Data!H56</f>
         <v/>
       </c>
-      <c r="M58" s="198" t="str">
+      <c r="M58" s="197" t="str">
         <f>Data!I56</f>
         <v/>
       </c>
-      <c r="N58" s="198" t="str">
+      <c r="N58" s="197" t="str">
         <f>Data!J56</f>
         <v/>
       </c>
-      <c r="O58" s="198" t="str">
+      <c r="O58" s="197" t="str">
         <f>Data!K56</f>
         <v/>
       </c>
-      <c r="P58" s="198" t="str">
+      <c r="P58" s="197" t="str">
         <f>Data!L56</f>
         <v/>
       </c>
-      <c r="Q58" s="198" t="str">
+      <c r="Q58" s="197" t="str">
         <f>Data!M56</f>
         <v/>
       </c>
@@ -10571,52 +10567,52 @@
       <c r="B59" s="40" t="s">
         <v>164</v>
       </c>
-      <c r="C59" s="198">
+      <c r="C59" s="197">
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="311"/>
-      <c r="G59" s="198">
+      <c r="E59" s="309"/>
+      <c r="G59" s="197">
         <f>Data!C55</f>
         <v>0</v>
       </c>
-      <c r="H59" s="198">
+      <c r="H59" s="197">
         <f>Data!D55</f>
         <v>0</v>
       </c>
-      <c r="I59" s="198">
+      <c r="I59" s="197">
         <f>Data!E55</f>
         <v>0</v>
       </c>
-      <c r="J59" s="198">
+      <c r="J59" s="197">
         <f>Data!F55</f>
         <v>0</v>
       </c>
-      <c r="K59" s="198">
+      <c r="K59" s="197">
         <f>Data!G55</f>
         <v>0</v>
       </c>
-      <c r="L59" s="198" t="str">
+      <c r="L59" s="197" t="str">
         <f>Data!H55</f>
         <v/>
       </c>
-      <c r="M59" s="198" t="str">
+      <c r="M59" s="197" t="str">
         <f>Data!I55</f>
         <v/>
       </c>
-      <c r="N59" s="198" t="str">
+      <c r="N59" s="197" t="str">
         <f>Data!J55</f>
         <v/>
       </c>
-      <c r="O59" s="198" t="str">
+      <c r="O59" s="197" t="str">
         <f>Data!K55</f>
         <v/>
       </c>
-      <c r="P59" s="198" t="str">
+      <c r="P59" s="197" t="str">
         <f>Data!L55</f>
         <v/>
       </c>
-      <c r="Q59" s="198" t="str">
+      <c r="Q59" s="197" t="str">
         <f>Data!M55</f>
         <v/>
       </c>
@@ -10626,52 +10622,52 @@
       <c r="B60" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="C60" s="198">
+      <c r="C60" s="197">
         <f>BS!$C81*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="311"/>
-      <c r="G60" s="198">
+      <c r="E60" s="309"/>
+      <c r="G60" s="197">
         <f>Data!C57</f>
         <v>0</v>
       </c>
-      <c r="H60" s="198">
+      <c r="H60" s="197">
         <f>Data!D57</f>
         <v>0</v>
       </c>
-      <c r="I60" s="198">
+      <c r="I60" s="197">
         <f>Data!E57</f>
         <v>0</v>
       </c>
-      <c r="J60" s="198">
+      <c r="J60" s="197">
         <f>Data!F57</f>
         <v>0</v>
       </c>
-      <c r="K60" s="198">
+      <c r="K60" s="197">
         <f>Data!G57</f>
         <v>0</v>
       </c>
-      <c r="L60" s="198" t="str">
+      <c r="L60" s="197" t="str">
         <f>Data!H57</f>
         <v/>
       </c>
-      <c r="M60" s="198" t="str">
+      <c r="M60" s="197" t="str">
         <f>Data!I57</f>
         <v/>
       </c>
-      <c r="N60" s="198" t="str">
+      <c r="N60" s="197" t="str">
         <f>Data!J57</f>
         <v/>
       </c>
-      <c r="O60" s="198" t="str">
+      <c r="O60" s="197" t="str">
         <f>Data!K57</f>
         <v/>
       </c>
-      <c r="P60" s="198" t="str">
+      <c r="P60" s="197" t="str">
         <f>Data!L57</f>
         <v/>
       </c>
-      <c r="Q60" s="198" t="str">
+      <c r="Q60" s="197" t="str">
         <f>Data!M57</f>
         <v/>
       </c>
@@ -10681,52 +10677,52 @@
       <c r="B61" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="C61" s="188">
+      <c r="C61" s="187">
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="311"/>
-      <c r="G61" s="188">
+      <c r="E61" s="309"/>
+      <c r="G61" s="187">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
       </c>
-      <c r="H61" s="188">
+      <c r="H61" s="187">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I61" s="188">
+      <c r="I61" s="187">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J61" s="188">
+      <c r="J61" s="187">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K61" s="188">
+      <c r="K61" s="187">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L61" s="188" t="str">
+      <c r="L61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="M61" s="188" t="str">
+      <c r="M61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="N61" s="188" t="str">
+      <c r="N61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="O61" s="188" t="str">
+      <c r="O61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="P61" s="188" t="str">
+      <c r="P61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="Q61" s="188" t="str">
+      <c r="Q61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -10736,53 +10732,53 @@
       <c r="B62" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="C62" s="306">
-        <v>0</v>
-      </c>
-      <c r="E62" s="309" t="s">
+      <c r="C62" s="304">
+        <v>0</v>
+      </c>
+      <c r="E62" s="307" t="s">
         <v>374</v>
       </c>
-      <c r="G62" s="198">
+      <c r="G62" s="197">
         <f>Data!C58</f>
         <v>39310</v>
       </c>
-      <c r="H62" s="198">
+      <c r="H62" s="197">
         <f>Data!D58</f>
         <v>39794</v>
       </c>
-      <c r="I62" s="198">
+      <c r="I62" s="197">
         <f>Data!E58</f>
         <v>-74687.603451000003</v>
       </c>
-      <c r="J62" s="198">
+      <c r="J62" s="197">
         <f>Data!F58</f>
         <v>-273680.96301000001</v>
       </c>
-      <c r="K62" s="198">
+      <c r="K62" s="197">
         <f>Data!G58</f>
         <v>-202918</v>
       </c>
-      <c r="L62" s="198" t="str">
+      <c r="L62" s="197" t="str">
         <f>Data!H58</f>
         <v/>
       </c>
-      <c r="M62" s="198" t="str">
+      <c r="M62" s="197" t="str">
         <f>Data!I58</f>
         <v/>
       </c>
-      <c r="N62" s="198" t="str">
+      <c r="N62" s="197" t="str">
         <f>Data!J58</f>
         <v/>
       </c>
-      <c r="O62" s="198" t="str">
+      <c r="O62" s="197" t="str">
         <f>Data!K58</f>
         <v/>
       </c>
-      <c r="P62" s="198" t="str">
+      <c r="P62" s="197" t="str">
         <f>Data!L58</f>
         <v/>
       </c>
-      <c r="Q62" s="198" t="str">
+      <c r="Q62" s="197" t="str">
         <f>Data!M58</f>
         <v/>
       </c>
@@ -10792,66 +10788,66 @@
       <c r="B63" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="C63" s="188">
+      <c r="C63" s="187">
         <f>C61+C62</f>
         <v>0</v>
       </c>
-      <c r="E63" s="311"/>
-      <c r="G63" s="188">
+      <c r="E63" s="309"/>
+      <c r="G63" s="187">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>39310</v>
       </c>
-      <c r="H63" s="188">
+      <c r="H63" s="187">
         <f t="shared" si="23"/>
         <v>39794</v>
       </c>
-      <c r="I63" s="188">
+      <c r="I63" s="187">
         <f t="shared" si="23"/>
         <v>-74687.603451000003</v>
       </c>
-      <c r="J63" s="188">
+      <c r="J63" s="187">
         <f t="shared" si="23"/>
         <v>-273680.96301000001</v>
       </c>
-      <c r="K63" s="188">
+      <c r="K63" s="187">
         <f t="shared" si="23"/>
         <v>-202918</v>
       </c>
-      <c r="L63" s="188" t="str">
+      <c r="L63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="M63" s="188" t="str">
+      <c r="M63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="N63" s="188" t="str">
+      <c r="N63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="O63" s="188" t="str">
+      <c r="O63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="P63" s="188" t="str">
+      <c r="P63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="Q63" s="188" t="str">
+      <c r="Q63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="10"/>
-      <c r="E64" s="311"/>
+      <c r="E64" s="309"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="10"/>
       <c r="B65" s="99" t="s">
         <v>174</v>
       </c>
-      <c r="E65" s="311"/>
+      <c r="E65" s="309"/>
       <c r="G65" s="100" t="s">
         <v>224</v>
       </c>
@@ -10861,75 +10857,75 @@
       <c r="B66" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="C66" s="181">
+      <c r="C66" s="180">
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="311"/>
+      <c r="E66" s="309"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
       </c>
-      <c r="H66" s="180"/>
-      <c r="I66" s="180"/>
-      <c r="J66" s="180"/>
-      <c r="K66" s="180"/>
-      <c r="L66" s="180"/>
-      <c r="M66" s="180"/>
-      <c r="N66" s="180"/>
-      <c r="O66" s="180"/>
-      <c r="P66" s="180"/>
-      <c r="Q66" s="180"/>
+      <c r="H66" s="179"/>
+      <c r="I66" s="179"/>
+      <c r="J66" s="179"/>
+      <c r="K66" s="179"/>
+      <c r="L66" s="179"/>
+      <c r="M66" s="179"/>
+      <c r="N66" s="179"/>
+      <c r="O66" s="179"/>
+      <c r="P66" s="179"/>
+      <c r="Q66" s="179"/>
     </row>
     <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="10"/>
       <c r="B67" s="108" t="s">
         <v>162</v>
       </c>
-      <c r="C67" s="181">
+      <c r="C67" s="180">
         <f>G67</f>
         <v>0</v>
       </c>
-      <c r="E67" s="311"/>
+      <c r="E67" s="309"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>0</v>
       </c>
-      <c r="H67" s="180"/>
-      <c r="I67" s="180"/>
-      <c r="J67" s="180"/>
-      <c r="K67" s="180"/>
-      <c r="L67" s="180"/>
-      <c r="M67" s="180"/>
-      <c r="N67" s="180"/>
-      <c r="O67" s="180"/>
-      <c r="P67" s="180"/>
-      <c r="Q67" s="180"/>
+      <c r="H67" s="179"/>
+      <c r="I67" s="179"/>
+      <c r="J67" s="179"/>
+      <c r="K67" s="179"/>
+      <c r="L67" s="179"/>
+      <c r="M67" s="179"/>
+      <c r="N67" s="179"/>
+      <c r="O67" s="179"/>
+      <c r="P67" s="179"/>
+      <c r="Q67" s="179"/>
     </row>
     <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="10"/>
       <c r="B68" s="108" t="s">
         <v>163</v>
       </c>
-      <c r="C68" s="181">
+      <c r="C68" s="180">
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="311"/>
+      <c r="E68" s="309"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$81,0)</f>
         <v>0</v>
       </c>
-      <c r="H68" s="180"/>
-      <c r="I68" s="180"/>
-      <c r="J68" s="180"/>
-      <c r="K68" s="180"/>
-      <c r="L68" s="180"/>
-      <c r="M68" s="180"/>
-      <c r="N68" s="180"/>
-      <c r="O68" s="180"/>
-      <c r="P68" s="180"/>
-      <c r="Q68" s="180"/>
+      <c r="H68" s="179"/>
+      <c r="I68" s="179"/>
+      <c r="J68" s="179"/>
+      <c r="K68" s="179"/>
+      <c r="L68" s="179"/>
+      <c r="M68" s="179"/>
+      <c r="N68" s="179"/>
+      <c r="O68" s="179"/>
+      <c r="P68" s="179"/>
+      <c r="Q68" s="179"/>
     </row>
     <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="10"/>
@@ -10941,22 +10937,22 @@
         <v>0</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="316"/>
+      <c r="E69" s="314"/>
       <c r="F69" s="9"/>
       <c r="G69" s="72">
         <f>G61/BS!C70</f>
         <v>0</v>
       </c>
-      <c r="H69" s="180"/>
-      <c r="I69" s="180"/>
-      <c r="J69" s="180"/>
-      <c r="K69" s="180"/>
-      <c r="L69" s="180"/>
-      <c r="M69" s="180"/>
-      <c r="N69" s="180"/>
-      <c r="O69" s="180"/>
-      <c r="P69" s="180"/>
-      <c r="Q69" s="180"/>
+      <c r="H69" s="179"/>
+      <c r="I69" s="179"/>
+      <c r="J69" s="179"/>
+      <c r="K69" s="179"/>
+      <c r="L69" s="179"/>
+      <c r="M69" s="179"/>
+      <c r="N69" s="179"/>
+      <c r="O69" s="179"/>
+      <c r="P69" s="179"/>
+      <c r="Q69" s="179"/>
     </row>
     <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="10"/>
@@ -10991,7 +10987,7 @@
       </c>
       <c r="C72" s="63"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="308"/>
+      <c r="E72" s="306"/>
       <c r="F72" s="27"/>
       <c r="G72" s="100"/>
       <c r="H72" s="12"/>
@@ -11015,7 +11011,7 @@
         <v>0.8518352538547358</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="308"/>
+      <c r="E73" s="306"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -11072,7 +11068,7 @@
         <v>0.1481647461452642</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="308"/>
+      <c r="E74" s="306"/>
       <c r="F74" s="27"/>
       <c r="G74" s="66">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -11129,7 +11125,7 @@
         <v>0.11115379737817763</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="308"/>
+      <c r="E75" s="306"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -11186,7 +11182,7 @@
         <v>3.7010948767086591E-2</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="308"/>
+      <c r="E76" s="306"/>
       <c r="F76" s="27"/>
       <c r="G76" s="66">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -11243,7 +11239,7 @@
         <v>2.2719648106287585E-2</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="308"/>
+      <c r="E77" s="306"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -11300,7 +11296,7 @@
         <v>2.2719648106287585E-2</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="309" t="s">
+      <c r="E78" s="307" t="s">
         <v>391</v>
       </c>
       <c r="F78" s="27"/>
@@ -11359,7 +11355,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="308"/>
+      <c r="E79" s="306"/>
       <c r="F79" s="27"/>
       <c r="G79" s="66">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -11416,7 +11412,7 @@
         <v>1.270248688892959E-2</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="308"/>
+      <c r="E80" s="306"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -11473,7 +11469,7 @@
         <v>4.9713435656016179E-2</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="308"/>
+      <c r="E81" s="306"/>
       <c r="F81" s="27"/>
       <c r="G81" s="66">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -11530,7 +11526,7 @@
         <v>1.2428358914004045E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="308"/>
+      <c r="E82" s="306"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -11583,12 +11579,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="307">
+      <c r="C83" s="305">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>1.3197490690642218E-3</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="308"/>
+      <c r="E83" s="306"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -11645,7 +11641,7 @@
         <v>3.5965327672947911E-2</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="308"/>
+      <c r="E84" s="306"/>
       <c r="F84" s="27"/>
       <c r="G84" s="66">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -11697,26 +11693,26 @@
       <c r="B85" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C85" s="307">
+      <c r="C85" s="305">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="310" t="str">
+      <c r="E85" s="308" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="260"/>
-      <c r="H85" s="260"/>
-      <c r="I85" s="260"/>
-      <c r="J85" s="260"/>
-      <c r="K85" s="260"/>
-      <c r="L85" s="260"/>
-      <c r="M85" s="260"/>
-      <c r="N85" s="260"/>
-      <c r="O85" s="260"/>
-      <c r="P85" s="260"/>
-      <c r="Q85" s="260"/>
+      <c r="G85" s="259"/>
+      <c r="H85" s="259"/>
+      <c r="I85" s="259"/>
+      <c r="J85" s="259"/>
+      <c r="K85" s="259"/>
+      <c r="L85" s="259"/>
+      <c r="M85" s="259"/>
+      <c r="N85" s="259"/>
+      <c r="O85" s="259"/>
+      <c r="P85" s="259"/>
+      <c r="Q85" s="259"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="10"/>
@@ -11726,21 +11722,21 @@
       <c r="C86" s="79">
         <v>0</v>
       </c>
-      <c r="E86" s="310" t="str">
+      <c r="E86" s="308" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
-      <c r="G86" s="174"/>
-      <c r="H86" s="174"/>
-      <c r="I86" s="174"/>
-      <c r="J86" s="174"/>
-      <c r="K86" s="174"/>
-      <c r="L86" s="174"/>
-      <c r="M86" s="174"/>
-      <c r="N86" s="174"/>
-      <c r="O86" s="174"/>
-      <c r="P86" s="174"/>
-      <c r="Q86" s="174"/>
+      <c r="G86" s="173"/>
+      <c r="H86" s="173"/>
+      <c r="I86" s="173"/>
+      <c r="J86" s="173"/>
+      <c r="K86" s="173"/>
+      <c r="L86" s="173"/>
+      <c r="M86" s="173"/>
+      <c r="N86" s="173"/>
+      <c r="O86" s="173"/>
+      <c r="P86" s="173"/>
+      <c r="Q86" s="173"/>
     </row>
     <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="10"/>
@@ -11752,7 +11748,7 @@
         <v>3.5965327672947911E-2</v>
       </c>
       <c r="D87" s="77"/>
-      <c r="E87" s="308"/>
+      <c r="E87" s="306"/>
       <c r="F87" s="77"/>
       <c r="G87" s="66">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -11801,14 +11797,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="10"/>
-      <c r="E88" s="311"/>
+      <c r="E88" s="309"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="10"/>
       <c r="B89" s="65" t="s">
         <v>219</v>
       </c>
-      <c r="E89" s="311"/>
+      <c r="E89" s="309"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="10"/>
@@ -11820,7 +11816,7 @@
         <f>G90</f>
         <v>0.1178</v>
       </c>
-      <c r="E90" s="311"/>
+      <c r="E90" s="309"/>
       <c r="G90" s="116">
         <f>Data!C64</f>
         <v>0.1178</v>
@@ -11876,7 +11872,7 @@
         <f>C90*Common_Shares/$C$3</f>
         <v>157066.6863</v>
       </c>
-      <c r="E91" s="311"/>
+      <c r="E91" s="309"/>
       <c r="G91" s="76">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
         <v>157066.6863</v>
@@ -11931,48 +11927,48 @@
         <f>C90/(C19*$C$3/Common_Shares)</f>
         <v>2.7581185559608659</v>
       </c>
-      <c r="E92" s="311"/>
-      <c r="G92" s="175">
+      <c r="E92" s="309"/>
+      <c r="G92" s="174">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
         <v>1.5820424578480456</v>
       </c>
-      <c r="H92" s="175">
+      <c r="H92" s="174">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="I92" s="175">
+      <c r="I92" s="174">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="J92" s="175">
+      <c r="J92" s="174">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="K92" s="175">
+      <c r="K92" s="174">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="L92" s="175" t="str">
+      <c r="L92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="M92" s="175" t="str">
+      <c r="M92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="N92" s="175" t="str">
+      <c r="N92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="O92" s="175" t="str">
+      <c r="O92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="P92" s="175" t="str">
+      <c r="P92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="Q92" s="175" t="str">
+      <c r="Q92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
@@ -11986,7 +11982,7 @@
         <f>C90/Market_Price</f>
         <v>5.4036697247706419E-2</v>
       </c>
-      <c r="E93" s="311"/>
+      <c r="E93" s="309"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>5.4036697247706419E-2</v>
@@ -12034,16 +12030,16 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="10"/>
-      <c r="E94" s="311"/>
+      <c r="E94" s="309"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="10"/>
-      <c r="B95" s="162" t="s">
+      <c r="B95" s="161" t="s">
         <v>89</v>
       </c>
       <c r="C95" s="63"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="308"/>
+      <c r="E95" s="306"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -12067,7 +12063,7 @@
         <v>-1.992949922164422E-2</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="308"/>
+      <c r="E96" s="306"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -12124,7 +12120,7 @@
         <v>-0.46058945186119171</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="308"/>
+      <c r="E97" s="306"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -12202,7 +12198,7 @@
       <c r="B100" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="E100" s="311"/>
+      <c r="E100" s="309"/>
       <c r="G100" s="100" t="s">
         <v>224</v>
       </c>
@@ -12212,54 +12208,54 @@
       <c r="B101" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="C101" s="206">
+      <c r="C101" s="205">
         <f>BS!G32</f>
         <v>3670169</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="312"/>
+      <c r="E101" s="310"/>
       <c r="F101" s="26"/>
-      <c r="G101" s="187">
+      <c r="G101" s="186">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
         <v>3670169</v>
       </c>
-      <c r="H101" s="187">
+      <c r="H101" s="186">
         <f t="shared" si="42"/>
         <v>3559477</v>
       </c>
-      <c r="I101" s="187">
+      <c r="I101" s="186">
         <f t="shared" si="42"/>
         <v>3413258</v>
       </c>
-      <c r="J101" s="187">
+      <c r="J101" s="186">
         <f t="shared" si="42"/>
         <v>1603329</v>
       </c>
-      <c r="K101" s="187">
+      <c r="K101" s="186">
         <f t="shared" si="42"/>
         <v>1218998</v>
       </c>
-      <c r="L101" s="187" t="str">
+      <c r="L101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="M101" s="187" t="str">
+      <c r="M101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="N101" s="187" t="str">
+      <c r="N101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="O101" s="187" t="str">
+      <c r="O101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="P101" s="187" t="str">
+      <c r="P101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="Q101" s="187" t="str">
+      <c r="Q101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -12269,54 +12265,54 @@
       <c r="B102" s="95" t="s">
         <v>215</v>
       </c>
-      <c r="C102" s="207">
+      <c r="C102" s="206">
         <f>BS!C4</f>
         <v>180994</v>
       </c>
       <c r="D102" s="91"/>
-      <c r="E102" s="313"/>
+      <c r="E102" s="311"/>
       <c r="F102" s="91"/>
-      <c r="G102" s="189">
+      <c r="G102" s="188">
         <f>IF(G$4="","",Data!D76)</f>
         <v>0</v>
       </c>
-      <c r="H102" s="189">
+      <c r="H102" s="188">
         <f>IF(H$4="","",Data!E76)</f>
         <v>0</v>
       </c>
-      <c r="I102" s="189">
+      <c r="I102" s="188">
         <f>IF(I$4="","",Data!F76)</f>
         <v>0</v>
       </c>
-      <c r="J102" s="189">
+      <c r="J102" s="188">
         <f>IF(J$4="","",Data!G76)</f>
         <v>0</v>
       </c>
-      <c r="K102" s="189" t="str">
+      <c r="K102" s="188" t="str">
         <f>IF(K$4="","",Data!H76)</f>
         <v/>
       </c>
-      <c r="L102" s="189" t="str">
+      <c r="L102" s="188" t="str">
         <f>IF(L$4="","",Data!I76)</f>
         <v/>
       </c>
-      <c r="M102" s="189" t="str">
+      <c r="M102" s="188" t="str">
         <f>IF(M$4="","",Data!J76)</f>
         <v/>
       </c>
-      <c r="N102" s="189" t="str">
+      <c r="N102" s="188" t="str">
         <f>IF(N$4="","",Data!K76)</f>
         <v/>
       </c>
-      <c r="O102" s="189" t="str">
+      <c r="O102" s="188" t="str">
         <f>IF(O$4="","",Data!L76)</f>
         <v/>
       </c>
-      <c r="P102" s="189" t="str">
+      <c r="P102" s="188" t="str">
         <f>IF(P$4="","",Data!M76)</f>
         <v/>
       </c>
-      <c r="Q102" s="189" t="str">
+      <c r="Q102" s="188" t="str">
         <f>IF(Q$4="","",Data!N76)</f>
         <v/>
       </c>
@@ -12326,54 +12322,54 @@
       <c r="B103" s="95" t="s">
         <v>216</v>
       </c>
-      <c r="C103" s="207">
+      <c r="C103" s="206">
         <f>BS!C6+BS!C7</f>
         <v>158110</v>
       </c>
       <c r="D103" s="91"/>
-      <c r="E103" s="313"/>
+      <c r="E103" s="311"/>
       <c r="F103" s="91"/>
-      <c r="G103" s="189">
+      <c r="G103" s="188">
         <f>IF(G$4="","",Data!D77)</f>
         <v>0</v>
       </c>
-      <c r="H103" s="189">
+      <c r="H103" s="188">
         <f>IF(H$4="","",Data!E77)</f>
         <v>0</v>
       </c>
-      <c r="I103" s="189">
+      <c r="I103" s="188">
         <f>IF(I$4="","",Data!F77)</f>
         <v>0</v>
       </c>
-      <c r="J103" s="189">
+      <c r="J103" s="188">
         <f>IF(J$4="","",Data!G77)</f>
         <v>0</v>
       </c>
-      <c r="K103" s="189" t="str">
+      <c r="K103" s="188" t="str">
         <f>IF(K$4="","",Data!H77)</f>
         <v/>
       </c>
-      <c r="L103" s="189" t="str">
+      <c r="L103" s="188" t="str">
         <f>IF(L$4="","",Data!I77)</f>
         <v/>
       </c>
-      <c r="M103" s="189" t="str">
+      <c r="M103" s="188" t="str">
         <f>IF(M$4="","",Data!J77)</f>
         <v/>
       </c>
-      <c r="N103" s="189" t="str">
+      <c r="N103" s="188" t="str">
         <f>IF(N$4="","",Data!K77)</f>
         <v/>
       </c>
-      <c r="O103" s="189" t="str">
+      <c r="O103" s="188" t="str">
         <f>IF(O$4="","",Data!L77)</f>
         <v/>
       </c>
-      <c r="P103" s="189" t="str">
+      <c r="P103" s="188" t="str">
         <f>IF(P$4="","",Data!M77)</f>
         <v/>
       </c>
-      <c r="Q103" s="189" t="str">
+      <c r="Q103" s="188" t="str">
         <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
@@ -12383,54 +12379,54 @@
       <c r="B104" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="C104" s="206">
+      <c r="C104" s="205">
         <f>BS!G30</f>
         <v>642877</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="312"/>
+      <c r="E104" s="310"/>
       <c r="F104" s="26"/>
-      <c r="G104" s="187">
+      <c r="G104" s="186">
         <f>Data!C78</f>
         <v>642877</v>
       </c>
-      <c r="H104" s="187">
+      <c r="H104" s="186">
         <f>Data!D78</f>
         <v>734909</v>
       </c>
-      <c r="I104" s="187">
+      <c r="I104" s="186">
         <f>Data!E78</f>
         <v>677999</v>
       </c>
-      <c r="J104" s="187">
+      <c r="J104" s="186">
         <f>Data!F78</f>
         <v>1352795</v>
       </c>
-      <c r="K104" s="187">
+      <c r="K104" s="186">
         <f>Data!G78</f>
         <v>1205068</v>
       </c>
-      <c r="L104" s="187" t="str">
+      <c r="L104" s="186" t="str">
         <f>Data!H78</f>
         <v/>
       </c>
-      <c r="M104" s="187" t="str">
+      <c r="M104" s="186" t="str">
         <f>Data!I78</f>
         <v/>
       </c>
-      <c r="N104" s="187" t="str">
+      <c r="N104" s="186" t="str">
         <f>Data!J78</f>
         <v/>
       </c>
-      <c r="O104" s="187" t="str">
+      <c r="O104" s="186" t="str">
         <f>Data!K78</f>
         <v/>
       </c>
-      <c r="P104" s="187" t="str">
+      <c r="P104" s="186" t="str">
         <f>Data!L78</f>
         <v/>
       </c>
-      <c r="Q104" s="187" t="str">
+      <c r="Q104" s="186" t="str">
         <f>Data!M78</f>
         <v/>
       </c>
@@ -12440,61 +12436,61 @@
       <c r="B105" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="C105" s="206">
+      <c r="C105" s="205">
         <f>BS!G27</f>
         <v>3027292</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="312"/>
+      <c r="E105" s="310"/>
       <c r="F105" s="26"/>
-      <c r="G105" s="187">
+      <c r="G105" s="186">
         <f>Data!C79</f>
         <v>3027292</v>
       </c>
-      <c r="H105" s="187">
+      <c r="H105" s="186">
         <f>Data!D79</f>
         <v>2824568</v>
       </c>
-      <c r="I105" s="187">
+      <c r="I105" s="186">
         <f>Data!E79</f>
         <v>2735259</v>
       </c>
-      <c r="J105" s="187">
+      <c r="J105" s="186">
         <f>Data!F79</f>
         <v>250534</v>
       </c>
-      <c r="K105" s="187">
+      <c r="K105" s="186">
         <f>Data!G79</f>
         <v>13930</v>
       </c>
-      <c r="L105" s="187" t="str">
+      <c r="L105" s="186" t="str">
         <f>Data!H79</f>
         <v/>
       </c>
-      <c r="M105" s="187" t="str">
+      <c r="M105" s="186" t="str">
         <f>Data!I79</f>
         <v/>
       </c>
-      <c r="N105" s="187" t="str">
+      <c r="N105" s="186" t="str">
         <f>Data!J79</f>
         <v/>
       </c>
-      <c r="O105" s="187" t="str">
+      <c r="O105" s="186" t="str">
         <f>Data!K79</f>
         <v/>
       </c>
-      <c r="P105" s="187" t="str">
+      <c r="P105" s="186" t="str">
         <f>Data!L79</f>
         <v/>
       </c>
-      <c r="Q105" s="187" t="str">
+      <c r="Q105" s="186" t="str">
         <f>Data!M79</f>
         <v/>
       </c>
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="10"/>
-      <c r="E106" s="311"/>
+      <c r="E106" s="309"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="10"/>
@@ -12503,7 +12499,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="312"/>
+      <c r="E107" s="310"/>
       <c r="F107" s="26"/>
       <c r="G107" s="100" t="s">
         <v>224</v>
@@ -12529,7 +12525,7 @@
         <v>0.11430811111773545</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="312"/>
+      <c r="E108" s="310"/>
       <c r="F108" s="26"/>
       <c r="G108" s="97">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -12586,7 +12582,7 @@
         <v>9.9855550177492911E-2</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="312"/>
+      <c r="E109" s="310"/>
       <c r="F109" s="26"/>
       <c r="G109" s="97">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -12643,26 +12639,26 @@
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="312"/>
+      <c r="E110" s="310"/>
       <c r="F110" s="26"/>
       <c r="G110" s="97">
         <f>BS!$G$38/G$4</f>
         <v>0</v>
       </c>
-      <c r="H110" s="232"/>
-      <c r="I110" s="232"/>
-      <c r="J110" s="232"/>
-      <c r="K110" s="232"/>
-      <c r="L110" s="232"/>
-      <c r="M110" s="232"/>
-      <c r="N110" s="232"/>
-      <c r="O110" s="232"/>
-      <c r="P110" s="232"/>
-      <c r="Q110" s="232"/>
+      <c r="H110" s="231"/>
+      <c r="I110" s="231"/>
+      <c r="J110" s="231"/>
+      <c r="K110" s="231"/>
+      <c r="L110" s="231"/>
+      <c r="M110" s="231"/>
+      <c r="N110" s="231"/>
+      <c r="O110" s="231"/>
+      <c r="P110" s="231"/>
+      <c r="Q110" s="231"/>
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="10"/>
-      <c r="E111" s="311"/>
+      <c r="E111" s="309"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="10"/>
@@ -12671,7 +12667,7 @@
       </c>
       <c r="C112" s="55"/>
       <c r="D112" s="55"/>
-      <c r="E112" s="314"/>
+      <c r="E112" s="312"/>
       <c r="F112" s="55"/>
       <c r="G112" s="23" t="str">
         <f>IFERROR(IF(#REF!*G114*(1/#REF!)=G116,"","Error"),"")</f>
@@ -12727,7 +12723,7 @@
         <f>C81</f>
         <v>4.9713435656016179E-2</v>
       </c>
-      <c r="E113" s="311"/>
+      <c r="E113" s="309"/>
       <c r="G113" s="23">
         <f t="shared" ref="G113:Q113" si="45">G81</f>
         <v>9.0325767538135676E-2</v>
@@ -12781,7 +12777,7 @@
         <f>C4/C101</f>
         <v>0.43142078743512902</v>
       </c>
-      <c r="E114" s="311"/>
+      <c r="E114" s="309"/>
       <c r="G114" s="42">
         <f t="shared" ref="G114:Q114" si="46">IF(G4="","",G4/G101)</f>
         <v>0.44019362596109335</v>
@@ -12836,7 +12832,7 @@
         <v>1.2123604198075375</v>
       </c>
       <c r="D115" s="11"/>
-      <c r="E115" s="315"/>
+      <c r="E115" s="313"/>
       <c r="F115" s="11"/>
       <c r="G115" s="15">
         <f t="shared" ref="G115:Q115" si="47">IF(G$4="","",G101/G105)</f>
@@ -12893,7 +12889,7 @@
         <v>1.9358113633458775E-2</v>
       </c>
       <c r="D116" s="106"/>
-      <c r="E116" s="314"/>
+      <c r="E116" s="312"/>
       <c r="F116" s="106"/>
       <c r="G116" s="105">
         <f t="shared" ref="G116:Q116" si="48">IF(G$4="","",G8/G105)</f>
@@ -12984,12 +12980,12 @@
     </row>
     <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="10"/>
-      <c r="B119" s="183" t="s">
+      <c r="B119" s="182" t="s">
         <v>175</v>
       </c>
-      <c r="C119" s="184"/>
+      <c r="C119" s="183"/>
       <c r="D119" s="27"/>
-      <c r="E119" s="308"/>
+      <c r="E119" s="306"/>
       <c r="F119" s="27"/>
       <c r="G119" s="12"/>
       <c r="H119" s="12"/>
@@ -13009,54 +13005,54 @@
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
         <v>FCFE per share (HKD)</v>
       </c>
-      <c r="C120" s="182">
+      <c r="C120" s="181">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>4.5723426463104268E-2</v>
+        <v>4.5723426463104282E-2</v>
       </c>
       <c r="D120" s="27"/>
-      <c r="E120" s="308"/>
+      <c r="E120" s="306"/>
       <c r="F120" s="27"/>
-      <c r="G120" s="182">
+      <c r="G120" s="181">
         <f t="shared" ref="G120:Q120" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>7.9713809414154707E-2</v>
-      </c>
-      <c r="H120" s="182">
+        <v>7.9713809414154721E-2</v>
+      </c>
+      <c r="H120" s="181">
         <f t="shared" si="49"/>
-        <v>1.055655588911119E-2</v>
-      </c>
-      <c r="I120" s="182">
+        <v>1.0556555889111191E-2</v>
+      </c>
+      <c r="I120" s="181">
         <f t="shared" si="49"/>
-        <v>6.4717883901121279E-2</v>
-      </c>
-      <c r="J120" s="182">
+        <v>6.4717883901121293E-2</v>
+      </c>
+      <c r="J120" s="181">
         <f t="shared" si="49"/>
-        <v>0.22763593412908437</v>
-      </c>
-      <c r="K120" s="182">
+        <v>0.22763593412908442</v>
+      </c>
+      <c r="K120" s="181">
         <f t="shared" si="49"/>
-        <v>0.1629251728548784</v>
-      </c>
-      <c r="L120" s="182" t="str">
+        <v>0.16292517285487843</v>
+      </c>
+      <c r="L120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="M120" s="182" t="str">
+      <c r="M120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="N120" s="182" t="str">
+      <c r="N120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="O120" s="182" t="str">
+      <c r="O120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="P120" s="182" t="str">
+      <c r="P120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="Q120" s="182" t="str">
+      <c r="Q120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
@@ -13071,27 +13067,27 @@
         <v>2.0974048836286365E-2</v>
       </c>
       <c r="D121" s="27"/>
-      <c r="E121" s="308"/>
+      <c r="E121" s="306"/>
       <c r="F121" s="27"/>
       <c r="G121" s="79">
         <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
-        <v>3.6565967621171883E-2</v>
+        <v>3.656596762117189E-2</v>
       </c>
       <c r="H121" s="79">
         <f t="shared" ref="H121" si="51">IF(H$4="","",H120/Market_Price)</f>
-        <v>4.8424568298675178E-3</v>
+        <v>4.8424568298675186E-3</v>
       </c>
       <c r="I121" s="79">
         <f t="shared" ref="I121" si="52">IF(I$4="","",I120/Market_Price)</f>
-        <v>2.9687102706936364E-2</v>
+        <v>2.968710270693637E-2</v>
       </c>
       <c r="J121" s="79">
         <f t="shared" ref="J121" si="53">IF(J$4="","",J120/Market_Price)</f>
-        <v>0.10442015327022218</v>
+        <v>0.10442015327022221</v>
       </c>
       <c r="K121" s="79">
         <f t="shared" ref="K121" si="54">IF(K$4="","",K120/Market_Price)</f>
-        <v>7.4736317823338713E-2</v>
+        <v>7.4736317823338727E-2</v>
       </c>
       <c r="L121" s="79" t="str">
         <f t="shared" ref="L121" si="55">IF(L$4="","",L120/Market_Price)</f>
@@ -13878,10 +13874,10 @@
       <c r="H4" s="124"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B5" s="234" t="s">
+      <c r="B5" s="233" t="s">
         <v>128</v>
       </c>
-      <c r="C5" s="235">
+      <c r="C5" s="234">
         <f>Thesis!C70</f>
         <v>0.08</v>
       </c>
@@ -13892,7 +13888,7 @@
       <c r="B6" s="153" t="s">
         <v>233</v>
       </c>
-      <c r="C6" s="239">
+      <c r="C6" s="238">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>711837.99351439381</v>
       </c>
@@ -13900,17 +13896,17 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="346" t="s">
+      <c r="E6" s="344" t="s">
         <v>256</v>
       </c>
-      <c r="F6" s="346"/>
+      <c r="F6" s="344"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" s="152" t="s">
         <v>229</v>
       </c>
-      <c r="C7" s="233">
+      <c r="C7" s="232">
         <f>BS!G31</f>
         <v>33999</v>
       </c>
@@ -13918,15 +13914,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="346"/>
-      <c r="F7" s="346"/>
+      <c r="E7" s="344"/>
+      <c r="F7" s="344"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B8" s="152" t="s">
         <v>230</v>
       </c>
-      <c r="C8" s="208">
+      <c r="C8" s="207">
         <f>BS!D66</f>
         <v>1902339.7312688304</v>
       </c>
@@ -13934,15 +13930,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="346"/>
-      <c r="F8" s="346"/>
+      <c r="E8" s="344"/>
+      <c r="F8" s="344"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B9" s="234" t="s">
+      <c r="B9" s="233" t="s">
         <v>195</v>
       </c>
-      <c r="C9" s="236">
+      <c r="C9" s="235">
         <f>BS!H42</f>
         <v>227656.8</v>
       </c>
@@ -13950,15 +13946,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="346"/>
-      <c r="F9" s="346"/>
+      <c r="E9" s="344"/>
+      <c r="F9" s="344"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B10" s="153" t="s">
         <v>232</v>
       </c>
-      <c r="C10" s="239">
+      <c r="C10" s="238">
         <f>C6-C7+C8+C9</f>
         <v>2807835.5247832239</v>
       </c>
@@ -13969,12 +13965,12 @@
       <c r="H10" s="124"/>
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="237" t="s">
+      <c r="B11" s="236" t="s">
         <v>171</v>
       </c>
-      <c r="C11" s="238">
+      <c r="C11" s="237">
         <f>Exchange_Rate</f>
-        <v>1.0705486499999999</v>
+        <v>1.0705486500000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -13988,7 +13984,7 @@
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>2.2544431160536518</v>
+        <v>2.2544431160536522</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14019,7 +14015,7 @@
       <c r="B16" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C16" s="166">
+      <c r="C16" s="165">
         <f>Scenarios!C65</f>
         <v>1.77907652777404E-2</v>
       </c>
@@ -14029,7 +14025,7 @@
       <c r="B17" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="C17" s="167">
+      <c r="C17" s="166">
         <f>Scenarios!C64</f>
         <v>10</v>
       </c>
@@ -14041,7 +14037,7 @@
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>2.2870920129293171</v>
+        <v>2.287092012929318</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14977,23 +14973,23 @@
       </c>
       <c r="B65" s="128">
         <f>C12</f>
-        <v>2.2544431160536518</v>
+        <v>2.2544431160536522</v>
       </c>
       <c r="C65" s="128">
         <f>C12</f>
-        <v>2.2544431160536518</v>
+        <v>2.2544431160536522</v>
       </c>
       <c r="D65" s="128">
         <f>C12</f>
-        <v>2.2544431160536518</v>
+        <v>2.2544431160536522</v>
       </c>
       <c r="E65" s="145">
         <f>C12</f>
-        <v>2.2544431160536518</v>
+        <v>2.2544431160536522</v>
       </c>
       <c r="F65" s="128">
         <f>C12</f>
-        <v>2.2544431160536518</v>
+        <v>2.2544431160536522</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -15004,23 +15000,23 @@
       </c>
       <c r="B66" s="128">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.2022026571100066</v>
+        <v>2.2022026571100071</v>
       </c>
       <c r="C66" s="128">
         <f t="shared" si="4"/>
-        <v>2.2022026571100066</v>
+        <v>2.2022026571100071</v>
       </c>
       <c r="D66" s="128">
         <f t="shared" si="4"/>
-        <v>2.2728840796483389</v>
+        <v>2.2728840796483394</v>
       </c>
       <c r="E66" s="128">
         <f t="shared" si="4"/>
-        <v>2.3114471399308276</v>
+        <v>2.3114471399308281</v>
       </c>
       <c r="F66" s="128">
         <f t="shared" si="4"/>
-        <v>2.3316184603619323</v>
+        <v>2.3316184603619328</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -15031,23 +15027,23 @@
       </c>
       <c r="B67" s="128">
         <f t="shared" si="4"/>
-        <v>2.162159934390032</v>
+        <v>2.1621599343900324</v>
       </c>
       <c r="C67" s="128">
         <f t="shared" si="4"/>
-        <v>2.162159934390032</v>
+        <v>2.1621599343900324</v>
       </c>
       <c r="D67" s="128">
         <f t="shared" si="4"/>
-        <v>2.2913420244563656</v>
+        <v>2.291342024456366</v>
       </c>
       <c r="E67" s="128">
         <f t="shared" si="4"/>
-        <v>2.3766772521994795</v>
+        <v>2.3766772521994799</v>
       </c>
       <c r="F67" s="128">
         <f t="shared" si="4"/>
-        <v>2.4260482606693805</v>
+        <v>2.426048260669381</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -15058,23 +15054,23 @@
       </c>
       <c r="B68" s="128">
         <f t="shared" si="4"/>
-        <v>2.1210080786417205</v>
+        <v>2.1210080786417209</v>
       </c>
       <c r="C68" s="128">
         <f t="shared" si="4"/>
-        <v>2.1210080786417205</v>
+        <v>2.1210080786417209</v>
       </c>
       <c r="D68" s="128">
         <f t="shared" si="4"/>
-        <v>2.3141888490648133</v>
+        <v>2.3141888490648137</v>
       </c>
       <c r="E68" s="128">
         <f t="shared" si="4"/>
-        <v>2.4664037882772836</v>
+        <v>2.466403788277284</v>
       </c>
       <c r="F68" s="128">
         <f t="shared" si="4"/>
-        <v>2.5633397495654178</v>
+        <v>2.5633397495654182</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -15085,23 +15081,23 @@
       </c>
       <c r="B69" s="128">
         <f t="shared" si="4"/>
-        <v>2.0860582808903976</v>
+        <v>2.086058280890398</v>
       </c>
       <c r="C69" s="128">
         <f t="shared" si="4"/>
-        <v>2.0860582808903976</v>
+        <v>2.086058280890398</v>
       </c>
       <c r="D69" s="128">
         <f t="shared" si="4"/>
-        <v>2.3374660994516825</v>
+        <v>2.3374660994516829</v>
       </c>
       <c r="E69" s="128">
         <f t="shared" si="4"/>
-        <v>2.5687573770088101</v>
+        <v>2.568757377008811</v>
       </c>
       <c r="F69" s="128">
         <f t="shared" si="4"/>
-        <v>2.7298021835113415</v>
+        <v>2.729802183511342</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -15112,23 +15108,23 @@
       </c>
       <c r="B70" s="128">
         <f t="shared" si="4"/>
-        <v>2.0588043587554337</v>
+        <v>2.0588043587554341</v>
       </c>
       <c r="C70" s="128">
         <f t="shared" si="4"/>
-        <v>2.0588043587554337</v>
+        <v>2.0588043587554341</v>
       </c>
       <c r="D70" s="128">
         <f t="shared" si="4"/>
-        <v>2.3591152339663179</v>
+        <v>2.3591152339663184</v>
       </c>
       <c r="E70" s="128">
         <f t="shared" si="4"/>
-        <v>2.6760208259490379</v>
+        <v>2.6760208259490383</v>
       </c>
       <c r="F70" s="128">
         <f t="shared" si="4"/>
-        <v>2.9161178724998149</v>
+        <v>2.9161178724998154</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15138,39 +15134,39 @@
       </c>
       <c r="B71" s="128">
         <f t="shared" si="4"/>
-        <v>2.0385237524445041</v>
+        <v>2.0385237524445046</v>
       </c>
       <c r="C71" s="128">
         <f t="shared" si="4"/>
-        <v>2.0385237524445041</v>
+        <v>2.0385237524445046</v>
       </c>
       <c r="D71" s="128">
         <f t="shared" si="4"/>
-        <v>2.3782127821799142</v>
+        <v>2.3782127821799146</v>
       </c>
       <c r="E71" s="128">
         <f t="shared" si="4"/>
-        <v>2.7832706438044896</v>
+        <v>2.7832706438044901</v>
       </c>
       <c r="F71" s="128">
         <f t="shared" si="4"/>
-        <v>3.115945353276671</v>
+        <v>3.1159453532766714</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B73" s="176" t="s">
+      <c r="B73" s="175" t="s">
         <v>122</v>
       </c>
-      <c r="C73" s="176" t="s">
+      <c r="C73" s="175" t="s">
         <v>137</v>
       </c>
-      <c r="D73" s="176" t="s">
+      <c r="D73" s="175" t="s">
         <v>117</v>
       </c>
-      <c r="E73" s="177" t="s">
+      <c r="E73" s="176" t="s">
         <v>118</v>
       </c>
-      <c r="F73" s="177" t="s">
+      <c r="F73" s="176" t="s">
         <v>124</v>
       </c>
     </row>
@@ -15189,7 +15185,7 @@
       </c>
       <c r="E74" s="139">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>2.5633397495654178</v>
+        <v>2.5633397495654182</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
@@ -15211,7 +15207,7 @@
       </c>
       <c r="E75" s="139">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>2.3766772521994795</v>
+        <v>2.3766772521994799</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -15234,7 +15230,7 @@
       </c>
       <c r="E76" s="139">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>2.2913420244563656</v>
+        <v>2.291342024456366</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15257,7 +15253,7 @@
       </c>
       <c r="E77" s="139">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>2.162159934390032</v>
+        <v>2.1621599343900324</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -15280,7 +15276,7 @@
       </c>
       <c r="E78" s="139">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.1210080786417205</v>
+        <v>2.1210080786417209</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
@@ -15288,27 +15284,27 @@
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B79" s="160"/>
-      <c r="C79" s="160"/>
-      <c r="D79" s="160"/>
-      <c r="E79" s="160"/>
-      <c r="F79" s="161"/>
+      <c r="B79" s="159"/>
+      <c r="C79" s="159"/>
+      <c r="D79" s="159"/>
+      <c r="E79" s="159"/>
+      <c r="F79" s="160"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B80" s="160" t="s">
+      <c r="B80" s="159" t="s">
         <v>341</v>
       </c>
-      <c r="C80" s="160" t="s">
+      <c r="C80" s="159" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="81" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C81" s="160" t="s">
+      <c r="C81" s="159" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="82" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C82" s="160" t="s">
+      <c r="C82" s="159" t="s">
         <v>108</v>
       </c>
     </row>
@@ -15367,19 +15363,19 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
-      <c r="H2" s="285" t="s">
+      <c r="H2" s="283" t="s">
         <v>323</v>
       </c>
-      <c r="I2" s="286"/>
+      <c r="I2" s="284"/>
     </row>
     <row r="3" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B3" s="164" t="s">
+      <c r="B3" s="163" t="s">
         <v>153</v>
       </c>
-      <c r="H3" s="284">
-        <v>0</v>
-      </c>
-      <c r="I3" s="272">
+      <c r="H3" s="282">
+        <v>0</v>
+      </c>
+      <c r="I3" s="270">
         <f>-Market_Price</f>
         <v>-2.1800000000000002</v>
       </c>
@@ -15392,29 +15388,29 @@
         <v>3</v>
       </c>
       <c r="D4" s="124"/>
-      <c r="E4" s="160" t="s">
+      <c r="E4" s="159" t="s">
         <v>155</v>
       </c>
-      <c r="F4" s="160"/>
-      <c r="H4" s="284">
+      <c r="F4" s="159"/>
+      <c r="H4" s="282">
         <v>1</v>
       </c>
-      <c r="I4" s="272">
+      <c r="I4" s="270">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>0.1178</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="H5" s="284">
+      <c r="H5" s="282">
         <v>2</v>
       </c>
-      <c r="I5" s="272">
+      <c r="I5" s="270">
         <f t="shared" si="0"/>
         <v>0.1178</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B6" s="164" t="s">
+      <c r="B6" s="163" t="s">
         <v>100</v>
       </c>
       <c r="C6" s="110">
@@ -15425,12 +15421,12 @@
         <v>298</v>
       </c>
       <c r="F6" s="103"/>
-      <c r="H6" s="284">
+      <c r="H6" s="282">
         <v>3</v>
       </c>
-      <c r="I6" s="272">
+      <c r="I6" s="270">
         <f t="shared" si="0"/>
-        <v>2.4073715355423078</v>
+        <v>2.4073715355423082</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15445,15 +15441,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="348" t="str">
+      <c r="E7" s="346" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 朝云集团(6601.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="348"/>
-      <c r="H7" s="284">
+      <c r="F7" s="346"/>
+      <c r="H7" s="282">
         <v>4</v>
       </c>
-      <c r="I7" s="272" t="str">
+      <c r="I7" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -15470,12 +15466,12 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="348"/>
-      <c r="F8" s="348"/>
-      <c r="H8" s="284">
+      <c r="E8" s="346"/>
+      <c r="F8" s="346"/>
+      <c r="H8" s="282">
         <v>5</v>
       </c>
-      <c r="I8" s="272" t="str">
+      <c r="I8" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -15484,7 +15480,7 @@
       <c r="B9" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="208">
+      <c r="C9" s="207">
         <f>Normalized_FCF!C19</f>
         <v>56947.039481151507</v>
       </c>
@@ -15492,37 +15488,37 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="348"/>
-      <c r="F9" s="348"/>
-      <c r="H9" s="284">
+      <c r="E9" s="346"/>
+      <c r="F9" s="346"/>
+      <c r="H9" s="282">
         <v>6</v>
       </c>
-      <c r="I9" s="272" t="str">
+      <c r="I9" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="348"/>
-      <c r="F10" s="348"/>
-      <c r="H10" s="284">
+      <c r="E10" s="346"/>
+      <c r="F10" s="346"/>
+      <c r="H10" s="282">
         <v>7</v>
       </c>
-      <c r="I10" s="272" t="str">
+      <c r="I10" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B11" s="164" t="s">
+      <c r="B11" s="163" t="s">
         <v>295</v>
       </c>
-      <c r="E11" s="348"/>
-      <c r="F11" s="348"/>
-      <c r="H11" s="284">
+      <c r="E11" s="346"/>
+      <c r="F11" s="346"/>
+      <c r="H11" s="282">
         <v>8</v>
       </c>
-      <c r="I11" s="272" t="str">
+      <c r="I11" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -15531,17 +15527,17 @@
       <c r="B12" s="122" t="s">
         <v>149</v>
       </c>
-      <c r="C12" s="163">
+      <c r="C12" s="162">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-1.7248638436905273E-2</v>
       </c>
-      <c r="D12" s="163"/>
-      <c r="E12" s="348"/>
-      <c r="F12" s="348"/>
-      <c r="H12" s="284">
+      <c r="D12" s="162"/>
+      <c r="E12" s="346"/>
+      <c r="F12" s="346"/>
+      <c r="H12" s="282">
         <v>9</v>
       </c>
-      <c r="I12" s="272" t="str">
+      <c r="I12" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -15550,16 +15546,16 @@
       <c r="B13" s="152" t="s">
         <v>157</v>
       </c>
-      <c r="C13" s="163">
+      <c r="C13" s="162">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.283580450424601</v>
       </c>
-      <c r="E13" s="348"/>
-      <c r="F13" s="348"/>
-      <c r="H13" s="284">
+      <c r="E13" s="346"/>
+      <c r="F13" s="346"/>
+      <c r="H13" s="282">
         <v>10</v>
       </c>
-      <c r="I13" s="272" t="str">
+      <c r="I13" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -15568,12 +15564,12 @@
       <c r="B14" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="163">
+      <c r="C14" s="162">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.2951485762236955</v>
       </c>
-      <c r="E14" s="348"/>
-      <c r="F14" s="348"/>
+      <c r="E14" s="346"/>
+      <c r="F14" s="346"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -15588,7 +15584,7 @@
       <c r="B17" s="112" t="s">
         <v>156</v>
       </c>
-      <c r="E17" s="164" t="s">
+      <c r="E17" s="163" t="s">
         <v>364</v>
       </c>
     </row>
@@ -15599,27 +15595,27 @@
       <c r="C18" s="154">
         <v>10</v>
       </c>
-      <c r="E18" s="348" t="s">
+      <c r="E18" s="346" t="s">
         <v>365</v>
       </c>
-      <c r="F18" s="349"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="349"/>
-      <c r="F19" s="349"/>
+      <c r="E19" s="347"/>
+      <c r="F19" s="347"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B20" s="164" t="s">
+      <c r="B20" s="163" t="s">
         <v>331</v>
       </c>
-      <c r="E20" s="349"/>
-      <c r="F20" s="349"/>
+      <c r="E20" s="347"/>
+      <c r="F20" s="347"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
         <v>296</v>
       </c>
-      <c r="C21" s="165">
+      <c r="C21" s="164">
         <f>Market_Price</f>
         <v>2.1800000000000002</v>
       </c>
@@ -15627,206 +15623,206 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="349"/>
-      <c r="F21" s="349"/>
+      <c r="E21" s="347"/>
+      <c r="F21" s="347"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
         <v>297</v>
       </c>
-      <c r="C22" s="165">
+      <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
-        <v>2.2544431160536518</v>
+        <v>2.2544431160536522</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="349"/>
-      <c r="F22" s="349"/>
+      <c r="E22" s="347"/>
+      <c r="F22" s="347"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B24" s="164" t="s">
+      <c r="B24" s="163" t="s">
         <v>120</v>
       </c>
-      <c r="E24" s="164" t="s">
+      <c r="E24" s="163" t="s">
         <v>154</v>
       </c>
-      <c r="F24" s="164"/>
+      <c r="F24" s="163"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C25" s="171">
+      <c r="C25" s="170">
         <f>C18</f>
         <v>10</v>
       </c>
-      <c r="D25" s="168"/>
-      <c r="E25" s="347"/>
-      <c r="F25" s="347"/>
+      <c r="D25" s="167"/>
+      <c r="E25" s="345"/>
+      <c r="F25" s="345"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="C26" s="169">
+      <c r="C26" s="168">
         <v>0.02</v>
       </c>
-      <c r="D26" s="169"/>
-      <c r="E26" s="347"/>
-      <c r="F26" s="347"/>
+      <c r="D26" s="168"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="C27" s="165">
+      <c r="C27" s="164">
         <f>Valuation_Model!E76</f>
-        <v>2.2913420244563656</v>
-      </c>
-      <c r="D27" s="165" t="str">
+        <v>2.291342024456366</v>
+      </c>
+      <c r="D27" s="164" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="347"/>
-      <c r="F27" s="347"/>
+      <c r="E27" s="345"/>
+      <c r="F27" s="345"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
         <v>152</v>
       </c>
-      <c r="C28" s="170">
+      <c r="C28" s="169">
         <v>0.6</v>
       </c>
-      <c r="D28" s="170"/>
-      <c r="E28" s="347"/>
-      <c r="F28" s="347"/>
+      <c r="D28" s="169"/>
+      <c r="E28" s="345"/>
+      <c r="F28" s="345"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B30" s="164" t="s">
+      <c r="B30" s="163" t="s">
         <v>121</v>
       </c>
-      <c r="E30" s="164" t="s">
+      <c r="E30" s="163" t="s">
         <v>154</v>
       </c>
-      <c r="F30" s="164"/>
+      <c r="F30" s="163"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B31" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C31" s="171">
+      <c r="C31" s="170">
         <f>C18</f>
         <v>10</v>
       </c>
-      <c r="D31" s="168"/>
-      <c r="E31" s="347"/>
-      <c r="F31" s="347"/>
+      <c r="D31" s="167"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="C32" s="169">
+      <c r="C32" s="168">
         <v>-0.06</v>
       </c>
-      <c r="D32" s="169"/>
-      <c r="E32" s="347"/>
-      <c r="F32" s="347"/>
+      <c r="D32" s="168"/>
+      <c r="E32" s="345"/>
+      <c r="F32" s="345"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="C33" s="165">
+      <c r="C33" s="164">
         <f>Valuation_Model!E77</f>
-        <v>2.162159934390032</v>
+        <v>2.1621599343900324</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="347"/>
-      <c r="F33" s="347"/>
+      <c r="E33" s="345"/>
+      <c r="F33" s="345"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
         <v>152</v>
       </c>
-      <c r="C34" s="170">
+      <c r="C34" s="169">
         <v>0.15</v>
       </c>
-      <c r="D34" s="170"/>
-      <c r="E34" s="347"/>
-      <c r="F34" s="347"/>
+      <c r="D34" s="169"/>
+      <c r="E34" s="345"/>
+      <c r="F34" s="345"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B36" s="164" t="s">
+      <c r="B36" s="163" t="s">
         <v>119</v>
       </c>
-      <c r="E36" s="164" t="s">
+      <c r="E36" s="163" t="s">
         <v>154</v>
       </c>
-      <c r="F36" s="164"/>
+      <c r="F36" s="163"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C37" s="171">
+      <c r="C37" s="170">
         <f>C18</f>
         <v>10</v>
       </c>
-      <c r="D37" s="168"/>
-      <c r="E37" s="347"/>
-      <c r="F37" s="347"/>
+      <c r="D37" s="167"/>
+      <c r="E37" s="345"/>
+      <c r="F37" s="345"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="C38" s="169">
+      <c r="C38" s="168">
         <v>0.06</v>
       </c>
-      <c r="D38" s="169"/>
-      <c r="E38" s="347"/>
-      <c r="F38" s="347"/>
+      <c r="D38" s="168"/>
+      <c r="E38" s="345"/>
+      <c r="F38" s="345"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="C39" s="165">
+      <c r="C39" s="164">
         <f>Valuation_Model!E75</f>
-        <v>2.3766772521994795</v>
+        <v>2.3766772521994799</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="347"/>
-      <c r="F39" s="347"/>
+      <c r="E39" s="345"/>
+      <c r="F39" s="345"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
         <v>152</v>
       </c>
-      <c r="C40" s="172">
+      <c r="C40" s="171">
         <f>1-C28-C34</f>
         <v>0.25</v>
       </c>
-      <c r="D40" s="170"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="D40" s="169"/>
+      <c r="E40" s="345"/>
+      <c r="F40" s="345"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
         <v>125</v>
       </c>
-      <c r="C42" s="159">
+      <c r="C42" s="158">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>2.2932985178821941</v>
+        <v>2.2932985178821945</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -15858,133 +15854,133 @@
       <c r="F46" s="103"/>
     </row>
     <row r="47" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B47" s="164"/>
-      <c r="E47" s="164"/>
-      <c r="F47" s="164"/>
+      <c r="B47" s="163"/>
+      <c r="E47" s="163"/>
+      <c r="F47" s="163"/>
     </row>
     <row r="48" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B48" s="164" t="s">
+      <c r="B48" s="163" t="s">
         <v>170</v>
       </c>
-      <c r="E48" s="164" t="s">
+      <c r="E48" s="163" t="s">
         <v>154</v>
       </c>
-      <c r="F48" s="164"/>
+      <c r="F48" s="163"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C49" s="171">
+      <c r="C49" s="170">
         <f>C46</f>
         <v>15</v>
       </c>
-      <c r="D49" s="168"/>
-      <c r="E49" s="347"/>
-      <c r="F49" s="347"/>
+      <c r="D49" s="167"/>
+      <c r="E49" s="345"/>
+      <c r="F49" s="345"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="C50" s="169">
+      <c r="C50" s="168">
         <v>-0.06</v>
       </c>
-      <c r="D50" s="169"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="D50" s="168"/>
+      <c r="E50" s="345"/>
+      <c r="F50" s="345"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="C51" s="165">
+      <c r="C51" s="164">
         <f>Valuation_Model!E78</f>
-        <v>2.1210080786417205</v>
+        <v>2.1210080786417209</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="347"/>
-      <c r="F51" s="347"/>
+      <c r="E51" s="345"/>
+      <c r="F51" s="345"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
         <v>152</v>
       </c>
-      <c r="C52" s="170">
+      <c r="C52" s="169">
         <v>0.1</v>
       </c>
-      <c r="D52" s="170"/>
-      <c r="E52" s="347"/>
-      <c r="F52" s="347"/>
+      <c r="D52" s="169"/>
+      <c r="E52" s="345"/>
+      <c r="F52" s="345"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B54" s="164" t="s">
+      <c r="B54" s="163" t="s">
         <v>349</v>
       </c>
-      <c r="E54" s="164" t="s">
+      <c r="E54" s="163" t="s">
         <v>154</v>
       </c>
-      <c r="F54" s="164"/>
+      <c r="F54" s="163"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B55" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C55" s="171">
+      <c r="C55" s="170">
         <f>C46</f>
         <v>15</v>
       </c>
-      <c r="D55" s="168"/>
-      <c r="E55" s="347"/>
-      <c r="F55" s="347"/>
+      <c r="D55" s="167"/>
+      <c r="E55" s="345"/>
+      <c r="F55" s="345"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="C56" s="169">
+      <c r="C56" s="168">
         <v>0.08</v>
       </c>
-      <c r="D56" s="169"/>
-      <c r="E56" s="347"/>
-      <c r="F56" s="347"/>
+      <c r="D56" s="168"/>
+      <c r="E56" s="345"/>
+      <c r="F56" s="345"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="C57" s="165">
+      <c r="C57" s="164">
         <f>Valuation_Model!E74</f>
-        <v>2.5633397495654178</v>
+        <v>2.5633397495654182</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="347"/>
-      <c r="F57" s="347"/>
+      <c r="E57" s="345"/>
+      <c r="F57" s="345"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
         <v>152</v>
       </c>
-      <c r="C58" s="170">
+      <c r="C58" s="169">
         <v>0.05</v>
       </c>
-      <c r="D58" s="170"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="D58" s="169"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
         <v>125</v>
       </c>
-      <c r="C60" s="159">
+      <c r="C60" s="158">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>2.2895715355423079</v>
+        <v>2.2895715355423083</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -15993,7 +15989,7 @@
       <c r="E60" s="103" t="s">
         <v>324</v>
       </c>
-      <c r="F60" s="321">
+      <c r="F60" s="319">
         <f>Thesis!E20</f>
         <v>3</v>
       </c>
@@ -16011,7 +16007,7 @@
       <c r="B63" s="112" t="s">
         <v>332</v>
       </c>
-      <c r="E63" s="290" t="s">
+      <c r="E63" s="288" t="s">
         <v>342</v>
       </c>
     </row>
@@ -16019,11 +16015,11 @@
       <c r="B64" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C64" s="171">
+      <c r="C64" s="170">
         <v>10</v>
       </c>
       <c r="D64" s="154"/>
-      <c r="E64" s="289" t="s">
+      <c r="E64" s="287" t="s">
         <v>343</v>
       </c>
     </row>
@@ -16035,7 +16031,7 @@
         <v>1.77907652777404E-2</v>
       </c>
       <c r="D65" s="155"/>
-      <c r="E65" s="289" t="s">
+      <c r="E65" s="287" t="s">
         <v>344</v>
       </c>
     </row>
@@ -16043,15 +16039,15 @@
       <c r="B66" s="103" t="s">
         <v>107</v>
       </c>
-      <c r="C66" s="165">
+      <c r="C66" s="164">
         <f>Valuation_Model!C18</f>
-        <v>2.2870920129293171</v>
-      </c>
-      <c r="D66" s="165" t="str">
+        <v>2.287092012929318</v>
+      </c>
+      <c r="D66" s="164" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E66" s="289" t="s">
+      <c r="E66" s="287" t="s">
         <v>345</v>
       </c>
     </row>
@@ -16059,7 +16055,7 @@
       <c r="B68" s="112" t="s">
         <v>319</v>
       </c>
-      <c r="E68" s="290" t="s">
+      <c r="E68" s="288" t="s">
         <v>346</v>
       </c>
     </row>
@@ -16067,7 +16063,7 @@
       <c r="B69" s="103" t="s">
         <v>333</v>
       </c>
-      <c r="C69" s="281" t="str">
+      <c r="C69" s="279" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>N</v>
       </c>
@@ -16077,11 +16073,11 @@
       <c r="B70" s="103" t="s">
         <v>321</v>
       </c>
-      <c r="C70" s="281" t="str">
+      <c r="C70" s="279" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
-      <c r="E70" s="289" t="s">
+      <c r="E70" s="287" t="s">
         <v>322</v>
       </c>
     </row>
@@ -16089,26 +16085,26 @@
       <c r="B71" s="103" t="s">
         <v>320</v>
       </c>
-      <c r="C71" s="281" t="str">
+      <c r="C71" s="279" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="289"/>
+      <c r="E71" s="287"/>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
         <v>311</v>
       </c>
-      <c r="C72" s="280" t="str">
+      <c r="C72" s="278" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="E72" s="138" t="s">
         <v>385</v>
       </c>
-      <c r="F72" s="339">
+      <c r="F72" s="337">
         <f>BS!D89/C60</f>
-        <v>0.7350284798444775</v>
+        <v>0.73502847984447739</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16126,10 +16122,10 @@
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B76" s="283" t="s">
+      <c r="B76" s="281" t="s">
         <v>325</v>
       </c>
-      <c r="C76" s="282">
+      <c r="C76" s="280">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -16139,7 +16135,7 @@
       <c r="B77" s="103" t="s">
         <v>116</v>
       </c>
-      <c r="C77" s="178">
+      <c r="C77" s="177">
         <f>Normalized_FCF!C90</f>
         <v>0.1178</v>
       </c>
@@ -16157,7 +16153,7 @@
       <c r="B80" s="152" t="s">
         <v>327</v>
       </c>
-      <c r="C80" s="172">
+      <c r="C80" s="171">
         <f>Thesis!C121</f>
         <v>0.2</v>
       </c>
@@ -16180,7 +16176,7 @@
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
-        <v>1.3249835275129096</v>
+        <v>1.3249835275129098</v>
       </c>
       <c r="D82" s="120"/>
     </row>
@@ -16190,7 +16186,7 @@
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
-        <v>1.5731270460314282</v>
+        <v>1.5731270460314284</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16199,9 +16195,9 @@
       <c r="E83" s="150" t="s">
         <v>131</v>
       </c>
-      <c r="F83" s="270">
-        <f>(C83/C60-1)</f>
-        <v>-0.31291640308638913</v>
+      <c r="F83" s="337">
+        <f>(1-C83/C60)</f>
+        <v>0.31291640308638913</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16216,7 +16212,7 @@
       <c r="B86" s="152" t="s">
         <v>328</v>
       </c>
-      <c r="C86" s="274">
+      <c r="C86" s="272">
         <f>Market_Price</f>
         <v>2.1800000000000002</v>
       </c>
@@ -16229,7 +16225,7 @@
       <c r="B87" s="103" t="s">
         <v>326</v>
       </c>
-      <c r="C87" s="273">
+      <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>6.9675781490122768E-2</v>
       </c>
@@ -16238,42 +16234,42 @@
       <c r="B88" s="103"/>
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
-      <c r="E89" s="330" t="s">
+      <c r="E89" s="328" t="s">
         <v>359</v>
       </c>
-      <c r="F89" s="327"/>
+      <c r="F89" s="325"/>
       <c r="G89" s="2"/>
-      <c r="H89" s="326"/>
+      <c r="H89" s="324"/>
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E90" s="323" t="s">
+      <c r="E90" s="321" t="s">
         <v>360</v>
       </c>
-      <c r="F90" s="328" t="s">
+      <c r="F90" s="326" t="s">
         <v>361</v>
       </c>
       <c r="G90" s="2"/>
-      <c r="H90" s="326"/>
+      <c r="H90" s="324"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E91" s="324" t="s">
+      <c r="E91" s="322" t="s">
         <v>360</v>
       </c>
-      <c r="F91" s="328" t="s">
+      <c r="F91" s="326" t="s">
         <v>362</v>
       </c>
       <c r="G91" s="2"/>
-      <c r="H91" s="326"/>
+      <c r="H91" s="324"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E92" s="325" t="s">
+      <c r="E92" s="323" t="s">
         <v>360</v>
       </c>
-      <c r="F92" s="329" t="s">
+      <c r="F92" s="327" t="s">
         <v>363</v>
       </c>
       <c r="G92" s="2"/>
-      <c r="H92" s="326"/>
+      <c r="H92" s="324"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A80A5DCF-4118-4689-8DB1-42FB0FFD3A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EDDA013-DF85-4A23-9478-2C3611481D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,12 +43,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="392">
   <si>
     <t>Number of Shares:</t>
-  </si>
-  <si>
-    <t>Reporting Currency:</t>
   </si>
   <si>
     <t>Exchange Rate:</t>
@@ -1566,10 +1563,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Categorize the investment</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Asset Play</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1599,10 +1592,6 @@
   </si>
   <si>
     <t>Total Non-FCF Value</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Type of Investment</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1662,10 +1651,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Investment Type:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Valuation Overview</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1718,10 +1703,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Status in Portfolio:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Snowball Scenario</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1743,10 +1724,6 @@
   </si>
   <si>
     <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1x for stable businesses, 2x for for volatile ones</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1986,7 +1963,31 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Not Held</t>
+    <t>Reporting Currency:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Growth Classification:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Growth Classification</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type of Company</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Variable + Fixed Costs &amp; Dividends</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1x for stable businesses, 2x for for volatile ones, 6x for cash hoarders</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Selected:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3275,9 +3276,6 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3340,9 +3338,6 @@
     <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="187" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3377,20 +3372,26 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="187" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3696,22 +3697,22 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C1" s="44">
         <v>45730</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="290" t="s">
-        <v>348</v>
-      </c>
-      <c r="F1" s="291" t="s">
+      <c r="E1" s="337" t="s">
         <v>386</v>
+      </c>
+      <c r="F1" s="290" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A2" s="253" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -3735,7 +3736,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C5" s="48" t="s">
         <v>387</v>
@@ -3746,13 +3747,13 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" s="50">
         <v>2.1800000000000002</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -3768,7 +3769,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C8" s="285">
         <v>6</v>
@@ -3778,7 +3779,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -3804,24 +3805,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="339" t="s">
-        <v>286</v>
-      </c>
-      <c r="C12" s="339"/>
-      <c r="D12" s="339"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="339"/>
+      <c r="B12" s="338" t="s">
+        <v>285</v>
+      </c>
+      <c r="C12" s="338"/>
+      <c r="D12" s="338"/>
+      <c r="E12" s="338"/>
+      <c r="F12" s="338"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>334</v>
+        <v>381</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -3831,7 +3832,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>1</v>
+        <v>380</v>
       </c>
       <c r="C16" s="48" t="s">
         <v>389</v>
@@ -3841,7 +3842,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" s="50">
         <v>1.0705486500000001</v>
@@ -3854,7 +3855,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B18" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C18" s="48" t="s">
         <v>390</v>
@@ -3863,7 +3864,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C19" s="255">
         <v>0.2</v>
@@ -3877,22 +3878,22 @@
       </c>
       <c r="C20" s="258">
         <f>C127</f>
-        <v>1.5731270460314284</v>
+        <v>1.5466941106484338</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="E20" s="320">
+        <v>334</v>
+      </c>
+      <c r="E20" s="336">
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
-        <v>6.9675781490122768E-2</v>
+        <v>6.3214262000776955E-2</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3903,7 +3904,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="253" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -3912,26 +3913,26 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="339" t="s">
-        <v>236</v>
-      </c>
-      <c r="C25" s="339"/>
-      <c r="D25" s="339"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="339"/>
+      <c r="B25" s="338" t="s">
+        <v>235</v>
+      </c>
+      <c r="C25" s="338"/>
+      <c r="D25" s="338"/>
+      <c r="E25" s="338"/>
+      <c r="F25" s="338"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="340" t="s">
-        <v>376</v>
-      </c>
-      <c r="C26" s="340"/>
-      <c r="D26" s="340"/>
-      <c r="E26" s="340"/>
-      <c r="F26" s="340"/>
+      <c r="B26" s="342" t="s">
+        <v>370</v>
+      </c>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C28" s="111">
         <f>Data!C3</f>
@@ -3939,17 +3940,17 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="338" t="s">
-        <v>238</v>
-      </c>
-      <c r="C29" s="338"/>
-      <c r="D29" s="338"/>
-      <c r="E29" s="338"/>
-      <c r="F29" s="338"/>
+      <c r="B29" s="340" t="s">
+        <v>237</v>
+      </c>
+      <c r="C29" s="340"/>
+      <c r="D29" s="340"/>
+      <c r="E29" s="340"/>
+      <c r="F29" s="340"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C30" s="191">
         <f>Normalized_FCF!C8</f>
@@ -3965,17 +3966,17 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="338" t="s">
-        <v>240</v>
-      </c>
-      <c r="C32" s="338"/>
-      <c r="D32" s="338"/>
-      <c r="E32" s="338"/>
-      <c r="F32" s="338"/>
+      <c r="B32" s="340" t="s">
+        <v>239</v>
+      </c>
+      <c r="C32" s="340"/>
+      <c r="D32" s="340"/>
+      <c r="E32" s="340"/>
+      <c r="F32" s="340"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C33" s="191">
         <f>Normalized_FCF!C9</f>
@@ -3988,7 +3989,7 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="52" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C34" s="191">
         <f>Normalized_FCF!C10</f>
@@ -4000,17 +4001,17 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="338" t="s">
-        <v>243</v>
-      </c>
-      <c r="C36" s="338"/>
-      <c r="D36" s="338"/>
-      <c r="E36" s="338"/>
-      <c r="F36" s="338"/>
+      <c r="B36" s="340" t="s">
+        <v>242</v>
+      </c>
+      <c r="C36" s="340"/>
+      <c r="D36" s="340"/>
+      <c r="E36" s="340"/>
+      <c r="F36" s="340"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C37" s="191">
         <f>Normalized_FCF!C11</f>
@@ -4022,34 +4023,34 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="338" t="s">
-        <v>247</v>
-      </c>
-      <c r="C39" s="338"/>
-      <c r="D39" s="338"/>
-      <c r="E39" s="338"/>
-      <c r="F39" s="338"/>
+      <c r="B39" s="340" t="s">
+        <v>246</v>
+      </c>
+      <c r="C39" s="340"/>
+      <c r="D39" s="340"/>
+      <c r="E39" s="340"/>
+      <c r="F39" s="340"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>377</v>
-      </c>
-      <c r="C40" s="330">
+        <v>371</v>
+      </c>
+      <c r="C40" s="328">
         <f>Normalized_FCF!C48</f>
-        <v>21115.955148098936</v>
+        <v>23291.09073065874</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E40" s="329"/>
-      <c r="F40" s="329"/>
+      <c r="E40" s="327"/>
+      <c r="F40" s="327"/>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>378</v>
-      </c>
-      <c r="C41" s="330">
+        <v>372</v>
+      </c>
+      <c r="C41" s="328">
         <f>Normalized_FCF!C47</f>
         <v>-1003</v>
       </c>
@@ -4057,16 +4058,16 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E41" s="329"/>
-      <c r="F41" s="329"/>
+      <c r="E41" s="327"/>
+      <c r="F41" s="327"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B42" s="47" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C42" s="191">
         <f>Normalized_FCF!C12</f>
-        <v>20112.955148098936</v>
+        <v>22288.09073065874</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4075,12 +4076,12 @@
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B44" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B45" s="47" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C45" s="191">
         <f>Normalized_FCF!C15</f>
@@ -4092,21 +4093,21 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="338" t="s">
-        <v>248</v>
-      </c>
-      <c r="C47" s="338"/>
-      <c r="D47" s="338"/>
-      <c r="E47" s="338"/>
-      <c r="F47" s="338"/>
+      <c r="B47" s="340" t="s">
+        <v>247</v>
+      </c>
+      <c r="C47" s="340"/>
+      <c r="D47" s="340"/>
+      <c r="E47" s="340"/>
+      <c r="F47" s="340"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C48" s="191">
         <f>Normalized_FCF!C14</f>
-        <v>-19678.904421439904</v>
+        <v>-20222.688317079854</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4114,17 +4115,17 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="338" t="s">
-        <v>375</v>
-      </c>
-      <c r="C50" s="342"/>
-      <c r="D50" s="342"/>
-      <c r="E50" s="342"/>
-      <c r="F50" s="342"/>
+      <c r="B50" s="340" t="s">
+        <v>369</v>
+      </c>
+      <c r="C50" s="341"/>
+      <c r="D50" s="341"/>
+      <c r="E50" s="341"/>
+      <c r="F50" s="341"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C51" s="1">
         <f>Normalized_FCF!C17</f>
@@ -4136,30 +4137,30 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="339" t="s">
-        <v>380</v>
-      </c>
-      <c r="C53" s="339"/>
-      <c r="D53" s="339"/>
-      <c r="E53" s="339"/>
-      <c r="F53" s="339"/>
+      <c r="B53" s="338" t="s">
+        <v>374</v>
+      </c>
+      <c r="C53" s="338"/>
+      <c r="D53" s="338"/>
+      <c r="E53" s="338"/>
+      <c r="F53" s="338"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="339" t="s">
-        <v>268</v>
-      </c>
-      <c r="C54" s="339"/>
-      <c r="D54" s="339"/>
-      <c r="E54" s="339"/>
-      <c r="F54" s="339"/>
+      <c r="B54" s="338" t="s">
+        <v>267</v>
+      </c>
+      <c r="C54" s="338"/>
+      <c r="D54" s="338"/>
+      <c r="E54" s="338"/>
+      <c r="F54" s="338"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C56" s="191">
         <f>Normalized_FCF!G19</f>
-        <v>99280.955148098932</v>
+        <v>101456.09073065873</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4168,11 +4169,11 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B57" s="47" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C57" s="191">
         <f>Normalized_FCF!C19</f>
-        <v>56947.039481151507</v>
+        <v>58578.391168071357</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4181,16 +4182,16 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="260" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C121</f>
-        <v>2.0974048836286365E-2</v>
+        <v>2.1574888673832972E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="260" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
@@ -4199,7 +4200,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="253" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4212,63 +4213,63 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
-        <v>303</v>
-      </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="B63" s="340" t="s">
+        <v>302</v>
+      </c>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="340" t="s">
-        <v>259</v>
-      </c>
-      <c r="C64" s="340"/>
-      <c r="D64" s="340"/>
-      <c r="E64" s="340"/>
-      <c r="F64" s="340"/>
+      <c r="B64" s="342" t="s">
+        <v>258</v>
+      </c>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="C67" s="318">
+        <v>306</v>
+      </c>
+      <c r="C67" s="317">
         <v>0.08</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C68" s="269">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
-      <c r="D68" s="293" t="s">
-        <v>354</v>
+      <c r="D68" s="292" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C69" s="269">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
-      <c r="D69" s="293" t="s">
-        <v>354</v>
+      <c r="D69" s="292" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C70" s="269">
         <f>SUM(C67:C69)</f>
@@ -4279,26 +4280,26 @@
       <c r="C71" s="125"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B72" s="339" t="s">
-        <v>381</v>
-      </c>
-      <c r="C72" s="339"/>
-      <c r="D72" s="339"/>
-      <c r="E72" s="339"/>
-      <c r="F72" s="339"/>
+      <c r="B72" s="338" t="s">
+        <v>375</v>
+      </c>
+      <c r="C72" s="338"/>
+      <c r="D72" s="338"/>
+      <c r="E72" s="338"/>
+      <c r="F72" s="338"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="339" t="s">
-        <v>382</v>
-      </c>
-      <c r="C73" s="339"/>
-      <c r="D73" s="339"/>
-      <c r="E73" s="339"/>
-      <c r="F73" s="339"/>
+      <c r="B73" s="338" t="s">
+        <v>376</v>
+      </c>
+      <c r="C73" s="338"/>
+      <c r="D73" s="338"/>
+      <c r="E73" s="338"/>
+      <c r="F73" s="338"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B75" s="47" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C75" s="269">
         <v>0</v>
@@ -4306,11 +4307,11 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C76" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.57154283078880352</v>
+        <v>0.58791571636194839</v>
       </c>
       <c r="D76" s="1" t="str">
         <f>Market_currency</f>
@@ -4319,7 +4320,7 @@
     </row>
     <row r="78" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A78" s="253" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -4331,36 +4332,36 @@
       <c r="A79" s="239"/>
     </row>
     <row r="80" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="339" t="s">
-        <v>261</v>
-      </c>
-      <c r="C80" s="339"/>
-      <c r="D80" s="339"/>
-      <c r="E80" s="339"/>
-      <c r="F80" s="339"/>
+      <c r="B80" s="338" t="s">
+        <v>260</v>
+      </c>
+      <c r="C80" s="338"/>
+      <c r="D80" s="338"/>
+      <c r="E80" s="338"/>
+      <c r="F80" s="338"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B83" s="240" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="84" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="339" t="s">
-        <v>383</v>
-      </c>
-      <c r="C84" s="339"/>
-      <c r="D84" s="339"/>
-      <c r="E84" s="339"/>
-      <c r="F84" s="339"/>
+      <c r="B84" s="338" t="s">
+        <v>377</v>
+      </c>
+      <c r="C84" s="338"/>
+      <c r="D84" s="338"/>
+      <c r="E84" s="338"/>
+      <c r="F84" s="338"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="47" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C85" s="191">
         <f>Valuation_Model!C7</f>
@@ -4373,7 +4374,7 @@
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C86" s="254">
         <f>C85*C28*Exchange_Rate/Common_Shares</f>
@@ -4386,12 +4387,12 @@
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B88" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B89" s="47" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C89" s="191">
         <f>BS!C66</f>
@@ -4404,11 +4405,11 @@
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="47" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C90" s="191">
         <f>Valuation_Model!C8</f>
-        <v>1902339.7312688304</v>
+        <v>1823806.3881188305</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4417,11 +4418,11 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="47" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C91" s="254">
         <f>C90*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.5274102324371279</v>
+        <v>1.4643549169521279</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Market_currency</f>
@@ -4430,12 +4431,12 @@
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B93" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B94" s="47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C94" s="191">
         <f>Valuation_Model!C9</f>
@@ -4448,7 +4449,7 @@
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="47" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C95" s="254">
         <f>C94*C28*Exchange_Rate/Common_Shares</f>
@@ -4460,21 +4461,21 @@
       </c>
     </row>
     <row r="97" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="339" t="s">
-        <v>267</v>
-      </c>
-      <c r="C97" s="339"/>
-      <c r="D97" s="339"/>
-      <c r="E97" s="339"/>
-      <c r="F97" s="339"/>
+      <c r="B97" s="338" t="s">
+        <v>266</v>
+      </c>
+      <c r="C97" s="338"/>
+      <c r="D97" s="338"/>
+      <c r="E97" s="338"/>
+      <c r="F97" s="338"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B99" s="47" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C99" s="254">
         <f>Valuation_Model!C12</f>
-        <v>2.2544431160536522</v>
+        <v>2.2077606861417975</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4483,7 +4484,7 @@
     </row>
     <row r="101" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A101" s="253" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B101" s="36"/>
       <c r="C101" s="36"/>
@@ -4492,29 +4493,29 @@
       <c r="F101" s="36"/>
     </row>
     <row r="103" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="338" t="s">
-        <v>366</v>
-      </c>
-      <c r="C103" s="338"/>
-      <c r="D103" s="338"/>
-      <c r="E103" s="338"/>
-      <c r="F103" s="338"/>
+      <c r="B103" s="340" t="s">
+        <v>360</v>
+      </c>
+      <c r="C103" s="340"/>
+      <c r="D103" s="340"/>
+      <c r="E103" s="340"/>
+      <c r="F103" s="340"/>
     </row>
     <row r="105" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B105" s="266" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C105" s="266" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D105" s="266" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E105" s="266" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F105" s="266" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
@@ -4532,7 +4533,7 @@
       </c>
       <c r="E106" s="264" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>2.56 HKD</v>
+        <v>2.53 HKD</v>
       </c>
       <c r="F106" s="265">
         <f>Valuation_Model!F74</f>
@@ -4554,7 +4555,7 @@
       </c>
       <c r="E107" s="251" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>2.38 HKD</v>
+        <v>2.33 HKD</v>
       </c>
       <c r="F107" s="252">
         <f>Valuation_Model!F75</f>
@@ -4576,7 +4577,7 @@
       </c>
       <c r="E108" s="251" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>2.29 HKD</v>
+        <v>2.25 HKD</v>
       </c>
       <c r="F108" s="252">
         <f>Valuation_Model!F76</f>
@@ -4598,7 +4599,7 @@
       </c>
       <c r="E109" s="251" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>2.16 HKD</v>
+        <v>2.11 HKD</v>
       </c>
       <c r="F109" s="252">
         <f>Valuation_Model!F77</f>
@@ -4620,7 +4621,7 @@
       </c>
       <c r="E110" s="251" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>2.12 HKD</v>
+        <v>2.07 HKD</v>
       </c>
       <c r="F110" s="252">
         <f>Valuation_Model!F78</f>
@@ -4629,11 +4630,11 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B112" s="241" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C112" s="247">
         <f>Scenarios!C60</f>
-        <v>2.2895715355423083</v>
+        <v>2.2438954232004935</v>
       </c>
       <c r="D112" s="242" t="str">
         <f>Market_currency</f>
@@ -4642,7 +4643,7 @@
     </row>
     <row r="114" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B114" s="343" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="C114" s="343"/>
       <c r="D114" s="343"/>
@@ -4651,7 +4652,7 @@
     </row>
     <row r="116" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A116" s="253" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B116" s="36"/>
       <c r="C116" s="36"/>
@@ -4660,22 +4661,22 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B118" s="341" t="s">
-        <v>275</v>
-      </c>
-      <c r="C118" s="341"/>
-      <c r="D118" s="341"/>
-      <c r="E118" s="341"/>
-      <c r="F118" s="341"/>
+      <c r="B118" s="339" t="s">
+        <v>274</v>
+      </c>
+      <c r="C118" s="339"/>
+      <c r="D118" s="339"/>
+      <c r="E118" s="339"/>
+      <c r="F118" s="339"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B119" s="240" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B120" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C120" s="257">
         <f>E20</f>
@@ -4684,7 +4685,7 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C121" s="256">
         <f>C19</f>
@@ -4693,7 +4694,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B122" s="242" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C122" s="243">
         <f>Scenarios!C77</f>
@@ -4706,7 +4707,7 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B124" s="240" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
@@ -4726,16 +4727,16 @@
       </c>
       <c r="C126" s="246">
         <f>Scenarios!C82</f>
-        <v>1.3249835275129098</v>
+        <v>1.2985505921299152</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B127" s="82" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C127" s="245">
         <f>Scenarios!C83</f>
-        <v>1.5731270460314284</v>
+        <v>1.5466941106484338</v>
       </c>
       <c r="D127" s="47" t="str">
         <f>Reporting_currency</f>
@@ -4744,15 +4745,21 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B128" s="244" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C128" s="94">
         <f>Scenarios!F83</f>
-        <v>0.31291640308638913</v>
+        <v>0.31071025206586211</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B97:F97"/>
@@ -4768,12 +4775,6 @@
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B84:F84"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -4781,7 +4782,7 @@
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
-      <formula1>"Not Held, Held"</formula1>
+      <formula1>"Y, N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D68:D69" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
@@ -4857,7 +4858,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -4873,7 +4874,7 @@
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" s="109">
         <v>1000</v>
@@ -4881,7 +4882,7 @@
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B4" s="32" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="193">
         <v>1615585</v>
@@ -4907,7 +4908,7 @@
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5" s="193">
         <v>897327</v>
@@ -4933,7 +4934,7 @@
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B6" s="40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C6" s="193">
         <v>613104</v>
@@ -4959,7 +4960,7 @@
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B7" s="70" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7" s="194">
         <v>425033</v>
@@ -4979,7 +4980,7 @@
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B8" s="40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C8" s="193"/>
       <c r="D8" s="184"/>
@@ -4995,7 +4996,7 @@
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B9" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C9" s="193"/>
       <c r="D9" s="184"/>
@@ -5011,7 +5012,7 @@
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B10" s="40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C10" s="193"/>
       <c r="D10" s="184"/>
@@ -5027,7 +5028,7 @@
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C11" s="193"/>
       <c r="D11" s="184"/>
@@ -5043,7 +5044,7 @@
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B12" s="40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" s="193">
         <v>1003</v>
@@ -5069,7 +5070,7 @@
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B13" s="40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C13" s="193">
         <v>73805</v>
@@ -5089,7 +5090,7 @@
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B14" s="40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C14" s="193">
         <v>44449</v>
@@ -5109,7 +5110,7 @@
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B15" s="43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" s="195">
         <v>172817</v>
@@ -5133,7 +5134,7 @@
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B16" s="28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="193">
         <v>2199</v>
@@ -5153,13 +5154,13 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B18" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B19" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C19" s="184">
         <v>35974</v>
@@ -5183,7 +5184,7 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B20" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C20" s="184">
         <v>15312</v>
@@ -5203,7 +5204,7 @@
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B21" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C21" s="184">
         <v>-169280</v>
@@ -5242,13 +5243,13 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C24" s="9"/>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B25" s="26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C25" s="186"/>
       <c r="D25" s="184"/>
@@ -5264,7 +5265,7 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B26" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="186"/>
       <c r="D26" s="184"/>
@@ -5280,7 +5281,7 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B27" s="29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C27" s="185">
         <v>642877</v>
@@ -5306,7 +5307,7 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28" s="185">
         <v>3027292</v>
@@ -5332,7 +5333,7 @@
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B29" s="26" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C29" s="184"/>
       <c r="D29" s="184"/>
@@ -5348,13 +5349,13 @@
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B31" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C31" s="9"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B32" s="26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C32" s="184"/>
       <c r="D32" s="184"/>
@@ -5370,7 +5371,7 @@
     </row>
     <row r="34" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B34" s="36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -5386,12 +5387,12 @@
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B35" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B36" s="32" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C36" s="186">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
@@ -5440,7 +5441,7 @@
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B37" s="40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37" s="186">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -5489,7 +5490,7 @@
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B38" s="31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C38" s="187">
         <f>IF(C36="","",C36+C37)</f>
@@ -5538,7 +5539,7 @@
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B39" s="40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C39" s="186">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -5587,7 +5588,7 @@
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B40" s="70" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C40" s="188">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -5636,7 +5637,7 @@
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B41" s="70" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C41" s="188">
         <f>IF(C$4="","",C39-C40)</f>
@@ -5685,7 +5686,7 @@
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B42" s="40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" s="186">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -5734,7 +5735,7 @@
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B43" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C43" s="189">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -5783,7 +5784,7 @@
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B44" s="43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C44" s="190">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -5832,7 +5833,7 @@
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B45" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C45" s="191">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -5881,7 +5882,7 @@
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B46" s="40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C46" s="186">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -5930,7 +5931,7 @@
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B47" s="43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C47" s="189">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -5979,7 +5980,7 @@
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B48" s="28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C48" s="186">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -6028,12 +6029,12 @@
     </row>
     <row r="50" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B50" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B51" s="40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C51" s="186">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
@@ -6082,7 +6083,7 @@
     </row>
     <row r="52" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B52" s="40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C52" s="186">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -6131,12 +6132,12 @@
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B54" s="178" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B55" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C55" s="191">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -6185,7 +6186,7 @@
     </row>
     <row r="56" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B56" s="40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C56" s="191">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -6234,7 +6235,7 @@
     </row>
     <row r="57" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B57" s="40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C57" s="191">
         <f>IF(C$4="","",C11)</f>
@@ -6283,7 +6284,7 @@
     </row>
     <row r="58" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B58" s="40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C58" s="191">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -6332,13 +6333,13 @@
     </row>
     <row r="60" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B60" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B61" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C61" s="186">
         <f t="shared" ref="C61:M61" si="29">IF(C$4="","",-C19)</f>
@@ -6387,7 +6388,7 @@
     </row>
     <row r="62" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B62" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C62" s="186">
         <f t="shared" ref="C62:M62" si="30">IF(C$4="","",-C20)</f>
@@ -6436,7 +6437,7 @@
     </row>
     <row r="63" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B63" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C63" s="186">
         <f t="shared" ref="C63:M63" si="31">IF(C$4="","",-C21)</f>
@@ -6485,7 +6486,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C64" s="75">
         <f t="shared" ref="C64:M64" si="32">IF(C$4="","",C22)</f>
@@ -6534,7 +6535,7 @@
     </row>
     <row r="66" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B66" s="93" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="67" spans="2:13" x14ac:dyDescent="0.35">
@@ -6789,7 +6790,7 @@
     </row>
     <row r="73" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B73" s="36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C73" s="37"/>
       <c r="D73" s="37"/>
@@ -6805,13 +6806,13 @@
     </row>
     <row r="74" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B74" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C74" s="9"/>
     </row>
     <row r="75" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B75" s="26" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C75" s="78">
         <f>IF(C$4="","",C78+C79)</f>
@@ -6860,7 +6861,7 @@
     </row>
     <row r="76" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B76" s="95" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C76" s="74">
         <f t="shared" ref="C76:H77" si="39">IF(C$4="","",C25)</f>
@@ -6894,7 +6895,7 @@
     </row>
     <row r="77" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B77" s="95" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C77" s="74">
         <f t="shared" si="39"/>
@@ -6928,7 +6929,7 @@
     </row>
     <row r="78" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B78" s="26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C78" s="58">
         <f t="shared" ref="C78:M78" si="40">IF(C$4="","",C27)</f>
@@ -6977,7 +6978,7 @@
     </row>
     <row r="79" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B79" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C79" s="58">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C28)</f>
@@ -7069,7 +7070,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C1" s="102">
         <v>45473</v>
@@ -7085,7 +7086,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="81" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -7096,177 +7097,177 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" s="209" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" s="210" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C3" s="209" t="s">
-        <v>141</v>
-      </c>
-      <c r="D3" s="210" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>190</v>
-      </c>
       <c r="G3" s="209" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H3" s="210" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" s="19">
         <v>180994</v>
       </c>
-      <c r="D4" s="301">
+      <c r="D4" s="300">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G4" s="19">
         <v>2385307</v>
       </c>
-      <c r="H4" s="301">
+      <c r="H4" s="300">
         <v>0.9</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="301">
+      <c r="D5" s="300">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
       <c r="F5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G5" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="301">
+      <c r="H5" s="300">
         <v>0.7</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="19">
         <v>158110</v>
       </c>
-      <c r="D6" s="301">
+      <c r="D6" s="300">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="301">
+      <c r="H6" s="300">
         <v>0.6</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="301">
+      <c r="D7" s="300">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G7" s="19">
         <v>253051</v>
       </c>
-      <c r="H7" s="301">
+      <c r="H7" s="300">
         <v>0.6</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="301">
+      <c r="D8" s="300">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="301">
+      <c r="H8" s="300">
         <v>0.6</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" s="19">
         <v>0</v>
       </c>
-      <c r="D9" s="301">
+      <c r="D9" s="300">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="301">
+      <c r="H9" s="300">
         <v>0.6</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="19">
         <v>5912</v>
       </c>
-      <c r="D10" s="301">
+      <c r="D10" s="300">
         <v>0.9</v>
       </c>
-      <c r="H10" s="302"/>
+      <c r="H10" s="301"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="19">
         <v>0</v>
       </c>
-      <c r="D11" s="301">
+      <c r="D11" s="300">
         <v>0.05</v>
       </c>
-      <c r="H11" s="302"/>
+      <c r="H11" s="301"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="82" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C12" s="83">
         <f>SUM(C4:C11)</f>
@@ -7277,7 +7278,7 @@
         <v>192972.19999999998</v>
       </c>
       <c r="F12" s="82" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G12" s="83">
         <f>SUM(G4:G9)</f>
@@ -7295,191 +7296,191 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C14" s="209" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D14" s="210" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G14" s="209" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H14" s="210" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C15" s="19">
         <v>0</v>
       </c>
-      <c r="D15" s="301">
+      <c r="D15" s="300">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G15" s="19">
         <v>279425</v>
       </c>
-      <c r="H15" s="301">
+      <c r="H15" s="300">
         <v>0.8</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="301">
+      <c r="D16" s="300">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="301">
+      <c r="H16" s="300">
         <v>0.6</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="301">
+      <c r="D17" s="300">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G17" s="19">
         <v>126127</v>
       </c>
-      <c r="H17" s="301">
+      <c r="H17" s="300">
         <v>0.6</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="301">
+      <c r="D18" s="300">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
       </c>
-      <c r="H18" s="301">
+      <c r="H18" s="300">
         <v>0.1</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C19" s="19">
         <v>193915</v>
       </c>
-      <c r="D19" s="301">
+      <c r="D19" s="300">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G19" s="19">
         <v>1500</v>
       </c>
-      <c r="H19" s="301">
+      <c r="H19" s="300">
         <v>0.1</v>
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="301">
+      <c r="D20" s="300">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="301">
+      <c r="H20" s="300">
         <v>0.2</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C21" s="19">
         <v>9704</v>
       </c>
-      <c r="D21" s="301">
+      <c r="D21" s="300">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="301">
+      <c r="H21" s="300">
         <v>0.1</v>
       </c>
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C22" s="19">
         <v>76124</v>
       </c>
-      <c r="D22" s="301">
+      <c r="D22" s="300">
         <v>0.9</v>
       </c>
-      <c r="H22" s="302"/>
+      <c r="H22" s="301"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C23" s="19">
         <v>0</v>
       </c>
-      <c r="D23" s="301">
-        <v>0</v>
-      </c>
-      <c r="H23" s="302"/>
+      <c r="D23" s="300">
+        <v>0</v>
+      </c>
+      <c r="H23" s="301"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="82" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C24" s="83">
         <f>SUM(C15:C23)</f>
@@ -7490,7 +7491,7 @@
         <v>88388.3</v>
       </c>
       <c r="F24" s="82" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G24" s="83">
         <f>SUM(G15:G21)</f>
@@ -7503,30 +7504,30 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C26" s="209" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F26" s="211" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G26" s="212" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H26" s="213" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" s="19">
         <v>0</v>
       </c>
       <c r="F27" s="214" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G27" s="87">
         <f>G32-G30</f>
@@ -7539,13 +7540,13 @@
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28" s="19">
         <v>13416</v>
       </c>
       <c r="F28" s="216" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G28" s="184">
         <v>3990</v>
@@ -7554,13 +7555,13 @@
     </row>
     <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C29" s="19">
         <v>0</v>
       </c>
       <c r="F29" s="217" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -7573,13 +7574,13 @@
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C30" s="19">
         <v>0</v>
       </c>
       <c r="F30" s="214" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G30" s="87">
         <f>C33+C42</f>
@@ -7589,14 +7590,14 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="82" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C31" s="83">
         <f>SUM(C27:C30)</f>
         <v>13416</v>
       </c>
       <c r="F31" s="217" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G31" s="218">
         <f>C31+C40</f>
@@ -7606,14 +7607,14 @@
     </row>
     <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32" s="21">
         <f>C33-C31</f>
         <v>598515</v>
       </c>
       <c r="F32" s="219" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G32" s="220">
         <f>G35+G40</f>
@@ -7626,7 +7627,7 @@
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="85" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33" s="86">
         <v>611931</v>
@@ -7639,24 +7640,24 @@
       <c r="B34" s="85"/>
       <c r="C34" s="86"/>
       <c r="F34" s="223" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G34" s="224" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H34" s="225" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C35" s="209" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F35" s="226" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G35" s="220">
         <f>C12+C24</f>
@@ -7669,13 +7670,13 @@
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C36" s="19">
         <v>0</v>
       </c>
       <c r="F36" s="217" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G36" s="218">
         <f>C4+C15</f>
@@ -7685,13 +7686,13 @@
     </row>
     <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C37" s="19">
         <v>20583</v>
       </c>
       <c r="F37" s="217" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G37" s="218">
         <f>C6</f>
@@ -7701,13 +7702,13 @@
     </row>
     <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C38" s="19">
         <v>0</v>
       </c>
       <c r="F38" s="217" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G38" s="218">
         <f>C7+C17</f>
@@ -7717,13 +7718,13 @@
     </row>
     <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C39" s="19">
         <v>0</v>
       </c>
       <c r="F39" s="217" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G39" s="218">
         <f>C7+C17+C19+C20</f>
@@ -7736,14 +7737,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="82" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C40" s="83">
         <f>SUM(C36:C39)</f>
         <v>20583</v>
       </c>
       <c r="F40" s="226" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G40" s="220">
         <f>G12+G24</f>
@@ -7756,14 +7757,14 @@
     </row>
     <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B41" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C41" s="21">
         <f>C42-C40</f>
         <v>10363</v>
       </c>
       <c r="F41" s="217" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G41" s="218">
         <f>C70</f>
@@ -7776,13 +7777,13 @@
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B42" s="85" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C42" s="86">
         <v>30946</v>
       </c>
       <c r="F42" s="228" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G42" s="229">
         <f>C82</f>
@@ -7795,7 +7796,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="81" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -7806,21 +7807,21 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="C45" s="267" t="s">
+        <v>140</v>
+      </c>
+      <c r="D45" s="209" t="s">
         <v>287</v>
       </c>
-      <c r="C45" s="267" t="s">
-        <v>141</v>
-      </c>
-      <c r="D45" s="209" t="s">
-        <v>288</v>
-      </c>
-      <c r="F45" s="294" t="s">
-        <v>63</v>
+      <c r="F45" s="293" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C46" s="191">
         <f>G29</f>
@@ -7852,20 +7853,20 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="161" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C49" s="268" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D49" s="224" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="289"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C50" s="98">
         <f>G31/Normalized_FCF!C8</f>
@@ -7879,7 +7880,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C51" s="208"/>
       <c r="D51" s="94">
@@ -7893,19 +7894,19 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="161" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C53" s="268" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D53" s="224" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F53" s="289"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C54" s="94">
         <f>Normalized_FCF!C8/G35</f>
@@ -7919,7 +7920,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C11/G40</f>
@@ -7936,19 +7937,19 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B57" s="161" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C57" s="268" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D57" s="224" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F57" s="289"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C58" s="101"/>
       <c r="D58" s="23">
@@ -7959,7 +7960,7 @@
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B59" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C59" s="101"/>
       <c r="D59" s="94">
@@ -7973,19 +7974,19 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="161" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C61" s="268" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D61" s="224" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F61" s="289"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C62" s="94">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -7996,12 +7997,12 @@
         <v>1.3197490690642218E-3</v>
       </c>
       <c r="F62" s="289" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" s="81" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -8012,21 +8013,21 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B65" s="16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C65" s="267" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D65" s="210" t="s">
-        <v>312</v>
-      </c>
-      <c r="F65" s="294" t="s">
-        <v>63</v>
+        <v>310</v>
+      </c>
+      <c r="F65" s="293" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B66" s="108" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -8034,15 +8035,15 @@
       </c>
       <c r="D66" s="191">
         <f>C66-D75</f>
-        <v>1902339.7312688304</v>
+        <v>1823806.3881188305</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B67" s="108" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -8052,7 +8053,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="108" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -8062,7 +8063,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="108" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -8072,7 +8073,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C70" s="83">
         <f>SUM(C66:C69)</f>
@@ -8084,70 +8085,73 @@
       <c r="F71" s="289"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="292" t="s">
-        <v>351</v>
+      <c r="B72" s="291" t="s">
+        <v>346</v>
       </c>
       <c r="C72" s="267" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D72" s="209" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F72" s="289"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
+        <v>345</v>
+      </c>
+      <c r="C73" s="191">
+        <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
+        <v>-138958.140525</v>
+      </c>
+      <c r="D73" s="191">
+        <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
+        <v>-140154.2686468616</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="294" t="s">
         <v>350</v>
       </c>
-      <c r="C73" s="191">
-        <f>(Normalized_FCF!G25+Normalized_FCF!G35)/12</f>
-        <v>-125869.25</v>
-      </c>
-      <c r="D73" s="191">
-        <f>(Normalized_FCF!C25+Normalized_FCF!C35)/12</f>
-        <v>-127065.37812186161</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="295" t="s">
-        <v>356</v>
-      </c>
-      <c r="C74" s="296">
+      <c r="C74" s="295">
         <f>-$C$66/C73</f>
-        <v>21.170635401418537</v>
-      </c>
-      <c r="D74" s="296">
+        <v>19.176508766829585</v>
+      </c>
+      <c r="D74" s="295">
         <f>-$C$66/D73</f>
-        <v>20.971345927483078</v>
+        <v>19.012849381806323</v>
       </c>
       <c r="F74" s="289" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="82" t="s">
-        <v>353</v>
-      </c>
-      <c r="C75" s="300"/>
-      <c r="D75" s="299">
+        <v>348</v>
+      </c>
+      <c r="C75" s="299"/>
+      <c r="D75" s="298">
         <f>MAX(-D73*D76,G5)</f>
-        <v>762392.26873116964</v>
+        <v>840925.61188116961</v>
       </c>
       <c r="F75" s="289" t="s">
-        <v>355</v>
+        <v>385</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="297" t="s">
-        <v>357</v>
-      </c>
-      <c r="C76" s="298"/>
-      <c r="D76" s="335">
-        <f>IF(D74&lt;=3,1,IF(D74&gt;18,IF(D74&gt;36,12,6),2))</f>
+      <c r="B76" s="296" t="s">
+        <v>351</v>
+      </c>
+      <c r="C76" s="297"/>
+      <c r="D76" s="333">
+        <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>6</v>
       </c>
       <c r="F76" s="289" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8155,19 +8159,19 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C78" s="267" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D78" s="210" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F78" s="289"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="108" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -8181,7 +8185,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="108" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -8195,7 +8199,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="108" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -8209,7 +8213,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B82" s="82" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C82" s="83">
         <f>SUM(C79:C81)</f>
@@ -8223,7 +8227,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8234,15 +8238,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D85" s="276" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="273" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -8259,15 +8263,15 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="273" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>2036547.2311512092</v>
+        <v>1952473.4666619902</v>
       </c>
       <c r="D87" s="254">
         <f>C87*$H$1/Common_Shares</f>
-        <v>1.5274102324371277</v>
+        <v>1.4643549169521279</v>
       </c>
       <c r="E87" s="275" t="str">
         <f>Market_currency</f>
@@ -8276,7 +8280,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B88" s="274" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C88" s="191">
         <f>Valuation_Model!C9*Exchange_Rate</f>
@@ -8293,15 +8297,15 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="82" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
-        <v>2243867.3275031792</v>
+        <v>2159793.5630139601</v>
       </c>
       <c r="D89" s="277">
         <f>SUM(D86:D88)</f>
-        <v>1.6829002852648487</v>
+        <v>1.6198449697798489</v>
       </c>
       <c r="E89" s="275" t="str">
         <f>Market_currency</f>
@@ -8341,7 +8345,7 @@
         <v>CNY</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
@@ -8394,12 +8398,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="37"/>
@@ -8417,28 +8421,28 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C3" s="110">
         <f>Data!C3</f>
         <v>1000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="309"/>
+      <c r="E3" s="308"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
     <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="196">
         <f>AVERAGE(G4:K4)</f>
         <v>1583387.2</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="307"/>
+      <c r="E4" s="306"/>
       <c r="F4" s="57"/>
       <c r="G4" s="186">
         <f>Data!C36</f>
@@ -8488,13 +8492,13 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C5" s="197">
         <f>C25</f>
         <v>-1348785.0374623393</v>
       </c>
-      <c r="E5" s="309"/>
+      <c r="E5" s="308"/>
       <c r="G5" s="186">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-1322360</v>
@@ -8543,13 +8547,13 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" s="187">
         <f>C4+C5</f>
         <v>234602.16253766068</v>
       </c>
-      <c r="E6" s="309"/>
+      <c r="E6" s="308"/>
       <c r="G6" s="187">
         <f>IF(G4="","",G4+G5)</f>
         <v>293225</v>
@@ -8598,13 +8602,13 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7" s="197">
         <f>C35</f>
         <v>-175999.5</v>
       </c>
-      <c r="E7" s="309"/>
+      <c r="E7" s="308"/>
       <c r="G7" s="197">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-188071</v>
@@ -8653,14 +8657,14 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C8" s="198">
         <f>C6+C7</f>
         <v>58602.662537660683</v>
       </c>
       <c r="D8" s="60"/>
-      <c r="E8" s="315"/>
+      <c r="E8" s="314"/>
       <c r="F8" s="60"/>
       <c r="G8" s="187">
         <f>IF(G$4="","",G6+G7)</f>
@@ -8710,13 +8714,13 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C9" s="197">
         <f>BS!$G$39*BS!D58</f>
         <v>35974</v>
       </c>
-      <c r="E9" s="309"/>
+      <c r="E9" s="308"/>
       <c r="G9" s="197">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>35974</v>
@@ -8765,13 +8769,13 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C10" s="197">
         <f>-C4*C78</f>
         <v>-35974</v>
       </c>
-      <c r="E10" s="309"/>
+      <c r="E10" s="308"/>
       <c r="G10" s="197">
         <f>Data!C62</f>
         <v>-15312</v>
@@ -8820,14 +8824,14 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C11" s="199">
         <f>C63</f>
         <v>0</v>
       </c>
       <c r="D11" s="172"/>
-      <c r="E11" s="308"/>
+      <c r="E11" s="307"/>
       <c r="F11" s="172"/>
       <c r="G11" s="189">
         <f>G61</f>
@@ -8877,20 +8881,20 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C12" s="197">
         <f>C50</f>
-        <v>20112.955148098936</v>
-      </c>
-      <c r="E12" s="309"/>
+        <v>22288.09073065874</v>
+      </c>
+      <c r="E12" s="308"/>
       <c r="G12" s="197">
         <f>G50</f>
-        <v>20112.955148098936</v>
+        <v>22288.09073065874</v>
       </c>
       <c r="H12" s="197">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>12111.846771442135</v>
+        <v>13448.374088955678</v>
       </c>
       <c r="I12" s="197">
         <f t="shared" si="6"/>
@@ -8932,20 +8936,20 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="10"/>
       <c r="B13" s="71" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C13" s="187">
         <f>SUM(C8:C12)</f>
-        <v>78715.617685759615</v>
-      </c>
-      <c r="E13" s="309"/>
+        <v>80890.753268319415</v>
+      </c>
+      <c r="E13" s="308"/>
       <c r="G13" s="187">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>145928.95514809893</v>
+        <v>148104.09073065873</v>
       </c>
       <c r="H13" s="187">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>34809.846771442135</v>
+        <v>36146.374088955679</v>
       </c>
       <c r="I13" s="187">
         <f t="shared" si="7"/>
@@ -8987,13 +8991,13 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C14" s="197">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-19678.904421439904</v>
-      </c>
-      <c r="E14" s="309"/>
+        <v>-20222.688317079854</v>
+      </c>
+      <c r="E14" s="308"/>
       <c r="G14" s="197">
         <f>Data!C46</f>
         <v>-44449</v>
@@ -9042,14 +9046,14 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C15" s="197">
         <f>-C4*C83</f>
         <v>-2089.6737831682049</v>
       </c>
       <c r="D15" s="61"/>
-      <c r="E15" s="316"/>
+      <c r="E15" s="315"/>
       <c r="F15" s="61"/>
       <c r="G15" s="186">
         <f>Data!C48</f>
@@ -9099,22 +9103,22 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C16" s="200">
         <f>SUM(C13:C15)</f>
-        <v>56947.039481151507</v>
+        <v>58578.391168071357</v>
       </c>
       <c r="D16" s="62"/>
-      <c r="E16" s="317"/>
+      <c r="E16" s="316"/>
       <c r="F16" s="62"/>
       <c r="G16" s="187">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>99280.955148098932</v>
+        <v>101456.09073065873</v>
       </c>
       <c r="H16" s="187">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>13147.846771442135</v>
+        <v>14484.374088955679</v>
       </c>
       <c r="I16" s="187">
         <f t="shared" si="8"/>
@@ -9156,15 +9160,15 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C17" s="197">
         <f>-C4*C85</f>
         <v>0</v>
       </c>
       <c r="D17" s="59"/>
-      <c r="E17" s="308" t="s">
-        <v>368</v>
+      <c r="E17" s="307" t="s">
+        <v>362</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="201"/>
@@ -9182,14 +9186,14 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C18" s="197">
         <v>0</v>
       </c>
       <c r="D18" s="59"/>
-      <c r="E18" s="308" t="s">
-        <v>369</v>
+      <c r="E18" s="307" t="s">
+        <v>363</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="202"/>
@@ -9207,22 +9211,22 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C19" s="187">
         <f>C16+C17</f>
-        <v>56947.039481151507</v>
+        <v>58578.391168071357</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="306"/>
+      <c r="E19" s="305"/>
       <c r="F19" s="27"/>
       <c r="G19" s="189">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>99280.955148098932</v>
+        <v>101456.09073065873</v>
       </c>
       <c r="H19" s="189">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>13147.846771442135</v>
+        <v>14484.374088955679</v>
       </c>
       <c r="I19" s="189">
         <f t="shared" si="9"/>
@@ -9283,12 +9287,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
       <c r="E21" s="67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="37"/>
@@ -9306,11 +9310,11 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="10"/>
       <c r="B22" s="65" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="306"/>
+      <c r="E22" s="305"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -9327,14 +9331,14 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C23" s="203">
         <f>-C4*C28</f>
         <v>-902304.82874495955</v>
       </c>
       <c r="D23" s="59"/>
-      <c r="E23" s="308"/>
+      <c r="E23" s="307"/>
       <c r="F23" s="59"/>
       <c r="G23" s="186">
         <f>Data!C37</f>
@@ -9384,14 +9388,14 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10"/>
       <c r="B24" s="69" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C24" s="197">
         <f>-C4*C29</f>
         <v>-446480.2087173796</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="306"/>
+      <c r="E24" s="305"/>
       <c r="F24" s="27"/>
       <c r="G24" s="186">
         <f>Data!C40</f>
@@ -9441,14 +9445,14 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10"/>
       <c r="B25" s="71" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C25" s="187">
         <f>C23+C24</f>
         <v>-1348785.0374623393</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="314"/>
+      <c r="E25" s="313"/>
       <c r="F25" s="9"/>
       <c r="G25" s="187">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -9497,27 +9501,27 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="10"/>
-      <c r="E26" s="309"/>
+      <c r="E26" s="308"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="65" t="s">
-        <v>211</v>
-      </c>
-      <c r="E27" s="309"/>
+        <v>210</v>
+      </c>
+      <c r="E27" s="308"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C28" s="64">
         <f>AVERAGE(G28:H28)</f>
         <v>0.56985734679739708</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="307" t="s">
-        <v>370</v>
+      <c r="E28" s="306" t="s">
+        <v>364</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -9576,8 +9580,8 @@
         <v>0.28197790705733861</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="307" t="s">
-        <v>370</v>
+      <c r="E29" s="306" t="s">
+        <v>364</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -9628,13 +9632,13 @@
     <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10"/>
       <c r="B30" s="71" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C30" s="72">
         <f>ABS(C25/$C$4)</f>
         <v>0.8518352538547358</v>
       </c>
-      <c r="E30" s="309"/>
+      <c r="E30" s="308"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.81850227626525374</v>
@@ -9682,26 +9686,26 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10"/>
-      <c r="E31" s="309"/>
+      <c r="E31" s="308"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10"/>
       <c r="B32" s="65" t="s">
-        <v>48</v>
-      </c>
-      <c r="E32" s="309"/>
+        <v>47</v>
+      </c>
+      <c r="E32" s="308"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C33" s="204">
         <f>AVERAGE(G33:H33)</f>
         <v>-175999.5</v>
       </c>
-      <c r="E33" s="307" t="s">
-        <v>370</v>
+      <c r="E33" s="306" t="s">
+        <v>364</v>
       </c>
       <c r="G33" s="197">
         <f>Data!C41</f>
@@ -9751,15 +9755,15 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C34" s="204">
         <f>AVERAGE(G34:J34)</f>
         <v>0</v>
       </c>
       <c r="D34" s="59"/>
-      <c r="E34" s="307" t="s">
-        <v>370</v>
+      <c r="E34" s="306" t="s">
+        <v>364</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="186">
@@ -9810,14 +9814,14 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="10"/>
       <c r="B35" s="71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C35" s="187">
         <f>C33+C34</f>
         <v>-175999.5</v>
       </c>
       <c r="D35" s="59"/>
-      <c r="E35" s="308"/>
+      <c r="E35" s="307"/>
       <c r="F35" s="59"/>
       <c r="G35" s="187">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -9866,14 +9870,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="10"/>
-      <c r="E36" s="309"/>
+      <c r="E36" s="308"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10"/>
       <c r="B37" s="65" t="s">
-        <v>212</v>
-      </c>
-      <c r="E37" s="309"/>
+        <v>211</v>
+      </c>
+      <c r="E37" s="308"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="10"/>
@@ -9886,7 +9890,7 @@
         <v>0.11115379737817763</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="306"/>
+      <c r="E38" s="305"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -9944,7 +9948,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="306"/>
+      <c r="E39" s="305"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -9994,13 +9998,13 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="10"/>
       <c r="B40" s="71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C40" s="72">
         <f>ABS(C35/$C$4)</f>
         <v>0.11115379737817763</v>
       </c>
-      <c r="E40" s="309"/>
+      <c r="E40" s="308"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>0.11641046432097352</v>
@@ -10048,35 +10052,35 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="10"/>
-      <c r="E41" s="309"/>
+      <c r="E41" s="308"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10"/>
       <c r="B42" s="65" t="s">
-        <v>213</v>
-      </c>
-      <c r="E42" s="309"/>
+        <v>212</v>
+      </c>
+      <c r="E42" s="308"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>176</v>
-      </c>
-      <c r="C43" s="303">
+        <v>175</v>
+      </c>
+      <c r="C43" s="302">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="306" t="s">
-        <v>371</v>
+      <c r="E43" s="305" t="s">
+        <v>365</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.35483420146557754</v>
+        <v>0.34877801945308878</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>1.4693250239481581</v>
+        <v>1.3437658127909475</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
@@ -10121,12 +10125,12 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
       <c r="E45" s="67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="37"/>
@@ -10144,20 +10148,20 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="10"/>
       <c r="B46" s="65" t="s">
-        <v>64</v>
-      </c>
-      <c r="E46" s="309"/>
+        <v>63</v>
+      </c>
+      <c r="E46" s="308"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C47" s="197">
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-1003</v>
       </c>
-      <c r="E47" s="309"/>
+      <c r="E47" s="308"/>
       <c r="G47" s="197">
         <f>Data!C51</f>
         <v>-1003</v>
@@ -10206,111 +10210,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C48" s="197">
         <f>BS!D75*C53</f>
-        <v>21115.955148098936</v>
-      </c>
-      <c r="E48" s="309"/>
-      <c r="G48" s="336">
+        <v>23291.09073065874</v>
+      </c>
+      <c r="E48" s="308"/>
+      <c r="G48" s="334">
         <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
-        <v>21115.955148098936</v>
-      </c>
-      <c r="H48" s="336">
+        <v>23291.09073065874</v>
+      </c>
+      <c r="H48" s="334">
         <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
-        <v>12974.846771442135</v>
-      </c>
-      <c r="I48" s="336">
+        <v>14311.374088955678</v>
+      </c>
+      <c r="I48" s="334">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J48" s="336">
+      <c r="J48" s="334">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K48" s="336">
+      <c r="K48" s="334">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="336" t="str">
+      <c r="L48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="M48" s="336" t="str">
+      <c r="M48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="N48" s="336" t="str">
+      <c r="N48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="O48" s="336" t="str">
+      <c r="O48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="P48" s="336" t="str">
+      <c r="P48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="336" t="str">
+      <c r="Q48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
-      <c r="B49" s="331" t="s">
-        <v>379</v>
-      </c>
-      <c r="C49" s="332">
+      <c r="B49" s="329" t="s">
+        <v>373</v>
+      </c>
+      <c r="C49" s="330">
         <f>BS!$C$66*C53</f>
         <v>73805</v>
       </c>
-      <c r="D49" s="333"/>
-      <c r="E49" s="334"/>
-      <c r="F49" s="333"/>
-      <c r="G49" s="332">
+      <c r="D49" s="331"/>
+      <c r="E49" s="332"/>
+      <c r="F49" s="331"/>
+      <c r="G49" s="330">
         <f>Data!C52</f>
         <v>73805</v>
       </c>
-      <c r="H49" s="332">
+      <c r="H49" s="330">
         <f>Data!D52</f>
         <v>45350</v>
       </c>
-      <c r="I49" s="332">
+      <c r="I49" s="330">
         <f>Data!E52</f>
         <v>0</v>
       </c>
-      <c r="J49" s="332">
+      <c r="J49" s="330">
         <f>Data!F52</f>
         <v>0</v>
       </c>
-      <c r="K49" s="332">
+      <c r="K49" s="330">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="332" t="str">
+      <c r="L49" s="330" t="str">
         <f>Data!H52</f>
         <v/>
       </c>
-      <c r="M49" s="332" t="str">
+      <c r="M49" s="330" t="str">
         <f>Data!I52</f>
         <v/>
       </c>
-      <c r="N49" s="332" t="str">
+      <c r="N49" s="330" t="str">
         <f>Data!J52</f>
         <v/>
       </c>
-      <c r="O49" s="332" t="str">
+      <c r="O49" s="330" t="str">
         <f>Data!K52</f>
         <v/>
       </c>
-      <c r="P49" s="332" t="str">
+      <c r="P49" s="330" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="332" t="str">
+      <c r="Q49" s="330" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -10318,20 +10322,20 @@
     <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="10"/>
       <c r="B50" s="71" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C50" s="187">
         <f>C47+C48</f>
-        <v>20112.955148098936</v>
-      </c>
-      <c r="E50" s="309"/>
+        <v>22288.09073065874</v>
+      </c>
+      <c r="E50" s="308"/>
       <c r="G50" s="187">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>20112.955148098936</v>
+        <v>22288.09073065874</v>
       </c>
       <c r="H50" s="187">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>12111.846771442135</v>
+        <v>13448.374088955678</v>
       </c>
       <c r="I50" s="187">
         <f t="shared" si="20"/>
@@ -10372,29 +10376,29 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="10"/>
-      <c r="E51" s="309"/>
+      <c r="E51" s="308"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="10"/>
       <c r="B52" s="73" t="s">
-        <v>160</v>
-      </c>
-      <c r="E52" s="309"/>
+        <v>159</v>
+      </c>
+      <c r="E52" s="308"/>
       <c r="G52" s="100" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C53" s="89">
         <f>G53</f>
         <v>2.7696969151119136E-2</v>
       </c>
-      <c r="E53" s="306" t="s">
-        <v>372</v>
+      <c r="E53" s="305" t="s">
+        <v>366</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -10414,14 +10418,14 @@
     <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C54" s="84">
         <f>G54</f>
         <v>2.9500867672578604E-2</v>
       </c>
-      <c r="E54" s="306" t="s">
-        <v>373</v>
+      <c r="E54" s="305" t="s">
+        <v>367</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -10441,13 +10445,13 @@
     <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
         <v>58.427380396471271</v>
       </c>
-      <c r="E55" s="309"/>
+      <c r="E55" s="308"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>104.839481555334</v>
@@ -10495,28 +10499,28 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="10"/>
-      <c r="E56" s="309"/>
+      <c r="E56" s="308"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="10"/>
       <c r="B57" s="65" t="s">
-        <v>173</v>
-      </c>
-      <c r="E57" s="309"/>
+        <v>172</v>
+      </c>
+      <c r="E57" s="308"/>
       <c r="G57" s="100" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C58" s="197">
         <f>BS!$C79*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="309"/>
+      <c r="E58" s="308"/>
       <c r="G58" s="197">
         <f>Data!C56</f>
         <v>0</v>
@@ -10565,13 +10569,13 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C59" s="197">
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="309"/>
+      <c r="E59" s="308"/>
       <c r="G59" s="197">
         <f>Data!C55</f>
         <v>0</v>
@@ -10620,13 +10624,13 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C60" s="197">
         <f>BS!$C81*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="309"/>
+      <c r="E60" s="308"/>
       <c r="G60" s="197">
         <f>Data!C57</f>
         <v>0</v>
@@ -10675,13 +10679,13 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C61" s="187">
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="309"/>
+      <c r="E61" s="308"/>
       <c r="G61" s="187">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
@@ -10730,13 +10734,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>165</v>
-      </c>
-      <c r="C62" s="304">
-        <v>0</v>
-      </c>
-      <c r="E62" s="307" t="s">
-        <v>374</v>
+        <v>164</v>
+      </c>
+      <c r="C62" s="303">
+        <v>0</v>
+      </c>
+      <c r="E62" s="306" t="s">
+        <v>368</v>
       </c>
       <c r="G62" s="197">
         <f>Data!C58</f>
@@ -10786,13 +10790,13 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C63" s="187">
         <f>C61+C62</f>
         <v>0</v>
       </c>
-      <c r="E63" s="309"/>
+      <c r="E63" s="308"/>
       <c r="G63" s="187">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>39310</v>
@@ -10840,28 +10844,28 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="10"/>
-      <c r="E64" s="309"/>
+      <c r="E64" s="308"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="10"/>
       <c r="B65" s="99" t="s">
-        <v>174</v>
-      </c>
-      <c r="E65" s="309"/>
+        <v>173</v>
+      </c>
+      <c r="E65" s="308"/>
       <c r="G65" s="100" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C66" s="180">
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="309"/>
+      <c r="E66" s="308"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -10880,13 +10884,13 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="10"/>
       <c r="B67" s="108" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C67" s="180">
         <f>G67</f>
         <v>0</v>
       </c>
-      <c r="E67" s="309"/>
+      <c r="E67" s="308"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>0</v>
@@ -10905,13 +10909,13 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="10"/>
       <c r="B68" s="108" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C68" s="180">
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="309"/>
+      <c r="E68" s="308"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$81,0)</f>
         <v>0</v>
@@ -10930,14 +10934,14 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C69" s="72">
         <f>C61/BS!C70</f>
         <v>0</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="314"/>
+      <c r="E69" s="313"/>
       <c r="F69" s="9"/>
       <c r="G69" s="72">
         <f>G61/BS!C70</f>
@@ -10960,12 +10964,12 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -10983,11 +10987,11 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="10"/>
       <c r="B72" s="73" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C72" s="63"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="306"/>
+      <c r="E72" s="305"/>
       <c r="F72" s="27"/>
       <c r="G72" s="100"/>
       <c r="H72" s="12"/>
@@ -11004,14 +11008,14 @@
     <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C73" s="79">
         <f>ABS(C5/C$4)</f>
         <v>0.8518352538547358</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="306"/>
+      <c r="E73" s="305"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -11061,14 +11065,14 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C74" s="80">
         <f>ABS(C6/C$4)</f>
         <v>0.1481647461452642</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="306"/>
+      <c r="E74" s="305"/>
       <c r="F74" s="27"/>
       <c r="G74" s="66">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -11118,14 +11122,14 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C75" s="79">
         <f>ABS(C7/C$4)</f>
         <v>0.11115379737817763</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="306"/>
+      <c r="E75" s="305"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -11175,14 +11179,14 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C76" s="80">
         <f>ABS(C8/C$4)</f>
         <v>3.7010948767086591E-2</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="306"/>
+      <c r="E76" s="305"/>
       <c r="F76" s="27"/>
       <c r="G76" s="66">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -11232,14 +11236,14 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C77" s="79">
         <f>ABS(C9/C$4)</f>
         <v>2.2719648106287585E-2</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="306"/>
+      <c r="E77" s="305"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -11289,14 +11293,14 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C78" s="90">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
         <v>2.2719648106287585E-2</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="307" t="s">
+      <c r="E78" s="306" t="s">
         <v>391</v>
       </c>
       <c r="F78" s="27"/>
@@ -11348,14 +11352,14 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C79" s="80">
         <f>ABS(C11/C$4)</f>
         <v>0</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="306"/>
+      <c r="E79" s="305"/>
       <c r="F79" s="27"/>
       <c r="G79" s="66">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -11405,22 +11409,22 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C80" s="79">
         <f>ABS(C12/C$4)</f>
-        <v>1.270248688892959E-2</v>
+        <v>1.4076209995040214E-2</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="306"/>
+      <c r="E80" s="305"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>1.2449332686363723E-2</v>
+        <v>1.379567817890036E-2</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>8.3724102169596918E-3</v>
+        <v>9.296295333701781E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
@@ -11462,22 +11466,22 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="10"/>
       <c r="B81" s="71" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C81" s="80">
         <f>C13/C4</f>
-        <v>4.9713435656016179E-2</v>
+        <v>5.10871587621268E-2</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="306"/>
+      <c r="E81" s="305"/>
       <c r="F81" s="27"/>
       <c r="G81" s="66">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>9.0325767538135676E-2</v>
+        <v>9.1672113030672311E-2</v>
       </c>
       <c r="H81" s="66">
         <f t="shared" si="32"/>
-        <v>2.406258287936729E-2</v>
+        <v>2.4986467996109377E-2</v>
       </c>
       <c r="I81" s="66">
         <f t="shared" si="32"/>
@@ -11519,14 +11523,14 @@
     <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C82" s="79">
         <f>ABS(C14/C$4)</f>
-        <v>1.2428358914004045E-2</v>
+        <v>1.27717896905317E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="306"/>
+      <c r="E82" s="305"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -11579,12 +11583,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="305">
+      <c r="C83" s="304">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>1.3197490690642218E-3</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="306"/>
+      <c r="E83" s="305"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -11634,22 +11638,22 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C84" s="80">
         <f>ABS(C16/C$4)</f>
-        <v>3.5965327672947911E-2</v>
+        <v>3.6995620002530878E-2</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="306"/>
+      <c r="E84" s="305"/>
       <c r="F84" s="27"/>
       <c r="G84" s="66">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>6.1452015924942933E-2</v>
+        <v>6.2798361417479576E-2</v>
       </c>
       <c r="H84" s="66">
         <f t="shared" si="35"/>
-        <v>9.0885534400742506E-3</v>
+        <v>1.0012438556816342E-2</v>
       </c>
       <c r="I84" s="66">
         <f t="shared" si="35"/>
@@ -11691,13 +11695,13 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C85" s="305">
+        <v>54</v>
+      </c>
+      <c r="C85" s="304">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="308" t="str">
+      <c r="E85" s="307" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
@@ -11717,12 +11721,12 @@
     <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C86" s="79">
         <v>0</v>
       </c>
-      <c r="E86" s="308" t="str">
+      <c r="E86" s="307" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -11741,22 +11745,22 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C87" s="80">
         <f>ABS(C19/C$4)</f>
-        <v>3.5965327672947911E-2</v>
+        <v>3.6995620002530878E-2</v>
       </c>
       <c r="D87" s="77"/>
-      <c r="E87" s="306"/>
+      <c r="E87" s="305"/>
       <c r="F87" s="77"/>
       <c r="G87" s="66">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>6.1452015924942933E-2</v>
+        <v>6.2798361417479576E-2</v>
       </c>
       <c r="H87" s="66">
         <f t="shared" si="36"/>
-        <v>9.0885534400742506E-3</v>
+        <v>1.0012438556816342E-2</v>
       </c>
       <c r="I87" s="66">
         <f t="shared" si="36"/>
@@ -11797,14 +11801,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="10"/>
-      <c r="E88" s="309"/>
+      <c r="E88" s="308"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="10"/>
       <c r="B89" s="65" t="s">
-        <v>219</v>
-      </c>
-      <c r="E89" s="309"/>
+        <v>218</v>
+      </c>
+      <c r="E89" s="308"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="10"/>
@@ -11816,7 +11820,7 @@
         <f>G90</f>
         <v>0.1178</v>
       </c>
-      <c r="E90" s="309"/>
+      <c r="E90" s="308"/>
       <c r="G90" s="116">
         <f>Data!C64</f>
         <v>0.1178</v>
@@ -11872,7 +11876,7 @@
         <f>C90*Common_Shares/$C$3</f>
         <v>157066.6863</v>
       </c>
-      <c r="E91" s="309"/>
+      <c r="E91" s="308"/>
       <c r="G91" s="76">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
         <v>157066.6863</v>
@@ -11921,16 +11925,16 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>2.7581185559608659</v>
-      </c>
-      <c r="E92" s="309"/>
+        <v>2.6813076147712724</v>
+      </c>
+      <c r="E92" s="308"/>
       <c r="G92" s="174">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>1.5820424578480456</v>
+        <v>1.5481247618437604</v>
       </c>
       <c r="H92" s="174">
         <f t="shared" si="38"/>
@@ -11976,13 +11980,13 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
         <v>5.4036697247706419E-2</v>
       </c>
-      <c r="E93" s="309"/>
+      <c r="E93" s="308"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>5.4036697247706419E-2</v>
@@ -12030,16 +12034,16 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="10"/>
-      <c r="E94" s="309"/>
+      <c r="E94" s="308"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="10"/>
       <c r="B95" s="161" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C95" s="63"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="306"/>
+      <c r="E95" s="305"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -12056,14 +12060,14 @@
     <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C96" s="79">
         <f>C4/G4-1</f>
         <v>-1.992949922164422E-2</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="306"/>
+      <c r="E96" s="305"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -12113,22 +12117,22 @@
     <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="10"/>
       <c r="B97" s="71" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C97" s="79">
         <f>C13/G13-1</f>
-        <v>-0.46058945186119171</v>
+        <v>-0.4538249897808232</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="306"/>
+      <c r="E97" s="305"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>3.1921745908924395</v>
+        <v>3.0973429414020011</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.56813757384350083</v>
+        <v>-0.55155617566166892</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
@@ -12173,12 +12177,12 @@
     <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C99" s="54"/>
       <c r="D99" s="56"/>
       <c r="E99" s="67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F99" s="56"/>
       <c r="G99" s="37"/>
@@ -12196,24 +12200,24 @@
     <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="10"/>
       <c r="B100" s="65" t="s">
-        <v>29</v>
-      </c>
-      <c r="E100" s="309"/>
+        <v>28</v>
+      </c>
+      <c r="E100" s="308"/>
       <c r="G100" s="100" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C101" s="205">
         <f>BS!G32</f>
         <v>3670169</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="310"/>
+      <c r="E101" s="309"/>
       <c r="F101" s="26"/>
       <c r="G101" s="186">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -12263,14 +12267,14 @@
     <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="10"/>
       <c r="B102" s="95" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C102" s="206">
         <f>BS!C4</f>
         <v>180994</v>
       </c>
       <c r="D102" s="91"/>
-      <c r="E102" s="311"/>
+      <c r="E102" s="310"/>
       <c r="F102" s="91"/>
       <c r="G102" s="188">
         <f>IF(G$4="","",Data!D76)</f>
@@ -12320,14 +12324,14 @@
     <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="10"/>
       <c r="B103" s="95" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C103" s="206">
         <f>BS!C6+BS!C7</f>
         <v>158110</v>
       </c>
       <c r="D103" s="91"/>
-      <c r="E103" s="311"/>
+      <c r="E103" s="310"/>
       <c r="F103" s="91"/>
       <c r="G103" s="188">
         <f>IF(G$4="","",Data!D77)</f>
@@ -12377,14 +12381,14 @@
     <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C104" s="205">
         <f>BS!G30</f>
         <v>642877</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="310"/>
+      <c r="E104" s="309"/>
       <c r="F104" s="26"/>
       <c r="G104" s="186">
         <f>Data!C78</f>
@@ -12434,14 +12438,14 @@
     <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C105" s="205">
         <f>BS!G27</f>
         <v>3027292</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="310"/>
+      <c r="E105" s="309"/>
       <c r="F105" s="26"/>
       <c r="G105" s="186">
         <f>Data!C79</f>
@@ -12490,19 +12494,19 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="10"/>
-      <c r="E106" s="309"/>
+      <c r="E106" s="308"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="10"/>
       <c r="B107" s="93" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="310"/>
+      <c r="E107" s="309"/>
       <c r="F107" s="26"/>
       <c r="G107" s="100" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H107" s="12"/>
       <c r="I107" s="12"/>
@@ -12518,14 +12522,14 @@
     <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C108" s="97">
         <f>C102/C$4</f>
         <v>0.11430811111773545</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="310"/>
+      <c r="E108" s="309"/>
       <c r="F108" s="26"/>
       <c r="G108" s="97">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -12575,14 +12579,14 @@
     <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C109" s="97">
         <f>C103/C$4</f>
         <v>9.9855550177492911E-2</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="310"/>
+      <c r="E109" s="309"/>
       <c r="F109" s="26"/>
       <c r="G109" s="97">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -12632,14 +12636,14 @@
     <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C110" s="97">
         <f>BS!$G$38/C$4</f>
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="310"/>
+      <c r="E110" s="309"/>
       <c r="F110" s="26"/>
       <c r="G110" s="97">
         <f>BS!$G$38/G$4</f>
@@ -12658,16 +12662,16 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="10"/>
-      <c r="E111" s="309"/>
+      <c r="E111" s="308"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="10"/>
       <c r="B112" s="93" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C112" s="55"/>
       <c r="D112" s="55"/>
-      <c r="E112" s="312"/>
+      <c r="E112" s="311"/>
       <c r="F112" s="55"/>
       <c r="G112" s="23" t="str">
         <f>IFERROR(IF(#REF!*G114*(1/#REF!)=G116,"","Error"),"")</f>
@@ -12717,20 +12721,20 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C113" s="23">
         <f>C81</f>
-        <v>4.9713435656016179E-2</v>
-      </c>
-      <c r="E113" s="309"/>
+        <v>5.10871587621268E-2</v>
+      </c>
+      <c r="E113" s="308"/>
       <c r="G113" s="23">
         <f t="shared" ref="G113:Q113" si="45">G81</f>
-        <v>9.0325767538135676E-2</v>
+        <v>9.1672113030672311E-2</v>
       </c>
       <c r="H113" s="23">
         <f t="shared" si="45"/>
-        <v>2.406258287936729E-2</v>
+        <v>2.4986467996109377E-2</v>
       </c>
       <c r="I113" s="23">
         <f t="shared" si="45"/>
@@ -12771,13 +12775,13 @@
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B114" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C114" s="42">
         <f>C4/C101</f>
         <v>0.43142078743512902</v>
       </c>
-      <c r="E114" s="309"/>
+      <c r="E114" s="308"/>
       <c r="G114" s="42">
         <f t="shared" ref="G114:Q114" si="46">IF(G4="","",G4/G101)</f>
         <v>0.44019362596109335</v>
@@ -12825,14 +12829,14 @@
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B115" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C115" s="15">
         <f>C101/C105</f>
         <v>1.2123604198075375</v>
       </c>
       <c r="D115" s="11"/>
-      <c r="E115" s="313"/>
+      <c r="E115" s="312"/>
       <c r="F115" s="11"/>
       <c r="G115" s="15">
         <f t="shared" ref="G115:Q115" si="47">IF(G$4="","",G101/G105)</f>
@@ -12882,14 +12886,14 @@
     <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="10"/>
       <c r="B116" s="71" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C116" s="105">
         <f>C8/C105</f>
         <v>1.9358113633458775E-2</v>
       </c>
       <c r="D116" s="106"/>
-      <c r="E116" s="312"/>
+      <c r="E116" s="311"/>
       <c r="F116" s="106"/>
       <c r="G116" s="105">
         <f t="shared" ref="G116:Q116" si="48">IF(G$4="","",G8/G105)</f>
@@ -12958,12 +12962,12 @@
     <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A118" s="10"/>
       <c r="B118" s="54" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C118" s="54"/>
       <c r="D118" s="56"/>
       <c r="E118" s="67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F118" s="56"/>
       <c r="G118" s="37"/>
@@ -12981,11 +12985,11 @@
     <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="10"/>
       <c r="B119" s="182" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C119" s="183"/>
       <c r="D119" s="27"/>
-      <c r="E119" s="306"/>
+      <c r="E119" s="305"/>
       <c r="F119" s="27"/>
       <c r="G119" s="12"/>
       <c r="H119" s="12"/>
@@ -13007,18 +13011,18 @@
       </c>
       <c r="C120" s="181">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>4.5723426463104282E-2</v>
+        <v>4.7033257308955877E-2</v>
       </c>
       <c r="D120" s="27"/>
-      <c r="E120" s="306"/>
+      <c r="E120" s="305"/>
       <c r="F120" s="27"/>
       <c r="G120" s="181">
         <f t="shared" ref="G120:Q120" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>7.9713809414154721E-2</v>
+        <v>8.1460250541956852E-2</v>
       </c>
       <c r="H120" s="181">
         <f t="shared" si="49"/>
-        <v>1.0556555889111191E-2</v>
+        <v>1.1629668891561253E-2</v>
       </c>
       <c r="I120" s="181">
         <f t="shared" si="49"/>
@@ -13060,22 +13064,22 @@
     <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="10"/>
       <c r="B121" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C121" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.0974048836286365E-2</v>
+        <v>2.1574888673832972E-2</v>
       </c>
       <c r="D121" s="27"/>
-      <c r="E121" s="306"/>
+      <c r="E121" s="305"/>
       <c r="F121" s="27"/>
       <c r="G121" s="79">
         <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
-        <v>3.656596762117189E-2</v>
+        <v>3.7367087404567359E-2</v>
       </c>
       <c r="H121" s="79">
         <f t="shared" ref="H121" si="51">IF(H$4="","",H120/Market_Price)</f>
-        <v>4.8424568298675186E-3</v>
+        <v>5.3347105007161702E-3</v>
       </c>
       <c r="I121" s="79">
         <f t="shared" ref="I121" si="52">IF(I$4="","",I120/Market_Price)</f>
@@ -13829,43 +13833,43 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="134" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="112" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C3" s="110">
         <f>Normalized_FCF!C3</f>
         <v>1000</v>
       </c>
       <c r="E3" s="112" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H3" s="124"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B4" s="103" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C4" s="113">
         <f>Normalized_FCF!C19</f>
-        <v>56947.039481151507</v>
+        <v>58578.391168071357</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
       <c r="E4" s="103" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F4" s="138">
         <f>Thesis!C75</f>
@@ -13875,7 +13879,7 @@
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B5" s="233" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C5" s="234">
         <f>Thesis!C70</f>
@@ -13886,25 +13890,25 @@
     </row>
     <row r="6" spans="2:8" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="153" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C6" s="238">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>711837.99351439381</v>
+        <v>732229.88960089197</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
       <c r="E6" s="344" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F6" s="344"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" s="152" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C7" s="232">
         <f>BS!G31</f>
@@ -13920,11 +13924,11 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B8" s="152" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C8" s="207">
         <f>BS!D66</f>
-        <v>1902339.7312688304</v>
+        <v>1823806.3881188305</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -13936,7 +13940,7 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B9" s="233" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C9" s="235">
         <f>BS!H42</f>
@@ -13952,11 +13956,11 @@
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B10" s="153" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C10" s="238">
         <f>C6-C7+C8+C9</f>
-        <v>2807835.5247832239</v>
+        <v>2749694.0777197224</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -13966,7 +13970,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="236" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C11" s="237">
         <f>Exchange_Rate</f>
@@ -13980,11 +13984,11 @@
     </row>
     <row r="12" spans="2:8" ht="13.5" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B12" s="153" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>2.2544431160536522</v>
+        <v>2.2077606861417975</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -13997,7 +14001,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B14" s="36" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -14007,13 +14011,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B15" s="123" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H15" s="124"/>
     </row>
     <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C16" s="165">
         <f>Scenarios!C65</f>
@@ -14023,7 +14027,7 @@
     </row>
     <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C17" s="166">
         <f>Scenarios!C64</f>
@@ -14033,11 +14037,11 @@
     </row>
     <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="157" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>2.287092012929318</v>
+        <v>2.2413448701452832</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14050,19 +14054,19 @@
     </row>
     <row r="20" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="132" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" s="132" t="s">
         <v>112</v>
       </c>
-      <c r="C20" s="132" t="s">
+      <c r="D20" s="132" t="s">
+        <v>122</v>
+      </c>
+      <c r="E20" s="132" t="s">
         <v>113</v>
       </c>
-      <c r="D20" s="132" t="s">
-        <v>123</v>
-      </c>
-      <c r="E20" s="132" t="s">
+      <c r="F20" s="133" t="s">
         <v>114</v>
-      </c>
-      <c r="F20" s="133" t="s">
-        <v>115</v>
       </c>
       <c r="H20" s="124"/>
     </row>
@@ -14072,7 +14076,7 @@
       </c>
       <c r="C21" s="127">
         <f>C4*(1+D21)</f>
-        <v>57960.170893822891</v>
+        <v>59620.545575690179</v>
       </c>
       <c r="D21" s="142">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -14084,7 +14088,7 @@
       </c>
       <c r="F21" s="129">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>53666.824901687854</v>
+        <v>55204.208866379791</v>
       </c>
       <c r="H21" s="124"/>
     </row>
@@ -14094,7 +14098,7 @@
       </c>
       <c r="C22" s="127">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>58991.326689652618</v>
+        <v>60681.240707758116</v>
       </c>
       <c r="D22" s="142">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -14106,7 +14110,7 @@
       </c>
       <c r="F22" s="129">
         <f t="shared" si="1"/>
-        <v>50575.554432143872</v>
+        <v>52024.383322837886</v>
       </c>
       <c r="H22" s="124"/>
     </row>
@@ -14116,7 +14120,7 @@
       </c>
       <c r="C23" s="127">
         <f t="shared" si="2"/>
-        <v>60040.827536210738</v>
+        <v>61760.806417951906</v>
       </c>
       <c r="D23" s="142">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -14128,7 +14132,7 @@
       </c>
       <c r="F23" s="129">
         <f t="shared" si="1"/>
-        <v>47662.344675775676</v>
+        <v>49027.71936597563</v>
       </c>
       <c r="H23" s="124"/>
     </row>
@@ -14138,7 +14142,7 @@
       </c>
       <c r="C24" s="127">
         <f t="shared" si="2"/>
-        <v>61108.999805988766</v>
+        <v>62859.57842829766</v>
       </c>
       <c r="D24" s="142">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -14150,7 +14154,7 @@
       </c>
       <c r="F24" s="129">
         <f t="shared" si="1"/>
-        <v>44916.939131934414</v>
+        <v>46203.666678998736</v>
       </c>
       <c r="H24" s="124"/>
     </row>
@@ -14160,7 +14164,7 @@
       </c>
       <c r="C25" s="127">
         <f t="shared" si="2"/>
-        <v>62196.1756778946</v>
+        <v>63977.898433573224</v>
       </c>
       <c r="D25" s="142">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -14172,7 +14176,7 @@
       </c>
       <c r="F25" s="129">
         <f t="shared" si="1"/>
-        <v>42329.672086134458</v>
+        <v>43542.282655422008</v>
       </c>
       <c r="H25" s="124"/>
     </row>
@@ -14182,7 +14186,7 @@
       </c>
       <c r="C26" s="127">
         <f t="shared" si="2"/>
-        <v>63302.693240553133</v>
+        <v>65116.11420756804</v>
       </c>
       <c r="D26" s="142">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -14194,7 +14198,7 @@
       </c>
       <c r="F26" s="129">
         <f t="shared" si="1"/>
-        <v>39891.434580094989</v>
+        <v>41034.197394260773</v>
       </c>
       <c r="H26" s="124"/>
     </row>
@@ -14204,7 +14208,7 @@
       </c>
       <c r="C27" s="127">
         <f t="shared" si="2"/>
-        <v>64428.896597444626</v>
+        <v>66274.57971123344</v>
       </c>
       <c r="D27" s="142">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -14216,7 +14220,7 @@
       </c>
       <c r="F27" s="129">
         <f t="shared" si="1"/>
-        <v>37593.642341946113</v>
+        <v>38670.580711539398</v>
       </c>
       <c r="H27" s="124"/>
     </row>
@@ -14226,7 +14230,7 @@
       </c>
       <c r="C28" s="127">
         <f t="shared" si="2"/>
-        <v>65575.135973913581</v>
+        <v>67453.655202756883</v>
       </c>
       <c r="D28" s="142">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -14238,7 +14242,7 @@
       </c>
       <c r="F28" s="129">
         <f t="shared" si="1"/>
-        <v>35428.20556369167</v>
+        <v>36443.111051974352</v>
       </c>
       <c r="H28" s="124"/>
     </row>
@@ -14248,7 +14252,7 @@
       </c>
       <c r="C29" s="127">
         <f t="shared" si="2"/>
-        <v>66741.767826081385</v>
+        <v>68653.70734959477</v>
       </c>
       <c r="D29" s="142">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -14260,7 +14264,7 @@
       </c>
       <c r="F29" s="129">
         <f t="shared" si="1"/>
-        <v>33387.500419524855</v>
+        <v>34343.946191380244</v>
       </c>
       <c r="H29" s="124"/>
     </row>
@@ -14270,7 +14274,7 @@
       </c>
       <c r="C30" s="127">
         <f t="shared" si="2"/>
-        <v>67929.154951696648</v>
+        <v>69875.109342498094</v>
       </c>
       <c r="D30" s="142">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -14282,7 +14286,7 @@
       </c>
       <c r="F30" s="129">
         <f t="shared" si="1"/>
-        <v>31464.342224721371</v>
+        <v>32365.695626650398</v>
       </c>
       <c r="H30" s="124"/>
     </row>
@@ -14728,11 +14732,11 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B51" s="130" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C51" s="127">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>724502.13617278612</v>
+        <v>745256.8196961272</v>
       </c>
       <c r="D51" s="143">
         <f>Terminal_Growth</f>
@@ -14744,18 +14748,18 @@
       </c>
       <c r="F51" s="129">
         <f t="shared" si="1"/>
-        <v>335584.67157867772</v>
+        <v>345198.10583394777</v>
       </c>
       <c r="H51" s="124"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C52" s="118"/>
       <c r="E52" s="131" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F52" s="141">
         <f>SUM(F21:F51)</f>
-        <v>752501.13193633303</v>
+        <v>774057.89769936702</v>
       </c>
       <c r="H52" s="124"/>
     </row>
@@ -14765,7 +14769,7 @@
     </row>
     <row r="54" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B54" s="123" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C54" s="140"/>
       <c r="D54" s="140"/>
@@ -14776,7 +14780,7 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="137">
         <f>F52</f>
-        <v>752501.13193633303</v>
+        <v>774057.89769936702</v>
       </c>
       <c r="B55" s="135">
         <f>C78</f>
@@ -14806,19 +14810,19 @@
       </c>
       <c r="B56" s="127">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>646774.20219119103</v>
+        <v>665302.22744788707</v>
       </c>
       <c r="C56" s="127">
-        <v>646774.20219119103</v>
+        <v>665302.22744788707</v>
       </c>
       <c r="D56" s="127">
-        <v>734805.6134661606</v>
+        <v>755855.45886651648</v>
       </c>
       <c r="E56" s="127">
-        <v>782834.64992065635</v>
+        <v>805260.37456521951</v>
       </c>
       <c r="F56" s="127">
-        <v>807957.37299356516</v>
+        <v>831102.78380686371</v>
       </c>
       <c r="H56" s="124"/>
     </row>
@@ -14827,19 +14831,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="127">
-        <v>596902.29432997096</v>
+        <v>614001.64793383703</v>
       </c>
       <c r="C57" s="127">
-        <v>596902.29432997096</v>
+        <v>614001.64793383703</v>
       </c>
       <c r="D57" s="127">
-        <v>757794.38296644716</v>
+        <v>779502.78354800644</v>
       </c>
       <c r="E57" s="127">
-        <v>864076.63168071466</v>
+        <v>888829.68089211243</v>
       </c>
       <c r="F57" s="127">
-        <v>925566.61583202088</v>
+        <v>952081.15765634226</v>
       </c>
       <c r="H57" s="124"/>
     </row>
@@ -14848,19 +14852,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="127">
-        <v>545648.99738135375</v>
+        <v>561280.10692549124</v>
       </c>
       <c r="C58" s="127">
-        <v>545648.99738135375</v>
+        <v>561280.10692549124</v>
       </c>
       <c r="D58" s="127">
-        <v>786249.35941153276</v>
+        <v>808772.90463007218</v>
       </c>
       <c r="E58" s="127">
-        <v>975828.1120001704</v>
+        <v>1003782.4859440906</v>
       </c>
       <c r="F58" s="127">
-        <v>1096558.6967710464</v>
+        <v>1127971.6182518224</v>
       </c>
       <c r="H58" s="124"/>
     </row>
@@ -14869,19 +14873,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="127">
-        <v>502120.1618071241</v>
+        <v>516504.30855932954</v>
       </c>
       <c r="C59" s="127">
-        <v>502120.1618071241</v>
+        <v>516504.30855932954</v>
       </c>
       <c r="D59" s="127">
-        <v>815240.41715440119</v>
+        <v>838594.46403528017</v>
       </c>
       <c r="E59" s="127">
-        <v>1103306.1754221052</v>
+        <v>1134912.3907207896</v>
       </c>
       <c r="F59" s="127">
-        <v>1303882.2403312929</v>
+        <v>1341234.3224006922</v>
       </c>
       <c r="H59" s="124"/>
     </row>
@@ -14890,19 +14894,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="127">
-        <v>468176.28883232875</v>
+        <v>481588.05150728382</v>
       </c>
       <c r="C60" s="127">
-        <v>468176.28883232875</v>
+        <v>481588.05150728382</v>
       </c>
       <c r="D60" s="127">
-        <v>842203.70956934139</v>
+        <v>866330.16908074159</v>
       </c>
       <c r="E60" s="127">
-        <v>1236899.3099307937</v>
+        <v>1272332.5439354072</v>
       </c>
       <c r="F60" s="127">
-        <v>1535932.3668752026</v>
+        <v>1579931.9475474516</v>
       </c>
       <c r="H60" s="124"/>
     </row>
@@ -14911,19 +14915,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="127">
-        <v>442917.45375306928</v>
+        <v>455605.63108291052</v>
       </c>
       <c r="C61" s="127">
-        <v>442917.45375306928</v>
+        <v>455605.63108291052</v>
       </c>
       <c r="D61" s="127">
-        <v>865989.08429383812</v>
+        <v>890796.9191942726</v>
       </c>
       <c r="E61" s="127">
-        <v>1370475.4673670502</v>
+        <v>1409735.2337384261</v>
       </c>
       <c r="F61" s="127">
-        <v>1784810.9903178543</v>
+        <v>1835940.1525432554</v>
       </c>
       <c r="H61" s="124"/>
     </row>
@@ -14936,7 +14940,7 @@
     </row>
     <row r="63" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B63" s="123" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C63" s="118"/>
       <c r="D63" s="118"/>
@@ -14973,23 +14977,23 @@
       </c>
       <c r="B65" s="128">
         <f>C12</f>
-        <v>2.2544431160536522</v>
+        <v>2.2077606861417975</v>
       </c>
       <c r="C65" s="128">
         <f>C12</f>
-        <v>2.2544431160536522</v>
+        <v>2.2077606861417975</v>
       </c>
       <c r="D65" s="128">
         <f>C12</f>
-        <v>2.2544431160536522</v>
+        <v>2.2077606861417975</v>
       </c>
       <c r="E65" s="145">
         <f>C12</f>
-        <v>2.2544431160536522</v>
+        <v>2.2077606861417975</v>
       </c>
       <c r="F65" s="128">
         <f>C12</f>
-        <v>2.2544431160536522</v>
+        <v>2.2077606861417975</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -15000,23 +15004,23 @@
       </c>
       <c r="B66" s="128">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.2022026571100071</v>
+        <v>2.1540237040847532</v>
       </c>
       <c r="C66" s="128">
         <f t="shared" si="4"/>
-        <v>2.2022026571100071</v>
+        <v>2.1540237040847532</v>
       </c>
       <c r="D66" s="128">
         <f t="shared" si="4"/>
-        <v>2.2728840796483394</v>
+        <v>2.2267299247327395</v>
       </c>
       <c r="E66" s="128">
         <f t="shared" si="4"/>
-        <v>2.3114471399308281</v>
+        <v>2.266397694127726</v>
       </c>
       <c r="F66" s="128">
         <f t="shared" si="4"/>
-        <v>2.3316184603619328</v>
+        <v>2.2871468587788724</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -15027,23 +15031,23 @@
       </c>
       <c r="B67" s="128">
         <f t="shared" si="4"/>
-        <v>2.1621599343900324</v>
+        <v>2.1128338846262427</v>
       </c>
       <c r="C67" s="128">
         <f t="shared" si="4"/>
-        <v>2.1621599343900324</v>
+        <v>2.1128338846262427</v>
       </c>
       <c r="D67" s="128">
         <f t="shared" si="4"/>
-        <v>2.291342024456366</v>
+        <v>2.2457166309948113</v>
       </c>
       <c r="E67" s="128">
         <f t="shared" si="4"/>
-        <v>2.3766772521994799</v>
+        <v>2.3334964417926516</v>
       </c>
       <c r="F67" s="128">
         <f t="shared" si="4"/>
-        <v>2.426048260669381</v>
+        <v>2.3842817727398242</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -15054,23 +15058,23 @@
       </c>
       <c r="B68" s="128">
         <f t="shared" si="4"/>
-        <v>2.1210080786417209</v>
+        <v>2.0705031590032803</v>
       </c>
       <c r="C68" s="128">
         <f t="shared" si="4"/>
-        <v>2.1210080786417209</v>
+        <v>2.0705031590032803</v>
       </c>
       <c r="D68" s="128">
         <f t="shared" si="4"/>
-        <v>2.3141888490648137</v>
+        <v>2.269217944514454</v>
       </c>
       <c r="E68" s="128">
         <f t="shared" si="4"/>
-        <v>2.466403788277284</v>
+        <v>2.4257933579521178</v>
       </c>
       <c r="F68" s="128">
         <f t="shared" si="4"/>
-        <v>2.5633397495654182</v>
+        <v>2.5255062264405446</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -15081,23 +15085,23 @@
       </c>
       <c r="B69" s="128">
         <f t="shared" si="4"/>
-        <v>2.086058280890398</v>
+        <v>2.0345521606269807</v>
       </c>
       <c r="C69" s="128">
         <f t="shared" si="4"/>
-        <v>2.086058280890398</v>
+        <v>2.0345521606269807</v>
       </c>
       <c r="D69" s="128">
         <f t="shared" si="4"/>
-        <v>2.3374660994516829</v>
+        <v>2.2931620141430504</v>
       </c>
       <c r="E69" s="128">
         <f t="shared" si="4"/>
-        <v>2.568757377008811</v>
+        <v>2.5310790516913988</v>
       </c>
       <c r="F69" s="128">
         <f t="shared" si="4"/>
-        <v>2.729802183511342</v>
+        <v>2.6967372800531044</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -15108,23 +15112,23 @@
       </c>
       <c r="B70" s="128">
         <f t="shared" si="4"/>
-        <v>2.0588043587554341</v>
+        <v>2.0065175002437226</v>
       </c>
       <c r="C70" s="128">
         <f t="shared" si="4"/>
-        <v>2.0588043587554341</v>
+        <v>2.0065175002437226</v>
       </c>
       <c r="D70" s="128">
         <f t="shared" si="4"/>
-        <v>2.3591152339663184</v>
+        <v>2.315431327554299</v>
       </c>
       <c r="E70" s="128">
         <f t="shared" si="4"/>
-        <v>2.6760208259490383</v>
+        <v>2.6414152575293999</v>
       </c>
       <c r="F70" s="128">
         <f t="shared" si="4"/>
-        <v>2.9161178724998154</v>
+        <v>2.888390321365776</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15134,40 +15138,40 @@
       </c>
       <c r="B71" s="128">
         <f t="shared" si="4"/>
-        <v>2.0385237524445046</v>
+        <v>1.9856559190196361</v>
       </c>
       <c r="C71" s="128">
         <f t="shared" si="4"/>
-        <v>2.0385237524445046</v>
+        <v>1.9856559190196361</v>
       </c>
       <c r="D71" s="128">
         <f t="shared" si="4"/>
-        <v>2.3782127821799146</v>
+        <v>2.3350759598266659</v>
       </c>
       <c r="E71" s="128">
         <f t="shared" si="4"/>
-        <v>2.7832706438044901</v>
+        <v>2.7517374417953699</v>
       </c>
       <c r="F71" s="128">
         <f t="shared" si="4"/>
-        <v>3.1159453532766714</v>
+        <v>3.0939422243571739</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B73" s="175" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C73" s="175" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D73" s="175" t="s">
+        <v>116</v>
+      </c>
+      <c r="E73" s="176" t="s">
         <v>117</v>
       </c>
-      <c r="E73" s="176" t="s">
-        <v>118</v>
-      </c>
       <c r="F73" s="176" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
@@ -15185,7 +15189,7 @@
       </c>
       <c r="E74" s="139">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>2.5633397495654182</v>
+        <v>2.5255062264405446</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
@@ -15207,7 +15211,7 @@
       </c>
       <c r="E75" s="139">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>2.3766772521994799</v>
+        <v>2.3334964417926516</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -15230,7 +15234,7 @@
       </c>
       <c r="E76" s="139">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>2.291342024456366</v>
+        <v>2.2457166309948113</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15253,7 +15257,7 @@
       </c>
       <c r="E77" s="139">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>2.1621599343900324</v>
+        <v>2.1128338846262427</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -15276,7 +15280,7 @@
       </c>
       <c r="E78" s="139">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.1210080786417209</v>
+        <v>2.0705031590032803</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
@@ -15292,20 +15296,20 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="159" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C80" s="159" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="81" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C81" s="159" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="82" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C82" s="159" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="92" spans="3:3" x14ac:dyDescent="0.35">
@@ -15357,20 +15361,20 @@
   <sheetData>
     <row r="2" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="283" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="I2" s="284"/>
     </row>
     <row r="3" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="163" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H3" s="282">
         <v>0</v>
@@ -15382,14 +15386,14 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B4" s="156" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C4" s="124">
         <v>3</v>
       </c>
       <c r="D4" s="124"/>
       <c r="E4" s="159" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F4" s="159"/>
       <c r="H4" s="282">
@@ -15411,14 +15415,14 @@
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B6" s="163" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" s="110">
         <f>Valuation_Model!C3</f>
         <v>1000</v>
       </c>
       <c r="E6" s="103" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F6" s="103"/>
       <c r="H6" s="282">
@@ -15426,12 +15430,12 @@
       </c>
       <c r="I6" s="270">
         <f t="shared" si="0"/>
-        <v>2.4073715355423082</v>
+        <v>2.3616954232004934</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="103" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C7" s="118">
         <f>Normalized_FCF!G8</f>
@@ -15456,11 +15460,11 @@
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" s="103" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" s="118">
         <f>Normalized_FCF!G19</f>
-        <v>99280.955148098932</v>
+        <v>101456.09073065873</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15478,11 +15482,11 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B9" s="103" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C9" s="207">
         <f>Normalized_FCF!C19</f>
-        <v>56947.039481151507</v>
+        <v>58578.391168071357</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -15511,7 +15515,7 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="163" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E11" s="346"/>
       <c r="F11" s="346"/>
@@ -15525,7 +15529,7 @@
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B12" s="122" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C12" s="162">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
@@ -15544,7 +15548,7 @@
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B13" s="152" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C13" s="162">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
@@ -15562,18 +15566,18 @@
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="103" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C14" s="162">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-0.2951485762236955</v>
+        <v>-0.29003821304292421</v>
       </c>
       <c r="E14" s="346"/>
       <c r="F14" s="346"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -15582,21 +15586,21 @@
     </row>
     <row r="17" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B17" s="112" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E17" s="163" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C18" s="154">
         <v>10</v>
       </c>
       <c r="E18" s="346" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="F18" s="347"/>
     </row>
@@ -15606,14 +15610,14 @@
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="163" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E20" s="347"/>
       <c r="F20" s="347"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
@@ -15628,11 +15632,11 @@
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
-        <v>2.2544431160536522</v>
+        <v>2.2077606861417975</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -15643,16 +15647,16 @@
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="163" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E24" s="163" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F24" s="163"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C25" s="170">
         <f>C18</f>
@@ -15664,7 +15668,7 @@
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C26" s="168">
         <v>0.02</v>
@@ -15675,11 +15679,11 @@
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C27" s="164">
         <f>Valuation_Model!E76</f>
-        <v>2.291342024456366</v>
+        <v>2.2457166309948113</v>
       </c>
       <c r="D27" s="164" t="str">
         <f>Market_currency</f>
@@ -15690,7 +15694,7 @@
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C28" s="169">
         <v>0.6</v>
@@ -15701,16 +15705,16 @@
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="163" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E30" s="163" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F30" s="163"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B31" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C31" s="170">
         <f>C18</f>
@@ -15722,7 +15726,7 @@
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C32" s="168">
         <v>-0.06</v>
@@ -15733,11 +15737,11 @@
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C33" s="164">
         <f>Valuation_Model!E77</f>
-        <v>2.1621599343900324</v>
+        <v>2.1128338846262427</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -15748,7 +15752,7 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C34" s="169">
         <v>0.15</v>
@@ -15759,16 +15763,16 @@
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="163" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E36" s="163" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F36" s="163"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C37" s="170">
         <f>C18</f>
@@ -15780,7 +15784,7 @@
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C38" s="168">
         <v>0.06</v>
@@ -15791,11 +15795,11 @@
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C39" s="164">
         <f>Valuation_Model!E75</f>
-        <v>2.3766772521994799</v>
+        <v>2.3334964417926516</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -15806,7 +15810,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C40" s="171">
         <f>1-C28-C34</f>
@@ -15818,11 +15822,11 @@
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C42" s="158">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>2.2932985178821945</v>
+        <v>2.2477291717389862</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -15831,7 +15835,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B44" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -15840,12 +15844,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B45" s="112" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C46" s="154">
         <v>15</v>
@@ -15860,16 +15864,16 @@
     </row>
     <row r="48" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B48" s="163" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E48" s="163" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F48" s="163"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C49" s="170">
         <f>C46</f>
@@ -15881,7 +15885,7 @@
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C50" s="168">
         <v>-0.06</v>
@@ -15892,11 +15896,11 @@
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C51" s="164">
         <f>Valuation_Model!E78</f>
-        <v>2.1210080786417209</v>
+        <v>2.0705031590032803</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -15907,7 +15911,7 @@
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C52" s="169">
         <v>0.1</v>
@@ -15918,16 +15922,16 @@
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="163" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="E54" s="163" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F54" s="163"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B55" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C55" s="170">
         <f>C46</f>
@@ -15939,7 +15943,7 @@
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C56" s="168">
         <v>0.08</v>
@@ -15950,11 +15954,11 @@
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C57" s="164">
         <f>Valuation_Model!E74</f>
-        <v>2.5633397495654182</v>
+        <v>2.5255062264405446</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -15965,7 +15969,7 @@
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C58" s="169">
         <v>0.05</v>
@@ -15976,27 +15980,27 @@
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C60" s="158">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>2.2895715355423083</v>
+        <v>2.2438954232004935</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E60" s="103" t="s">
-        <v>324</v>
-      </c>
-      <c r="F60" s="319">
+        <v>321</v>
+      </c>
+      <c r="F60" s="318">
         <f>Thesis!E20</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>310</v>
+        <v>382</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16005,63 +16009,63 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="112" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E63" s="288" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B64" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C64" s="170">
         <v>10</v>
       </c>
       <c r="D64" s="154"/>
       <c r="E64" s="287" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B65" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C65" s="155">
         <v>1.77907652777404E-2</v>
       </c>
       <c r="D65" s="155"/>
       <c r="E65" s="287" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B66" s="103" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C66" s="164">
         <f>Valuation_Model!C18</f>
-        <v>2.287092012929318</v>
+        <v>2.2413448701452832</v>
       </c>
       <c r="D66" s="164" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E66" s="287" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="112" t="s">
-        <v>319</v>
+        <v>383</v>
       </c>
       <c r="E68" s="288" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="103" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C69" s="279" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16071,19 +16075,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="103" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C70" s="279" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="287" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="103" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C71" s="279" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16093,23 +16097,23 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C72" s="278" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="E72" s="138" t="s">
-        <v>385</v>
-      </c>
-      <c r="F72" s="337">
+        <v>379</v>
+      </c>
+      <c r="F72" s="335">
         <f>BS!D89/C60</f>
-        <v>0.73502847984447739</v>
+        <v>0.72188968925719621</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B74" s="36" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -16118,12 +16122,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B75" s="112" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="281" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C76" s="280">
         <f>F60</f>
@@ -16133,7 +16137,7 @@
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B77" s="103" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C77" s="177">
         <f>Normalized_FCF!C90</f>
@@ -16146,12 +16150,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="112" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="152" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C80" s="171">
         <f>Thesis!C121</f>
@@ -16160,7 +16164,7 @@
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B81" s="103" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C81" s="120">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -16172,32 +16176,32 @@
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B82" s="103" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
-        <v>1.3249835275129098</v>
+        <v>1.2985505921299152</v>
       </c>
       <c r="D82" s="120"/>
     </row>
     <row r="83" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B83" s="114" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
-        <v>1.5731270460314284</v>
+        <v>1.5466941106484338</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E83" s="150" t="s">
-        <v>131</v>
-      </c>
-      <c r="F83" s="337">
+        <v>130</v>
+      </c>
+      <c r="F83" s="335">
         <f>(1-C83/C60)</f>
-        <v>0.31291640308638913</v>
+        <v>0.31071025206586211</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16205,12 +16209,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="112" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="152" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
@@ -16223,53 +16227,53 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="103" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>6.9675781490122768E-2</v>
+        <v>6.3214262000776955E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B88" s="103"/>
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
-      <c r="E89" s="328" t="s">
-        <v>359</v>
-      </c>
-      <c r="F89" s="325"/>
+      <c r="E89" s="326" t="s">
+        <v>353</v>
+      </c>
+      <c r="F89" s="323"/>
       <c r="G89" s="2"/>
-      <c r="H89" s="324"/>
+      <c r="H89" s="322"/>
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E90" s="321" t="s">
-        <v>360</v>
-      </c>
-      <c r="F90" s="326" t="s">
-        <v>361</v>
+      <c r="E90" s="319" t="s">
+        <v>354</v>
+      </c>
+      <c r="F90" s="324" t="s">
+        <v>355</v>
       </c>
       <c r="G90" s="2"/>
-      <c r="H90" s="324"/>
+      <c r="H90" s="322"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E91" s="322" t="s">
-        <v>360</v>
-      </c>
-      <c r="F91" s="326" t="s">
-        <v>362</v>
+      <c r="E91" s="320" t="s">
+        <v>354</v>
+      </c>
+      <c r="F91" s="324" t="s">
+        <v>356</v>
       </c>
       <c r="G91" s="2"/>
-      <c r="H91" s="324"/>
+      <c r="H91" s="322"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E92" s="323" t="s">
-        <v>360</v>
-      </c>
-      <c r="F92" s="327" t="s">
-        <v>363</v>
+      <c r="E92" s="321" t="s">
+        <v>354</v>
+      </c>
+      <c r="F92" s="325" t="s">
+        <v>357</v>
       </c>
       <c r="G92" s="2"/>
-      <c r="H92" s="324"/>
+      <c r="H92" s="322"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EDDA013-DF85-4A23-9478-2C3611481D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C73890BB-4DA2-4882-B0CC-92609CA7BE55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2003,7 +2003,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>C0001</t>
+    <t>CNS_04</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3690,7 +3690,7 @@
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
     <col min="3" max="3" width="25.59765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.59765625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.86328125" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C73890BB-4DA2-4882-B0CC-92609CA7BE55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D181FCB-8977-4B59-96CC-3DE9843EE1AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D181FCB-8977-4B59-96CC-3DE9843EE1AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A67C9126-F021-43D8-8035-E5A7AA649313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3378,20 +3378,20 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3750,7 +3750,7 @@
         <v>98</v>
       </c>
       <c r="C6" s="50">
-        <v>2.1800000000000002</v>
+        <v>2.15</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>42</v>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>2906.6670300000001</v>
+        <v>2866.6670250000002</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -3805,13 +3805,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
+      <c r="B12" s="339" t="s">
         <v>285</v>
       </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="C12" s="339"/>
+      <c r="D12" s="339"/>
+      <c r="E12" s="339"/>
+      <c r="F12" s="339"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3845,7 +3845,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0705486500000001</v>
+        <v>1.0726275699999999</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="C20" s="258">
         <f>C127</f>
-        <v>1.5466941106484338</v>
+        <v>1.5492157922151617</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>334</v>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
-        <v>6.3214262000776955E-2</v>
+        <v>6.9019080849287207E-2</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3913,22 +3913,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
+      <c r="B25" s="339" t="s">
         <v>235</v>
       </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="C25" s="339"/>
+      <c r="D25" s="339"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="340"/>
+      <c r="D26" s="340"/>
+      <c r="E26" s="340"/>
+      <c r="F26" s="340"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
@@ -3940,13 +3940,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="340" t="s">
+      <c r="B29" s="338" t="s">
         <v>237</v>
       </c>
-      <c r="C29" s="340"/>
-      <c r="D29" s="340"/>
-      <c r="E29" s="340"/>
-      <c r="F29" s="340"/>
+      <c r="C29" s="338"/>
+      <c r="D29" s="338"/>
+      <c r="E29" s="338"/>
+      <c r="F29" s="338"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3966,13 +3966,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="340" t="s">
+      <c r="B32" s="338" t="s">
         <v>239</v>
       </c>
-      <c r="C32" s="340"/>
-      <c r="D32" s="340"/>
-      <c r="E32" s="340"/>
-      <c r="F32" s="340"/>
+      <c r="C32" s="338"/>
+      <c r="D32" s="338"/>
+      <c r="E32" s="338"/>
+      <c r="F32" s="338"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4001,13 +4001,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="340" t="s">
+      <c r="B36" s="338" t="s">
         <v>242</v>
       </c>
-      <c r="C36" s="340"/>
-      <c r="D36" s="340"/>
-      <c r="E36" s="340"/>
-      <c r="F36" s="340"/>
+      <c r="C36" s="338"/>
+      <c r="D36" s="338"/>
+      <c r="E36" s="338"/>
+      <c r="F36" s="338"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4023,13 +4023,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="340" t="s">
+      <c r="B39" s="338" t="s">
         <v>246</v>
       </c>
-      <c r="C39" s="340"/>
-      <c r="D39" s="340"/>
-      <c r="E39" s="340"/>
-      <c r="F39" s="340"/>
+      <c r="C39" s="338"/>
+      <c r="D39" s="338"/>
+      <c r="E39" s="338"/>
+      <c r="F39" s="338"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4093,13 +4093,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="340" t="s">
+      <c r="B47" s="338" t="s">
         <v>247</v>
       </c>
-      <c r="C47" s="340"/>
-      <c r="D47" s="340"/>
-      <c r="E47" s="340"/>
-      <c r="F47" s="340"/>
+      <c r="C47" s="338"/>
+      <c r="D47" s="338"/>
+      <c r="E47" s="338"/>
+      <c r="F47" s="338"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4115,13 +4115,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="340" t="s">
+      <c r="B50" s="338" t="s">
         <v>369</v>
       </c>
-      <c r="C50" s="341"/>
-      <c r="D50" s="341"/>
-      <c r="E50" s="341"/>
-      <c r="F50" s="341"/>
+      <c r="C50" s="342"/>
+      <c r="D50" s="342"/>
+      <c r="E50" s="342"/>
+      <c r="F50" s="342"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4137,22 +4137,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
+      <c r="B53" s="339" t="s">
         <v>374</v>
       </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="C53" s="339"/>
+      <c r="D53" s="339"/>
+      <c r="E53" s="339"/>
+      <c r="F53" s="339"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
+      <c r="B54" s="339" t="s">
         <v>267</v>
       </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="C54" s="339"/>
+      <c r="D54" s="339"/>
+      <c r="E54" s="339"/>
+      <c r="F54" s="339"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C121</f>
-        <v>2.1574888673832972E-2</v>
+        <v>2.1918414948495051E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
-        <v>5.4036697247706419E-2</v>
+        <v>5.4790697674418611E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4213,22 +4213,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="338" t="s">
         <v>302</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="338"/>
+      <c r="D63" s="338"/>
+      <c r="E63" s="338"/>
+      <c r="F63" s="338"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="340" t="s">
         <v>258</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="340"/>
+      <c r="D64" s="340"/>
+      <c r="E64" s="340"/>
+      <c r="F64" s="340"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
@@ -4280,22 +4280,22 @@
       <c r="C71" s="125"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B72" s="338" t="s">
+      <c r="B72" s="339" t="s">
         <v>375</v>
       </c>
-      <c r="C72" s="338"/>
-      <c r="D72" s="338"/>
-      <c r="E72" s="338"/>
-      <c r="F72" s="338"/>
+      <c r="C72" s="339"/>
+      <c r="D72" s="339"/>
+      <c r="E72" s="339"/>
+      <c r="F72" s="339"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
+      <c r="B73" s="339" t="s">
         <v>376</v>
       </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
+      <c r="C73" s="339"/>
+      <c r="D73" s="339"/>
+      <c r="E73" s="339"/>
+      <c r="F73" s="339"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B75" s="47" t="s">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="C76" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.58791571636194839</v>
+        <v>0.58905740174080445</v>
       </c>
       <c r="D76" s="1" t="str">
         <f>Market_currency</f>
@@ -4332,13 +4332,13 @@
       <c r="A79" s="239"/>
     </row>
     <row r="80" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="338" t="s">
+      <c r="B80" s="339" t="s">
         <v>260</v>
       </c>
-      <c r="C80" s="338"/>
-      <c r="D80" s="338"/>
-      <c r="E80" s="338"/>
-      <c r="F80" s="338"/>
+      <c r="C80" s="339"/>
+      <c r="D80" s="339"/>
+      <c r="E80" s="339"/>
+      <c r="F80" s="339"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="1" t="s">
@@ -4351,13 +4351,13 @@
       </c>
     </row>
     <row r="84" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="338" t="s">
+      <c r="B84" s="339" t="s">
         <v>377</v>
       </c>
-      <c r="C84" s="338"/>
-      <c r="D84" s="338"/>
-      <c r="E84" s="338"/>
-      <c r="F84" s="338"/>
+      <c r="C84" s="339"/>
+      <c r="D84" s="339"/>
+      <c r="E84" s="339"/>
+      <c r="F84" s="339"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="47" t="s">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="C86" s="254">
         <f>C85*C28*Exchange_Rate/Common_Shares</f>
-        <v>2.7298184251239473E-2</v>
+        <v>2.7351195145423102E-2</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="C91" s="254">
         <f>C90*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.4643549169521279</v>
+        <v>1.4671985772789613</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Market_currency</f>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="C95" s="254">
         <f>C94*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.18278823707896039</v>
+        <v>0.18314319724058234</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4461,13 +4461,13 @@
       </c>
     </row>
     <row r="97" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="338" t="s">
+      <c r="B97" s="339" t="s">
         <v>266</v>
       </c>
-      <c r="C97" s="338"/>
-      <c r="D97" s="338"/>
-      <c r="E97" s="338"/>
-      <c r="F97" s="338"/>
+      <c r="C97" s="339"/>
+      <c r="D97" s="339"/>
+      <c r="E97" s="339"/>
+      <c r="F97" s="339"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B99" s="47" t="s">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="C99" s="254">
         <f>Valuation_Model!C12</f>
-        <v>2.2077606861417975</v>
+        <v>2.212047981114925</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4493,13 +4493,13 @@
       <c r="F101" s="36"/>
     </row>
     <row r="103" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="340" t="s">
+      <c r="B103" s="338" t="s">
         <v>360</v>
       </c>
-      <c r="C103" s="340"/>
-      <c r="D103" s="340"/>
-      <c r="E103" s="340"/>
-      <c r="F103" s="340"/>
+      <c r="C103" s="338"/>
+      <c r="D103" s="338"/>
+      <c r="E103" s="338"/>
+      <c r="F103" s="338"/>
     </row>
     <row r="105" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B105" s="266" t="s">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="E107" s="251" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>2.33 HKD</v>
+        <v>2.34 HKD</v>
       </c>
       <c r="F107" s="252">
         <f>Valuation_Model!F75</f>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="E109" s="251" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>2.11 HKD</v>
+        <v>2.12 HKD</v>
       </c>
       <c r="F109" s="252">
         <f>Valuation_Model!F77</f>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="C112" s="247">
         <f>Scenarios!C60</f>
-        <v>2.2438954232004935</v>
+        <v>2.2482528889477993</v>
       </c>
       <c r="D112" s="242" t="str">
         <f>Market_currency</f>
@@ -4661,13 +4661,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B118" s="339" t="s">
+      <c r="B118" s="341" t="s">
         <v>274</v>
       </c>
-      <c r="C118" s="339"/>
-      <c r="D118" s="339"/>
-      <c r="E118" s="339"/>
-      <c r="F118" s="339"/>
+      <c r="C118" s="341"/>
+      <c r="D118" s="341"/>
+      <c r="E118" s="341"/>
+      <c r="F118" s="341"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B119" s="240" t="s">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="C126" s="246">
         <f>Scenarios!C82</f>
-        <v>1.2985505921299152</v>
+        <v>1.3010722736966431</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="C127" s="245">
         <f>Scenarios!C83</f>
-        <v>1.5466941106484338</v>
+        <v>1.5492157922151617</v>
       </c>
       <c r="D127" s="47" t="str">
         <f>Reporting_currency</f>
@@ -4749,17 +4749,11 @@
       </c>
       <c r="C128" s="94">
         <f>Scenarios!F83</f>
-        <v>0.31071025206586211</v>
+        <v>0.31092458511630894</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B97:F97"/>
@@ -4775,6 +4769,12 @@
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -7840,11 +7840,11 @@
       </c>
       <c r="C47" s="151">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>2.4274436025512749</v>
+        <v>2.4321575042074168</v>
       </c>
       <c r="D47" s="151">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.7924728545409614</v>
+        <v>1.79595369370391</v>
       </c>
       <c r="F47" s="289"/>
     </row>
@@ -8250,11 +8250,11 @@
       </c>
       <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-36397.583551350006</v>
+        <v>-36468.264752429997</v>
       </c>
       <c r="D86" s="254">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-2.7298184251239473E-2</v>
+        <v>-2.7351195145423106E-2</v>
       </c>
       <c r="E86" s="275" t="str">
         <f>Market_currency</f>
@@ -8267,11 +8267,11 @@
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>1952473.4666619902</v>
+        <v>1956265.0142383778</v>
       </c>
       <c r="D87" s="254">
         <f>C87*$H$1/Common_Shares</f>
-        <v>1.4643549169521279</v>
+        <v>1.4671985772789613</v>
       </c>
       <c r="E87" s="275" t="str">
         <f>Market_currency</f>
@@ -8284,11 +8284,11 @@
       </c>
       <c r="C88" s="191">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>243717.67990332001</v>
+        <v>244190.96017797597</v>
       </c>
       <c r="D88" s="254">
         <f>C88*$H$1/Common_Shares</f>
-        <v>0.18278823707896039</v>
+        <v>0.18314319724058234</v>
       </c>
       <c r="E88" s="275" t="str">
         <f>Market_currency</f>
@@ -8301,11 +8301,11 @@
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
-        <v>2159793.5630139601</v>
+        <v>2163987.7096639238</v>
       </c>
       <c r="D89" s="277">
         <f>SUM(D86:D88)</f>
-        <v>1.6198449697798489</v>
+        <v>1.6229905793741206</v>
       </c>
       <c r="E89" s="275" t="str">
         <f>Market_currency</f>
@@ -11984,12 +11984,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.4036697247706419E-2</v>
+        <v>5.4790697674418611E-2</v>
       </c>
       <c r="E93" s="308"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.4036697247706419E-2</v>
+        <v>5.4790697674418611E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -13011,30 +13011,30 @@
       </c>
       <c r="C120" s="181">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>4.7033257308955877E-2</v>
+        <v>4.7124592139264357E-2</v>
       </c>
       <c r="D120" s="27"/>
       <c r="E120" s="305"/>
       <c r="F120" s="27"/>
       <c r="G120" s="181">
         <f t="shared" ref="G120:Q120" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>8.1460250541956852E-2</v>
+        <v>8.1618439844289514E-2</v>
       </c>
       <c r="H120" s="181">
         <f t="shared" si="49"/>
-        <v>1.1629668891561253E-2</v>
+        <v>1.1652252779974023E-2</v>
       </c>
       <c r="I120" s="181">
         <f t="shared" si="49"/>
-        <v>6.4717883901121293E-2</v>
+        <v>6.4843560864237079E-2</v>
       </c>
       <c r="J120" s="181">
         <f t="shared" si="49"/>
-        <v>0.22763593412908442</v>
+        <v>0.22807798493749895</v>
       </c>
       <c r="K120" s="181">
         <f t="shared" si="49"/>
-        <v>0.16292517285487843</v>
+        <v>0.16324156053174993</v>
       </c>
       <c r="L120" s="181" t="str">
         <f t="shared" si="49"/>
@@ -13068,30 +13068,30 @@
       </c>
       <c r="C121" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.1574888673832972E-2</v>
+        <v>2.1918414948495051E-2</v>
       </c>
       <c r="D121" s="27"/>
       <c r="E121" s="305"/>
       <c r="F121" s="27"/>
       <c r="G121" s="79">
         <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
-        <v>3.7367087404567359E-2</v>
+        <v>3.7962065043855589E-2</v>
       </c>
       <c r="H121" s="79">
         <f t="shared" ref="H121" si="51">IF(H$4="","",H120/Market_Price)</f>
-        <v>5.3347105007161702E-3</v>
+        <v>5.4196524558018716E-3</v>
       </c>
       <c r="I121" s="79">
         <f t="shared" ref="I121" si="52">IF(I$4="","",I120/Market_Price)</f>
-        <v>2.968710270693637E-2</v>
+        <v>3.0159795750807947E-2</v>
       </c>
       <c r="J121" s="79">
         <f t="shared" ref="J121" si="53">IF(J$4="","",J120/Market_Price)</f>
-        <v>0.10442015327022221</v>
+        <v>0.10608278369185999</v>
       </c>
       <c r="K121" s="79">
         <f t="shared" ref="K121" si="54">IF(K$4="","",K120/Market_Price)</f>
-        <v>7.4736317823338727E-2</v>
+        <v>7.5926307224069733E-2</v>
       </c>
       <c r="L121" s="79" t="str">
         <f t="shared" ref="L121" si="55">IF(L$4="","",L120/Market_Price)</f>
@@ -13974,7 +13974,7 @@
       </c>
       <c r="C11" s="237">
         <f>Exchange_Rate</f>
-        <v>1.0705486500000001</v>
+        <v>1.0726275699999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -13988,7 +13988,7 @@
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>2.2077606861417975</v>
+        <v>2.212047981114925</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14041,7 +14041,7 @@
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>2.2413448701452832</v>
+        <v>2.2456973829222053</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14977,23 +14977,23 @@
       </c>
       <c r="B65" s="128">
         <f>C12</f>
-        <v>2.2077606861417975</v>
+        <v>2.212047981114925</v>
       </c>
       <c r="C65" s="128">
         <f>C12</f>
-        <v>2.2077606861417975</v>
+        <v>2.212047981114925</v>
       </c>
       <c r="D65" s="128">
         <f>C12</f>
-        <v>2.2077606861417975</v>
+        <v>2.212047981114925</v>
       </c>
       <c r="E65" s="145">
         <f>C12</f>
-        <v>2.2077606861417975</v>
+        <v>2.212047981114925</v>
       </c>
       <c r="F65" s="128">
         <f>C12</f>
-        <v>2.2077606861417975</v>
+        <v>2.212047981114925</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -15004,23 +15004,23 @@
       </c>
       <c r="B66" s="128">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.1540237040847532</v>
+        <v>2.1582066461293725</v>
       </c>
       <c r="C66" s="128">
         <f t="shared" si="4"/>
-        <v>2.1540237040847532</v>
+        <v>2.1582066461293725</v>
       </c>
       <c r="D66" s="128">
         <f t="shared" si="4"/>
-        <v>2.2267299247327395</v>
+        <v>2.2310540564526056</v>
       </c>
       <c r="E66" s="128">
         <f t="shared" si="4"/>
-        <v>2.266397694127726</v>
+        <v>2.2707988574884714</v>
       </c>
       <c r="F66" s="128">
         <f t="shared" si="4"/>
-        <v>2.2871468587788724</v>
+        <v>2.2915883153606469</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -15031,23 +15031,23 @@
       </c>
       <c r="B67" s="128">
         <f t="shared" si="4"/>
-        <v>2.1128338846262427</v>
+        <v>2.1169368393302879</v>
       </c>
       <c r="C67" s="128">
         <f t="shared" si="4"/>
-        <v>2.1128338846262427</v>
+        <v>2.1169368393302879</v>
       </c>
       <c r="D67" s="128">
         <f t="shared" si="4"/>
-        <v>2.2457166309948113</v>
+        <v>2.2500776333822388</v>
       </c>
       <c r="E67" s="128">
         <f t="shared" si="4"/>
-        <v>2.3334964417926516</v>
+        <v>2.3380279055638415</v>
       </c>
       <c r="F67" s="128">
         <f t="shared" si="4"/>
-        <v>2.3842817727398242</v>
+        <v>2.3889118575687425</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -15058,23 +15058,23 @@
       </c>
       <c r="B68" s="128">
         <f t="shared" si="4"/>
-        <v>2.0705031590032803</v>
+        <v>2.0745239108180762</v>
       </c>
       <c r="C68" s="128">
         <f t="shared" si="4"/>
-        <v>2.0705031590032803</v>
+        <v>2.0745239108180762</v>
       </c>
       <c r="D68" s="128">
         <f t="shared" si="4"/>
-        <v>2.269217944514454</v>
+        <v>2.2736245845762668</v>
       </c>
       <c r="E68" s="128">
         <f t="shared" si="4"/>
-        <v>2.4257933579521178</v>
+        <v>2.4305040549650125</v>
       </c>
       <c r="F68" s="128">
         <f t="shared" si="4"/>
-        <v>2.5255062264405446</v>
+        <v>2.5304105578824378</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -15085,23 +15085,23 @@
       </c>
       <c r="B69" s="128">
         <f t="shared" si="4"/>
-        <v>2.0345521606269807</v>
+        <v>2.0385030984734485</v>
       </c>
       <c r="C69" s="128">
         <f t="shared" si="4"/>
-        <v>2.0345521606269807</v>
+        <v>2.0385030984734485</v>
       </c>
       <c r="D69" s="128">
         <f t="shared" si="4"/>
-        <v>2.2931620141430504</v>
+        <v>2.2976151516762595</v>
       </c>
       <c r="E69" s="128">
         <f t="shared" si="4"/>
-        <v>2.5310790516913988</v>
+        <v>2.5359942051149647</v>
       </c>
       <c r="F69" s="128">
         <f t="shared" si="4"/>
-        <v>2.6967372800531044</v>
+        <v>2.7019741285291143</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -15112,23 +15112,23 @@
       </c>
       <c r="B70" s="128">
         <f t="shared" si="4"/>
-        <v>2.0065175002437226</v>
+        <v>2.0104139970181629</v>
       </c>
       <c r="C70" s="128">
         <f t="shared" si="4"/>
-        <v>2.0065175002437226</v>
+        <v>2.0104139970181629</v>
       </c>
       <c r="D70" s="128">
         <f t="shared" si="4"/>
-        <v>2.315431327554299</v>
+        <v>2.3199277103160525</v>
       </c>
       <c r="E70" s="128">
         <f t="shared" si="4"/>
-        <v>2.6414152575293999</v>
+        <v>2.6465446750548738</v>
       </c>
       <c r="F70" s="128">
         <f t="shared" si="4"/>
-        <v>2.888390321365776</v>
+        <v>2.8939993447454171</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15138,23 +15138,23 @@
       </c>
       <c r="B71" s="128">
         <f t="shared" si="4"/>
-        <v>1.9856559190196361</v>
+        <v>1.9895119042690388</v>
       </c>
       <c r="C71" s="128">
         <f t="shared" si="4"/>
-        <v>1.9856559190196361</v>
+        <v>1.9895119042690388</v>
       </c>
       <c r="D71" s="128">
         <f t="shared" si="4"/>
-        <v>2.3350759598266659</v>
+        <v>2.3396104908957605</v>
       </c>
       <c r="E71" s="128">
         <f t="shared" si="4"/>
-        <v>2.7517374417953699</v>
+        <v>2.757081096193978</v>
       </c>
       <c r="F71" s="128">
         <f t="shared" si="4"/>
-        <v>3.0939422243571739</v>
+        <v>3.0999504131200664</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="E74" s="139">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>2.5255062264405446</v>
+        <v>2.5304105578824378</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="E75" s="139">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>2.3334964417926516</v>
+        <v>2.3380279055638415</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -15234,7 +15234,7 @@
       </c>
       <c r="E76" s="139">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>2.2457166309948113</v>
+        <v>2.2500776333822388</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15257,7 +15257,7 @@
       </c>
       <c r="E77" s="139">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>2.1128338846262427</v>
+        <v>2.1169368393302879</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="E78" s="139">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.0705031590032803</v>
+        <v>2.0745239108180762</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
@@ -15381,7 +15381,7 @@
       </c>
       <c r="I3" s="270">
         <f>-Market_Price</f>
-        <v>-2.1800000000000002</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -15430,7 +15430,7 @@
       </c>
       <c r="I6" s="270">
         <f t="shared" si="0"/>
-        <v>2.3616954232004934</v>
+        <v>2.3660528889477992</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15621,7 +15621,7 @@
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
-        <v>2.1800000000000002</v>
+        <v>2.15</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -15636,7 +15636,7 @@
       </c>
       <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
-        <v>2.2077606861417975</v>
+        <v>2.212047981114925</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="C27" s="164">
         <f>Valuation_Model!E76</f>
-        <v>2.2457166309948113</v>
+        <v>2.2500776333822388</v>
       </c>
       <c r="D27" s="164" t="str">
         <f>Market_currency</f>
@@ -15741,7 +15741,7 @@
       </c>
       <c r="C33" s="164">
         <f>Valuation_Model!E77</f>
-        <v>2.1128338846262427</v>
+        <v>2.1169368393302879</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -15799,7 +15799,7 @@
       </c>
       <c r="C39" s="164">
         <f>Valuation_Model!E75</f>
-        <v>2.3334964417926516</v>
+        <v>2.3380279055638415</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -15826,7 +15826,7 @@
       </c>
       <c r="C42" s="158">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>2.2477291717389862</v>
+        <v>2.252094082319847</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -15900,7 +15900,7 @@
       </c>
       <c r="C51" s="164">
         <f>Valuation_Model!E78</f>
-        <v>2.0705031590032803</v>
+        <v>2.0745239108180762</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -15958,7 +15958,7 @@
       </c>
       <c r="C57" s="164">
         <f>Valuation_Model!E74</f>
-        <v>2.5255062264405446</v>
+        <v>2.5304105578824378</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C60" s="158">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>2.2438954232004935</v>
+        <v>2.2482528889477993</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16045,7 +16045,7 @@
       </c>
       <c r="C66" s="164">
         <f>Valuation_Model!C18</f>
-        <v>2.2413448701452832</v>
+        <v>2.2456973829222053</v>
       </c>
       <c r="D66" s="164" t="str">
         <f>Market_currency</f>
@@ -16180,7 +16180,7 @@
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
-        <v>1.2985505921299152</v>
+        <v>1.3010722736966431</v>
       </c>
       <c r="D82" s="120"/>
     </row>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
-        <v>1.5466941106484338</v>
+        <v>1.5492157922151617</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16201,7 +16201,7 @@
       </c>
       <c r="F83" s="335">
         <f>(1-C83/C60)</f>
-        <v>0.31071025206586211</v>
+        <v>0.31092458511630894</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16218,7 +16218,7 @@
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
-        <v>2.1800000000000002</v>
+        <v>2.15</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16231,7 +16231,7 @@
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>6.3214262000776955E-2</v>
+        <v>6.9019080849287207E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A67C9126-F021-43D8-8035-E5A7AA649313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01709A03-C49B-43FD-BAF8-6841E3430369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3378,20 +3378,20 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3805,13 +3805,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="339" t="s">
+      <c r="B12" s="338" t="s">
         <v>285</v>
       </c>
-      <c r="C12" s="339"/>
-      <c r="D12" s="339"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="339"/>
+      <c r="C12" s="338"/>
+      <c r="D12" s="338"/>
+      <c r="E12" s="338"/>
+      <c r="F12" s="338"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3845,7 +3845,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0726275699999999</v>
+        <v>1.0656545000000002</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="C20" s="258">
         <f>C127</f>
-        <v>1.5492157922151617</v>
+        <v>1.5407576206248625</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>334</v>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
-        <v>6.9019080849287207E-2</v>
+        <v>6.6927308782200656E-2</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3913,22 +3913,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="339" t="s">
+      <c r="B25" s="338" t="s">
         <v>235</v>
       </c>
-      <c r="C25" s="339"/>
-      <c r="D25" s="339"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="339"/>
+      <c r="C25" s="338"/>
+      <c r="D25" s="338"/>
+      <c r="E25" s="338"/>
+      <c r="F25" s="338"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="340" t="s">
+      <c r="B26" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C26" s="340"/>
-      <c r="D26" s="340"/>
-      <c r="E26" s="340"/>
-      <c r="F26" s="340"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
@@ -3940,13 +3940,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="338" t="s">
+      <c r="B29" s="340" t="s">
         <v>237</v>
       </c>
-      <c r="C29" s="338"/>
-      <c r="D29" s="338"/>
-      <c r="E29" s="338"/>
-      <c r="F29" s="338"/>
+      <c r="C29" s="340"/>
+      <c r="D29" s="340"/>
+      <c r="E29" s="340"/>
+      <c r="F29" s="340"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3966,13 +3966,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="338" t="s">
+      <c r="B32" s="340" t="s">
         <v>239</v>
       </c>
-      <c r="C32" s="338"/>
-      <c r="D32" s="338"/>
-      <c r="E32" s="338"/>
-      <c r="F32" s="338"/>
+      <c r="C32" s="340"/>
+      <c r="D32" s="340"/>
+      <c r="E32" s="340"/>
+      <c r="F32" s="340"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4001,13 +4001,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="338" t="s">
+      <c r="B36" s="340" t="s">
         <v>242</v>
       </c>
-      <c r="C36" s="338"/>
-      <c r="D36" s="338"/>
-      <c r="E36" s="338"/>
-      <c r="F36" s="338"/>
+      <c r="C36" s="340"/>
+      <c r="D36" s="340"/>
+      <c r="E36" s="340"/>
+      <c r="F36" s="340"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4023,13 +4023,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="338" t="s">
+      <c r="B39" s="340" t="s">
         <v>246</v>
       </c>
-      <c r="C39" s="338"/>
-      <c r="D39" s="338"/>
-      <c r="E39" s="338"/>
-      <c r="F39" s="338"/>
+      <c r="C39" s="340"/>
+      <c r="D39" s="340"/>
+      <c r="E39" s="340"/>
+      <c r="F39" s="340"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4093,13 +4093,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="338" t="s">
+      <c r="B47" s="340" t="s">
         <v>247</v>
       </c>
-      <c r="C47" s="338"/>
-      <c r="D47" s="338"/>
-      <c r="E47" s="338"/>
-      <c r="F47" s="338"/>
+      <c r="C47" s="340"/>
+      <c r="D47" s="340"/>
+      <c r="E47" s="340"/>
+      <c r="F47" s="340"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4115,13 +4115,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="338" t="s">
+      <c r="B50" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C50" s="342"/>
-      <c r="D50" s="342"/>
-      <c r="E50" s="342"/>
-      <c r="F50" s="342"/>
+      <c r="C50" s="341"/>
+      <c r="D50" s="341"/>
+      <c r="E50" s="341"/>
+      <c r="F50" s="341"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4137,22 +4137,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="339" t="s">
+      <c r="B53" s="338" t="s">
         <v>374</v>
       </c>
-      <c r="C53" s="339"/>
-      <c r="D53" s="339"/>
-      <c r="E53" s="339"/>
-      <c r="F53" s="339"/>
+      <c r="C53" s="338"/>
+      <c r="D53" s="338"/>
+      <c r="E53" s="338"/>
+      <c r="F53" s="338"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="339" t="s">
+      <c r="B54" s="338" t="s">
         <v>267</v>
       </c>
-      <c r="C54" s="339"/>
-      <c r="D54" s="339"/>
-      <c r="E54" s="339"/>
-      <c r="F54" s="339"/>
+      <c r="C54" s="338"/>
+      <c r="D54" s="338"/>
+      <c r="E54" s="338"/>
+      <c r="F54" s="338"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C121</f>
-        <v>2.1918414948495051E-2</v>
+        <v>2.1775925005107808E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4213,22 +4213,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
+      <c r="B63" s="340" t="s">
         <v>302</v>
       </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="340" t="s">
+      <c r="B64" s="342" t="s">
         <v>258</v>
       </c>
-      <c r="C64" s="340"/>
-      <c r="D64" s="340"/>
-      <c r="E64" s="340"/>
-      <c r="F64" s="340"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
@@ -4280,22 +4280,22 @@
       <c r="C71" s="125"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B72" s="339" t="s">
+      <c r="B72" s="338" t="s">
         <v>375</v>
       </c>
-      <c r="C72" s="339"/>
-      <c r="D72" s="339"/>
-      <c r="E72" s="339"/>
-      <c r="F72" s="339"/>
+      <c r="C72" s="338"/>
+      <c r="D72" s="338"/>
+      <c r="E72" s="338"/>
+      <c r="F72" s="338"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="339" t="s">
+      <c r="B73" s="338" t="s">
         <v>376</v>
       </c>
-      <c r="C73" s="339"/>
-      <c r="D73" s="339"/>
-      <c r="E73" s="339"/>
-      <c r="F73" s="339"/>
+      <c r="C73" s="338"/>
+      <c r="D73" s="338"/>
+      <c r="E73" s="338"/>
+      <c r="F73" s="338"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B75" s="47" t="s">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="C76" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.58905740174080445</v>
+        <v>0.58522798451227231</v>
       </c>
       <c r="D76" s="1" t="str">
         <f>Market_currency</f>
@@ -4332,13 +4332,13 @@
       <c r="A79" s="239"/>
     </row>
     <row r="80" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="339" t="s">
+      <c r="B80" s="338" t="s">
         <v>260</v>
       </c>
-      <c r="C80" s="339"/>
-      <c r="D80" s="339"/>
-      <c r="E80" s="339"/>
-      <c r="F80" s="339"/>
+      <c r="C80" s="338"/>
+      <c r="D80" s="338"/>
+      <c r="E80" s="338"/>
+      <c r="F80" s="338"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="1" t="s">
@@ -4351,13 +4351,13 @@
       </c>
     </row>
     <row r="84" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="339" t="s">
+      <c r="B84" s="338" t="s">
         <v>377</v>
       </c>
-      <c r="C84" s="339"/>
-      <c r="D84" s="339"/>
-      <c r="E84" s="339"/>
-      <c r="F84" s="339"/>
+      <c r="C84" s="338"/>
+      <c r="D84" s="338"/>
+      <c r="E84" s="338"/>
+      <c r="F84" s="338"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="47" t="s">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="C86" s="254">
         <f>C85*C28*Exchange_Rate/Common_Shares</f>
-        <v>2.7351195145423102E-2</v>
+        <v>2.7173387112451618E-2</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="C91" s="254">
         <f>C90*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.4671985772789613</v>
+        <v>1.4576604312631301</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Market_currency</f>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="C95" s="254">
         <f>C94*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.18314319724058234</v>
+        <v>0.18195259728762536</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4461,13 +4461,13 @@
       </c>
     </row>
     <row r="97" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="339" t="s">
+      <c r="B97" s="338" t="s">
         <v>266</v>
       </c>
-      <c r="C97" s="339"/>
-      <c r="D97" s="339"/>
-      <c r="E97" s="339"/>
-      <c r="F97" s="339"/>
+      <c r="C97" s="338"/>
+      <c r="D97" s="338"/>
+      <c r="E97" s="338"/>
+      <c r="F97" s="338"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B99" s="47" t="s">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="C99" s="254">
         <f>Valuation_Model!C12</f>
-        <v>2.212047981114925</v>
+        <v>2.1976676259505763</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4493,13 +4493,13 @@
       <c r="F101" s="36"/>
     </row>
     <row r="103" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="338" t="s">
+      <c r="B103" s="340" t="s">
         <v>360</v>
       </c>
-      <c r="C103" s="338"/>
-      <c r="D103" s="338"/>
-      <c r="E103" s="338"/>
-      <c r="F103" s="338"/>
+      <c r="C103" s="340"/>
+      <c r="D103" s="340"/>
+      <c r="E103" s="340"/>
+      <c r="F103" s="340"/>
     </row>
     <row r="105" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B105" s="266" t="s">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="E106" s="264" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>2.53 HKD</v>
+        <v>2.51 HKD</v>
       </c>
       <c r="F106" s="265">
         <f>Valuation_Model!F74</f>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="E107" s="251" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>2.34 HKD</v>
+        <v>2.32 HKD</v>
       </c>
       <c r="F107" s="252">
         <f>Valuation_Model!F75</f>
@@ -4577,7 +4577,7 @@
       </c>
       <c r="E108" s="251" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>2.25 HKD</v>
+        <v>2.24 HKD</v>
       </c>
       <c r="F108" s="252">
         <f>Valuation_Model!F76</f>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="E109" s="251" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>2.12 HKD</v>
+        <v>2.1 HKD</v>
       </c>
       <c r="F109" s="252">
         <f>Valuation_Model!F77</f>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="E110" s="251" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>2.07 HKD</v>
+        <v>2.06 HKD</v>
       </c>
       <c r="F110" s="252">
         <f>Valuation_Model!F78</f>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="C112" s="247">
         <f>Scenarios!C60</f>
-        <v>2.2482528889477993</v>
+        <v>2.2336371684397625</v>
       </c>
       <c r="D112" s="242" t="str">
         <f>Market_currency</f>
@@ -4661,13 +4661,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B118" s="341" t="s">
+      <c r="B118" s="339" t="s">
         <v>274</v>
       </c>
-      <c r="C118" s="341"/>
-      <c r="D118" s="341"/>
-      <c r="E118" s="341"/>
-      <c r="F118" s="341"/>
+      <c r="C118" s="339"/>
+      <c r="D118" s="339"/>
+      <c r="E118" s="339"/>
+      <c r="F118" s="339"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B119" s="240" t="s">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="C126" s="246">
         <f>Scenarios!C82</f>
-        <v>1.3010722736966431</v>
+        <v>1.292614102106344</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="C127" s="245">
         <f>Scenarios!C83</f>
-        <v>1.5492157922151617</v>
+        <v>1.5407576206248625</v>
       </c>
       <c r="D127" s="47" t="str">
         <f>Reporting_currency</f>
@@ -4749,11 +4749,17 @@
       </c>
       <c r="C128" s="94">
         <f>Scenarios!F83</f>
-        <v>0.31092458511630894</v>
+        <v>0.31020237198993661</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B97:F97"/>
@@ -4769,12 +4775,6 @@
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B84:F84"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -7840,11 +7840,11 @@
       </c>
       <c r="C47" s="151">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>2.4321575042074168</v>
+        <v>2.4163462338259714</v>
       </c>
       <c r="D47" s="151">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.79595369370391</v>
+        <v>1.7842783357574838</v>
       </c>
       <c r="F47" s="289"/>
     </row>
@@ -8250,11 +8250,11 @@
       </c>
       <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-36468.264752429997</v>
+        <v>-36231.187345500002</v>
       </c>
       <c r="D86" s="254">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-2.7351195145423106E-2</v>
+        <v>-2.7173387112451611E-2</v>
       </c>
       <c r="E86" s="275" t="str">
         <f>Market_currency</f>
@@ -8267,11 +8267,11 @@
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>1956265.0142383778</v>
+        <v>1943547.4846275786</v>
       </c>
       <c r="D87" s="254">
         <f>C87*$H$1/Common_Shares</f>
-        <v>1.4671985772789613</v>
+        <v>1.4576604312631301</v>
       </c>
       <c r="E87" s="275" t="str">
         <f>Market_currency</f>
@@ -8284,11 +8284,11 @@
       </c>
       <c r="C88" s="191">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>244190.96017797597</v>
+        <v>242603.49337560002</v>
       </c>
       <c r="D88" s="254">
         <f>C88*$H$1/Common_Shares</f>
-        <v>0.18314319724058234</v>
+        <v>0.18195259728762533</v>
       </c>
       <c r="E88" s="275" t="str">
         <f>Market_currency</f>
@@ -8301,11 +8301,11 @@
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
-        <v>2163987.7096639238</v>
+        <v>2149919.7906576786</v>
       </c>
       <c r="D89" s="277">
         <f>SUM(D86:D88)</f>
-        <v>1.6229905793741206</v>
+        <v>1.6124396414383038</v>
       </c>
       <c r="E89" s="275" t="str">
         <f>Market_currency</f>
@@ -13011,30 +13011,30 @@
       </c>
       <c r="C120" s="181">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>4.7124592139264357E-2</v>
+        <v>4.681823876098179E-2</v>
       </c>
       <c r="D120" s="27"/>
       <c r="E120" s="305"/>
       <c r="F120" s="27"/>
       <c r="G120" s="181">
         <f t="shared" ref="G120:Q120" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>8.1618439844289514E-2</v>
+        <v>8.1087844593670522E-2</v>
       </c>
       <c r="H120" s="181">
         <f t="shared" si="49"/>
-        <v>1.1652252779974023E-2</v>
+        <v>1.1576502373621471E-2</v>
       </c>
       <c r="I120" s="181">
         <f t="shared" si="49"/>
-        <v>6.4843560864237079E-2</v>
+        <v>6.4422017822083538E-2</v>
       </c>
       <c r="J120" s="181">
         <f t="shared" si="49"/>
-        <v>0.22807798493749895</v>
+        <v>0.22659526735787525</v>
       </c>
       <c r="K120" s="181">
         <f t="shared" si="49"/>
-        <v>0.16324156053174993</v>
+        <v>0.16218033960070757</v>
       </c>
       <c r="L120" s="181" t="str">
         <f t="shared" si="49"/>
@@ -13068,30 +13068,30 @@
       </c>
       <c r="C121" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.1918414948495051E-2</v>
+        <v>2.1775925005107808E-2</v>
       </c>
       <c r="D121" s="27"/>
       <c r="E121" s="305"/>
       <c r="F121" s="27"/>
       <c r="G121" s="79">
         <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
-        <v>3.7962065043855589E-2</v>
+        <v>3.771527655519559E-2</v>
       </c>
       <c r="H121" s="79">
         <f t="shared" ref="H121" si="51">IF(H$4="","",H120/Market_Price)</f>
-        <v>5.4196524558018716E-3</v>
+        <v>5.3844197086611494E-3</v>
       </c>
       <c r="I121" s="79">
         <f t="shared" ref="I121" si="52">IF(I$4="","",I120/Market_Price)</f>
-        <v>3.0159795750807947E-2</v>
+        <v>2.9963729219573739E-2</v>
       </c>
       <c r="J121" s="79">
         <f t="shared" ref="J121" si="53">IF(J$4="","",J120/Market_Price)</f>
-        <v>0.10608278369185999</v>
+        <v>0.10539314760831407</v>
       </c>
       <c r="K121" s="79">
         <f t="shared" ref="K121" si="54">IF(K$4="","",K120/Market_Price)</f>
-        <v>7.5926307224069733E-2</v>
+        <v>7.5432716093352364E-2</v>
       </c>
       <c r="L121" s="79" t="str">
         <f t="shared" ref="L121" si="55">IF(L$4="","",L120/Market_Price)</f>
@@ -13974,7 +13974,7 @@
       </c>
       <c r="C11" s="237">
         <f>Exchange_Rate</f>
-        <v>1.0726275699999999</v>
+        <v>1.0656545000000002</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -13988,7 +13988,7 @@
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>2.212047981114925</v>
+        <v>2.1976676259505763</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14041,7 +14041,7 @@
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>2.2456973829222053</v>
+        <v>2.2310982755638773</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14977,23 +14977,23 @@
       </c>
       <c r="B65" s="128">
         <f>C12</f>
-        <v>2.212047981114925</v>
+        <v>2.1976676259505763</v>
       </c>
       <c r="C65" s="128">
         <f>C12</f>
-        <v>2.212047981114925</v>
+        <v>2.1976676259505763</v>
       </c>
       <c r="D65" s="128">
         <f>C12</f>
-        <v>2.212047981114925</v>
+        <v>2.1976676259505763</v>
       </c>
       <c r="E65" s="145">
         <f>C12</f>
-        <v>2.212047981114925</v>
+        <v>2.1976676259505763</v>
       </c>
       <c r="F65" s="128">
         <f>C12</f>
-        <v>2.212047981114925</v>
+        <v>2.1976676259505763</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -15004,23 +15004,23 @@
       </c>
       <c r="B66" s="128">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.1582066461293725</v>
+        <v>2.1441763093761184</v>
       </c>
       <c r="C66" s="128">
         <f t="shared" si="4"/>
-        <v>2.1582066461293725</v>
+        <v>2.1441763093761184</v>
       </c>
       <c r="D66" s="128">
         <f t="shared" si="4"/>
-        <v>2.2310540564526056</v>
+        <v>2.216550144242492</v>
       </c>
       <c r="E66" s="128">
         <f t="shared" si="4"/>
-        <v>2.2707988574884714</v>
+        <v>2.2560365673590219</v>
       </c>
       <c r="F66" s="128">
         <f t="shared" si="4"/>
-        <v>2.2915883153606469</v>
+        <v>2.2766908745516332</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -15031,23 +15031,23 @@
       </c>
       <c r="B67" s="128">
         <f t="shared" si="4"/>
-        <v>2.1169368393302879</v>
+        <v>2.1031747944424914</v>
       </c>
       <c r="C67" s="128">
         <f t="shared" si="4"/>
-        <v>2.1169368393302879</v>
+        <v>2.1031747944424914</v>
       </c>
       <c r="D67" s="128">
         <f t="shared" si="4"/>
-        <v>2.2500776333822388</v>
+        <v>2.2354500503498467</v>
       </c>
       <c r="E67" s="128">
         <f t="shared" si="4"/>
-        <v>2.3380279055638415</v>
+        <v>2.3228285645218714</v>
       </c>
       <c r="F67" s="128">
         <f t="shared" si="4"/>
-        <v>2.3889118575687425</v>
+        <v>2.3733817238368116</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -15058,23 +15058,23 @@
       </c>
       <c r="B68" s="128">
         <f t="shared" si="4"/>
-        <v>2.0745239108180762</v>
+        <v>2.0610375891427837</v>
       </c>
       <c r="C68" s="128">
         <f t="shared" si="4"/>
-        <v>2.0745239108180762</v>
+        <v>2.0610375891427837</v>
       </c>
       <c r="D68" s="128">
         <f t="shared" si="4"/>
-        <v>2.2736245845762668</v>
+        <v>2.2588439246105989</v>
       </c>
       <c r="E68" s="128">
         <f t="shared" si="4"/>
-        <v>2.4305040549650125</v>
+        <v>2.4147035335309472</v>
       </c>
       <c r="F68" s="128">
         <f t="shared" si="4"/>
-        <v>2.5304105578824378</v>
+        <v>2.5139605518949426</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -15085,23 +15085,23 @@
       </c>
       <c r="B69" s="128">
         <f t="shared" si="4"/>
-        <v>2.0385030984734485</v>
+        <v>2.0252509453511194</v>
       </c>
       <c r="C69" s="128">
         <f t="shared" si="4"/>
-        <v>2.0385030984734485</v>
+        <v>2.0252509453511194</v>
       </c>
       <c r="D69" s="128">
         <f t="shared" si="4"/>
-        <v>2.2976151516762595</v>
+        <v>2.282678530864156</v>
       </c>
       <c r="E69" s="128">
         <f t="shared" si="4"/>
-        <v>2.5359942051149647</v>
+        <v>2.5195079002627967</v>
       </c>
       <c r="F69" s="128">
         <f t="shared" si="4"/>
-        <v>2.7019741285291143</v>
+        <v>2.68440880085772</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -15112,23 +15112,23 @@
       </c>
       <c r="B70" s="128">
         <f t="shared" si="4"/>
-        <v>2.0104139970181629</v>
+        <v>1.9973444490014296</v>
       </c>
       <c r="C70" s="128">
         <f t="shared" si="4"/>
-        <v>2.0104139970181629</v>
+        <v>1.9973444490014296</v>
       </c>
       <c r="D70" s="128">
         <f t="shared" si="4"/>
-        <v>2.3199277103160525</v>
+        <v>2.3048460372624939</v>
       </c>
       <c r="E70" s="128">
         <f t="shared" si="4"/>
-        <v>2.6465446750548738</v>
+        <v>2.6293396900317085</v>
       </c>
       <c r="F70" s="128">
         <f t="shared" si="4"/>
-        <v>2.8939993447454171</v>
+        <v>2.8751856757933285</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15138,23 +15138,23 @@
       </c>
       <c r="B71" s="128">
         <f t="shared" si="4"/>
-        <v>1.9895119042690388</v>
+        <v>1.9765782391626117</v>
       </c>
       <c r="C71" s="128">
         <f t="shared" si="4"/>
-        <v>1.9895119042690388</v>
+        <v>1.9765782391626117</v>
       </c>
       <c r="D71" s="128">
         <f t="shared" si="4"/>
-        <v>2.3396104908957605</v>
+        <v>2.3244008615872862</v>
       </c>
       <c r="E71" s="128">
         <f t="shared" si="4"/>
-        <v>2.757081096193978</v>
+        <v>2.739157522329998</v>
       </c>
       <c r="F71" s="128">
         <f t="shared" si="4"/>
-        <v>3.0999504131200664</v>
+        <v>3.0797978719848298</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="E74" s="139">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>2.5304105578824378</v>
+        <v>2.5139605518949426</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="E75" s="139">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>2.3380279055638415</v>
+        <v>2.3228285645218714</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -15234,7 +15234,7 @@
       </c>
       <c r="E76" s="139">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>2.2500776333822388</v>
+        <v>2.2354500503498467</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15257,7 +15257,7 @@
       </c>
       <c r="E77" s="139">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>2.1169368393302879</v>
+        <v>2.1031747944424914</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="E78" s="139">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.0745239108180762</v>
+        <v>2.0610375891427837</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
@@ -15430,7 +15430,7 @@
       </c>
       <c r="I6" s="270">
         <f t="shared" si="0"/>
-        <v>2.3660528889477992</v>
+        <v>2.3514371684397624</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15636,7 +15636,7 @@
       </c>
       <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
-        <v>2.212047981114925</v>
+        <v>2.1976676259505763</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="C27" s="164">
         <f>Valuation_Model!E76</f>
-        <v>2.2500776333822388</v>
+        <v>2.2354500503498467</v>
       </c>
       <c r="D27" s="164" t="str">
         <f>Market_currency</f>
@@ -15741,7 +15741,7 @@
       </c>
       <c r="C33" s="164">
         <f>Valuation_Model!E77</f>
-        <v>2.1169368393302879</v>
+        <v>2.1031747944424914</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -15799,7 +15799,7 @@
       </c>
       <c r="C39" s="164">
         <f>Valuation_Model!E75</f>
-        <v>2.3380279055638415</v>
+        <v>2.3228285645218714</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -15826,7 +15826,7 @@
       </c>
       <c r="C42" s="158">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>2.252094082319847</v>
+        <v>2.2374533905067491</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -15900,7 +15900,7 @@
       </c>
       <c r="C51" s="164">
         <f>Valuation_Model!E78</f>
-        <v>2.0745239108180762</v>
+        <v>2.0610375891427837</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -15958,7 +15958,7 @@
       </c>
       <c r="C57" s="164">
         <f>Valuation_Model!E74</f>
-        <v>2.5304105578824378</v>
+        <v>2.5139605518949426</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C60" s="158">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>2.2482528889477993</v>
+        <v>2.2336371684397625</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16045,7 +16045,7 @@
       </c>
       <c r="C66" s="164">
         <f>Valuation_Model!C18</f>
-        <v>2.2456973829222053</v>
+        <v>2.2310982755638773</v>
       </c>
       <c r="D66" s="164" t="str">
         <f>Market_currency</f>
@@ -16180,7 +16180,7 @@
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
-        <v>1.3010722736966431</v>
+        <v>1.292614102106344</v>
       </c>
       <c r="D82" s="120"/>
     </row>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
-        <v>1.5492157922151617</v>
+        <v>1.5407576206248625</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16201,7 +16201,7 @@
       </c>
       <c r="F83" s="335">
         <f>(1-C83/C60)</f>
-        <v>0.31092458511630894</v>
+        <v>0.31020237198993661</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16231,7 +16231,7 @@
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>6.9019080849287207E-2</v>
+        <v>6.6927308782200656E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01709A03-C49B-43FD-BAF8-6841E3430369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1BD0B25-BEAA-4678-94DE-DBAAA52FDB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="395">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -183,10 +183,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Contingent Liabilities</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>HKD</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -240,10 +236,6 @@
   </si>
   <si>
     <t>CAPX</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Other Data</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -952,14 +944,6 @@
   </si>
   <si>
     <t>Implied Growth Scenario Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 1: Calculate FCFE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>FCFE represents the cash available to equity holders after accounting for operating expenses, reinvestments, taxes, and interest obligations.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1254,14 +1238,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 3: Calculate Equity Value</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>The Equity Value adjusts the stable income value for debt and incorporates non-operating resources available to equity holders. The formula is:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -1325,58 +1301,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Purpose:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> This step ensures the equity value reflects all resources available to shareholders by deducting debt and adding excess cash and non-operating assets, avoiding double-counting of income-generating assets.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve">Purpose: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>This step ensures a comprehensive measure of cash flow by incorporating both operating and stable non-operating sources while accounting for taxes and reinvestment needs.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Expected Equity Value =</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -1401,18 +1325,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Assume the Equity Value will be realized over the holding period.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Expected Holding period = </t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
   <si>
-    <t>Step 4: Scenario Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Total Cash =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1445,32 +1361,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve">Guidance Note: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>This valuation method estimates the equity value of a company through a five-step process. Each step is designed to systematically derive cash flows available to equity holders, discount them appropriately, and adjust for debt and non-operating assets.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Asset Value Stress Test</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1519,23 +1409,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 5: Calculate Target Buy Price</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>No Growth Equity Value per share =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>No Growth SIV Per Share =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 2: Calculate Stable Income Value (SIV) Using FCFE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>The Stable Income Value (SIV) represents the present value of FCFE, assuming it grows at a constant rate indefinitely. This is calculated using the Gordon Growth Model:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1659,10 +1537,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Market Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>assuming a holding period of</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1764,14 +1638,6 @@
   </si>
   <si>
     <t>Fundamental analysis and market signal analysis should be combined, with fundamental analysis given priority and market signal analysis serving as a supplement. Market signal analysis predicts a company's future trend, while fundamental analysis interprets the trend and identifies relevant fundamental factors and possibilities.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Based on fundamental research, the following scenarios have been developed, considering driving factors of high growth periods (HGP) and high growth rates (HGR), along with their associated probabilities.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Note that this model prioritizes fundamental analysis when combined with supplementary market signal analysis. While market signal analysis predicts future trends, fundamental analysis interprets these trends and identifies relevant factors and possibilities.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1887,58 +1753,6 @@
         <family val="2"/>
         <scheme val="major"/>
       </rPr>
-      <t>Note on Cost of Equity:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> Cost of Equity reflects the company’s risk profile, while target annual return is the investor’s hurdle rate.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Note on Terminal Growth Rate:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> Setting g=0 can be a conservative assumption to avoid overestimating the stock’s value, especially if future growth is uncertain or unreliable.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
       <t xml:space="preserve">Note on debt: </t>
     </r>
     <r>
@@ -1991,6 +1805,360 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Historical Average or D&amp;A</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 1: Establishing the Company’s Sustainable Earning Power (Calculating Normalized FCFE)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 2: The No-Growth Baseline (Calculating Stable Income Value)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Note:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 3: Adjusting for Financial Structure (Calculating No Growth Equity Value)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 4: Incorporating Future Potential &amp; Risk (Scenario Analysis)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 5: Determining the Investment Decision (Calculating Target Buy Price)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Implied Market Annual Return:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Guidance Note: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>This model determines a target buy price consistent with defined investment criteria. It follows a logical progression: establishing current sustainable earnings, adjusting for financial structure, incorporating growth scenarios, and finally applying the investor’s required return.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> To quantify the underlying FCFE the business consistently generates for its equity owners, stripping away temporary fluctuations or accounting choices.The FCFE/Market Cap yield gives a direct measure of this cash generation relative to the current market price.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Insight: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>This step ensures a comprehensive measure of cash flow by incorporating both operating and stable non-operating sources while accounting for taxes and reinvestment needs.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> To determine the intrinsic value of the company’s equity if the Normalized FCFE (calculated in Step 1) were to remain constant perpetually, with zero future growth. This establishes a baseline value derived solely from the current sustainable earnings power.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Cost of Equity:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Cost of Equity reflects the company’s risk profile and represents the minimum return the investor requires for taking on the general risk of owning this type of business, while the target annual return serves as the investor’s hurdle rate.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Terminal Growth Rate:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Setting g=0% is a conservative assumption, valuing the company based only on its current demonstrated earning power without relying on potentially optimistic future growth projections.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> To refine the Stable Income Value (SIV) by incorporating the company’s balance sheet structure. </t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Insight:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> The No Growth Equity Value per share represents an estimate of the company’s intrinsic worth based on its current sustainable operations and net financial position, before factoring in any future growth potential. It serves as a fundamentally anchored valuation baseline.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> To estimate the company’s intrinsic value by considering plausible future scenarios beyond the static no-growth assumption. Based on fundamental research, each scenario defines high growth periods (HGP), high growth rates (HGR), and its probability.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Goal: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>To translate our estimate of the company’s intrinsic value (from Step 4) into a concrete buy price that meets the specific investment requirements.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Calculation Logic:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> The Target Buy Price is determined by discounting future cash flows—expected annual dividends and the Expected Equity Value—at the Target Annual Return, realized over the holding period.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Insight:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Significant market volatility is analyzed as an indicator of the range of market-perceived outcomes, including extremes that define boundaries for scenarios like "Snowball" or "Devil’s Advocate." Scenario Analysis then filters these using fundamental reasoning to evaluate their likelihood.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFO</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFF</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>朝云集团</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2004,10 +2172,6 @@
   </si>
   <si>
     <t>CNS_04</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Historical Average or D&amp;A</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2675,7 +2839,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="348">
+  <cellXfs count="349">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3378,23 +3542,24 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3684,7 +3849,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -3697,22 +3862,22 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C1" s="44">
         <v>45730</v>
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="337" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="F1" s="290" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A2" s="253" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -3736,24 +3901,24 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C6" s="50">
         <v>2.15</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -3769,7 +3934,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="C8" s="285">
         <v>6</v>
@@ -3779,7 +3944,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -3805,24 +3970,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
-        <v>285</v>
-      </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="B12" s="341" t="s">
+        <v>376</v>
+      </c>
+      <c r="C12" s="341"/>
+      <c r="D12" s="341"/>
+      <c r="E12" s="341"/>
+      <c r="F12" s="341"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -3832,10 +3997,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -3845,7 +4010,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0656545000000002</v>
+        <v>1.0656544999999999</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -3855,16 +4020,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B18" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="C19" s="255">
         <v>0.2</v>
@@ -3877,11 +4042,11 @@
         <v>Target Buy Price (HKD):</v>
       </c>
       <c r="C20" s="258">
-        <f>C127</f>
+        <f>C129</f>
         <v>1.5407576206248625</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="E20" s="336">
         <v>3</v>
@@ -3889,7 +4054,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>333</v>
+        <v>375</v>
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
@@ -3904,7 +4069,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="253" t="s">
-        <v>234</v>
+        <v>369</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -3912,27 +4077,27 @@
       <c r="E23" s="36"/>
       <c r="F23" s="36"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
-        <v>235</v>
-      </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+    <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="341" t="s">
+        <v>377</v>
+      </c>
+      <c r="C25" s="341"/>
+      <c r="D25" s="341"/>
+      <c r="E25" s="341"/>
+      <c r="F25" s="341"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="342" t="s">
-        <v>370</v>
-      </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="B26" s="339" t="s">
+        <v>353</v>
+      </c>
+      <c r="C26" s="339"/>
+      <c r="D26" s="339"/>
+      <c r="E26" s="339"/>
+      <c r="F26" s="339"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C28" s="111">
         <f>Data!C3</f>
@@ -3941,7 +4106,7 @@
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="340" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C29" s="340"/>
       <c r="D29" s="340"/>
@@ -3950,7 +4115,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C30" s="191">
         <f>Normalized_FCF!C8</f>
@@ -3967,7 +4132,7 @@
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="340" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C32" s="340"/>
       <c r="D32" s="340"/>
@@ -3976,7 +4141,7 @@
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C33" s="191">
         <f>Normalized_FCF!C9</f>
@@ -3989,7 +4154,7 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="52" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C34" s="191">
         <f>Normalized_FCF!C10</f>
@@ -4002,7 +4167,7 @@
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B36" s="340" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C36" s="340"/>
       <c r="D36" s="340"/>
@@ -4011,7 +4176,7 @@
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C37" s="191">
         <f>Normalized_FCF!C11</f>
@@ -4024,7 +4189,7 @@
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="340" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C39" s="340"/>
       <c r="D39" s="340"/>
@@ -4033,7 +4198,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="C40" s="328">
         <f>Normalized_FCF!C48</f>
@@ -4048,7 +4213,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="C41" s="328">
         <f>Normalized_FCF!C47</f>
@@ -4063,7 +4228,7 @@
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B42" s="47" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C42" s="191">
         <f>Normalized_FCF!C12</f>
@@ -4076,12 +4241,12 @@
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B44" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B45" s="47" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="C45" s="191">
         <f>Normalized_FCF!C15</f>
@@ -4094,7 +4259,7 @@
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B47" s="340" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C47" s="340"/>
       <c r="D47" s="340"/>
@@ -4103,7 +4268,7 @@
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C48" s="191">
         <f>Normalized_FCF!C14</f>
@@ -4116,16 +4281,16 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B50" s="340" t="s">
-        <v>369</v>
-      </c>
-      <c r="C50" s="341"/>
-      <c r="D50" s="341"/>
-      <c r="E50" s="341"/>
-      <c r="F50" s="341"/>
+        <v>352</v>
+      </c>
+      <c r="C50" s="344"/>
+      <c r="D50" s="344"/>
+      <c r="E50" s="344"/>
+      <c r="F50" s="344"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C51" s="1">
         <f>Normalized_FCF!C17</f>
@@ -4137,26 +4302,26 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
-        <v>374</v>
-      </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="B53" s="341" t="s">
+        <v>357</v>
+      </c>
+      <c r="C53" s="341"/>
+      <c r="D53" s="341"/>
+      <c r="E53" s="341"/>
+      <c r="F53" s="341"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
-        <v>267</v>
-      </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="B54" s="341" t="s">
+        <v>378</v>
+      </c>
+      <c r="C54" s="341"/>
+      <c r="D54" s="341"/>
+      <c r="E54" s="341"/>
+      <c r="F54" s="341"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="C56" s="191">
         <f>Normalized_FCF!G19</f>
@@ -4169,7 +4334,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B57" s="47" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C57" s="191">
         <f>Normalized_FCF!C19</f>
@@ -4182,16 +4347,16 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="260" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C121</f>
-        <v>2.1775925005107808E-2</v>
+        <v>2.1775925005107801E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="260" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
@@ -4200,7 +4365,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="253" t="s">
-        <v>301</v>
+        <v>370</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4213,31 +4378,31 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
-        <v>302</v>
-      </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="B63" s="341" t="s">
+        <v>379</v>
+      </c>
+      <c r="C63" s="341"/>
+      <c r="D63" s="341"/>
+      <c r="E63" s="341"/>
+      <c r="F63" s="341"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="342" t="s">
-        <v>258</v>
-      </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="B64" s="339" t="s">
+        <v>254</v>
+      </c>
+      <c r="C64" s="339"/>
+      <c r="D64" s="339"/>
+      <c r="E64" s="339"/>
+      <c r="F64" s="339"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="C67" s="317">
         <v>0.08</v>
@@ -4245,31 +4410,31 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="C68" s="269">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="292" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="C69" s="269">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="292" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C70" s="269">
         <f>SUM(C67:C69)</f>
@@ -4281,135 +4446,128 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="338" t="s">
-        <v>375</v>
-      </c>
-      <c r="C72" s="338"/>
-      <c r="D72" s="338"/>
-      <c r="E72" s="338"/>
-      <c r="F72" s="338"/>
+        <v>371</v>
+      </c>
+      <c r="C72" s="125"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
-        <v>376</v>
-      </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B75" s="47" t="s">
-        <v>257</v>
-      </c>
-      <c r="C75" s="269">
-        <v>0</v>
-      </c>
+      <c r="B73" s="341" t="s">
+        <v>380</v>
+      </c>
+      <c r="C73" s="341"/>
+      <c r="D73" s="341"/>
+      <c r="E73" s="341"/>
+      <c r="F73" s="341"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="341" t="s">
+        <v>381</v>
+      </c>
+      <c r="C74" s="341"/>
+      <c r="D74" s="341"/>
+      <c r="E74" s="341"/>
+      <c r="F74" s="341"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
-        <v>300</v>
-      </c>
-      <c r="C76" s="254">
+        <v>253</v>
+      </c>
+      <c r="C76" s="269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B77" s="47" t="s">
+        <v>288</v>
+      </c>
+      <c r="C77" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.58522798451227231</v>
-      </c>
-      <c r="D76" s="1" t="str">
+        <v>0.5852279845122722</v>
+      </c>
+      <c r="D77" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A78" s="253" t="s">
-        <v>259</v>
-      </c>
-      <c r="B78" s="36"/>
-      <c r="C78" s="36"/>
-      <c r="D78" s="36"/>
-      <c r="E78" s="36"/>
-      <c r="F78" s="36"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A79" s="239"/>
-    </row>
-    <row r="80" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="338" t="s">
-        <v>260</v>
-      </c>
-      <c r="C80" s="338"/>
-      <c r="D80" s="338"/>
-      <c r="E80" s="338"/>
-      <c r="F80" s="338"/>
+    <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A79" s="253" t="s">
+        <v>372</v>
+      </c>
+      <c r="B79" s="36"/>
+      <c r="C79" s="36"/>
+      <c r="D79" s="36"/>
+      <c r="E79" s="36"/>
+      <c r="F79" s="36"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" s="239"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B83" s="240" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="84" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="338" t="s">
-        <v>377</v>
-      </c>
-      <c r="C84" s="338"/>
-      <c r="D84" s="338"/>
-      <c r="E84" s="338"/>
-      <c r="F84" s="338"/>
-    </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B85" s="47" t="s">
-        <v>263</v>
-      </c>
-      <c r="C85" s="191">
+      <c r="B81" s="341" t="s">
+        <v>382</v>
+      </c>
+      <c r="C81" s="341"/>
+      <c r="D81" s="341"/>
+      <c r="E81" s="341"/>
+      <c r="F81" s="341"/>
+    </row>
+    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B82" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B84" s="240" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B85" s="341" t="s">
+        <v>358</v>
+      </c>
+      <c r="C85" s="341"/>
+      <c r="D85" s="341"/>
+      <c r="E85" s="341"/>
+      <c r="F85" s="341"/>
+    </row>
+    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B86" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="C86" s="191">
         <f>Valuation_Model!C7</f>
         <v>33999</v>
       </c>
-      <c r="D85" s="1" t="str">
+      <c r="D86" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B86" s="47" t="s">
-        <v>303</v>
-      </c>
-      <c r="C86" s="254">
-        <f>C85*C28*Exchange_Rate/Common_Shares</f>
-        <v>2.7173387112451618E-2</v>
-      </c>
-      <c r="D86" s="1" t="str">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B87" s="47" t="s">
+        <v>289</v>
+      </c>
+      <c r="C87" s="254">
+        <f>C86*C28*Exchange_Rate/Common_Shares</f>
+        <v>2.7173387112451611E-2</v>
+      </c>
+      <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B88" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B89" s="47" t="s">
-        <v>277</v>
-      </c>
-      <c r="C89" s="191">
+      <c r="B89" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B90" s="47" t="s">
+        <v>267</v>
+      </c>
+      <c r="C90" s="191">
         <f>BS!C66</f>
         <v>2664732</v>
-      </c>
-      <c r="D89" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B90" s="47" t="s">
-        <v>279</v>
-      </c>
-      <c r="C90" s="191">
-        <f>Valuation_Model!C8</f>
-        <v>1823806.3881188305</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4418,363 +4576,386 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="47" t="s">
-        <v>304</v>
-      </c>
-      <c r="C91" s="254">
-        <f>C90*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.4576604312631301</v>
+        <v>269</v>
+      </c>
+      <c r="C91" s="191">
+        <f>Valuation_Model!C8</f>
+        <v>1823806.3881188305</v>
       </c>
       <c r="D91" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B92" s="47" t="s">
+        <v>290</v>
+      </c>
+      <c r="C92" s="254">
+        <f>C91*C28*Exchange_Rate/Common_Shares</f>
+        <v>1.4576604312631296</v>
+      </c>
+      <c r="D92" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B93" s="1" t="s">
-        <v>264</v>
-      </c>
-    </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B94" s="47" t="s">
-        <v>265</v>
-      </c>
-      <c r="C94" s="191">
+      <c r="B94" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B95" s="47" t="s">
+        <v>259</v>
+      </c>
+      <c r="C95" s="191">
         <f>Valuation_Model!C9</f>
         <v>227656.8</v>
       </c>
-      <c r="D94" s="1" t="str">
+      <c r="D95" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B95" s="47" t="s">
-        <v>305</v>
-      </c>
-      <c r="C95" s="254">
-        <f>C94*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.18195259728762536</v>
-      </c>
-      <c r="D95" s="1" t="str">
+    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B96" s="47" t="s">
+        <v>291</v>
+      </c>
+      <c r="C96" s="254">
+        <f>C95*C28*Exchange_Rate/Common_Shares</f>
+        <v>0.18195259728762533</v>
+      </c>
+      <c r="D96" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="338" t="s">
-        <v>266</v>
-      </c>
-      <c r="C97" s="338"/>
-      <c r="D97" s="338"/>
-      <c r="E97" s="338"/>
-      <c r="F97" s="338"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B99" s="47" t="s">
-        <v>299</v>
-      </c>
-      <c r="C99" s="254">
+    <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B98" s="341" t="s">
+        <v>383</v>
+      </c>
+      <c r="C98" s="341"/>
+      <c r="D98" s="341"/>
+      <c r="E98" s="341"/>
+      <c r="F98" s="341"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B100" s="47" t="s">
+        <v>287</v>
+      </c>
+      <c r="C100" s="254">
         <f>Valuation_Model!C12</f>
-        <v>2.1976676259505763</v>
-      </c>
-      <c r="D99" s="1" t="str">
+        <v>2.1976676259505759</v>
+      </c>
+      <c r="D100" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A101" s="253" t="s">
-        <v>276</v>
-      </c>
-      <c r="B101" s="36"/>
-      <c r="C101" s="36"/>
-      <c r="D101" s="36"/>
-      <c r="E101" s="36"/>
-      <c r="F101" s="36"/>
-    </row>
-    <row r="103" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="340" t="s">
-        <v>360</v>
-      </c>
-      <c r="C103" s="340"/>
-      <c r="D103" s="340"/>
-      <c r="E103" s="340"/>
-      <c r="F103" s="340"/>
-    </row>
-    <row r="105" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
-      <c r="B105" s="266" t="s">
-        <v>121</v>
-      </c>
-      <c r="C105" s="266" t="s">
-        <v>136</v>
-      </c>
-      <c r="D105" s="266" t="s">
-        <v>116</v>
-      </c>
-      <c r="E105" s="266" t="s">
-        <v>269</v>
-      </c>
-      <c r="F105" s="266" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B106" s="261" t="str">
+    <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A102" s="253" t="s">
+        <v>373</v>
+      </c>
+      <c r="B102" s="36"/>
+      <c r="C102" s="36"/>
+      <c r="D102" s="36"/>
+      <c r="E102" s="36"/>
+      <c r="F102" s="36"/>
+    </row>
+    <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B104" s="340" t="s">
+        <v>384</v>
+      </c>
+      <c r="C104" s="340"/>
+      <c r="D104" s="340"/>
+      <c r="E104" s="340"/>
+      <c r="F104" s="340"/>
+    </row>
+    <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
+      <c r="B106" s="266" t="s">
+        <v>119</v>
+      </c>
+      <c r="C106" s="266" t="s">
+        <v>134</v>
+      </c>
+      <c r="D106" s="266" t="s">
+        <v>114</v>
+      </c>
+      <c r="E106" s="266" t="s">
+        <v>261</v>
+      </c>
+      <c r="F106" s="266" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B107" s="261" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C106" s="262">
+      <c r="C107" s="262">
         <f>Valuation_Model!C74</f>
         <v>0.08</v>
       </c>
-      <c r="D106" s="263">
+      <c r="D107" s="263">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E106" s="264" t="str">
+      <c r="E107" s="264" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>2.51 HKD</v>
       </c>
-      <c r="F106" s="265">
+      <c r="F107" s="265">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B107" s="248" t="str">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B108" s="248" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C107" s="249">
+      <c r="C108" s="249">
         <f>Valuation_Model!C75</f>
         <v>0.06</v>
       </c>
-      <c r="D107" s="250">
+      <c r="D108" s="250">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E107" s="251" t="str">
+      <c r="E108" s="251" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>2.32 HKD</v>
       </c>
-      <c r="F107" s="252">
+      <c r="F108" s="252">
         <f>Valuation_Model!F75</f>
         <v>0.21249999999999999</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B108" s="248" t="str">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B109" s="248" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C108" s="249">
+      <c r="C109" s="249">
         <f>Valuation_Model!C76</f>
         <v>0.02</v>
       </c>
-      <c r="D108" s="250">
+      <c r="D109" s="250">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E108" s="251" t="str">
+      <c r="E109" s="251" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>2.24 HKD</v>
       </c>
-      <c r="F108" s="252">
+      <c r="F109" s="252">
         <f>Valuation_Model!F76</f>
         <v>0.51</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B109" s="248" t="str">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B110" s="248" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C109" s="249">
+      <c r="C110" s="249">
         <f>Valuation_Model!C77</f>
         <v>-0.06</v>
       </c>
-      <c r="D109" s="250">
+      <c r="D110" s="250">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E109" s="251" t="str">
+      <c r="E110" s="251" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>2.1 HKD</v>
       </c>
-      <c r="F109" s="252">
+      <c r="F110" s="252">
         <f>Valuation_Model!F77</f>
         <v>0.1275</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B110" s="248" t="str">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B111" s="248" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C110" s="249">
+      <c r="C111" s="249">
         <f>Valuation_Model!C78</f>
         <v>-0.06</v>
       </c>
-      <c r="D110" s="250">
+      <c r="D111" s="250">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E110" s="251" t="str">
+      <c r="E111" s="251" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>2.06 HKD</v>
       </c>
-      <c r="F110" s="252">
+      <c r="F111" s="252">
         <f>Valuation_Model!F78</f>
         <v>0.1</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B112" s="241" t="s">
-        <v>268</v>
-      </c>
-      <c r="C112" s="247">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B113" s="241" t="s">
+        <v>260</v>
+      </c>
+      <c r="C113" s="247">
         <f>Scenarios!C60</f>
         <v>2.2336371684397625</v>
       </c>
-      <c r="D112" s="242" t="str">
+      <c r="D113" s="242" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B114" s="343" t="s">
-        <v>361</v>
-      </c>
-      <c r="C114" s="343"/>
-      <c r="D114" s="343"/>
-      <c r="E114" s="343"/>
-      <c r="F114" s="343"/>
-    </row>
-    <row r="116" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A116" s="253" t="s">
-        <v>298</v>
-      </c>
-      <c r="B116" s="36"/>
-      <c r="C116" s="36"/>
-      <c r="D116" s="36"/>
-      <c r="E116" s="36"/>
-      <c r="F116" s="36"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B118" s="339" t="s">
-        <v>274</v>
-      </c>
-      <c r="C118" s="339"/>
-      <c r="D118" s="339"/>
-      <c r="E118" s="339"/>
-      <c r="F118" s="339"/>
+    <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B115" s="342" t="s">
+        <v>387</v>
+      </c>
+      <c r="C115" s="342"/>
+      <c r="D115" s="342"/>
+      <c r="E115" s="342"/>
+      <c r="F115" s="342"/>
+    </row>
+    <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A117" s="253" t="s">
+        <v>374</v>
+      </c>
+      <c r="B117" s="36"/>
+      <c r="C117" s="36"/>
+      <c r="D117" s="36"/>
+      <c r="E117" s="36"/>
+      <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="240" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B120" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C120" s="257">
+      <c r="B119" s="343" t="s">
+        <v>385</v>
+      </c>
+      <c r="C119" s="343"/>
+      <c r="D119" s="343"/>
+      <c r="E119" s="343"/>
+      <c r="F119" s="343"/>
+    </row>
+    <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B120" s="341" t="s">
+        <v>386</v>
+      </c>
+      <c r="C120" s="341"/>
+      <c r="D120" s="341"/>
+      <c r="E120" s="341"/>
+      <c r="F120" s="341"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B121" s="240" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B122" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C122" s="257">
         <f>E20</f>
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B121" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="C121" s="256">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B123" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C123" s="256">
         <f>C19</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B122" s="242" t="s">
-        <v>271</v>
-      </c>
-      <c r="C122" s="243">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B124" s="242" t="s">
+        <v>263</v>
+      </c>
+      <c r="C124" s="243">
         <f>Scenarios!C77</f>
         <v>0.1178</v>
       </c>
-      <c r="D122" s="242" t="str">
+      <c r="D124" s="242" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B124" s="240" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B125" s="242" t="str">
-        <f>"PV("&amp;C120&amp;" yrs of Dividends)"</f>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B126" s="240" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B127" s="242" t="str">
+        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C125" s="246">
+      <c r="C127" s="246">
         <f>Scenarios!C81</f>
         <v>0.24814351851851849</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B126" s="242" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C120&amp;")"</f>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B128" s="242" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C126" s="246">
+      <c r="C128" s="246">
         <f>Scenarios!C82</f>
         <v>1.292614102106344</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B127" s="82" t="s">
-        <v>270</v>
-      </c>
-      <c r="C127" s="245">
+    <row r="129" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B129" s="82" t="s">
+        <v>262</v>
+      </c>
+      <c r="C129" s="245">
         <f>Scenarios!C83</f>
         <v>1.5407576206248625</v>
       </c>
-      <c r="D127" s="47" t="str">
+      <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B128" s="244" t="s">
-        <v>272</v>
-      </c>
-      <c r="C128" s="94">
+    <row r="130" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B130" s="244" t="s">
+        <v>264</v>
+      </c>
+      <c r="C130" s="94">
         <f>Scenarios!F83</f>
         <v>0.31020237198993661</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
+    <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B98:F98"/>
+    <mergeCell ref="B119:F119"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
     <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B103:F103"/>
-    <mergeCell ref="B72:F72"/>
-    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
     <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B85:F85"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -4858,7 +5039,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -4908,7 +5089,7 @@
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" s="193">
         <v>897327</v>
@@ -4934,7 +5115,7 @@
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B6" s="40" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C6" s="193">
         <v>613104</v>
@@ -4960,7 +5141,7 @@
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B7" s="70" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C7" s="194">
         <v>425033</v>
@@ -4980,7 +5161,7 @@
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B8" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" s="193"/>
       <c r="D8" s="184"/>
@@ -4996,7 +5177,7 @@
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B9" s="40" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C9" s="193"/>
       <c r="D9" s="184"/>
@@ -5012,7 +5193,7 @@
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B10" s="40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C10" s="193"/>
       <c r="D10" s="184"/>
@@ -5028,7 +5209,7 @@
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="40" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C11" s="193"/>
       <c r="D11" s="184"/>
@@ -5070,7 +5251,7 @@
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B13" s="40" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C13" s="193">
         <v>73805</v>
@@ -5090,7 +5271,7 @@
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B14" s="40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C14" s="193">
         <v>44449</v>
@@ -5110,7 +5291,7 @@
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B15" s="43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" s="195">
         <v>172817</v>
@@ -5134,7 +5315,7 @@
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B16" s="28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C16" s="193">
         <v>2199</v>
@@ -5154,13 +5335,13 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B18" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B19" s="27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C19" s="184">
         <v>35974</v>
@@ -5184,7 +5365,7 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B20" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C20" s="184">
         <v>15312</v>
@@ -5204,7 +5385,7 @@
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B21" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C21" s="184">
         <v>-169280</v>
@@ -5223,155 +5404,181 @@
       <c r="M21" s="184"/>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B22" s="24" t="str">
+      <c r="B22" s="27" t="s">
+        <v>388</v>
+      </c>
+      <c r="C22" s="184"/>
+      <c r="D22" s="184"/>
+      <c r="E22" s="184"/>
+      <c r="F22" s="184"/>
+      <c r="G22" s="184"/>
+      <c r="H22" s="184"/>
+      <c r="I22" s="184"/>
+      <c r="J22" s="184"/>
+      <c r="K22" s="184"/>
+      <c r="L22" s="184"/>
+      <c r="M22" s="184"/>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B23" s="27" t="s">
+        <v>390</v>
+      </c>
+      <c r="C23" s="184"/>
+      <c r="D23" s="184"/>
+      <c r="E23" s="184"/>
+      <c r="F23" s="184"/>
+      <c r="G23" s="184"/>
+      <c r="H23" s="184"/>
+      <c r="I23" s="184"/>
+      <c r="J23" s="184"/>
+      <c r="K23" s="184"/>
+      <c r="L23" s="184"/>
+      <c r="M23" s="184"/>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B24" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="C24" s="184"/>
+      <c r="D24" s="184"/>
+      <c r="E24" s="184"/>
+      <c r="F24" s="184"/>
+      <c r="G24" s="184"/>
+      <c r="H24" s="184"/>
+      <c r="I24" s="184"/>
+      <c r="J24" s="184"/>
+      <c r="K24" s="184"/>
+      <c r="L24" s="184"/>
+      <c r="M24" s="184"/>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
       </c>
-      <c r="C22" s="39">
+      <c r="C25" s="39">
         <v>0.1178</v>
       </c>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="39"/>
-      <c r="L22" s="39"/>
-      <c r="M22" s="39"/>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B24" s="16" t="s">
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="39"/>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="9"/>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B25" s="26" t="s">
+      <c r="C27" s="9"/>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="186"/>
-      <c r="D25" s="184"/>
-      <c r="E25" s="184"/>
-      <c r="F25" s="184"/>
-      <c r="G25" s="184"/>
-      <c r="H25" s="184"/>
-      <c r="I25" s="184"/>
-      <c r="J25" s="184"/>
-      <c r="K25" s="184"/>
-      <c r="L25" s="184"/>
-      <c r="M25" s="184"/>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B26" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" s="186"/>
-      <c r="D26" s="184"/>
-      <c r="E26" s="184"/>
-      <c r="F26" s="184"/>
-      <c r="G26" s="184"/>
-      <c r="H26" s="184"/>
-      <c r="I26" s="184"/>
-      <c r="J26" s="184"/>
-      <c r="K26" s="184"/>
-      <c r="L26" s="184"/>
-      <c r="M26" s="184"/>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B27" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="C27" s="185">
-        <v>642877</v>
-      </c>
-      <c r="D27" s="185">
-        <v>734909</v>
-      </c>
-      <c r="E27" s="185">
-        <v>677999</v>
-      </c>
-      <c r="F27" s="185">
-        <v>1352795</v>
-      </c>
-      <c r="G27" s="185">
-        <v>1205068</v>
-      </c>
-      <c r="H27" s="185"/>
-      <c r="I27" s="185"/>
-      <c r="J27" s="185"/>
-      <c r="K27" s="185"/>
-      <c r="L27" s="185"/>
-      <c r="M27" s="185"/>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B28" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="C28" s="185">
-        <v>3027292</v>
-      </c>
-      <c r="D28" s="185">
-        <v>2824568</v>
-      </c>
-      <c r="E28" s="185">
-        <v>2735259</v>
-      </c>
-      <c r="F28" s="185">
-        <v>250534</v>
-      </c>
-      <c r="G28" s="185">
-        <v>13930</v>
-      </c>
-      <c r="H28" s="185"/>
-      <c r="I28" s="185"/>
-      <c r="J28" s="185"/>
-      <c r="K28" s="185"/>
-      <c r="L28" s="185"/>
-      <c r="M28" s="185"/>
+      <c r="C28" s="186"/>
+      <c r="D28" s="184"/>
+      <c r="E28" s="184"/>
+      <c r="F28" s="184"/>
+      <c r="G28" s="184"/>
+      <c r="H28" s="184"/>
+      <c r="I28" s="184"/>
+      <c r="J28" s="184"/>
+      <c r="K28" s="184"/>
+      <c r="L28" s="184"/>
+      <c r="M28" s="184"/>
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B29" s="26" t="s">
-        <v>176</v>
-      </c>
-      <c r="C29" s="184"/>
+        <v>32</v>
+      </c>
+      <c r="C29" s="186"/>
       <c r="D29" s="184"/>
       <c r="E29" s="184"/>
       <c r="F29" s="184"/>
-      <c r="G29" s="185"/>
-      <c r="H29" s="185"/>
-      <c r="I29" s="185"/>
-      <c r="J29" s="185"/>
-      <c r="K29" s="185"/>
-      <c r="L29" s="185"/>
-      <c r="M29" s="185"/>
+      <c r="G29" s="184"/>
+      <c r="H29" s="184"/>
+      <c r="I29" s="184"/>
+      <c r="J29" s="184"/>
+      <c r="K29" s="184"/>
+      <c r="L29" s="184"/>
+      <c r="M29" s="184"/>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B30" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="185">
+        <v>642877</v>
+      </c>
+      <c r="D30" s="185">
+        <v>734909</v>
+      </c>
+      <c r="E30" s="185">
+        <v>677999</v>
+      </c>
+      <c r="F30" s="185">
+        <v>1352795</v>
+      </c>
+      <c r="G30" s="185">
+        <v>1205068</v>
+      </c>
+      <c r="H30" s="185"/>
+      <c r="I30" s="185"/>
+      <c r="J30" s="185"/>
+      <c r="K30" s="185"/>
+      <c r="L30" s="185"/>
+      <c r="M30" s="185"/>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B31" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C31" s="9"/>
+      <c r="B31" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="185">
+        <v>3027292</v>
+      </c>
+      <c r="D31" s="185">
+        <v>2824568</v>
+      </c>
+      <c r="E31" s="185">
+        <v>2735259</v>
+      </c>
+      <c r="F31" s="185">
+        <v>250534</v>
+      </c>
+      <c r="G31" s="185">
+        <v>13930</v>
+      </c>
+      <c r="H31" s="185"/>
+      <c r="I31" s="185"/>
+      <c r="J31" s="185"/>
+      <c r="K31" s="185"/>
+      <c r="L31" s="185"/>
+      <c r="M31" s="185"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B32" s="26" t="s">
-        <v>41</v>
+        <v>174</v>
       </c>
       <c r="C32" s="184"/>
       <c r="D32" s="184"/>
       <c r="E32" s="184"/>
       <c r="F32" s="184"/>
-      <c r="G32" s="184"/>
-      <c r="H32" s="184"/>
-      <c r="I32" s="184"/>
-      <c r="J32" s="184"/>
-      <c r="K32" s="184"/>
-      <c r="L32" s="184"/>
-      <c r="M32" s="184"/>
+      <c r="G32" s="185"/>
+      <c r="H32" s="185"/>
+      <c r="I32" s="185"/>
+      <c r="J32" s="185"/>
+      <c r="K32" s="185"/>
+      <c r="L32" s="185"/>
+      <c r="M32" s="185"/>
     </row>
     <row r="34" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B34" s="36" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -5441,7 +5648,7 @@
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B37" s="40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C37" s="186">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -5490,7 +5697,7 @@
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B38" s="31" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C38" s="187">
         <f>IF(C36="","",C36+C37)</f>
@@ -5539,7 +5746,7 @@
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B39" s="40" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C39" s="186">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -5588,7 +5795,7 @@
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B40" s="70" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C40" s="188">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -5637,7 +5844,7 @@
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B41" s="70" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C41" s="188">
         <f>IF(C$4="","",C39-C40)</f>
@@ -5686,7 +5893,7 @@
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B42" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C42" s="186">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -5735,7 +5942,7 @@
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B43" s="43" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C43" s="189">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -5784,7 +5991,7 @@
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B44" s="43" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C44" s="190">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -5833,7 +6040,7 @@
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B45" s="40" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C45" s="191">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -5882,7 +6089,7 @@
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B46" s="40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C46" s="186">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -5931,7 +6138,7 @@
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B47" s="43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C47" s="189">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -5980,7 +6187,7 @@
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B48" s="28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C48" s="186">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -6029,7 +6236,7 @@
     </row>
     <row r="50" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B50" s="16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.35">
@@ -6083,7 +6290,7 @@
     </row>
     <row r="52" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B52" s="40" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C52" s="186">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -6132,12 +6339,12 @@
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B54" s="178" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B55" s="40" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C55" s="191">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -6186,7 +6393,7 @@
     </row>
     <row r="56" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B56" s="40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C56" s="191">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -6235,14 +6442,14 @@
     </row>
     <row r="57" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B57" s="40" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C57" s="191">
-        <f>IF(C$4="","",C11)</f>
+        <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
         <v>0</v>
       </c>
       <c r="D57" s="191">
-        <f t="shared" ref="D57:M57" si="27">IF(D$4="","",D11)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="E57" s="191">
@@ -6284,7 +6491,7 @@
     </row>
     <row r="58" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B58" s="40" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C58" s="191">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -6333,13 +6540,13 @@
     </row>
     <row r="60" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B60" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B61" s="27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C61" s="186">
         <f t="shared" ref="C61:M61" si="29">IF(C$4="","",-C19)</f>
@@ -6388,7 +6595,7 @@
     </row>
     <row r="62" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B62" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C62" s="186">
         <f t="shared" ref="C62:M62" si="30">IF(C$4="","",-C20)</f>
@@ -6437,7 +6644,7 @@
     </row>
     <row r="63" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B63" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C63" s="186">
         <f t="shared" ref="C63:M63" si="31">IF(C$4="","",-C21)</f>
@@ -6489,7 +6696,7 @@
         <v>36</v>
       </c>
       <c r="C64" s="75">
-        <f t="shared" ref="C64:M64" si="32">IF(C$4="","",C22)</f>
+        <f t="shared" ref="C64:M64" si="32">IF(C$4="","",C25)</f>
         <v>0.1178</v>
       </c>
       <c r="D64" s="75">
@@ -6535,7 +6742,7 @@
     </row>
     <row r="66" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B66" s="93" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="67" spans="2:13" x14ac:dyDescent="0.35">
@@ -6790,7 +6997,7 @@
     </row>
     <row r="73" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B73" s="36" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C73" s="37"/>
       <c r="D73" s="37"/>
@@ -6861,10 +7068,10 @@
     </row>
     <row r="76" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B76" s="95" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C76" s="74">
-        <f t="shared" ref="C76:H77" si="39">IF(C$4="","",C25)</f>
+        <f t="shared" ref="C76:H77" si="39">IF(C$4="","",C28)</f>
         <v>0</v>
       </c>
       <c r="D76" s="74">
@@ -6895,7 +7102,7 @@
     </row>
     <row r="77" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B77" s="95" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C77" s="74">
         <f t="shared" si="39"/>
@@ -6932,7 +7139,7 @@
         <v>40</v>
       </c>
       <c r="C78" s="58">
-        <f t="shared" ref="C78:M78" si="40">IF(C$4="","",C27)</f>
+        <f t="shared" ref="C78:M78" si="40">IF(C$4="","",C30)</f>
         <v>642877</v>
       </c>
       <c r="D78" s="58">
@@ -6981,7 +7188,7 @@
         <v>30</v>
       </c>
       <c r="C79" s="58">
-        <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C28)</f>
+        <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C31)</f>
         <v>3027292</v>
       </c>
       <c r="D79" s="58">
@@ -7027,14 +7234,14 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="C4:M16 C19:M22 C32:M32 C39:M43 C45:M48 C51:M52 C55:M58 C76:H77 C78:M79">
+  <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C76:H77 C78:M79">
     <cfRule type="expression" dxfId="5" priority="4">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C25:M29">
+  <conditionalFormatting sqref="C28:M32">
     <cfRule type="expression" dxfId="4" priority="1">
-      <formula>ISBLANK(C25)</formula>
+      <formula>ISBLANK(C28)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36:M37 C61:M64">
@@ -7086,7 +7293,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="81" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -7097,19 +7304,19 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C3" s="209" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D3" s="210" t="s">
         <v>35</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G3" s="209" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H3" s="210" t="s">
         <v>35</v>
@@ -7127,7 +7334,7 @@
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G4" s="19">
         <v>2385307</v>
@@ -7169,7 +7376,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -7180,7 +7387,7 @@
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" s="19">
         <v>0</v>
@@ -7190,7 +7397,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G7" s="19">
         <v>253051</v>
@@ -7201,7 +7408,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -7211,7 +7418,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -7232,7 +7439,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -7267,7 +7474,7 @@
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="82" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C12" s="83">
         <f>SUM(C4:C11)</f>
@@ -7278,7 +7485,7 @@
         <v>192972.19999999998</v>
       </c>
       <c r="F12" s="82" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G12" s="83">
         <f>SUM(G4:G9)</f>
@@ -7296,19 +7503,19 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C14" s="209" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D14" s="210" t="s">
         <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G14" s="209" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H14" s="210" t="s">
         <v>35</v>
@@ -7316,7 +7523,7 @@
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C15" s="19">
         <v>0</v>
@@ -7325,7 +7532,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G15" s="19">
         <v>279425</v>
@@ -7345,7 +7552,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -7356,7 +7563,7 @@
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C17" s="19">
         <v>0</v>
@@ -7365,7 +7572,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G17" s="19">
         <v>126127</v>
@@ -7376,7 +7583,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -7385,7 +7592,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -7405,7 +7612,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G19" s="19">
         <v>1500</v>
@@ -7425,7 +7632,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -7445,7 +7652,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -7480,7 +7687,7 @@
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="82" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C24" s="83">
         <f>SUM(C15:C23)</f>
@@ -7491,7 +7698,7 @@
         <v>88388.3</v>
       </c>
       <c r="F24" s="82" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G24" s="83">
         <f>SUM(G15:G21)</f>
@@ -7504,16 +7711,16 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="16" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C26" s="209" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F26" s="211" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G26" s="212" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H26" s="213" t="s">
         <v>35</v>
@@ -7546,7 +7753,7 @@
         <v>13416</v>
       </c>
       <c r="F28" s="216" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="G28" s="184">
         <v>3990</v>
@@ -7561,7 +7768,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="217" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -7590,14 +7797,14 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="82" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C31" s="83">
         <f>SUM(C27:C30)</f>
         <v>13416</v>
       </c>
       <c r="F31" s="217" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G31" s="218">
         <f>C31+C40</f>
@@ -7614,7 +7821,7 @@
         <v>598515</v>
       </c>
       <c r="F32" s="219" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G32" s="220">
         <f>G35+G40</f>
@@ -7640,10 +7847,10 @@
       <c r="B34" s="85"/>
       <c r="C34" s="86"/>
       <c r="F34" s="223" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G34" s="224" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H34" s="225" t="s">
         <v>35</v>
@@ -7651,10 +7858,10 @@
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="16" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C35" s="209" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F35" s="226" t="s">
         <v>31</v>
@@ -7676,7 +7883,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="217" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G36" s="218">
         <f>C4+C15</f>
@@ -7692,7 +7899,7 @@
         <v>20583</v>
       </c>
       <c r="F37" s="217" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G37" s="218">
         <f>C6</f>
@@ -7708,7 +7915,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="217" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G38" s="218">
         <f>C7+C17</f>
@@ -7724,7 +7931,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="217" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G39" s="218">
         <f>C7+C17+C19+C20</f>
@@ -7737,14 +7944,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="82" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C40" s="83">
         <f>SUM(C36:C39)</f>
         <v>20583</v>
       </c>
       <c r="F40" s="226" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G40" s="220">
         <f>G12+G24</f>
@@ -7764,7 +7971,7 @@
         <v>10363</v>
       </c>
       <c r="F41" s="217" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G41" s="218">
         <f>C70</f>
@@ -7783,7 +7990,7 @@
         <v>30946</v>
       </c>
       <c r="F42" s="228" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G42" s="229">
         <f>C82</f>
@@ -7796,7 +8003,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="81" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -7807,21 +8014,21 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="C45" s="267" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D45" s="209" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="F45" s="293" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="C46" s="191">
         <f>G29</f>
@@ -7840,11 +8047,11 @@
       </c>
       <c r="C47" s="151">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>2.4163462338259714</v>
+        <v>2.4163462338259705</v>
       </c>
       <c r="D47" s="151">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.7842783357574838</v>
+        <v>1.7842783357574834</v>
       </c>
       <c r="F47" s="289"/>
     </row>
@@ -7853,20 +8060,20 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="161" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C49" s="268" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D49" s="224" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="289"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C50" s="98">
         <f>G31/Normalized_FCF!C8</f>
@@ -7880,7 +8087,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C51" s="208"/>
       <c r="D51" s="94">
@@ -7894,19 +8101,19 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="161" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C53" s="268" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D53" s="224" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F53" s="289"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C54" s="94">
         <f>Normalized_FCF!C8/G35</f>
@@ -7920,7 +8127,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C11/G40</f>
@@ -7937,19 +8144,19 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B57" s="161" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C57" s="268" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D57" s="224" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F57" s="289"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C58" s="101"/>
       <c r="D58" s="23">
@@ -7960,7 +8167,7 @@
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B59" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C59" s="101"/>
       <c r="D59" s="94">
@@ -7974,19 +8181,19 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="161" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="C61" s="268" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D61" s="224" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F61" s="289"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C62" s="94">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -7997,12 +8204,12 @@
         <v>1.3197490690642218E-3</v>
       </c>
       <c r="F62" s="289" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" s="81" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -8013,21 +8220,21 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B65" s="16" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C65" s="267" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D65" s="210" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="F65" s="293" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B66" s="108" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -8038,12 +8245,12 @@
         <v>1823806.3881188305</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B67" s="108" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -8053,7 +8260,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="108" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -8063,7 +8270,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="108" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -8073,7 +8280,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C70" s="83">
         <f>SUM(C66:C69)</f>
@@ -8086,19 +8293,19 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="291" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="C72" s="267" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D72" s="209" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F72" s="289"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="C73" s="191">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8109,12 +8316,12 @@
         <v>-140154.2686468616</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>384</v>
+        <v>365</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="294" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="C74" s="295">
         <f>-$C$66/C73</f>
@@ -8125,12 +8332,12 @@
         <v>19.012849381806323</v>
       </c>
       <c r="F74" s="289" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="82" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="C75" s="299"/>
       <c r="D75" s="298">
@@ -8138,12 +8345,12 @@
         <v>840925.61188116961</v>
       </c>
       <c r="F75" s="289" t="s">
-        <v>385</v>
+        <v>366</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="296" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="C76" s="297"/>
       <c r="D76" s="333">
@@ -8151,7 +8358,7 @@
         <v>6</v>
       </c>
       <c r="F76" s="289" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8159,10 +8366,10 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C78" s="267" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D78" s="210" t="s">
         <v>35</v>
@@ -8171,7 +8378,7 @@
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="108" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -8185,7 +8392,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="108" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -8199,7 +8406,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="108" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -8213,7 +8420,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B82" s="82" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C82" s="83">
         <f>SUM(C79:C81)</f>
@@ -8227,7 +8434,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8238,23 +8445,23 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="D85" s="276" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="273" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-36231.187345500002</v>
+        <v>-36231.187345499995</v>
       </c>
       <c r="D86" s="254">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-2.7173387112451611E-2</v>
+        <v>-2.7173387112451604E-2</v>
       </c>
       <c r="E86" s="275" t="str">
         <f>Market_currency</f>
@@ -8263,15 +8470,15 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="273" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>1943547.4846275786</v>
+        <v>1943547.4846275782</v>
       </c>
       <c r="D87" s="254">
         <f>C87*$H$1/Common_Shares</f>
-        <v>1.4576604312631301</v>
+        <v>1.4576604312631298</v>
       </c>
       <c r="E87" s="275" t="str">
         <f>Market_currency</f>
@@ -8280,11 +8487,11 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B88" s="274" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C88" s="191">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>242603.49337560002</v>
+        <v>242603.49337559997</v>
       </c>
       <c r="D88" s="254">
         <f>C88*$H$1/Common_Shares</f>
@@ -8297,15 +8504,15 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="82" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
-        <v>2149919.7906576786</v>
+        <v>2149919.7906576782</v>
       </c>
       <c r="D89" s="277">
         <f>SUM(D86:D88)</f>
-        <v>1.6124396414383038</v>
+        <v>1.6124396414383035</v>
       </c>
       <c r="E89" s="275" t="str">
         <f>Market_currency</f>
@@ -8345,7 +8552,7 @@
         <v>CNY</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
@@ -8398,12 +8605,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="37"/>
@@ -8421,7 +8628,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C3" s="110">
         <f>Data!C3</f>
@@ -8492,7 +8699,7 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" s="197">
         <f>C25</f>
@@ -8547,7 +8754,7 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C6" s="187">
         <f>C4+C5</f>
@@ -8602,7 +8809,7 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" s="197">
         <f>C35</f>
@@ -8657,7 +8864,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C8" s="198">
         <f>C6+C7</f>
@@ -8714,7 +8921,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C9" s="197">
         <f>BS!$G$39*BS!D58</f>
@@ -8769,7 +8976,7 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C10" s="197">
         <f>-C4*C78</f>
@@ -8824,7 +9031,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C11" s="199">
         <f>C63</f>
@@ -8881,7 +9088,7 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C12" s="197">
         <f>C50</f>
@@ -8936,7 +9143,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="10"/>
       <c r="B13" s="71" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C13" s="187">
         <f>SUM(C8:C12)</f>
@@ -8991,7 +9198,7 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14" s="197">
         <f>-SUM(C8+C11,C12)*C43</f>
@@ -9046,7 +9253,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C15" s="197">
         <f>-C4*C83</f>
@@ -9103,7 +9310,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C16" s="200">
         <f>SUM(C13:C15)</f>
@@ -9160,7 +9367,7 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C17" s="197">
         <f>-C4*C85</f>
@@ -9168,7 +9375,7 @@
       </c>
       <c r="D17" s="59"/>
       <c r="E17" s="307" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="201"/>
@@ -9186,14 +9393,14 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C18" s="197">
         <v>0</v>
       </c>
       <c r="D18" s="59"/>
       <c r="E18" s="307" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="202"/>
@@ -9211,7 +9418,7 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C19" s="187">
         <f>C16+C17</f>
@@ -9287,12 +9494,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
       <c r="E21" s="67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="37"/>
@@ -9310,7 +9517,7 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="10"/>
       <c r="B22" s="65" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="27"/>
@@ -9331,7 +9538,7 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" s="203">
         <f>-C4*C28</f>
@@ -9388,7 +9595,7 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10"/>
       <c r="B24" s="69" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C24" s="197">
         <f>-C4*C29</f>
@@ -9445,7 +9652,7 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10"/>
       <c r="B25" s="71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C25" s="187">
         <f>C23+C24</f>
@@ -9506,14 +9713,14 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="65" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E27" s="308"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" s="64">
         <f>AVERAGE(G28:H28)</f>
@@ -9521,7 +9728,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="306" t="s">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -9581,7 +9788,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="306" t="s">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -9632,7 +9839,7 @@
     <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10"/>
       <c r="B30" s="71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C30" s="72">
         <f>ABS(C25/$C$4)</f>
@@ -9691,21 +9898,21 @@
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10"/>
       <c r="B32" s="65" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E32" s="308"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C33" s="204">
         <f>AVERAGE(G33:H33)</f>
         <v>-175999.5</v>
       </c>
       <c r="E33" s="306" t="s">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="G33" s="197">
         <f>Data!C41</f>
@@ -9755,7 +9962,7 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C34" s="204">
         <f>AVERAGE(G34:J34)</f>
@@ -9763,7 +9970,7 @@
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="306" t="s">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="186">
@@ -9814,7 +10021,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="10"/>
       <c r="B35" s="71" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C35" s="187">
         <f>C33+C34</f>
@@ -9875,7 +10082,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10"/>
       <c r="B37" s="65" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E37" s="308"/>
     </row>
@@ -9998,7 +10205,7 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="10"/>
       <c r="B40" s="71" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C40" s="72">
         <f>ABS(C35/$C$4)</f>
@@ -10057,21 +10264,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10"/>
       <c r="B42" s="65" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E42" s="308"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C43" s="302">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="305" t="s">
-        <v>365</v>
+        <v>348</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10125,12 +10332,12 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
       <c r="E45" s="67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="37"/>
@@ -10148,7 +10355,7 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="10"/>
       <c r="B46" s="65" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E46" s="308"/>
     </row>
@@ -10210,7 +10417,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>378</v>
+        <v>359</v>
       </c>
       <c r="C48" s="197">
         <f>BS!D75*C53</f>
@@ -10265,7 +10472,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="329" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="C49" s="330">
         <f>BS!$C$66*C53</f>
@@ -10322,7 +10529,7 @@
     <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="10"/>
       <c r="B50" s="71" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C50" s="187">
         <f>C47+C48</f>
@@ -10381,24 +10588,24 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="10"/>
       <c r="B52" s="73" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E52" s="308"/>
       <c r="G52" s="100" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C53" s="89">
         <f>G53</f>
         <v>2.7696969151119136E-2</v>
       </c>
       <c r="E53" s="305" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -10418,14 +10625,14 @@
     <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C54" s="84">
         <f>G54</f>
         <v>2.9500867672578604E-2</v>
       </c>
       <c r="E54" s="305" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -10445,7 +10652,7 @@
     <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
@@ -10504,17 +10711,17 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="10"/>
       <c r="B57" s="65" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E57" s="308"/>
       <c r="G57" s="100" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C58" s="197">
         <f>BS!$C79*C66</f>
@@ -10569,7 +10776,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C59" s="197">
         <f>BS!$C68*C67</f>
@@ -10624,7 +10831,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C60" s="197">
         <f>BS!$C81*C68</f>
@@ -10679,7 +10886,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C61" s="187">
         <f>SUM(C58:C60)</f>
@@ -10734,13 +10941,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C62" s="303">
         <v>0</v>
       </c>
       <c r="E62" s="306" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="G62" s="197">
         <f>Data!C58</f>
@@ -10790,7 +10997,7 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C63" s="187">
         <f>C61+C62</f>
@@ -10849,17 +11056,17 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="10"/>
       <c r="B65" s="99" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E65" s="308"/>
       <c r="G65" s="100" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C66" s="180">
         <f>G66</f>
@@ -10884,7 +11091,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="10"/>
       <c r="B67" s="108" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C67" s="180">
         <f>G67</f>
@@ -10909,7 +11116,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="10"/>
       <c r="B68" s="108" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C68" s="180">
         <f>G68</f>
@@ -10934,7 +11141,7 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C69" s="72">
         <f>C61/BS!C70</f>
@@ -10964,12 +11171,12 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -10987,7 +11194,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="10"/>
       <c r="B72" s="73" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C72" s="63"/>
       <c r="D72" s="27"/>
@@ -11008,7 +11215,7 @@
     <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C73" s="79">
         <f>ABS(C5/C$4)</f>
@@ -11065,7 +11272,7 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C74" s="80">
         <f>ABS(C6/C$4)</f>
@@ -11122,7 +11329,7 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C75" s="79">
         <f>ABS(C7/C$4)</f>
@@ -11179,7 +11386,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C76" s="80">
         <f>ABS(C8/C$4)</f>
@@ -11236,7 +11443,7 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C77" s="79">
         <f>ABS(C9/C$4)</f>
@@ -11293,7 +11500,7 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C78" s="90">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
@@ -11301,7 +11508,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="306" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -11352,7 +11559,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C79" s="80">
         <f>ABS(C11/C$4)</f>
@@ -11409,7 +11616,7 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C80" s="79">
         <f>ABS(C12/C$4)</f>
@@ -11466,7 +11673,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="10"/>
       <c r="B81" s="71" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C81" s="80">
         <f>C13/C4</f>
@@ -11523,7 +11730,7 @@
     <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C82" s="79">
         <f>ABS(C14/C$4)</f>
@@ -11638,7 +11845,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C84" s="80">
         <f>ABS(C16/C$4)</f>
@@ -11695,7 +11902,7 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C85" s="304">
         <v>0</v>
@@ -11721,7 +11928,7 @@
     <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C86" s="79">
         <v>0</v>
@@ -11745,7 +11952,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C87" s="80">
         <f>ABS(C19/C$4)</f>
@@ -11806,7 +12013,7 @@
     <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="10"/>
       <c r="B89" s="65" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E89" s="308"/>
     </row>
@@ -11925,7 +12132,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
@@ -11980,7 +12187,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -12039,7 +12246,7 @@
     <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="10"/>
       <c r="B95" s="161" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C95" s="63"/>
       <c r="D95" s="27"/>
@@ -12060,7 +12267,7 @@
     <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C96" s="79">
         <f>C4/G4-1</f>
@@ -12117,7 +12324,7 @@
     <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="10"/>
       <c r="B97" s="71" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C97" s="79">
         <f>C13/G13-1</f>
@@ -12177,12 +12384,12 @@
     <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C99" s="54"/>
       <c r="D99" s="56"/>
       <c r="E99" s="67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F99" s="56"/>
       <c r="G99" s="37"/>
@@ -12204,7 +12411,7 @@
       </c>
       <c r="E100" s="308"/>
       <c r="G100" s="100" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -12267,7 +12474,7 @@
     <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="10"/>
       <c r="B102" s="95" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C102" s="206">
         <f>BS!C4</f>
@@ -12324,7 +12531,7 @@
     <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="10"/>
       <c r="B103" s="95" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C103" s="206">
         <f>BS!C6+BS!C7</f>
@@ -12499,14 +12706,14 @@
     <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="10"/>
       <c r="B107" s="93" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
       <c r="E107" s="309"/>
       <c r="F107" s="26"/>
       <c r="G107" s="100" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H107" s="12"/>
       <c r="I107" s="12"/>
@@ -12522,7 +12729,7 @@
     <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C108" s="97">
         <f>C102/C$4</f>
@@ -12579,7 +12786,7 @@
     <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C109" s="97">
         <f>C103/C$4</f>
@@ -12636,7 +12843,7 @@
     <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C110" s="97">
         <f>BS!$G$38/C$4</f>
@@ -12721,7 +12928,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C113" s="23">
         <f>C81</f>
@@ -12775,7 +12982,7 @@
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B114" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C114" s="42">
         <f>C4/C101</f>
@@ -12829,7 +13036,7 @@
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B115" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C115" s="15">
         <f>C101/C105</f>
@@ -12886,7 +13093,7 @@
     <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="10"/>
       <c r="B116" s="71" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C116" s="105">
         <f>C8/C105</f>
@@ -12962,12 +13169,12 @@
     <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A118" s="10"/>
       <c r="B118" s="54" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C118" s="54"/>
       <c r="D118" s="56"/>
       <c r="E118" s="67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F118" s="56"/>
       <c r="G118" s="37"/>
@@ -12985,7 +13192,7 @@
     <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="10"/>
       <c r="B119" s="182" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C119" s="183"/>
       <c r="D119" s="27"/>
@@ -13011,30 +13218,30 @@
       </c>
       <c r="C120" s="181">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>4.681823876098179E-2</v>
+        <v>4.6818238760981776E-2</v>
       </c>
       <c r="D120" s="27"/>
       <c r="E120" s="305"/>
       <c r="F120" s="27"/>
       <c r="G120" s="181">
         <f t="shared" ref="G120:Q120" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>8.1087844593670522E-2</v>
+        <v>8.1087844593670494E-2</v>
       </c>
       <c r="H120" s="181">
         <f t="shared" si="49"/>
-        <v>1.1576502373621471E-2</v>
+        <v>1.1576502373621468E-2</v>
       </c>
       <c r="I120" s="181">
         <f t="shared" si="49"/>
-        <v>6.4422017822083538E-2</v>
+        <v>6.4422017822083524E-2</v>
       </c>
       <c r="J120" s="181">
         <f t="shared" si="49"/>
-        <v>0.22659526735787525</v>
+        <v>0.22659526735787519</v>
       </c>
       <c r="K120" s="181">
         <f t="shared" si="49"/>
-        <v>0.16218033960070757</v>
+        <v>0.16218033960070755</v>
       </c>
       <c r="L120" s="181" t="str">
         <f t="shared" si="49"/>
@@ -13064,34 +13271,34 @@
     <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="10"/>
       <c r="B121" s="27" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="C121" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.1775925005107808E-2</v>
+        <v>2.1775925005107801E-2</v>
       </c>
       <c r="D121" s="27"/>
       <c r="E121" s="305"/>
       <c r="F121" s="27"/>
       <c r="G121" s="79">
         <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
-        <v>3.771527655519559E-2</v>
+        <v>3.7715276555195583E-2</v>
       </c>
       <c r="H121" s="79">
         <f t="shared" ref="H121" si="51">IF(H$4="","",H120/Market_Price)</f>
-        <v>5.3844197086611494E-3</v>
+        <v>5.3844197086611477E-3</v>
       </c>
       <c r="I121" s="79">
         <f t="shared" ref="I121" si="52">IF(I$4="","",I120/Market_Price)</f>
-        <v>2.9963729219573739E-2</v>
+        <v>2.9963729219573732E-2</v>
       </c>
       <c r="J121" s="79">
         <f t="shared" ref="J121" si="53">IF(J$4="","",J120/Market_Price)</f>
-        <v>0.10539314760831407</v>
+        <v>0.10539314760831404</v>
       </c>
       <c r="K121" s="79">
         <f t="shared" ref="K121" si="54">IF(K$4="","",K120/Market_Price)</f>
-        <v>7.5432716093352364E-2</v>
+        <v>7.5432716093352351E-2</v>
       </c>
       <c r="L121" s="79" t="str">
         <f t="shared" ref="L121" si="55">IF(L$4="","",L120/Market_Price)</f>
@@ -13833,32 +14040,32 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="134" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="112" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C3" s="110">
         <f>Normalized_FCF!C3</f>
         <v>1000</v>
       </c>
       <c r="E3" s="112" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H3" s="124"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B4" s="103" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C4" s="113">
         <f>Normalized_FCF!C19</f>
@@ -13869,17 +14076,17 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="103" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F4" s="138">
-        <f>Thesis!C75</f>
+        <f>Thesis!C76</f>
         <v>0</v>
       </c>
       <c r="H4" s="124"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B5" s="233" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C5" s="234">
         <f>Thesis!C70</f>
@@ -13890,7 +14097,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="153" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C6" s="238">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -13900,15 +14107,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="344" t="s">
-        <v>255</v>
-      </c>
-      <c r="F6" s="344"/>
+      <c r="E6" s="345" t="s">
+        <v>251</v>
+      </c>
+      <c r="F6" s="345"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" s="152" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C7" s="232">
         <f>BS!G31</f>
@@ -13918,13 +14125,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="344"/>
-      <c r="F7" s="344"/>
+      <c r="E7" s="345"/>
+      <c r="F7" s="345"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B8" s="152" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C8" s="207">
         <f>BS!D66</f>
@@ -13934,13 +14141,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="344"/>
-      <c r="F8" s="344"/>
+      <c r="E8" s="345"/>
+      <c r="F8" s="345"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B9" s="233" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C9" s="235">
         <f>BS!H42</f>
@@ -13950,13 +14157,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="344"/>
-      <c r="F9" s="344"/>
+      <c r="E9" s="345"/>
+      <c r="F9" s="345"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B10" s="153" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C10" s="238">
         <f>C6-C7+C8+C9</f>
@@ -13970,11 +14177,11 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="236" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C11" s="237">
         <f>Exchange_Rate</f>
-        <v>1.0656545000000002</v>
+        <v>1.0656544999999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -13984,11 +14191,11 @@
     </row>
     <row r="12" spans="2:8" ht="13.5" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B12" s="153" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>2.1976676259505763</v>
+        <v>2.1976676259505759</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14001,7 +14208,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B14" s="36" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -14011,13 +14218,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B15" s="123" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H15" s="124"/>
     </row>
     <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C16" s="165">
         <f>Scenarios!C65</f>
@@ -14027,7 +14234,7 @@
     </row>
     <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C17" s="166">
         <f>Scenarios!C64</f>
@@ -14037,11 +14244,11 @@
     </row>
     <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="157" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>2.2310982755638773</v>
+        <v>2.2310982755638769</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14054,19 +14261,19 @@
     </row>
     <row r="20" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="132" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" s="132" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="132" t="s">
+        <v>120</v>
+      </c>
+      <c r="E20" s="132" t="s">
         <v>111</v>
       </c>
-      <c r="C20" s="132" t="s">
+      <c r="F20" s="133" t="s">
         <v>112</v>
-      </c>
-      <c r="D20" s="132" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" s="132" t="s">
-        <v>113</v>
-      </c>
-      <c r="F20" s="133" t="s">
-        <v>114</v>
       </c>
       <c r="H20" s="124"/>
     </row>
@@ -14732,7 +14939,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B51" s="130" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C51" s="127">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -14755,7 +14962,7 @@
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C52" s="118"/>
       <c r="E52" s="131" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F52" s="141">
         <f>SUM(F21:F51)</f>
@@ -14769,7 +14976,7 @@
     </row>
     <row r="54" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B54" s="123" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C54" s="140"/>
       <c r="D54" s="140"/>
@@ -14940,7 +15147,7 @@
     </row>
     <row r="63" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B63" s="123" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C63" s="118"/>
       <c r="D63" s="118"/>
@@ -14977,23 +15184,23 @@
       </c>
       <c r="B65" s="128">
         <f>C12</f>
-        <v>2.1976676259505763</v>
+        <v>2.1976676259505759</v>
       </c>
       <c r="C65" s="128">
         <f>C12</f>
-        <v>2.1976676259505763</v>
+        <v>2.1976676259505759</v>
       </c>
       <c r="D65" s="128">
         <f>C12</f>
-        <v>2.1976676259505763</v>
+        <v>2.1976676259505759</v>
       </c>
       <c r="E65" s="145">
         <f>C12</f>
-        <v>2.1976676259505763</v>
+        <v>2.1976676259505759</v>
       </c>
       <c r="F65" s="128">
         <f>C12</f>
-        <v>2.1976676259505763</v>
+        <v>2.1976676259505759</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -15004,23 +15211,23 @@
       </c>
       <c r="B66" s="128">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.1441763093761184</v>
+        <v>2.1441763093761179</v>
       </c>
       <c r="C66" s="128">
         <f t="shared" si="4"/>
-        <v>2.1441763093761184</v>
+        <v>2.1441763093761179</v>
       </c>
       <c r="D66" s="128">
         <f t="shared" si="4"/>
-        <v>2.216550144242492</v>
+        <v>2.2165501442424915</v>
       </c>
       <c r="E66" s="128">
         <f t="shared" si="4"/>
-        <v>2.2560365673590219</v>
+        <v>2.2560365673590215</v>
       </c>
       <c r="F66" s="128">
         <f t="shared" si="4"/>
-        <v>2.2766908745516332</v>
+        <v>2.2766908745516328</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -15031,23 +15238,23 @@
       </c>
       <c r="B67" s="128">
         <f t="shared" si="4"/>
-        <v>2.1031747944424914</v>
+        <v>2.103174794442491</v>
       </c>
       <c r="C67" s="128">
         <f t="shared" si="4"/>
-        <v>2.1031747944424914</v>
+        <v>2.103174794442491</v>
       </c>
       <c r="D67" s="128">
         <f t="shared" si="4"/>
-        <v>2.2354500503498467</v>
+        <v>2.2354500503498462</v>
       </c>
       <c r="E67" s="128">
         <f t="shared" si="4"/>
-        <v>2.3228285645218714</v>
+        <v>2.3228285645218709</v>
       </c>
       <c r="F67" s="128">
         <f t="shared" si="4"/>
-        <v>2.3733817238368116</v>
+        <v>2.3733817238368111</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -15058,23 +15265,23 @@
       </c>
       <c r="B68" s="128">
         <f t="shared" si="4"/>
-        <v>2.0610375891427837</v>
+        <v>2.0610375891427832</v>
       </c>
       <c r="C68" s="128">
         <f t="shared" si="4"/>
-        <v>2.0610375891427837</v>
+        <v>2.0610375891427832</v>
       </c>
       <c r="D68" s="128">
         <f t="shared" si="4"/>
-        <v>2.2588439246105989</v>
+        <v>2.2588439246105985</v>
       </c>
       <c r="E68" s="128">
         <f t="shared" si="4"/>
-        <v>2.4147035335309472</v>
+        <v>2.4147035335309468</v>
       </c>
       <c r="F68" s="128">
         <f t="shared" si="4"/>
-        <v>2.5139605518949426</v>
+        <v>2.5139605518949422</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -15085,23 +15292,23 @@
       </c>
       <c r="B69" s="128">
         <f t="shared" si="4"/>
-        <v>2.0252509453511194</v>
+        <v>2.0252509453511189</v>
       </c>
       <c r="C69" s="128">
         <f t="shared" si="4"/>
-        <v>2.0252509453511194</v>
+        <v>2.0252509453511189</v>
       </c>
       <c r="D69" s="128">
         <f t="shared" si="4"/>
-        <v>2.282678530864156</v>
+        <v>2.2826785308641555</v>
       </c>
       <c r="E69" s="128">
         <f t="shared" si="4"/>
-        <v>2.5195079002627967</v>
+        <v>2.5195079002627963</v>
       </c>
       <c r="F69" s="128">
         <f t="shared" si="4"/>
-        <v>2.68440880085772</v>
+        <v>2.6844088008577196</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -15112,23 +15319,23 @@
       </c>
       <c r="B70" s="128">
         <f t="shared" si="4"/>
-        <v>1.9973444490014296</v>
+        <v>1.9973444490014292</v>
       </c>
       <c r="C70" s="128">
         <f t="shared" si="4"/>
-        <v>1.9973444490014296</v>
+        <v>1.9973444490014292</v>
       </c>
       <c r="D70" s="128">
         <f t="shared" si="4"/>
-        <v>2.3048460372624939</v>
+        <v>2.3048460372624935</v>
       </c>
       <c r="E70" s="128">
         <f t="shared" si="4"/>
-        <v>2.6293396900317085</v>
+        <v>2.6293396900317076</v>
       </c>
       <c r="F70" s="128">
         <f t="shared" si="4"/>
-        <v>2.8751856757933285</v>
+        <v>2.8751856757933281</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15138,40 +15345,40 @@
       </c>
       <c r="B71" s="128">
         <f t="shared" si="4"/>
-        <v>1.9765782391626117</v>
+        <v>1.9765782391626112</v>
       </c>
       <c r="C71" s="128">
         <f t="shared" si="4"/>
-        <v>1.9765782391626117</v>
+        <v>1.9765782391626112</v>
       </c>
       <c r="D71" s="128">
         <f t="shared" si="4"/>
-        <v>2.3244008615872862</v>
+        <v>2.3244008615872858</v>
       </c>
       <c r="E71" s="128">
         <f t="shared" si="4"/>
-        <v>2.739157522329998</v>
+        <v>2.7391575223299971</v>
       </c>
       <c r="F71" s="128">
         <f t="shared" si="4"/>
-        <v>3.0797978719848298</v>
+        <v>3.0797978719848289</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B73" s="175" t="s">
+        <v>119</v>
+      </c>
+      <c r="C73" s="175" t="s">
+        <v>134</v>
+      </c>
+      <c r="D73" s="175" t="s">
+        <v>114</v>
+      </c>
+      <c r="E73" s="176" t="s">
+        <v>115</v>
+      </c>
+      <c r="F73" s="176" t="s">
         <v>121</v>
-      </c>
-      <c r="C73" s="175" t="s">
-        <v>136</v>
-      </c>
-      <c r="D73" s="175" t="s">
-        <v>116</v>
-      </c>
-      <c r="E73" s="176" t="s">
-        <v>117</v>
-      </c>
-      <c r="F73" s="176" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
@@ -15189,7 +15396,7 @@
       </c>
       <c r="E74" s="139">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>2.5139605518949426</v>
+        <v>2.5139605518949422</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
@@ -15211,7 +15418,7 @@
       </c>
       <c r="E75" s="139">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>2.3228285645218714</v>
+        <v>2.3228285645218709</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -15234,7 +15441,7 @@
       </c>
       <c r="E76" s="139">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>2.2354500503498467</v>
+        <v>2.2354500503498462</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15257,7 +15464,7 @@
       </c>
       <c r="E77" s="139">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>2.1031747944424914</v>
+        <v>2.103174794442491</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -15280,7 +15487,7 @@
       </c>
       <c r="E78" s="139">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.0610375891427837</v>
+        <v>2.0610375891427832</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
@@ -15296,20 +15503,20 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="159" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="C80" s="159" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="81" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C81" s="159" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="82" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C82" s="159" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="92" spans="3:3" x14ac:dyDescent="0.35">
@@ -15361,20 +15568,20 @@
   <sheetData>
     <row r="2" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="283" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="I2" s="284"/>
     </row>
     <row r="3" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="163" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H3" s="282">
         <v>0</v>
@@ -15386,14 +15593,14 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B4" s="156" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C4" s="124">
         <v>3</v>
       </c>
       <c r="D4" s="124"/>
       <c r="E4" s="159" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F4" s="159"/>
       <c r="H4" s="282">
@@ -15415,14 +15622,14 @@
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B6" s="163" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C6" s="110">
         <f>Valuation_Model!C3</f>
         <v>1000</v>
       </c>
       <c r="E6" s="103" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="F6" s="103"/>
       <c r="H6" s="282">
@@ -15435,7 +15642,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="103" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="C7" s="118">
         <f>Normalized_FCF!G8</f>
@@ -15445,11 +15652,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="346" t="str">
+      <c r="E7" s="347" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 朝云集团(6601.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="346"/>
+      <c r="F7" s="347"/>
       <c r="H7" s="282">
         <v>4</v>
       </c>
@@ -15460,7 +15667,7 @@
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" s="103" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C8" s="118">
         <f>Normalized_FCF!G19</f>
@@ -15470,8 +15677,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="346"/>
-      <c r="F8" s="346"/>
+      <c r="E8" s="347"/>
+      <c r="F8" s="347"/>
       <c r="H8" s="282">
         <v>5</v>
       </c>
@@ -15482,7 +15689,7 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B9" s="103" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C9" s="207">
         <f>Normalized_FCF!C19</f>
@@ -15492,8 +15699,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="346"/>
-      <c r="F9" s="346"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
       <c r="H9" s="282">
         <v>6</v>
       </c>
@@ -15503,8 +15710,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="346"/>
-      <c r="F10" s="346"/>
+      <c r="E10" s="347"/>
+      <c r="F10" s="347"/>
       <c r="H10" s="282">
         <v>7</v>
       </c>
@@ -15515,10 +15722,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="163" t="s">
-        <v>294</v>
-      </c>
-      <c r="E11" s="346"/>
-      <c r="F11" s="346"/>
+        <v>283</v>
+      </c>
+      <c r="E11" s="347"/>
+      <c r="F11" s="347"/>
       <c r="H11" s="282">
         <v>8</v>
       </c>
@@ -15529,15 +15736,15 @@
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B12" s="122" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C12" s="162">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-1.7248638436905273E-2</v>
       </c>
       <c r="D12" s="162"/>
-      <c r="E12" s="346"/>
-      <c r="F12" s="346"/>
+      <c r="E12" s="347"/>
+      <c r="F12" s="347"/>
       <c r="H12" s="282">
         <v>9</v>
       </c>
@@ -15548,14 +15755,14 @@
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B13" s="152" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C13" s="162">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.283580450424601</v>
       </c>
-      <c r="E13" s="346"/>
-      <c r="F13" s="346"/>
+      <c r="E13" s="347"/>
+      <c r="F13" s="347"/>
       <c r="H13" s="282">
         <v>10</v>
       </c>
@@ -15566,18 +15773,18 @@
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="103" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C14" s="162">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.29003821304292421</v>
       </c>
-      <c r="E14" s="346"/>
-      <c r="F14" s="346"/>
+      <c r="E14" s="347"/>
+      <c r="F14" s="347"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -15586,38 +15793,38 @@
     </row>
     <row r="17" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B17" s="112" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E17" s="163" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C18" s="154">
         <v>10</v>
       </c>
-      <c r="E18" s="346" t="s">
-        <v>359</v>
-      </c>
-      <c r="F18" s="347"/>
+      <c r="E18" s="347" t="s">
+        <v>344</v>
+      </c>
+      <c r="F18" s="348"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="347"/>
-      <c r="F19" s="347"/>
+      <c r="E19" s="348"/>
+      <c r="F19" s="348"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="163" t="s">
-        <v>328</v>
-      </c>
-      <c r="E20" s="347"/>
-      <c r="F20" s="347"/>
+        <v>314</v>
+      </c>
+      <c r="E20" s="348"/>
+      <c r="F20" s="348"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
@@ -15627,202 +15834,202 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="347"/>
-      <c r="F21" s="347"/>
+      <c r="E21" s="348"/>
+      <c r="F21" s="348"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
-        <v>2.1976676259505763</v>
+        <v>2.1976676259505759</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="347"/>
-      <c r="F22" s="347"/>
+      <c r="E22" s="348"/>
+      <c r="F22" s="348"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="163" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E24" s="163" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F24" s="163"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C25" s="170">
         <f>C18</f>
         <v>10</v>
       </c>
       <c r="D25" s="167"/>
-      <c r="E25" s="345"/>
-      <c r="F25" s="345"/>
+      <c r="E25" s="346"/>
+      <c r="F25" s="346"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C26" s="168">
         <v>0.02</v>
       </c>
       <c r="D26" s="168"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="E26" s="346"/>
+      <c r="F26" s="346"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C27" s="164">
         <f>Valuation_Model!E76</f>
-        <v>2.2354500503498467</v>
+        <v>2.2354500503498462</v>
       </c>
       <c r="D27" s="164" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="345"/>
-      <c r="F27" s="345"/>
+      <c r="E27" s="346"/>
+      <c r="F27" s="346"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C28" s="169">
         <v>0.6</v>
       </c>
       <c r="D28" s="169"/>
-      <c r="E28" s="345"/>
-      <c r="F28" s="345"/>
+      <c r="E28" s="346"/>
+      <c r="F28" s="346"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="163" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E30" s="163" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F30" s="163"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B31" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C31" s="170">
         <f>C18</f>
         <v>10</v>
       </c>
       <c r="D31" s="167"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="E31" s="346"/>
+      <c r="F31" s="346"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C32" s="168">
         <v>-0.06</v>
       </c>
       <c r="D32" s="168"/>
-      <c r="E32" s="345"/>
-      <c r="F32" s="345"/>
+      <c r="E32" s="346"/>
+      <c r="F32" s="346"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C33" s="164">
         <f>Valuation_Model!E77</f>
-        <v>2.1031747944424914</v>
+        <v>2.103174794442491</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="345"/>
-      <c r="F33" s="345"/>
+      <c r="E33" s="346"/>
+      <c r="F33" s="346"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C34" s="169">
         <v>0.15</v>
       </c>
       <c r="D34" s="169"/>
-      <c r="E34" s="345"/>
-      <c r="F34" s="345"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="163" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E36" s="163" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F36" s="163"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C37" s="170">
         <f>C18</f>
         <v>10</v>
       </c>
       <c r="D37" s="167"/>
-      <c r="E37" s="345"/>
-      <c r="F37" s="345"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C38" s="168">
         <v>0.06</v>
       </c>
       <c r="D38" s="168"/>
-      <c r="E38" s="345"/>
-      <c r="F38" s="345"/>
+      <c r="E38" s="346"/>
+      <c r="F38" s="346"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C39" s="164">
         <f>Valuation_Model!E75</f>
-        <v>2.3228285645218714</v>
+        <v>2.3228285645218709</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="345"/>
-      <c r="F39" s="345"/>
+      <c r="E39" s="346"/>
+      <c r="F39" s="346"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C40" s="171">
         <f>1-C28-C34</f>
         <v>0.25</v>
       </c>
       <c r="D40" s="169"/>
-      <c r="E40" s="345"/>
-      <c r="F40" s="345"/>
+      <c r="E40" s="346"/>
+      <c r="F40" s="346"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C42" s="158">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -15835,7 +16042,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B44" s="36" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -15844,12 +16051,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B45" s="112" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C46" s="154">
         <v>15</v>
@@ -15864,123 +16071,123 @@
     </row>
     <row r="48" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B48" s="163" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E48" s="163" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F48" s="163"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C49" s="170">
         <f>C46</f>
         <v>15</v>
       </c>
       <c r="D49" s="167"/>
-      <c r="E49" s="345"/>
-      <c r="F49" s="345"/>
+      <c r="E49" s="346"/>
+      <c r="F49" s="346"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C50" s="168">
         <v>-0.06</v>
       </c>
       <c r="D50" s="168"/>
-      <c r="E50" s="345"/>
-      <c r="F50" s="345"/>
+      <c r="E50" s="346"/>
+      <c r="F50" s="346"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C51" s="164">
         <f>Valuation_Model!E78</f>
-        <v>2.0610375891427837</v>
+        <v>2.0610375891427832</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="345"/>
-      <c r="F51" s="345"/>
+      <c r="E51" s="346"/>
+      <c r="F51" s="346"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C52" s="169">
         <v>0.1</v>
       </c>
       <c r="D52" s="169"/>
-      <c r="E52" s="345"/>
-      <c r="F52" s="345"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="163" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="E54" s="163" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F54" s="163"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B55" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C55" s="170">
         <f>C46</f>
         <v>15</v>
       </c>
       <c r="D55" s="167"/>
-      <c r="E55" s="345"/>
-      <c r="F55" s="345"/>
+      <c r="E55" s="346"/>
+      <c r="F55" s="346"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C56" s="168">
         <v>0.08</v>
       </c>
       <c r="D56" s="168"/>
-      <c r="E56" s="345"/>
-      <c r="F56" s="345"/>
+      <c r="E56" s="346"/>
+      <c r="F56" s="346"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C57" s="164">
         <f>Valuation_Model!E74</f>
-        <v>2.5139605518949426</v>
+        <v>2.5139605518949422</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="345"/>
-      <c r="F57" s="345"/>
+      <c r="E57" s="346"/>
+      <c r="F57" s="346"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C58" s="169">
         <v>0.05</v>
       </c>
       <c r="D58" s="169"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="E58" s="346"/>
+      <c r="F58" s="346"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C60" s="158">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -15991,7 +16198,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="103" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="F60" s="318">
         <f>Thesis!E20</f>
@@ -16000,7 +16207,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16009,63 +16216,63 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="112" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="E63" s="288" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B64" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C64" s="170">
         <v>10</v>
       </c>
       <c r="D64" s="154"/>
       <c r="E64" s="287" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B65" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C65" s="155">
         <v>1.77907652777404E-2</v>
       </c>
       <c r="D65" s="155"/>
       <c r="E65" s="287" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B66" s="103" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C66" s="164">
         <f>Valuation_Model!C18</f>
-        <v>2.2310982755638773</v>
+        <v>2.2310982755638769</v>
       </c>
       <c r="D66" s="164" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E66" s="287" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="112" t="s">
-        <v>383</v>
+        <v>364</v>
       </c>
       <c r="E68" s="288" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="103" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="C69" s="279" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16075,19 +16282,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="103" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="C70" s="279" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="287" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="103" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="C71" s="279" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16097,23 +16304,23 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="C72" s="278" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="E72" s="138" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
       <c r="F72" s="335">
         <f>BS!D89/C60</f>
-        <v>0.72188968925719621</v>
+        <v>0.7218896892571961</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B74" s="36" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -16122,12 +16329,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B75" s="112" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="281" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C76" s="280">
         <f>F60</f>
@@ -16137,7 +16344,7 @@
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B77" s="103" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C77" s="177">
         <f>Normalized_FCF!C90</f>
@@ -16150,21 +16357,21 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="112" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="152" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="C80" s="171">
-        <f>Thesis!C121</f>
+        <f>Thesis!C123</f>
         <v>0.2</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B81" s="103" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C81" s="120">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -16176,7 +16383,7 @@
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B82" s="103" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
@@ -16186,7 +16393,7 @@
     </row>
     <row r="83" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B83" s="114" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
@@ -16197,7 +16404,7 @@
         <v>HKD</v>
       </c>
       <c r="E83" s="150" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F83" s="335">
         <f>(1-C83/C60)</f>
@@ -16209,12 +16416,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="112" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="152" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
@@ -16227,7 +16434,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="103" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -16239,7 +16446,7 @@
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E89" s="326" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="F89" s="323"/>
       <c r="G89" s="2"/>
@@ -16247,30 +16454,30 @@
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E90" s="319" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="F90" s="324" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="322"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E91" s="320" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="F91" s="324" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="322"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E92" s="321" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="F92" s="325" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="322"/>

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1BD0B25-BEAA-4678-94DE-DBAAA52FDB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7747590-F8FB-466A-98AB-F849DDA1215E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="411">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1353,10 +1353,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>FCFE/Market Cap =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Latest FCFE =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2156,6 +2152,149 @@
   </si>
   <si>
     <t>CFI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 6:  Risk Analysis</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Key Risk Factors</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Goal: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>To identify and assess the key risk factors inherent in this valuation model, focusing on those with the greatest potential impact on the final result.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Sustainable Revenue &amp; Margins</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Capital Expenditures</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Working Capital</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Accuracy of Normalized FCFE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>, which is affacted by uncertainties include:</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Cost of Equity is established as an investor’s hurdle rate. This rate serves as an opportunity cost threshold for capital allocation, prioritizing consistency and long-term decision-making over market-derived metrics.The model calculates intrinsic value using a standardized base cost of equity as the discount rate in DCF analysis. This rate serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium to account for ownership risks.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- The Expected Equity Value is heavily dependent on the specific growth rates (HGR), durations (HGP), and probabilities assigned to each scenario. These are inherently forecasts about an uncertain future.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- The extreme scenarios (“Snowball”, “Devil’s Advocate”) have low probabilities; if market conditions shift drastically, these might become more relevant than anticipated.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Appropriateness of Cost of Equity</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Reliability of Growth Scenarios</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Macroeconomic Sensitivity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Input Cost Volatility</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Intense Competition</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>External &amp; Company-Specific Risks</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normalized FCFE/Market Cap =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2839,7 +2978,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="349">
+  <cellXfs count="351">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3543,23 +3682,29 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3849,7 +3994,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J130"/>
+  <dimension ref="A1:J152"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -3869,10 +4014,10 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="337" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F1" s="290" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -3901,13 +4046,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>392</v>
+        <v>408</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -3915,7 +4060,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -3934,7 +4079,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C8" s="285">
         <v>6</v>
@@ -3960,7 +4105,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>2866.6670250000002</v>
+        <v>2840.0003550000001</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -3970,24 +4115,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="341" t="s">
-        <v>376</v>
-      </c>
-      <c r="C12" s="341"/>
-      <c r="D12" s="341"/>
-      <c r="E12" s="341"/>
-      <c r="F12" s="341"/>
+      <c r="B12" s="339" t="s">
+        <v>375</v>
+      </c>
+      <c r="C12" s="339"/>
+      <c r="D12" s="339"/>
+      <c r="E12" s="339"/>
+      <c r="F12" s="339"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -3997,10 +4142,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4010,7 +4155,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0656544999999999</v>
+        <v>1.06326432</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4023,13 +4168,13 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C19" s="255">
         <v>0.2</v>
@@ -4043,10 +4188,10 @@
       </c>
       <c r="C20" s="258">
         <f>C129</f>
-        <v>1.5407576206248625</v>
+        <v>1.5378583879236705</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E20" s="336">
         <v>3</v>
@@ -4054,11 +4199,11 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
-        <v>6.6927308782200656E-2</v>
+        <v>6.9712118192507999E-2</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4069,7 +4214,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="253" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4078,22 +4223,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="341" t="s">
-        <v>377</v>
-      </c>
-      <c r="C25" s="341"/>
-      <c r="D25" s="341"/>
-      <c r="E25" s="341"/>
-      <c r="F25" s="341"/>
+      <c r="B25" s="339" t="s">
+        <v>376</v>
+      </c>
+      <c r="C25" s="339"/>
+      <c r="D25" s="339"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="339" t="s">
-        <v>353</v>
-      </c>
-      <c r="C26" s="339"/>
-      <c r="D26" s="339"/>
-      <c r="E26" s="339"/>
-      <c r="F26" s="339"/>
+      <c r="B26" s="341" t="s">
+        <v>352</v>
+      </c>
+      <c r="C26" s="341"/>
+      <c r="D26" s="341"/>
+      <c r="E26" s="341"/>
+      <c r="F26" s="341"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
@@ -4198,7 +4343,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C40" s="328">
         <f>Normalized_FCF!C48</f>
@@ -4213,7 +4358,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C41" s="328">
         <f>Normalized_FCF!C47</f>
@@ -4281,12 +4426,12 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B50" s="340" t="s">
-        <v>352</v>
-      </c>
-      <c r="C50" s="344"/>
-      <c r="D50" s="344"/>
-      <c r="E50" s="344"/>
-      <c r="F50" s="344"/>
+        <v>351</v>
+      </c>
+      <c r="C50" s="343"/>
+      <c r="D50" s="343"/>
+      <c r="E50" s="343"/>
+      <c r="F50" s="343"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4302,26 +4447,26 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="341" t="s">
-        <v>357</v>
-      </c>
-      <c r="C53" s="341"/>
-      <c r="D53" s="341"/>
-      <c r="E53" s="341"/>
-      <c r="F53" s="341"/>
+      <c r="B53" s="339" t="s">
+        <v>356</v>
+      </c>
+      <c r="C53" s="339"/>
+      <c r="D53" s="339"/>
+      <c r="E53" s="339"/>
+      <c r="F53" s="339"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="341" t="s">
-        <v>378</v>
-      </c>
-      <c r="C54" s="341"/>
-      <c r="D54" s="341"/>
-      <c r="E54" s="341"/>
-      <c r="F54" s="341"/>
+      <c r="B54" s="339" t="s">
+        <v>377</v>
+      </c>
+      <c r="C54" s="339"/>
+      <c r="D54" s="339"/>
+      <c r="E54" s="339"/>
+      <c r="F54" s="339"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C56" s="191">
         <f>Normalized_FCF!G19</f>
@@ -4347,25 +4492,25 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="260" t="s">
-        <v>273</v>
+        <v>406</v>
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C121</f>
-        <v>2.1775925005107801E-2</v>
+        <v>2.1931093474110992E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="260" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
-        <v>5.4790697674418611E-2</v>
+        <v>5.5305164319248833E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="253" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4378,22 +4523,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="341" t="s">
-        <v>379</v>
-      </c>
-      <c r="C63" s="341"/>
-      <c r="D63" s="341"/>
-      <c r="E63" s="341"/>
-      <c r="F63" s="341"/>
+      <c r="B63" s="339" t="s">
+        <v>378</v>
+      </c>
+      <c r="C63" s="339"/>
+      <c r="D63" s="339"/>
+      <c r="E63" s="339"/>
+      <c r="F63" s="339"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="339" t="s">
+      <c r="B64" s="341" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="339"/>
-      <c r="D64" s="339"/>
-      <c r="E64" s="339"/>
-      <c r="F64" s="339"/>
+      <c r="C64" s="341"/>
+      <c r="D64" s="341"/>
+      <c r="E64" s="341"/>
+      <c r="F64" s="341"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
@@ -4402,7 +4547,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C67" s="317">
         <v>0.08</v>
@@ -4410,26 +4555,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C68" s="269">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="292" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C69" s="269">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="292" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4446,27 +4591,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="338" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C72" s="125"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="341" t="s">
+      <c r="B73" s="339" t="s">
+        <v>379</v>
+      </c>
+      <c r="C73" s="339"/>
+      <c r="D73" s="339"/>
+      <c r="E73" s="339"/>
+      <c r="F73" s="339"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="339" t="s">
         <v>380</v>
       </c>
-      <c r="C73" s="341"/>
-      <c r="D73" s="341"/>
-      <c r="E73" s="341"/>
-      <c r="F73" s="341"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="341" t="s">
-        <v>381</v>
-      </c>
-      <c r="C74" s="341"/>
-      <c r="D74" s="341"/>
-      <c r="E74" s="341"/>
-      <c r="F74" s="341"/>
+      <c r="C74" s="339"/>
+      <c r="D74" s="339"/>
+      <c r="E74" s="339"/>
+      <c r="F74" s="339"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4478,11 +4623,11 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B77" s="47" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C77" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.5852279845122722</v>
+        <v>0.58391536374820519</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4491,7 +4636,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="253" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4503,13 +4648,13 @@
       <c r="A80" s="239"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="341" t="s">
-        <v>382</v>
-      </c>
-      <c r="C81" s="341"/>
-      <c r="D81" s="341"/>
-      <c r="E81" s="341"/>
-      <c r="F81" s="341"/>
+      <c r="B81" s="339" t="s">
+        <v>381</v>
+      </c>
+      <c r="C81" s="339"/>
+      <c r="D81" s="339"/>
+      <c r="E81" s="339"/>
+      <c r="F81" s="339"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4522,13 +4667,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="341" t="s">
-        <v>358</v>
-      </c>
-      <c r="C85" s="341"/>
-      <c r="D85" s="341"/>
-      <c r="E85" s="341"/>
-      <c r="F85" s="341"/>
+      <c r="B85" s="339" t="s">
+        <v>357</v>
+      </c>
+      <c r="C85" s="339"/>
+      <c r="D85" s="339"/>
+      <c r="E85" s="339"/>
+      <c r="F85" s="339"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4545,11 +4690,11 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C87" s="254">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>2.7173387112451611E-2</v>
+        <v>2.7112439322705087E-2</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4589,11 +4734,11 @@
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B92" s="47" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C92" s="254">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.4576604312631296</v>
+        <v>1.4543910125072417</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4620,11 +4765,11 @@
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B96" s="47" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C96" s="254">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.18195259728762533</v>
+        <v>0.18154449179097051</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4632,21 +4777,21 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="341" t="s">
-        <v>383</v>
-      </c>
-      <c r="C98" s="341"/>
-      <c r="D98" s="341"/>
-      <c r="E98" s="341"/>
-      <c r="F98" s="341"/>
+      <c r="B98" s="339" t="s">
+        <v>382</v>
+      </c>
+      <c r="C98" s="339"/>
+      <c r="D98" s="339"/>
+      <c r="E98" s="339"/>
+      <c r="F98" s="339"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C100" s="254">
         <f>Valuation_Model!C12</f>
-        <v>2.1976676259505759</v>
+        <v>2.1927384287237124</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4655,7 +4800,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="253" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4665,7 +4810,7 @@
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B104" s="340" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C104" s="340"/>
       <c r="D104" s="340"/>
@@ -4748,7 +4893,7 @@
       </c>
       <c r="E109" s="251" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>2.24 HKD</v>
+        <v>2.23 HKD</v>
       </c>
       <c r="F109" s="252">
         <f>Valuation_Model!F76</f>
@@ -4805,7 +4950,7 @@
       </c>
       <c r="C113" s="247">
         <f>Scenarios!C60</f>
-        <v>2.2336371684397625</v>
+        <v>2.2286272943321026</v>
       </c>
       <c r="D113" s="242" t="str">
         <f>Market_currency</f>
@@ -4813,17 +4958,17 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="342" t="s">
-        <v>387</v>
-      </c>
-      <c r="C115" s="342"/>
-      <c r="D115" s="342"/>
-      <c r="E115" s="342"/>
-      <c r="F115" s="342"/>
+      <c r="B115" s="344" t="s">
+        <v>386</v>
+      </c>
+      <c r="C115" s="344"/>
+      <c r="D115" s="344"/>
+      <c r="E115" s="344"/>
+      <c r="F115" s="344"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="253" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -4832,22 +4977,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="343" t="s">
+      <c r="B119" s="342" t="s">
+        <v>384</v>
+      </c>
+      <c r="C119" s="342"/>
+      <c r="D119" s="342"/>
+      <c r="E119" s="342"/>
+      <c r="F119" s="342"/>
+    </row>
+    <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B120" s="339" t="s">
         <v>385</v>
       </c>
-      <c r="C119" s="343"/>
-      <c r="D119" s="343"/>
-      <c r="E119" s="343"/>
-      <c r="F119" s="343"/>
-    </row>
-    <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="341" t="s">
-        <v>386</v>
-      </c>
-      <c r="C120" s="341"/>
-      <c r="D120" s="341"/>
-      <c r="E120" s="341"/>
-      <c r="F120" s="341"/>
+      <c r="C120" s="339"/>
+      <c r="D120" s="339"/>
+      <c r="E120" s="339"/>
+      <c r="F120" s="339"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="240" t="s">
@@ -4865,7 +5010,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B123" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C123" s="256">
         <f>C19</f>
@@ -4907,33 +5052,149 @@
       </c>
       <c r="C128" s="246">
         <f>Scenarios!C82</f>
-        <v>1.292614102106344</v>
-      </c>
-    </row>
-    <row r="129" spans="2:4" x14ac:dyDescent="0.35">
+        <v>1.2897148694051519</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B129" s="82" t="s">
         <v>262</v>
       </c>
       <c r="C129" s="245">
         <f>Scenarios!C83</f>
-        <v>1.5407576206248625</v>
+        <v>1.5378583879236705</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="130" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B130" s="244" t="s">
         <v>264</v>
       </c>
       <c r="C130" s="94">
         <f>Scenarios!F83</f>
-        <v>0.31020237198993661</v>
+        <v>0.3099526368384754</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A132" s="253" t="s">
+        <v>390</v>
+      </c>
+      <c r="B132" s="36"/>
+      <c r="C132" s="36"/>
+      <c r="D132" s="36"/>
+      <c r="E132" s="36"/>
+      <c r="F132" s="36"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B134" s="346" t="s">
+        <v>392</v>
+      </c>
+      <c r="C134" s="339"/>
+      <c r="D134" s="339"/>
+      <c r="E134" s="339"/>
+      <c r="F134" s="339"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B136" s="240" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B137" s="343" t="s">
+        <v>396</v>
+      </c>
+      <c r="C137" s="343"/>
+      <c r="D137" s="343"/>
+      <c r="E137" s="343"/>
+      <c r="F137" s="343"/>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B138" s="244" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B139" s="244" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B140" s="244" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B142" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B143" s="340" t="s">
+        <v>397</v>
+      </c>
+      <c r="C143" s="340"/>
+      <c r="D143" s="340"/>
+      <c r="E143" s="340"/>
+      <c r="F143" s="340"/>
+    </row>
+    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B145" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B146" s="345" t="s">
+        <v>398</v>
+      </c>
+      <c r="C146" s="345"/>
+      <c r="D146" s="345"/>
+      <c r="E146" s="345"/>
+      <c r="F146" s="345"/>
+    </row>
+    <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B147" s="345" t="s">
+        <v>399</v>
+      </c>
+      <c r="C147" s="345"/>
+      <c r="D147" s="345"/>
+      <c r="E147" s="345"/>
+      <c r="F147" s="345"/>
+    </row>
+    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B149" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B150" s="244" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B151" s="244" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B152" s="244" t="s">
+        <v>404</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="27">
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -4950,15 +5211,9 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5405,7 +5660,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C22" s="184"/>
       <c r="D22" s="184"/>
@@ -5421,7 +5676,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C23" s="184"/>
       <c r="D23" s="184"/>
@@ -5437,7 +5692,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C24" s="184"/>
       <c r="D24" s="184"/>
@@ -8014,13 +8269,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C45" s="267" t="s">
         <v>138</v>
       </c>
       <c r="D45" s="209" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F45" s="293" t="s">
         <v>60</v>
@@ -8028,7 +8283,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C46" s="191">
         <f>G29</f>
@@ -8047,11 +8302,11 @@
       </c>
       <c r="C47" s="151">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>2.4163462338259705</v>
+        <v>2.4109265575226604</v>
       </c>
       <c r="D47" s="151">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.7842783357574834</v>
+        <v>1.7802763384942422</v>
       </c>
       <c r="F47" s="289"/>
     </row>
@@ -8181,7 +8436,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="161" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C61" s="268" t="s">
         <v>139</v>
@@ -8204,7 +8459,7 @@
         <v>1.3197490690642218E-3</v>
       </c>
       <c r="F62" s="289" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8226,7 +8481,7 @@
         <v>138</v>
       </c>
       <c r="D65" s="210" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F65" s="293" t="s">
         <v>60</v>
@@ -8293,7 +8548,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="291" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C72" s="267" t="s">
         <v>97</v>
@@ -8305,7 +8560,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C73" s="191">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8316,12 +8571,12 @@
         <v>-140154.2686468616</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="294" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C74" s="295">
         <f>-$C$66/C73</f>
@@ -8332,12 +8587,12 @@
         <v>19.012849381806323</v>
       </c>
       <c r="F74" s="289" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="82" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C75" s="299"/>
       <c r="D75" s="298">
@@ -8345,12 +8600,12 @@
         <v>840925.61188116961</v>
       </c>
       <c r="F75" s="289" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="296" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C76" s="297"/>
       <c r="D76" s="333">
@@ -8358,7 +8613,7 @@
         <v>6</v>
       </c>
       <c r="F76" s="289" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8434,7 +8689,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8445,23 +8700,23 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="D85" s="276" t="s">
         <v>300</v>
-      </c>
-      <c r="D85" s="276" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="273" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-36231.187345499995</v>
+        <v>-36149.923615680003</v>
       </c>
       <c r="D86" s="254">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-2.7173387112451604E-2</v>
+        <v>-2.7112439322705087E-2</v>
       </c>
       <c r="E86" s="275" t="str">
         <f>Market_currency</f>
@@ -8470,15 +8725,15 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="273" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>1943547.4846275782</v>
+        <v>1939188.2590748244</v>
       </c>
       <c r="D87" s="254">
         <f>C87*$H$1/Common_Shares</f>
-        <v>1.4576604312631298</v>
+        <v>1.4543910125072417</v>
       </c>
       <c r="E87" s="275" t="str">
         <f>Market_currency</f>
@@ -8491,11 +8746,11 @@
       </c>
       <c r="C88" s="191">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>242603.49337559997</v>
+        <v>242059.352645376</v>
       </c>
       <c r="D88" s="254">
         <f>C88*$H$1/Common_Shares</f>
-        <v>0.18195259728762533</v>
+        <v>0.18154449179097051</v>
       </c>
       <c r="E88" s="275" t="str">
         <f>Market_currency</f>
@@ -8504,15 +8759,15 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="82" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
-        <v>2149919.7906576782</v>
+        <v>2145097.6881045206</v>
       </c>
       <c r="D89" s="277">
         <f>SUM(D86:D88)</f>
-        <v>1.6124396414383035</v>
+        <v>1.6088230649755071</v>
       </c>
       <c r="E89" s="275" t="str">
         <f>Market_currency</f>
@@ -9375,7 +9630,7 @@
       </c>
       <c r="D17" s="59"/>
       <c r="E17" s="307" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="201"/>
@@ -9400,7 +9655,7 @@
       </c>
       <c r="D18" s="59"/>
       <c r="E18" s="307" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="202"/>
@@ -9728,7 +9983,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="306" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -9788,7 +10043,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="306" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -9912,7 +10167,7 @@
         <v>-175999.5</v>
       </c>
       <c r="E33" s="306" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G33" s="197">
         <f>Data!C41</f>
@@ -9970,7 +10225,7 @@
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="306" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="186">
@@ -10278,7 +10533,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="305" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10417,7 +10672,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C48" s="197">
         <f>BS!D75*C53</f>
@@ -10472,7 +10727,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="329" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C49" s="330">
         <f>BS!$C$66*C53</f>
@@ -10605,7 +10860,7 @@
         <v>2.7696969151119136E-2</v>
       </c>
       <c r="E53" s="305" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -10632,7 +10887,7 @@
         <v>2.9500867672578604E-2</v>
       </c>
       <c r="E54" s="305" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -10947,7 +11202,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="306" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G62" s="197">
         <f>Data!C58</f>
@@ -11508,7 +11763,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="306" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12187,16 +12442,16 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.4790697674418611E-2</v>
+        <v>5.5305164319248833E-2</v>
       </c>
       <c r="E93" s="308"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.4790697674418611E-2</v>
+        <v>5.5305164319248833E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -13218,30 +13473,30 @@
       </c>
       <c r="C120" s="181">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>4.6818238760981776E-2</v>
+        <v>4.6713229099856417E-2</v>
       </c>
       <c r="D120" s="27"/>
       <c r="E120" s="305"/>
       <c r="F120" s="27"/>
       <c r="G120" s="181">
         <f t="shared" ref="G120:Q120" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>8.1087844593670494E-2</v>
+        <v>8.0905970877197766E-2</v>
       </c>
       <c r="H120" s="181">
         <f t="shared" si="49"/>
-        <v>1.1576502373621468E-2</v>
+        <v>1.1550537180922164E-2</v>
       </c>
       <c r="I120" s="181">
         <f t="shared" si="49"/>
-        <v>6.4422017822083524E-2</v>
+        <v>6.4277524256337787E-2</v>
       </c>
       <c r="J120" s="181">
         <f t="shared" si="49"/>
-        <v>0.22659526735787519</v>
+        <v>0.2260870318311323</v>
       </c>
       <c r="K120" s="181">
         <f t="shared" si="49"/>
-        <v>0.16218033960070755</v>
+        <v>0.16181658173724731</v>
       </c>
       <c r="L120" s="181" t="str">
         <f t="shared" si="49"/>
@@ -13275,30 +13530,30 @@
       </c>
       <c r="C121" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.1775925005107801E-2</v>
+        <v>2.1931093474110992E-2</v>
       </c>
       <c r="D121" s="27"/>
       <c r="E121" s="305"/>
       <c r="F121" s="27"/>
       <c r="G121" s="79">
         <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
-        <v>3.7715276555195583E-2</v>
+        <v>3.7984023886008342E-2</v>
       </c>
       <c r="H121" s="79">
         <f t="shared" ref="H121" si="51">IF(H$4="","",H120/Market_Price)</f>
-        <v>5.3844197086611477E-3</v>
+        <v>5.4227874088836449E-3</v>
       </c>
       <c r="I121" s="79">
         <f t="shared" ref="I121" si="52">IF(I$4="","",I120/Market_Price)</f>
-        <v>2.9963729219573732E-2</v>
+        <v>3.017724143490037E-2</v>
       </c>
       <c r="J121" s="79">
         <f t="shared" ref="J121" si="53">IF(J$4="","",J120/Market_Price)</f>
-        <v>0.10539314760831404</v>
+        <v>0.10614414639959263</v>
       </c>
       <c r="K121" s="79">
         <f t="shared" ref="K121" si="54">IF(K$4="","",K120/Market_Price)</f>
-        <v>7.5432716093352351E-2</v>
+        <v>7.5970226167721741E-2</v>
       </c>
       <c r="L121" s="79" t="str">
         <f t="shared" ref="L121" si="55">IF(L$4="","",L120/Market_Price)</f>
@@ -14107,10 +14362,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="345" t="s">
+      <c r="E6" s="347" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="345"/>
+      <c r="F6" s="347"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14125,8 +14380,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="345"/>
-      <c r="F7" s="345"/>
+      <c r="E7" s="347"/>
+      <c r="F7" s="347"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14141,8 +14396,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="345"/>
-      <c r="F8" s="345"/>
+      <c r="E8" s="347"/>
+      <c r="F8" s="347"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14157,8 +14412,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="345"/>
-      <c r="F9" s="345"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -14181,7 +14436,7 @@
       </c>
       <c r="C11" s="237">
         <f>Exchange_Rate</f>
-        <v>1.0656544999999999</v>
+        <v>1.06326432</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14195,7 +14450,7 @@
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>2.1976676259505759</v>
+        <v>2.1927384287237124</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14248,7 +14503,7 @@
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>2.2310982755638769</v>
+        <v>2.2260940959950886</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15184,23 +15439,23 @@
       </c>
       <c r="B65" s="128">
         <f>C12</f>
-        <v>2.1976676259505759</v>
+        <v>2.1927384287237124</v>
       </c>
       <c r="C65" s="128">
         <f>C12</f>
-        <v>2.1976676259505759</v>
+        <v>2.1927384287237124</v>
       </c>
       <c r="D65" s="128">
         <f>C12</f>
-        <v>2.1976676259505759</v>
+        <v>2.1927384287237124</v>
       </c>
       <c r="E65" s="145">
         <f>C12</f>
-        <v>2.1976676259505759</v>
+        <v>2.1927384287237124</v>
       </c>
       <c r="F65" s="128">
         <f>C12</f>
-        <v>2.1976676259505759</v>
+        <v>2.1927384287237124</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -15211,23 +15466,23 @@
       </c>
       <c r="B66" s="128">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.1441763093761179</v>
+        <v>2.1393670890039012</v>
       </c>
       <c r="C66" s="128">
         <f t="shared" si="4"/>
-        <v>2.1441763093761179</v>
+        <v>2.1393670890039012</v>
       </c>
       <c r="D66" s="128">
         <f t="shared" si="4"/>
-        <v>2.2165501442424915</v>
+        <v>2.2115785949985618</v>
       </c>
       <c r="E66" s="128">
         <f t="shared" si="4"/>
-        <v>2.2560365673590215</v>
+        <v>2.2509764531451086</v>
       </c>
       <c r="F66" s="128">
         <f t="shared" si="4"/>
-        <v>2.2766908745516328</v>
+        <v>2.2715844343362197</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -15238,23 +15493,23 @@
       </c>
       <c r="B67" s="128">
         <f t="shared" si="4"/>
-        <v>2.103174794442491</v>
+        <v>2.098457537273136</v>
       </c>
       <c r="C67" s="128">
         <f t="shared" si="4"/>
-        <v>2.103174794442491</v>
+        <v>2.098457537273136</v>
       </c>
       <c r="D67" s="128">
         <f t="shared" si="4"/>
-        <v>2.2354500503498462</v>
+        <v>2.2304361100893351</v>
       </c>
       <c r="E67" s="128">
         <f t="shared" si="4"/>
-        <v>2.3228285645218709</v>
+        <v>2.3176186410632371</v>
       </c>
       <c r="F67" s="128">
         <f t="shared" si="4"/>
-        <v>2.3733817238368111</v>
+        <v>2.3680584135813012</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -15265,23 +15520,23 @@
       </c>
       <c r="B68" s="128">
         <f t="shared" si="4"/>
-        <v>2.0610375891427832</v>
+        <v>2.0564148424412796</v>
       </c>
       <c r="C68" s="128">
         <f t="shared" si="4"/>
-        <v>2.0610375891427832</v>
+        <v>2.0564148424412796</v>
       </c>
       <c r="D68" s="128">
         <f t="shared" si="4"/>
-        <v>2.2588439246105985</v>
+        <v>2.2537775137131404</v>
       </c>
       <c r="E68" s="128">
         <f t="shared" si="4"/>
-        <v>2.4147035335309468</v>
+        <v>2.4092875416763873</v>
       </c>
       <c r="F68" s="128">
         <f t="shared" si="4"/>
-        <v>2.5139605518949422</v>
+        <v>2.5083219342830163</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -15292,23 +15547,23 @@
       </c>
       <c r="B69" s="128">
         <f t="shared" si="4"/>
-        <v>2.0252509453511189</v>
+        <v>2.0207084653028864</v>
       </c>
       <c r="C69" s="128">
         <f t="shared" si="4"/>
-        <v>2.0252509453511189</v>
+        <v>2.0207084653028864</v>
       </c>
       <c r="D69" s="128">
         <f t="shared" si="4"/>
-        <v>2.2826785308641555</v>
+        <v>2.2775586608022351</v>
       </c>
       <c r="E69" s="128">
         <f t="shared" si="4"/>
-        <v>2.5195079002627963</v>
+        <v>2.5138568403807708</v>
       </c>
       <c r="F69" s="128">
         <f t="shared" si="4"/>
-        <v>2.6844088008577196</v>
+        <v>2.6783878811059294</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -15319,23 +15574,23 @@
       </c>
       <c r="B70" s="128">
         <f t="shared" si="4"/>
-        <v>1.9973444490014292</v>
+        <v>1.9928645610498332</v>
       </c>
       <c r="C70" s="128">
         <f t="shared" si="4"/>
-        <v>1.9973444490014292</v>
+        <v>1.9928645610498332</v>
       </c>
       <c r="D70" s="128">
         <f t="shared" si="4"/>
-        <v>2.3048460372624935</v>
+        <v>2.2996764472111741</v>
       </c>
       <c r="E70" s="128">
         <f t="shared" si="4"/>
-        <v>2.6293396900317076</v>
+        <v>2.6234422860041176</v>
       </c>
       <c r="F70" s="128">
         <f t="shared" si="4"/>
-        <v>2.8751856757933281</v>
+        <v>2.8687368583777704</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15345,23 +15600,23 @@
       </c>
       <c r="B71" s="128">
         <f t="shared" si="4"/>
-        <v>1.9765782391626112</v>
+        <v>1.9721449282014305</v>
       </c>
       <c r="C71" s="128">
         <f t="shared" si="4"/>
-        <v>1.9765782391626112</v>
+        <v>1.9721449282014305</v>
       </c>
       <c r="D71" s="128">
         <f t="shared" si="4"/>
-        <v>2.3244008615872858</v>
+        <v>2.3191874115888589</v>
       </c>
       <c r="E71" s="128">
         <f t="shared" si="4"/>
-        <v>2.7391575223299971</v>
+        <v>2.7330138054623609</v>
       </c>
       <c r="F71" s="128">
         <f t="shared" si="4"/>
-        <v>3.0797978719848289</v>
+        <v>3.0728901253580747</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15396,7 +15651,7 @@
       </c>
       <c r="E74" s="139">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>2.5139605518949422</v>
+        <v>2.5083219342830163</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
@@ -15418,7 +15673,7 @@
       </c>
       <c r="E75" s="139">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>2.3228285645218709</v>
+        <v>2.3176186410632371</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -15441,7 +15696,7 @@
       </c>
       <c r="E76" s="139">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>2.2354500503498462</v>
+        <v>2.2304361100893351</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15464,7 +15719,7 @@
       </c>
       <c r="E77" s="139">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>2.103174794442491</v>
+        <v>2.098457537273136</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -15487,7 +15742,7 @@
       </c>
       <c r="E78" s="139">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.0610375891427832</v>
+        <v>2.0564148424412796</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
@@ -15503,7 +15758,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="159" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C80" s="159" t="s">
         <v>107</v>
@@ -15575,7 +15830,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="283" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I2" s="284"/>
     </row>
@@ -15588,7 +15843,7 @@
       </c>
       <c r="I3" s="270">
         <f>-Market_Price</f>
-        <v>-2.15</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -15629,7 +15884,7 @@
         <v>1000</v>
       </c>
       <c r="E6" s="103" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F6" s="103"/>
       <c r="H6" s="282">
@@ -15637,12 +15892,12 @@
       </c>
       <c r="I6" s="270">
         <f t="shared" si="0"/>
-        <v>2.3514371684397624</v>
+        <v>2.3464272943321025</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="103" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C7" s="118">
         <f>Normalized_FCF!G8</f>
@@ -15652,11 +15907,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="347" t="str">
+      <c r="E7" s="349" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 朝云集团(6601.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="347"/>
+      <c r="F7" s="349"/>
       <c r="H7" s="282">
         <v>4</v>
       </c>
@@ -15677,8 +15932,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="347"/>
-      <c r="F8" s="347"/>
+      <c r="E8" s="349"/>
+      <c r="F8" s="349"/>
       <c r="H8" s="282">
         <v>5</v>
       </c>
@@ -15699,8 +15954,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
+      <c r="E9" s="349"/>
+      <c r="F9" s="349"/>
       <c r="H9" s="282">
         <v>6</v>
       </c>
@@ -15710,8 +15965,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="347"/>
-      <c r="F10" s="347"/>
+      <c r="E10" s="349"/>
+      <c r="F10" s="349"/>
       <c r="H10" s="282">
         <v>7</v>
       </c>
@@ -15722,10 +15977,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="163" t="s">
-        <v>283</v>
-      </c>
-      <c r="E11" s="347"/>
-      <c r="F11" s="347"/>
+        <v>282</v>
+      </c>
+      <c r="E11" s="349"/>
+      <c r="F11" s="349"/>
       <c r="H11" s="282">
         <v>8</v>
       </c>
@@ -15743,8 +15998,8 @@
         <v>-1.7248638436905273E-2</v>
       </c>
       <c r="D12" s="162"/>
-      <c r="E12" s="347"/>
-      <c r="F12" s="347"/>
+      <c r="E12" s="349"/>
+      <c r="F12" s="349"/>
       <c r="H12" s="282">
         <v>9</v>
       </c>
@@ -15761,8 +16016,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.283580450424601</v>
       </c>
-      <c r="E13" s="347"/>
-      <c r="F13" s="347"/>
+      <c r="E13" s="349"/>
+      <c r="F13" s="349"/>
       <c r="H13" s="282">
         <v>10</v>
       </c>
@@ -15779,8 +16034,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.29003821304292421</v>
       </c>
-      <c r="E14" s="347"/>
-      <c r="F14" s="347"/>
+      <c r="E14" s="349"/>
+      <c r="F14" s="349"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -15796,7 +16051,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="163" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -15806,51 +16061,51 @@
       <c r="C18" s="154">
         <v>10</v>
       </c>
-      <c r="E18" s="347" t="s">
-        <v>344</v>
-      </c>
-      <c r="F18" s="348"/>
+      <c r="E18" s="349" t="s">
+        <v>343</v>
+      </c>
+      <c r="F18" s="350"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="348"/>
-      <c r="F19" s="348"/>
+      <c r="E19" s="350"/>
+      <c r="F19" s="350"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="163" t="s">
-        <v>314</v>
-      </c>
-      <c r="E20" s="348"/>
-      <c r="F20" s="348"/>
+        <v>313</v>
+      </c>
+      <c r="E20" s="350"/>
+      <c r="F20" s="350"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="348"/>
-      <c r="F21" s="348"/>
+      <c r="E21" s="350"/>
+      <c r="F21" s="350"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
-        <v>2.1976676259505759</v>
+        <v>2.1927384287237124</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="348"/>
-      <c r="F22" s="348"/>
+      <c r="E22" s="350"/>
+      <c r="F22" s="350"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="163" t="s">
@@ -15870,8 +16125,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="167"/>
-      <c r="E25" s="346"/>
-      <c r="F25" s="346"/>
+      <c r="E25" s="348"/>
+      <c r="F25" s="348"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
@@ -15881,8 +16136,8 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="168"/>
-      <c r="E26" s="346"/>
-      <c r="F26" s="346"/>
+      <c r="E26" s="348"/>
+      <c r="F26" s="348"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
@@ -15890,14 +16145,14 @@
       </c>
       <c r="C27" s="164">
         <f>Valuation_Model!E76</f>
-        <v>2.2354500503498462</v>
+        <v>2.2304361100893351</v>
       </c>
       <c r="D27" s="164" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="346"/>
-      <c r="F27" s="346"/>
+      <c r="E27" s="348"/>
+      <c r="F27" s="348"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
@@ -15907,8 +16162,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="169"/>
-      <c r="E28" s="346"/>
-      <c r="F28" s="346"/>
+      <c r="E28" s="348"/>
+      <c r="F28" s="348"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="163" t="s">
@@ -15928,8 +16183,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="167"/>
-      <c r="E31" s="346"/>
-      <c r="F31" s="346"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
@@ -15939,8 +16194,8 @@
         <v>-0.06</v>
       </c>
       <c r="D32" s="168"/>
-      <c r="E32" s="346"/>
-      <c r="F32" s="346"/>
+      <c r="E32" s="348"/>
+      <c r="F32" s="348"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
@@ -15948,14 +16203,14 @@
       </c>
       <c r="C33" s="164">
         <f>Valuation_Model!E77</f>
-        <v>2.103174794442491</v>
+        <v>2.098457537273136</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="346"/>
-      <c r="F33" s="346"/>
+      <c r="E33" s="348"/>
+      <c r="F33" s="348"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
@@ -15965,8 +16220,8 @@
         <v>0.15</v>
       </c>
       <c r="D34" s="169"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="E34" s="348"/>
+      <c r="F34" s="348"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="163" t="s">
@@ -15986,8 +16241,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="167"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="E37" s="348"/>
+      <c r="F37" s="348"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
@@ -15997,8 +16252,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="168"/>
-      <c r="E38" s="346"/>
-      <c r="F38" s="346"/>
+      <c r="E38" s="348"/>
+      <c r="F38" s="348"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
@@ -16006,14 +16261,14 @@
       </c>
       <c r="C39" s="164">
         <f>Valuation_Model!E75</f>
-        <v>2.3228285645218709</v>
+        <v>2.3176186410632371</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="346"/>
-      <c r="F39" s="346"/>
+      <c r="E39" s="348"/>
+      <c r="F39" s="348"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
@@ -16024,8 +16279,8 @@
         <v>0.25</v>
       </c>
       <c r="D40" s="169"/>
-      <c r="E40" s="346"/>
-      <c r="F40" s="346"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
@@ -16033,7 +16288,7 @@
       </c>
       <c r="C42" s="158">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>2.2374533905067491</v>
+        <v>2.2324349569103807</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16087,8 +16342,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="167"/>
-      <c r="E49" s="346"/>
-      <c r="F49" s="346"/>
+      <c r="E49" s="348"/>
+      <c r="F49" s="348"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
@@ -16098,8 +16353,8 @@
         <v>-0.06</v>
       </c>
       <c r="D50" s="168"/>
-      <c r="E50" s="346"/>
-      <c r="F50" s="346"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
@@ -16107,14 +16362,14 @@
       </c>
       <c r="C51" s="164">
         <f>Valuation_Model!E78</f>
-        <v>2.0610375891427832</v>
+        <v>2.0564148424412796</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="346"/>
-      <c r="F51" s="346"/>
+      <c r="E51" s="348"/>
+      <c r="F51" s="348"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
@@ -16124,12 +16379,12 @@
         <v>0.1</v>
       </c>
       <c r="D52" s="169"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="E52" s="348"/>
+      <c r="F52" s="348"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="163" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E54" s="163" t="s">
         <v>151</v>
@@ -16145,8 +16400,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="167"/>
-      <c r="E55" s="346"/>
-      <c r="F55" s="346"/>
+      <c r="E55" s="348"/>
+      <c r="F55" s="348"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
@@ -16156,8 +16411,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="168"/>
-      <c r="E56" s="346"/>
-      <c r="F56" s="346"/>
+      <c r="E56" s="348"/>
+      <c r="F56" s="348"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
@@ -16165,14 +16420,14 @@
       </c>
       <c r="C57" s="164">
         <f>Valuation_Model!E74</f>
-        <v>2.5139605518949422</v>
+        <v>2.5083219342830163</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="346"/>
-      <c r="F57" s="346"/>
+      <c r="E57" s="348"/>
+      <c r="F57" s="348"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
@@ -16182,8 +16437,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="169"/>
-      <c r="E58" s="346"/>
-      <c r="F58" s="346"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
@@ -16191,14 +16446,14 @@
       </c>
       <c r="C60" s="158">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>2.2336371684397625</v>
+        <v>2.2286272943321026</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E60" s="103" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F60" s="318">
         <f>Thesis!E20</f>
@@ -16207,7 +16462,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16216,10 +16471,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="112" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E63" s="288" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -16231,7 +16486,7 @@
       </c>
       <c r="D64" s="154"/>
       <c r="E64" s="287" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16243,7 +16498,7 @@
       </c>
       <c r="D65" s="155"/>
       <c r="E65" s="287" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16252,27 +16507,27 @@
       </c>
       <c r="C66" s="164">
         <f>Valuation_Model!C18</f>
-        <v>2.2310982755638769</v>
+        <v>2.2260940959950886</v>
       </c>
       <c r="D66" s="164" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E66" s="287" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="112" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E68" s="288" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="103" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C69" s="279" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16282,19 +16537,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="103" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C70" s="279" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="287" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="103" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C71" s="279" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16304,18 +16559,18 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C72" s="278" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="E72" s="138" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F72" s="335">
         <f>BS!D89/C60</f>
-        <v>0.7218896892571961</v>
+        <v>0.72188968925719599</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16334,7 +16589,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="281" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C76" s="280">
         <f>F60</f>
@@ -16357,12 +16612,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="112" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="152" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C80" s="171">
         <f>Thesis!C123</f>
@@ -16387,7 +16642,7 @@
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
-        <v>1.292614102106344</v>
+        <v>1.2897148694051519</v>
       </c>
       <c r="D82" s="120"/>
     </row>
@@ -16397,7 +16652,7 @@
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
-        <v>1.5407576206248625</v>
+        <v>1.5378583879236705</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16408,7 +16663,7 @@
       </c>
       <c r="F83" s="335">
         <f>(1-C83/C60)</f>
-        <v>0.31020237198993661</v>
+        <v>0.3099526368384754</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16416,16 +16671,16 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="112" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="152" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16434,11 +16689,11 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="103" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>6.6927308782200656E-2</v>
+        <v>6.9712118192507999E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">
@@ -16446,7 +16701,7 @@
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E89" s="326" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F89" s="323"/>
       <c r="G89" s="2"/>
@@ -16454,30 +16709,30 @@
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E90" s="319" t="s">
+        <v>338</v>
+      </c>
+      <c r="F90" s="324" t="s">
         <v>339</v>
-      </c>
-      <c r="F90" s="324" t="s">
-        <v>340</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="322"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E91" s="320" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F91" s="324" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="322"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E92" s="321" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F92" s="325" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="322"/>

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7747590-F8FB-466A-98AB-F849DDA1215E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F87279-4546-4599-9102-EA2021B9E150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="414">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2298,15 +2298,27 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>CNY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFO/Net Income</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFO/FCFE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Net Change in Cash</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>朝云集团</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>6601.HK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CNY</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2338,7 +2350,7 @@
     <numFmt numFmtId="192" formatCode="0.0\x"/>
     <numFmt numFmtId="193" formatCode="0\x"/>
   </numFmts>
-  <fonts count="58" x14ac:knownFonts="1">
+  <fonts count="59" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2771,6 +2783,13 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -2978,7 +2997,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="351">
+  <cellXfs count="353">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3682,6 +3701,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4044,15 +4067,15 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="C5" s="48" t="s">
-        <v>407</v>
+      <c r="C5" s="339" t="s">
+        <v>411</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4060,7 +4083,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4105,7 +4128,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>2840.0003550000001</v>
+        <v>2640.0003299999998</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4115,13 +4138,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="339" t="s">
+      <c r="B12" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C12" s="339"/>
-      <c r="D12" s="339"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="339"/>
+      <c r="C12" s="341"/>
+      <c r="D12" s="341"/>
+      <c r="E12" s="341"/>
+      <c r="F12" s="341"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4145,7 +4168,7 @@
         <v>360</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4155,7 +4178,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.06326432</v>
+        <v>1.06349396</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4168,7 +4191,7 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4188,7 +4211,7 @@
       </c>
       <c r="C20" s="258">
         <f>C129</f>
-        <v>1.5378583879236705</v>
+        <v>1.5381369358980914</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>318</v>
@@ -4203,7 +4226,7 @@
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
-        <v>6.9712118192507999E-2</v>
+        <v>9.7593325788780882E-2</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4223,22 +4246,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="339" t="s">
+      <c r="B25" s="341" t="s">
         <v>376</v>
       </c>
-      <c r="C25" s="339"/>
-      <c r="D25" s="339"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="339"/>
+      <c r="C25" s="341"/>
+      <c r="D25" s="341"/>
+      <c r="E25" s="341"/>
+      <c r="F25" s="341"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
+      <c r="B26" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="C26" s="343"/>
+      <c r="D26" s="343"/>
+      <c r="E26" s="343"/>
+      <c r="F26" s="343"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
@@ -4250,13 +4273,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="340" t="s">
+      <c r="B29" s="342" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="340"/>
-      <c r="D29" s="340"/>
-      <c r="E29" s="340"/>
-      <c r="F29" s="340"/>
+      <c r="C29" s="342"/>
+      <c r="D29" s="342"/>
+      <c r="E29" s="342"/>
+      <c r="F29" s="342"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4276,13 +4299,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="340" t="s">
+      <c r="B32" s="342" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="340"/>
-      <c r="D32" s="340"/>
-      <c r="E32" s="340"/>
-      <c r="F32" s="340"/>
+      <c r="C32" s="342"/>
+      <c r="D32" s="342"/>
+      <c r="E32" s="342"/>
+      <c r="F32" s="342"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4311,13 +4334,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="340" t="s">
+      <c r="B36" s="342" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="340"/>
-      <c r="D36" s="340"/>
-      <c r="E36" s="340"/>
-      <c r="F36" s="340"/>
+      <c r="C36" s="342"/>
+      <c r="D36" s="342"/>
+      <c r="E36" s="342"/>
+      <c r="F36" s="342"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4333,13 +4356,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="340" t="s">
+      <c r="B39" s="342" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="340"/>
-      <c r="D39" s="340"/>
-      <c r="E39" s="340"/>
-      <c r="F39" s="340"/>
+      <c r="C39" s="342"/>
+      <c r="D39" s="342"/>
+      <c r="E39" s="342"/>
+      <c r="F39" s="342"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4403,13 +4426,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="340" t="s">
+      <c r="B47" s="342" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="340"/>
-      <c r="D47" s="340"/>
-      <c r="E47" s="340"/>
-      <c r="F47" s="340"/>
+      <c r="C47" s="342"/>
+      <c r="D47" s="342"/>
+      <c r="E47" s="342"/>
+      <c r="F47" s="342"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4425,13 +4448,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="340" t="s">
+      <c r="B50" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C50" s="343"/>
-      <c r="D50" s="343"/>
-      <c r="E50" s="343"/>
-      <c r="F50" s="343"/>
+      <c r="C50" s="345"/>
+      <c r="D50" s="345"/>
+      <c r="E50" s="345"/>
+      <c r="F50" s="345"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4447,22 +4470,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="339" t="s">
+      <c r="B53" s="341" t="s">
         <v>356</v>
       </c>
-      <c r="C53" s="339"/>
-      <c r="D53" s="339"/>
-      <c r="E53" s="339"/>
-      <c r="F53" s="339"/>
+      <c r="C53" s="341"/>
+      <c r="D53" s="341"/>
+      <c r="E53" s="341"/>
+      <c r="F53" s="341"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="339" t="s">
+      <c r="B54" s="341" t="s">
         <v>377</v>
       </c>
-      <c r="C54" s="339"/>
-      <c r="D54" s="339"/>
-      <c r="E54" s="339"/>
-      <c r="F54" s="339"/>
+      <c r="C54" s="341"/>
+      <c r="D54" s="341"/>
+      <c r="E54" s="341"/>
+      <c r="F54" s="341"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4495,8 +4518,8 @@
         <v>406</v>
       </c>
       <c r="C58" s="94">
-        <f>Normalized_FCF!C121</f>
-        <v>2.1931093474110992E-2</v>
+        <f>Normalized_FCF!C125</f>
+        <v>2.359763538126574E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4505,7 +4528,7 @@
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
-        <v>5.5305164319248833E-2</v>
+        <v>5.9494949494949496E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4523,22 +4546,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="339" t="s">
+      <c r="B63" s="341" t="s">
         <v>378</v>
       </c>
-      <c r="C63" s="339"/>
-      <c r="D63" s="339"/>
-      <c r="E63" s="339"/>
-      <c r="F63" s="339"/>
+      <c r="C63" s="341"/>
+      <c r="D63" s="341"/>
+      <c r="E63" s="341"/>
+      <c r="F63" s="341"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="343" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="343"/>
+      <c r="D64" s="343"/>
+      <c r="E64" s="343"/>
+      <c r="F64" s="343"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
@@ -4596,22 +4619,22 @@
       <c r="C72" s="125"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="339" t="s">
+      <c r="B73" s="341" t="s">
         <v>379</v>
       </c>
-      <c r="C73" s="339"/>
-      <c r="D73" s="339"/>
-      <c r="E73" s="339"/>
-      <c r="F73" s="339"/>
+      <c r="C73" s="341"/>
+      <c r="D73" s="341"/>
+      <c r="E73" s="341"/>
+      <c r="F73" s="341"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="339" t="s">
+      <c r="B74" s="341" t="s">
         <v>380</v>
       </c>
-      <c r="C74" s="339"/>
-      <c r="D74" s="339"/>
-      <c r="E74" s="339"/>
-      <c r="F74" s="339"/>
+      <c r="C74" s="341"/>
+      <c r="D74" s="341"/>
+      <c r="E74" s="341"/>
+      <c r="F74" s="341"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4627,7 +4650,7 @@
       </c>
       <c r="C77" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.58391536374820519</v>
+        <v>0.58404147568632703</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4648,13 +4671,13 @@
       <c r="A80" s="239"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="339" t="s">
+      <c r="B81" s="341" t="s">
         <v>381</v>
       </c>
-      <c r="C81" s="339"/>
-      <c r="D81" s="339"/>
-      <c r="E81" s="339"/>
-      <c r="F81" s="339"/>
+      <c r="C81" s="341"/>
+      <c r="D81" s="341"/>
+      <c r="E81" s="341"/>
+      <c r="F81" s="341"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4667,13 +4690,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="339" t="s">
+      <c r="B85" s="341" t="s">
         <v>357</v>
       </c>
-      <c r="C85" s="339"/>
-      <c r="D85" s="339"/>
-      <c r="E85" s="339"/>
-      <c r="F85" s="339"/>
+      <c r="C85" s="341"/>
+      <c r="D85" s="341"/>
+      <c r="E85" s="341"/>
+      <c r="F85" s="341"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4694,7 +4717,7 @@
       </c>
       <c r="C87" s="254">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>2.7112439322705087E-2</v>
+        <v>2.7118294969743127E-2</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4738,7 +4761,7 @@
       </c>
       <c r="C92" s="254">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.4543910125072417</v>
+        <v>1.4547051266422031</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4769,7 +4792,7 @@
       </c>
       <c r="C96" s="254">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.18154449179097051</v>
+        <v>0.18158370111673336</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4777,13 +4800,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="339" t="s">
+      <c r="B98" s="341" t="s">
         <v>382</v>
       </c>
-      <c r="C98" s="339"/>
-      <c r="D98" s="339"/>
-      <c r="E98" s="339"/>
-      <c r="F98" s="339"/>
+      <c r="C98" s="341"/>
+      <c r="D98" s="341"/>
+      <c r="E98" s="341"/>
+      <c r="F98" s="341"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4791,7 +4814,7 @@
       </c>
       <c r="C100" s="254">
         <f>Valuation_Model!C12</f>
-        <v>2.1927384287237124</v>
+        <v>2.1932120084755207</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4809,13 +4832,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="340" t="s">
+      <c r="B104" s="342" t="s">
         <v>383</v>
       </c>
-      <c r="C104" s="340"/>
-      <c r="D104" s="340"/>
-      <c r="E104" s="340"/>
-      <c r="F104" s="340"/>
+      <c r="C104" s="342"/>
+      <c r="D104" s="342"/>
+      <c r="E104" s="342"/>
+      <c r="F104" s="342"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="266" t="s">
@@ -4950,7 +4973,7 @@
       </c>
       <c r="C113" s="247">
         <f>Scenarios!C60</f>
-        <v>2.2286272943321026</v>
+        <v>2.2291086252319019</v>
       </c>
       <c r="D113" s="242" t="str">
         <f>Market_currency</f>
@@ -4958,13 +4981,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="344" t="s">
+      <c r="B115" s="346" t="s">
         <v>386</v>
       </c>
-      <c r="C115" s="344"/>
-      <c r="D115" s="344"/>
-      <c r="E115" s="344"/>
-      <c r="F115" s="344"/>
+      <c r="C115" s="346"/>
+      <c r="D115" s="346"/>
+      <c r="E115" s="346"/>
+      <c r="F115" s="346"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="253" t="s">
@@ -4977,22 +5000,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="342" t="s">
+      <c r="B119" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C119" s="342"/>
-      <c r="D119" s="342"/>
-      <c r="E119" s="342"/>
-      <c r="F119" s="342"/>
+      <c r="C119" s="344"/>
+      <c r="D119" s="344"/>
+      <c r="E119" s="344"/>
+      <c r="F119" s="344"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="339" t="s">
+      <c r="B120" s="341" t="s">
         <v>385</v>
       </c>
-      <c r="C120" s="339"/>
-      <c r="D120" s="339"/>
-      <c r="E120" s="339"/>
-      <c r="F120" s="339"/>
+      <c r="C120" s="341"/>
+      <c r="D120" s="341"/>
+      <c r="E120" s="341"/>
+      <c r="F120" s="341"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="240" t="s">
@@ -5052,7 +5075,7 @@
       </c>
       <c r="C128" s="246">
         <f>Scenarios!C82</f>
-        <v>1.2897148694051519</v>
+        <v>1.2899934173795728</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5061,7 +5084,7 @@
       </c>
       <c r="C129" s="245">
         <f>Scenarios!C83</f>
-        <v>1.5378583879236705</v>
+        <v>1.5381369358980914</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5074,7 +5097,7 @@
       </c>
       <c r="C130" s="94">
         <f>Scenarios!F83</f>
-        <v>0.3099526368384754</v>
+        <v>0.30997667924860606</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -5088,13 +5111,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="346" t="s">
+      <c r="B134" s="348" t="s">
         <v>392</v>
       </c>
-      <c r="C134" s="339"/>
-      <c r="D134" s="339"/>
-      <c r="E134" s="339"/>
-      <c r="F134" s="339"/>
+      <c r="C134" s="341"/>
+      <c r="D134" s="341"/>
+      <c r="E134" s="341"/>
+      <c r="F134" s="341"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="240" t="s">
@@ -5102,13 +5125,13 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B137" s="343" t="s">
+      <c r="B137" s="345" t="s">
         <v>396</v>
       </c>
-      <c r="C137" s="343"/>
-      <c r="D137" s="343"/>
-      <c r="E137" s="343"/>
-      <c r="F137" s="343"/>
+      <c r="C137" s="345"/>
+      <c r="D137" s="345"/>
+      <c r="E137" s="345"/>
+      <c r="F137" s="345"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B138" s="244" t="s">
@@ -5131,13 +5154,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="340" t="s">
+      <c r="B143" s="342" t="s">
         <v>397</v>
       </c>
-      <c r="C143" s="340"/>
-      <c r="D143" s="340"/>
-      <c r="E143" s="340"/>
-      <c r="F143" s="340"/>
+      <c r="C143" s="342"/>
+      <c r="D143" s="342"/>
+      <c r="E143" s="342"/>
+      <c r="F143" s="342"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5145,22 +5168,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="345" t="s">
+      <c r="B146" s="347" t="s">
         <v>398</v>
       </c>
-      <c r="C146" s="345"/>
-      <c r="D146" s="345"/>
-      <c r="E146" s="345"/>
-      <c r="F146" s="345"/>
+      <c r="C146" s="347"/>
+      <c r="D146" s="347"/>
+      <c r="E146" s="347"/>
+      <c r="F146" s="347"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="345" t="s">
+      <c r="B147" s="347" t="s">
         <v>399</v>
       </c>
-      <c r="C147" s="345"/>
-      <c r="D147" s="345"/>
-      <c r="E147" s="345"/>
-      <c r="F147" s="345"/>
+      <c r="C147" s="347"/>
+      <c r="D147" s="347"/>
+      <c r="E147" s="347"/>
+      <c r="F147" s="347"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5213,7 +5236,7 @@
     <mergeCell ref="B63:F63"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5225,7 +5248,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="87" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5234,7 +5257,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:M79"/>
+  <dimension ref="B1:M80"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
@@ -5450,7 +5473,7 @@
       <c r="B10" s="40" t="s">
         <v>169</v>
       </c>
-      <c r="C10" s="193"/>
+      <c r="C10" s="184"/>
       <c r="D10" s="184"/>
       <c r="E10" s="184"/>
       <c r="F10" s="184"/>
@@ -5735,7 +5758,7 @@
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="186"/>
+      <c r="C28" s="184"/>
       <c r="D28" s="184"/>
       <c r="E28" s="184"/>
       <c r="F28" s="184"/>
@@ -5751,7 +5774,7 @@
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="186"/>
+      <c r="C29" s="184"/>
       <c r="D29" s="184"/>
       <c r="E29" s="184"/>
       <c r="F29" s="184"/>
@@ -6947,440 +6970,455 @@
       </c>
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B64" s="24" t="s">
+      <c r="B64" s="27" t="s">
+        <v>410</v>
+      </c>
+      <c r="C64" s="186">
+        <f>IF(C$4="","",C22+C23+C24)</f>
+        <v>0</v>
+      </c>
+      <c r="D64" s="186">
+        <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
+        <v>0</v>
+      </c>
+      <c r="E64" s="186">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="F64" s="186">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="G64" s="186">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="H64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="I64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="J64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="K64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="L64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="M64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="C64" s="75">
-        <f t="shared" ref="C64:M64" si="32">IF(C$4="","",C25)</f>
+      <c r="C65" s="75">
+        <f t="shared" ref="C65:M65" si="33">IF(C$4="","",C25)</f>
         <v>0.1178</v>
       </c>
-      <c r="D64" s="75">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="E64" s="75">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="F64" s="75">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="G64" s="75">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="H64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="I64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="J64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="K64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="L64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B66" s="93" t="s">
+      <c r="D65" s="75">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="E65" s="75">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="F65" s="75">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="G65" s="75">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="H65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="I65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="J65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="K65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="L65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="M65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B67" s="93" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B67" s="1" t="str">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
       </c>
-      <c r="C67" s="94">
-        <f t="shared" ref="C67:M67" si="33">IF(D$36="","",C36/D36-1)</f>
+      <c r="C68" s="94">
+        <f t="shared" ref="C68:M68" si="34">IF(D$36="","",C36/D36-1)</f>
         <v>0.11678595474472542</v>
       </c>
-      <c r="D67" s="94">
-        <f t="shared" si="33"/>
+      <c r="D68" s="94">
+        <f t="shared" si="34"/>
         <v>-0.18230094898304672</v>
       </c>
-      <c r="E67" s="94">
-        <f t="shared" si="33"/>
+      <c r="E68" s="94">
+        <f t="shared" si="34"/>
         <v>3.9363653347464389E-2</v>
       </c>
-      <c r="F67" s="94">
-        <f t="shared" si="33"/>
+      <c r="F68" s="94">
+        <f t="shared" si="34"/>
         <v>0.2304116952266948</v>
       </c>
-      <c r="G67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="H67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="I67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="J67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="K67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="L67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="M67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B68" s="82" t="str">
+      <c r="G68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="H68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="I68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="J68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="K68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="L68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="M68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B69" s="82" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
       </c>
-      <c r="C68" s="104">
-        <f t="shared" ref="C68:M68" si="34">IF(D$36="","",C37/D37-1)</f>
+      <c r="C69" s="104">
+        <f t="shared" ref="C69:M69" si="35">IF(D$36="","",C37/D37-1)</f>
         <v>6.15937742527779E-2</v>
       </c>
-      <c r="D68" s="104">
-        <f t="shared" si="34"/>
+      <c r="D69" s="104">
+        <f t="shared" si="35"/>
         <v>-0.13900650992990948</v>
       </c>
-      <c r="E68" s="104">
-        <f t="shared" si="34"/>
+      <c r="E69" s="104">
+        <f t="shared" si="35"/>
         <v>2.3092587111753993E-2</v>
       </c>
-      <c r="F68" s="104">
-        <f t="shared" si="34"/>
+      <c r="F69" s="104">
+        <f t="shared" si="35"/>
         <v>0.22465930352170016</v>
       </c>
-      <c r="G68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="H68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="I68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="J68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="K68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="L68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="M68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B69" s="1" t="str">
+      <c r="G69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="H69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="I69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="J69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="K69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="L69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="M69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B70" s="1" t="str">
         <f>B58</f>
         <v>Other Non-operating Income</v>
       </c>
-      <c r="C69" s="94">
-        <f t="shared" ref="C69:M69" si="35">IF(D$36="","",C38/D38-1)</f>
+      <c r="C70" s="94">
+        <f t="shared" ref="C70:M70" si="36">IF(D$36="","",C38/D38-1)</f>
         <v>0.19436157865155468</v>
       </c>
-      <c r="D69" s="94">
-        <f t="shared" si="35"/>
+      <c r="D70" s="94">
+        <f t="shared" si="36"/>
         <v>-0.23627871063439609</v>
       </c>
-      <c r="E69" s="94">
-        <f t="shared" si="35"/>
+      <c r="E70" s="94">
+        <f t="shared" si="36"/>
         <v>6.0389290340999269E-2</v>
       </c>
-      <c r="F69" s="94">
-        <f t="shared" si="35"/>
+      <c r="F70" s="94">
+        <f t="shared" si="36"/>
         <v>0.23792551595372258</v>
       </c>
-      <c r="G69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="H69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="I69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="J69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="K69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="L69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="M69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B70" s="82" t="str">
+      <c r="G70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="H70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="I70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="J70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="K70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="L70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="M70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B71" s="82" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
       </c>
-      <c r="C70" s="104">
-        <f t="shared" ref="C70:M70" si="36">IF(D$36="","",C39/D39-1)</f>
+      <c r="C71" s="104">
+        <f t="shared" ref="C71:M71" si="37">IF(D$36="","",C39/D39-1)</f>
         <v>2.3235010397508526E-2</v>
       </c>
-      <c r="D70" s="104">
-        <f t="shared" si="36"/>
+      <c r="D71" s="104">
+        <f t="shared" si="37"/>
         <v>-0.15056635336480528</v>
       </c>
-      <c r="E70" s="104">
-        <f t="shared" si="36"/>
+      <c r="E71" s="104">
+        <f t="shared" si="37"/>
         <v>0.54484133067606932</v>
       </c>
-      <c r="F70" s="104">
-        <f t="shared" si="36"/>
+      <c r="F71" s="104">
+        <f t="shared" si="37"/>
         <v>0.15118633128531189</v>
       </c>
-      <c r="G70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="H70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="I70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="J70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="K70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="L70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="M70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B71" s="1" t="str">
+      <c r="G71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="H71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="I71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="J71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="K71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="L71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="M71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B72" s="1" t="str">
         <f>B48</f>
         <v>Non-controling Interests</v>
       </c>
-      <c r="C71" s="94" t="e">
-        <f>IF(D$36="","",C64/D64-1)</f>
+      <c r="C72" s="94" t="e">
+        <f>IF(D$36="","",C65/D65-1)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D71" s="94" t="e">
-        <f t="shared" ref="D71:M71" si="37">IF(E$36="","",D64/E64-1)</f>
+      <c r="D72" s="94" t="e">
+        <f t="shared" ref="D72:M72" si="38">IF(E$36="","",D65/E65-1)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E71" s="94" t="e">
-        <f t="shared" si="37"/>
+      <c r="E72" s="94" t="e">
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F71" s="94" t="e">
-        <f t="shared" si="37"/>
+      <c r="F72" s="94" t="e">
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="H71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="I71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="J71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="K71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="L71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="M71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-    </row>
-    <row r="73" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="B73" s="36" t="s">
+      <c r="G72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="H72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="I72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="J72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="K72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="L72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="M72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="B74" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="C73" s="37"/>
-      <c r="D73" s="37"/>
-      <c r="E73" s="37"/>
-      <c r="F73" s="37"/>
-      <c r="G73" s="37"/>
-      <c r="H73" s="37"/>
-      <c r="I73" s="37"/>
-      <c r="J73" s="37"/>
-      <c r="K73" s="37"/>
-      <c r="L73" s="37"/>
-      <c r="M73" s="37"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B74" s="16" t="s">
+      <c r="C74" s="37"/>
+      <c r="D74" s="37"/>
+      <c r="E74" s="37"/>
+      <c r="F74" s="37"/>
+      <c r="G74" s="37"/>
+      <c r="H74" s="37"/>
+      <c r="I74" s="37"/>
+      <c r="J74" s="37"/>
+      <c r="K74" s="37"/>
+      <c r="L74" s="37"/>
+      <c r="M74" s="37"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C74" s="9"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B75" s="26" t="s">
+      <c r="C75" s="9"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C75" s="78">
-        <f>IF(C$4="","",C78+C79)</f>
+      <c r="C76" s="78">
+        <f>IF(C$4="","",C79+C80)</f>
         <v>3670169</v>
       </c>
-      <c r="D75" s="78">
-        <f t="shared" ref="D75:M75" si="38">IF(D$4="","",D78+D79)</f>
+      <c r="D76" s="78">
+        <f t="shared" ref="D76:M76" si="39">IF(D$4="","",D79+D80)</f>
         <v>3559477</v>
       </c>
-      <c r="E75" s="78">
-        <f t="shared" si="38"/>
+      <c r="E76" s="78">
+        <f t="shared" si="39"/>
         <v>3413258</v>
       </c>
-      <c r="F75" s="78">
-        <f t="shared" si="38"/>
+      <c r="F76" s="78">
+        <f t="shared" si="39"/>
         <v>1603329</v>
       </c>
-      <c r="G75" s="78">
-        <f t="shared" si="38"/>
+      <c r="G76" s="78">
+        <f t="shared" si="39"/>
         <v>1218998</v>
       </c>
-      <c r="H75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="I75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="J75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="K75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="L75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="M75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B76" s="95" t="s">
-        <v>87</v>
-      </c>
-      <c r="C76" s="74">
-        <f t="shared" ref="C76:H77" si="39">IF(C$4="","",C28)</f>
-        <v>0</v>
-      </c>
-      <c r="D76" s="74">
+      <c r="H76" s="78" t="str">
         <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="E76" s="74">
+        <v/>
+      </c>
+      <c r="I76" s="78" t="str">
         <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="F76" s="74">
+        <v/>
+      </c>
+      <c r="J76" s="78" t="str">
         <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="G76" s="74">
+        <v/>
+      </c>
+      <c r="K76" s="78" t="str">
         <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="H76" s="74" t="str">
+        <v/>
+      </c>
+      <c r="L76" s="78" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="I76" s="96"/>
-      <c r="J76" s="96"/>
-      <c r="K76" s="96"/>
-      <c r="L76" s="96"/>
-      <c r="M76" s="96"/>
+      <c r="M76" s="78" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
     </row>
     <row r="77" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B77" s="95" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C77" s="74">
-        <f t="shared" si="39"/>
+        <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
         <v>0</v>
       </c>
       <c r="D77" s="74">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="E77" s="74">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="F77" s="74">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="G77" s="74">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="H77" s="74" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="I77" s="96"/>
@@ -7390,77 +7428,62 @@
       <c r="M77" s="96"/>
     </row>
     <row r="78" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B78" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C78" s="58">
-        <f t="shared" ref="C78:M78" si="40">IF(C$4="","",C30)</f>
-        <v>642877</v>
-      </c>
-      <c r="D78" s="58">
+      <c r="B78" s="95" t="s">
+        <v>88</v>
+      </c>
+      <c r="C78" s="74">
         <f t="shared" si="40"/>
-        <v>734909</v>
-      </c>
-      <c r="E78" s="58">
+        <v>0</v>
+      </c>
+      <c r="D78" s="74">
         <f t="shared" si="40"/>
-        <v>677999</v>
-      </c>
-      <c r="F78" s="58">
+        <v>0</v>
+      </c>
+      <c r="E78" s="74">
         <f t="shared" si="40"/>
-        <v>1352795</v>
-      </c>
-      <c r="G78" s="58">
+        <v>0</v>
+      </c>
+      <c r="F78" s="74">
         <f t="shared" si="40"/>
-        <v>1205068</v>
-      </c>
-      <c r="H78" s="58" t="str">
+        <v>0</v>
+      </c>
+      <c r="G78" s="74">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="I78" s="58" t="str">
+        <v>0</v>
+      </c>
+      <c r="H78" s="74" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="J78" s="58" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="K78" s="58" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="L78" s="58" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="M78" s="58" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
+      <c r="I78" s="96"/>
+      <c r="J78" s="96"/>
+      <c r="K78" s="96"/>
+      <c r="L78" s="96"/>
+      <c r="M78" s="96"/>
     </row>
     <row r="79" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B79" s="26" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C79" s="58">
-        <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C31)</f>
-        <v>3027292</v>
+        <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
+        <v>642877</v>
       </c>
       <c r="D79" s="58">
         <f t="shared" si="41"/>
-        <v>2824568</v>
+        <v>734909</v>
       </c>
       <c r="E79" s="58">
         <f t="shared" si="41"/>
-        <v>2735259</v>
+        <v>677999</v>
       </c>
       <c r="F79" s="58">
         <f t="shared" si="41"/>
-        <v>250534</v>
+        <v>1352795</v>
       </c>
       <c r="G79" s="58">
         <f t="shared" si="41"/>
-        <v>13930</v>
+        <v>1205068</v>
       </c>
       <c r="H79" s="58" t="str">
         <f t="shared" si="41"/>
@@ -7487,9 +7510,58 @@
         <v/>
       </c>
     </row>
+    <row r="80" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B80" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C80" s="58">
+        <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
+        <v>3027292</v>
+      </c>
+      <c r="D80" s="58">
+        <f t="shared" si="42"/>
+        <v>2824568</v>
+      </c>
+      <c r="E80" s="58">
+        <f t="shared" si="42"/>
+        <v>2735259</v>
+      </c>
+      <c r="F80" s="58">
+        <f t="shared" si="42"/>
+        <v>250534</v>
+      </c>
+      <c r="G80" s="58">
+        <f t="shared" si="42"/>
+        <v>13930</v>
+      </c>
+      <c r="H80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="I80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="J80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="K80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="L80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="M80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C76:H77 C78:M79">
+  <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C77:H78 C79:M80">
     <cfRule type="expression" dxfId="5" priority="4">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
@@ -7499,7 +7571,7 @@
       <formula>ISBLANK(C28)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C36:M37 C61:M64">
+  <conditionalFormatting sqref="C36:M37 C61:M65">
     <cfRule type="expression" dxfId="3" priority="2">
       <formula>ISBLANK(C36)</formula>
     </cfRule>
@@ -8302,11 +8374,11 @@
       </c>
       <c r="C47" s="151">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>2.4109265575226604</v>
+        <v>2.4114472607610322</v>
       </c>
       <c r="D47" s="151">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.7802763384942422</v>
+        <v>1.780660836168698</v>
       </c>
       <c r="F47" s="289"/>
     </row>
@@ -8712,11 +8784,11 @@
       </c>
       <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-36149.923615680003</v>
+        <v>-36157.731146040001</v>
       </c>
       <c r="D86" s="254">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-2.7112439322705087E-2</v>
+        <v>-2.7118294969743127E-2</v>
       </c>
       <c r="E86" s="275" t="str">
         <f>Market_currency</f>
@@ -8729,11 +8801,11 @@
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>1939188.2590748244</v>
+        <v>1939607.0779737919</v>
       </c>
       <c r="D87" s="254">
         <f>C87*$H$1/Common_Shares</f>
-        <v>1.4543910125072417</v>
+        <v>1.4547051266422031</v>
       </c>
       <c r="E87" s="275" t="str">
         <f>Market_currency</f>
@@ -8746,11 +8818,11 @@
       </c>
       <c r="C88" s="191">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>242059.352645376</v>
+        <v>242111.63175292799</v>
       </c>
       <c r="D88" s="254">
         <f>C88*$H$1/Common_Shares</f>
-        <v>0.18154449179097051</v>
+        <v>0.18158370111673336</v>
       </c>
       <c r="E88" s="275" t="str">
         <f>Market_currency</f>
@@ -8763,11 +8835,11 @@
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
-        <v>2145097.6881045206</v>
+        <v>2145560.9785806797</v>
       </c>
       <c r="D89" s="277">
         <f>SUM(D86:D88)</f>
-        <v>1.6088230649755071</v>
+        <v>1.6091705327891934</v>
       </c>
       <c r="E89" s="275" t="str">
         <f>Market_currency</f>
@@ -8787,7 +8859,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q804"/>
+  <dimension ref="A1:Q808"/>
   <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
@@ -12284,47 +12356,47 @@
       </c>
       <c r="E90" s="308"/>
       <c r="G90" s="116">
-        <f>Data!C64</f>
+        <f>Data!C65</f>
         <v>0.1178</v>
       </c>
       <c r="H90" s="116">
-        <f>Data!D64</f>
+        <f>Data!D65</f>
         <v>0</v>
       </c>
       <c r="I90" s="116">
-        <f>Data!E64</f>
+        <f>Data!E65</f>
         <v>0</v>
       </c>
       <c r="J90" s="116">
-        <f>Data!F64</f>
+        <f>Data!F65</f>
         <v>0</v>
       </c>
       <c r="K90" s="116">
-        <f>Data!G64</f>
+        <f>Data!G65</f>
         <v>0</v>
       </c>
       <c r="L90" s="116" t="str">
-        <f>Data!H64</f>
+        <f>Data!H65</f>
         <v/>
       </c>
       <c r="M90" s="116" t="str">
-        <f>Data!I64</f>
+        <f>Data!I65</f>
         <v/>
       </c>
       <c r="N90" s="116" t="str">
-        <f>Data!J64</f>
+        <f>Data!J65</f>
         <v/>
       </c>
       <c r="O90" s="116" t="str">
-        <f>Data!K64</f>
+        <f>Data!K65</f>
         <v/>
       </c>
       <c r="P90" s="116" t="str">
-        <f>Data!L64</f>
+        <f>Data!L65</f>
         <v/>
       </c>
       <c r="Q90" s="116" t="str">
-        <f>Data!M64</f>
+        <f>Data!M65</f>
         <v/>
       </c>
     </row>
@@ -12446,12 +12518,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.5305164319248833E-2</v>
+        <v>5.9494949494949496E-2</v>
       </c>
       <c r="E93" s="308"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.5305164319248833E-2</v>
+        <v>5.9494949494949496E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -12739,47 +12811,47 @@
       <c r="E102" s="310"/>
       <c r="F102" s="91"/>
       <c r="G102" s="188">
-        <f>IF(G$4="","",Data!D76)</f>
+        <f>IF(G$4="","",Data!D77)</f>
         <v>0</v>
       </c>
       <c r="H102" s="188">
-        <f>IF(H$4="","",Data!E76)</f>
+        <f>IF(H$4="","",Data!E77)</f>
         <v>0</v>
       </c>
       <c r="I102" s="188">
-        <f>IF(I$4="","",Data!F76)</f>
+        <f>IF(I$4="","",Data!F77)</f>
         <v>0</v>
       </c>
       <c r="J102" s="188">
-        <f>IF(J$4="","",Data!G76)</f>
+        <f>IF(J$4="","",Data!G77)</f>
         <v>0</v>
       </c>
       <c r="K102" s="188" t="str">
-        <f>IF(K$4="","",Data!H76)</f>
+        <f>IF(K$4="","",Data!H77)</f>
         <v/>
       </c>
       <c r="L102" s="188" t="str">
-        <f>IF(L$4="","",Data!I76)</f>
+        <f>IF(L$4="","",Data!I77)</f>
         <v/>
       </c>
       <c r="M102" s="188" t="str">
-        <f>IF(M$4="","",Data!J76)</f>
+        <f>IF(M$4="","",Data!J77)</f>
         <v/>
       </c>
       <c r="N102" s="188" t="str">
-        <f>IF(N$4="","",Data!K76)</f>
+        <f>IF(N$4="","",Data!K77)</f>
         <v/>
       </c>
       <c r="O102" s="188" t="str">
-        <f>IF(O$4="","",Data!L76)</f>
+        <f>IF(O$4="","",Data!L77)</f>
         <v/>
       </c>
       <c r="P102" s="188" t="str">
-        <f>IF(P$4="","",Data!M76)</f>
+        <f>IF(P$4="","",Data!M77)</f>
         <v/>
       </c>
       <c r="Q102" s="188" t="str">
-        <f>IF(Q$4="","",Data!N76)</f>
+        <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
     </row>
@@ -12796,47 +12868,47 @@
       <c r="E103" s="310"/>
       <c r="F103" s="91"/>
       <c r="G103" s="188">
-        <f>IF(G$4="","",Data!D77)</f>
+        <f>IF(G$4="","",Data!D78)</f>
         <v>0</v>
       </c>
       <c r="H103" s="188">
-        <f>IF(H$4="","",Data!E77)</f>
+        <f>IF(H$4="","",Data!E78)</f>
         <v>0</v>
       </c>
       <c r="I103" s="188">
-        <f>IF(I$4="","",Data!F77)</f>
+        <f>IF(I$4="","",Data!F78)</f>
         <v>0</v>
       </c>
       <c r="J103" s="188">
-        <f>IF(J$4="","",Data!G77)</f>
+        <f>IF(J$4="","",Data!G78)</f>
         <v>0</v>
       </c>
       <c r="K103" s="188" t="str">
-        <f>IF(K$4="","",Data!H77)</f>
+        <f>IF(K$4="","",Data!H78)</f>
         <v/>
       </c>
       <c r="L103" s="188" t="str">
-        <f>IF(L$4="","",Data!I77)</f>
+        <f>IF(L$4="","",Data!I78)</f>
         <v/>
       </c>
       <c r="M103" s="188" t="str">
-        <f>IF(M$4="","",Data!J77)</f>
+        <f>IF(M$4="","",Data!J78)</f>
         <v/>
       </c>
       <c r="N103" s="188" t="str">
-        <f>IF(N$4="","",Data!K77)</f>
+        <f>IF(N$4="","",Data!K78)</f>
         <v/>
       </c>
       <c r="O103" s="188" t="str">
-        <f>IF(O$4="","",Data!L77)</f>
+        <f>IF(O$4="","",Data!L78)</f>
         <v/>
       </c>
       <c r="P103" s="188" t="str">
-        <f>IF(P$4="","",Data!M77)</f>
+        <f>IF(P$4="","",Data!M78)</f>
         <v/>
       </c>
       <c r="Q103" s="188" t="str">
-        <f>IF(Q$4="","",Data!N77)</f>
+        <f>IF(Q$4="","",Data!N78)</f>
         <v/>
       </c>
     </row>
@@ -12853,47 +12925,47 @@
       <c r="E104" s="309"/>
       <c r="F104" s="26"/>
       <c r="G104" s="186">
-        <f>Data!C78</f>
+        <f>Data!C79</f>
         <v>642877</v>
       </c>
       <c r="H104" s="186">
-        <f>Data!D78</f>
+        <f>Data!D79</f>
         <v>734909</v>
       </c>
       <c r="I104" s="186">
-        <f>Data!E78</f>
+        <f>Data!E79</f>
         <v>677999</v>
       </c>
       <c r="J104" s="186">
-        <f>Data!F78</f>
+        <f>Data!F79</f>
         <v>1352795</v>
       </c>
       <c r="K104" s="186">
-        <f>Data!G78</f>
+        <f>Data!G79</f>
         <v>1205068</v>
       </c>
       <c r="L104" s="186" t="str">
-        <f>Data!H78</f>
+        <f>Data!H79</f>
         <v/>
       </c>
       <c r="M104" s="186" t="str">
-        <f>Data!I78</f>
+        <f>Data!I79</f>
         <v/>
       </c>
       <c r="N104" s="186" t="str">
-        <f>Data!J78</f>
+        <f>Data!J79</f>
         <v/>
       </c>
       <c r="O104" s="186" t="str">
-        <f>Data!K78</f>
+        <f>Data!K79</f>
         <v/>
       </c>
       <c r="P104" s="186" t="str">
-        <f>Data!L78</f>
+        <f>Data!L79</f>
         <v/>
       </c>
       <c r="Q104" s="186" t="str">
-        <f>Data!M78</f>
+        <f>Data!M79</f>
         <v/>
       </c>
     </row>
@@ -12910,47 +12982,47 @@
       <c r="E105" s="309"/>
       <c r="F105" s="26"/>
       <c r="G105" s="186">
-        <f>Data!C79</f>
+        <f>Data!C80</f>
         <v>3027292</v>
       </c>
       <c r="H105" s="186">
-        <f>Data!D79</f>
+        <f>Data!D80</f>
         <v>2824568</v>
       </c>
       <c r="I105" s="186">
-        <f>Data!E79</f>
+        <f>Data!E80</f>
         <v>2735259</v>
       </c>
       <c r="J105" s="186">
-        <f>Data!F79</f>
+        <f>Data!F80</f>
         <v>250534</v>
       </c>
       <c r="K105" s="186">
-        <f>Data!G79</f>
+        <f>Data!G80</f>
         <v>13930</v>
       </c>
       <c r="L105" s="186" t="str">
-        <f>Data!H79</f>
+        <f>Data!H80</f>
         <v/>
       </c>
       <c r="M105" s="186" t="str">
-        <f>Data!I79</f>
+        <f>Data!I80</f>
         <v/>
       </c>
       <c r="N105" s="186" t="str">
-        <f>Data!J79</f>
+        <f>Data!J80</f>
         <v/>
       </c>
       <c r="O105" s="186" t="str">
-        <f>Data!K79</f>
+        <f>Data!K80</f>
         <v/>
       </c>
       <c r="P105" s="186" t="str">
-        <f>Data!L79</f>
+        <f>Data!L80</f>
         <v/>
       </c>
       <c r="Q105" s="186" t="str">
-        <f>Data!M79</f>
+        <f>Data!M80</f>
         <v/>
       </c>
     </row>
@@ -13128,462 +13200,573 @@
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="10"/>
-      <c r="B112" s="93" t="s">
-        <v>38</v>
-      </c>
-      <c r="C112" s="55"/>
-      <c r="D112" s="55"/>
-      <c r="E112" s="311"/>
-      <c r="F112" s="55"/>
-      <c r="G112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*G114*(1/#REF!)=G116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="H112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*H114*(1/#REF!)=H116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="I112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*I114*(1/#REF!)=I116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="J112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*J114*(1/#REF!)=J116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="K112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*K114*(1/#REF!)=K116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="L112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*L114*(1/#REF!)=L116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="M112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*M114*(1/#REF!)=M116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="N112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*N114*(1/#REF!)=N116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="O112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*O114*(1/#REF!)=O116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="P112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*P114*(1/#REF!)=P116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="Q112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*Q114*(1/#REF!)=Q116,"","Error"),"")</f>
-        <v/>
-      </c>
+      <c r="B112" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="E112" s="308"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
-      <c r="B113" s="7" t="s">
+      <c r="B113" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C113" s="173"/>
+      <c r="E113" s="308"/>
+      <c r="G113" s="340">
+        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
+        <v>0</v>
+      </c>
+      <c r="H113" s="340">
+        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
+        <v>0</v>
+      </c>
+      <c r="I113" s="340">
+        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
+        <v>0</v>
+      </c>
+      <c r="J113" s="340">
+        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
+        <v>0</v>
+      </c>
+      <c r="K113" s="340" t="e">
+        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L113" s="340" t="str">
+        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
+        <v/>
+      </c>
+      <c r="M113" s="340" t="str">
+        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
+        <v/>
+      </c>
+      <c r="N113" s="340" t="str">
+        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
+        <v/>
+      </c>
+      <c r="O113" s="340" t="str">
+        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
+        <v/>
+      </c>
+      <c r="P113" s="340" t="str">
+        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
+        <v/>
+      </c>
+      <c r="Q113" s="340" t="str">
+        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="10"/>
+      <c r="B114" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C114" s="173"/>
+      <c r="E114" s="308"/>
+      <c r="G114" s="340">
+        <f>IF(G$4="","",Data!C$22/G19)</f>
+        <v>0</v>
+      </c>
+      <c r="H114" s="340">
+        <f>IF(H$4="","",Data!D$22/H19)</f>
+        <v>0</v>
+      </c>
+      <c r="I114" s="340">
+        <f>IF(I$4="","",Data!E$22/I19)</f>
+        <v>0</v>
+      </c>
+      <c r="J114" s="340">
+        <f>IF(J$4="","",Data!F$22/J19)</f>
+        <v>0</v>
+      </c>
+      <c r="K114" s="340">
+        <f>IF(K$4="","",Data!G$22/K19)</f>
+        <v>0</v>
+      </c>
+      <c r="L114" s="340" t="str">
+        <f>IF(L$4="","",Data!H$22/L19)</f>
+        <v/>
+      </c>
+      <c r="M114" s="340" t="str">
+        <f>IF(M$4="","",Data!I$22/M19)</f>
+        <v/>
+      </c>
+      <c r="N114" s="340" t="str">
+        <f>IF(N$4="","",Data!J$22/N19)</f>
+        <v/>
+      </c>
+      <c r="O114" s="340" t="str">
+        <f>IF(O$4="","",Data!K$22/O19)</f>
+        <v/>
+      </c>
+      <c r="P114" s="340" t="str">
+        <f>IF(P$4="","",Data!L$22/P19)</f>
+        <v/>
+      </c>
+      <c r="Q114" s="340" t="str">
+        <f>IF(Q$4="","",Data!M$22/Q19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A115" s="10"/>
+      <c r="E115" s="308"/>
+    </row>
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="10"/>
+      <c r="B116" s="93" t="s">
+        <v>38</v>
+      </c>
+      <c r="C116" s="55"/>
+      <c r="D116" s="55"/>
+      <c r="E116" s="311"/>
+      <c r="F116" s="55"/>
+      <c r="G116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="H116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*H118*(1/#REF!)=H120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="I116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*I118*(1/#REF!)=I120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="J116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*J118*(1/#REF!)=J120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="K116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*K118*(1/#REF!)=K120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="L116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*L118*(1/#REF!)=L120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="M116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*M118*(1/#REF!)=M120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="N116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*N118*(1/#REF!)=N120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="O116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*O118*(1/#REF!)=O120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="P116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*P118*(1/#REF!)=P120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="Q116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*Q118*(1/#REF!)=Q120,"","Error"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="10"/>
+      <c r="B117" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="C113" s="23">
+      <c r="C117" s="23">
         <f>C81</f>
         <v>5.10871587621268E-2</v>
       </c>
-      <c r="E113" s="308"/>
-      <c r="G113" s="23">
-        <f t="shared" ref="G113:Q113" si="45">G81</f>
+      <c r="E117" s="308"/>
+      <c r="G117" s="23">
+        <f t="shared" ref="G117:Q117" si="45">G81</f>
         <v>9.1672113030672311E-2</v>
       </c>
-      <c r="H113" s="23">
+      <c r="H117" s="23">
         <f t="shared" si="45"/>
         <v>2.4986467996109377E-2</v>
       </c>
-      <c r="I113" s="23">
+      <c r="I117" s="23">
         <f t="shared" si="45"/>
         <v>4.5560692465394535E-2</v>
       </c>
-      <c r="J113" s="23">
+      <c r="J117" s="23">
         <f t="shared" si="45"/>
         <v>0.16656139632489186</v>
       </c>
-      <c r="K113" s="23">
+      <c r="K117" s="23">
         <f t="shared" si="45"/>
         <v>0.14668042983890439</v>
       </c>
-      <c r="L113" s="23" t="str">
+      <c r="L117" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="M113" s="23" t="str">
+      <c r="M117" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="N113" s="23" t="str">
+      <c r="N117" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="O113" s="23" t="str">
+      <c r="O117" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="P113" s="23" t="str">
+      <c r="P117" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="Q113" s="23" t="str">
+      <c r="Q117" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B114" s="7" t="s">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B118" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C114" s="42">
+      <c r="C118" s="42">
         <f>C4/C101</f>
         <v>0.43142078743512902</v>
       </c>
-      <c r="E114" s="308"/>
-      <c r="G114" s="42">
-        <f t="shared" ref="G114:Q114" si="46">IF(G4="","",G4/G101)</f>
+      <c r="E118" s="308"/>
+      <c r="G118" s="42">
+        <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>0.44019362596109335</v>
       </c>
-      <c r="H114" s="42">
+      <c r="H118" s="42">
         <f t="shared" si="46"/>
         <v>0.40641869578030704</v>
       </c>
-      <c r="I114" s="42">
+      <c r="I118" s="42">
         <f t="shared" si="46"/>
         <v>0.51831915430946029</v>
       </c>
-      <c r="J114" s="42">
+      <c r="J118" s="42">
         <f t="shared" si="46"/>
         <v>1.0616373807247297</v>
       </c>
-      <c r="K114" s="42">
+      <c r="K118" s="42">
         <f t="shared" si="46"/>
         <v>1.1348681458049972</v>
       </c>
-      <c r="L114" s="42" t="str">
+      <c r="L118" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="M114" s="42" t="str">
+      <c r="M118" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="N114" s="42" t="str">
+      <c r="N118" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="O114" s="42" t="str">
+      <c r="O118" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="P114" s="42" t="str">
+      <c r="P118" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="Q114" s="42" t="str">
+      <c r="Q118" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="7" t="s">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B119" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C115" s="15">
+      <c r="C119" s="15">
         <f>C101/C105</f>
         <v>1.2123604198075375</v>
       </c>
-      <c r="D115" s="11"/>
-      <c r="E115" s="312"/>
-      <c r="F115" s="11"/>
-      <c r="G115" s="15">
-        <f t="shared" ref="G115:Q115" si="47">IF(G$4="","",G101/G105)</f>
+      <c r="D119" s="11"/>
+      <c r="E119" s="312"/>
+      <c r="F119" s="11"/>
+      <c r="G119" s="15">
+        <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
         <v>1.2123604198075375</v>
       </c>
-      <c r="H115" s="15">
+      <c r="H119" s="15">
         <f t="shared" si="47"/>
         <v>1.2601845662770377</v>
       </c>
-      <c r="I115" s="15">
+      <c r="I119" s="15">
         <f t="shared" si="47"/>
         <v>1.2478737845300938</v>
       </c>
-      <c r="J115" s="15">
+      <c r="J119" s="15">
         <f t="shared" si="47"/>
         <v>6.3996463553848981</v>
       </c>
-      <c r="K115" s="15">
+      <c r="K119" s="15">
         <f t="shared" si="47"/>
         <v>87.508829863603736</v>
       </c>
-      <c r="L115" s="15" t="str">
+      <c r="L119" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="M115" s="15" t="str">
+      <c r="M119" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="N115" s="15" t="str">
+      <c r="N119" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="O115" s="15" t="str">
+      <c r="O119" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="P115" s="15" t="str">
+      <c r="P119" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="Q115" s="15" t="str">
+      <c r="Q119" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="10"/>
-      <c r="B116" s="71" t="s">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A120" s="10"/>
+      <c r="B120" s="71" t="s">
         <v>224</v>
       </c>
-      <c r="C116" s="105">
+      <c r="C120" s="105">
         <f>C8/C105</f>
         <v>1.9358113633458775E-2</v>
       </c>
-      <c r="D116" s="106"/>
-      <c r="E116" s="311"/>
-      <c r="F116" s="106"/>
-      <c r="G116" s="105">
-        <f t="shared" ref="G116:Q116" si="48">IF(G$4="","",G8/G105)</f>
+      <c r="D120" s="106"/>
+      <c r="E120" s="311"/>
+      <c r="F120" s="106"/>
+      <c r="G120" s="105">
+        <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
         <v>3.4735334417690791E-2</v>
       </c>
-      <c r="H116" s="105">
+      <c r="H120" s="105">
         <f t="shared" si="48"/>
         <v>7.7604787705588959E-4</v>
       </c>
-      <c r="I116" s="105">
+      <c r="I120" s="105">
         <f t="shared" si="48"/>
         <v>2.9992040973085183E-2</v>
       </c>
-      <c r="J116" s="105">
+      <c r="J120" s="105">
         <f t="shared" si="48"/>
         <v>1.1414498630924346</v>
       </c>
-      <c r="K116" s="105">
+      <c r="K120" s="105">
         <f t="shared" si="48"/>
         <v>14.588442211055277</v>
       </c>
-      <c r="L116" s="105" t="str">
+      <c r="L120" s="105" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
-      <c r="M116" s="105" t="str">
+      <c r="M120" s="105" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
-      <c r="N116" s="105" t="str">
+      <c r="N120" s="105" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
-      <c r="O116" s="105" t="str">
+      <c r="O120" s="105" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
-      <c r="P116" s="105" t="str">
+      <c r="P120" s="105" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
-      <c r="Q116" s="105" t="str">
+      <c r="Q120" s="105" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="10"/>
-      <c r="B117" s="27"/>
-      <c r="C117" s="63"/>
-      <c r="D117" s="27"/>
-      <c r="E117" s="68"/>
-      <c r="F117" s="27"/>
-      <c r="G117" s="12"/>
-      <c r="H117" s="12"/>
-      <c r="I117" s="12"/>
-      <c r="J117" s="12"/>
-      <c r="K117" s="12"/>
-      <c r="L117" s="12"/>
-      <c r="M117" s="12"/>
-      <c r="N117" s="12"/>
-      <c r="O117" s="12"/>
-      <c r="P117" s="12"/>
-      <c r="Q117" s="12"/>
-    </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A118" s="10"/>
-      <c r="B118" s="54" t="s">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="10"/>
+      <c r="B121" s="27"/>
+      <c r="C121" s="63"/>
+      <c r="D121" s="27"/>
+      <c r="E121" s="68"/>
+      <c r="F121" s="27"/>
+      <c r="G121" s="12"/>
+      <c r="H121" s="12"/>
+      <c r="I121" s="12"/>
+      <c r="J121" s="12"/>
+      <c r="K121" s="12"/>
+      <c r="L121" s="12"/>
+      <c r="M121" s="12"/>
+      <c r="N121" s="12"/>
+      <c r="O121" s="12"/>
+      <c r="P121" s="12"/>
+      <c r="Q121" s="12"/>
+    </row>
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A122" s="10"/>
+      <c r="B122" s="54" t="s">
         <v>225</v>
       </c>
-      <c r="C118" s="54"/>
-      <c r="D118" s="56"/>
-      <c r="E118" s="67" t="s">
+      <c r="C122" s="54"/>
+      <c r="D122" s="56"/>
+      <c r="E122" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="F118" s="56"/>
-      <c r="G118" s="37"/>
-      <c r="H118" s="37"/>
-      <c r="I118" s="37"/>
-      <c r="J118" s="37"/>
-      <c r="K118" s="37"/>
-      <c r="L118" s="37"/>
-      <c r="M118" s="37"/>
-      <c r="N118" s="37"/>
-      <c r="O118" s="37"/>
-      <c r="P118" s="37"/>
-      <c r="Q118" s="37"/>
-    </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="10"/>
-      <c r="B119" s="182" t="s">
+      <c r="F122" s="56"/>
+      <c r="G122" s="37"/>
+      <c r="H122" s="37"/>
+      <c r="I122" s="37"/>
+      <c r="J122" s="37"/>
+      <c r="K122" s="37"/>
+      <c r="L122" s="37"/>
+      <c r="M122" s="37"/>
+      <c r="N122" s="37"/>
+      <c r="O122" s="37"/>
+      <c r="P122" s="37"/>
+      <c r="Q122" s="37"/>
+    </row>
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A123" s="10"/>
+      <c r="B123" s="182" t="s">
         <v>172</v>
       </c>
-      <c r="C119" s="183"/>
-      <c r="D119" s="27"/>
-      <c r="E119" s="305"/>
-      <c r="F119" s="27"/>
-      <c r="G119" s="12"/>
-      <c r="H119" s="12"/>
-      <c r="I119" s="12"/>
-      <c r="J119" s="12"/>
-      <c r="K119" s="12"/>
-      <c r="L119" s="12"/>
-      <c r="M119" s="12"/>
-      <c r="N119" s="12"/>
-      <c r="O119" s="12"/>
-      <c r="P119" s="12"/>
-      <c r="Q119" s="12"/>
-    </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="10"/>
-      <c r="B120" s="27" t="str">
+      <c r="C123" s="183"/>
+      <c r="D123" s="27"/>
+      <c r="E123" s="305"/>
+      <c r="F123" s="27"/>
+      <c r="G123" s="12"/>
+      <c r="H123" s="12"/>
+      <c r="I123" s="12"/>
+      <c r="J123" s="12"/>
+      <c r="K123" s="12"/>
+      <c r="L123" s="12"/>
+      <c r="M123" s="12"/>
+      <c r="N123" s="12"/>
+      <c r="O123" s="12"/>
+      <c r="P123" s="12"/>
+      <c r="Q123" s="12"/>
+    </row>
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="10"/>
+      <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
         <v>FCFE per share (HKD)</v>
       </c>
-      <c r="C120" s="181">
+      <c r="C124" s="181">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>4.6713229099856417E-2</v>
-      </c>
-      <c r="D120" s="27"/>
-      <c r="E120" s="305"/>
-      <c r="F120" s="27"/>
-      <c r="G120" s="181">
-        <f t="shared" ref="G120:Q120" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>8.0905970877197766E-2</v>
-      </c>
-      <c r="H120" s="181">
+        <v>4.672331805490617E-2</v>
+      </c>
+      <c r="D124" s="27"/>
+      <c r="E124" s="305"/>
+      <c r="F124" s="27"/>
+      <c r="G124" s="181">
+        <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
+        <v>8.0923444657520077E-2</v>
+      </c>
+      <c r="H124" s="181">
         <f t="shared" si="49"/>
-        <v>1.1550537180922164E-2</v>
-      </c>
-      <c r="I120" s="181">
+        <v>1.1553031824359673E-2</v>
+      </c>
+      <c r="I124" s="181">
         <f t="shared" si="49"/>
-        <v>6.4277524256337787E-2</v>
-      </c>
-      <c r="J120" s="181">
+        <v>6.4291406684622618E-2</v>
+      </c>
+      <c r="J124" s="181">
         <f t="shared" si="49"/>
-        <v>0.2260870318311323</v>
-      </c>
-      <c r="K120" s="181">
+        <v>0.22613586129433641</v>
+      </c>
+      <c r="K124" s="181">
         <f t="shared" si="49"/>
-        <v>0.16181658173724731</v>
-      </c>
-      <c r="L120" s="181" t="str">
+        <v>0.16185153030001873</v>
+      </c>
+      <c r="L124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="M120" s="181" t="str">
+      <c r="M124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="N120" s="181" t="str">
+      <c r="N124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="O120" s="181" t="str">
+      <c r="O124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="P120" s="181" t="str">
+      <c r="P124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="Q120" s="181" t="str">
+      <c r="Q124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="10"/>
-      <c r="B121" s="27" t="s">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="10"/>
+      <c r="B125" s="27" t="s">
         <v>272</v>
       </c>
-      <c r="C121" s="79">
+      <c r="C125" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.1931093474110992E-2</v>
-      </c>
-      <c r="D121" s="27"/>
-      <c r="E121" s="305"/>
-      <c r="F121" s="27"/>
-      <c r="G121" s="79">
-        <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
-        <v>3.7984023886008342E-2</v>
-      </c>
-      <c r="H121" s="79">
-        <f t="shared" ref="H121" si="51">IF(H$4="","",H120/Market_Price)</f>
-        <v>5.4227874088836449E-3</v>
-      </c>
-      <c r="I121" s="79">
-        <f t="shared" ref="I121" si="52">IF(I$4="","",I120/Market_Price)</f>
-        <v>3.017724143490037E-2</v>
-      </c>
-      <c r="J121" s="79">
-        <f t="shared" ref="J121" si="53">IF(J$4="","",J120/Market_Price)</f>
-        <v>0.10614414639959263</v>
-      </c>
-      <c r="K121" s="79">
-        <f t="shared" ref="K121" si="54">IF(K$4="","",K120/Market_Price)</f>
-        <v>7.5970226167721741E-2</v>
-      </c>
-      <c r="L121" s="79" t="str">
-        <f t="shared" ref="L121" si="55">IF(L$4="","",L120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="M121" s="79" t="str">
-        <f t="shared" ref="M121" si="56">IF(M$4="","",M120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="N121" s="79" t="str">
-        <f t="shared" ref="N121" si="57">IF(N$4="","",N120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="O121" s="79" t="str">
-        <f t="shared" ref="O121" si="58">IF(O$4="","",O120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="P121" s="79" t="str">
-        <f t="shared" ref="P121" si="59">IF(P$4="","",P120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="Q121" s="79" t="str">
-        <f t="shared" ref="Q121" si="60">IF(Q$4="","",Q120/Market_Price)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+        <v>2.359763538126574E-2</v>
+      </c>
+      <c r="D125" s="27"/>
+      <c r="E125" s="305"/>
+      <c r="F125" s="27"/>
+      <c r="G125" s="79">
+        <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
+        <v>4.0870426594707111E-2</v>
+      </c>
+      <c r="H125" s="79">
+        <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
+        <v>5.8348645577574101E-3</v>
+      </c>
+      <c r="I125" s="79">
+        <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
+        <v>3.2470407416476069E-2</v>
+      </c>
+      <c r="J125" s="79">
+        <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
+        <v>0.11421003095673556</v>
+      </c>
+      <c r="K125" s="79">
+        <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
+        <v>8.1743197121221578E-2</v>
+      </c>
+      <c r="L125" s="79" t="str">
+        <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="M125" s="79" t="str">
+        <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="N125" s="79" t="str">
+        <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="O125" s="79" t="str">
+        <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="P125" s="79" t="str">
+        <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="Q125" s="79" t="str">
+        <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
+        <v/>
+      </c>
+    </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -14263,6 +14446,10 @@
     <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -14362,10 +14549,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="347" t="s">
+      <c r="E6" s="349" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="347"/>
+      <c r="F6" s="349"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14380,8 +14567,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="347"/>
-      <c r="F7" s="347"/>
+      <c r="E7" s="349"/>
+      <c r="F7" s="349"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14396,8 +14583,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="347"/>
-      <c r="F8" s="347"/>
+      <c r="E8" s="349"/>
+      <c r="F8" s="349"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14412,8 +14599,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
+      <c r="E9" s="349"/>
+      <c r="F9" s="349"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -14436,7 +14623,7 @@
       </c>
       <c r="C11" s="237">
         <f>Exchange_Rate</f>
-        <v>1.06326432</v>
+        <v>1.06349396</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14450,7 +14637,7 @@
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>2.1927384287237124</v>
+        <v>2.1932120084755207</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14503,7 +14690,7 @@
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>2.2260940959950886</v>
+        <v>2.2265748797838305</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15439,23 +15626,23 @@
       </c>
       <c r="B65" s="128">
         <f>C12</f>
-        <v>2.1927384287237124</v>
+        <v>2.1932120084755207</v>
       </c>
       <c r="C65" s="128">
         <f>C12</f>
-        <v>2.1927384287237124</v>
+        <v>2.1932120084755207</v>
       </c>
       <c r="D65" s="128">
         <f>C12</f>
-        <v>2.1927384287237124</v>
+        <v>2.1932120084755207</v>
       </c>
       <c r="E65" s="145">
         <f>C12</f>
-        <v>2.1927384287237124</v>
+        <v>2.1932120084755207</v>
       </c>
       <c r="F65" s="128">
         <f>C12</f>
-        <v>2.1927384287237124</v>
+        <v>2.1932120084755207</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -15466,23 +15653,23 @@
       </c>
       <c r="B66" s="128">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.1393670890039012</v>
+        <v>2.1398291418058975</v>
       </c>
       <c r="C66" s="128">
         <f t="shared" si="4"/>
-        <v>2.1393670890039012</v>
+        <v>2.1398291418058975</v>
       </c>
       <c r="D66" s="128">
         <f t="shared" si="4"/>
-        <v>2.2115785949985618</v>
+        <v>2.2120562437816558</v>
       </c>
       <c r="E66" s="128">
         <f t="shared" si="4"/>
-        <v>2.2509764531451086</v>
+        <v>2.25146261093577</v>
       </c>
       <c r="F66" s="128">
         <f t="shared" si="4"/>
-        <v>2.2715844343362197</v>
+        <v>2.2720750429644685</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -15493,23 +15680,23 @@
       </c>
       <c r="B67" s="128">
         <f t="shared" si="4"/>
-        <v>2.098457537273136</v>
+        <v>2.0989107545774273</v>
       </c>
       <c r="C67" s="128">
         <f t="shared" si="4"/>
-        <v>2.098457537273136</v>
+        <v>2.0989107545774273</v>
       </c>
       <c r="D67" s="128">
         <f t="shared" si="4"/>
-        <v>2.2304361100893351</v>
+        <v>2.2309178316506499</v>
       </c>
       <c r="E67" s="128">
         <f t="shared" si="4"/>
-        <v>2.3176186410632371</v>
+        <v>2.3181191919937278</v>
       </c>
       <c r="F67" s="128">
         <f t="shared" si="4"/>
-        <v>2.3680584135813012</v>
+        <v>2.3685698583122732</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -15520,23 +15707,23 @@
       </c>
       <c r="B68" s="128">
         <f t="shared" si="4"/>
-        <v>2.0564148424412796</v>
+        <v>2.056858979515698</v>
       </c>
       <c r="C68" s="128">
         <f t="shared" si="4"/>
-        <v>2.0564148424412796</v>
+        <v>2.056858979515698</v>
       </c>
       <c r="D68" s="128">
         <f t="shared" si="4"/>
-        <v>2.2537775137131404</v>
+        <v>2.2542642764667788</v>
       </c>
       <c r="E68" s="128">
         <f t="shared" si="4"/>
-        <v>2.4092875416763873</v>
+        <v>2.4098078909260172</v>
       </c>
       <c r="F68" s="128">
         <f t="shared" si="4"/>
-        <v>2.5083219342830163</v>
+        <v>2.5088636726242299</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -15547,23 +15734,23 @@
       </c>
       <c r="B69" s="128">
         <f t="shared" si="4"/>
-        <v>2.0207084653028864</v>
+        <v>2.0211448906425162</v>
       </c>
       <c r="C69" s="128">
         <f t="shared" si="4"/>
-        <v>2.0207084653028864</v>
+        <v>2.0211448906425162</v>
       </c>
       <c r="D69" s="128">
         <f t="shared" si="4"/>
-        <v>2.2775586608022351</v>
+        <v>2.2780505597224079</v>
       </c>
       <c r="E69" s="128">
         <f t="shared" si="4"/>
-        <v>2.5138568403807708</v>
+        <v>2.5143997741310775</v>
       </c>
       <c r="F69" s="128">
         <f t="shared" si="4"/>
-        <v>2.6783878811059294</v>
+        <v>2.6789663496780873</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -15574,23 +15761,23 @@
       </c>
       <c r="B70" s="128">
         <f t="shared" si="4"/>
-        <v>1.9928645610498332</v>
+        <v>1.9932949727632625</v>
       </c>
       <c r="C70" s="128">
         <f t="shared" si="4"/>
-        <v>1.9928645610498332</v>
+        <v>1.9932949727632625</v>
       </c>
       <c r="D70" s="128">
         <f t="shared" si="4"/>
-        <v>2.2996764472111741</v>
+        <v>2.3001731230512301</v>
       </c>
       <c r="E70" s="128">
         <f t="shared" si="4"/>
-        <v>2.6234422860041176</v>
+        <v>2.6240088876244538</v>
       </c>
       <c r="F70" s="128">
         <f t="shared" si="4"/>
-        <v>2.8687368583777704</v>
+        <v>2.8693564378367684</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15600,23 +15787,23 @@
       </c>
       <c r="B71" s="128">
         <f t="shared" si="4"/>
-        <v>1.9721449282014305</v>
+        <v>1.9725708649631495</v>
       </c>
       <c r="C71" s="128">
         <f t="shared" si="4"/>
-        <v>1.9721449282014305</v>
+        <v>1.9725708649631495</v>
       </c>
       <c r="D71" s="128">
         <f t="shared" si="4"/>
-        <v>2.3191874115888589</v>
+        <v>2.3196883013367597</v>
       </c>
       <c r="E71" s="128">
         <f t="shared" si="4"/>
-        <v>2.7330138054623609</v>
+        <v>2.7336040719450039</v>
       </c>
       <c r="F71" s="128">
         <f t="shared" si="4"/>
-        <v>3.0728901253580747</v>
+        <v>3.073553797104708</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15651,7 +15838,7 @@
       </c>
       <c r="E74" s="139">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>2.5083219342830163</v>
+        <v>2.5088636726242299</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
@@ -15673,7 +15860,7 @@
       </c>
       <c r="E75" s="139">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>2.3176186410632371</v>
+        <v>2.3181191919937278</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -15696,7 +15883,7 @@
       </c>
       <c r="E76" s="139">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>2.2304361100893351</v>
+        <v>2.2309178316506499</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15719,7 +15906,7 @@
       </c>
       <c r="E77" s="139">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>2.098457537273136</v>
+        <v>2.0989107545774273</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -15742,7 +15929,7 @@
       </c>
       <c r="E78" s="139">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.0564148424412796</v>
+        <v>2.056858979515698</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
@@ -15843,7 +16030,7 @@
       </c>
       <c r="I3" s="270">
         <f>-Market_Price</f>
-        <v>-2.13</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -15892,7 +16079,7 @@
       </c>
       <c r="I6" s="270">
         <f t="shared" si="0"/>
-        <v>2.3464272943321025</v>
+        <v>2.3469086252319018</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15907,11 +16094,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="349" t="str">
+      <c r="E7" s="351" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 朝云集团(6601.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="349"/>
+      <c r="F7" s="351"/>
       <c r="H7" s="282">
         <v>4</v>
       </c>
@@ -15932,8 +16119,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="349"/>
-      <c r="F8" s="349"/>
+      <c r="E8" s="351"/>
+      <c r="F8" s="351"/>
       <c r="H8" s="282">
         <v>5</v>
       </c>
@@ -15954,8 +16141,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="349"/>
-      <c r="F9" s="349"/>
+      <c r="E9" s="351"/>
+      <c r="F9" s="351"/>
       <c r="H9" s="282">
         <v>6</v>
       </c>
@@ -15965,8 +16152,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="349"/>
-      <c r="F10" s="349"/>
+      <c r="E10" s="351"/>
+      <c r="F10" s="351"/>
       <c r="H10" s="282">
         <v>7</v>
       </c>
@@ -15979,8 +16166,8 @@
       <c r="B11" s="163" t="s">
         <v>282</v>
       </c>
-      <c r="E11" s="349"/>
-      <c r="F11" s="349"/>
+      <c r="E11" s="351"/>
+      <c r="F11" s="351"/>
       <c r="H11" s="282">
         <v>8</v>
       </c>
@@ -15998,8 +16185,8 @@
         <v>-1.7248638436905273E-2</v>
       </c>
       <c r="D12" s="162"/>
-      <c r="E12" s="349"/>
-      <c r="F12" s="349"/>
+      <c r="E12" s="351"/>
+      <c r="F12" s="351"/>
       <c r="H12" s="282">
         <v>9</v>
       </c>
@@ -16016,8 +16203,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.283580450424601</v>
       </c>
-      <c r="E13" s="349"/>
-      <c r="F13" s="349"/>
+      <c r="E13" s="351"/>
+      <c r="F13" s="351"/>
       <c r="H13" s="282">
         <v>10</v>
       </c>
@@ -16034,8 +16221,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.29003821304292421</v>
       </c>
-      <c r="E14" s="349"/>
-      <c r="F14" s="349"/>
+      <c r="E14" s="351"/>
+      <c r="F14" s="351"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -16061,21 +16248,21 @@
       <c r="C18" s="154">
         <v>10</v>
       </c>
-      <c r="E18" s="349" t="s">
+      <c r="E18" s="351" t="s">
         <v>343</v>
       </c>
-      <c r="F18" s="350"/>
+      <c r="F18" s="352"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="350"/>
-      <c r="F19" s="350"/>
+      <c r="E19" s="352"/>
+      <c r="F19" s="352"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="163" t="s">
         <v>313</v>
       </c>
-      <c r="E20" s="350"/>
-      <c r="F20" s="350"/>
+      <c r="E20" s="352"/>
+      <c r="F20" s="352"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
@@ -16083,14 +16270,14 @@
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="350"/>
-      <c r="F21" s="350"/>
+      <c r="E21" s="352"/>
+      <c r="F21" s="352"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
@@ -16098,14 +16285,14 @@
       </c>
       <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
-        <v>2.1927384287237124</v>
+        <v>2.1932120084755207</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="350"/>
-      <c r="F22" s="350"/>
+      <c r="E22" s="352"/>
+      <c r="F22" s="352"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="163" t="s">
@@ -16125,8 +16312,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="167"/>
-      <c r="E25" s="348"/>
-      <c r="F25" s="348"/>
+      <c r="E25" s="350"/>
+      <c r="F25" s="350"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
@@ -16136,8 +16323,8 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="168"/>
-      <c r="E26" s="348"/>
-      <c r="F26" s="348"/>
+      <c r="E26" s="350"/>
+      <c r="F26" s="350"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
@@ -16145,14 +16332,14 @@
       </c>
       <c r="C27" s="164">
         <f>Valuation_Model!E76</f>
-        <v>2.2304361100893351</v>
+        <v>2.2309178316506499</v>
       </c>
       <c r="D27" s="164" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="348"/>
-      <c r="F27" s="348"/>
+      <c r="E27" s="350"/>
+      <c r="F27" s="350"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
@@ -16162,8 +16349,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="169"/>
-      <c r="E28" s="348"/>
-      <c r="F28" s="348"/>
+      <c r="E28" s="350"/>
+      <c r="F28" s="350"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="163" t="s">
@@ -16183,8 +16370,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="167"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="E31" s="350"/>
+      <c r="F31" s="350"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
@@ -16194,8 +16381,8 @@
         <v>-0.06</v>
       </c>
       <c r="D32" s="168"/>
-      <c r="E32" s="348"/>
-      <c r="F32" s="348"/>
+      <c r="E32" s="350"/>
+      <c r="F32" s="350"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
@@ -16203,14 +16390,14 @@
       </c>
       <c r="C33" s="164">
         <f>Valuation_Model!E77</f>
-        <v>2.098457537273136</v>
+        <v>2.0989107545774273</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="348"/>
-      <c r="F33" s="348"/>
+      <c r="E33" s="350"/>
+      <c r="F33" s="350"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
@@ -16220,8 +16407,8 @@
         <v>0.15</v>
       </c>
       <c r="D34" s="169"/>
-      <c r="E34" s="348"/>
-      <c r="F34" s="348"/>
+      <c r="E34" s="350"/>
+      <c r="F34" s="350"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="163" t="s">
@@ -16241,8 +16428,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="167"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
@@ -16252,8 +16439,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="168"/>
-      <c r="E38" s="348"/>
-      <c r="F38" s="348"/>
+      <c r="E38" s="350"/>
+      <c r="F38" s="350"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
@@ -16261,14 +16448,14 @@
       </c>
       <c r="C39" s="164">
         <f>Valuation_Model!E75</f>
-        <v>2.3176186410632371</v>
+        <v>2.3181191919937278</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="348"/>
-      <c r="F39" s="348"/>
+      <c r="E39" s="350"/>
+      <c r="F39" s="350"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
@@ -16279,8 +16466,8 @@
         <v>0.25</v>
       </c>
       <c r="D40" s="169"/>
-      <c r="E40" s="348"/>
-      <c r="F40" s="348"/>
+      <c r="E40" s="350"/>
+      <c r="F40" s="350"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
@@ -16288,7 +16475,7 @@
       </c>
       <c r="C42" s="158">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>2.2324349569103807</v>
+        <v>2.2329171101754359</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16342,8 +16529,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="167"/>
-      <c r="E49" s="348"/>
-      <c r="F49" s="348"/>
+      <c r="E49" s="350"/>
+      <c r="F49" s="350"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
@@ -16353,8 +16540,8 @@
         <v>-0.06</v>
       </c>
       <c r="D50" s="168"/>
-      <c r="E50" s="348"/>
-      <c r="F50" s="348"/>
+      <c r="E50" s="350"/>
+      <c r="F50" s="350"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
@@ -16362,14 +16549,14 @@
       </c>
       <c r="C51" s="164">
         <f>Valuation_Model!E78</f>
-        <v>2.0564148424412796</v>
+        <v>2.056858979515698</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="348"/>
-      <c r="F51" s="348"/>
+      <c r="E51" s="350"/>
+      <c r="F51" s="350"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
@@ -16379,8 +16566,8 @@
         <v>0.1</v>
       </c>
       <c r="D52" s="169"/>
-      <c r="E52" s="348"/>
-      <c r="F52" s="348"/>
+      <c r="E52" s="350"/>
+      <c r="F52" s="350"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="163" t="s">
@@ -16400,8 +16587,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="167"/>
-      <c r="E55" s="348"/>
-      <c r="F55" s="348"/>
+      <c r="E55" s="350"/>
+      <c r="F55" s="350"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
@@ -16411,8 +16598,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="168"/>
-      <c r="E56" s="348"/>
-      <c r="F56" s="348"/>
+      <c r="E56" s="350"/>
+      <c r="F56" s="350"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
@@ -16420,14 +16607,14 @@
       </c>
       <c r="C57" s="164">
         <f>Valuation_Model!E74</f>
-        <v>2.5083219342830163</v>
+        <v>2.5088636726242299</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="348"/>
-      <c r="F57" s="348"/>
+      <c r="E57" s="350"/>
+      <c r="F57" s="350"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
@@ -16437,8 +16624,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="169"/>
-      <c r="E58" s="348"/>
-      <c r="F58" s="348"/>
+      <c r="E58" s="350"/>
+      <c r="F58" s="350"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
@@ -16446,7 +16633,7 @@
       </c>
       <c r="C60" s="158">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>2.2286272943321026</v>
+        <v>2.2291086252319019</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16507,7 +16694,7 @@
       </c>
       <c r="C66" s="164">
         <f>Valuation_Model!C18</f>
-        <v>2.2260940959950886</v>
+        <v>2.2265748797838305</v>
       </c>
       <c r="D66" s="164" t="str">
         <f>Market_currency</f>
@@ -16570,7 +16757,7 @@
       </c>
       <c r="F72" s="335">
         <f>BS!D89/C60</f>
-        <v>0.72188968925719599</v>
+        <v>0.72188968925719621</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16642,7 +16829,7 @@
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
-        <v>1.2897148694051519</v>
+        <v>1.2899934173795728</v>
       </c>
       <c r="D82" s="120"/>
     </row>
@@ -16652,7 +16839,7 @@
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
-        <v>1.5378583879236705</v>
+        <v>1.5381369358980914</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16663,7 +16850,7 @@
       </c>
       <c r="F83" s="335">
         <f>(1-C83/C60)</f>
-        <v>0.3099526368384754</v>
+        <v>0.30997667924860606</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16680,7 +16867,7 @@
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16693,7 +16880,7 @@
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>6.9712118192507999E-2</v>
+        <v>9.7593325788780882E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F87279-4546-4599-9102-EA2021B9E150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE2CB7DA-2903-434E-BFEB-374A06E655D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="415">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2311,6 +2311,10 @@
   </si>
   <si>
     <t>Net Change in Cash</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Net Income/Market Cap</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -4072,10 +4076,10 @@
         <v>327</v>
       </c>
       <c r="C5" s="339" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4191,7 +4195,7 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -5752,13 +5756,13 @@
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="9"/>
+      <c r="C27" s="100"/>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="184"/>
+      <c r="C28" s="186"/>
       <c r="D28" s="184"/>
       <c r="E28" s="184"/>
       <c r="F28" s="184"/>
@@ -5774,7 +5778,7 @@
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="184"/>
+      <c r="C29" s="186"/>
       <c r="D29" s="184"/>
       <c r="E29" s="184"/>
       <c r="F29" s="184"/>
@@ -5790,7 +5794,7 @@
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="185">
+      <c r="C30" s="189">
         <v>642877</v>
       </c>
       <c r="D30" s="185">
@@ -5816,7 +5820,7 @@
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="185">
+      <c r="C31" s="189">
         <v>3027292</v>
       </c>
       <c r="D31" s="185">
@@ -5842,7 +5846,7 @@
       <c r="B32" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="C32" s="184"/>
+      <c r="C32" s="186"/>
       <c r="D32" s="184"/>
       <c r="E32" s="184"/>
       <c r="F32" s="184"/>
@@ -7576,7 +7580,7 @@
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{87139493-416E-4F03-A3A9-B1C3E5C019E4}"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13767,7 +13771,56 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B126" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C126" s="173"/>
+      <c r="G126" s="23">
+        <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v>6.5460976665862772E-2</v>
+      </c>
+      <c r="H126" s="23">
+        <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v>2.4793936294697356E-2</v>
+      </c>
+      <c r="I126" s="23">
+        <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v>2.1724984212407273E-3</v>
+      </c>
+      <c r="J126" s="23">
+        <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v>3.653801433426336E-3</v>
+      </c>
+      <c r="K126" s="23">
+        <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v>0</v>
+      </c>
+      <c r="L126" s="23" t="str">
+        <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="M126" s="23" t="str">
+        <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="N126" s="23" t="str">
+        <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="O126" s="23" t="str">
+        <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="P126" s="23" t="str">
+        <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="Q126" s="23" t="str">
+        <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+    </row>
     <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE2CB7DA-2903-434E-BFEB-374A06E655D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5603C044-B72A-4E14-8745-C82B5F070117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="417">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2327,6 +2327,13 @@
   </si>
   <si>
     <t>CNS_04</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t>Y</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4044,7 +4051,7 @@
         <v>366</v>
       </c>
       <c r="F1" s="290" t="s">
-        <v>333</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -4087,7 +4094,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4120,7 +4127,7 @@
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
-        <v>45716</v>
+        <v>45900</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
@@ -4132,7 +4139,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>2640.0003299999998</v>
+        <v>2720.0003400000001</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4182,7 +4189,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.06349396</v>
+        <v>1.0598962000000001</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4204,7 +4211,7 @@
         <v>280</v>
       </c>
       <c r="C19" s="255">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="E19" s="5"/>
     </row>
@@ -4215,7 +4222,7 @@
       </c>
       <c r="C20" s="258">
         <f>C129</f>
-        <v>1.5381369358980914</v>
+        <v>1.5968726986927759</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>318</v>
@@ -4230,7 +4237,7 @@
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
-        <v>9.7593325788780882E-2</v>
+        <v>0.14703263371672559</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4291,7 +4298,7 @@
       </c>
       <c r="C30" s="191">
         <f>Normalized_FCF!C8</f>
-        <v>58602.662537660683</v>
+        <v>113776.93034265516</v>
       </c>
       <c r="D30" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4374,7 +4381,7 @@
       </c>
       <c r="C40" s="328">
         <f>Normalized_FCF!C48</f>
-        <v>23291.09073065874</v>
+        <v>25087.710958398427</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4389,7 +4396,7 @@
       </c>
       <c r="C41" s="328">
         <f>Normalized_FCF!C47</f>
-        <v>-1003</v>
+        <v>-1880</v>
       </c>
       <c r="D41" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4404,7 +4411,7 @@
       </c>
       <c r="C42" s="191">
         <f>Normalized_FCF!C12</f>
-        <v>22288.09073065874</v>
+        <v>23207.710958398427</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4422,7 +4429,7 @@
       </c>
       <c r="C45" s="191">
         <f>Normalized_FCF!C15</f>
-        <v>-2089.6737831682049</v>
+        <v>0</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4444,7 +4451,7 @@
       </c>
       <c r="C48" s="191">
         <f>Normalized_FCF!C14</f>
-        <v>-20222.688317079854</v>
+        <v>-34246.160325263394</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4497,7 +4504,7 @@
       </c>
       <c r="C56" s="191">
         <f>Normalized_FCF!G19</f>
-        <v>101456.09073065873</v>
+        <v>169799.71095839841</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4510,7 +4517,7 @@
       </c>
       <c r="C57" s="191">
         <f>Normalized_FCF!C19</f>
-        <v>58578.391168071357</v>
+        <v>102738.48097579018</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4523,7 +4530,7 @@
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C125</f>
-        <v>2.359763538126574E-2</v>
+        <v>4.0033864694300855E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4532,7 +4539,7 @@
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
-        <v>5.9494949494949496E-2</v>
+        <v>5.6424319257515447E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4654,7 +4661,7 @@
       </c>
       <c r="C77" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.58404147568632703</v>
+        <v>1.0208635497046716</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4721,7 +4728,7 @@
       </c>
       <c r="C87" s="254">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>2.7118294969743127E-2</v>
+        <v>2.7026554799530651E-2</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4739,7 +4746,7 @@
       </c>
       <c r="C90" s="191">
         <f>BS!C66</f>
-        <v>2664732</v>
+        <v>2707640</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4752,7 +4759,7 @@
       </c>
       <c r="C91" s="191">
         <f>Valuation_Model!C8</f>
-        <v>1823806.3881188305</v>
+        <v>1874069.548055639</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4765,7 +4772,7 @@
       </c>
       <c r="C92" s="254">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.4547051266422031</v>
+        <v>1.489739208172516</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4783,7 +4790,7 @@
       </c>
       <c r="C95" s="191">
         <f>Valuation_Model!C9</f>
-        <v>227656.8</v>
+        <v>229590.09999999998</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4796,7 +4803,7 @@
       </c>
       <c r="C96" s="254">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.18158370111673336</v>
+        <v>0.18250623309743585</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4818,7 +4825,7 @@
       </c>
       <c r="C100" s="254">
         <f>Valuation_Model!C12</f>
-        <v>2.1932120084755207</v>
+        <v>2.6660824361750932</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4876,7 +4883,7 @@
       </c>
       <c r="E107" s="264" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>2.51 HKD</v>
+        <v>3.22 HKD</v>
       </c>
       <c r="F107" s="265">
         <f>Valuation_Model!F74</f>
@@ -4890,7 +4897,7 @@
       </c>
       <c r="C108" s="249">
         <f>Valuation_Model!C75</f>
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="D108" s="250">
         <f>Valuation_Model!D75</f>
@@ -4898,11 +4905,11 @@
       </c>
       <c r="E108" s="251" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>2.32 HKD</v>
+        <v>2.8 HKD</v>
       </c>
       <c r="F108" s="252">
         <f>Valuation_Model!F75</f>
-        <v>0.21249999999999999</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
@@ -4920,7 +4927,7 @@
       </c>
       <c r="E109" s="251" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>2.23 HKD</v>
+        <v>2.73 HKD</v>
       </c>
       <c r="F109" s="252">
         <f>Valuation_Model!F76</f>
@@ -4934,7 +4941,7 @@
       </c>
       <c r="C110" s="249">
         <f>Valuation_Model!C77</f>
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="D110" s="250">
         <f>Valuation_Model!D77</f>
@@ -4942,11 +4949,11 @@
       </c>
       <c r="E110" s="251" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>2.1 HKD</v>
+        <v>2.46 HKD</v>
       </c>
       <c r="F110" s="252">
         <f>Valuation_Model!F77</f>
-        <v>0.1275</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
@@ -4956,7 +4963,7 @@
       </c>
       <c r="C111" s="249">
         <f>Valuation_Model!C78</f>
-        <v>-0.06</v>
+        <v>-0.1</v>
       </c>
       <c r="D111" s="250">
         <f>Valuation_Model!D78</f>
@@ -4964,7 +4971,7 @@
       </c>
       <c r="E111" s="251" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>2.06 HKD</v>
+        <v>2.32 HKD</v>
       </c>
       <c r="F111" s="252">
         <f>Valuation_Model!F78</f>
@@ -4977,7 +4984,7 @@
       </c>
       <c r="C113" s="247">
         <f>Scenarios!C60</f>
-        <v>2.2291086252319019</v>
+        <v>2.6800518466090013</v>
       </c>
       <c r="D113" s="242" t="str">
         <f>Market_currency</f>
@@ -5041,7 +5048,7 @@
       </c>
       <c r="C123" s="256">
         <f>C19</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
@@ -5050,7 +5057,7 @@
       </c>
       <c r="C124" s="243">
         <f>Scenarios!C77</f>
-        <v>0.1178</v>
+        <v>0.11510561128533152</v>
       </c>
       <c r="D124" s="242" t="str">
         <f>Market_currency</f>
@@ -5069,7 +5076,7 @@
       </c>
       <c r="C127" s="246">
         <f>Scenarios!C81</f>
-        <v>0.24814351851851849</v>
+        <v>0.22468615322896712</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5079,7 +5086,7 @@
       </c>
       <c r="C128" s="246">
         <f>Scenarios!C82</f>
-        <v>1.2899934173795728</v>
+        <v>1.3721865454638087</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5088,7 +5095,7 @@
       </c>
       <c r="C129" s="245">
         <f>Scenarios!C83</f>
-        <v>1.5381369358980914</v>
+        <v>1.5968726986927759</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5101,7 +5108,7 @@
       </c>
       <c r="C130" s="94">
         <f>Scenarios!F83</f>
-        <v>0.30997667924860606</v>
+        <v>0.40416350500336151</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -5276,47 +5283,47 @@
         <v>CNY</v>
       </c>
       <c r="C1" s="107">
-        <v>45291</v>
+        <v>45657</v>
       </c>
       <c r="D1" s="38">
         <f>EOMONTH(EDATE(C1,-12),0)</f>
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="E1" s="38">
         <f t="shared" ref="E1:M1" si="0">EOMONTH(EDATE(D1,-12),0)</f>
-        <v>44561</v>
+        <v>44926</v>
       </c>
       <c r="F1" s="38">
         <f t="shared" si="0"/>
-        <v>44196</v>
+        <v>44561</v>
       </c>
       <c r="G1" s="38">
         <f t="shared" si="0"/>
-        <v>43830</v>
+        <v>44196</v>
       </c>
       <c r="H1" s="38">
         <f t="shared" si="0"/>
-        <v>43465</v>
+        <v>43830</v>
       </c>
       <c r="I1" s="38">
         <f t="shared" si="0"/>
-        <v>43100</v>
+        <v>43465</v>
       </c>
       <c r="J1" s="38">
         <f t="shared" si="0"/>
-        <v>42735</v>
+        <v>43100</v>
       </c>
       <c r="K1" s="38">
         <f t="shared" si="0"/>
-        <v>42369</v>
+        <v>42735</v>
       </c>
       <c r="L1" s="38">
         <f t="shared" si="0"/>
-        <v>42004</v>
+        <v>42369</v>
       </c>
       <c r="M1" s="38">
         <f t="shared" si="0"/>
-        <v>41639</v>
+        <v>42004</v>
       </c>
     </row>
     <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
@@ -5348,20 +5355,16 @@
         <v>2</v>
       </c>
       <c r="C4" s="193">
+        <v>1820108</v>
+      </c>
+      <c r="D4" s="184">
         <v>1615585</v>
       </c>
-      <c r="D4" s="184">
+      <c r="E4" s="184">
         <v>1446638</v>
       </c>
-      <c r="E4" s="184">
-        <v>1769157</v>
-      </c>
-      <c r="F4" s="184">
-        <v>1702154</v>
-      </c>
-      <c r="G4" s="184">
-        <v>1383402</v>
-      </c>
+      <c r="F4" s="184"/>
+      <c r="G4" s="184"/>
       <c r="H4" s="184"/>
       <c r="I4" s="184"/>
       <c r="J4" s="184"/>
@@ -5374,20 +5377,16 @@
         <v>44</v>
       </c>
       <c r="C5" s="193">
+        <v>925767</v>
+      </c>
+      <c r="D5" s="184">
         <v>897327</v>
       </c>
-      <c r="D5" s="184">
+      <c r="E5" s="184">
         <v>845264</v>
       </c>
-      <c r="E5" s="184">
-        <v>981731</v>
-      </c>
-      <c r="F5" s="184">
-        <v>959572</v>
-      </c>
-      <c r="G5" s="184">
-        <v>783542</v>
-      </c>
+      <c r="F5" s="184"/>
+      <c r="G5" s="184"/>
       <c r="H5" s="184"/>
       <c r="I5" s="184"/>
       <c r="J5" s="184"/>
@@ -5400,20 +5399,17 @@
         <v>55</v>
       </c>
       <c r="C6" s="193">
+        <f>197703+C7</f>
+        <v>736453</v>
+      </c>
+      <c r="D6" s="184">
         <v>613104</v>
       </c>
-      <c r="D6" s="184">
+      <c r="E6" s="184">
         <v>599182</v>
       </c>
-      <c r="E6" s="184">
-        <v>705390</v>
-      </c>
-      <c r="F6" s="184">
-        <v>456610</v>
-      </c>
-      <c r="G6" s="184">
-        <v>396643</v>
-      </c>
+      <c r="F6" s="184"/>
+      <c r="G6" s="184"/>
       <c r="H6" s="184"/>
       <c r="I6" s="184"/>
       <c r="J6" s="184"/>
@@ -5426,12 +5422,14 @@
         <v>62</v>
       </c>
       <c r="C7" s="194">
+        <v>538750</v>
+      </c>
+      <c r="D7" s="192">
         <v>425033</v>
       </c>
-      <c r="D7" s="192">
+      <c r="E7" s="192">
         <v>435254</v>
       </c>
-      <c r="E7" s="192"/>
       <c r="F7" s="192"/>
       <c r="G7" s="192"/>
       <c r="H7" s="192"/>
@@ -5510,20 +5508,16 @@
         <v>39</v>
       </c>
       <c r="C12" s="193">
+        <v>1880</v>
+      </c>
+      <c r="D12" s="184">
         <v>1003</v>
       </c>
-      <c r="D12" s="184">
+      <c r="E12" s="184">
         <v>863</v>
       </c>
-      <c r="E12" s="184">
-        <v>1613</v>
-      </c>
-      <c r="F12" s="184">
-        <v>2645</v>
-      </c>
-      <c r="G12" s="184">
-        <v>299</v>
-      </c>
+      <c r="F12" s="184"/>
+      <c r="G12" s="184"/>
       <c r="H12" s="184"/>
       <c r="I12" s="184"/>
       <c r="J12" s="184"/>
@@ -5536,12 +5530,14 @@
         <v>68</v>
       </c>
       <c r="C13" s="193">
+        <v>81491</v>
+      </c>
+      <c r="D13" s="184">
         <v>73805</v>
       </c>
-      <c r="D13" s="184">
+      <c r="E13" s="184">
         <v>45350</v>
       </c>
-      <c r="E13" s="184"/>
       <c r="F13" s="184"/>
       <c r="G13" s="184"/>
       <c r="H13" s="184"/>
@@ -5556,12 +5552,14 @@
         <v>51</v>
       </c>
       <c r="C14" s="193">
+        <v>47270</v>
+      </c>
+      <c r="D14" s="184">
         <v>44449</v>
       </c>
-      <c r="D14" s="184">
+      <c r="E14" s="184">
         <v>21017</v>
       </c>
-      <c r="E14" s="184"/>
       <c r="F14" s="184"/>
       <c r="G14" s="184"/>
       <c r="H14" s="184"/>
@@ -5576,17 +5574,15 @@
         <v>43</v>
       </c>
       <c r="C15" s="195">
+        <v>195249</v>
+      </c>
+      <c r="D15" s="185">
         <v>172817</v>
       </c>
-      <c r="D15" s="185">
+      <c r="E15" s="185">
         <v>65456</v>
       </c>
-      <c r="E15" s="185">
-        <v>5735.3965490000001</v>
-      </c>
-      <c r="F15" s="185">
-        <v>9646.0369900000005</v>
-      </c>
+      <c r="F15" s="185"/>
       <c r="G15" s="185"/>
       <c r="H15" s="185"/>
       <c r="I15" s="185"/>
@@ -5599,13 +5595,15 @@
       <c r="B16" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="193">
-        <v>2199</v>
+      <c r="C16" s="184">
+        <v>-8130</v>
       </c>
       <c r="D16" s="184">
-        <v>645</v>
-      </c>
-      <c r="E16" s="184"/>
+        <v>-2199</v>
+      </c>
+      <c r="E16" s="184">
+        <v>-645</v>
+      </c>
       <c r="F16" s="184"/>
       <c r="G16" s="184"/>
       <c r="H16" s="184"/>
@@ -5629,14 +5627,12 @@
         <v>35974</v>
       </c>
       <c r="D19" s="184">
+        <v>35974</v>
+      </c>
+      <c r="E19" s="184">
         <v>32106</v>
       </c>
-      <c r="E19" s="184">
-        <v>181.018</v>
-      </c>
-      <c r="F19" s="184">
-        <v>186.14699999999999</v>
-      </c>
+      <c r="F19" s="184"/>
       <c r="G19" s="184"/>
       <c r="H19" s="184"/>
       <c r="I19" s="184"/>
@@ -5649,13 +5645,13 @@
       <c r="B20" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="184">
+      <c r="C20" s="184"/>
+      <c r="D20" s="184">
         <v>15312</v>
       </c>
-      <c r="D20" s="184">
+      <c r="E20" s="184">
         <v>11600</v>
       </c>
-      <c r="E20" s="184"/>
       <c r="F20" s="184"/>
       <c r="G20" s="184"/>
       <c r="H20" s="184"/>
@@ -5669,13 +5665,13 @@
       <c r="B21" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="184">
+      <c r="C21" s="184"/>
+      <c r="D21" s="184">
         <v>-169280</v>
       </c>
-      <c r="D21" s="184">
+      <c r="E21" s="184">
         <v>-50846</v>
       </c>
-      <c r="E21" s="184"/>
       <c r="F21" s="184"/>
       <c r="G21" s="184"/>
       <c r="H21" s="184"/>
@@ -5739,10 +5735,17 @@
         <v>Dividend per share (HKD)</v>
       </c>
       <c r="C25" s="39">
-        <v>0.1178</v>
-      </c>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
+        <f>(0.0682+0.0538)/Exchange_Rate</f>
+        <v>0.11510561128533152</v>
+      </c>
+      <c r="D25" s="39">
+        <f>(0.064+0.041)/Exchange_Rate</f>
+        <v>9.9066304794752549E-2</v>
+      </c>
+      <c r="E25" s="39">
+        <f>(0.022+0.0168)/Exchange_Rate</f>
+        <v>3.6607358343203798E-2</v>
+      </c>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
       <c r="H25" s="39"/>
@@ -5756,13 +5759,18 @@
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="100"/>
+      <c r="C27" s="100" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="186"/>
+      <c r="C28" s="186">
+        <f>BS!C4</f>
+        <v>109763</v>
+      </c>
       <c r="D28" s="184"/>
       <c r="E28" s="184"/>
       <c r="F28" s="184"/>
@@ -5778,7 +5786,10 @@
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="186"/>
+      <c r="C29" s="186">
+        <f>BS!C6</f>
+        <v>318027</v>
+      </c>
       <c r="D29" s="184"/>
       <c r="E29" s="184"/>
       <c r="F29" s="184"/>
@@ -5795,20 +5806,17 @@
         <v>40</v>
       </c>
       <c r="C30" s="189">
+        <f>BS!C33+BS!C42</f>
         <v>642877</v>
       </c>
       <c r="D30" s="185">
+        <v>642877</v>
+      </c>
+      <c r="E30" s="185">
         <v>734909</v>
       </c>
-      <c r="E30" s="185">
-        <v>677999</v>
-      </c>
-      <c r="F30" s="185">
-        <v>1352795</v>
-      </c>
-      <c r="G30" s="185">
-        <v>1205068</v>
-      </c>
+      <c r="F30" s="185"/>
+      <c r="G30" s="185"/>
       <c r="H30" s="185"/>
       <c r="I30" s="185"/>
       <c r="J30" s="185"/>
@@ -5821,20 +5829,17 @@
         <v>30</v>
       </c>
       <c r="C31" s="189">
+        <f>BS!G27</f>
+        <v>3158826</v>
+      </c>
+      <c r="D31" s="185">
         <v>3027292</v>
       </c>
-      <c r="D31" s="185">
+      <c r="E31" s="185">
         <v>2824568</v>
       </c>
-      <c r="E31" s="185">
-        <v>2735259</v>
-      </c>
-      <c r="F31" s="185">
-        <v>250534</v>
-      </c>
-      <c r="G31" s="185">
-        <v>13930</v>
-      </c>
+      <c r="F31" s="185"/>
+      <c r="G31" s="185"/>
       <c r="H31" s="185"/>
       <c r="I31" s="185"/>
       <c r="J31" s="185"/>
@@ -5846,7 +5851,10 @@
       <c r="B32" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="C32" s="186"/>
+      <c r="C32" s="186">
+        <f>BS!G28</f>
+        <v>-1648</v>
+      </c>
       <c r="D32" s="184"/>
       <c r="E32" s="184"/>
       <c r="F32" s="184"/>
@@ -5885,23 +5893,23 @@
       </c>
       <c r="C36" s="186">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
-        <v>1615585</v>
+        <v>1820108</v>
       </c>
       <c r="D36" s="186">
         <f t="shared" si="1"/>
-        <v>1446638</v>
+        <v>1615585</v>
       </c>
       <c r="E36" s="186">
         <f t="shared" si="1"/>
-        <v>1769157</v>
-      </c>
-      <c r="F36" s="186">
+        <v>1446638</v>
+      </c>
+      <c r="F36" s="186" t="str">
         <f t="shared" si="1"/>
-        <v>1702154</v>
-      </c>
-      <c r="G36" s="186">
+        <v/>
+      </c>
+      <c r="G36" s="186" t="str">
         <f t="shared" si="1"/>
-        <v>1383402</v>
+        <v/>
       </c>
       <c r="H36" s="186" t="str">
         <f t="shared" si="1"/>
@@ -5934,23 +5942,23 @@
       </c>
       <c r="C37" s="186">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
-        <v>-897327</v>
+        <v>-925767</v>
       </c>
       <c r="D37" s="186">
         <f t="shared" si="2"/>
-        <v>-845264</v>
+        <v>-897327</v>
       </c>
       <c r="E37" s="186">
         <f t="shared" si="2"/>
-        <v>-981731</v>
-      </c>
-      <c r="F37" s="186">
+        <v>-845264</v>
+      </c>
+      <c r="F37" s="186" t="str">
         <f t="shared" si="2"/>
-        <v>-959572</v>
-      </c>
-      <c r="G37" s="186">
+        <v/>
+      </c>
+      <c r="G37" s="186" t="str">
         <f t="shared" si="2"/>
-        <v>-783542</v>
+        <v/>
       </c>
       <c r="H37" s="186" t="str">
         <f t="shared" si="2"/>
@@ -5983,23 +5991,23 @@
       </c>
       <c r="C38" s="187">
         <f>IF(C36="","",C36+C37)</f>
-        <v>718258</v>
+        <v>894341</v>
       </c>
       <c r="D38" s="187">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
-        <v>601374</v>
+        <v>718258</v>
       </c>
       <c r="E38" s="187">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
-        <v>787426</v>
-      </c>
-      <c r="F38" s="187">
+        <v>601374</v>
+      </c>
+      <c r="F38" s="187" t="str">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
-        <v>742582</v>
-      </c>
-      <c r="G38" s="187">
+        <v/>
+      </c>
+      <c r="G38" s="187" t="str">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
-        <v>599860</v>
+        <v/>
       </c>
       <c r="H38" s="187" t="str">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
@@ -6032,23 +6040,23 @@
       </c>
       <c r="C39" s="186">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
-        <v>-613104</v>
+        <v>-736453</v>
       </c>
       <c r="D39" s="186">
         <f t="shared" si="13"/>
-        <v>-599182</v>
+        <v>-613104</v>
       </c>
       <c r="E39" s="186">
         <f t="shared" si="13"/>
-        <v>-705390</v>
-      </c>
-      <c r="F39" s="186">
+        <v>-599182</v>
+      </c>
+      <c r="F39" s="186" t="str">
         <f t="shared" si="13"/>
-        <v>-456610</v>
-      </c>
-      <c r="G39" s="186">
+        <v/>
+      </c>
+      <c r="G39" s="186" t="str">
         <f t="shared" si="13"/>
-        <v>-396643</v>
+        <v/>
       </c>
       <c r="H39" s="186" t="str">
         <f t="shared" si="13"/>
@@ -6081,23 +6089,23 @@
       </c>
       <c r="C40" s="188">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
-        <v>-425033</v>
+        <v>-538750</v>
       </c>
       <c r="D40" s="188">
         <f t="shared" si="14"/>
-        <v>-435254</v>
+        <v>-425033</v>
       </c>
       <c r="E40" s="188">
         <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="F40" s="188">
+        <v>-435254</v>
+      </c>
+      <c r="F40" s="188" t="str">
         <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="G40" s="188">
+        <v/>
+      </c>
+      <c r="G40" s="188" t="str">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H40" s="188" t="str">
         <f t="shared" si="14"/>
@@ -6130,23 +6138,23 @@
       </c>
       <c r="C41" s="188">
         <f>IF(C$4="","",C39-C40)</f>
-        <v>-188071</v>
+        <v>-197703</v>
       </c>
       <c r="D41" s="188">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
-        <v>-163928</v>
+        <v>-188071</v>
       </c>
       <c r="E41" s="188">
         <f t="shared" si="15"/>
-        <v>-705390</v>
-      </c>
-      <c r="F41" s="188">
+        <v>-163928</v>
+      </c>
+      <c r="F41" s="188" t="str">
         <f t="shared" si="15"/>
-        <v>-456610</v>
-      </c>
-      <c r="G41" s="188">
+        <v/>
+      </c>
+      <c r="G41" s="188" t="str">
         <f t="shared" si="15"/>
-        <v>-396643</v>
+        <v/>
       </c>
       <c r="H41" s="188" t="str">
         <f t="shared" si="15"/>
@@ -6189,13 +6197,13 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F42" s="186">
+      <c r="F42" s="186" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="G42" s="186">
+        <v/>
+      </c>
+      <c r="G42" s="186" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H42" s="186" t="str">
         <f t="shared" si="16"/>
@@ -6228,23 +6236,23 @@
       </c>
       <c r="C43" s="189">
         <f>IF(C$4="","",C38+C39+C42)</f>
-        <v>105154</v>
+        <v>157888</v>
       </c>
       <c r="D43" s="189">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
-        <v>2192</v>
+        <v>105154</v>
       </c>
       <c r="E43" s="189">
         <f t="shared" si="17"/>
-        <v>82036</v>
-      </c>
-      <c r="F43" s="189">
+        <v>2192</v>
+      </c>
+      <c r="F43" s="189" t="str">
         <f t="shared" si="17"/>
-        <v>285972</v>
-      </c>
-      <c r="G43" s="189">
+        <v/>
+      </c>
+      <c r="G43" s="189" t="str">
         <f t="shared" si="17"/>
-        <v>203217</v>
+        <v/>
       </c>
       <c r="H43" s="189" t="str">
         <f t="shared" si="17"/>
@@ -6277,23 +6285,23 @@
       </c>
       <c r="C44" s="190">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
-        <v>39310</v>
+        <v>5020</v>
       </c>
       <c r="D44" s="190">
         <f t="shared" si="18"/>
-        <v>39794</v>
+        <v>39310</v>
       </c>
       <c r="E44" s="190">
         <f t="shared" si="18"/>
-        <v>-74687.603451000003</v>
-      </c>
-      <c r="F44" s="190">
+        <v>39794</v>
+      </c>
+      <c r="F44" s="190" t="str">
         <f t="shared" si="18"/>
-        <v>-273680.96301000001</v>
-      </c>
-      <c r="G44" s="190">
+        <v/>
+      </c>
+      <c r="G44" s="190" t="str">
         <f t="shared" si="18"/>
-        <v>-202918</v>
+        <v/>
       </c>
       <c r="H44" s="190" t="str">
         <f t="shared" si="18"/>
@@ -6326,23 +6334,23 @@
       </c>
       <c r="C45" s="191">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
-        <v>72802</v>
+        <v>79611</v>
       </c>
       <c r="D45" s="191">
         <f t="shared" si="19"/>
-        <v>44487</v>
+        <v>72802</v>
       </c>
       <c r="E45" s="191">
         <f t="shared" si="19"/>
-        <v>-1613</v>
-      </c>
-      <c r="F45" s="191">
+        <v>44487</v>
+      </c>
+      <c r="F45" s="191" t="str">
         <f t="shared" si="19"/>
-        <v>-2645</v>
-      </c>
-      <c r="G45" s="191">
+        <v/>
+      </c>
+      <c r="G45" s="191" t="str">
         <f t="shared" si="19"/>
-        <v>-299</v>
+        <v/>
       </c>
       <c r="H45" s="191" t="str">
         <f t="shared" si="19"/>
@@ -6375,23 +6383,23 @@
       </c>
       <c r="C46" s="186">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
-        <v>-44449</v>
+        <v>-47270</v>
       </c>
       <c r="D46" s="186">
         <f t="shared" si="20"/>
-        <v>-21017</v>
+        <v>-44449</v>
       </c>
       <c r="E46" s="186">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="F46" s="186">
+        <v>-21017</v>
+      </c>
+      <c r="F46" s="186" t="str">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="G46" s="186">
+        <v/>
+      </c>
+      <c r="G46" s="186" t="str">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H46" s="186" t="str">
         <f t="shared" si="20"/>
@@ -6424,23 +6432,23 @@
       </c>
       <c r="C47" s="189">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
-        <v>172817</v>
+        <v>195249</v>
       </c>
       <c r="D47" s="189">
         <f t="shared" si="21"/>
-        <v>65456</v>
+        <v>172817</v>
       </c>
       <c r="E47" s="189">
         <f t="shared" si="21"/>
-        <v>5735.3965490000001</v>
-      </c>
-      <c r="F47" s="189">
+        <v>65456</v>
+      </c>
+      <c r="F47" s="189" t="str">
         <f t="shared" si="21"/>
-        <v>9646.0369900000005</v>
-      </c>
-      <c r="G47" s="189">
+        <v/>
+      </c>
+      <c r="G47" s="189" t="str">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H47" s="189" t="str">
         <f t="shared" si="21"/>
@@ -6473,23 +6481,23 @@
       </c>
       <c r="C48" s="186">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
-        <v>-2199</v>
+        <v>0</v>
       </c>
       <c r="D48" s="186">
         <f t="shared" si="22"/>
-        <v>-645</v>
+        <v>0</v>
       </c>
       <c r="E48" s="186">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F48" s="186">
+      <c r="F48" s="186" t="str">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="G48" s="186">
+        <v/>
+      </c>
+      <c r="G48" s="186" t="str">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H48" s="186" t="str">
         <f t="shared" si="22"/>
@@ -6527,23 +6535,23 @@
       </c>
       <c r="C51" s="186">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
-        <v>-1003</v>
+        <v>-1880</v>
       </c>
       <c r="D51" s="186">
         <f t="shared" si="23"/>
-        <v>-863</v>
+        <v>-1003</v>
       </c>
       <c r="E51" s="186">
         <f t="shared" si="23"/>
-        <v>-1613</v>
-      </c>
-      <c r="F51" s="186">
+        <v>-863</v>
+      </c>
+      <c r="F51" s="186" t="str">
         <f t="shared" si="23"/>
-        <v>-2645</v>
-      </c>
-      <c r="G51" s="186">
+        <v/>
+      </c>
+      <c r="G51" s="186" t="str">
         <f t="shared" si="23"/>
-        <v>-299</v>
+        <v/>
       </c>
       <c r="H51" s="186" t="str">
         <f t="shared" si="23"/>
@@ -6576,23 +6584,23 @@
       </c>
       <c r="C52" s="186">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
-        <v>73805</v>
+        <v>81491</v>
       </c>
       <c r="D52" s="186">
         <f t="shared" si="24"/>
-        <v>45350</v>
+        <v>73805</v>
       </c>
       <c r="E52" s="186">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="F52" s="186">
+        <v>45350</v>
+      </c>
+      <c r="F52" s="186" t="str">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="G52" s="186">
+        <v/>
+      </c>
+      <c r="G52" s="186" t="str">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H52" s="186" t="str">
         <f t="shared" si="24"/>
@@ -6640,13 +6648,13 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="F55" s="191">
+      <c r="F55" s="191" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="G55" s="191">
+        <v/>
+      </c>
+      <c r="G55" s="191" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H55" s="191" t="str">
         <f t="shared" si="25"/>
@@ -6689,13 +6697,13 @@
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="F56" s="191">
+      <c r="F56" s="191" t="str">
         <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="G56" s="191">
+        <v/>
+      </c>
+      <c r="G56" s="191" t="str">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H56" s="191" t="str">
         <f t="shared" si="26"/>
@@ -6738,13 +6746,13 @@
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="F57" s="191">
+      <c r="F57" s="191" t="str">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="G57" s="191">
+        <v/>
+      </c>
+      <c r="G57" s="191" t="str">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H57" s="191" t="str">
         <f t="shared" si="27"/>
@@ -6777,23 +6785,23 @@
       </c>
       <c r="C58" s="191">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
-        <v>39310</v>
+        <v>5020</v>
       </c>
       <c r="D58" s="191">
         <f t="shared" ref="D58:M58" si="28">IF(D$4="","",D44-D55-D56-D57)</f>
-        <v>39794</v>
+        <v>39310</v>
       </c>
       <c r="E58" s="191">
         <f t="shared" si="28"/>
-        <v>-74687.603451000003</v>
-      </c>
-      <c r="F58" s="191">
+        <v>39794</v>
+      </c>
+      <c r="F58" s="191" t="str">
         <f t="shared" si="28"/>
-        <v>-273680.96301000001</v>
-      </c>
-      <c r="G58" s="191">
+        <v/>
+      </c>
+      <c r="G58" s="191" t="str">
         <f t="shared" si="28"/>
-        <v>-202918</v>
+        <v/>
       </c>
       <c r="H58" s="191" t="str">
         <f t="shared" si="28"/>
@@ -6836,19 +6844,19 @@
       </c>
       <c r="D61" s="186">
         <f t="shared" si="29"/>
-        <v>-32106</v>
+        <v>-35974</v>
       </c>
       <c r="E61" s="186">
         <f t="shared" si="29"/>
-        <v>-181.018</v>
-      </c>
-      <c r="F61" s="186">
+        <v>-32106</v>
+      </c>
+      <c r="F61" s="186" t="str">
         <f t="shared" si="29"/>
-        <v>-186.14699999999999</v>
-      </c>
-      <c r="G61" s="186">
+        <v/>
+      </c>
+      <c r="G61" s="186" t="str">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H61" s="186" t="str">
         <f t="shared" si="29"/>
@@ -6881,23 +6889,23 @@
       </c>
       <c r="C62" s="186">
         <f t="shared" ref="C62:M62" si="30">IF(C$4="","",-C20)</f>
-        <v>-15312</v>
+        <v>0</v>
       </c>
       <c r="D62" s="186">
         <f t="shared" si="30"/>
-        <v>-11600</v>
+        <v>-15312</v>
       </c>
       <c r="E62" s="186">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="F62" s="186">
+        <v>-11600</v>
+      </c>
+      <c r="F62" s="186" t="str">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G62" s="186">
+        <v/>
+      </c>
+      <c r="G62" s="186" t="str">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H62" s="186" t="str">
         <f t="shared" si="30"/>
@@ -6930,23 +6938,23 @@
       </c>
       <c r="C63" s="186">
         <f t="shared" ref="C63:M63" si="31">IF(C$4="","",-C21)</f>
-        <v>169280</v>
+        <v>0</v>
       </c>
       <c r="D63" s="186">
         <f t="shared" si="31"/>
-        <v>50846</v>
+        <v>169280</v>
       </c>
       <c r="E63" s="186">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="F63" s="186">
+        <v>50846</v>
+      </c>
+      <c r="F63" s="186" t="str">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="G63" s="186">
+        <v/>
+      </c>
+      <c r="G63" s="186" t="str">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H63" s="186" t="str">
         <f t="shared" si="31"/>
@@ -6989,13 +6997,13 @@
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="F64" s="186">
+      <c r="F64" s="186" t="str">
         <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="G64" s="186">
+        <v/>
+      </c>
+      <c r="G64" s="186" t="str">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H64" s="186" t="str">
         <f t="shared" si="32"/>
@@ -7028,23 +7036,23 @@
       </c>
       <c r="C65" s="75">
         <f t="shared" ref="C65:M65" si="33">IF(C$4="","",C25)</f>
-        <v>0.1178</v>
+        <v>0.11510561128533152</v>
       </c>
       <c r="D65" s="75">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>9.9066304794752549E-2</v>
       </c>
       <c r="E65" s="75">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="F65" s="75">
+        <v>3.6607358343203798E-2</v>
+      </c>
+      <c r="F65" s="75" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="G65" s="75">
+        <v/>
+      </c>
+      <c r="G65" s="75" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H65" s="75" t="str">
         <f t="shared" si="33"/>
@@ -7083,19 +7091,19 @@
       </c>
       <c r="C68" s="94">
         <f t="shared" ref="C68:M68" si="34">IF(D$36="","",C36/D36-1)</f>
-        <v>0.11678595474472542</v>
+        <v>0.12659377253440707</v>
       </c>
       <c r="D68" s="94">
         <f t="shared" si="34"/>
-        <v>-0.18230094898304672</v>
-      </c>
-      <c r="E68" s="94">
+        <v>0.11678595474472542</v>
+      </c>
+      <c r="E68" s="94" t="str">
         <f t="shared" si="34"/>
-        <v>3.9363653347464389E-2</v>
-      </c>
-      <c r="F68" s="94">
+        <v/>
+      </c>
+      <c r="F68" s="94" t="str">
         <f t="shared" si="34"/>
-        <v>0.2304116952266948</v>
+        <v/>
       </c>
       <c r="G68" s="94" t="str">
         <f t="shared" si="34"/>
@@ -7133,19 +7141,19 @@
       </c>
       <c r="C69" s="104">
         <f t="shared" ref="C69:M69" si="35">IF(D$36="","",C37/D37-1)</f>
-        <v>6.15937742527779E-2</v>
+        <v>3.1694131570765283E-2</v>
       </c>
       <c r="D69" s="104">
         <f t="shared" si="35"/>
-        <v>-0.13900650992990948</v>
-      </c>
-      <c r="E69" s="104">
+        <v>6.15937742527779E-2</v>
+      </c>
+      <c r="E69" s="104" t="str">
         <f t="shared" si="35"/>
-        <v>2.3092587111753993E-2</v>
-      </c>
-      <c r="F69" s="104">
+        <v/>
+      </c>
+      <c r="F69" s="104" t="str">
         <f t="shared" si="35"/>
-        <v>0.22465930352170016</v>
+        <v/>
       </c>
       <c r="G69" s="104" t="str">
         <f t="shared" si="35"/>
@@ -7183,19 +7191,19 @@
       </c>
       <c r="C70" s="94">
         <f t="shared" ref="C70:M70" si="36">IF(D$36="","",C38/D38-1)</f>
-        <v>0.19436157865155468</v>
+        <v>0.24515285593755998</v>
       </c>
       <c r="D70" s="94">
         <f t="shared" si="36"/>
-        <v>-0.23627871063439609</v>
-      </c>
-      <c r="E70" s="94">
+        <v>0.19436157865155468</v>
+      </c>
+      <c r="E70" s="94" t="str">
         <f t="shared" si="36"/>
-        <v>6.0389290340999269E-2</v>
-      </c>
-      <c r="F70" s="94">
+        <v/>
+      </c>
+      <c r="F70" s="94" t="str">
         <f t="shared" si="36"/>
-        <v>0.23792551595372258</v>
+        <v/>
       </c>
       <c r="G70" s="94" t="str">
         <f t="shared" si="36"/>
@@ -7233,19 +7241,19 @@
       </c>
       <c r="C71" s="104">
         <f t="shared" ref="C71:M71" si="37">IF(D$36="","",C39/D39-1)</f>
-        <v>2.3235010397508526E-2</v>
+        <v>0.20118772671520646</v>
       </c>
       <c r="D71" s="104">
         <f t="shared" si="37"/>
-        <v>-0.15056635336480528</v>
-      </c>
-      <c r="E71" s="104">
+        <v>2.3235010397508526E-2</v>
+      </c>
+      <c r="E71" s="104" t="str">
         <f t="shared" si="37"/>
-        <v>0.54484133067606932</v>
-      </c>
-      <c r="F71" s="104">
+        <v/>
+      </c>
+      <c r="F71" s="104" t="str">
         <f t="shared" si="37"/>
-        <v>0.15118633128531189</v>
+        <v/>
       </c>
       <c r="G71" s="104" t="str">
         <f t="shared" si="37"/>
@@ -7281,21 +7289,21 @@
         <f>B48</f>
         <v>Non-controling Interests</v>
       </c>
-      <c r="C72" s="94" t="e">
+      <c r="C72" s="94">
         <f>IF(D$36="","",C65/D65-1)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D72" s="94" t="e">
+        <v>0.16190476190476177</v>
+      </c>
+      <c r="D72" s="94">
         <f t="shared" ref="D72:M72" si="38">IF(E$36="","",D65/E65-1)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E72" s="94" t="e">
+        <v>1.7061855670103094</v>
+      </c>
+      <c r="E72" s="94" t="str">
         <f t="shared" si="38"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F72" s="94" t="e">
+        <v/>
+      </c>
+      <c r="F72" s="94" t="str">
         <f t="shared" si="38"/>
-        <v>#DIV/0!</v>
+        <v/>
       </c>
       <c r="G72" s="94" t="str">
         <f t="shared" si="38"/>
@@ -7354,23 +7362,23 @@
       </c>
       <c r="C76" s="78">
         <f>IF(C$4="","",C79+C80)</f>
-        <v>3670169</v>
+        <v>3801703</v>
       </c>
       <c r="D76" s="78">
         <f t="shared" ref="D76:M76" si="39">IF(D$4="","",D79+D80)</f>
-        <v>3559477</v>
+        <v>3670169</v>
       </c>
       <c r="E76" s="78">
         <f t="shared" si="39"/>
-        <v>3413258</v>
-      </c>
-      <c r="F76" s="78">
+        <v>3559477</v>
+      </c>
+      <c r="F76" s="78" t="str">
         <f t="shared" si="39"/>
-        <v>1603329</v>
-      </c>
-      <c r="G76" s="78">
+        <v/>
+      </c>
+      <c r="G76" s="78" t="str">
         <f t="shared" si="39"/>
-        <v>1218998</v>
+        <v/>
       </c>
       <c r="H76" s="78" t="str">
         <f t="shared" si="39"/>
@@ -7403,7 +7411,7 @@
       </c>
       <c r="C77" s="74">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
-        <v>0</v>
+        <v>109763</v>
       </c>
       <c r="D77" s="74">
         <f t="shared" si="40"/>
@@ -7413,13 +7421,13 @@
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="F77" s="74">
+      <c r="F77" s="74" t="str">
         <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="G77" s="74">
+        <v/>
+      </c>
+      <c r="G77" s="74" t="str">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H77" s="74" t="str">
         <f t="shared" si="40"/>
@@ -7437,7 +7445,7 @@
       </c>
       <c r="C78" s="74">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>318027</v>
       </c>
       <c r="D78" s="74">
         <f t="shared" si="40"/>
@@ -7447,13 +7455,13 @@
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="F78" s="74">
+      <c r="F78" s="74" t="str">
         <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="G78" s="74">
+        <v/>
+      </c>
+      <c r="G78" s="74" t="str">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H78" s="74" t="str">
         <f t="shared" si="40"/>
@@ -7475,19 +7483,19 @@
       </c>
       <c r="D79" s="58">
         <f t="shared" si="41"/>
-        <v>734909</v>
+        <v>642877</v>
       </c>
       <c r="E79" s="58">
         <f t="shared" si="41"/>
-        <v>677999</v>
-      </c>
-      <c r="F79" s="58">
+        <v>734909</v>
+      </c>
+      <c r="F79" s="58" t="str">
         <f t="shared" si="41"/>
-        <v>1352795</v>
-      </c>
-      <c r="G79" s="58">
+        <v/>
+      </c>
+      <c r="G79" s="58" t="str">
         <f t="shared" si="41"/>
-        <v>1205068</v>
+        <v/>
       </c>
       <c r="H79" s="58" t="str">
         <f t="shared" si="41"/>
@@ -7520,23 +7528,23 @@
       </c>
       <c r="C80" s="58">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
-        <v>3027292</v>
+        <v>3158826</v>
       </c>
       <c r="D80" s="58">
         <f t="shared" si="42"/>
-        <v>2824568</v>
+        <v>3027292</v>
       </c>
       <c r="E80" s="58">
         <f t="shared" si="42"/>
-        <v>2735259</v>
-      </c>
-      <c r="F80" s="58">
+        <v>2824568</v>
+      </c>
+      <c r="F80" s="58" t="str">
         <f t="shared" si="42"/>
-        <v>250534</v>
-      </c>
-      <c r="G80" s="58">
+        <v/>
+      </c>
+      <c r="G80" s="58" t="str">
         <f t="shared" si="42"/>
-        <v>13930</v>
+        <v/>
       </c>
       <c r="H80" s="58" t="str">
         <f t="shared" si="42"/>
@@ -7580,7 +7588,7 @@
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{87139493-416E-4F03-A3A9-B1C3E5C019E4}"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7611,11 +7619,11 @@
         <v>37</v>
       </c>
       <c r="C1" s="102">
-        <v>45473</v>
+        <v>45657</v>
       </c>
       <c r="F1" s="88" t="str">
         <f>IF(MONTH(C1)=MONTH(Normalized_FCF!G1),"FY","Quarter")&amp;" Report"</f>
-        <v>Quarter Report</v>
+        <v>FY Report</v>
       </c>
       <c r="H1" s="110">
         <f>Data!C3</f>
@@ -7658,7 +7666,8 @@
         <v>24</v>
       </c>
       <c r="C4" s="19">
-        <v>180994</v>
+        <f>97460+12303</f>
+        <v>109763</v>
       </c>
       <c r="D4" s="300">
         <v>0.6</v>
@@ -7668,7 +7677,8 @@
         <v>79</v>
       </c>
       <c r="G4" s="19">
-        <v>2385307</v>
+        <f>1713053+891425</f>
+        <v>2604478</v>
       </c>
       <c r="H4" s="300">
         <v>0.9</v>
@@ -7700,7 +7710,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="19">
-        <v>158110</v>
+        <v>318027</v>
       </c>
       <c r="D6" s="300">
         <v>0.5</v>
@@ -7731,7 +7741,7 @@
         <v>180</v>
       </c>
       <c r="G7" s="19">
-        <v>253051</v>
+        <v>270180</v>
       </c>
       <c r="H7" s="300">
         <v>0.6</v>
@@ -7784,7 +7794,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="19">
-        <v>5912</v>
+        <v>19230</v>
       </c>
       <c r="D10" s="300">
         <v>0.9</v>
@@ -7809,22 +7819,22 @@
       </c>
       <c r="C12" s="83">
         <f>SUM(C4:C11)</f>
-        <v>345016</v>
+        <v>447020</v>
       </c>
       <c r="D12" s="20">
         <f>C4*D4+C5*D5+C9*D9+C6*D6+C8*D8+C7*D7+C10*D10+C11*D11</f>
-        <v>192972.19999999998</v>
+        <v>242178.3</v>
       </c>
       <c r="F12" s="82" t="s">
         <v>71</v>
       </c>
       <c r="G12" s="83">
         <f>SUM(G4:G9)</f>
-        <v>2638358</v>
+        <v>2874658</v>
       </c>
       <c r="H12" s="20">
         <f>G4*H4+G5*H5+G6*H6+G7*H7+G8*H8+G9*H9</f>
-        <v>2298606.9000000004</v>
+        <v>2506138.2000000002</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7866,7 +7876,7 @@
         <v>80</v>
       </c>
       <c r="G15" s="19">
-        <v>279425</v>
+        <v>103162</v>
       </c>
       <c r="H15" s="300">
         <v>0.8</v>
@@ -7906,7 +7916,7 @@
         <v>180</v>
       </c>
       <c r="G17" s="19">
-        <v>126127</v>
+        <v>111923</v>
       </c>
       <c r="H17" s="300">
         <v>0.6</v>
@@ -7937,7 +7947,8 @@
         <v>26</v>
       </c>
       <c r="C19" s="19">
-        <v>193915</v>
+        <f>147013+53837+407</f>
+        <v>201257</v>
       </c>
       <c r="D19" s="300">
         <v>0.1</v>
@@ -7946,7 +7957,7 @@
         <v>184</v>
       </c>
       <c r="G19" s="19">
-        <v>1500</v>
+        <v>3283</v>
       </c>
       <c r="H19" s="300">
         <v>0.1</v>
@@ -7977,7 +7988,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="19">
-        <v>9704</v>
+        <v>0</v>
       </c>
       <c r="D21" s="300">
         <v>0.05</v>
@@ -7997,7 +8008,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="19">
-        <v>76124</v>
+        <v>60400</v>
       </c>
       <c r="D22" s="300">
         <v>0.9</v>
@@ -8022,22 +8033,22 @@
       </c>
       <c r="C24" s="83">
         <f>SUM(C15:C23)</f>
-        <v>279743</v>
+        <v>261657</v>
       </c>
       <c r="D24" s="20">
         <f>C15*D15+C16*D16+C18*D18+C17*D17+C19*D19+C20*D20+C21*D21+C22*D22+C23*D23</f>
-        <v>88388.3</v>
+        <v>74485.7</v>
       </c>
       <c r="F24" s="82" t="s">
         <v>72</v>
       </c>
       <c r="G24" s="83">
         <f>SUM(G15:G21)</f>
-        <v>407052</v>
+        <v>218368</v>
       </c>
       <c r="H24" s="20">
         <f>G15*H15+G16*H16+G17*H17+G18*H18+G19*H19+G20*H20+G21*H21</f>
-        <v>299366.2</v>
+        <v>150011.70000000001</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8069,11 +8080,11 @@
       </c>
       <c r="G27" s="87">
         <f>G32-G30</f>
-        <v>3027292</v>
+        <v>3158826</v>
       </c>
       <c r="H27" s="215">
         <f>H32-G30</f>
-        <v>2236456.6000000006</v>
+        <v>2329936.9000000004</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8087,7 +8098,7 @@
         <v>246</v>
       </c>
       <c r="G28" s="184">
-        <v>3990</v>
+        <v>-1648</v>
       </c>
       <c r="H28" s="215"/>
     </row>
@@ -8103,11 +8114,11 @@
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
-        <v>3023302</v>
+        <v>3160474</v>
       </c>
       <c r="H29" s="215">
         <f>H27-G28</f>
-        <v>2232466.6000000006</v>
+        <v>2331584.9000000004</v>
       </c>
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8156,11 +8167,11 @@
       </c>
       <c r="G32" s="220">
         <f>G35+G40</f>
-        <v>3670169</v>
+        <v>3801703</v>
       </c>
       <c r="H32" s="215">
         <f>H35+H40</f>
-        <v>2879333.6000000006</v>
+        <v>2972813.9000000004</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8199,11 +8210,11 @@
       </c>
       <c r="G35" s="220">
         <f>C12+C24</f>
-        <v>624759</v>
+        <v>708677</v>
       </c>
       <c r="H35" s="227">
         <f>D12+D24</f>
-        <v>281360.5</v>
+        <v>316664</v>
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8218,7 +8229,7 @@
       </c>
       <c r="G36" s="218">
         <f>C4+C15</f>
-        <v>180994</v>
+        <v>109763</v>
       </c>
       <c r="H36" s="222"/>
     </row>
@@ -8234,7 +8245,7 @@
       </c>
       <c r="G37" s="218">
         <f>C6</f>
-        <v>158110</v>
+        <v>318027</v>
       </c>
       <c r="H37" s="222"/>
     </row>
@@ -8266,11 +8277,11 @@
       </c>
       <c r="G39" s="218">
         <f>C7+C17+C19+C20</f>
-        <v>193915</v>
+        <v>201257</v>
       </c>
       <c r="H39" s="215">
         <f>C7*D7+C17*D17+C19*D19+C20*D20</f>
-        <v>19391.5</v>
+        <v>20125.7</v>
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8286,11 +8297,11 @@
       </c>
       <c r="G40" s="220">
         <f>G12+G24</f>
-        <v>3045410</v>
+        <v>3093026</v>
       </c>
       <c r="H40" s="227">
         <f>H12+H24</f>
-        <v>2597973.1000000006</v>
+        <v>2656149.9000000004</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8306,11 +8317,11 @@
       </c>
       <c r="G41" s="218">
         <f>C70</f>
-        <v>2664732</v>
+        <v>2707640</v>
       </c>
       <c r="H41" s="227">
         <f>H40-H42</f>
-        <v>2370316.3000000007</v>
+        <v>2426559.8000000003</v>
       </c>
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8325,11 +8336,11 @@
       </c>
       <c r="G42" s="229">
         <f>C82</f>
-        <v>380678</v>
+        <v>385386</v>
       </c>
       <c r="H42" s="230">
         <f>D82</f>
-        <v>227656.8</v>
+        <v>229590.09999999998</v>
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8363,11 +8374,11 @@
       </c>
       <c r="C46" s="191">
         <f>G29</f>
-        <v>3023302</v>
+        <v>3160474</v>
       </c>
       <c r="D46" s="191">
         <f>H29</f>
-        <v>2232466.6000000006</v>
+        <v>2331584.9000000004</v>
       </c>
       <c r="F46" s="289"/>
     </row>
@@ -8378,11 +8389,11 @@
       </c>
       <c r="C47" s="151">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>2.4114472607610322</v>
+        <v>2.5123304730577911</v>
       </c>
       <c r="D47" s="151">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.780660836168698</v>
+        <v>1.8534282499370043</v>
       </c>
       <c r="F47" s="289"/>
     </row>
@@ -8408,11 +8419,11 @@
       </c>
       <c r="C50" s="98">
         <f>G31/Normalized_FCF!C8</f>
-        <v>0.58016135321753903</v>
+        <v>0.29882156160837919</v>
       </c>
       <c r="D50" s="98">
         <f>G31/Normalized_FCF!G8</f>
-        <v>0.3233257888430302</v>
+        <v>0.21533618767734089</v>
       </c>
       <c r="F50" s="289"/>
     </row>
@@ -8423,7 +8434,7 @@
       <c r="C51" s="208"/>
       <c r="D51" s="94">
         <f>G29/G32</f>
-        <v>0.82375007799368372</v>
+        <v>0.83133111660747827</v>
       </c>
       <c r="F51" s="289"/>
     </row>
@@ -8448,11 +8459,11 @@
       </c>
       <c r="C54" s="94">
         <f>Normalized_FCF!C8/G35</f>
-        <v>9.3800429505874555E-2</v>
+        <v>0.16054836031457936</v>
       </c>
       <c r="D54" s="94">
         <f>Normalized_FCF!G8/G35</f>
-        <v>0.16831130083760298</v>
+        <v>0.2227926121491173</v>
       </c>
       <c r="F54" s="289"/>
     </row>
@@ -8492,7 +8503,7 @@
       <c r="C58" s="101"/>
       <c r="D58" s="23">
         <f>Normalized_FCF!G9/BS!$G$39</f>
-        <v>0.18551427171698939</v>
+        <v>0.17874657775878602</v>
       </c>
       <c r="F58" s="5"/>
     </row>
@@ -8503,7 +8514,7 @@
       <c r="C59" s="101"/>
       <c r="D59" s="94">
         <f>G39/G32</f>
-        <v>5.2835441637701153E-2</v>
+        <v>5.2938643550009039E-2</v>
       </c>
       <c r="F59" s="289"/>
     </row>
@@ -8528,11 +8539,11 @@
       </c>
       <c r="C62" s="94">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
-        <v>1.3197490690642218E-3</v>
+        <v>0</v>
       </c>
       <c r="D62" s="94">
         <f>G28/G29</f>
-        <v>1.3197490690642218E-3</v>
+        <v>-5.2144077122608828E-4</v>
       </c>
       <c r="F62" s="289" t="s">
         <v>276</v>
@@ -8569,11 +8580,11 @@
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
-        <v>2664732</v>
+        <v>2707640</v>
       </c>
       <c r="D66" s="191">
         <f>C66-D75</f>
-        <v>1823806.3881188305</v>
+        <v>1874069.548055639</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>228</v>
@@ -8615,7 +8626,7 @@
       </c>
       <c r="C70" s="83">
         <f>SUM(C66:C69)</f>
-        <v>2664732</v>
+        <v>2707640</v>
       </c>
       <c r="F70" s="289"/>
     </row>
@@ -8640,11 +8651,11 @@
       </c>
       <c r="C73" s="191">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-138958.140525</v>
+        <v>-151307.84729705923</v>
       </c>
       <c r="D73" s="191">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-140154.2686468616</v>
+        <v>-138928.40865739351</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>364</v>
@@ -8656,11 +8667,11 @@
       </c>
       <c r="C74" s="295">
         <f>-$C$66/C73</f>
-        <v>19.176508766829585</v>
+        <v>17.894907953347275</v>
       </c>
       <c r="D74" s="295">
         <f>-$C$66/D73</f>
-        <v>19.012849381806323</v>
+        <v>19.489462422888728</v>
       </c>
       <c r="F74" s="289" t="s">
         <v>331</v>
@@ -8673,7 +8684,7 @@
       <c r="C75" s="299"/>
       <c r="D75" s="298">
         <f>MAX(-D73*D76,G5)</f>
-        <v>840925.61188116961</v>
+        <v>833570.45194436098</v>
       </c>
       <c r="F75" s="289" t="s">
         <v>365</v>
@@ -8713,11 +8724,11 @@
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
-        <v>379178</v>
+        <v>382103</v>
       </c>
       <c r="D79" s="191">
         <f>G7*H7+G17*H17</f>
-        <v>227506.8</v>
+        <v>229261.8</v>
       </c>
       <c r="F79" s="289"/>
     </row>
@@ -8727,11 +8738,11 @@
       </c>
       <c r="C80" s="20">
         <f>G19</f>
-        <v>1500</v>
+        <v>3283</v>
       </c>
       <c r="D80" s="191">
         <f>G19*H19</f>
-        <v>150</v>
+        <v>328.3</v>
       </c>
       <c r="F80" s="289"/>
     </row>
@@ -8755,11 +8766,11 @@
       </c>
       <c r="C82" s="83">
         <f>SUM(C79:C81)</f>
-        <v>380678</v>
+        <v>385386</v>
       </c>
       <c r="D82" s="83">
         <f>SUM(D79:D81)</f>
-        <v>227656.8</v>
+        <v>229590.09999999998</v>
       </c>
       <c r="F82" s="289"/>
     </row>
@@ -8788,11 +8799,11 @@
       </c>
       <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-36157.731146040001</v>
+        <v>-36035.410903800002</v>
       </c>
       <c r="D86" s="254">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-2.7118294969743127E-2</v>
+        <v>-2.7026554799530651E-2</v>
       </c>
       <c r="E86" s="275" t="str">
         <f>Market_currency</f>
@@ -8805,11 +8816,11 @@
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>1939607.0779737919</v>
+        <v>1986319.1925198892</v>
       </c>
       <c r="D87" s="254">
         <f>C87*$H$1/Common_Shares</f>
-        <v>1.4547051266422031</v>
+        <v>1.4897392081725158</v>
       </c>
       <c r="E87" s="275" t="str">
         <f>Market_currency</f>
@@ -8822,11 +8833,11 @@
       </c>
       <c r="C88" s="191">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>242111.63175292799</v>
+        <v>243341.67454762</v>
       </c>
       <c r="D88" s="254">
         <f>C88*$H$1/Common_Shares</f>
-        <v>0.18158370111673336</v>
+        <v>0.18250623309743585</v>
       </c>
       <c r="E88" s="275" t="str">
         <f>Market_currency</f>
@@ -8839,11 +8850,11 @@
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
-        <v>2145560.9785806797</v>
+        <v>2193625.4561637091</v>
       </c>
       <c r="D89" s="277">
         <f>SUM(D86:D88)</f>
-        <v>1.6091705327891934</v>
+        <v>1.6452188864704209</v>
       </c>
       <c r="E89" s="275" t="str">
         <f>Market_currency</f>
@@ -8890,47 +8901,47 @@
       <c r="F1" s="53"/>
       <c r="G1" s="38">
         <f>Data!C1</f>
-        <v>45291</v>
+        <v>45657</v>
       </c>
       <c r="H1" s="38">
         <f>EOMONTH(EDATE(G1,-12),0)</f>
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="I1" s="38">
         <f t="shared" ref="I1:Q1" si="0">EOMONTH(EDATE(H1,-12),0)</f>
-        <v>44561</v>
+        <v>44926</v>
       </c>
       <c r="J1" s="38">
         <f t="shared" si="0"/>
-        <v>44196</v>
+        <v>44561</v>
       </c>
       <c r="K1" s="38">
         <f t="shared" si="0"/>
-        <v>43830</v>
+        <v>44196</v>
       </c>
       <c r="L1" s="38">
         <f t="shared" si="0"/>
-        <v>43465</v>
+        <v>43830</v>
       </c>
       <c r="M1" s="38">
         <f t="shared" si="0"/>
-        <v>43100</v>
+        <v>43465</v>
       </c>
       <c r="N1" s="38">
         <f t="shared" si="0"/>
-        <v>42735</v>
+        <v>43100</v>
       </c>
       <c r="O1" s="38">
         <f t="shared" si="0"/>
-        <v>42369</v>
+        <v>42735</v>
       </c>
       <c r="P1" s="38">
         <f t="shared" si="0"/>
-        <v>42004</v>
+        <v>42369</v>
       </c>
       <c r="Q1" s="38">
         <f t="shared" si="0"/>
-        <v>41639</v>
+        <v>42004</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
@@ -8977,30 +8988,30 @@
       </c>
       <c r="C4" s="196">
         <f>AVERAGE(G4:K4)</f>
-        <v>1583387.2</v>
+        <v>1627443.6666666667</v>
       </c>
       <c r="D4" s="57"/>
       <c r="E4" s="306"/>
       <c r="F4" s="57"/>
       <c r="G4" s="186">
         <f>Data!C36</f>
-        <v>1615585</v>
+        <v>1820108</v>
       </c>
       <c r="H4" s="186">
         <f>Data!D36</f>
-        <v>1446638</v>
+        <v>1615585</v>
       </c>
       <c r="I4" s="186">
         <f>Data!E36</f>
-        <v>1769157</v>
-      </c>
-      <c r="J4" s="186">
+        <v>1446638</v>
+      </c>
+      <c r="J4" s="186" t="str">
         <f>Data!F36</f>
-        <v>1702154</v>
-      </c>
-      <c r="K4" s="186">
+        <v/>
+      </c>
+      <c r="K4" s="186" t="str">
         <f>Data!G36</f>
-        <v>1383402</v>
+        <v/>
       </c>
       <c r="L4" s="186" t="str">
         <f>Data!H36</f>
@@ -9034,28 +9045,28 @@
       </c>
       <c r="C5" s="197">
         <f>C25</f>
-        <v>-1348785.0374623393</v>
+        <v>-1320779.7363240116</v>
       </c>
       <c r="E5" s="308"/>
       <c r="G5" s="186">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
-        <v>-1322360</v>
+        <v>-1464517</v>
       </c>
       <c r="H5" s="186">
         <f t="shared" si="1"/>
-        <v>-1280518</v>
+        <v>-1322360</v>
       </c>
       <c r="I5" s="186">
         <f t="shared" si="1"/>
-        <v>-981731</v>
-      </c>
-      <c r="J5" s="186">
+        <v>-1280518</v>
+      </c>
+      <c r="J5" s="186" t="str">
         <f t="shared" si="1"/>
-        <v>-959572</v>
-      </c>
-      <c r="K5" s="186">
+        <v/>
+      </c>
+      <c r="K5" s="186" t="str">
         <f t="shared" si="1"/>
-        <v>-783542</v>
+        <v/>
       </c>
       <c r="L5" s="186" t="str">
         <f t="shared" si="1"/>
@@ -9089,28 +9100,28 @@
       </c>
       <c r="C6" s="187">
         <f>C4+C5</f>
-        <v>234602.16253766068</v>
+        <v>306663.93034265516</v>
       </c>
       <c r="E6" s="308"/>
       <c r="G6" s="187">
         <f>IF(G4="","",G4+G5)</f>
-        <v>293225</v>
+        <v>355591</v>
       </c>
       <c r="H6" s="187">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
-        <v>166120</v>
+        <v>293225</v>
       </c>
       <c r="I6" s="187">
         <f t="shared" si="2"/>
-        <v>787426</v>
-      </c>
-      <c r="J6" s="187">
+        <v>166120</v>
+      </c>
+      <c r="J6" s="187" t="str">
         <f t="shared" si="2"/>
-        <v>742582</v>
-      </c>
-      <c r="K6" s="187">
+        <v/>
+      </c>
+      <c r="K6" s="187" t="str">
         <f t="shared" si="2"/>
-        <v>599860</v>
+        <v/>
       </c>
       <c r="L6" s="187" t="str">
         <f t="shared" si="2"/>
@@ -9144,28 +9155,28 @@
       </c>
       <c r="C7" s="197">
         <f>C35</f>
-        <v>-175999.5</v>
+        <v>-192887</v>
       </c>
       <c r="E7" s="308"/>
       <c r="G7" s="197">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
-        <v>-188071</v>
+        <v>-197703</v>
       </c>
       <c r="H7" s="197">
         <f t="shared" si="3"/>
-        <v>-163928</v>
+        <v>-188071</v>
       </c>
       <c r="I7" s="197">
         <f t="shared" si="3"/>
-        <v>-705390</v>
-      </c>
-      <c r="J7" s="197">
+        <v>-163928</v>
+      </c>
+      <c r="J7" s="197" t="str">
         <f t="shared" si="3"/>
-        <v>-456610</v>
-      </c>
-      <c r="K7" s="197">
+        <v/>
+      </c>
+      <c r="K7" s="197" t="str">
         <f t="shared" si="3"/>
-        <v>-396643</v>
+        <v/>
       </c>
       <c r="L7" s="197" t="str">
         <f t="shared" si="3"/>
@@ -9199,30 +9210,30 @@
       </c>
       <c r="C8" s="198">
         <f>C6+C7</f>
-        <v>58602.662537660683</v>
+        <v>113776.93034265516</v>
       </c>
       <c r="D8" s="60"/>
       <c r="E8" s="314"/>
       <c r="F8" s="60"/>
       <c r="G8" s="187">
         <f>IF(G$4="","",G6+G7)</f>
-        <v>105154</v>
+        <v>157888</v>
       </c>
       <c r="H8" s="187">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
-        <v>2192</v>
+        <v>105154</v>
       </c>
       <c r="I8" s="187">
         <f t="shared" si="4"/>
-        <v>82036</v>
-      </c>
-      <c r="J8" s="187">
+        <v>2192</v>
+      </c>
+      <c r="J8" s="187" t="str">
         <f t="shared" si="4"/>
-        <v>285972</v>
-      </c>
-      <c r="K8" s="187">
+        <v/>
+      </c>
+      <c r="K8" s="187" t="str">
         <f t="shared" si="4"/>
-        <v>203217</v>
+        <v/>
       </c>
       <c r="L8" s="187" t="str">
         <f t="shared" si="4"/>
@@ -9265,19 +9276,19 @@
       </c>
       <c r="H9" s="197">
         <f>IF(Data!D61="","",-Data!D61)</f>
-        <v>32106</v>
+        <v>35974</v>
       </c>
       <c r="I9" s="197">
         <f>IF(Data!E61="","",-Data!E61)</f>
-        <v>181.018</v>
-      </c>
-      <c r="J9" s="197">
+        <v>32106</v>
+      </c>
+      <c r="J9" s="197" t="str">
         <f>IF(Data!F61="","",-Data!F61)</f>
-        <v>186.14699999999999</v>
-      </c>
-      <c r="K9" s="197">
+        <v/>
+      </c>
+      <c r="K9" s="197" t="str">
         <f>IF(Data!G61="","",-Data!G61)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L9" s="197" t="str">
         <f>IF(Data!H61="","",-Data!H61)</f>
@@ -9316,23 +9327,23 @@
       <c r="E10" s="308"/>
       <c r="G10" s="197">
         <f>Data!C62</f>
-        <v>-15312</v>
+        <v>0</v>
       </c>
       <c r="H10" s="197">
         <f>Data!D62</f>
-        <v>-11600</v>
+        <v>-15312</v>
       </c>
       <c r="I10" s="197">
         <f>Data!E62</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="197">
+        <v>-11600</v>
+      </c>
+      <c r="J10" s="197" t="str">
         <f>Data!F62</f>
-        <v>0</v>
-      </c>
-      <c r="K10" s="197">
+        <v/>
+      </c>
+      <c r="K10" s="197" t="str">
         <f>Data!G62</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L10" s="197" t="str">
         <f>Data!H62</f>
@@ -9383,13 +9394,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J11" s="189">
+      <c r="J11" s="189" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="189">
+        <v/>
+      </c>
+      <c r="K11" s="189" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L11" s="189" t="str">
         <f t="shared" si="5"/>
@@ -9423,28 +9434,28 @@
       </c>
       <c r="C12" s="197">
         <f>C50</f>
-        <v>22288.09073065874</v>
+        <v>23207.710958398427</v>
       </c>
       <c r="E12" s="308"/>
       <c r="G12" s="197">
         <f>G50</f>
-        <v>22288.09073065874</v>
+        <v>23207.710958398427</v>
       </c>
       <c r="H12" s="197">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>13448.374088955678</v>
+        <v>21718.509213098328</v>
       </c>
       <c r="I12" s="197">
         <f t="shared" si="6"/>
-        <v>-1613</v>
-      </c>
-      <c r="J12" s="197">
+        <v>13098.390729815177</v>
+      </c>
+      <c r="J12" s="197" t="str">
         <f t="shared" si="6"/>
-        <v>-2645</v>
-      </c>
-      <c r="K12" s="197">
+        <v/>
+      </c>
+      <c r="K12" s="197" t="str">
         <f t="shared" si="6"/>
-        <v>-299</v>
+        <v/>
       </c>
       <c r="L12" s="197" t="str">
         <f t="shared" si="6"/>
@@ -9478,28 +9489,28 @@
       </c>
       <c r="C13" s="187">
         <f>SUM(C8:C12)</f>
-        <v>80890.753268319415</v>
+        <v>136984.64130105358</v>
       </c>
       <c r="E13" s="308"/>
       <c r="G13" s="187">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>148104.09073065873</v>
+        <v>217069.71095839841</v>
       </c>
       <c r="H13" s="187">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>36146.374088955679</v>
+        <v>147534.50921309832</v>
       </c>
       <c r="I13" s="187">
         <f t="shared" si="7"/>
-        <v>80604.017999999996</v>
-      </c>
-      <c r="J13" s="187">
+        <v>35796.390729815175</v>
+      </c>
+      <c r="J13" s="187" t="str">
         <f t="shared" si="7"/>
-        <v>283513.147</v>
-      </c>
-      <c r="K13" s="187">
+        <v/>
+      </c>
+      <c r="K13" s="187" t="str">
         <f t="shared" si="7"/>
-        <v>202918</v>
+        <v/>
       </c>
       <c r="L13" s="187" t="str">
         <f t="shared" si="7"/>
@@ -9533,28 +9544,28 @@
       </c>
       <c r="C14" s="197">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-20222.688317079854</v>
+        <v>-34246.160325263394</v>
       </c>
       <c r="E14" s="308"/>
       <c r="G14" s="197">
         <f>Data!C46</f>
-        <v>-44449</v>
+        <v>-47270</v>
       </c>
       <c r="H14" s="197">
         <f>Data!D46</f>
-        <v>-21017</v>
+        <v>-44449</v>
       </c>
       <c r="I14" s="197">
         <f>Data!E46</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="197">
+        <v>-21017</v>
+      </c>
+      <c r="J14" s="197" t="str">
         <f>Data!F46</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="197">
+        <v/>
+      </c>
+      <c r="K14" s="197" t="str">
         <f>Data!G46</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L14" s="197" t="str">
         <f>Data!H46</f>
@@ -9588,30 +9599,30 @@
       </c>
       <c r="C15" s="197">
         <f>-C4*C83</f>
-        <v>-2089.6737831682049</v>
+        <v>0</v>
       </c>
       <c r="D15" s="61"/>
       <c r="E15" s="315"/>
       <c r="F15" s="61"/>
       <c r="G15" s="186">
         <f>Data!C48</f>
-        <v>-2199</v>
+        <v>0</v>
       </c>
       <c r="H15" s="186">
         <f>Data!D48</f>
-        <v>-645</v>
+        <v>0</v>
       </c>
       <c r="I15" s="186">
         <f>Data!E48</f>
         <v>0</v>
       </c>
-      <c r="J15" s="186">
+      <c r="J15" s="186" t="str">
         <f>Data!F48</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="186">
+        <v/>
+      </c>
+      <c r="K15" s="186" t="str">
         <f>Data!G48</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L15" s="186" t="str">
         <f>Data!H48</f>
@@ -9645,30 +9656,30 @@
       </c>
       <c r="C16" s="200">
         <f>SUM(C13:C15)</f>
-        <v>58578.391168071357</v>
+        <v>102738.48097579018</v>
       </c>
       <c r="D16" s="62"/>
       <c r="E16" s="316"/>
       <c r="F16" s="62"/>
       <c r="G16" s="187">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>101456.09073065873</v>
+        <v>169799.71095839841</v>
       </c>
       <c r="H16" s="187">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>14484.374088955679</v>
+        <v>103085.50921309832</v>
       </c>
       <c r="I16" s="187">
         <f t="shared" si="8"/>
-        <v>80604.017999999996</v>
-      </c>
-      <c r="J16" s="187">
+        <v>14779.390729815175</v>
+      </c>
+      <c r="J16" s="187" t="str">
         <f t="shared" si="8"/>
-        <v>283513.147</v>
-      </c>
-      <c r="K16" s="187">
+        <v/>
+      </c>
+      <c r="K16" s="187" t="str">
         <f t="shared" si="8"/>
-        <v>202918</v>
+        <v/>
       </c>
       <c r="L16" s="187" t="str">
         <f t="shared" si="8"/>
@@ -9753,30 +9764,30 @@
       </c>
       <c r="C19" s="187">
         <f>C16+C17</f>
-        <v>58578.391168071357</v>
+        <v>102738.48097579018</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="305"/>
       <c r="F19" s="27"/>
       <c r="G19" s="189">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>101456.09073065873</v>
+        <v>169799.71095839841</v>
       </c>
       <c r="H19" s="189">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>14484.374088955679</v>
+        <v>103085.50921309832</v>
       </c>
       <c r="I19" s="189">
         <f t="shared" si="9"/>
-        <v>80604.017999999996</v>
-      </c>
-      <c r="J19" s="189">
+        <v>14779.390729815175</v>
+      </c>
+      <c r="J19" s="189" t="str">
         <f t="shared" si="9"/>
-        <v>283513.147</v>
-      </c>
-      <c r="K19" s="189">
+        <v/>
+      </c>
+      <c r="K19" s="189" t="str">
         <f t="shared" si="9"/>
-        <v>202918</v>
+        <v/>
       </c>
       <c r="L19" s="189" t="str">
         <f t="shared" si="9"/>
@@ -9873,30 +9884,30 @@
       </c>
       <c r="C23" s="203">
         <f>-C4*C28</f>
-        <v>-902304.82874495955</v>
+        <v>-865842.54650761362</v>
       </c>
       <c r="D23" s="59"/>
       <c r="E23" s="307"/>
       <c r="F23" s="59"/>
       <c r="G23" s="186">
         <f>Data!C37</f>
-        <v>-897327</v>
+        <v>-925767</v>
       </c>
       <c r="H23" s="186">
         <f>Data!D37</f>
-        <v>-845264</v>
+        <v>-897327</v>
       </c>
       <c r="I23" s="186">
         <f>Data!E37</f>
-        <v>-981731</v>
-      </c>
-      <c r="J23" s="186">
+        <v>-845264</v>
+      </c>
+      <c r="J23" s="186" t="str">
         <f>Data!F37</f>
-        <v>-959572</v>
-      </c>
-      <c r="K23" s="186">
+        <v/>
+      </c>
+      <c r="K23" s="186" t="str">
         <f>Data!G37</f>
-        <v>-783542</v>
+        <v/>
       </c>
       <c r="L23" s="186" t="str">
         <f>Data!H37</f>
@@ -9930,30 +9941,30 @@
       </c>
       <c r="C24" s="197">
         <f>-C4*C29</f>
-        <v>-446480.2087173796</v>
+        <v>-454937.18981639796</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="305"/>
       <c r="F24" s="27"/>
       <c r="G24" s="186">
         <f>Data!C40</f>
-        <v>-425033</v>
+        <v>-538750</v>
       </c>
       <c r="H24" s="186">
         <f>Data!D40</f>
-        <v>-435254</v>
+        <v>-425033</v>
       </c>
       <c r="I24" s="186">
         <f>Data!E40</f>
-        <v>0</v>
-      </c>
-      <c r="J24" s="186">
+        <v>-435254</v>
+      </c>
+      <c r="J24" s="186" t="str">
         <f>Data!F40</f>
-        <v>0</v>
-      </c>
-      <c r="K24" s="186">
+        <v/>
+      </c>
+      <c r="K24" s="186" t="str">
         <f>Data!G40</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L24" s="186" t="str">
         <f>Data!H40</f>
@@ -9987,30 +9998,30 @@
       </c>
       <c r="C25" s="187">
         <f>C23+C24</f>
-        <v>-1348785.0374623393</v>
+        <v>-1320779.7363240116</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="313"/>
       <c r="F25" s="9"/>
       <c r="G25" s="187">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
-        <v>-1322360</v>
+        <v>-1464517</v>
       </c>
       <c r="H25" s="187">
         <f t="shared" si="10"/>
-        <v>-1280518</v>
+        <v>-1322360</v>
       </c>
       <c r="I25" s="187">
         <f t="shared" si="10"/>
-        <v>-981731</v>
-      </c>
-      <c r="J25" s="187">
+        <v>-1280518</v>
+      </c>
+      <c r="J25" s="187" t="str">
         <f t="shared" si="10"/>
-        <v>-959572</v>
-      </c>
-      <c r="K25" s="187">
+        <v/>
+      </c>
+      <c r="K25" s="187" t="str">
         <f t="shared" si="10"/>
-        <v>-783542</v>
+        <v/>
       </c>
       <c r="L25" s="187" t="str">
         <f t="shared" si="10"/>
@@ -10055,7 +10066,7 @@
       </c>
       <c r="C28" s="64">
         <f>AVERAGE(G28:H28)</f>
-        <v>0.56985734679739708</v>
+        <v>0.53202612430882723</v>
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="306" t="s">
@@ -10064,23 +10075,23 @@
       <c r="F28" s="26"/>
       <c r="G28" s="13">
         <f t="shared" ref="G28:Q28" si="11">IF(G$4="","",ABS(G23/G$4))</f>
-        <v>0.55541924442229906</v>
+        <v>0.5086330041953554</v>
       </c>
       <c r="H28" s="13">
         <f t="shared" si="11"/>
-        <v>0.5842954491724951</v>
+        <v>0.55541924442229906</v>
       </c>
       <c r="I28" s="13">
         <f t="shared" si="11"/>
-        <v>0.55491457230760188</v>
-      </c>
-      <c r="J28" s="13">
+        <v>0.5842954491724951</v>
+      </c>
+      <c r="J28" s="13" t="str">
         <f t="shared" si="11"/>
-        <v>0.56373982612619067</v>
-      </c>
-      <c r="K28" s="13">
+        <v/>
+      </c>
+      <c r="K28" s="13" t="str">
         <f t="shared" si="11"/>
-        <v>0.56638778894348862</v>
+        <v/>
       </c>
       <c r="L28" s="13" t="str">
         <f t="shared" si="11"/>
@@ -10115,7 +10126,7 @@
       </c>
       <c r="C29" s="64">
         <f>AVERAGE(G29:H29)</f>
-        <v>0.28197790705733861</v>
+        <v>0.27954097529421784</v>
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="306" t="s">
@@ -10124,23 +10135,23 @@
       <c r="F29" s="26"/>
       <c r="G29" s="13">
         <f t="shared" ref="G29:Q29" si="12">IF(G$4="","",ABS(G24/G$4))</f>
-        <v>0.26308303184295473</v>
+        <v>0.29599891874548101</v>
       </c>
       <c r="H29" s="13">
         <f t="shared" si="12"/>
-        <v>0.30087278227172243</v>
+        <v>0.26308303184295473</v>
       </c>
       <c r="I29" s="13">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="J29" s="13">
+        <v>0.30087278227172243</v>
+      </c>
+      <c r="J29" s="13" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K29" s="13">
+        <v/>
+      </c>
+      <c r="K29" s="13" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L29" s="13" t="str">
         <f t="shared" si="12"/>
@@ -10174,28 +10185,28 @@
       </c>
       <c r="C30" s="72">
         <f>ABS(C25/$C$4)</f>
-        <v>0.8518352538547358</v>
+        <v>0.81156709960304507</v>
       </c>
       <c r="E30" s="308"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
-        <v>0.81850227626525374</v>
+        <v>0.80463192294083652</v>
       </c>
       <c r="H30" s="30">
         <f t="shared" si="13"/>
-        <v>0.88516823144421752</v>
+        <v>0.81850227626525374</v>
       </c>
       <c r="I30" s="30">
         <f t="shared" si="13"/>
-        <v>0.55491457230760188</v>
-      </c>
-      <c r="J30" s="30">
+        <v>0.88516823144421752</v>
+      </c>
+      <c r="J30" s="30" t="str">
         <f t="shared" si="13"/>
-        <v>0.56373982612619067</v>
-      </c>
-      <c r="K30" s="30">
+        <v/>
+      </c>
+      <c r="K30" s="30" t="str">
         <f t="shared" si="13"/>
-        <v>0.56638778894348862</v>
+        <v/>
       </c>
       <c r="L30" s="30" t="str">
         <f t="shared" si="13"/>
@@ -10240,30 +10251,30 @@
       </c>
       <c r="C33" s="204">
         <f>AVERAGE(G33:H33)</f>
-        <v>-175999.5</v>
+        <v>-192887</v>
       </c>
       <c r="E33" s="306" t="s">
         <v>346</v>
       </c>
       <c r="G33" s="197">
         <f>Data!C41</f>
-        <v>-188071</v>
+        <v>-197703</v>
       </c>
       <c r="H33" s="197">
         <f>Data!D41</f>
-        <v>-163928</v>
+        <v>-188071</v>
       </c>
       <c r="I33" s="197">
         <f>Data!E41</f>
-        <v>-705390</v>
-      </c>
-      <c r="J33" s="197">
+        <v>-163928</v>
+      </c>
+      <c r="J33" s="197" t="str">
         <f>Data!F41</f>
-        <v>-456610</v>
-      </c>
-      <c r="K33" s="197">
+        <v/>
+      </c>
+      <c r="K33" s="197" t="str">
         <f>Data!G41</f>
-        <v>-396643</v>
+        <v/>
       </c>
       <c r="L33" s="197" t="str">
         <f>Data!H41</f>
@@ -10316,13 +10327,13 @@
         <f>Data!E42</f>
         <v>0</v>
       </c>
-      <c r="J34" s="186">
+      <c r="J34" s="186" t="str">
         <f>Data!F42</f>
-        <v>0</v>
-      </c>
-      <c r="K34" s="186">
+        <v/>
+      </c>
+      <c r="K34" s="186" t="str">
         <f>Data!G42</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L34" s="186" t="str">
         <f>Data!H42</f>
@@ -10356,30 +10367,30 @@
       </c>
       <c r="C35" s="187">
         <f>C33+C34</f>
-        <v>-175999.5</v>
+        <v>-192887</v>
       </c>
       <c r="D35" s="59"/>
       <c r="E35" s="307"/>
       <c r="F35" s="59"/>
       <c r="G35" s="187">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
-        <v>-188071</v>
+        <v>-197703</v>
       </c>
       <c r="H35" s="187">
         <f t="shared" si="14"/>
-        <v>-163928</v>
+        <v>-188071</v>
       </c>
       <c r="I35" s="187">
         <f t="shared" si="14"/>
-        <v>-705390</v>
-      </c>
-      <c r="J35" s="187">
+        <v>-163928</v>
+      </c>
+      <c r="J35" s="187" t="str">
         <f t="shared" si="14"/>
-        <v>-456610</v>
-      </c>
-      <c r="K35" s="187">
+        <v/>
+      </c>
+      <c r="K35" s="187" t="str">
         <f t="shared" si="14"/>
-        <v>-396643</v>
+        <v/>
       </c>
       <c r="L35" s="187" t="str">
         <f t="shared" si="14"/>
@@ -10425,30 +10436,30 @@
       </c>
       <c r="C38" s="23">
         <f>ABS(C33/$C$4)</f>
-        <v>0.11115379737817763</v>
+        <v>0.11852146034343021</v>
       </c>
       <c r="D38" s="27"/>
       <c r="E38" s="305"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
-        <v>0.11641046432097352</v>
+        <v>0.10862157630206559</v>
       </c>
       <c r="H38" s="13">
         <f t="shared" si="15"/>
-        <v>0.11331653115706901</v>
+        <v>0.11641046432097352</v>
       </c>
       <c r="I38" s="13">
         <f t="shared" si="15"/>
-        <v>0.39871532034748752</v>
-      </c>
-      <c r="J38" s="13">
+        <v>0.11331653115706901</v>
+      </c>
+      <c r="J38" s="13" t="str">
         <f t="shared" si="15"/>
-        <v>0.2682542237658872</v>
-      </c>
-      <c r="K38" s="13">
+        <v/>
+      </c>
+      <c r="K38" s="13" t="str">
         <f t="shared" si="15"/>
-        <v>0.28671564736786559</v>
+        <v/>
       </c>
       <c r="L38" s="13" t="str">
         <f t="shared" si="15"/>
@@ -10500,13 +10511,13 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="J39" s="13">
+      <c r="J39" s="13" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K39" s="13">
+        <v/>
+      </c>
+      <c r="K39" s="13" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L39" s="13" t="str">
         <f t="shared" si="16"/>
@@ -10540,28 +10551,28 @@
       </c>
       <c r="C40" s="72">
         <f>ABS(C35/$C$4)</f>
-        <v>0.11115379737817763</v>
+        <v>0.11852146034343021</v>
       </c>
       <c r="E40" s="308"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
-        <v>0.11641046432097352</v>
+        <v>0.10862157630206559</v>
       </c>
       <c r="H40" s="30">
         <f t="shared" si="17"/>
-        <v>0.11331653115706901</v>
+        <v>0.11641046432097352</v>
       </c>
       <c r="I40" s="30">
         <f t="shared" si="17"/>
-        <v>0.39871532034748752</v>
-      </c>
-      <c r="J40" s="30">
+        <v>0.11331653115706901</v>
+      </c>
+      <c r="J40" s="30" t="str">
         <f t="shared" si="17"/>
-        <v>0.2682542237658872</v>
-      </c>
-      <c r="K40" s="30">
+        <v/>
+      </c>
+      <c r="K40" s="30" t="str">
         <f t="shared" si="17"/>
-        <v>0.28671564736786559</v>
+        <v/>
       </c>
       <c r="L40" s="30" t="str">
         <f t="shared" si="17"/>
@@ -10614,23 +10625,23 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.34877801945308878</v>
+        <v>0.26102219511349412</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>1.3437658127909475</v>
+        <v>0.3503438236989726</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="J43" s="6">
+        <v>1.3745234095959589</v>
+      </c>
+      <c r="J43" s="6" t="str">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="K43" s="6">
+        <v/>
+      </c>
+      <c r="K43" s="6" t="str">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -10697,28 +10708,28 @@
       </c>
       <c r="C47" s="197">
         <f>-BS!G31*Normalized_FCF!C54</f>
-        <v>-1003</v>
+        <v>-1880</v>
       </c>
       <c r="E47" s="308"/>
       <c r="G47" s="197">
         <f>Data!C51</f>
-        <v>-1003</v>
+        <v>-1880</v>
       </c>
       <c r="H47" s="197">
         <f>Data!D51</f>
-        <v>-863</v>
+        <v>-1003</v>
       </c>
       <c r="I47" s="197">
         <f>Data!E51</f>
-        <v>-1613</v>
-      </c>
-      <c r="J47" s="197">
+        <v>-863</v>
+      </c>
+      <c r="J47" s="197" t="str">
         <f>Data!F51</f>
-        <v>-2645</v>
-      </c>
-      <c r="K47" s="197">
+        <v/>
+      </c>
+      <c r="K47" s="197" t="str">
         <f>Data!G51</f>
-        <v>-299</v>
+        <v/>
       </c>
       <c r="L47" s="197" t="str">
         <f>Data!H51</f>
@@ -10752,28 +10763,28 @@
       </c>
       <c r="C48" s="197">
         <f>BS!D75*C53</f>
-        <v>23291.09073065874</v>
+        <v>25087.710958398427</v>
       </c>
       <c r="E48" s="308"/>
       <c r="G48" s="334">
         <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
-        <v>23291.09073065874</v>
+        <v>25087.710958398427</v>
       </c>
       <c r="H48" s="334">
         <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
-        <v>14311.374088955678</v>
+        <v>22721.509213098328</v>
       </c>
       <c r="I48" s="334">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="J48" s="334">
+        <v>13961.390729815177</v>
+      </c>
+      <c r="J48" s="334" t="str">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="K48" s="334">
+        <v/>
+      </c>
+      <c r="K48" s="334" t="str">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L48" s="334" t="str">
         <f t="shared" si="19"/>
@@ -10807,30 +10818,30 @@
       </c>
       <c r="C49" s="330">
         <f>BS!$C$66*C53</f>
-        <v>73805</v>
+        <v>81491</v>
       </c>
       <c r="D49" s="331"/>
       <c r="E49" s="332"/>
       <c r="F49" s="331"/>
       <c r="G49" s="330">
         <f>Data!C52</f>
-        <v>73805</v>
+        <v>81491</v>
       </c>
       <c r="H49" s="330">
         <f>Data!D52</f>
-        <v>45350</v>
+        <v>73805</v>
       </c>
       <c r="I49" s="330">
         <f>Data!E52</f>
-        <v>0</v>
-      </c>
-      <c r="J49" s="330">
+        <v>45350</v>
+      </c>
+      <c r="J49" s="330" t="str">
         <f>Data!F52</f>
-        <v>0</v>
-      </c>
-      <c r="K49" s="330">
+        <v/>
+      </c>
+      <c r="K49" s="330" t="str">
         <f>Data!G52</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L49" s="330" t="str">
         <f>Data!H52</f>
@@ -10864,28 +10875,28 @@
       </c>
       <c r="C50" s="187">
         <f>C47+C48</f>
-        <v>22288.09073065874</v>
+        <v>23207.710958398427</v>
       </c>
       <c r="E50" s="308"/>
       <c r="G50" s="187">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>22288.09073065874</v>
+        <v>23207.710958398427</v>
       </c>
       <c r="H50" s="187">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>13448.374088955678</v>
+        <v>21718.509213098328</v>
       </c>
       <c r="I50" s="187">
         <f t="shared" si="20"/>
-        <v>-1613</v>
-      </c>
-      <c r="J50" s="187">
+        <v>13098.390729815177</v>
+      </c>
+      <c r="J50" s="187" t="str">
         <f t="shared" si="20"/>
-        <v>-2645</v>
-      </c>
-      <c r="K50" s="187">
+        <v/>
+      </c>
+      <c r="K50" s="187" t="str">
         <f t="shared" si="20"/>
-        <v>-299</v>
+        <v/>
       </c>
       <c r="L50" s="187" t="str">
         <f t="shared" si="20"/>
@@ -10933,14 +10944,14 @@
       </c>
       <c r="C53" s="89">
         <f>G53</f>
-        <v>2.7696969151119136E-2</v>
+        <v>3.0096689367862788E-2</v>
       </c>
       <c r="E53" s="305" t="s">
         <v>348</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
-        <v>2.7696969151119136E-2</v>
+        <v>3.0096689367862788E-2</v>
       </c>
       <c r="H53" s="173"/>
       <c r="I53" s="173"/>
@@ -10960,14 +10971,14 @@
       </c>
       <c r="C54" s="84">
         <f>G54</f>
-        <v>2.9500867672578604E-2</v>
+        <v>5.5295743992470364E-2</v>
       </c>
       <c r="E54" s="305" t="s">
         <v>349</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
-        <v>2.9500867672578604E-2</v>
+        <v>5.5295743992470364E-2</v>
       </c>
       <c r="H54" s="173"/>
       <c r="I54" s="173"/>
@@ -10987,28 +10998,28 @@
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
-        <v>58.427380396471271</v>
+        <v>60.519643799284658</v>
       </c>
       <c r="E55" s="308"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
-        <v>104.839481555334</v>
+        <v>83.982978723404258</v>
       </c>
       <c r="H55" s="42">
         <f t="shared" si="21"/>
-        <v>2.5399768250289689</v>
+        <v>104.839481555334</v>
       </c>
       <c r="I55" s="42">
         <f t="shared" si="21"/>
-        <v>50.859268443893363</v>
-      </c>
-      <c r="J55" s="42">
+        <v>2.5399768250289689</v>
+      </c>
+      <c r="J55" s="42" t="str">
         <f t="shared" si="21"/>
-        <v>108.1179584120983</v>
-      </c>
-      <c r="K55" s="42">
+        <v/>
+      </c>
+      <c r="K55" s="42" t="str">
         <f t="shared" si="21"/>
-        <v>679.65551839464888</v>
+        <v/>
       </c>
       <c r="L55" s="42" t="str">
         <f t="shared" si="21"/>
@@ -11071,13 +11082,13 @@
         <f>Data!E56</f>
         <v>0</v>
       </c>
-      <c r="J58" s="197">
+      <c r="J58" s="197" t="str">
         <f>Data!F56</f>
-        <v>0</v>
-      </c>
-      <c r="K58" s="197">
+        <v/>
+      </c>
+      <c r="K58" s="197" t="str">
         <f>Data!G56</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L58" s="197" t="str">
         <f>Data!H56</f>
@@ -11126,13 +11137,13 @@
         <f>Data!E55</f>
         <v>0</v>
       </c>
-      <c r="J59" s="197">
+      <c r="J59" s="197" t="str">
         <f>Data!F55</f>
-        <v>0</v>
-      </c>
-      <c r="K59" s="197">
+        <v/>
+      </c>
+      <c r="K59" s="197" t="str">
         <f>Data!G55</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L59" s="197" t="str">
         <f>Data!H55</f>
@@ -11181,13 +11192,13 @@
         <f>Data!E57</f>
         <v>0</v>
       </c>
-      <c r="J60" s="197">
+      <c r="J60" s="197" t="str">
         <f>Data!F57</f>
-        <v>0</v>
-      </c>
-      <c r="K60" s="197">
+        <v/>
+      </c>
+      <c r="K60" s="197" t="str">
         <f>Data!G57</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L60" s="197" t="str">
         <f>Data!H57</f>
@@ -11236,13 +11247,13 @@
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J61" s="187">
+      <c r="J61" s="187" t="str">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="K61" s="187">
+        <v/>
+      </c>
+      <c r="K61" s="187" t="str">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L61" s="187" t="str">
         <f t="shared" si="22"/>
@@ -11282,23 +11293,23 @@
       </c>
       <c r="G62" s="197">
         <f>Data!C58</f>
-        <v>39310</v>
+        <v>5020</v>
       </c>
       <c r="H62" s="197">
         <f>Data!D58</f>
-        <v>39794</v>
+        <v>39310</v>
       </c>
       <c r="I62" s="197">
         <f>Data!E58</f>
-        <v>-74687.603451000003</v>
-      </c>
-      <c r="J62" s="197">
+        <v>39794</v>
+      </c>
+      <c r="J62" s="197" t="str">
         <f>Data!F58</f>
-        <v>-273680.96301000001</v>
-      </c>
-      <c r="K62" s="197">
+        <v/>
+      </c>
+      <c r="K62" s="197" t="str">
         <f>Data!G58</f>
-        <v>-202918</v>
+        <v/>
       </c>
       <c r="L62" s="197" t="str">
         <f>Data!H58</f>
@@ -11337,23 +11348,23 @@
       <c r="E63" s="308"/>
       <c r="G63" s="187">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
-        <v>39310</v>
+        <v>5020</v>
       </c>
       <c r="H63" s="187">
         <f t="shared" si="23"/>
-        <v>39794</v>
+        <v>39310</v>
       </c>
       <c r="I63" s="187">
         <f t="shared" si="23"/>
-        <v>-74687.603451000003</v>
-      </c>
-      <c r="J63" s="187">
+        <v>39794</v>
+      </c>
+      <c r="J63" s="187" t="str">
         <f t="shared" si="23"/>
-        <v>-273680.96301000001</v>
-      </c>
-      <c r="K63" s="187">
+        <v/>
+      </c>
+      <c r="K63" s="187" t="str">
         <f t="shared" si="23"/>
-        <v>-202918</v>
+        <v/>
       </c>
       <c r="L63" s="187" t="str">
         <f t="shared" si="23"/>
@@ -11550,30 +11561,30 @@
       </c>
       <c r="C73" s="79">
         <f>ABS(C5/C$4)</f>
-        <v>0.8518352538547358</v>
+        <v>0.81156709960304507</v>
       </c>
       <c r="D73" s="27"/>
       <c r="E73" s="305"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
-        <v>0.81850227626525374</v>
+        <v>0.80463192294083652</v>
       </c>
       <c r="H73" s="6">
         <f t="shared" si="24"/>
-        <v>0.88516823144421752</v>
+        <v>0.81850227626525374</v>
       </c>
       <c r="I73" s="6">
         <f t="shared" si="24"/>
-        <v>0.55491457230760188</v>
-      </c>
-      <c r="J73" s="6">
+        <v>0.88516823144421752</v>
+      </c>
+      <c r="J73" s="6" t="str">
         <f t="shared" si="24"/>
-        <v>0.56373982612619067</v>
-      </c>
-      <c r="K73" s="6">
+        <v/>
+      </c>
+      <c r="K73" s="6" t="str">
         <f t="shared" si="24"/>
-        <v>0.56638778894348862</v>
+        <v/>
       </c>
       <c r="L73" s="6" t="str">
         <f t="shared" si="24"/>
@@ -11607,30 +11618,30 @@
       </c>
       <c r="C74" s="80">
         <f>ABS(C6/C$4)</f>
-        <v>0.1481647461452642</v>
+        <v>0.18843290039695496</v>
       </c>
       <c r="D74" s="27"/>
       <c r="E74" s="305"/>
       <c r="F74" s="27"/>
       <c r="G74" s="66">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
-        <v>0.18149772373474624</v>
+        <v>0.19536807705916351</v>
       </c>
       <c r="H74" s="66">
         <f t="shared" si="25"/>
-        <v>0.11483176855578245</v>
+        <v>0.18149772373474624</v>
       </c>
       <c r="I74" s="66">
         <f t="shared" si="25"/>
-        <v>0.44508542769239812</v>
-      </c>
-      <c r="J74" s="66">
+        <v>0.11483176855578245</v>
+      </c>
+      <c r="J74" s="66" t="str">
         <f t="shared" si="25"/>
-        <v>0.43626017387380928</v>
-      </c>
-      <c r="K74" s="66">
+        <v/>
+      </c>
+      <c r="K74" s="66" t="str">
         <f t="shared" si="25"/>
-        <v>0.43361221105651143</v>
+        <v/>
       </c>
       <c r="L74" s="66" t="str">
         <f t="shared" si="25"/>
@@ -11664,30 +11675,30 @@
       </c>
       <c r="C75" s="79">
         <f>ABS(C7/C$4)</f>
-        <v>0.11115379737817763</v>
+        <v>0.11852146034343021</v>
       </c>
       <c r="D75" s="27"/>
       <c r="E75" s="305"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
-        <v>0.11641046432097352</v>
+        <v>0.10862157630206559</v>
       </c>
       <c r="H75" s="6">
         <f t="shared" si="26"/>
-        <v>0.11331653115706901</v>
+        <v>0.11641046432097352</v>
       </c>
       <c r="I75" s="6">
         <f t="shared" si="26"/>
-        <v>0.39871532034748752</v>
-      </c>
-      <c r="J75" s="6">
+        <v>0.11331653115706901</v>
+      </c>
+      <c r="J75" s="6" t="str">
         <f t="shared" si="26"/>
-        <v>0.2682542237658872</v>
-      </c>
-      <c r="K75" s="6">
+        <v/>
+      </c>
+      <c r="K75" s="6" t="str">
         <f t="shared" si="26"/>
-        <v>0.28671564736786559</v>
+        <v/>
       </c>
       <c r="L75" s="6" t="str">
         <f t="shared" si="26"/>
@@ -11721,30 +11732,30 @@
       </c>
       <c r="C76" s="80">
         <f>ABS(C8/C$4)</f>
-        <v>3.7010948767086591E-2</v>
+        <v>6.9911440053524732E-2</v>
       </c>
       <c r="D76" s="27"/>
       <c r="E76" s="305"/>
       <c r="F76" s="27"/>
       <c r="G76" s="66">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
-        <v>6.5087259413772719E-2</v>
+        <v>8.674650075709793E-2</v>
       </c>
       <c r="H76" s="66">
         <f t="shared" si="27"/>
-        <v>1.5152373987134308E-3</v>
+        <v>6.5087259413772719E-2</v>
       </c>
       <c r="I76" s="66">
         <f t="shared" si="27"/>
-        <v>4.6370107344910601E-2</v>
-      </c>
-      <c r="J76" s="66">
+        <v>1.5152373987134308E-3</v>
+      </c>
+      <c r="J76" s="66" t="str">
         <f t="shared" si="27"/>
-        <v>0.16800595010792208</v>
-      </c>
-      <c r="K76" s="66">
+        <v/>
+      </c>
+      <c r="K76" s="66" t="str">
         <f t="shared" si="27"/>
-        <v>0.14689656368864581</v>
+        <v/>
       </c>
       <c r="L76" s="66" t="str">
         <f t="shared" si="27"/>
@@ -11778,30 +11789,30 @@
       </c>
       <c r="C77" s="79">
         <f>ABS(C9/C$4)</f>
-        <v>2.2719648106287585E-2</v>
+        <v>2.2104605361660239E-2</v>
       </c>
       <c r="D77" s="27"/>
       <c r="E77" s="305"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
-        <v>2.2266856897037297E-2</v>
+        <v>1.9764761211972036E-2</v>
       </c>
       <c r="H77" s="6">
         <f t="shared" si="28"/>
-        <v>2.2193527337177648E-2</v>
+        <v>2.2266856897037297E-2</v>
       </c>
       <c r="I77" s="6">
         <f t="shared" si="28"/>
-        <v>1.0231878798772523E-4</v>
-      </c>
-      <c r="J77" s="6">
+        <v>2.2193527337177648E-2</v>
+      </c>
+      <c r="J77" s="6" t="str">
         <f t="shared" si="28"/>
-        <v>1.0935967015910428E-4</v>
-      </c>
-      <c r="K77" s="6">
+        <v/>
+      </c>
+      <c r="K77" s="6" t="str">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L77" s="6" t="str">
         <f t="shared" si="28"/>
@@ -11835,7 +11846,7 @@
       </c>
       <c r="C78" s="90">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
-        <v>2.2719648106287585E-2</v>
+        <v>2.2104605361660239E-2</v>
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="306" t="s">
@@ -11844,23 +11855,23 @@
       <c r="F78" s="27"/>
       <c r="G78" s="6">
         <f t="shared" ref="G78:Q78" si="29">IF(G$4="","",-G10/G$4)</f>
-        <v>9.4776814590380575E-3</v>
+        <v>0</v>
       </c>
       <c r="H78" s="6">
         <f t="shared" si="29"/>
-        <v>8.0185920734834829E-3</v>
+        <v>9.4776814590380575E-3</v>
       </c>
       <c r="I78" s="6">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="J78" s="6">
+        <v>8.0185920734834829E-3</v>
+      </c>
+      <c r="J78" s="6" t="str">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="K78" s="6">
+        <v/>
+      </c>
+      <c r="K78" s="6" t="str">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L78" s="6" t="str">
         <f t="shared" si="29"/>
@@ -11911,13 +11922,13 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="J79" s="66">
+      <c r="J79" s="66" t="str">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="K79" s="66">
+        <v/>
+      </c>
+      <c r="K79" s="66" t="str">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L79" s="66" t="str">
         <f t="shared" si="30"/>
@@ -11951,30 +11962,30 @@
       </c>
       <c r="C80" s="79">
         <f>ABS(C12/C$4)</f>
-        <v>1.4076209995040214E-2</v>
+        <v>1.42602238306242E-2</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="305"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>1.379567817890036E-2</v>
+        <v>1.275073290068415E-2</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>9.296295333701781E-3</v>
+        <v>1.3443123830128609E-2</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>9.1173366750378854E-4</v>
-      </c>
-      <c r="J80" s="6">
+        <v>9.0543665587487516E-3</v>
+      </c>
+      <c r="J80" s="6" t="str">
         <f t="shared" si="31"/>
-        <v>1.5539134531893119E-3</v>
-      </c>
-      <c r="K80" s="6">
+        <v/>
+      </c>
+      <c r="K80" s="6" t="str">
         <f t="shared" si="31"/>
-        <v>2.1613384974143452E-4</v>
+        <v/>
       </c>
       <c r="L80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -12008,30 +12019,30 @@
       </c>
       <c r="C81" s="80">
         <f>C13/C4</f>
-        <v>5.10871587621268E-2</v>
+        <v>8.4171663884148928E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="305"/>
       <c r="F81" s="27"/>
       <c r="G81" s="66">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>9.1672113030672311E-2</v>
+        <v>0.11926199486975411</v>
       </c>
       <c r="H81" s="66">
         <f t="shared" si="32"/>
-        <v>2.4986467996109377E-2</v>
+        <v>9.1319558681900559E-2</v>
       </c>
       <c r="I81" s="66">
         <f t="shared" si="32"/>
-        <v>4.5560692465394535E-2</v>
-      </c>
-      <c r="J81" s="66">
+        <v>2.4744539221156346E-2</v>
+      </c>
+      <c r="J81" s="66" t="str">
         <f t="shared" si="32"/>
-        <v>0.16656139632489186</v>
-      </c>
-      <c r="K81" s="66">
+        <v/>
+      </c>
+      <c r="K81" s="66" t="str">
         <f t="shared" si="32"/>
-        <v>0.14668042983890439</v>
+        <v/>
       </c>
       <c r="L81" s="66" t="str">
         <f t="shared" si="32"/>
@@ -12065,30 +12076,30 @@
       </c>
       <c r="C82" s="79">
         <f>ABS(C14/C$4)</f>
-        <v>1.27717896905317E-2</v>
+        <v>2.1042915971037232E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="305"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>2.7512634742214121E-2</v>
+        <v>2.5970986337074502E-2</v>
       </c>
       <c r="H82" s="6">
         <f t="shared" si="33"/>
-        <v>1.4528168069689861E-2</v>
+        <v>2.7512634742214121E-2</v>
       </c>
       <c r="I82" s="6">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="J82" s="6">
+        <v>1.4528168069689861E-2</v>
+      </c>
+      <c r="J82" s="6" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K82" s="6">
+        <v/>
+      </c>
+      <c r="K82" s="6" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L82" s="6" t="str">
         <f t="shared" si="33"/>
@@ -12123,30 +12134,30 @@
       </c>
       <c r="C83" s="304">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
-        <v>1.3197490690642218E-3</v>
+        <v>0</v>
       </c>
       <c r="D83" s="27"/>
       <c r="E83" s="305"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
-        <v>1.3611168709786237E-3</v>
+        <v>0</v>
       </c>
       <c r="H83" s="6">
         <f t="shared" si="34"/>
-        <v>4.4586136960317649E-4</v>
+        <v>0</v>
       </c>
       <c r="I83" s="6">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="J83" s="6">
+      <c r="J83" s="6" t="str">
         <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="K83" s="6">
+        <v/>
+      </c>
+      <c r="K83" s="6" t="str">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L83" s="6" t="str">
         <f t="shared" si="34"/>
@@ -12180,30 +12191,30 @@
       </c>
       <c r="C84" s="80">
         <f>ABS(C16/C$4)</f>
-        <v>3.6995620002530878E-2</v>
+        <v>6.3128747913111696E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="305"/>
       <c r="F84" s="27"/>
       <c r="G84" s="66">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>6.2798361417479576E-2</v>
+        <v>9.3291008532679603E-2</v>
       </c>
       <c r="H84" s="66">
         <f t="shared" si="35"/>
-        <v>1.0012438556816342E-2</v>
+        <v>6.3806923939686441E-2</v>
       </c>
       <c r="I84" s="66">
         <f t="shared" si="35"/>
-        <v>4.5560692465394535E-2</v>
-      </c>
-      <c r="J84" s="66">
+        <v>1.0216371151466487E-2</v>
+      </c>
+      <c r="J84" s="66" t="str">
         <f t="shared" si="35"/>
-        <v>0.16656139632489186</v>
-      </c>
-      <c r="K84" s="66">
+        <v/>
+      </c>
+      <c r="K84" s="66" t="str">
         <f t="shared" si="35"/>
-        <v>0.14668042983890439</v>
+        <v/>
       </c>
       <c r="L84" s="66" t="str">
         <f t="shared" si="35"/>
@@ -12287,30 +12298,30 @@
       </c>
       <c r="C87" s="80">
         <f>ABS(C19/C$4)</f>
-        <v>3.6995620002530878E-2</v>
+        <v>6.3128747913111696E-2</v>
       </c>
       <c r="D87" s="77"/>
       <c r="E87" s="305"/>
       <c r="F87" s="77"/>
       <c r="G87" s="66">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>6.2798361417479576E-2</v>
+        <v>9.3291008532679603E-2</v>
       </c>
       <c r="H87" s="66">
         <f t="shared" si="36"/>
-        <v>1.0012438556816342E-2</v>
+        <v>6.3806923939686441E-2</v>
       </c>
       <c r="I87" s="66">
         <f t="shared" si="36"/>
-        <v>4.5560692465394535E-2</v>
-      </c>
-      <c r="J87" s="66">
+        <v>1.0216371151466487E-2</v>
+      </c>
+      <c r="J87" s="66" t="str">
         <f t="shared" si="36"/>
-        <v>0.16656139632489186</v>
-      </c>
-      <c r="K87" s="66">
+        <v/>
+      </c>
+      <c r="K87" s="66" t="str">
         <f t="shared" si="36"/>
-        <v>0.14668042983890439</v>
+        <v/>
       </c>
       <c r="L87" s="66" t="str">
         <f t="shared" si="36"/>
@@ -12356,28 +12367,28 @@
       </c>
       <c r="C90" s="117">
         <f>G90</f>
-        <v>0.1178</v>
+        <v>0.11510561128533152</v>
       </c>
       <c r="E90" s="308"/>
       <c r="G90" s="116">
         <f>Data!C65</f>
-        <v>0.1178</v>
+        <v>0.11510561128533152</v>
       </c>
       <c r="H90" s="116">
         <f>Data!D65</f>
-        <v>0</v>
+        <v>9.9066304794752549E-2</v>
       </c>
       <c r="I90" s="116">
         <f>Data!E65</f>
-        <v>0</v>
-      </c>
-      <c r="J90" s="116">
+        <v>3.6607358343203798E-2</v>
+      </c>
+      <c r="J90" s="116" t="str">
         <f>Data!F65</f>
-        <v>0</v>
-      </c>
-      <c r="K90" s="116">
+        <v/>
+      </c>
+      <c r="K90" s="116" t="str">
         <f>Data!G65</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L90" s="116" t="str">
         <f>Data!H65</f>
@@ -12412,28 +12423,28 @@
       </c>
       <c r="C91" s="76">
         <f>C90*Common_Shares/$C$3</f>
-        <v>157066.6863</v>
+        <v>153474.16756471057</v>
       </c>
       <c r="E91" s="308"/>
       <c r="G91" s="76">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
-        <v>157066.6863</v>
+        <v>153474.16756471057</v>
       </c>
       <c r="H91" s="76">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>132088.4229040542</v>
       </c>
       <c r="I91" s="76">
         <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="J91" s="76">
+        <v>48809.817225498125</v>
+      </c>
+      <c r="J91" s="76" t="str">
         <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="K91" s="76">
+        <v/>
+      </c>
+      <c r="K91" s="76" t="str">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L91" s="76" t="str">
         <f t="shared" si="37"/>
@@ -12467,28 +12478,28 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>2.6813076147712724</v>
+        <v>1.4938333339858898</v>
       </c>
       <c r="E92" s="308"/>
       <c r="G92" s="174">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>1.5481247618437604</v>
+        <v>0.90385411552503969</v>
       </c>
       <c r="H92" s="174">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>1.2813481149033379</v>
       </c>
       <c r="I92" s="174">
         <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="J92" s="174">
+        <v>3.3025594977357038</v>
+      </c>
+      <c r="J92" s="174" t="str">
         <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="K92" s="174">
+        <v/>
+      </c>
+      <c r="K92" s="174" t="str">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L92" s="174" t="str">
         <f t="shared" si="38"/>
@@ -12522,28 +12533,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.9494949494949496E-2</v>
+        <v>5.6424319257515447E-2</v>
       </c>
       <c r="E93" s="308"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.9494949494949496E-2</v>
+        <v>5.6424319257515447E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>4.8561914115074781E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="J93" s="23">
+        <v>1.7944783501570489E-2</v>
+      </c>
+      <c r="J93" s="23" t="str">
         <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="K93" s="23">
+        <v/>
+      </c>
+      <c r="K93" s="23" t="str">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -12602,26 +12613,26 @@
       </c>
       <c r="C96" s="79">
         <f>C4/G4-1</f>
-        <v>-1.992949922164422E-2</v>
+        <v>-0.10585324240832594</v>
       </c>
       <c r="D96" s="27"/>
       <c r="E96" s="305"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
-        <v>0.11678595474472542</v>
+        <v>0.12659377253440707</v>
       </c>
       <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v>-0.18230094898304672</v>
-      </c>
-      <c r="I96" s="6">
+        <v>0.11678595474472542</v>
+      </c>
+      <c r="I96" s="6" t="str">
         <f t="shared" si="40"/>
-        <v>3.9363653347464389E-2</v>
-      </c>
-      <c r="J96" s="6">
+        <v/>
+      </c>
+      <c r="J96" s="6" t="str">
         <f t="shared" si="40"/>
-        <v>0.2304116952266948</v>
+        <v/>
       </c>
       <c r="K96" s="6" t="str">
         <f t="shared" si="40"/>
@@ -12659,26 +12670,26 @@
       </c>
       <c r="C97" s="79">
         <f>C13/G13-1</f>
-        <v>-0.4538249897808232</v>
+        <v>-0.36893709999315938</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="305"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>3.0973429414020011</v>
+        <v>0.47131482739989794</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.55155617566166892</v>
-      </c>
-      <c r="I97" s="6">
+        <v>3.1214911952063185</v>
+      </c>
+      <c r="I97" s="6" t="str">
         <f t="shared" si="41"/>
-        <v>-0.71569566049083433</v>
-      </c>
-      <c r="J97" s="6">
+        <v/>
+      </c>
+      <c r="J97" s="6" t="str">
         <f t="shared" si="41"/>
-        <v>0.39718086616268633</v>
+        <v/>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -12752,30 +12763,30 @@
       </c>
       <c r="C101" s="205">
         <f>BS!G32</f>
-        <v>3670169</v>
+        <v>3801703</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="309"/>
       <c r="F101" s="26"/>
       <c r="G101" s="186">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
-        <v>3670169</v>
+        <v>3801703</v>
       </c>
       <c r="H101" s="186">
         <f t="shared" si="42"/>
-        <v>3559477</v>
+        <v>3670169</v>
       </c>
       <c r="I101" s="186">
         <f t="shared" si="42"/>
-        <v>3413258</v>
-      </c>
-      <c r="J101" s="186">
+        <v>3559477</v>
+      </c>
+      <c r="J101" s="186" t="str">
         <f t="shared" si="42"/>
-        <v>1603329</v>
-      </c>
-      <c r="K101" s="186">
+        <v/>
+      </c>
+      <c r="K101" s="186" t="str">
         <f t="shared" si="42"/>
-        <v>1218998</v>
+        <v/>
       </c>
       <c r="L101" s="186" t="str">
         <f t="shared" si="42"/>
@@ -12809,7 +12820,7 @@
       </c>
       <c r="C102" s="206">
         <f>BS!C4</f>
-        <v>180994</v>
+        <v>109763</v>
       </c>
       <c r="D102" s="91"/>
       <c r="E102" s="310"/>
@@ -12822,13 +12833,13 @@
         <f>IF(H$4="","",Data!E77)</f>
         <v>0</v>
       </c>
-      <c r="I102" s="188">
+      <c r="I102" s="188" t="str">
         <f>IF(I$4="","",Data!F77)</f>
-        <v>0</v>
-      </c>
-      <c r="J102" s="188">
+        <v/>
+      </c>
+      <c r="J102" s="188" t="str">
         <f>IF(J$4="","",Data!G77)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="K102" s="188" t="str">
         <f>IF(K$4="","",Data!H77)</f>
@@ -12866,7 +12877,7 @@
       </c>
       <c r="C103" s="206">
         <f>BS!C6+BS!C7</f>
-        <v>158110</v>
+        <v>318027</v>
       </c>
       <c r="D103" s="91"/>
       <c r="E103" s="310"/>
@@ -12879,13 +12890,13 @@
         <f>IF(H$4="","",Data!E78)</f>
         <v>0</v>
       </c>
-      <c r="I103" s="188">
+      <c r="I103" s="188" t="str">
         <f>IF(I$4="","",Data!F78)</f>
-        <v>0</v>
-      </c>
-      <c r="J103" s="188">
+        <v/>
+      </c>
+      <c r="J103" s="188" t="str">
         <f>IF(J$4="","",Data!G78)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="K103" s="188" t="str">
         <f>IF(K$4="","",Data!H78)</f>
@@ -12934,19 +12945,19 @@
       </c>
       <c r="H104" s="186">
         <f>Data!D79</f>
-        <v>734909</v>
+        <v>642877</v>
       </c>
       <c r="I104" s="186">
         <f>Data!E79</f>
-        <v>677999</v>
-      </c>
-      <c r="J104" s="186">
+        <v>734909</v>
+      </c>
+      <c r="J104" s="186" t="str">
         <f>Data!F79</f>
-        <v>1352795</v>
-      </c>
-      <c r="K104" s="186">
+        <v/>
+      </c>
+      <c r="K104" s="186" t="str">
         <f>Data!G79</f>
-        <v>1205068</v>
+        <v/>
       </c>
       <c r="L104" s="186" t="str">
         <f>Data!H79</f>
@@ -12980,30 +12991,30 @@
       </c>
       <c r="C105" s="205">
         <f>BS!G27</f>
-        <v>3027292</v>
+        <v>3158826</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="309"/>
       <c r="F105" s="26"/>
       <c r="G105" s="186">
         <f>Data!C80</f>
-        <v>3027292</v>
+        <v>3158826</v>
       </c>
       <c r="H105" s="186">
         <f>Data!D80</f>
-        <v>2824568</v>
+        <v>3027292</v>
       </c>
       <c r="I105" s="186">
         <f>Data!E80</f>
-        <v>2735259</v>
-      </c>
-      <c r="J105" s="186">
+        <v>2824568</v>
+      </c>
+      <c r="J105" s="186" t="str">
         <f>Data!F80</f>
-        <v>250534</v>
-      </c>
-      <c r="K105" s="186">
+        <v/>
+      </c>
+      <c r="K105" s="186" t="str">
         <f>Data!G80</f>
-        <v>13930</v>
+        <v/>
       </c>
       <c r="L105" s="186" t="str">
         <f>Data!H80</f>
@@ -13064,7 +13075,7 @@
       </c>
       <c r="C108" s="97">
         <f>C102/C$4</f>
-        <v>0.11430811111773545</v>
+        <v>6.7445038036134788E-2</v>
       </c>
       <c r="D108" s="26"/>
       <c r="E108" s="309"/>
@@ -13077,17 +13088,17 @@
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
-      <c r="I108" s="97">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="J108" s="97">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="K108" s="97" t="e">
+      <c r="I108" s="97" t="e">
         <f t="shared" si="43"/>
         <v>#VALUE!</v>
+      </c>
+      <c r="J108" s="97" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="K108" s="97" t="str">
+        <f t="shared" si="43"/>
+        <v/>
       </c>
       <c r="L108" s="97" t="str">
         <f t="shared" si="43"/>
@@ -13121,7 +13132,7 @@
       </c>
       <c r="C109" s="97">
         <f>C103/C$4</f>
-        <v>9.9855550177492911E-2</v>
+        <v>0.19541505891345751</v>
       </c>
       <c r="D109" s="26"/>
       <c r="E109" s="309"/>
@@ -13134,17 +13145,17 @@
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
-      <c r="I109" s="97">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="J109" s="97">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="K109" s="97" t="e">
+      <c r="I109" s="97" t="e">
         <f t="shared" si="44"/>
         <v>#VALUE!</v>
+      </c>
+      <c r="J109" s="97" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="K109" s="97" t="str">
+        <f t="shared" si="44"/>
+        <v/>
       </c>
       <c r="L109" s="97" t="str">
         <f t="shared" si="44"/>
@@ -13228,13 +13239,13 @@
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>0</v>
       </c>
-      <c r="J113" s="340">
+      <c r="J113" s="340" t="str">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
-        <v>0</v>
-      </c>
-      <c r="K113" s="340" t="e">
+        <v/>
+      </c>
+      <c r="K113" s="340" t="str">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
-        <v>#DIV/0!</v>
+        <v/>
       </c>
       <c r="L113" s="340" t="str">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
@@ -13280,13 +13291,13 @@
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>0</v>
       </c>
-      <c r="J114" s="340">
+      <c r="J114" s="340" t="str">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>0</v>
-      </c>
-      <c r="K114" s="340">
+        <v/>
+      </c>
+      <c r="K114" s="340" t="str">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L114" s="340" t="str">
         <f>IF(L$4="","",Data!H$22/L19)</f>
@@ -13378,28 +13389,28 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>5.10871587621268E-2</v>
+        <v>8.4171663884148928E-2</v>
       </c>
       <c r="E117" s="308"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>9.1672113030672311E-2</v>
+        <v>0.11926199486975411</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>2.4986467996109377E-2</v>
+        <v>9.1319558681900559E-2</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>4.5560692465394535E-2</v>
-      </c>
-      <c r="J117" s="23">
+        <v>2.4744539221156346E-2</v>
+      </c>
+      <c r="J117" s="23" t="str">
         <f t="shared" si="45"/>
-        <v>0.16656139632489186</v>
-      </c>
-      <c r="K117" s="23">
+        <v/>
+      </c>
+      <c r="K117" s="23" t="str">
         <f t="shared" si="45"/>
-        <v>0.14668042983890439</v>
+        <v/>
       </c>
       <c r="L117" s="23" t="str">
         <f t="shared" si="45"/>
@@ -13432,28 +13443,28 @@
       </c>
       <c r="C118" s="42">
         <f>C4/C101</f>
-        <v>0.43142078743512902</v>
+        <v>0.42808280043619051</v>
       </c>
       <c r="E118" s="308"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
-        <v>0.44019362596109335</v>
+        <v>0.47876122884928152</v>
       </c>
       <c r="H118" s="42">
         <f t="shared" si="46"/>
-        <v>0.40641869578030704</v>
+        <v>0.44019362596109335</v>
       </c>
       <c r="I118" s="42">
         <f t="shared" si="46"/>
-        <v>0.51831915430946029</v>
-      </c>
-      <c r="J118" s="42">
+        <v>0.40641869578030704</v>
+      </c>
+      <c r="J118" s="42" t="str">
         <f t="shared" si="46"/>
-        <v>1.0616373807247297</v>
-      </c>
-      <c r="K118" s="42">
+        <v/>
+      </c>
+      <c r="K118" s="42" t="str">
         <f t="shared" si="46"/>
-        <v>1.1348681458049972</v>
+        <v/>
       </c>
       <c r="L118" s="42" t="str">
         <f t="shared" si="46"/>
@@ -13486,30 +13497,30 @@
       </c>
       <c r="C119" s="15">
         <f>C101/C105</f>
-        <v>1.2123604198075375</v>
+        <v>1.2035176992971439</v>
       </c>
       <c r="D119" s="11"/>
       <c r="E119" s="312"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
-        <v>1.2123604198075375</v>
+        <v>1.2035176992971439</v>
       </c>
       <c r="H119" s="15">
         <f t="shared" si="47"/>
-        <v>1.2601845662770377</v>
+        <v>1.2123604198075375</v>
       </c>
       <c r="I119" s="15">
         <f t="shared" si="47"/>
-        <v>1.2478737845300938</v>
-      </c>
-      <c r="J119" s="15">
+        <v>1.2601845662770377</v>
+      </c>
+      <c r="J119" s="15" t="str">
         <f t="shared" si="47"/>
-        <v>6.3996463553848981</v>
-      </c>
-      <c r="K119" s="15">
+        <v/>
+      </c>
+      <c r="K119" s="15" t="str">
         <f t="shared" si="47"/>
-        <v>87.508829863603736</v>
+        <v/>
       </c>
       <c r="L119" s="15" t="str">
         <f t="shared" si="47"/>
@@ -13543,30 +13554,30 @@
       </c>
       <c r="C120" s="105">
         <f>C8/C105</f>
-        <v>1.9358113633458775E-2</v>
+        <v>3.6018739348940135E-2</v>
       </c>
       <c r="D120" s="106"/>
       <c r="E120" s="311"/>
       <c r="F120" s="106"/>
       <c r="G120" s="105">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
-        <v>3.4735334417690791E-2</v>
+        <v>4.9983126642619759E-2</v>
       </c>
       <c r="H120" s="105">
         <f t="shared" si="48"/>
-        <v>7.7604787705588959E-4</v>
+        <v>3.4735334417690791E-2</v>
       </c>
       <c r="I120" s="105">
         <f t="shared" si="48"/>
-        <v>2.9992040973085183E-2</v>
-      </c>
-      <c r="J120" s="105">
+        <v>7.7604787705588959E-4</v>
+      </c>
+      <c r="J120" s="105" t="str">
         <f t="shared" si="48"/>
-        <v>1.1414498630924346</v>
-      </c>
-      <c r="K120" s="105">
+        <v/>
+      </c>
+      <c r="K120" s="105" t="str">
         <f t="shared" si="48"/>
-        <v>14.588442211055277</v>
+        <v/>
       </c>
       <c r="L120" s="105" t="str">
         <f t="shared" si="48"/>
@@ -13664,30 +13675,30 @@
       </c>
       <c r="C124" s="181">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>4.672331805490617E-2</v>
+        <v>8.1669083976373749E-2</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="305"/>
       <c r="F124" s="27"/>
       <c r="G124" s="181">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>8.0923444657520077E-2</v>
+        <v>0.13497753443223681</v>
       </c>
       <c r="H124" s="181">
         <f t="shared" si="49"/>
-        <v>1.1553031824359673E-2</v>
+        <v>8.1944944374402889E-2</v>
       </c>
       <c r="I124" s="181">
         <f t="shared" si="49"/>
-        <v>6.4291406684622618E-2</v>
-      </c>
-      <c r="J124" s="181">
+        <v>1.1748463586076801E-2</v>
+      </c>
+      <c r="J124" s="181" t="str">
         <f t="shared" si="49"/>
-        <v>0.22613586129433641</v>
-      </c>
-      <c r="K124" s="181">
+        <v/>
+      </c>
+      <c r="K124" s="181" t="str">
         <f t="shared" si="49"/>
-        <v>0.16185153030001873</v>
+        <v/>
       </c>
       <c r="L124" s="181" t="str">
         <f t="shared" si="49"/>
@@ -13721,30 +13732,30 @@
       </c>
       <c r="C125" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.359763538126574E-2</v>
+        <v>4.0033864694300855E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="305"/>
       <c r="F125" s="27"/>
       <c r="G125" s="79">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>4.0870426594707111E-2</v>
+        <v>6.6165458055018042E-2</v>
       </c>
       <c r="H125" s="79">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.8348645577574101E-3</v>
+        <v>4.0169090379609258E-2</v>
       </c>
       <c r="I125" s="79">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.2470407416476069E-2</v>
-      </c>
-      <c r="J125" s="79">
+        <v>5.7590507774886272E-3</v>
+      </c>
+      <c r="J125" s="79" t="str">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.11421003095673556</v>
-      </c>
-      <c r="K125" s="79">
+        <v/>
+      </c>
+      <c r="K125" s="79" t="str">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>8.1743197121221578E-2</v>
+        <v/>
       </c>
       <c r="L125" s="79" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13778,23 +13789,23 @@
       <c r="C126" s="173"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.5460976665862772E-2</v>
+        <v>7.1782711615396344E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.4793936294697356E-2</v>
+        <v>6.3535653822749158E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1724984212407273E-3</v>
-      </c>
-      <c r="J126" s="23">
+        <v>2.4064702874265081E-2</v>
+      </c>
+      <c r="J126" s="23" t="str">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.653801433426336E-3</v>
-      </c>
-      <c r="K126" s="23">
+        <v/>
+      </c>
+      <c r="K126" s="23" t="str">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14564,7 +14575,7 @@
       </c>
       <c r="C4" s="113">
         <f>Normalized_FCF!C19</f>
-        <v>58578.391168071357</v>
+        <v>102738.48097579018</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14596,7 +14607,7 @@
       </c>
       <c r="C6" s="238">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>732229.88960089197</v>
+        <v>1284231.0121973772</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14630,7 +14641,7 @@
       </c>
       <c r="C8" s="207">
         <f>BS!D66</f>
-        <v>1823806.3881188305</v>
+        <v>1874069.548055639</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -14646,7 +14657,7 @@
       </c>
       <c r="C9" s="235">
         <f>BS!H42</f>
-        <v>227656.8</v>
+        <v>229590.09999999998</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -14662,7 +14673,7 @@
       </c>
       <c r="C10" s="238">
         <f>C6-C7+C8+C9</f>
-        <v>2749694.0777197224</v>
+        <v>3353891.6602530163</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -14676,7 +14687,7 @@
       </c>
       <c r="C11" s="237">
         <f>Exchange_Rate</f>
-        <v>1.06349396</v>
+        <v>1.0598962000000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14690,7 +14701,7 @@
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>2.1932120084755207</v>
+        <v>2.6660824361750932</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14723,7 +14734,7 @@
       </c>
       <c r="C16" s="165">
         <f>Scenarios!C65</f>
-        <v>1.77907652777404E-2</v>
+        <v>8.577901479280229E-3</v>
       </c>
       <c r="H16" s="124"/>
     </row>
@@ -14743,7 +14754,7 @@
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>2.2265748797838305</v>
+        <v>2.6935879741024711</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14778,11 +14789,11 @@
       </c>
       <c r="C21" s="127">
         <f>C4*(1+D21)</f>
-        <v>59620.545575690179</v>
+        <v>103619.76154373141</v>
       </c>
       <c r="D21" s="142">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
-        <v>1.77907652777404E-2</v>
+        <v>8.577901479280229E-3</v>
       </c>
       <c r="E21" s="128">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -14790,7 +14801,7 @@
       </c>
       <c r="F21" s="129">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>55204.208866379791</v>
+        <v>95944.223651603141</v>
       </c>
       <c r="H21" s="124"/>
     </row>
@@ -14800,11 +14811,11 @@
       </c>
       <c r="C22" s="127">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>60681.240707758116</v>
+        <v>104508.60164956003</v>
       </c>
       <c r="D22" s="142">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
-        <v>1.77907652777404E-2</v>
+        <v>8.577901479280229E-3</v>
       </c>
       <c r="E22" s="128">
         <f t="shared" si="0"/>
@@ -14812,7 +14823,7 @@
       </c>
       <c r="F22" s="129">
         <f t="shared" si="1"/>
-        <v>52024.383322837886</v>
+        <v>89599.2812496228</v>
       </c>
       <c r="H22" s="124"/>
     </row>
@@ -14822,11 +14833,11 @@
       </c>
       <c r="C23" s="127">
         <f t="shared" si="2"/>
-        <v>61760.806417951906</v>
+        <v>105405.06613824729</v>
       </c>
       <c r="D23" s="142">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
-        <v>1.77907652777404E-2</v>
+        <v>8.577901479280229E-3</v>
       </c>
       <c r="E23" s="128">
         <f t="shared" si="0"/>
@@ -14834,7 +14845,7 @@
       </c>
       <c r="F23" s="129">
         <f t="shared" si="1"/>
-        <v>49027.71936597563</v>
+        <v>83673.939867404042</v>
       </c>
       <c r="H23" s="124"/>
     </row>
@@ -14844,11 +14855,11 @@
       </c>
       <c r="C24" s="127">
         <f t="shared" si="2"/>
-        <v>62859.57842829766</v>
+        <v>106309.22041099818</v>
       </c>
       <c r="D24" s="142">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
-        <v>1.77907652777404E-2</v>
+        <v>8.577901479280229E-3</v>
       </c>
       <c r="E24" s="128">
         <f t="shared" si="0"/>
@@ -14856,7 +14867,7 @@
       </c>
       <c r="F24" s="129">
         <f t="shared" si="1"/>
-        <v>46203.666678998736</v>
+        <v>78140.450629601706</v>
       </c>
       <c r="H24" s="124"/>
     </row>
@@ -14866,11 +14877,11 @@
       </c>
       <c r="C25" s="127">
         <f t="shared" si="2"/>
-        <v>63977.898433573224</v>
+        <v>107221.13043002281</v>
       </c>
       <c r="D25" s="142">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
-        <v>1.77907652777404E-2</v>
+        <v>8.577901479280229E-3</v>
       </c>
       <c r="E25" s="128">
         <f t="shared" si="0"/>
@@ -14878,7 +14889,7 @@
       </c>
       <c r="F25" s="129">
         <f t="shared" si="1"/>
-        <v>43542.282655422008</v>
+        <v>72972.899737637941</v>
       </c>
       <c r="H25" s="124"/>
     </row>
@@ -14888,11 +14899,11 @@
       </c>
       <c r="C26" s="127">
         <f t="shared" si="2"/>
-        <v>65116.11420756804</v>
+        <v>108140.8627233486</v>
       </c>
       <c r="D26" s="142">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
-        <v>1.77907652777404E-2</v>
+        <v>8.577901479280229E-3</v>
       </c>
       <c r="E26" s="128">
         <f t="shared" si="0"/>
@@ -14900,7 +14911,7 @@
       </c>
       <c r="F26" s="129">
         <f t="shared" si="1"/>
-        <v>41034.197394260773</v>
+        <v>68147.087113189613</v>
       </c>
       <c r="H26" s="124"/>
     </row>
@@ -14910,11 +14921,11 @@
       </c>
       <c r="C27" s="127">
         <f t="shared" si="2"/>
-        <v>66274.57971123344</v>
+        <v>109068.48438967383</v>
       </c>
       <c r="D27" s="142">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
-        <v>1.77907652777404E-2</v>
+        <v>8.577901479280229E-3</v>
       </c>
       <c r="E27" s="128">
         <f t="shared" si="0"/>
@@ -14922,7 +14933,7 @@
       </c>
       <c r="F27" s="129">
         <f t="shared" si="1"/>
-        <v>38670.580711539398</v>
+        <v>63640.41306717266</v>
       </c>
       <c r="H27" s="124"/>
     </row>
@@ -14932,11 +14943,11 @@
       </c>
       <c r="C28" s="127">
         <f t="shared" si="2"/>
-        <v>67453.655202756883</v>
+        <v>110004.06310326286</v>
       </c>
       <c r="D28" s="142">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
-        <v>1.77907652777404E-2</v>
+        <v>8.577901479280229E-3</v>
       </c>
       <c r="E28" s="128">
         <f t="shared" si="0"/>
@@ -14944,7 +14955,7 @@
       </c>
       <c r="F28" s="129">
         <f t="shared" si="1"/>
-        <v>36443.111051974352</v>
+        <v>59431.772463484776</v>
       </c>
       <c r="H28" s="124"/>
     </row>
@@ -14954,11 +14965,11 @@
       </c>
       <c r="C29" s="127">
         <f t="shared" si="2"/>
-        <v>68653.70734959477</v>
+        <v>110947.66711888317</v>
       </c>
       <c r="D29" s="142">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
-        <v>1.77907652777404E-2</v>
+        <v>8.577901479280229E-3</v>
       </c>
       <c r="E29" s="128">
         <f t="shared" si="0"/>
@@ -14966,7 +14977,7 @@
       </c>
       <c r="F29" s="129">
         <f t="shared" si="1"/>
-        <v>34343.946191380244</v>
+        <v>55501.455881866248</v>
       </c>
       <c r="H29" s="124"/>
     </row>
@@ -14976,11 +14987,11 @@
       </c>
       <c r="C30" s="127">
         <f t="shared" si="2"/>
-        <v>69875.109342498094</v>
+        <v>111899.36527678493</v>
       </c>
       <c r="D30" s="142">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
-        <v>1.77907652777404E-2</v>
+        <v>8.577901479280229E-3</v>
       </c>
       <c r="E30" s="128">
         <f t="shared" si="0"/>
@@ -14988,7 +14999,7 @@
       </c>
       <c r="F30" s="129">
         <f t="shared" si="1"/>
-        <v>32365.695626650398</v>
+        <v>51831.05731701621</v>
       </c>
       <c r="H30" s="124"/>
     </row>
@@ -15438,7 +15449,7 @@
       </c>
       <c r="C51" s="127">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>745256.8196961272</v>
+        <v>1295247.0192966426</v>
       </c>
       <c r="D51" s="143">
         <f>Terminal_Growth</f>
@@ -15450,7 +15461,7 @@
       </c>
       <c r="F51" s="129">
         <f t="shared" si="1"/>
-        <v>345198.10583394777</v>
+        <v>599949.98479930218</v>
       </c>
       <c r="H51" s="124"/>
     </row>
@@ -15461,7 +15472,7 @@
       </c>
       <c r="F52" s="141">
         <f>SUM(F21:F51)</f>
-        <v>774057.89769936702</v>
+        <v>1318832.5657779013</v>
       </c>
       <c r="H52" s="124"/>
     </row>
@@ -15482,15 +15493,15 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="137">
         <f>F52</f>
-        <v>774057.89769936702</v>
+        <v>1318832.5657779013</v>
       </c>
       <c r="B55" s="135">
         <f>C78</f>
-        <v>-0.06</v>
+        <v>-0.1</v>
       </c>
       <c r="C55" s="135">
         <f>C77</f>
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="D55" s="135">
         <f>C76</f>
@@ -15498,7 +15509,7 @@
       </c>
       <c r="E55" s="135">
         <f>C75</f>
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="F55" s="135">
         <f>C74</f>
@@ -15512,19 +15523,19 @@
       </c>
       <c r="B56" s="127">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>665302.22744788707</v>
+        <v>1093874.3916529666</v>
       </c>
       <c r="C56" s="127">
-        <v>665302.22744788707</v>
+        <v>1129865.1970228264</v>
       </c>
       <c r="D56" s="127">
-        <v>755855.45886651648</v>
+        <v>1325667.0272558033</v>
       </c>
       <c r="E56" s="127">
-        <v>805260.37456521951</v>
+        <v>1368344.0328832779</v>
       </c>
       <c r="F56" s="127">
-        <v>831102.78380686371</v>
+        <v>1457640.5367310294</v>
       </c>
       <c r="H56" s="124"/>
     </row>
@@ -15533,19 +15544,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="127">
-        <v>614001.64793383703</v>
+        <v>966090.91144449427</v>
       </c>
       <c r="C57" s="127">
-        <v>614001.64793383703</v>
+        <v>1019144.2763026257</v>
       </c>
       <c r="D57" s="127">
-        <v>779502.78354800644</v>
+        <v>1367141.1983361761</v>
       </c>
       <c r="E57" s="127">
-        <v>888829.68089211243</v>
+        <v>1458361.2300051935</v>
       </c>
       <c r="F57" s="127">
-        <v>952081.15765634226</v>
+        <v>1669820.0471678278</v>
       </c>
       <c r="H57" s="124"/>
     </row>
@@ -15554,19 +15565,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="127">
-        <v>561280.10692549124</v>
+        <v>844709.81359427259</v>
       </c>
       <c r="C58" s="127">
-        <v>561280.10692549124</v>
+        <v>909885.43268162361</v>
       </c>
       <c r="D58" s="127">
-        <v>808772.90463007218</v>
+        <v>1418476.9847581831</v>
       </c>
       <c r="E58" s="127">
-        <v>1003782.4859440906</v>
+        <v>1575710.0619971021</v>
       </c>
       <c r="F58" s="127">
-        <v>1127971.6182518224</v>
+        <v>1978307.8424004384</v>
       </c>
       <c r="H58" s="124"/>
     </row>
@@ -15575,19 +15586,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="127">
-        <v>516504.30855932954</v>
+        <v>748269.74021160579</v>
       </c>
       <c r="C59" s="127">
-        <v>516504.30855932954</v>
+        <v>820317.70740897022</v>
       </c>
       <c r="D59" s="127">
-        <v>838594.46403528017</v>
+        <v>1470779.9185282441</v>
       </c>
       <c r="E59" s="127">
-        <v>1134912.3907207896</v>
+        <v>1702015.6673859565</v>
       </c>
       <c r="F59" s="127">
-        <v>1341234.3224006922</v>
+        <v>2352341.4380002194</v>
       </c>
       <c r="H59" s="124"/>
     </row>
@@ -15596,19 +15607,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="127">
-        <v>481588.05150728382</v>
+        <v>677076.22456772218</v>
       </c>
       <c r="C60" s="127">
-        <v>481588.05150728382</v>
+        <v>752537.72450801823</v>
       </c>
       <c r="D60" s="127">
-        <v>866330.16908074159</v>
+        <v>1519424.5492246982</v>
       </c>
       <c r="E60" s="127">
-        <v>1272332.5439354072</v>
+        <v>1826430.9855199228</v>
       </c>
       <c r="F60" s="127">
-        <v>1579931.9475474516</v>
+        <v>2770984.4039660259</v>
       </c>
       <c r="H60" s="124"/>
     </row>
@@ -15617,19 +15628,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="127">
-        <v>455605.63108291052</v>
+        <v>626389.46962424996</v>
       </c>
       <c r="C61" s="127">
-        <v>455605.63108291052</v>
+        <v>703347.86924713815</v>
       </c>
       <c r="D61" s="127">
-        <v>890796.9191942726</v>
+        <v>1562335.8803649866</v>
       </c>
       <c r="E61" s="127">
-        <v>1409735.2337384261</v>
+        <v>1942947.0335488864</v>
       </c>
       <c r="F61" s="127">
-        <v>1835940.1525432554</v>
+        <v>3219987.7578332042</v>
       </c>
       <c r="H61" s="124"/>
     </row>
@@ -15653,11 +15664,11 @@
     <row r="64" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B64" s="136">
         <f>B55</f>
-        <v>-0.06</v>
+        <v>-0.1</v>
       </c>
       <c r="C64" s="136">
         <f>C55</f>
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="D64" s="136">
         <f>D55</f>
@@ -15665,7 +15676,7 @@
       </c>
       <c r="E64" s="136">
         <f>E55</f>
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="F64" s="136">
         <f>F55</f>
@@ -15679,23 +15690,23 @@
       </c>
       <c r="B65" s="128">
         <f>C12</f>
-        <v>2.1932120084755207</v>
+        <v>2.6660824361750932</v>
       </c>
       <c r="C65" s="128">
         <f>C12</f>
-        <v>2.1932120084755207</v>
+        <v>2.6660824361750932</v>
       </c>
       <c r="D65" s="128">
         <f>C12</f>
-        <v>2.1932120084755207</v>
+        <v>2.6660824361750932</v>
       </c>
       <c r="E65" s="145">
         <f>C12</f>
-        <v>2.1932120084755207</v>
+        <v>2.6660824361750932</v>
       </c>
       <c r="F65" s="128">
         <f>C12</f>
-        <v>2.1932120084755207</v>
+        <v>2.6660824361750932</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -15706,23 +15717,23 @@
       </c>
       <c r="B66" s="128">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.1398291418058975</v>
+        <v>2.51476376102003</v>
       </c>
       <c r="C66" s="128">
         <f t="shared" si="4"/>
-        <v>2.1398291418058975</v>
+        <v>2.5433736458286349</v>
       </c>
       <c r="D66" s="128">
         <f t="shared" si="4"/>
-        <v>2.2120562437816558</v>
+        <v>2.699020838235469</v>
       </c>
       <c r="E66" s="128">
         <f t="shared" si="4"/>
-        <v>2.25146261093577</v>
+        <v>2.7329457310638112</v>
       </c>
       <c r="F66" s="128">
         <f t="shared" si="4"/>
-        <v>2.2720750429644685</v>
+        <v>2.8039294910169796</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -15733,23 +15744,23 @@
       </c>
       <c r="B67" s="128">
         <f t="shared" si="4"/>
-        <v>2.0989107545774273</v>
+        <v>2.4131858548954668</v>
       </c>
       <c r="C67" s="128">
         <f t="shared" si="4"/>
-        <v>2.0989107545774273</v>
+        <v>2.4553591444815663</v>
       </c>
       <c r="D67" s="128">
         <f t="shared" si="4"/>
-        <v>2.2309178316506499</v>
+        <v>2.7319895713590552</v>
       </c>
       <c r="E67" s="128">
         <f t="shared" si="4"/>
-        <v>2.3181191919937278</v>
+        <v>2.8045023859923566</v>
       </c>
       <c r="F67" s="128">
         <f t="shared" si="4"/>
-        <v>2.3685698583122732</v>
+        <v>2.9725956625560754</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -15760,23 +15771,23 @@
       </c>
       <c r="B68" s="128">
         <f t="shared" si="4"/>
-        <v>2.056858979515698</v>
+        <v>2.3166973436840723</v>
       </c>
       <c r="C68" s="128">
         <f t="shared" si="4"/>
-        <v>2.056858979515698</v>
+        <v>2.3685068804603784</v>
       </c>
       <c r="D68" s="128">
         <f t="shared" si="4"/>
-        <v>2.2542642764667788</v>
+        <v>2.7727975199725843</v>
       </c>
       <c r="E68" s="128">
         <f t="shared" si="4"/>
-        <v>2.4098078909260172</v>
+        <v>2.8977855601589568</v>
       </c>
       <c r="F68" s="128">
         <f t="shared" si="4"/>
-        <v>2.5088636726242299</v>
+        <v>3.217819413338173</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -15787,23 +15798,23 @@
       </c>
       <c r="B69" s="128">
         <f t="shared" si="4"/>
-        <v>2.0211448906425162</v>
+        <v>2.2400350027873577</v>
       </c>
       <c r="C69" s="128">
         <f t="shared" si="4"/>
-        <v>2.0211448906425162</v>
+        <v>2.2973075206159517</v>
       </c>
       <c r="D69" s="128">
         <f t="shared" si="4"/>
-        <v>2.2780505597224079</v>
+        <v>2.8143742753392944</v>
       </c>
       <c r="E69" s="128">
         <f t="shared" si="4"/>
-        <v>2.5143997741310775</v>
+        <v>2.9981886710013281</v>
       </c>
       <c r="F69" s="128">
         <f t="shared" si="4"/>
-        <v>2.6789663496780873</v>
+        <v>3.5151469661586376</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -15814,23 +15825,23 @@
       </c>
       <c r="B70" s="128">
         <f t="shared" si="4"/>
-        <v>1.9932949727632625</v>
+        <v>2.1834417073398247</v>
       </c>
       <c r="C70" s="128">
         <f t="shared" si="4"/>
-        <v>1.9932949727632625</v>
+        <v>2.2434277176163384</v>
       </c>
       <c r="D70" s="128">
         <f t="shared" si="4"/>
-        <v>2.3001731230512301</v>
+        <v>2.8530429649248896</v>
       </c>
       <c r="E70" s="128">
         <f t="shared" si="4"/>
-        <v>2.6240088876244538</v>
+        <v>3.0970891508227543</v>
       </c>
       <c r="F70" s="128">
         <f t="shared" si="4"/>
-        <v>2.8693564378367684</v>
+        <v>3.8479354911479877</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15840,23 +15851,23 @@
       </c>
       <c r="B71" s="128">
         <f t="shared" si="4"/>
-        <v>1.9725708649631495</v>
+        <v>2.1431496881601397</v>
       </c>
       <c r="C71" s="128">
         <f t="shared" si="4"/>
-        <v>1.9725708649631495</v>
+        <v>2.2043256170019334</v>
       </c>
       <c r="D71" s="128">
         <f t="shared" si="4"/>
-        <v>2.3196883013367597</v>
+        <v>2.8871541282703941</v>
       </c>
       <c r="E71" s="128">
         <f t="shared" si="4"/>
-        <v>2.7336040719450039</v>
+        <v>3.1897103266537945</v>
       </c>
       <c r="F71" s="128">
         <f t="shared" si="4"/>
-        <v>3.073553797104708</v>
+        <v>4.2048581579459618</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15891,7 +15902,7 @@
       </c>
       <c r="E74" s="139">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>2.5088636726242299</v>
+        <v>3.217819413338173</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
@@ -15905,7 +15916,7 @@
       </c>
       <c r="C75" s="146">
         <f>Scenarios!C38</f>
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="D75" s="149">
         <f>Scenarios!C37</f>
@@ -15913,11 +15924,11 @@
       </c>
       <c r="E75" s="139">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>2.3181191919937278</v>
+        <v>2.8045023859923566</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
-        <v>0.21249999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="H75" s="124"/>
     </row>
@@ -15936,7 +15947,7 @@
       </c>
       <c r="E76" s="139">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>2.2309178316506499</v>
+        <v>2.7319895713590552</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15951,7 +15962,7 @@
       </c>
       <c r="C77" s="146">
         <f>Scenarios!C32</f>
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="D77" s="149">
         <f>Scenarios!C31</f>
@@ -15959,11 +15970,11 @@
       </c>
       <c r="E77" s="139">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>2.0989107545774273</v>
+        <v>2.4553591444815663</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
-        <v>0.1275</v>
+        <v>0.17</v>
       </c>
       <c r="H77" s="124"/>
     </row>
@@ -15974,7 +15985,7 @@
       </c>
       <c r="C78" s="146">
         <f>Scenarios!C50</f>
-        <v>-0.06</v>
+        <v>-0.1</v>
       </c>
       <c r="D78" s="149">
         <f>Scenarios!C49</f>
@@ -15982,7 +15993,7 @@
       </c>
       <c r="E78" s="139">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.056858979515698</v>
+        <v>2.3166973436840723</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
@@ -16083,7 +16094,7 @@
       </c>
       <c r="I3" s="270">
         <f>-Market_Price</f>
-        <v>-1.98</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16091,7 +16102,7 @@
         <v>148</v>
       </c>
       <c r="C4" s="124">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="124"/>
       <c r="E4" s="159" t="s">
@@ -16103,7 +16114,7 @@
       </c>
       <c r="I4" s="270">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.1178</v>
+        <v>0.11510561128533152</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -16112,7 +16123,7 @@
       </c>
       <c r="I5" s="270">
         <f t="shared" si="0"/>
-        <v>0.1178</v>
+        <v>0.11510561128533152</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
@@ -16132,7 +16143,7 @@
       </c>
       <c r="I6" s="270">
         <f t="shared" si="0"/>
-        <v>2.3469086252319018</v>
+        <v>2.7951574578943328</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16141,7 +16152,7 @@
       </c>
       <c r="C7" s="118">
         <f>Normalized_FCF!G8</f>
-        <v>105154</v>
+        <v>157888</v>
       </c>
       <c r="D7" t="str">
         <f>Reporting_currency</f>
@@ -16166,7 +16177,7 @@
       </c>
       <c r="C8" s="118">
         <f>Normalized_FCF!G19</f>
-        <v>101456.09073065873</v>
+        <v>169799.71095839841</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16188,7 +16199,7 @@
       </c>
       <c r="C9" s="207">
         <f>Normalized_FCF!C19</f>
-        <v>58578.391168071357</v>
+        <v>102738.48097579018</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16235,7 +16246,7 @@
       </c>
       <c r="C12" s="162">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-1.7248638436905273E-2</v>
+        <v>0.12167914390403989</v>
       </c>
       <c r="D12" s="162"/>
       <c r="E12" s="351"/>
@@ -16254,7 +16265,7 @@
       </c>
       <c r="C13" s="162">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-0.283580450424601</v>
+        <v>7.4870016543118432</v>
       </c>
       <c r="E13" s="351"/>
       <c r="F13" s="351"/>
@@ -16272,7 +16283,7 @@
       </c>
       <c r="C14" s="162">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-0.29003821304292421</v>
+        <v>2.3895356641522589</v>
       </c>
       <c r="E14" s="351"/>
       <c r="F14" s="351"/>
@@ -16323,7 +16334,7 @@
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16338,7 +16349,7 @@
       </c>
       <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
-        <v>2.1932120084755207</v>
+        <v>2.6660824361750932</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16385,7 +16396,7 @@
       </c>
       <c r="C27" s="164">
         <f>Valuation_Model!E76</f>
-        <v>2.2309178316506499</v>
+        <v>2.7319895713590552</v>
       </c>
       <c r="D27" s="164" t="str">
         <f>Market_currency</f>
@@ -16431,7 +16442,7 @@
         <v>136</v>
       </c>
       <c r="C32" s="168">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="D32" s="168"/>
       <c r="E32" s="350"/>
@@ -16443,7 +16454,7 @@
       </c>
       <c r="C33" s="164">
         <f>Valuation_Model!E77</f>
-        <v>2.0989107545774273</v>
+        <v>2.4553591444815663</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16457,7 +16468,7 @@
         <v>149</v>
       </c>
       <c r="C34" s="169">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="D34" s="169"/>
       <c r="E34" s="350"/>
@@ -16489,7 +16500,7 @@
         <v>136</v>
       </c>
       <c r="C38" s="168">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="D38" s="168"/>
       <c r="E38" s="350"/>
@@ -16501,7 +16512,7 @@
       </c>
       <c r="C39" s="164">
         <f>Valuation_Model!E75</f>
-        <v>2.3181191919937278</v>
+        <v>2.8045023859923566</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16516,7 +16527,7 @@
       </c>
       <c r="C40" s="171">
         <f>1-C28-C34</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D40" s="169"/>
       <c r="E40" s="350"/>
@@ -16528,7 +16539,7 @@
       </c>
       <c r="C42" s="158">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>2.2329171101754359</v>
+        <v>2.691166048910218</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16590,7 +16601,7 @@
         <v>136</v>
       </c>
       <c r="C50" s="168">
-        <v>-0.06</v>
+        <v>-0.1</v>
       </c>
       <c r="D50" s="168"/>
       <c r="E50" s="350"/>
@@ -16602,7 +16613,7 @@
       </c>
       <c r="C51" s="164">
         <f>Valuation_Model!E78</f>
-        <v>2.056858979515698</v>
+        <v>2.3166973436840723</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16660,7 +16671,7 @@
       </c>
       <c r="C57" s="164">
         <f>Valuation_Model!E74</f>
-        <v>2.5088636726242299</v>
+        <v>3.217819413338173</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16686,7 +16697,7 @@
       </c>
       <c r="C60" s="158">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>2.2291086252319019</v>
+        <v>2.6800518466090013</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16734,7 +16745,7 @@
         <v>136</v>
       </c>
       <c r="C65" s="155">
-        <v>1.77907652777404E-2</v>
+        <v>8.577901479280229E-3</v>
       </c>
       <c r="D65" s="155"/>
       <c r="E65" s="287" t="s">
@@ -16747,7 +16758,7 @@
       </c>
       <c r="C66" s="164">
         <f>Valuation_Model!C18</f>
-        <v>2.2265748797838305</v>
+        <v>2.6935879741024711</v>
       </c>
       <c r="D66" s="164" t="str">
         <f>Market_currency</f>
@@ -16810,7 +16821,7 @@
       </c>
       <c r="F72" s="335">
         <f>BS!D89/C60</f>
-        <v>0.72188968925719621</v>
+        <v>0.6138757683184648</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16843,7 +16854,7 @@
       </c>
       <c r="C77" s="177">
         <f>Normalized_FCF!C90</f>
-        <v>0.1178</v>
+        <v>0.11510561128533152</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -16861,7 +16872,7 @@
       </c>
       <c r="C80" s="171">
         <f>Thesis!C123</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.35">
@@ -16870,7 +16881,7 @@
       </c>
       <c r="C81" s="120">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.24814351851851849</v>
+        <v>0.22468615322896712</v>
       </c>
       <c r="D81" s="120"/>
       <c r="E81" s="103"/>
@@ -16882,7 +16893,7 @@
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
-        <v>1.2899934173795728</v>
+        <v>1.3721865454638087</v>
       </c>
       <c r="D82" s="120"/>
     </row>
@@ -16892,7 +16903,7 @@
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
-        <v>1.5381369358980914</v>
+        <v>1.5968726986927759</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16903,7 +16914,7 @@
       </c>
       <c r="F83" s="335">
         <f>(1-C83/C60)</f>
-        <v>0.30997667924860606</v>
+        <v>0.40416350500336151</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16920,7 +16931,7 @@
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16933,7 +16944,7 @@
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.7593325788780882E-2</v>
+        <v>0.14703263371672559</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8CED322-8F57-49FD-B844-CF6C35BB957A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A667453-E58A-4C91-95F5-23F219E7200C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -1557,10 +1557,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Always use 10yrs to identify the HGR</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Use Excel Goal Seek to find the HGR</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2335,6 +2331,10 @@
   </si>
   <si>
     <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use general Scenarios' HGP assumption </t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F1" s="284" t="s">
         <v>291</v>
@@ -4065,13 +4065,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C5" s="333" t="s">
+        <v>412</v>
+      </c>
+      <c r="D5" s="49" t="s">
         <v>413</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4079,7 +4079,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>2826.6670199999999</v>
+        <v>2840.0003550000001</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4135,7 +4135,7 @@
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="338" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C12" s="338"/>
       <c r="D12" s="338"/>
@@ -4151,7 +4151,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4174,7 +4174,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0562040500000001</v>
+        <v>1.0614312000000001</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4187,7 +4187,7 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>1.5928004364498562</v>
+        <v>1.5985673372765861</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>319</v>
@@ -4218,11 +4218,11 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13066415339637483</v>
+        <v>0.1302840611640077</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4233,7 +4233,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4243,7 +4243,7 @@
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="338" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C25" s="338"/>
       <c r="D25" s="338"/>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="341" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C26" s="341"/>
       <c r="D26" s="341"/>
@@ -4362,11 +4362,11 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>25095.784340823666</v>
+        <v>25084.371003923323</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4377,7 +4377,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>23215.784340823666</v>
+        <v>23204.371003923323</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-34248.178670869704</v>
+        <v>-34245.325336644622</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4445,7 +4445,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B50" s="339" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C50" s="340"/>
       <c r="D50" s="340"/>
@@ -4467,7 +4467,7 @@
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="338" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C53" s="338"/>
       <c r="D53" s="338"/>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="338" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C54" s="338"/>
       <c r="D54" s="338"/>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>169807.78434082365</v>
+        <v>169796.37100392333</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>102744.53601260911</v>
+        <v>102735.97600993386</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4511,11 +4511,11 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.8391219865680747E-2</v>
+        <v>3.8396886150880542E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.448489788627562E-2</v>
+        <v>5.3962042292674567E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4543,7 +4543,7 @@
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
       <c r="B63" s="338" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="338"/>
@@ -4581,7 +4581,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
@@ -4593,7 +4593,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4610,13 +4610,13 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="338" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C73" s="338"/>
       <c r="D73" s="338"/>
@@ -4625,7 +4625,7 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="338" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C74" s="338"/>
       <c r="D74" s="338"/>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.0173673264405401</v>
+        <v>1.0223170937671944</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4655,7 +4655,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4668,7 +4668,7 @@
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="338" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C81" s="338"/>
       <c r="D81" s="338"/>
@@ -4687,7 +4687,7 @@
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="338" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C85" s="338"/>
       <c r="D85" s="338"/>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>2.693240775541153E-2</v>
+        <v>2.7065696143387986E-2</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="C91" s="188">
         <f>Valuation_Model!C8</f>
-        <v>1873801.2998663927</v>
+        <v>1874180.5222041337</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.4843372058184607</v>
+        <v>1.4919850740266862</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C96" s="248">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.18187047236111969</v>
+        <v>0.18277054866702142</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4797,7 +4797,7 @@
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B98" s="338" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C98" s="338"/>
       <c r="D98" s="338"/>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
-        <v>2.6566425968647089</v>
+        <v>2.6700070203175144</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4819,7 +4819,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="247" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4829,7 +4829,7 @@
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B104" s="339" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C104" s="339"/>
       <c r="D104" s="339"/>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="E107" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>3.21 HKD</v>
+        <v>3.22 HKD</v>
       </c>
       <c r="F107" s="259">
         <f>Valuation_Model!F74</f>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="E108" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>2.79 HKD</v>
+        <v>2.81 HKD</v>
       </c>
       <c r="F108" s="246">
         <f>Valuation_Model!F75</f>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="E109" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>2.72 HKD</v>
+        <v>2.74 HKD</v>
       </c>
       <c r="F109" s="246">
         <f>Valuation_Model!F76</f>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="E110" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>2.45 HKD</v>
+        <v>2.46 HKD</v>
       </c>
       <c r="F110" s="246">
         <f>Valuation_Model!F77</f>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="E111" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>2.31 HKD</v>
+        <v>2.32 HKD</v>
       </c>
       <c r="F111" s="246">
         <f>Valuation_Model!F78</f>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="C113" s="241">
         <f>Scenarios!C60</f>
-        <v>2.6705641652753029</v>
+        <v>2.6839963209253819</v>
       </c>
       <c r="D113" s="236" t="str">
         <f>Market_currency</f>
@@ -4978,7 +4978,7 @@
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B115" s="342" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C115" s="342"/>
       <c r="D115" s="342"/>
@@ -4987,7 +4987,7 @@
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -4997,7 +4997,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B119" s="343" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C119" s="343"/>
       <c r="D119" s="343"/>
@@ -5006,7 +5006,7 @@
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B120" s="338" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C120" s="338"/>
       <c r="D120" s="338"/>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="C124" s="237">
         <f>Scenarios!C77</f>
-        <v>0.11550798351890432</v>
+        <v>0.11493915008339682</v>
       </c>
       <c r="D124" s="236" t="str">
         <f>Market_currency</f>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="C127" s="240">
         <f>Scenarios!C81</f>
-        <v>0.22547158382890123</v>
+        <v>0.22436122096279057</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>1.367328852620955</v>
+        <v>1.3742061163137955</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>1.5928004364498562</v>
+        <v>1.5985673372765861</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5093,12 +5093,12 @@
       </c>
       <c r="C130" s="92">
         <f>Scenarios!F83</f>
-        <v>0.40357155347148987</v>
+        <v>0.40440777626497049</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A132" s="247" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B132" s="36"/>
       <c r="C132" s="36"/>
@@ -5108,7 +5108,7 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B134" s="337" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C134" s="338"/>
       <c r="D134" s="338"/>
@@ -5117,12 +5117,12 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B137" s="340" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C137" s="340"/>
       <c r="D137" s="340"/>
@@ -5131,27 +5131,27 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B138" s="238" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B139" s="238" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B140" s="238" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B142" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B143" s="339" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C143" s="339"/>
       <c r="D143" s="339"/>
@@ -5160,12 +5160,12 @@
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B146" s="336" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C146" s="336"/>
       <c r="D146" s="336"/>
@@ -5174,7 +5174,7 @@
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B147" s="336" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C147" s="336"/>
       <c r="D147" s="336"/>
@@ -5183,22 +5183,22 @@
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="150" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B150" s="238" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="151" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B151" s="238" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="152" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B152" s="238" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -5668,7 +5668,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C22" s="181"/>
       <c r="D22" s="181"/>
@@ -5684,7 +5684,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C23" s="181"/>
       <c r="D23" s="181"/>
@@ -5700,7 +5700,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C24" s="181"/>
       <c r="D24" s="181"/>
@@ -5721,15 +5721,15 @@
       </c>
       <c r="C25" s="39">
         <f>(0.0682+0.0538)/Exchange_Rate</f>
-        <v>0.11550798351890432</v>
+        <v>0.11493915008339682</v>
       </c>
       <c r="D25" s="39">
         <f>(0.064+0.041)/Exchange_Rate</f>
-        <v>9.9412608766270116E-2</v>
+        <v>9.8923039006202196E-2</v>
       </c>
       <c r="E25" s="39">
         <f>(0.022+0.0168)/Exchange_Rate</f>
-        <v>3.6735325906012195E-2</v>
+        <v>3.6554418223244234E-2</v>
       </c>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
@@ -5745,7 +5745,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -6968,7 +6968,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7021,15 +7021,15 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.11550798351890432</v>
+        <v>0.11493915008339682</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>9.9412608766270116E-2</v>
+        <v>9.8923039006202196E-2</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>3.6735325906012195E-2</v>
+        <v>3.6554418223244234E-2</v>
       </c>
       <c r="F65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8372,11 +8372,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>2.5035787660924291</v>
+        <v>2.5159689682954793</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.8469718298526556</v>
+        <v>1.8561124867175998</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>1873801.2998663927</v>
+        <v>1874180.5222041337</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>228</v>
@@ -8618,7 +8618,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>97</v>
@@ -8630,52 +8630,52 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-151352.55532860025</v>
+        <v>-151289.3516056434</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-138973.11668893453</v>
+        <v>-138909.91296597771</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>17.889621976460628</v>
+        <v>17.897095673050657</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>19.483192609550152</v>
+        <v>19.492057421871429</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>833838.70013360726</v>
+        <v>833459.47779586632</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8683,7 +8683,7 @@
         <v>6</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8782,11 +8782,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-35909.881495950001</v>
+        <v>-36087.599368800002</v>
       </c>
       <c r="D86" s="248">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-2.693240775541153E-2</v>
+        <v>-2.7065696143387982E-2</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -8799,11 +8799,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>1979116.5218141486</v>
+        <v>1989313.6806997606</v>
       </c>
       <c r="D87" s="248">
         <f>C87*$H$1/Common_Shares</f>
-        <v>1.4843372058184607</v>
+        <v>1.4919850740266862</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -8816,11 +8816,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>242493.993459905</v>
+        <v>243694.09535111999</v>
       </c>
       <c r="D88" s="248">
         <f>C88*$H$1/Common_Shares</f>
-        <v>0.18187047236111969</v>
+        <v>0.18277054866702142</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -8833,11 +8833,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>2185700.6337781036</v>
+        <v>2196920.1766820806</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>1.6392752704241689</v>
+        <v>1.6476899265503198</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9417,20 +9417,20 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>23215.784340823666</v>
+        <v>23204.371003923323</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>23215.784340823666</v>
+        <v>23204.371003923323</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>21725.821136990475</v>
+        <v>21715.484273656733</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>13102.883592744638</v>
+        <v>13096.532034555015</v>
       </c>
       <c r="J12" s="191" t="str">
         <f t="shared" si="6"/>
@@ -9472,20 +9472,20 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>136992.71468347881</v>
+        <v>136981.30134657849</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>217077.78434082365</v>
+        <v>217066.37100392333</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>147541.82113699047</v>
+        <v>147531.48427365674</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>35800.883592744634</v>
+        <v>35794.532034555014</v>
       </c>
       <c r="J13" s="184" t="str">
         <f t="shared" si="7"/>
@@ -9527,7 +9527,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-34248.178670869704</v>
+        <v>-34245.325336644622</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -9639,22 +9639,22 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>102744.53601260911</v>
+        <v>102735.97600993386</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>169807.78434082365</v>
+        <v>169796.37100392333</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>103092.82113699047</v>
+        <v>103082.48427365674</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>14783.883592744634</v>
+        <v>14777.532034555014</v>
       </c>
       <c r="J16" s="184" t="str">
         <f t="shared" si="8"/>
@@ -9700,7 +9700,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -9747,22 +9747,22 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>102744.53601260911</v>
+        <v>102735.97600993386</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>169807.78434082365</v>
+        <v>169796.37100392333</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>103092.82113699047</v>
+        <v>103082.48427365674</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>14783.883592744634</v>
+        <v>14777.532034555014</v>
       </c>
       <c r="J19" s="186" t="str">
         <f t="shared" si="9"/>
@@ -10053,7 +10053,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10237,7 +10237,7 @@
         <v>-192887</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10295,7 +10295,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10603,20 +10603,20 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.26101055906728832</v>
+        <v>0.26102700924367433</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.35032363382676113</v>
+        <v>0.35035217692005249</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>1.3741196441645189</v>
+        <v>1.3746905165582639</v>
       </c>
       <c r="J43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -10742,24 +10742,24 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>25095.784340823666</v>
+        <v>25084.371003923323</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
-        <v>25095.784340823666</v>
+        <v>25084.371003923323</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
-        <v>22728.821136990475</v>
+        <v>22718.484273656733</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>13965.883592744638</v>
+        <v>13959.532034555015</v>
       </c>
       <c r="J48" s="328" t="str">
         <f t="shared" si="19"/>
@@ -10797,7 +10797,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -10858,20 +10858,20 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>23215.784340823666</v>
+        <v>23204.371003923323</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>23215.784340823666</v>
+        <v>23204.371003923323</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>21725.821136990475</v>
+        <v>21715.484273656733</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>13102.883592744638</v>
+        <v>13096.532034555015</v>
       </c>
       <c r="J50" s="184" t="str">
         <f t="shared" si="20"/>
@@ -10930,7 +10930,7 @@
         <v>3.0096689367862788E-2</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -10957,7 +10957,7 @@
         <v>5.5295743992470364E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11272,7 +11272,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -11945,22 +11945,22 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>1.4265184605974276E-2</v>
+        <v>1.4258171560217848E-2</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>1.2755168561878562E-2</v>
+        <v>1.2748897869754609E-2</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>1.3447649697781594E-2</v>
+        <v>1.3441251480829999E-2</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>9.0574722859102542E-3</v>
+        <v>9.053081720897015E-3</v>
       </c>
       <c r="J80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -12002,22 +12002,22 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>8.4176624659499003E-2</v>
+        <v>8.416961161374259E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.11926643053094853</v>
+        <v>0.11926015983882458</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>9.1324084549553555E-2</v>
+        <v>9.1317686332601955E-2</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>2.4747644948317847E-2</v>
+        <v>2.474325438330461E-2</v>
       </c>
       <c r="J81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -12059,7 +12059,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.1044156164874751E-2</v>
+        <v>2.1042402903435647E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12174,22 +12174,22 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>6.3132468494624255E-2</v>
+        <v>6.3127208710306928E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.3295444193874019E-2</v>
+        <v>9.3289173501750075E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>6.3811449807339438E-2</v>
+        <v>6.3805051590387837E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>1.0219476878627988E-2</v>
+        <v>1.0215086313614749E-2</v>
       </c>
       <c r="J84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -12281,22 +12281,22 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>6.3132468494624255E-2</v>
+        <v>6.3127208710306928E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.3295444193874019E-2</v>
+        <v>9.3289173501750075E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>6.3811449807339438E-2</v>
+        <v>6.3805051590387837E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>1.0219476878627988E-2</v>
+        <v>1.0215086313614749E-2</v>
       </c>
       <c r="J87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -12350,20 +12350,20 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.11550798351890432</v>
+        <v>0.11493915008339682</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.11550798351890432</v>
+        <v>0.11493915008339682</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>9.9412608766270116E-2</v>
+        <v>9.8923039006202196E-2</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>3.6735325906012195E-2</v>
+        <v>3.6554418223244234E-2</v>
       </c>
       <c r="J90" s="113" t="str">
         <f>Data!F65</f>
@@ -12406,20 +12406,20 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/$C$3</f>
-        <v>154010.66394320299</v>
+        <v>153252.21926772079</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
-        <v>154010.66394320299</v>
+        <v>153252.21926772079</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>132550.16159046162</v>
+        <v>131897.40182877608</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>48980.440663903915</v>
+        <v>48739.230390062017</v>
       </c>
       <c r="J91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12461,20 +12461,20 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>1.4989669516275044</v>
+        <v>1.4917093818518097</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>0.90697057582522822</v>
+        <v>0.90256475071649045</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>1.2857360980967629</v>
+        <v>1.2795326263055842</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>3.313097019239359</v>
+        <v>3.2981982563862982</v>
       </c>
       <c r="J92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12516,20 +12516,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.448489788627562E-2</v>
+        <v>5.3962042292674567E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.448489788627562E-2</v>
+        <v>5.3962042292674567E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>4.6892739984089674E-2</v>
+        <v>4.644274131746582E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>1.7327983917930279E-2</v>
+        <v>1.7161698696358797E-2</v>
       </c>
       <c r="J93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -12653,18 +12653,18 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.36892337878116088</v>
+        <v>-0.36894277675051446</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>0.47129663079914152</v>
+        <v>0.47132235585243665</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>3.1211782037382765</v>
+        <v>3.1216207026043552</v>
       </c>
       <c r="I97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13206,7 +13206,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13258,7 +13258,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13372,20 +13372,20 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>8.4176624659499003E-2</v>
+        <v>8.416961161374259E-2</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.11926643053094853</v>
+        <v>0.11926015983882458</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>9.1324084549553555E-2</v>
+        <v>9.1317686332601955E-2</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>2.4747644948317847E-2</v>
+        <v>2.474325438330461E-2</v>
       </c>
       <c r="J117" s="23" t="str">
         <f t="shared" si="45"/>
@@ -13658,22 +13658,22 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>8.1389386115243184E-2</v>
+        <v>8.178536750137555E-2</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.13451373534251149</v>
+        <v>0.13517035747645997</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>8.1665281199951062E-2</v>
+        <v>8.2061213478524783E-2</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.171109683015197E-2</v>
+        <v>1.1763998699857293E-2</v>
       </c>
       <c r="J124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -13715,22 +13715,22 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.8391219865680747E-2</v>
+        <v>3.8396886150880542E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.3449875161562017E-2</v>
+        <v>6.3460261726037553E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>3.852135905658069E-2</v>
+        <v>3.8526391304471733E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>5.5241022783735711E-3</v>
+        <v>5.5230040844400441E-3</v>
       </c>
       <c r="J125" s="77" t="str">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
@@ -13767,20 +13767,20 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9073930045004034E-2</v>
+        <v>6.8749639293619033E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.1138081980381259E-2</v>
+        <v>6.0851048731647074E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.3156600879009795E-2</v>
+        <v>2.3047884442958105E-2</v>
       </c>
       <c r="J126" s="23" t="str">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14558,7 +14558,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>102744.53601260911</v>
+        <v>102735.97600993386</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14590,7 +14590,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>1284306.700157614</v>
+        <v>1284199.7001241732</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14624,7 +14624,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>1873801.2998663927</v>
+        <v>1874180.5222041337</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -14656,7 +14656,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>3353699.1000240068</v>
+        <v>3353971.3223283072</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -14670,7 +14670,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0562040500000001</v>
+        <v>1.0614312000000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>2.6566425968647089</v>
+        <v>2.6700070203175144</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14737,7 +14737,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>2.6840539346400467</v>
+        <v>2.6975517216682041</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14772,7 +14772,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>103625.86852005962</v>
+        <v>103617.23509052476</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>95949.878259314457</v>
+        <v>95941.884343078462</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -14794,7 +14794,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>104514.76101092953</v>
+        <v>104506.05352468669</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -14806,7 +14806,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>89604.561909233133</v>
+        <v>89597.096643249897</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -14816,7 +14816,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>105411.27833401179</v>
+        <v>105402.49615580983</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -14828,7 +14828,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>83678.871308689428</v>
+        <v>83671.89973248633</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -14838,7 +14838,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>106315.48589436592</v>
+        <v>106306.62838350456</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -14850,7 +14850,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>78145.055946919194</v>
+        <v>78138.545412014617</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>107227.44965808959</v>
+        <v>107218.51616837272</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -14872,7 +14872,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>72977.200498078426</v>
+        <v>72971.120515086252</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -14882,7 +14882,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>108147.23615713116</v>
+        <v>108138.22603681963</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -14894,7 +14894,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>68151.103457578341</v>
+        <v>68145.42555342344</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -14904,7 +14904,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>109074.91249414347</v>
+        <v>109065.82508590758</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -14916,7 +14916,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>63644.163804390439</v>
+        <v>63638.861388966965</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -14926,7 +14926,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>110010.54634737934</v>
+        <v>110001.38098825091</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>59435.275158551536</v>
+        <v>59430.323400199159</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -14948,7 +14948,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>110954.20597562894</v>
+        <v>110944.96199695287</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -14960,7 +14960,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>55504.726938199536</v>
+        <v>55500.102647414649</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>111905.96022319965</v>
+        <v>111896.63695058523</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>51834.112053249781</v>
+        <v>51829.79357408714</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15432,7 +15432,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>1295323.3565007453</v>
+        <v>1295215.4386315595</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15444,7 +15444,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>599985.34369514114</v>
+        <v>599935.35684088629</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>1318910.2930293453</v>
+        <v>1318800.4100508932</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15476,7 +15476,7 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>1318910.2930293453</v>
+        <v>1318800.4100508932</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15506,19 +15506,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>1093938.8606781443</v>
+        <v>1093847.7208478684</v>
       </c>
       <c r="C56" s="124">
-        <v>1129931.787216719</v>
+        <v>1129837.6486912381</v>
       </c>
       <c r="D56" s="124">
-        <v>1325745.1573058432</v>
+        <v>1325634.7048912074</v>
       </c>
       <c r="E56" s="124">
-        <v>1368424.6781626453</v>
+        <v>1368310.6699695038</v>
       </c>
       <c r="F56" s="124">
-        <v>1457726.444825395</v>
+        <v>1457604.9965931899</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15527,19 +15527,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>966147.84937061195</v>
+        <v>966067.35625150055</v>
       </c>
       <c r="C57" s="124">
-        <v>1019204.34100339</v>
+        <v>1019119.4275644454</v>
       </c>
       <c r="D57" s="124">
-        <v>1367221.7727247984</v>
+        <v>1367107.8647498696</v>
       </c>
       <c r="E57" s="124">
-        <v>1458447.1805746309</v>
+        <v>1458325.6722954372</v>
       </c>
       <c r="F57" s="124">
-        <v>1669918.4603599501</v>
+        <v>1669779.3336769857</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15548,19 +15548,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>844759.59775473573</v>
+        <v>844689.21791073261</v>
       </c>
       <c r="C58" s="124">
-        <v>909939.05805882951</v>
+        <v>909863.24788854131</v>
       </c>
       <c r="D58" s="124">
-        <v>1418560.5846935522</v>
+        <v>1418442.3995046241</v>
       </c>
       <c r="E58" s="124">
-        <v>1575802.9286849364</v>
+        <v>1575671.6430924493</v>
       </c>
       <c r="F58" s="124">
-        <v>1978424.4367544828</v>
+        <v>1978259.6073715433</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15569,19 +15569,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>748313.8405407567</v>
+        <v>748251.49592638039</v>
       </c>
       <c r="C59" s="124">
-        <v>820366.0539863616</v>
+        <v>820297.70645286422</v>
       </c>
       <c r="D59" s="124">
-        <v>1470866.6010105489</v>
+        <v>1470744.0580264819</v>
       </c>
       <c r="E59" s="124">
-        <v>1702115.9780722205</v>
+        <v>1701974.1689026887</v>
       </c>
       <c r="F59" s="124">
-        <v>2352480.0765500837</v>
+        <v>2352284.0832979833</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -15590,19 +15590,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>677116.12900693575</v>
+        <v>677059.71612017101</v>
       </c>
       <c r="C60" s="124">
-        <v>752582.07637682371</v>
+        <v>752519.37616095715</v>
       </c>
       <c r="D60" s="124">
-        <v>1519514.0986467036</v>
+        <v>1519387.502671343</v>
       </c>
       <c r="E60" s="124">
-        <v>1826538.6287978797</v>
+        <v>1826386.4535469541</v>
       </c>
       <c r="F60" s="124">
-        <v>2771147.7158276699</v>
+        <v>2770916.8419264238</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -15611,19 +15611,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>626426.38676829915</v>
+        <v>626374.1970192896</v>
       </c>
       <c r="C61" s="124">
-        <v>703389.32204266672</v>
+        <v>703330.72024531488</v>
       </c>
       <c r="D61" s="124">
-        <v>1562427.9588266225</v>
+        <v>1562297.7875491367</v>
       </c>
       <c r="E61" s="124">
-        <v>1943061.5438639466</v>
+        <v>1942899.660685929</v>
       </c>
       <c r="F61" s="124">
-        <v>3220177.5323387734</v>
+        <v>3219909.2482103775</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -15673,23 +15673,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>2.6566425968647089</v>
+        <v>2.6700070203175144</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>2.6566425968647089</v>
+        <v>2.6700070203175144</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>2.6566425968647089</v>
+        <v>2.6700070203175144</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>2.6566425968647089</v>
+        <v>2.6700070203175144</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>2.6566425968647089</v>
+        <v>2.6700070203175144</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -15700,23 +15700,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.50584215342879</v>
+        <v>2.5184728919200623</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>2.534354055950848</v>
+        <v>2.5471235125627611</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>2.6894681924607924</v>
+        <v>2.7029923213182605</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>2.7232769003204647</v>
+        <v>2.736965517689772</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>2.7940175571938961</v>
+        <v>2.8080503470001963</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15727,23 +15727,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>2.4046121283100845</v>
+        <v>2.4167503553379093</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>2.4466409840624763</v>
+        <v>2.458983692845881</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>2.7223240152431596</v>
+        <v>2.7360079965687296</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>2.7945884901355216</v>
+        <v>2.8086240576850683</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>2.9621060858217749</v>
+        <v>2.9769566718019487</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -15754,23 +15754,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>2.3084540680955117</v>
+        <v>2.3201244601415412</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>2.3600861691039974</v>
+        <v>2.3720077652922638</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>2.762992206002326</v>
+        <v>2.7768740490801092</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>2.8875521908487225</v>
+        <v>2.9020400519567464</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>3.206490001561618</v>
+        <v>3.2225295814182924</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -15781,23 +15781,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>2.2320542781144441</v>
+        <v>2.2433529645096399</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>2.2891306507194322</v>
+        <v>2.3007070291113156</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>2.8044265705280638</v>
+        <v>2.8185100030007493</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>2.9876114440893398</v>
+        <v>3.0025861205388331</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>3.5027992757810495</v>
+        <v>3.5202804804334096</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -15808,23 +15808,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>2.1756548017098138</v>
+        <v>2.186679089391494</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>2.2354353736741142</v>
+        <v>2.2467505100140786</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>2.8429628287302848</v>
+        <v>2.8572337505264271</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>3.0861732124752517</v>
+        <v>3.1016274185971993</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>3.8344480764816438</v>
+        <v>3.853542842288336</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15834,23 +15834,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>2.135500773444639</v>
+        <v>2.1463297009137636</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>2.1964671887763432</v>
+        <v>2.2075927343526054</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>2.876957169173366</v>
+        <v>2.8913934826340943</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>3.1784771820451949</v>
+        <v>3.1943804719550957</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>4.1901483650964453</v>
+        <v>4.2109737090541248</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15885,7 +15885,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>3.206490001561618</v>
+        <v>3.2225295814182924</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -15907,7 +15907,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>2.7945884901355216</v>
+        <v>2.8086240576850683</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -15930,7 +15930,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>2.7223240152431596</v>
+        <v>2.7360079965687296</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15953,7 +15953,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>2.4466409840624763</v>
+        <v>2.458983692845881</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -15976,7 +15976,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.3084540680955117</v>
+        <v>2.3201244601415412</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-2.12</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16097,7 +16097,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.11550798351890432</v>
+        <v>0.11493915008339682</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.11550798351890432</v>
+        <v>0.11493915008339682</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
@@ -16126,7 +16126,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>2.7860721487942071</v>
+        <v>2.7989354710087788</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>169807.78434082365</v>
+        <v>169796.37100392333</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16182,7 +16182,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>102744.53601260911</v>
+        <v>102735.97600993386</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16266,7 +16266,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>2.3891011474854635</v>
+        <v>2.3897154844568171</v>
       </c>
       <c r="E14" s="346"/>
       <c r="F14" s="346"/>
@@ -16285,7 +16285,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16296,7 +16296,7 @@
         <v>10</v>
       </c>
       <c r="E18" s="346" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F18" s="347"/>
     </row>
@@ -16317,7 +16317,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16332,7 +16332,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>2.6566425968647089</v>
+        <v>2.6700070203175144</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16379,7 +16379,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>2.7223240152431596</v>
+        <v>2.7360079965687296</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16437,7 +16437,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>2.4466409840624763</v>
+        <v>2.458983692845881</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16495,7 +16495,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>2.7945884901355216</v>
+        <v>2.8086240576850683</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16522,7 +16522,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>2.6816403039854952</v>
+        <v>2.6951263480474275</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16596,7 +16596,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>2.3084540680955117</v>
+        <v>2.3201244601415412</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16618,7 +16618,7 @@
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>151</v>
@@ -16654,7 +16654,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>3.206490001561618</v>
+        <v>3.2225295814182924</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16680,7 +16680,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>2.6705641652753029</v>
+        <v>2.6839963209253819</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16696,7 +16696,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16716,11 +16716,12 @@
         <v>135</v>
       </c>
       <c r="C64" s="167">
+        <f>C18</f>
         <v>10</v>
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>324</v>
+        <v>416</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16732,7 +16733,7 @@
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16741,22 +16742,22 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>2.6840539346400467</v>
+        <v>2.6975517216682041</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
@@ -16800,11 +16801,11 @@
         <v>Y</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.61383107424987837</v>
+        <v>0.61389425674854614</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16837,7 +16838,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.11550798351890432</v>
+        <v>0.11493915008339682</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -16864,7 +16865,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.22547158382890123</v>
+        <v>0.22436122096279057</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -16876,7 +16877,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>1.367328852620955</v>
+        <v>1.3742061163137955</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -16886,7 +16887,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>1.5928004364498562</v>
+        <v>1.5985673372765861</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16897,7 +16898,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.40357155347148987</v>
+        <v>0.40440777626497049</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16914,7 +16915,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16927,7 +16928,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13066415339637483</v>
+        <v>0.1302840611640077</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">
@@ -16935,7 +16936,7 @@
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E89" s="320" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F89" s="317"/>
       <c r="G89" s="2"/>
@@ -16943,30 +16944,30 @@
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E90" s="313" t="s">
+        <v>338</v>
+      </c>
+      <c r="F90" s="318" t="s">
         <v>339</v>
-      </c>
-      <c r="F90" s="318" t="s">
-        <v>340</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="316"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E91" s="314" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F91" s="318" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="316"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E92" s="315" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F92" s="319" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="316"/>

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A667453-E58A-4C91-95F5-23F219E7200C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E98A4EE4-CF35-4B22-AC1F-D887EE6B00EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2318,6 +2318,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve">Use general Scenarios' HGP assumption </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>朝云集团</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2331,10 +2335,6 @@
   </si>
   <si>
     <t>Latest Asset Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use general Scenarios' HGP assumption </t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3701,29 +3701,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4068,10 +4068,10 @@
         <v>327</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4079,7 +4079,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>2840.0003550000001</v>
+        <v>2826.6670199999999</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4134,13 +4134,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
+      <c r="B12" s="336" t="s">
         <v>375</v>
       </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="C12" s="336"/>
+      <c r="D12" s="336"/>
+      <c r="E12" s="336"/>
+      <c r="F12" s="336"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4174,7 +4174,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0614312000000001</v>
+        <v>1.0624809</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4187,7 +4187,7 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>1.5985673372765861</v>
+        <v>1.5997267456616144</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>319</v>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1302840611640077</v>
+        <v>0.13244092382946393</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4242,22 +4242,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
+      <c r="B25" s="336" t="s">
         <v>376</v>
       </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="C25" s="336"/>
+      <c r="D25" s="336"/>
+      <c r="E25" s="336"/>
+      <c r="F25" s="336"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
+      <c r="B26" s="338" t="s">
         <v>352</v>
       </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="C26" s="338"/>
+      <c r="D26" s="338"/>
+      <c r="E26" s="338"/>
+      <c r="F26" s="338"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4269,13 +4269,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="339" t="s">
+      <c r="B29" s="337" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="339"/>
-      <c r="D29" s="339"/>
-      <c r="E29" s="339"/>
-      <c r="F29" s="339"/>
+      <c r="C29" s="337"/>
+      <c r="D29" s="337"/>
+      <c r="E29" s="337"/>
+      <c r="F29" s="337"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4295,13 +4295,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="339" t="s">
+      <c r="B32" s="337" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="339"/>
-      <c r="D32" s="339"/>
-      <c r="E32" s="339"/>
-      <c r="F32" s="339"/>
+      <c r="C32" s="337"/>
+      <c r="D32" s="337"/>
+      <c r="E32" s="337"/>
+      <c r="F32" s="337"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4330,13 +4330,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="339" t="s">
+      <c r="B36" s="337" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="339"/>
-      <c r="D36" s="339"/>
-      <c r="E36" s="339"/>
-      <c r="F36" s="339"/>
+      <c r="C36" s="337"/>
+      <c r="D36" s="337"/>
+      <c r="E36" s="337"/>
+      <c r="F36" s="337"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4352,13 +4352,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="339" t="s">
+      <c r="B39" s="337" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="339"/>
-      <c r="D39" s="339"/>
-      <c r="E39" s="339"/>
-      <c r="F39" s="339"/>
+      <c r="C39" s="337"/>
+      <c r="D39" s="337"/>
+      <c r="E39" s="337"/>
+      <c r="F39" s="337"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>25084.371003923323</v>
+        <v>25082.092553579027</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>23204.371003923323</v>
+        <v>23202.092553579027</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4422,13 +4422,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="339" t="s">
+      <c r="B47" s="337" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="339"/>
-      <c r="D47" s="339"/>
-      <c r="E47" s="339"/>
-      <c r="F47" s="339"/>
+      <c r="C47" s="337"/>
+      <c r="D47" s="337"/>
+      <c r="E47" s="337"/>
+      <c r="F47" s="337"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-34245.325336644622</v>
+        <v>-34244.755724058545</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4444,7 +4444,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="339" t="s">
+      <c r="B50" s="337" t="s">
         <v>351</v>
       </c>
       <c r="C50" s="340"/>
@@ -4466,22 +4466,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
+      <c r="B53" s="336" t="s">
         <v>356</v>
       </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="C53" s="336"/>
+      <c r="D53" s="336"/>
+      <c r="E53" s="336"/>
+      <c r="F53" s="336"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
+      <c r="B54" s="336" t="s">
         <v>377</v>
       </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="C54" s="336"/>
+      <c r="D54" s="336"/>
+      <c r="E54" s="336"/>
+      <c r="F54" s="336"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>169796.37100392333</v>
+        <v>169794.09255357902</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>102735.97600993386</v>
+        <v>102734.26717217563</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.8396886150880542E-2</v>
+        <v>3.8615512854405329E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.3962042292674567E-2</v>
+        <v>5.4163015835221838E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4542,22 +4542,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
+      <c r="B63" s="336" t="s">
         <v>378</v>
       </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="C63" s="336"/>
+      <c r="D63" s="336"/>
+      <c r="E63" s="336"/>
+      <c r="F63" s="336"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="338" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="338"/>
+      <c r="D64" s="338"/>
+      <c r="E64" s="338"/>
+      <c r="F64" s="338"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4615,22 +4615,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
+      <c r="B73" s="336" t="s">
         <v>379</v>
       </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
+      <c r="C73" s="336"/>
+      <c r="D73" s="336"/>
+      <c r="E73" s="336"/>
+      <c r="F73" s="336"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="338" t="s">
+      <c r="B74" s="336" t="s">
         <v>380</v>
       </c>
-      <c r="C74" s="338"/>
-      <c r="D74" s="338"/>
-      <c r="E74" s="338"/>
-      <c r="F74" s="338"/>
+      <c r="C74" s="336"/>
+      <c r="D74" s="336"/>
+      <c r="E74" s="336"/>
+      <c r="F74" s="336"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.0223170937671944</v>
+        <v>1.0233110906417415</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4667,13 +4667,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="338" t="s">
+      <c r="B81" s="336" t="s">
         <v>381</v>
       </c>
-      <c r="C81" s="338"/>
-      <c r="D81" s="338"/>
-      <c r="E81" s="338"/>
-      <c r="F81" s="338"/>
+      <c r="C81" s="336"/>
+      <c r="D81" s="336"/>
+      <c r="E81" s="336"/>
+      <c r="F81" s="336"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="338" t="s">
+      <c r="B85" s="336" t="s">
         <v>357</v>
       </c>
-      <c r="C85" s="338"/>
-      <c r="D85" s="338"/>
-      <c r="E85" s="338"/>
-      <c r="F85" s="338"/>
+      <c r="C85" s="336"/>
+      <c r="D85" s="336"/>
+      <c r="E85" s="336"/>
+      <c r="F85" s="336"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>2.7065696143387986E-2</v>
+        <v>2.7092462702767162E-2</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="C91" s="188">
         <f>Valuation_Model!C8</f>
-        <v>1874180.5222041337</v>
+        <v>1874256.2265554145</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.4919850740266862</v>
+        <v>1.4935208951257886</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C96" s="248">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.18277054866702142</v>
+        <v>0.18295129919040506</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4796,13 +4796,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="338" t="s">
+      <c r="B98" s="336" t="s">
         <v>382</v>
       </c>
-      <c r="C98" s="338"/>
-      <c r="D98" s="338"/>
-      <c r="E98" s="338"/>
-      <c r="F98" s="338"/>
+      <c r="C98" s="336"/>
+      <c r="D98" s="336"/>
+      <c r="E98" s="336"/>
+      <c r="F98" s="336"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
-        <v>2.6700070203175144</v>
+        <v>2.6726908222551682</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4828,13 +4828,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="339" t="s">
+      <c r="B104" s="337" t="s">
         <v>383</v>
       </c>
-      <c r="C104" s="339"/>
-      <c r="D104" s="339"/>
-      <c r="E104" s="339"/>
-      <c r="F104" s="339"/>
+      <c r="C104" s="337"/>
+      <c r="D104" s="337"/>
+      <c r="E104" s="337"/>
+      <c r="F104" s="337"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="E107" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>3.22 HKD</v>
+        <v>3.23 HKD</v>
       </c>
       <c r="F107" s="259">
         <f>Valuation_Model!F74</f>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="C113" s="241">
         <f>Scenarios!C60</f>
-        <v>2.6839963209253819</v>
+        <v>2.6866937246321601</v>
       </c>
       <c r="D113" s="236" t="str">
         <f>Market_currency</f>
@@ -4977,13 +4977,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="342" t="s">
+      <c r="B115" s="341" t="s">
         <v>386</v>
       </c>
-      <c r="C115" s="342"/>
-      <c r="D115" s="342"/>
-      <c r="E115" s="342"/>
-      <c r="F115" s="342"/>
+      <c r="C115" s="341"/>
+      <c r="D115" s="341"/>
+      <c r="E115" s="341"/>
+      <c r="F115" s="341"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4996,22 +4996,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="343" t="s">
+      <c r="B119" s="339" t="s">
         <v>384</v>
       </c>
-      <c r="C119" s="343"/>
-      <c r="D119" s="343"/>
-      <c r="E119" s="343"/>
-      <c r="F119" s="343"/>
+      <c r="C119" s="339"/>
+      <c r="D119" s="339"/>
+      <c r="E119" s="339"/>
+      <c r="F119" s="339"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="338" t="s">
+      <c r="B120" s="336" t="s">
         <v>385</v>
       </c>
-      <c r="C120" s="338"/>
-      <c r="D120" s="338"/>
-      <c r="E120" s="338"/>
-      <c r="F120" s="338"/>
+      <c r="C120" s="336"/>
+      <c r="D120" s="336"/>
+      <c r="E120" s="336"/>
+      <c r="F120" s="336"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="C124" s="237">
         <f>Scenarios!C77</f>
-        <v>0.11493915008339682</v>
+        <v>0.11482559357067031</v>
       </c>
       <c r="D124" s="236" t="str">
         <f>Market_currency</f>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="C127" s="240">
         <f>Scenarios!C81</f>
-        <v>0.22436122096279057</v>
+        <v>0.22413955864994844</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>1.3742061163137955</v>
+        <v>1.375587187011666</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>1.5985673372765861</v>
+        <v>1.5997267456616144</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="C130" s="92">
         <f>Scenarios!F83</f>
-        <v>0.40440777626497049</v>
+        <v>0.40457420546488387</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -5107,13 +5107,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="337" t="s">
+      <c r="B134" s="343" t="s">
         <v>392</v>
       </c>
-      <c r="C134" s="338"/>
-      <c r="D134" s="338"/>
-      <c r="E134" s="338"/>
-      <c r="F134" s="338"/>
+      <c r="C134" s="336"/>
+      <c r="D134" s="336"/>
+      <c r="E134" s="336"/>
+      <c r="F134" s="336"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5150,13 +5150,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="339" t="s">
+      <c r="B143" s="337" t="s">
         <v>397</v>
       </c>
-      <c r="C143" s="339"/>
-      <c r="D143" s="339"/>
-      <c r="E143" s="339"/>
-      <c r="F143" s="339"/>
+      <c r="C143" s="337"/>
+      <c r="D143" s="337"/>
+      <c r="E143" s="337"/>
+      <c r="F143" s="337"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5164,22 +5164,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="336" t="s">
+      <c r="B146" s="342" t="s">
         <v>398</v>
       </c>
-      <c r="C146" s="336"/>
-      <c r="D146" s="336"/>
-      <c r="E146" s="336"/>
-      <c r="F146" s="336"/>
+      <c r="C146" s="342"/>
+      <c r="D146" s="342"/>
+      <c r="E146" s="342"/>
+      <c r="F146" s="342"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="336" t="s">
+      <c r="B147" s="342" t="s">
         <v>399</v>
       </c>
-      <c r="C147" s="336"/>
-      <c r="D147" s="336"/>
-      <c r="E147" s="336"/>
-      <c r="F147" s="336"/>
+      <c r="C147" s="342"/>
+      <c r="D147" s="342"/>
+      <c r="E147" s="342"/>
+      <c r="F147" s="342"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5203,6 +5203,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5219,17 +5230,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -5721,15 +5721,15 @@
       </c>
       <c r="C25" s="39">
         <f>(0.0682+0.0538)/Exchange_Rate</f>
-        <v>0.11493915008339682</v>
+        <v>0.11482559357067031</v>
       </c>
       <c r="D25" s="39">
         <f>(0.064+0.041)/Exchange_Rate</f>
-        <v>9.8923039006202196E-2</v>
+        <v>9.8825305941970365E-2</v>
       </c>
       <c r="E25" s="39">
         <f>(0.022+0.0168)/Exchange_Rate</f>
-        <v>3.6554418223244234E-2</v>
+        <v>3.6518303529032854E-2</v>
       </c>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
@@ -5745,7 +5745,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7021,15 +7021,15 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.11493915008339682</v>
+        <v>0.11482559357067031</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>9.8923039006202196E-2</v>
+        <v>9.8825305941970365E-2</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>3.6554418223244234E-2</v>
+        <v>3.6518303529032854E-2</v>
       </c>
       <c r="F65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8372,11 +8372,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>2.5159689682954793</v>
+        <v>2.5184571301528087</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.8561124867175998</v>
+        <v>1.8579480849902972</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>1874180.5222041337</v>
+        <v>1874256.2265554145</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>228</v>
@@ -8634,11 +8634,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-151289.3516056434</v>
+        <v>-151276.73421376329</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-138909.91296597771</v>
+        <v>-138897.29557409757</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>364</v>
@@ -8650,11 +8650,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>17.897095673050657</v>
+        <v>17.898588398754953</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>19.492057421871429</v>
+        <v>19.493828074971802</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>331</v>
@@ -8667,7 +8667,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>833459.47779586632</v>
+        <v>833383.7734445855</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>365</v>
@@ -8782,11 +8782,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-36087.599368800002</v>
+        <v>-36123.288119099998</v>
       </c>
       <c r="D86" s="248">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-2.7065696143387982E-2</v>
+        <v>-2.7092462702767162E-2</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -8799,11 +8799,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>1989313.6806997606</v>
+        <v>1991361.4424212007</v>
       </c>
       <c r="D87" s="248">
         <f>C87*$H$1/Common_Shares</f>
-        <v>1.4919850740266862</v>
+        <v>1.4935208951257888</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -8816,11 +8816,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>243694.09535111999</v>
+        <v>243935.09607908997</v>
       </c>
       <c r="D88" s="248">
         <f>C88*$H$1/Common_Shares</f>
-        <v>0.18277054866702142</v>
+        <v>0.18295129919040506</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -8833,11 +8833,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>2196920.1766820806</v>
+        <v>2199173.2503811908</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>1.6476899265503198</v>
+        <v>1.6493797316134267</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9417,20 +9417,20 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>23204.371003923323</v>
+        <v>23202.092553579027</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>23204.371003923323</v>
+        <v>23202.092553579027</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>21715.484273656733</v>
+        <v>21713.420720286904</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>13096.532034555015</v>
+        <v>13095.264069710875</v>
       </c>
       <c r="J12" s="191" t="str">
         <f t="shared" si="6"/>
@@ -9472,20 +9472,20 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>136981.30134657849</v>
+        <v>136979.02289623418</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>217066.37100392333</v>
+        <v>217064.09255357902</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>147531.48427365674</v>
+        <v>147529.4207202869</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>35794.532034555014</v>
+        <v>35793.264069710873</v>
       </c>
       <c r="J13" s="184" t="str">
         <f t="shared" si="7"/>
@@ -9527,7 +9527,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-34245.325336644622</v>
+        <v>-34244.755724058545</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -9639,22 +9639,22 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>102735.97600993386</v>
+        <v>102734.26717217563</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>169796.37100392333</v>
+        <v>169794.09255357902</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>103082.48427365674</v>
+        <v>103080.4207202869</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>14777.532034555014</v>
+        <v>14776.264069710873</v>
       </c>
       <c r="J16" s="184" t="str">
         <f t="shared" si="8"/>
@@ -9747,22 +9747,22 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>102735.97600993386</v>
+        <v>102734.26717217563</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>169796.37100392333</v>
+        <v>169794.09255357902</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>103082.48427365674</v>
+        <v>103080.4207202869</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>14777.532034555014</v>
+        <v>14776.264069710873</v>
       </c>
       <c r="J19" s="186" t="str">
         <f t="shared" si="9"/>
@@ -10608,15 +10608,15 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.26102700924367433</v>
+        <v>0.26103029344918055</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.35035217692005249</v>
+        <v>0.35035787554946585</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>1.3746905165582639</v>
+        <v>1.3748045369113253</v>
       </c>
       <c r="J43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -10746,20 +10746,20 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>25084.371003923323</v>
+        <v>25082.092553579027</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
-        <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
-        <v>25084.371003923323</v>
+        <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
+        <v>25082.092553579027</v>
       </c>
       <c r="H48" s="328">
-        <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
-        <v>22718.484273656733</v>
+        <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
+        <v>22716.420720286904</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>13959.532034555015</v>
+        <v>13958.264069710875</v>
       </c>
       <c r="J48" s="328" t="str">
         <f t="shared" si="19"/>
@@ -10858,20 +10858,20 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>23204.371003923323</v>
+        <v>23202.092553579027</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>23204.371003923323</v>
+        <v>23202.092553579027</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>21715.484273656733</v>
+        <v>21713.420720286904</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>13096.532034555015</v>
+        <v>13095.264069710875</v>
       </c>
       <c r="J50" s="184" t="str">
         <f t="shared" si="20"/>
@@ -11049,7 +11049,7 @@
         <v>169</v>
       </c>
       <c r="C58" s="191">
-        <f>BS!$C79*C66</f>
+        <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
       <c r="E58" s="302"/>
@@ -11159,7 +11159,7 @@
         <v>160</v>
       </c>
       <c r="C60" s="191">
-        <f>BS!$C81*C68</f>
+        <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
       <c r="E60" s="302"/>
@@ -11449,7 +11449,7 @@
       </c>
       <c r="E68" s="302"/>
       <c r="G68" s="23">
-        <f>IFERROR(G60/BS!$C$81,0)</f>
+        <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
       </c>
       <c r="H68" s="176"/>
@@ -11945,22 +11945,22 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>1.4258171560217848E-2</v>
+        <v>1.4256771542268861E-2</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>1.2748897869754609E-2</v>
+        <v>1.2747646048244955E-2</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>1.3441251480829999E-2</v>
+        <v>1.343997420147309E-2</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>9.053081720897015E-3</v>
+        <v>9.0522052301341971E-3</v>
       </c>
       <c r="J80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -12002,22 +12002,22 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>8.416961161374259E-2</v>
+        <v>8.4168211595793588E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.11926015983882458</v>
+        <v>0.11925890801731491</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>9.1317686332601955E-2</v>
+        <v>9.1316409053245048E-2</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>2.474325438330461E-2</v>
+        <v>2.4742377892541793E-2</v>
       </c>
       <c r="J81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -12059,7 +12059,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.1042402903435647E-2</v>
+        <v>2.1042052898948397E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12174,22 +12174,22 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>6.3127208710306928E-2</v>
+        <v>6.3126158696845194E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.3289173501750075E-2</v>
+        <v>9.3287921680240415E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>6.3805051590387837E-2</v>
+        <v>6.3803774311030931E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>1.0215086313614749E-2</v>
+        <v>1.0214209822851931E-2</v>
       </c>
       <c r="J84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -12281,22 +12281,22 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>6.3127208710306928E-2</v>
+        <v>6.3126158696845194E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.3289173501750075E-2</v>
+        <v>9.3287921680240415E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>6.3805051590387837E-2</v>
+        <v>6.3803774311030931E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>1.0215086313614749E-2</v>
+        <v>1.0214209822851931E-2</v>
       </c>
       <c r="J87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -12350,20 +12350,20 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.11493915008339682</v>
+        <v>0.11482559357067031</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.11493915008339682</v>
+        <v>0.11482559357067031</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>9.8923039006202196E-2</v>
+        <v>9.8825305941970365E-2</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>3.6554418223244234E-2</v>
+        <v>3.6518303529032854E-2</v>
       </c>
       <c r="J90" s="113" t="str">
         <f>Data!F65</f>
@@ -12406,20 +12406,20 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/$C$3</f>
-        <v>153252.21926772079</v>
+        <v>153100.81056515937</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
-        <v>153252.21926772079</v>
+        <v>153100.81056515937</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>131897.40182877608</v>
+        <v>131767.09106017815</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>48739.230390062017</v>
+        <v>48691.077458427724</v>
       </c>
       <c r="J91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12461,20 +12461,20 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>1.4917093818518097</v>
+        <v>1.4902604046279202</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>0.90256475071649045</v>
+        <v>0.90168514264916466</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>1.2795326263055842</v>
+        <v>1.2782940750478089</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>3.2981982563862982</v>
+        <v>3.295222474958142</v>
       </c>
       <c r="J92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12516,20 +12516,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.3962042292674567E-2</v>
+        <v>5.4163015835221838E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.3962042292674567E-2</v>
+        <v>5.4163015835221838E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>4.644274131746582E-2</v>
+        <v>4.6615710349986017E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>1.7161698696358797E-2</v>
+        <v>1.7225614872185307E-2</v>
       </c>
       <c r="J93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -12653,18 +12653,18 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.36894277675051446</v>
+        <v>-0.36894664942142397</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>0.47132235585243665</v>
+        <v>0.47132749178978073</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>3.1216207026043552</v>
+        <v>3.1217090576863562</v>
       </c>
       <c r="I97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13372,20 +13372,20 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>8.416961161374259E-2</v>
+        <v>8.4168211595793588E-2</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.11926015983882458</v>
+        <v>0.11925890801731491</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>9.1317686332601955E-2</v>
+        <v>9.1316409053245048E-2</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>2.474325438330461E-2</v>
+        <v>2.4742377892541793E-2</v>
       </c>
       <c r="J117" s="23" t="str">
         <f t="shared" si="45"/>
@@ -13658,22 +13658,22 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>8.178536750137555E-2</v>
+        <v>8.1864887251339308E-2</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.13517035747645997</v>
+        <v>0.13530221829048014</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>8.2061213478524783E-2</v>
+        <v>8.2140723366861387E-2</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.1763998699857293E-2</v>
+        <v>1.1774622288740266E-2</v>
       </c>
       <c r="J124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -13715,22 +13715,22 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.8396886150880542E-2</v>
+        <v>3.8615512854405329E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.3460261726037553E-2</v>
+        <v>6.3821801080415158E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>3.8526391304471733E-2</v>
+        <v>3.8745624229651596E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>5.5230040844400441E-3</v>
+        <v>5.5540671173303141E-3</v>
       </c>
       <c r="J125" s="77" t="str">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
@@ -13772,15 +13772,15 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8749639293619033E-2</v>
+        <v>6.9073930045004034E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0851048731647074E-2</v>
+        <v>6.1138081980381259E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.3047884442958105E-2</v>
+        <v>2.3156600879009795E-2</v>
       </c>
       <c r="J126" s="23" t="str">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14558,7 +14558,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>102735.97600993386</v>
+        <v>102734.26717217563</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14590,7 +14590,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>1284199.7001241732</v>
+        <v>1284178.3396521953</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14624,7 +14624,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>1874180.5222041337</v>
+        <v>1874256.2265554145</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -14656,7 +14656,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>3353971.3223283072</v>
+        <v>3354025.6662076102</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -14670,7 +14670,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0614312000000001</v>
+        <v>1.0624809</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>2.6700070203175144</v>
+        <v>2.6726908222551682</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14737,7 +14737,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>2.6975517216682041</v>
+        <v>2.7002623052641317</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14772,7 +14772,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>103617.23509052476</v>
+        <v>103615.51159452461</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>95941.884343078462</v>
+        <v>95940.288513448701</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -14794,7 +14794,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>104506.05352468669</v>
+        <v>104504.31524470766</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -14806,7 +14806,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>89597.096643249897</v>
+        <v>89595.606348343324</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -14816,7 +14816,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>105402.49615580983</v>
+        <v>105400.74296503638</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -14828,7 +14828,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>83671.89973248633</v>
+        <v>83670.507993125706</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -14838,7 +14838,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>106306.62838350456</v>
+        <v>106304.86015403339</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -14850,7 +14850,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>78138.545412014617</v>
+        <v>78137.245710566713</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>107218.51616837272</v>
+        <v>107216.73277120334</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -14872,7 +14872,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>72971.120515086252</v>
+        <v>72969.906764939136</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -14882,7 +14882,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>108138.22603681963</v>
+        <v>108136.42734184505</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -14894,7 +14894,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>68145.42555342344</v>
+        <v>68144.292070482436</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -14904,7 +14904,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>109065.82508590758</v>
+        <v>109064.01096190471</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -14916,7 +14916,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>63638.861388966965</v>
+        <v>63637.802865035483</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -14926,7 +14926,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>110001.38098825091</v>
+        <v>109999.55130287107</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>59430.323400199159</v>
+        <v>59429.334878120004</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -14948,7 +14948,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>110944.96199695287</v>
+        <v>110943.11661671211</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -14960,7 +14960,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>55500.102647414649</v>
+        <v>55499.179497855243</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>111896.63695058523</v>
+        <v>111894.77574085457</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>51829.79357408714</v>
+        <v>51828.931473859935</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15432,7 +15432,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>1295215.4386315595</v>
+        <v>1295193.8949315576</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15444,7 +15444,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>599935.35684088629</v>
+        <v>599925.37793933623</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>1318800.4100508932</v>
+        <v>1318778.4740551128</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15476,7 +15476,7 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>1318800.4100508932</v>
+        <v>1318778.4740551128</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15506,19 +15506,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>1093847.7208478684</v>
+        <v>1093829.5265564455</v>
       </c>
       <c r="C56" s="124">
-        <v>1129837.6486912381</v>
+        <v>1129818.8557687418</v>
       </c>
       <c r="D56" s="124">
-        <v>1325634.7048912074</v>
+        <v>1325612.6552185873</v>
       </c>
       <c r="E56" s="124">
-        <v>1368310.6699695038</v>
+        <v>1368287.9104549829</v>
       </c>
       <c r="F56" s="124">
-        <v>1457604.9965931899</v>
+        <v>1457580.751819825</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15527,19 +15527,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>966067.35625150055</v>
+        <v>966051.28736853006</v>
       </c>
       <c r="C57" s="124">
-        <v>1019119.4275644454</v>
+        <v>1019102.4762507419</v>
       </c>
       <c r="D57" s="124">
-        <v>1367107.8647498696</v>
+        <v>1367085.1252419623</v>
       </c>
       <c r="E57" s="124">
-        <v>1458325.6722954372</v>
+        <v>1458301.4155348614</v>
       </c>
       <c r="F57" s="124">
-        <v>1669779.3336769857</v>
+        <v>1669751.5597453592</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15548,19 +15548,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>844689.21791073261</v>
+        <v>844675.16794609907</v>
       </c>
       <c r="C58" s="124">
-        <v>909863.24788854131</v>
+        <v>909848.11386506481</v>
       </c>
       <c r="D58" s="124">
-        <v>1418442.3995046241</v>
+        <v>1418418.8061342752</v>
       </c>
       <c r="E58" s="124">
-        <v>1575671.6430924493</v>
+        <v>1575645.4344817675</v>
       </c>
       <c r="F58" s="124">
-        <v>1978259.6073715433</v>
+        <v>1978226.7023966366</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15569,19 +15569,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>748251.49592638039</v>
+        <v>748239.0500387901</v>
       </c>
       <c r="C59" s="124">
-        <v>820297.70645286422</v>
+        <v>820284.06219942705</v>
       </c>
       <c r="D59" s="124">
-        <v>1470744.0580264819</v>
+        <v>1470719.5947072371</v>
       </c>
       <c r="E59" s="124">
-        <v>1701974.1689026887</v>
+        <v>1701945.8594648822</v>
       </c>
       <c r="F59" s="124">
-        <v>2352284.0832979833</v>
+        <v>2352244.957063769</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -15590,19 +15590,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>677059.71612017101</v>
+        <v>677048.45438642963</v>
       </c>
       <c r="C60" s="124">
-        <v>752519.37616095715</v>
+        <v>752506.8592844574</v>
       </c>
       <c r="D60" s="124">
-        <v>1519387.502671343</v>
+        <v>1519362.2302513521</v>
       </c>
       <c r="E60" s="124">
-        <v>1826386.4535469541</v>
+        <v>1826356.0747229613</v>
       </c>
       <c r="F60" s="124">
-        <v>2770916.8419264238</v>
+        <v>2770870.7524501928</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -15611,19 +15611,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>626374.1970192896</v>
+        <v>626363.7783527209</v>
       </c>
       <c r="C61" s="124">
-        <v>703330.72024531488</v>
+        <v>703319.02153822163</v>
       </c>
       <c r="D61" s="124">
-        <v>1562297.7875491367</v>
+        <v>1562271.801389735</v>
       </c>
       <c r="E61" s="124">
-        <v>1942899.660685929</v>
+        <v>1942867.3438634337</v>
       </c>
       <c r="F61" s="124">
-        <v>3219909.2482103775</v>
+        <v>3219855.6905111652</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -15673,23 +15673,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>2.6700070203175144</v>
+        <v>2.6726908222551682</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>2.6700070203175144</v>
+        <v>2.6726908222551682</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>2.6700070203175144</v>
+        <v>2.6726908222551682</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>2.6700070203175144</v>
+        <v>2.6726908222551682</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>2.6700070203175144</v>
+        <v>2.6726908222551682</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -15700,23 +15700,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.5184728919200623</v>
+        <v>2.521009357526423</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>2.5471235125627611</v>
+        <v>2.5496878351105212</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>2.7029923213182605</v>
+        <v>2.7057081947983943</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>2.736965517689772</v>
+        <v>2.7397144232410873</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>2.8080503470001963</v>
+        <v>2.8108683681894999</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15727,23 +15727,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>2.4167503553379093</v>
+        <v>2.4191879163245091</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>2.458983692845881</v>
+        <v>2.4614623172224408</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>2.7360079965687296</v>
+        <v>2.7387559711241662</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>2.8086240576850683</v>
+        <v>2.8114426366921283</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>2.9769566718019487</v>
+        <v>2.9799389202745177</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -15754,23 +15754,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>2.3201244601415412</v>
+        <v>2.3224680719626507</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>2.3720077652922638</v>
+        <v>2.3744018231476578</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>2.7768740490801092</v>
+        <v>2.7796617576170255</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>2.9020400519567464</v>
+        <v>2.9049494591490195</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>3.2225295814182924</v>
+        <v>3.2257505999418763</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -15781,23 +15781,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>2.2433529645096399</v>
+        <v>2.2456219315584205</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>2.3007070291113156</v>
+        <v>2.3030317614028997</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>2.8185100030007493</v>
+        <v>2.8213381940927542</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>3.0025861205388331</v>
+        <v>3.0055932884733729</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>3.5202804804334096</v>
+        <v>3.5237910015631986</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -15808,23 +15808,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>2.186679089391494</v>
+        <v>2.188892952544351</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>2.2467505100140786</v>
+        <v>2.2490227804895881</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>2.8572337505264271</v>
+        <v>2.8600995926410424</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>3.1016274185971993</v>
+        <v>3.1047308841886223</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>3.853542842288336</v>
+        <v>3.8573773937489366</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15834,23 +15834,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>2.1463297009137636</v>
+        <v>2.1485043324365507</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>2.2075927343526054</v>
+        <v>2.2098269318008135</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>2.8913934826340943</v>
+        <v>2.8942925381882159</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>3.1943804719550957</v>
+        <v>3.1975741211556006</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>4.2109737090541248</v>
+        <v>4.2151557898347374</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15885,7 +15885,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>3.2225295814182924</v>
+        <v>3.2257505999418763</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -15907,7 +15907,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>2.8086240576850683</v>
+        <v>2.8114426366921283</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -15930,7 +15930,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>2.7360079965687296</v>
+        <v>2.7387559711241662</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15953,7 +15953,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>2.458983692845881</v>
+        <v>2.4614623172224408</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -15976,7 +15976,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.3201244601415412</v>
+        <v>2.3224680719626507</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-2.13</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16097,7 +16097,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.11493915008339682</v>
+        <v>0.11482559357067031</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.11493915008339682</v>
+        <v>0.11482559357067031</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
@@ -16126,7 +16126,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>2.7989354710087788</v>
+        <v>2.8015193182028302</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>169796.37100392333</v>
+        <v>169794.09255357902</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16182,7 +16182,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>102735.97600993386</v>
+        <v>102734.26717217563</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16266,7 +16266,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>2.3897154844568171</v>
+        <v>2.3898381747651194</v>
       </c>
       <c r="E14" s="346"/>
       <c r="F14" s="346"/>
@@ -16317,7 +16317,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16332,7 +16332,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>2.6700070203175144</v>
+        <v>2.6726908222551682</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16379,7 +16379,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>2.7360079965687296</v>
+        <v>2.7387559711241662</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16437,7 +16437,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>2.458983692845881</v>
+        <v>2.4614623172224408</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16495,7 +16495,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>2.8086240576850683</v>
+        <v>2.8114426366921283</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16522,7 +16522,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>2.6951263480474275</v>
+        <v>2.6978345734574134</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16596,7 +16596,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>2.3201244601415412</v>
+        <v>2.3224680719626507</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16654,7 +16654,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>3.2225295814182924</v>
+        <v>3.2257505999418763</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16680,7 +16680,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>2.6839963209253819</v>
+        <v>2.6866937246321601</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16721,7 +16721,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>2.6975517216682041</v>
+        <v>2.7002623052641317</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -16805,7 +16805,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.61389425674854614</v>
+        <v>0.6139068686882968</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16838,7 +16838,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.11493915008339682</v>
+        <v>0.11482559357067031</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -16865,7 +16865,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.22436122096279057</v>
+        <v>0.22413955864994844</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -16877,7 +16877,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>1.3742061163137955</v>
+        <v>1.375587187011666</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>1.5985673372765861</v>
+        <v>1.5997267456616144</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16898,7 +16898,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.40440777626497049</v>
+        <v>0.40457420546488387</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16915,7 +16915,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16928,7 +16928,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1302840611640077</v>
+        <v>0.13244092382946393</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E98A4EE4-CF35-4B22-AC1F-D887EE6B00EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD8E736-4DB2-438B-81C9-7BFA61A884A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3701,29 +3701,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4079,7 +4079,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>2826.6670199999999</v>
+        <v>2946.6670349999999</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4134,13 +4134,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="336" t="s">
+      <c r="B12" s="338" t="s">
         <v>375</v>
       </c>
-      <c r="C12" s="336"/>
-      <c r="D12" s="336"/>
-      <c r="E12" s="336"/>
-      <c r="F12" s="336"/>
+      <c r="C12" s="338"/>
+      <c r="D12" s="338"/>
+      <c r="E12" s="338"/>
+      <c r="F12" s="338"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4174,7 +4174,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0624809</v>
+        <v>1.0653656200000001</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>1.5997267456616144</v>
+        <v>1.6029152090321055</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>319</v>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13244092382946393</v>
+        <v>0.11692472124626607</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4242,22 +4242,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="336" t="s">
+      <c r="B25" s="338" t="s">
         <v>376</v>
       </c>
-      <c r="C25" s="336"/>
-      <c r="D25" s="336"/>
-      <c r="E25" s="336"/>
-      <c r="F25" s="336"/>
+      <c r="C25" s="338"/>
+      <c r="D25" s="338"/>
+      <c r="E25" s="338"/>
+      <c r="F25" s="338"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="338" t="s">
+      <c r="B26" s="341" t="s">
         <v>352</v>
       </c>
-      <c r="C26" s="338"/>
-      <c r="D26" s="338"/>
-      <c r="E26" s="338"/>
-      <c r="F26" s="338"/>
+      <c r="C26" s="341"/>
+      <c r="D26" s="341"/>
+      <c r="E26" s="341"/>
+      <c r="F26" s="341"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4269,13 +4269,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="337" t="s">
+      <c r="B29" s="339" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="337"/>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
+      <c r="C29" s="339"/>
+      <c r="D29" s="339"/>
+      <c r="E29" s="339"/>
+      <c r="F29" s="339"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4295,13 +4295,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="337" t="s">
+      <c r="B32" s="339" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="337"/>
-      <c r="D32" s="337"/>
-      <c r="E32" s="337"/>
-      <c r="F32" s="337"/>
+      <c r="C32" s="339"/>
+      <c r="D32" s="339"/>
+      <c r="E32" s="339"/>
+      <c r="F32" s="339"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4330,13 +4330,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="337" t="s">
+      <c r="B36" s="339" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="337"/>
-      <c r="D36" s="337"/>
-      <c r="E36" s="337"/>
-      <c r="F36" s="337"/>
+      <c r="C36" s="339"/>
+      <c r="D36" s="339"/>
+      <c r="E36" s="339"/>
+      <c r="F36" s="339"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4352,13 +4352,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="337" t="s">
+      <c r="B39" s="339" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="337"/>
-      <c r="D39" s="337"/>
-      <c r="E39" s="337"/>
-      <c r="F39" s="337"/>
+      <c r="C39" s="339"/>
+      <c r="D39" s="339"/>
+      <c r="E39" s="339"/>
+      <c r="F39" s="339"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>25082.092553579027</v>
+        <v>25075.854182448693</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>23202.092553579027</v>
+        <v>23195.854182448693</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4422,13 +4422,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="337" t="s">
+      <c r="B47" s="339" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="337"/>
-      <c r="D47" s="337"/>
-      <c r="E47" s="337"/>
-      <c r="F47" s="337"/>
+      <c r="C47" s="339"/>
+      <c r="D47" s="339"/>
+      <c r="E47" s="339"/>
+      <c r="F47" s="339"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-34244.755724058545</v>
+        <v>-34243.196131275967</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4444,7 +4444,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="337" t="s">
+      <c r="B50" s="339" t="s">
         <v>351</v>
       </c>
       <c r="C50" s="340"/>
@@ -4466,22 +4466,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="336" t="s">
+      <c r="B53" s="338" t="s">
         <v>356</v>
       </c>
-      <c r="C53" s="336"/>
-      <c r="D53" s="336"/>
-      <c r="E53" s="336"/>
-      <c r="F53" s="336"/>
+      <c r="C53" s="338"/>
+      <c r="D53" s="338"/>
+      <c r="E53" s="338"/>
+      <c r="F53" s="338"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="336" t="s">
+      <c r="B54" s="338" t="s">
         <v>377</v>
       </c>
-      <c r="C54" s="336"/>
-      <c r="D54" s="336"/>
-      <c r="E54" s="336"/>
-      <c r="F54" s="336"/>
+      <c r="C54" s="338"/>
+      <c r="D54" s="338"/>
+      <c r="E54" s="338"/>
+      <c r="F54" s="338"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>169794.09255357902</v>
+        <v>169787.8541824487</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>102734.26717217563</v>
+        <v>102729.5883938279</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.8615512854405329E-2</v>
+        <v>3.7141818309151198E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.4163015835221838E-2</v>
+        <v>5.1816595986551785E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4542,22 +4542,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="336" t="s">
+      <c r="B63" s="338" t="s">
         <v>378</v>
       </c>
-      <c r="C63" s="336"/>
-      <c r="D63" s="336"/>
-      <c r="E63" s="336"/>
-      <c r="F63" s="336"/>
+      <c r="C63" s="338"/>
+      <c r="D63" s="338"/>
+      <c r="E63" s="338"/>
+      <c r="F63" s="338"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="338" t="s">
+      <c r="B64" s="341" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="338"/>
-      <c r="D64" s="338"/>
-      <c r="E64" s="338"/>
-      <c r="F64" s="338"/>
+      <c r="C64" s="341"/>
+      <c r="D64" s="341"/>
+      <c r="E64" s="341"/>
+      <c r="F64" s="341"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4615,22 +4615,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="336" t="s">
+      <c r="B73" s="338" t="s">
         <v>379</v>
       </c>
-      <c r="C73" s="336"/>
-      <c r="D73" s="336"/>
-      <c r="E73" s="336"/>
-      <c r="F73" s="336"/>
+      <c r="C73" s="338"/>
+      <c r="D73" s="338"/>
+      <c r="E73" s="338"/>
+      <c r="F73" s="338"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="336" t="s">
+      <c r="B74" s="338" t="s">
         <v>380</v>
       </c>
-      <c r="C74" s="336"/>
-      <c r="D74" s="336"/>
-      <c r="E74" s="336"/>
-      <c r="F74" s="336"/>
+      <c r="C74" s="338"/>
+      <c r="D74" s="338"/>
+      <c r="E74" s="338"/>
+      <c r="F74" s="338"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.0233110906417415</v>
+        <v>1.0260427307903019</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4667,13 +4667,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="336" t="s">
+      <c r="B81" s="338" t="s">
         <v>381</v>
       </c>
-      <c r="C81" s="336"/>
-      <c r="D81" s="336"/>
-      <c r="E81" s="336"/>
-      <c r="F81" s="336"/>
+      <c r="C81" s="338"/>
+      <c r="D81" s="338"/>
+      <c r="E81" s="338"/>
+      <c r="F81" s="338"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="336" t="s">
+      <c r="B85" s="338" t="s">
         <v>357</v>
       </c>
-      <c r="C85" s="336"/>
-      <c r="D85" s="336"/>
-      <c r="E85" s="336"/>
-      <c r="F85" s="336"/>
+      <c r="C85" s="338"/>
+      <c r="D85" s="338"/>
+      <c r="E85" s="338"/>
+      <c r="F85" s="338"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>2.7092462702767162E-2</v>
+        <v>2.7166020890032391E-2</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="C91" s="188">
         <f>Valuation_Model!C8</f>
-        <v>1874256.2265554145</v>
+        <v>1874463.5042082514</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.4935208951257886</v>
+        <v>1.4977415427784546</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C96" s="248">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.18295129919040506</v>
+        <v>0.18344802649326819</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4796,13 +4796,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="336" t="s">
+      <c r="B98" s="338" t="s">
         <v>382</v>
       </c>
-      <c r="C98" s="336"/>
-      <c r="D98" s="336"/>
-      <c r="E98" s="336"/>
-      <c r="F98" s="336"/>
+      <c r="C98" s="338"/>
+      <c r="D98" s="338"/>
+      <c r="E98" s="338"/>
+      <c r="F98" s="338"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
-        <v>2.6726908222551682</v>
+        <v>2.6800662791719922</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4828,13 +4828,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="337" t="s">
+      <c r="B104" s="339" t="s">
         <v>383</v>
       </c>
-      <c r="C104" s="337"/>
-      <c r="D104" s="337"/>
-      <c r="E104" s="337"/>
-      <c r="F104" s="337"/>
+      <c r="C104" s="339"/>
+      <c r="D104" s="339"/>
+      <c r="E104" s="339"/>
+      <c r="F104" s="339"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="E108" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>2.81 HKD</v>
+        <v>2.82 HKD</v>
       </c>
       <c r="F108" s="246">
         <f>Valuation_Model!F75</f>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="E109" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>2.74 HKD</v>
+        <v>2.75 HKD</v>
       </c>
       <c r="F109" s="246">
         <f>Valuation_Model!F76</f>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="E110" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>2.46 HKD</v>
+        <v>2.47 HKD</v>
       </c>
       <c r="F110" s="246">
         <f>Valuation_Model!F77</f>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="E111" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>2.32 HKD</v>
+        <v>2.33 HKD</v>
       </c>
       <c r="F111" s="246">
         <f>Valuation_Model!F78</f>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="C113" s="241">
         <f>Scenarios!C60</f>
-        <v>2.6866937246321601</v>
+        <v>2.6941065610816408</v>
       </c>
       <c r="D113" s="236" t="str">
         <f>Market_currency</f>
@@ -4977,13 +4977,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="341" t="s">
+      <c r="B115" s="342" t="s">
         <v>386</v>
       </c>
-      <c r="C115" s="341"/>
-      <c r="D115" s="341"/>
-      <c r="E115" s="341"/>
-      <c r="F115" s="341"/>
+      <c r="C115" s="342"/>
+      <c r="D115" s="342"/>
+      <c r="E115" s="342"/>
+      <c r="F115" s="342"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4996,22 +4996,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="339" t="s">
+      <c r="B119" s="343" t="s">
         <v>384</v>
       </c>
-      <c r="C119" s="339"/>
-      <c r="D119" s="339"/>
-      <c r="E119" s="339"/>
-      <c r="F119" s="339"/>
+      <c r="C119" s="343"/>
+      <c r="D119" s="343"/>
+      <c r="E119" s="343"/>
+      <c r="F119" s="343"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="336" t="s">
+      <c r="B120" s="338" t="s">
         <v>385</v>
       </c>
-      <c r="C120" s="336"/>
-      <c r="D120" s="336"/>
-      <c r="E120" s="336"/>
-      <c r="F120" s="336"/>
+      <c r="C120" s="338"/>
+      <c r="D120" s="338"/>
+      <c r="E120" s="338"/>
+      <c r="F120" s="338"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="C124" s="237">
         <f>Scenarios!C77</f>
-        <v>0.11482559357067031</v>
+        <v>0.11451467713027945</v>
       </c>
       <c r="D124" s="236" t="str">
         <f>Market_currency</f>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="C127" s="240">
         <f>Scenarios!C81</f>
-        <v>0.22413955864994844</v>
+        <v>0.2235326497583055</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>1.375587187011666</v>
+        <v>1.3793825592738</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>1.5997267456616144</v>
+        <v>1.6029152090321055</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="C130" s="92">
         <f>Scenarios!F83</f>
-        <v>0.40457420546488387</v>
+        <v>0.405029024394432</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -5107,13 +5107,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="343" t="s">
+      <c r="B134" s="337" t="s">
         <v>392</v>
       </c>
-      <c r="C134" s="336"/>
-      <c r="D134" s="336"/>
-      <c r="E134" s="336"/>
-      <c r="F134" s="336"/>
+      <c r="C134" s="338"/>
+      <c r="D134" s="338"/>
+      <c r="E134" s="338"/>
+      <c r="F134" s="338"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5150,13 +5150,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="337" t="s">
+      <c r="B143" s="339" t="s">
         <v>397</v>
       </c>
-      <c r="C143" s="337"/>
-      <c r="D143" s="337"/>
-      <c r="E143" s="337"/>
-      <c r="F143" s="337"/>
+      <c r="C143" s="339"/>
+      <c r="D143" s="339"/>
+      <c r="E143" s="339"/>
+      <c r="F143" s="339"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5164,22 +5164,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="342" t="s">
+      <c r="B146" s="336" t="s">
         <v>398</v>
       </c>
-      <c r="C146" s="342"/>
-      <c r="D146" s="342"/>
-      <c r="E146" s="342"/>
-      <c r="F146" s="342"/>
+      <c r="C146" s="336"/>
+      <c r="D146" s="336"/>
+      <c r="E146" s="336"/>
+      <c r="F146" s="336"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="342" t="s">
+      <c r="B147" s="336" t="s">
         <v>399</v>
       </c>
-      <c r="C147" s="342"/>
-      <c r="D147" s="342"/>
-      <c r="E147" s="342"/>
-      <c r="F147" s="342"/>
+      <c r="C147" s="336"/>
+      <c r="D147" s="336"/>
+      <c r="E147" s="336"/>
+      <c r="F147" s="336"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5203,17 +5203,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5230,6 +5219,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -5721,15 +5721,15 @@
       </c>
       <c r="C25" s="39">
         <f>(0.0682+0.0538)/Exchange_Rate</f>
-        <v>0.11482559357067031</v>
+        <v>0.11451467713027945</v>
       </c>
       <c r="D25" s="39">
         <f>(0.064+0.041)/Exchange_Rate</f>
-        <v>9.8825305941970365E-2</v>
+        <v>9.8557713923601173E-2</v>
       </c>
       <c r="E25" s="39">
         <f>(0.022+0.0168)/Exchange_Rate</f>
-        <v>3.6518303529032854E-2</v>
+        <v>3.6419421907006908E-2</v>
       </c>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
@@ -7021,15 +7021,15 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.11482559357067031</v>
+        <v>0.11451467713027945</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>9.8825305941970365E-2</v>
+        <v>9.8557713923601173E-2</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>3.6518303529032854E-2</v>
+        <v>3.6419421907006908E-2</v>
       </c>
       <c r="F65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8372,11 +8372,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>2.5184571301528087</v>
+        <v>2.5252949412160426</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.8579480849902972</v>
+        <v>1.8629925615542839</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>1874256.2265554145</v>
+        <v>1874463.5042082514</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>228</v>
@@ -8634,11 +8634,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-151276.73421376329</v>
+        <v>-151242.18793829044</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-138897.29557409757</v>
+        <v>-138862.74929862475</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>364</v>
@@ -8650,11 +8650,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>17.898588398754953</v>
+        <v>17.902676739275726</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>19.493828074971802</v>
+        <v>19.498677749618885</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>331</v>
@@ -8667,7 +8667,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>833383.7734445855</v>
+        <v>833176.49579174852</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>365</v>
@@ -8782,11 +8782,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-36123.288119099998</v>
+        <v>-36221.365714380001</v>
       </c>
       <c r="D86" s="248">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-2.7092462702767162E-2</v>
+        <v>-2.7166020890032391E-2</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -8799,11 +8799,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>1991361.4424212007</v>
+        <v>1996988.9733281967</v>
       </c>
       <c r="D87" s="248">
         <f>C87*$H$1/Common_Shares</f>
-        <v>1.4935208951257888</v>
+        <v>1.4977415427784546</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -8816,11 +8816,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>243935.09607908997</v>
+        <v>244597.39923236199</v>
       </c>
       <c r="D88" s="248">
         <f>C88*$H$1/Common_Shares</f>
-        <v>0.18295129919040506</v>
+        <v>0.18344802649326819</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -8833,11 +8833,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>2199173.2503811908</v>
+        <v>2205365.0068461788</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>1.6493797316134267</v>
+        <v>1.6540235483816903</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9417,20 +9417,20 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>23202.092553579027</v>
+        <v>23195.854182448693</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>23202.092553579027</v>
+        <v>23195.854182448693</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>21713.420720286904</v>
+        <v>21707.770734628681</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>13095.264069710875</v>
+        <v>13091.792396387922</v>
       </c>
       <c r="J12" s="191" t="str">
         <f t="shared" si="6"/>
@@ -9472,20 +9472,20 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>136979.02289623418</v>
+        <v>136972.78452510387</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>217064.09255357902</v>
+        <v>217057.8541824487</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>147529.4207202869</v>
+        <v>147523.77073462869</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>35793.264069710873</v>
+        <v>35789.792396387922</v>
       </c>
       <c r="J13" s="184" t="str">
         <f t="shared" si="7"/>
@@ -9527,7 +9527,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-34244.755724058545</v>
+        <v>-34243.196131275967</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -9639,22 +9639,22 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>102734.26717217563</v>
+        <v>102729.5883938279</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>169794.09255357902</v>
+        <v>169787.8541824487</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>103080.4207202869</v>
+        <v>103074.77073462869</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>14776.264069710873</v>
+        <v>14772.792396387922</v>
       </c>
       <c r="J16" s="184" t="str">
         <f t="shared" si="8"/>
@@ -9747,22 +9747,22 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>102734.26717217563</v>
+        <v>102729.5883938279</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>169794.09255357902</v>
+        <v>169787.8541824487</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>103080.4207202869</v>
+        <v>103074.77073462869</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>14776.264069710873</v>
+        <v>14772.792396387922</v>
       </c>
       <c r="J19" s="186" t="str">
         <f t="shared" si="9"/>
@@ -10608,15 +10608,15 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.26103029344918055</v>
+        <v>0.26103928598942744</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.35035787554946585</v>
+        <v>0.35037347928068158</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>1.3748045369113253</v>
+        <v>1.3751168201530288</v>
       </c>
       <c r="J43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -10746,20 +10746,20 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>25082.092553579027</v>
+        <v>25075.854182448693</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>25082.092553579027</v>
+        <v>25075.854182448693</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>22716.420720286904</v>
+        <v>22710.770734628681</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>13958.264069710875</v>
+        <v>13954.792396387922</v>
       </c>
       <c r="J48" s="328" t="str">
         <f t="shared" si="19"/>
@@ -10858,20 +10858,20 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>23202.092553579027</v>
+        <v>23195.854182448693</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>23202.092553579027</v>
+        <v>23195.854182448693</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>21713.420720286904</v>
+        <v>21707.770734628681</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>13095.264069710875</v>
+        <v>13091.792396387922</v>
       </c>
       <c r="J50" s="184" t="str">
         <f t="shared" si="20"/>
@@ -11945,22 +11945,22 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>1.4256771542268861E-2</v>
+        <v>1.4252938309046658E-2</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>1.2747646048244955E-2</v>
+        <v>1.2744218575188227E-2</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>1.343997420147309E-2</v>
+        <v>1.3436477025120115E-2</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>9.0522052301341971E-3</v>
+        <v>9.0498054083937522E-3</v>
       </c>
       <c r="J80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -12002,22 +12002,22 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>8.4168211595793588E-2</v>
+        <v>8.4164378362571401E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.11925890801731491</v>
+        <v>0.1192554805442582</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>9.1316409053245048E-2</v>
+        <v>9.1312911876892083E-2</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>2.4742377892541793E-2</v>
+        <v>2.473997807080135E-2</v>
       </c>
       <c r="J81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -12059,7 +12059,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.1042052898948397E-2</v>
+        <v>2.104109459064285E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12174,22 +12174,22 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>6.3126158696845194E-2</v>
+        <v>6.3123283771928551E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.3287921680240415E-2</v>
+        <v>9.3284494207183696E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>6.3803774311030931E-2</v>
+        <v>6.3800277134677966E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>1.0214209822851931E-2</v>
+        <v>1.0211810001111489E-2</v>
       </c>
       <c r="J84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -12281,22 +12281,22 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>6.3126158696845194E-2</v>
+        <v>6.3123283771928551E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.3287921680240415E-2</v>
+        <v>9.3284494207183696E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>6.3803774311030931E-2</v>
+        <v>6.3800277134677966E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>1.0214209822851931E-2</v>
+        <v>1.0211810001111489E-2</v>
       </c>
       <c r="J87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -12350,20 +12350,20 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.11482559357067031</v>
+        <v>0.11451467713027945</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.11482559357067031</v>
+        <v>0.11451467713027945</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>9.8825305941970365E-2</v>
+        <v>9.8557713923601173E-2</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>3.6518303529032854E-2</v>
+        <v>3.6419421907006908E-2</v>
       </c>
       <c r="J90" s="113" t="str">
         <f>Data!F65</f>
@@ -12406,20 +12406,20 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/$C$3</f>
-        <v>153100.81056515937</v>
+        <v>152686.25525948545</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
-        <v>153100.81056515937</v>
+        <v>152686.25525948545</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>131767.09106017815</v>
+        <v>131410.30165775388</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>48691.077458427724</v>
+        <v>48559.235279246197</v>
       </c>
       <c r="J91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12461,20 +12461,20 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>1.4902604046279202</v>
+        <v>1.4862928747863942</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>0.90168514264916466</v>
+        <v>0.89927666495751568</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>1.2782940750478089</v>
+        <v>1.2749026820159173</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>3.295222474958142</v>
+        <v>3.2870722051925236</v>
       </c>
       <c r="J92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12516,20 +12516,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.4163015835221838E-2</v>
+        <v>5.1816595986551785E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.4163015835221838E-2</v>
+        <v>5.1816595986551785E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>4.6615710349986017E-2</v>
+        <v>4.4596250644163428E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>1.7225614872185307E-2</v>
+        <v>1.6479376428509912E-2</v>
       </c>
       <c r="J93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -12653,18 +12653,18 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.36894664942142397</v>
+        <v>-0.36895725316637962</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>0.47132749178978073</v>
+        <v>0.47134155466308236</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>3.1217090576863562</v>
+        <v>3.1219510049328338</v>
       </c>
       <c r="I97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13372,20 +13372,20 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>8.4168211595793588E-2</v>
+        <v>8.4164378362571401E-2</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.11925890801731491</v>
+        <v>0.1192554805442582</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>9.1316409053245048E-2</v>
+        <v>9.1312911876892083E-2</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>2.4742377892541793E-2</v>
+        <v>2.473997807080135E-2</v>
       </c>
       <c r="J117" s="23" t="str">
         <f t="shared" si="45"/>
@@ -13658,22 +13658,22 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>8.1864887251339308E-2</v>
+        <v>8.2083418463224159E-2</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.13530221829048014</v>
+        <v>0.13566458994659183</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>8.2140723366861387E-2</v>
+        <v>8.2359227477638228E-2</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.1774622288740266E-2</v>
+        <v>1.1803817372404659E-2</v>
       </c>
       <c r="J124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -13715,22 +13715,22 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.8615512854405329E-2</v>
+        <v>3.7141818309151198E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.3821801080415158E-2</v>
+        <v>6.1386692283525716E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>3.8745624229651596E-2</v>
+        <v>3.7266618768162098E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>5.5540671173303141E-3</v>
+        <v>5.3410938336672662E-3</v>
       </c>
       <c r="J125" s="77" t="str">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
@@ -13772,15 +13772,15 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9073930045004034E-2</v>
+        <v>6.6260964568058162E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.1138081980381259E-2</v>
+        <v>5.8648295836383833E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.3156600879009795E-2</v>
+        <v>2.2213571883936998E-2</v>
       </c>
       <c r="J126" s="23" t="str">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14558,7 +14558,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>102734.26717217563</v>
+        <v>102729.5883938279</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14590,7 +14590,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>1284178.3396521953</v>
+        <v>1284119.8549228488</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14624,7 +14624,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>1874256.2265554145</v>
+        <v>1874463.5042082514</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -14656,7 +14656,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>3354025.6662076102</v>
+        <v>3354174.4591311002</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -14670,7 +14670,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0624809</v>
+        <v>1.0653656200000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>2.6726908222551682</v>
+        <v>2.6800662791719922</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14737,7 +14737,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>2.7002623052641317</v>
+        <v>2.7077113618620618</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14772,7 +14772,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>103615.51159452461</v>
+        <v>103610.79268207715</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>95940.288513448701</v>
+        <v>95935.919150071422</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -14794,7 +14794,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>104504.31524470766</v>
+        <v>104499.55585389414</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -14806,7 +14806,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>89595.606348343324</v>
+        <v>89591.525937837912</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -14816,7 +14816,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>105400.74296503638</v>
+        <v>105395.94274863736</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -14828,7 +14828,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>83670.507993125706</v>
+        <v>83666.697426584287</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -14838,7 +14838,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>106304.86015403339</v>
+        <v>106300.01876185102</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -14850,7 +14850,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>78137.245710566713</v>
+        <v>78133.687142783587</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>107216.73277120334</v>
+        <v>107211.84985003581</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -14872,7 +14872,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>72969.906764939136</v>
+        <v>72966.583530840071</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -14882,7 +14882,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>108136.42734184505</v>
+        <v>108131.50253546081</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -14894,7 +14894,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>68144.292070482436</v>
+        <v>68141.18860708081</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -14904,7 +14904,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>109064.01096190471</v>
+        <v>109059.0439110165</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -14916,7 +14916,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>63637.802865035483</v>
+        <v>63634.904638549429</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -14926,7 +14926,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>109999.55130287107</v>
+        <v>109994.5416451097</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>59429.334878120004</v>
+        <v>59426.628315909533</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -14948,7 +14948,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>110943.11661671211</v>
+        <v>110938.06398660003</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -14960,7 +14960,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>55499.179497855243</v>
+        <v>55496.65192486038</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>111894.77574085457</v>
+        <v>111889.67976977916</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>51828.931473859935</v>
+        <v>51826.57105324234</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15432,7 +15432,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>1295193.8949315576</v>
+        <v>1295134.9085259645</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15444,7 +15444,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>599925.37793933623</v>
+        <v>599898.05582037999</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>1318778.4740551128</v>
+        <v>1318718.4135481399</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15476,7 +15476,7 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>1318778.4740551128</v>
+        <v>1318718.4135481399</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15506,19 +15506,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>1093829.5265564455</v>
+        <v>1093779.71079345</v>
       </c>
       <c r="C56" s="124">
-        <v>1129818.8557687418</v>
+        <v>1129767.4009606747</v>
       </c>
       <c r="D56" s="124">
-        <v>1325612.6552185873</v>
+        <v>1325552.28346572</v>
       </c>
       <c r="E56" s="124">
-        <v>1368287.9104549829</v>
+        <v>1368225.5951630641</v>
       </c>
       <c r="F56" s="124">
-        <v>1457580.751819825</v>
+        <v>1457514.3699060839</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15527,19 +15527,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>966051.28736853006</v>
+        <v>966007.29094970552</v>
       </c>
       <c r="C57" s="124">
-        <v>1019102.4762507419</v>
+        <v>1019056.0637466062</v>
       </c>
       <c r="D57" s="124">
-        <v>1367085.1252419623</v>
+        <v>1367022.8647279236</v>
       </c>
       <c r="E57" s="124">
-        <v>1458301.4155348614</v>
+        <v>1458235.000800272</v>
       </c>
       <c r="F57" s="124">
-        <v>1669751.5597453592</v>
+        <v>1669675.515036433</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15548,19 +15548,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>844675.16794609907</v>
+        <v>844636.69930272014</v>
       </c>
       <c r="C58" s="124">
-        <v>909848.11386506481</v>
+        <v>909806.6770809025</v>
       </c>
       <c r="D58" s="124">
-        <v>1418418.8061342752</v>
+        <v>1418354.2077545833</v>
       </c>
       <c r="E58" s="124">
-        <v>1575645.4344817675</v>
+        <v>1575573.6756037856</v>
       </c>
       <c r="F58" s="124">
-        <v>1978226.7023966366</v>
+        <v>1978136.608949563</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15569,19 +15569,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>748239.0500387901</v>
+        <v>748204.97334011295</v>
       </c>
       <c r="C59" s="124">
-        <v>820284.06219942705</v>
+        <v>820246.7043886903</v>
       </c>
       <c r="D59" s="124">
-        <v>1470719.5947072371</v>
+        <v>1470652.6144173618</v>
       </c>
       <c r="E59" s="124">
-        <v>1701945.8594648822</v>
+        <v>1701868.3485461257</v>
       </c>
       <c r="F59" s="124">
-        <v>2352244.957063769</v>
+        <v>2352137.8298794646</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -15590,19 +15590,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>677048.45438642963</v>
+        <v>677017.61988752359</v>
       </c>
       <c r="C60" s="124">
-        <v>752506.8592844574</v>
+        <v>752472.58821895358</v>
       </c>
       <c r="D60" s="124">
-        <v>1519362.2302513521</v>
+        <v>1519293.0346528338</v>
       </c>
       <c r="E60" s="124">
-        <v>1826356.0747229613</v>
+        <v>1826272.8978483616</v>
       </c>
       <c r="F60" s="124">
-        <v>2770870.7524501928</v>
+        <v>2770744.5599884391</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -15611,19 +15611,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>626363.7783527209</v>
+        <v>626335.2521621458</v>
       </c>
       <c r="C61" s="124">
-        <v>703319.02153822163</v>
+        <v>703286.99061124749</v>
       </c>
       <c r="D61" s="124">
-        <v>1562271.801389735</v>
+        <v>1562200.6515808266</v>
       </c>
       <c r="E61" s="124">
-        <v>1942867.3438634337</v>
+        <v>1942778.8607709736</v>
       </c>
       <c r="F61" s="124">
-        <v>3219855.6905111652</v>
+        <v>3219709.0501398249</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -15673,23 +15673,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>2.6726908222551682</v>
+        <v>2.6800662791719922</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>2.6726908222551682</v>
+        <v>2.6800662791719922</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>2.6726908222551682</v>
+        <v>2.6800662791719922</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>2.6726908222551682</v>
+        <v>2.6800662791719922</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>2.6726908222551682</v>
+        <v>2.6800662791719922</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -15700,23 +15700,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.521009357526423</v>
+        <v>2.5279799139368087</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>2.5496878351105212</v>
+        <v>2.5567349462279592</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>2.7057081947983943</v>
+        <v>2.7131717887258149</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>2.7397144232410873</v>
+        <v>2.74726879384411</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>2.8108683681894999</v>
+        <v>2.8186126780734777</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15727,23 +15727,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>2.4191879163245091</v>
+        <v>2.4258866692341656</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>2.4614623172224408</v>
+        <v>2.4682739179765165</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>2.7387559711241662</v>
+        <v>2.7463077832224418</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>2.8114426366921283</v>
+        <v>2.8191884795360358</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>2.9799389202745177</v>
+        <v>2.9881345493245219</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -15754,23 +15754,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>2.3224680719626507</v>
+        <v>2.3289086396416012</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>2.3744018231476578</v>
+        <v>2.3809810234683333</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>2.7796617576170255</v>
+        <v>2.7873227641623415</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>2.9049494591490195</v>
+        <v>2.9129449103404998</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>3.2257505999418763</v>
+        <v>3.23460240193802</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -15781,23 +15781,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>2.2456219315584205</v>
+        <v>2.2518573651346436</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>2.3030317614028997</v>
+        <v>2.3094204455375884</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>2.8213381940927542</v>
+        <v>2.8291104522683574</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>3.0055932884733729</v>
+        <v>3.0138573996328737</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>3.5237910015631986</v>
+        <v>3.5334383965460776</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -15808,23 +15808,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>2.188892952544351</v>
+        <v>2.1949769530343124</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>2.2490227804895881</v>
+        <v>2.2552672923368897</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>2.8600995926410424</v>
+        <v>2.8679753210061674</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>3.1047308841886223</v>
+        <v>3.1132596345562424</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>3.8573773937489366</v>
+        <v>3.8679152686555085</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15834,23 +15834,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>2.1485043324365507</v>
+        <v>2.1544805190102547</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>2.2098269318008135</v>
+        <v>2.2159668137316464</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>2.8942925381882159</v>
+        <v>2.90225954165405</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>3.1975741211556006</v>
+        <v>3.2063507084869172</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>4.2151557898347374</v>
+        <v>4.2266487231199132</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15885,7 +15885,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>3.2257505999418763</v>
+        <v>3.23460240193802</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -15907,7 +15907,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>2.8114426366921283</v>
+        <v>2.8191884795360358</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -15930,7 +15930,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>2.7387559711241662</v>
+        <v>2.7463077832224418</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15953,7 +15953,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>2.4614623172224408</v>
+        <v>2.4682739179765165</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -15976,7 +15976,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.3224680719626507</v>
+        <v>2.3289086396416012</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-2.12</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16097,7 +16097,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.11482559357067031</v>
+        <v>0.11451467713027945</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.11482559357067031</v>
+        <v>0.11451467713027945</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
@@ -16126,7 +16126,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>2.8015193182028302</v>
+        <v>2.8086212382119204</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>169794.09255357902</v>
+        <v>169787.8541824487</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16182,7 +16182,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>102734.26717217563</v>
+        <v>102729.5883938279</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16266,7 +16266,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>2.3898381747651194</v>
+        <v>2.3901741844763329</v>
       </c>
       <c r="E14" s="346"/>
       <c r="F14" s="346"/>
@@ -16317,7 +16317,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16332,7 +16332,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>2.6726908222551682</v>
+        <v>2.6800662791719922</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16379,7 +16379,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>2.7387559711241662</v>
+        <v>2.7463077832224418</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16437,7 +16437,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>2.4614623172224408</v>
+        <v>2.4682739179765165</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16495,7 +16495,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>2.8114426366921283</v>
+        <v>2.8191884795360358</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16522,7 +16522,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>2.6978345734574134</v>
+        <v>2.7052771494359757</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16596,7 +16596,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>2.3224680719626507</v>
+        <v>2.3289086396416012</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16654,7 +16654,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>3.2257505999418763</v>
+        <v>3.23460240193802</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16680,7 +16680,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>2.6866937246321601</v>
+        <v>2.6941065610816408</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>2.7002623052641317</v>
+        <v>2.7077113618620618</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -16805,7 +16805,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.6139068686882968</v>
+        <v>0.61394139796668856</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16838,7 +16838,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.11482559357067031</v>
+        <v>0.11451467713027945</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -16865,7 +16865,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.22413955864994844</v>
+        <v>0.2235326497583055</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -16877,7 +16877,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>1.375587187011666</v>
+        <v>1.3793825592738</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>1.5997267456616144</v>
+        <v>1.6029152090321055</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16898,7 +16898,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.40457420546488387</v>
+        <v>0.405029024394432</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16915,7 +16915,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16928,7 +16928,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13244092382946393</v>
+        <v>0.11692472124626607</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD8E736-4DB2-438B-81C9-7BFA61A884A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F774E9-2F59-47C8-93C2-594CD86AE19C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3701,29 +3701,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4079,7 +4079,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>2.21</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>2946.6670349999999</v>
+        <v>3066.66705</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4134,13 +4134,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
+      <c r="B12" s="336" t="s">
         <v>375</v>
       </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="C12" s="336"/>
+      <c r="D12" s="336"/>
+      <c r="E12" s="336"/>
+      <c r="F12" s="336"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4174,7 +4174,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0653656200000001</v>
+        <v>1.0667112500000002</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>1.6029152090321055</v>
+        <v>1.6044036483689859</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>319</v>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11692472124626607</v>
+        <v>0.10185445179346719</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4242,22 +4242,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
+      <c r="B25" s="336" t="s">
         <v>376</v>
       </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="C25" s="336"/>
+      <c r="D25" s="336"/>
+      <c r="E25" s="336"/>
+      <c r="F25" s="336"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
+      <c r="B26" s="338" t="s">
         <v>352</v>
       </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="C26" s="338"/>
+      <c r="D26" s="338"/>
+      <c r="E26" s="338"/>
+      <c r="F26" s="338"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4269,13 +4269,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="339" t="s">
+      <c r="B29" s="337" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="339"/>
-      <c r="D29" s="339"/>
-      <c r="E29" s="339"/>
-      <c r="F29" s="339"/>
+      <c r="C29" s="337"/>
+      <c r="D29" s="337"/>
+      <c r="E29" s="337"/>
+      <c r="F29" s="337"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4295,13 +4295,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="339" t="s">
+      <c r="B32" s="337" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="339"/>
-      <c r="D32" s="339"/>
-      <c r="E32" s="339"/>
-      <c r="F32" s="339"/>
+      <c r="C32" s="337"/>
+      <c r="D32" s="337"/>
+      <c r="E32" s="337"/>
+      <c r="F32" s="337"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4330,13 +4330,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="339" t="s">
+      <c r="B36" s="337" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="339"/>
-      <c r="D36" s="339"/>
-      <c r="E36" s="339"/>
-      <c r="F36" s="339"/>
+      <c r="C36" s="337"/>
+      <c r="D36" s="337"/>
+      <c r="E36" s="337"/>
+      <c r="F36" s="337"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4352,13 +4352,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="339" t="s">
+      <c r="B39" s="337" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="339"/>
-      <c r="D39" s="339"/>
-      <c r="E39" s="339"/>
-      <c r="F39" s="339"/>
+      <c r="C39" s="337"/>
+      <c r="D39" s="337"/>
+      <c r="E39" s="337"/>
+      <c r="F39" s="337"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>25075.854182448693</v>
+        <v>25072.955721459057</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>23195.854182448693</v>
+        <v>23192.955721459057</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4422,13 +4422,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="339" t="s">
+      <c r="B47" s="337" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="339"/>
-      <c r="D47" s="339"/>
-      <c r="E47" s="339"/>
-      <c r="F47" s="339"/>
+      <c r="C47" s="337"/>
+      <c r="D47" s="337"/>
+      <c r="E47" s="337"/>
+      <c r="F47" s="337"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-34243.196131275967</v>
+        <v>-34242.471516028556</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4444,7 +4444,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="339" t="s">
+      <c r="B50" s="337" t="s">
         <v>351</v>
       </c>
       <c r="C50" s="340"/>
@@ -4466,22 +4466,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
+      <c r="B53" s="336" t="s">
         <v>356</v>
       </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="C53" s="336"/>
+      <c r="D53" s="336"/>
+      <c r="E53" s="336"/>
+      <c r="F53" s="336"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
+      <c r="B54" s="336" t="s">
         <v>377</v>
       </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="C54" s="336"/>
+      <c r="D54" s="336"/>
+      <c r="E54" s="336"/>
+      <c r="F54" s="336"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>169787.8541824487</v>
+        <v>169784.95572145906</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>102729.5883938279</v>
+        <v>102727.41454808567</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.7141818309151198E-2</v>
+        <v>3.5732763614444767E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.1816595986551785E-2</v>
+        <v>4.972618247053226E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4542,22 +4542,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
+      <c r="B63" s="336" t="s">
         <v>378</v>
       </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="C63" s="336"/>
+      <c r="D63" s="336"/>
+      <c r="E63" s="336"/>
+      <c r="F63" s="336"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="338" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="338"/>
+      <c r="D64" s="338"/>
+      <c r="E64" s="338"/>
+      <c r="F64" s="338"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4615,22 +4615,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
+      <c r="B73" s="336" t="s">
         <v>379</v>
       </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
+      <c r="C73" s="336"/>
+      <c r="D73" s="336"/>
+      <c r="E73" s="336"/>
+      <c r="F73" s="336"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="338" t="s">
+      <c r="B74" s="336" t="s">
         <v>380</v>
       </c>
-      <c r="C74" s="338"/>
-      <c r="D74" s="338"/>
-      <c r="E74" s="338"/>
-      <c r="F74" s="338"/>
+      <c r="C74" s="336"/>
+      <c r="D74" s="336"/>
+      <c r="E74" s="336"/>
+      <c r="F74" s="336"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.0260427307903019</v>
+        <v>1.0273169539152871</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4667,13 +4667,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="338" t="s">
+      <c r="B81" s="336" t="s">
         <v>381</v>
       </c>
-      <c r="C81" s="338"/>
-      <c r="D81" s="338"/>
-      <c r="E81" s="338"/>
-      <c r="F81" s="338"/>
+      <c r="C81" s="336"/>
+      <c r="D81" s="336"/>
+      <c r="E81" s="336"/>
+      <c r="F81" s="336"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="338" t="s">
+      <c r="B85" s="336" t="s">
         <v>357</v>
       </c>
-      <c r="C85" s="338"/>
-      <c r="D85" s="338"/>
-      <c r="E85" s="338"/>
-      <c r="F85" s="338"/>
+      <c r="C85" s="336"/>
+      <c r="D85" s="336"/>
+      <c r="E85" s="336"/>
+      <c r="F85" s="336"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>2.7166020890032391E-2</v>
+        <v>2.7200333441520827E-2</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="C91" s="188">
         <f>Valuation_Model!C8</f>
-        <v>1874463.5042082514</v>
+        <v>1874559.8091856597</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.4977415427784546</v>
+        <v>1.4997103404783552</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C96" s="248">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.18344802649326819</v>
+        <v>0.18367973395900203</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4796,13 +4796,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="338" t="s">
+      <c r="B98" s="336" t="s">
         <v>382</v>
       </c>
-      <c r="C98" s="338"/>
-      <c r="D98" s="338"/>
-      <c r="E98" s="338"/>
-      <c r="F98" s="338"/>
+      <c r="C98" s="336"/>
+      <c r="D98" s="336"/>
+      <c r="E98" s="336"/>
+      <c r="F98" s="336"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
-        <v>2.6800662791719922</v>
+        <v>2.6835066949111237</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4828,13 +4828,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="339" t="s">
+      <c r="B104" s="337" t="s">
         <v>383</v>
       </c>
-      <c r="C104" s="339"/>
-      <c r="D104" s="339"/>
-      <c r="E104" s="339"/>
-      <c r="F104" s="339"/>
+      <c r="C104" s="337"/>
+      <c r="D104" s="337"/>
+      <c r="E104" s="337"/>
+      <c r="F104" s="337"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="E107" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>3.23 HKD</v>
+        <v>3.24 HKD</v>
       </c>
       <c r="F107" s="259">
         <f>Valuation_Model!F74</f>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="C113" s="241">
         <f>Scenarios!C60</f>
-        <v>2.6941065610816408</v>
+        <v>2.6975644131821959</v>
       </c>
       <c r="D113" s="236" t="str">
         <f>Market_currency</f>
@@ -4977,13 +4977,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="342" t="s">
+      <c r="B115" s="341" t="s">
         <v>386</v>
       </c>
-      <c r="C115" s="342"/>
-      <c r="D115" s="342"/>
-      <c r="E115" s="342"/>
-      <c r="F115" s="342"/>
+      <c r="C115" s="341"/>
+      <c r="D115" s="341"/>
+      <c r="E115" s="341"/>
+      <c r="F115" s="341"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4996,22 +4996,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="343" t="s">
+      <c r="B119" s="339" t="s">
         <v>384</v>
       </c>
-      <c r="C119" s="343"/>
-      <c r="D119" s="343"/>
-      <c r="E119" s="343"/>
-      <c r="F119" s="343"/>
+      <c r="C119" s="339"/>
+      <c r="D119" s="339"/>
+      <c r="E119" s="339"/>
+      <c r="F119" s="339"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="338" t="s">
+      <c r="B120" s="336" t="s">
         <v>385</v>
       </c>
-      <c r="C120" s="338"/>
-      <c r="D120" s="338"/>
-      <c r="E120" s="338"/>
-      <c r="F120" s="338"/>
+      <c r="C120" s="336"/>
+      <c r="D120" s="336"/>
+      <c r="E120" s="336"/>
+      <c r="F120" s="336"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="C124" s="237">
         <f>Scenarios!C77</f>
-        <v>0.11451467713027945</v>
+        <v>0.11437021968222419</v>
       </c>
       <c r="D124" s="236" t="str">
         <f>Market_currency</f>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="C127" s="240">
         <f>Scenarios!C81</f>
-        <v>0.2235326497583055</v>
+        <v>0.22325066881970163</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>1.3793825592738</v>
+        <v>1.3811529795492843</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>1.6029152090321055</v>
+        <v>1.6044036483689859</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="C130" s="92">
         <f>Scenarios!F83</f>
-        <v>0.405029024394432</v>
+        <v>0.40523991177792018</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -5107,13 +5107,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="337" t="s">
+      <c r="B134" s="343" t="s">
         <v>392</v>
       </c>
-      <c r="C134" s="338"/>
-      <c r="D134" s="338"/>
-      <c r="E134" s="338"/>
-      <c r="F134" s="338"/>
+      <c r="C134" s="336"/>
+      <c r="D134" s="336"/>
+      <c r="E134" s="336"/>
+      <c r="F134" s="336"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5150,13 +5150,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="339" t="s">
+      <c r="B143" s="337" t="s">
         <v>397</v>
       </c>
-      <c r="C143" s="339"/>
-      <c r="D143" s="339"/>
-      <c r="E143" s="339"/>
-      <c r="F143" s="339"/>
+      <c r="C143" s="337"/>
+      <c r="D143" s="337"/>
+      <c r="E143" s="337"/>
+      <c r="F143" s="337"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5164,22 +5164,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="336" t="s">
+      <c r="B146" s="342" t="s">
         <v>398</v>
       </c>
-      <c r="C146" s="336"/>
-      <c r="D146" s="336"/>
-      <c r="E146" s="336"/>
-      <c r="F146" s="336"/>
+      <c r="C146" s="342"/>
+      <c r="D146" s="342"/>
+      <c r="E146" s="342"/>
+      <c r="F146" s="342"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="336" t="s">
+      <c r="B147" s="342" t="s">
         <v>399</v>
       </c>
-      <c r="C147" s="336"/>
-      <c r="D147" s="336"/>
-      <c r="E147" s="336"/>
-      <c r="F147" s="336"/>
+      <c r="C147" s="342"/>
+      <c r="D147" s="342"/>
+      <c r="E147" s="342"/>
+      <c r="F147" s="342"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5203,6 +5203,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5219,17 +5230,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -5721,15 +5721,15 @@
       </c>
       <c r="C25" s="39">
         <f>(0.0682+0.0538)/Exchange_Rate</f>
-        <v>0.11451467713027945</v>
+        <v>0.11437021968222419</v>
       </c>
       <c r="D25" s="39">
         <f>(0.064+0.041)/Exchange_Rate</f>
-        <v>9.8557713923601173E-2</v>
+        <v>9.8433385792078207E-2</v>
       </c>
       <c r="E25" s="39">
         <f>(0.022+0.0168)/Exchange_Rate</f>
-        <v>3.6419421907006908E-2</v>
+        <v>3.6373479702215564E-2</v>
       </c>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
@@ -7021,15 +7021,15 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.11451467713027945</v>
+        <v>0.11437021968222419</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>9.8557713923601173E-2</v>
+        <v>9.8433385792078207E-2</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>3.6419421907006908E-2</v>
+        <v>3.6373479702215564E-2</v>
       </c>
       <c r="F65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8372,11 +8372,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>2.5252949412160426</v>
+        <v>2.528484562288805</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.8629925615542839</v>
+        <v>1.8653456492018885</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>1874463.5042082514</v>
+        <v>1874559.8091856597</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>228</v>
@@ -8634,11 +8634,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-151242.18793829044</v>
+        <v>-151226.13710872241</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-138862.74929862475</v>
+        <v>-138846.69846905672</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>364</v>
@@ -8650,11 +8650,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>17.902676739275726</v>
+        <v>17.904576892375232</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>19.498677749618885</v>
+        <v>19.500931818003746</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>331</v>
@@ -8667,7 +8667,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>833176.49579174852</v>
+        <v>833080.19081434025</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>365</v>
@@ -8782,11 +8782,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-36221.365714380001</v>
+        <v>-36267.115788750009</v>
       </c>
       <c r="D86" s="248">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-2.7166020890032391E-2</v>
+        <v>-2.7200333441520827E-2</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -8799,11 +8799,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>1996988.9733281967</v>
+        <v>1999614.0372561971</v>
       </c>
       <c r="D87" s="248">
         <f>C87*$H$1/Common_Shares</f>
-        <v>1.4977415427784546</v>
+        <v>1.4997103404783552</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -8816,11 +8816,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>244597.39923236199</v>
+        <v>244906.34255862504</v>
       </c>
       <c r="D88" s="248">
         <f>C88*$H$1/Common_Shares</f>
-        <v>0.18344802649326819</v>
+        <v>0.18367973395900203</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -8833,11 +8833,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>2205365.0068461788</v>
+        <v>2208253.2640260719</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>1.6540235483816903</v>
+        <v>1.6561897409958364</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9417,20 +9417,20 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>23195.854182448693</v>
+        <v>23192.955721459057</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>23195.854182448693</v>
+        <v>23192.955721459057</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>21707.770734628681</v>
+        <v>21705.145648259142</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>13091.792396387922</v>
+        <v>13090.179393652897</v>
       </c>
       <c r="J12" s="191" t="str">
         <f t="shared" si="6"/>
@@ -9472,20 +9472,20 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>136972.78452510387</v>
+        <v>136969.88606411422</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>217057.8541824487</v>
+        <v>217054.95572145906</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>147523.77073462869</v>
+        <v>147521.14564825915</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>35789.792396387922</v>
+        <v>35788.179393652899</v>
       </c>
       <c r="J13" s="184" t="str">
         <f t="shared" si="7"/>
@@ -9527,7 +9527,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-34243.196131275967</v>
+        <v>-34242.471516028556</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -9639,22 +9639,22 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>102729.5883938279</v>
+        <v>102727.41454808567</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>169787.8541824487</v>
+        <v>169784.95572145906</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>103074.77073462869</v>
+        <v>103072.14564825915</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>14772.792396387922</v>
+        <v>14771.179393652899</v>
       </c>
       <c r="J16" s="184" t="str">
         <f t="shared" si="8"/>
@@ -9747,22 +9747,22 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>102729.5883938279</v>
+        <v>102727.41454808567</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>169787.8541824487</v>
+        <v>169784.95572145906</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>103074.77073462869</v>
+        <v>103072.14564825915</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>14772.792396387922</v>
+        <v>14771.179393652899</v>
       </c>
       <c r="J19" s="186" t="str">
         <f t="shared" si="9"/>
@@ -10608,15 +10608,15 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.26103928598942744</v>
+        <v>0.26104346429842845</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.35037347928068158</v>
+        <v>0.35038072953165883</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>1.3751168201530288</v>
+        <v>1.3752619609169703</v>
       </c>
       <c r="J43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -10746,20 +10746,20 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>25075.854182448693</v>
+        <v>25072.955721459057</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>25075.854182448693</v>
+        <v>25072.955721459057</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>22710.770734628681</v>
+        <v>22708.145648259142</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>13954.792396387922</v>
+        <v>13953.179393652897</v>
       </c>
       <c r="J48" s="328" t="str">
         <f t="shared" si="19"/>
@@ -10858,20 +10858,20 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>23195.854182448693</v>
+        <v>23192.955721459057</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>23195.854182448693</v>
+        <v>23192.955721459057</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>21707.770734628681</v>
+        <v>21705.145648259142</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>13091.792396387922</v>
+        <v>13090.179393652897</v>
       </c>
       <c r="J50" s="184" t="str">
         <f t="shared" si="20"/>
@@ -11945,22 +11945,22 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>1.4252938309046658E-2</v>
+        <v>1.4251157318989058E-2</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>1.2744218575188227E-2</v>
+        <v>1.2742626108702922E-2</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>1.3436477025120115E-2</v>
+        <v>1.3434852173212268E-2</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>9.0498054083937522E-3</v>
+        <v>9.0486904074501689E-3</v>
       </c>
       <c r="J80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -12002,22 +12002,22 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>8.4164378362571401E-2</v>
+        <v>8.4162597372513789E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.1192554805442582</v>
+        <v>0.11925388807777289</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>9.1312911876892083E-2</v>
+        <v>9.1311287024984228E-2</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>2.473997807080135E-2</v>
+        <v>2.4738863069857765E-2</v>
       </c>
       <c r="J81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -12059,7 +12059,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.104109459064285E-2</v>
+        <v>2.1040649343128447E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12174,22 +12174,22 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>6.3123283771928551E-2</v>
+        <v>6.3121948029385352E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.3284494207183696E-2</v>
+        <v>9.3282901740698393E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>6.3800277134677966E-2</v>
+        <v>6.379865228277011E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>1.0211810001111489E-2</v>
+        <v>1.0210695000167906E-2</v>
       </c>
       <c r="J84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -12281,22 +12281,22 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>6.3123283771928551E-2</v>
+        <v>6.3121948029385352E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.3284494207183696E-2</v>
+        <v>9.3282901740698393E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>6.3800277134677966E-2</v>
+        <v>6.379865228277011E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>1.0211810001111489E-2</v>
+        <v>1.0210695000167906E-2</v>
       </c>
       <c r="J87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -12350,20 +12350,20 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.11451467713027945</v>
+        <v>0.11437021968222419</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.11451467713027945</v>
+        <v>0.11437021968222419</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>9.8557713923601173E-2</v>
+        <v>9.8433385792078207E-2</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>3.6419421907006908E-2</v>
+        <v>3.6373479702215564E-2</v>
       </c>
       <c r="J90" s="113" t="str">
         <f>Data!F65</f>
@@ -12406,20 +12406,20 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/$C$3</f>
-        <v>152686.25525948545</v>
+        <v>152493.64530466887</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
-        <v>152686.25525948545</v>
+        <v>152493.64530466887</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>131410.30165775388</v>
+        <v>131244.53079500192</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>48559.235279246197</v>
+        <v>48497.978998534039</v>
       </c>
       <c r="J91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12461,20 +12461,20 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>1.4862928747863942</v>
+        <v>1.4844493651038801</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>0.89927666495751568</v>
+        <v>0.89815758208190444</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>1.2749026820159173</v>
+        <v>1.2733268524639332</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>3.2870722051925236</v>
+        <v>3.2832841377157314</v>
       </c>
       <c r="J92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12516,20 +12516,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.1816595986551785E-2</v>
+        <v>4.972618247053226E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.1816595986551785E-2</v>
+        <v>4.972618247053226E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>4.4596250644163428E-2</v>
+        <v>4.2797124257425309E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>1.6479376428509912E-2</v>
+        <v>1.5814556392267639E-2</v>
       </c>
       <c r="J93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -12653,18 +12653,18 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.36895725316637962</v>
+        <v>-0.36896218006704218</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>0.47134155466308236</v>
+        <v>0.47134808889697943</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>3.1219510049328338</v>
+        <v>3.1220634340069919</v>
       </c>
       <c r="I97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13372,20 +13372,20 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>8.4164378362571401E-2</v>
+        <v>8.4162597372513789E-2</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.1192554805442582</v>
+        <v>0.11925388807777289</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>9.1312911876892083E-2</v>
+        <v>9.1311287024984228E-2</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>2.473997807080135E-2</v>
+        <v>2.4738863069857765E-2</v>
       </c>
       <c r="J117" s="23" t="str">
         <f t="shared" si="45"/>
@@ -13658,22 +13658,22 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>8.2083418463224159E-2</v>
+        <v>8.2185356313222963E-2</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.13566458994659183</v>
+        <v>0.13583362478242111</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>8.2359227477638228E-2</v>
+        <v>8.2461152685833372E-2</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.1803817372404659E-2</v>
+        <v>1.1817435949053802E-2</v>
       </c>
       <c r="J124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -13715,22 +13715,22 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.7141818309151198E-2</v>
+        <v>3.5732763614444767E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.1386692283525716E-2</v>
+        <v>5.9058097731487444E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>3.7266618768162098E-2</v>
+        <v>3.585267508079712E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>5.3410938336672662E-3</v>
+        <v>5.1380156300233929E-3</v>
       </c>
       <c r="J125" s="77" t="str">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
@@ -13772,15 +13772,15 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.6260964568058162E-2</v>
+        <v>6.3668144215395017E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8648295836383833E-2</v>
+        <v>5.6353362521047078E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.2213571883936998E-2</v>
+        <v>2.1344345158043811E-2</v>
       </c>
       <c r="J126" s="23" t="str">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14558,7 +14558,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>102729.5883938279</v>
+        <v>102727.41454808567</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14590,7 +14590,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>1284119.8549228488</v>
+        <v>1284092.6818510708</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14624,7 +14624,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>1874463.5042082514</v>
+        <v>1874559.8091856597</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -14656,7 +14656,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>3354174.4591311002</v>
+        <v>3354243.5910367309</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -14670,7 +14670,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0653656200000001</v>
+        <v>1.0667112500000002</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>2.6800662791719922</v>
+        <v>2.6835066949111237</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14737,7 +14737,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>2.7077113618620618</v>
+        <v>2.7111861095082364</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14772,7 +14772,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>103610.79268207715</v>
+        <v>103608.60018930031</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>95935.919150071422</v>
+        <v>95933.889064166942</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -14794,7 +14794,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>104499.55585389414</v>
+        <v>104497.34455413026</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -14806,7 +14806,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>89591.525937837912</v>
+        <v>89589.630104707016</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -14816,7 +14816,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>105395.94274863736</v>
+        <v>105393.71248056197</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -14828,7 +14828,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>83666.697426584287</v>
+        <v>83664.926967879917</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -14838,7 +14838,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>106300.01876185102</v>
+        <v>106297.7693627558</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -14850,7 +14850,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>78133.687142783587</v>
+        <v>78132.033767297733</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>107211.84985003581</v>
+        <v>107209.58115581678</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -14872,7 +14872,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>72966.583530840071</v>
+        <v>72965.039495675388</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -14882,7 +14882,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>108131.50253546081</v>
+        <v>108129.21438060627</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -14894,7 +14894,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>68141.18860708081</v>
+        <v>68139.746681389865</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -14904,7 +14904,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>109059.0439110165</v>
+        <v>109056.73612859506</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -14916,7 +14916,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>63634.904638549429</v>
+        <v>63633.558069672166</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -14926,7 +14926,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>109994.5416451097</v>
+        <v>109992.214066758</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>59426.628315909533</v>
+        <v>59425.370797749863</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -14948,7 +14948,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>110938.06398660003</v>
+        <v>110935.71644251054</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -14960,7 +14960,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>55496.65192486038</v>
+        <v>55495.477568354319</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>111889.67976977916</v>
+        <v>111887.31208868777</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>51826.57105324234</v>
+        <v>51825.474358778949</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15432,7 +15432,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>1295134.9085259645</v>
+        <v>1295107.5023662539</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15444,7 +15444,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>599898.05582037999</v>
+        <v>599885.36146566854</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>1318718.4135481399</v>
+        <v>1318690.5083413408</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15476,7 +15476,7 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>1318718.4135481399</v>
+        <v>1318690.5083413408</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15506,19 +15506,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>1093779.71079345</v>
+        <v>1093756.5654815256</v>
       </c>
       <c r="C56" s="124">
-        <v>1129767.4009606747</v>
+        <v>1129743.4941185208</v>
       </c>
       <c r="D56" s="124">
-        <v>1325552.28346572</v>
+        <v>1325524.2336484026</v>
       </c>
       <c r="E56" s="124">
-        <v>1368225.5951630641</v>
+        <v>1368196.6423420613</v>
       </c>
       <c r="F56" s="124">
-        <v>1457514.3699060839</v>
+        <v>1457483.5276584239</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15527,19 +15527,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>966007.29094970552</v>
+        <v>965986.84941120422</v>
       </c>
       <c r="C57" s="124">
-        <v>1019056.0637466062</v>
+        <v>1019034.4996508096</v>
       </c>
       <c r="D57" s="124">
-        <v>1367022.8647279236</v>
+        <v>1366993.9373577232</v>
       </c>
       <c r="E57" s="124">
-        <v>1458235.000800272</v>
+        <v>1458204.1433034472</v>
       </c>
       <c r="F57" s="124">
-        <v>1669675.515036433</v>
+        <v>1669640.1832779199</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15548,19 +15548,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>844636.69930272014</v>
+        <v>844618.82606949471</v>
       </c>
       <c r="C58" s="124">
-        <v>909806.6770809025</v>
+        <v>909787.42479534238</v>
       </c>
       <c r="D58" s="124">
-        <v>1418354.2077545833</v>
+        <v>1418324.1941693667</v>
       </c>
       <c r="E58" s="124">
-        <v>1575573.6756037856</v>
+        <v>1575540.3351204854</v>
       </c>
       <c r="F58" s="124">
-        <v>1978136.608949563</v>
+        <v>1978094.7498911149</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15569,19 +15569,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>748204.97334011295</v>
+        <v>748189.1406844873</v>
       </c>
       <c r="C59" s="124">
-        <v>820246.7043886903</v>
+        <v>820229.3472685673</v>
       </c>
       <c r="D59" s="124">
-        <v>1470652.6144173618</v>
+        <v>1470621.4941532377</v>
       </c>
       <c r="E59" s="124">
-        <v>1701868.3485461257</v>
+        <v>1701832.3355597877</v>
       </c>
       <c r="F59" s="124">
-        <v>2352137.8298794646</v>
+        <v>2352088.0566360736</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -15590,19 +15590,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>677017.61988752359</v>
+        <v>677003.29361703596</v>
       </c>
       <c r="C60" s="124">
-        <v>752472.58821895358</v>
+        <v>752456.66525695566</v>
       </c>
       <c r="D60" s="124">
-        <v>1519293.0346528338</v>
+        <v>1519260.8851159164</v>
       </c>
       <c r="E60" s="124">
-        <v>1826272.8978483616</v>
+        <v>1826234.2523556151</v>
       </c>
       <c r="F60" s="124">
-        <v>2770744.5599884391</v>
+        <v>2770685.9286694713</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -15611,19 +15611,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>626335.2521621458</v>
+        <v>626321.99837380298</v>
       </c>
       <c r="C61" s="124">
-        <v>703286.99061124749</v>
+        <v>703272.10845846147</v>
       </c>
       <c r="D61" s="124">
-        <v>1562200.6515808266</v>
+        <v>1562167.5940821248</v>
       </c>
       <c r="E61" s="124">
-        <v>1942778.8607709736</v>
+        <v>1942737.7499126457</v>
       </c>
       <c r="F61" s="124">
-        <v>3219709.0501398249</v>
+        <v>3219640.9183491757</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -15673,23 +15673,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>2.6800662791719922</v>
+        <v>2.6835066949111237</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>2.6800662791719922</v>
+        <v>2.6835066949111237</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>2.6800662791719922</v>
+        <v>2.6835066949111237</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>2.6800662791719922</v>
+        <v>2.6835066949111237</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>2.6800662791719922</v>
+        <v>2.6835066949111237</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -15700,23 +15700,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.5279799139368087</v>
+        <v>2.531231456486001</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>2.5567349462279592</v>
+        <v>2.5600221991096808</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>2.7131717887258149</v>
+        <v>2.7166533175731744</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>2.74726879384411</v>
+        <v>2.7507926671193488</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>2.8186126780734777</v>
+        <v>2.8222251519736057</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15727,23 +15727,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>2.4258866692341656</v>
+        <v>2.429011424107367</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>2.4682739179765165</v>
+        <v>2.4714513127748696</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>2.7463077832224418</v>
+        <v>2.7498304630367056</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>2.8191884795360358</v>
+        <v>2.8228016685131454</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>2.9881345493245219</v>
+        <v>2.9919575492408246</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -15754,23 +15754,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>2.3289086396416012</v>
+        <v>2.3319129593280263</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>2.3809810234683333</v>
+        <v>2.3840500108665932</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>2.7873227641623415</v>
+        <v>2.7908963797082422</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>2.9129449103404998</v>
+        <v>2.9166745336615816</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>3.23460240193802</v>
+        <v>3.2387314856342102</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -15781,23 +15781,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>2.2518573651346436</v>
+        <v>2.2547659962957858</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>2.3094204455375884</v>
+        <v>2.3124005632031368</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>2.8291104522683574</v>
+        <v>2.83273596315636</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>3.0138573996328737</v>
+        <v>3.0177123442720619</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>3.5334383965460776</v>
+        <v>3.5379385990304821</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -15808,23 +15808,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>2.1949769530343124</v>
+        <v>2.1978149454839451</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>2.2552672923368897</v>
+        <v>2.2581801582223431</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>2.8679753210061674</v>
+        <v>2.8716490974419964</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>3.1132596345562424</v>
+        <v>3.1172380249571066</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>3.8679152686555085</v>
+        <v>3.8728308516620142</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15834,23 +15834,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>2.1544805190102547</v>
+        <v>2.1572682197018893</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>2.2159668137316464</v>
+        <v>2.2188308730935908</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>2.90225954165405</v>
+        <v>2.9059758950171948</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>3.2063507084869172</v>
+        <v>3.210444706937595</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>4.2266487231199132</v>
+        <v>4.2320098104408759</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15885,7 +15885,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>3.23460240193802</v>
+        <v>3.2387314856342102</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -15907,7 +15907,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>2.8191884795360358</v>
+        <v>2.8228016685131454</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -15930,7 +15930,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>2.7463077832224418</v>
+        <v>2.7498304630367056</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15953,7 +15953,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>2.4682739179765165</v>
+        <v>2.4714513127748696</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -15976,7 +15976,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.3289086396416012</v>
+        <v>2.3319129593280263</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-2.21</v>
+        <v>-2.2999999999999998</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16097,7 +16097,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.11451467713027945</v>
+        <v>0.11437021968222419</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.11451467713027945</v>
+        <v>0.11437021968222419</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
@@ -16126,7 +16126,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>2.8086212382119204</v>
+        <v>2.8119346328644199</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>169787.8541824487</v>
+        <v>169784.95572145906</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16182,7 +16182,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>102729.5883938279</v>
+        <v>102727.41454808567</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16266,7 +16266,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>2.3901741844763329</v>
+        <v>2.3903303431197065</v>
       </c>
       <c r="E14" s="346"/>
       <c r="F14" s="346"/>
@@ -16317,7 +16317,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>2.21</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16332,7 +16332,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>2.6800662791719922</v>
+        <v>2.6835066949111237</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16379,7 +16379,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>2.7463077832224418</v>
+        <v>2.7498304630367056</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16437,7 +16437,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>2.4682739179765165</v>
+        <v>2.4714513127748696</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16495,7 +16495,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>2.8191884795360358</v>
+        <v>2.8228016685131454</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16522,7 +16522,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>2.7052771494359757</v>
+        <v>2.7087488740796264</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16596,7 +16596,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>2.3289086396416012</v>
+        <v>2.3319129593280263</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16654,7 +16654,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>3.23460240193802</v>
+        <v>3.2387314856342102</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16680,7 +16680,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>2.6941065610816408</v>
+        <v>2.6975644131821959</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>2.7077113618620618</v>
+        <v>2.7111861095082364</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -16805,7 +16805,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.61394139796668856</v>
+        <v>0.61395743986780416</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16838,7 +16838,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.11451467713027945</v>
+        <v>0.11437021968222419</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -16865,7 +16865,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.2235326497583055</v>
+        <v>0.22325066881970163</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -16877,7 +16877,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>1.3793825592738</v>
+        <v>1.3811529795492843</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>1.6029152090321055</v>
+        <v>1.6044036483689859</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16898,7 +16898,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.405029024394432</v>
+        <v>0.40523991177792018</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16915,7 +16915,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>2.21</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16928,7 +16928,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11692472124626607</v>
+        <v>0.10185445179346719</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F774E9-2F59-47C8-93C2-594CD86AE19C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3C6D29-D3C0-4C45-985E-BDE89851C05C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="424">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1321,10 +1321,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Result</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Expected Holding period = </t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -1825,14 +1821,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 5: Determining the Investment Decision (Calculating Target Buy Price)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Implied Market Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -2319,6 +2307,45 @@
   </si>
   <si>
     <t xml:space="preserve">Use general Scenarios' HGP assumption </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>in contrast to a cash yield of</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HKD</t>
+  </si>
+  <si>
+    <t>Sell Price Output</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>@Cash Yield</t>
+    <phoneticPr fontId="28" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Implied Annual Return:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Buy)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Sell)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 5: Determining the Investment Decision</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3008,7 +3035,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="348">
+  <cellXfs count="349">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3701,29 +3728,32 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4013,7 +4043,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J152"/>
+  <dimension ref="A1:J158"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4033,15 +4063,15 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A2" s="247" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4065,13 +4095,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4098,7 +4128,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C8" s="279">
         <v>6</v>
@@ -4108,7 +4138,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -4134,24 +4164,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="336" t="s">
-        <v>375</v>
-      </c>
-      <c r="C12" s="336"/>
-      <c r="D12" s="336"/>
-      <c r="E12" s="336"/>
-      <c r="F12" s="336"/>
+      <c r="B12" s="339" t="s">
+        <v>372</v>
+      </c>
+      <c r="C12" s="339"/>
+      <c r="D12" s="339"/>
+      <c r="E12" s="339"/>
+      <c r="F12" s="339"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4161,10 +4191,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4174,7 +4204,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0667112500000002</v>
+        <v>1.06671125</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4187,18 +4217,23 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C19" s="249">
         <v>0.25</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="D19" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="E19" s="336">
+        <v>3.4500000000000003E-2</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B20" s="2" t="str">
@@ -4207,10 +4242,10 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>1.6044036483689859</v>
+        <v>1.6044036483689856</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
@@ -4218,11 +4253,11 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>374</v>
+        <v>415</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10185445179346719</v>
+        <v>0.10185445179346697</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4233,7 +4268,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4242,22 +4277,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="336" t="s">
-        <v>376</v>
-      </c>
-      <c r="C25" s="336"/>
-      <c r="D25" s="336"/>
-      <c r="E25" s="336"/>
-      <c r="F25" s="336"/>
+      <c r="B25" s="339" t="s">
+        <v>373</v>
+      </c>
+      <c r="C25" s="339"/>
+      <c r="D25" s="339"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="338" t="s">
-        <v>352</v>
-      </c>
-      <c r="C26" s="338"/>
-      <c r="D26" s="338"/>
-      <c r="E26" s="338"/>
-      <c r="F26" s="338"/>
+      <c r="B26" s="342" t="s">
+        <v>351</v>
+      </c>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4269,13 +4304,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="337" t="s">
+      <c r="B29" s="340" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="337"/>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
+      <c r="C29" s="340"/>
+      <c r="D29" s="340"/>
+      <c r="E29" s="340"/>
+      <c r="F29" s="340"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4295,13 +4330,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="337" t="s">
+      <c r="B32" s="340" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="337"/>
-      <c r="D32" s="337"/>
-      <c r="E32" s="337"/>
-      <c r="F32" s="337"/>
+      <c r="C32" s="340"/>
+      <c r="D32" s="340"/>
+      <c r="E32" s="340"/>
+      <c r="F32" s="340"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4330,13 +4365,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="337" t="s">
+      <c r="B36" s="340" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="337"/>
-      <c r="D36" s="337"/>
-      <c r="E36" s="337"/>
-      <c r="F36" s="337"/>
+      <c r="C36" s="340"/>
+      <c r="D36" s="340"/>
+      <c r="E36" s="340"/>
+      <c r="F36" s="340"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4352,17 +4387,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="337" t="s">
+      <c r="B39" s="340" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="337"/>
-      <c r="D39" s="337"/>
-      <c r="E39" s="337"/>
-      <c r="F39" s="337"/>
+      <c r="C39" s="340"/>
+      <c r="D39" s="340"/>
+      <c r="E39" s="340"/>
+      <c r="F39" s="340"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4377,7 +4412,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4410,7 +4445,7 @@
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B45" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C45" s="188">
         <f>Normalized_FCF!C15</f>
@@ -4422,13 +4457,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="337" t="s">
+      <c r="B47" s="340" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="337"/>
-      <c r="D47" s="337"/>
-      <c r="E47" s="337"/>
-      <c r="F47" s="337"/>
+      <c r="C47" s="340"/>
+      <c r="D47" s="340"/>
+      <c r="E47" s="340"/>
+      <c r="F47" s="340"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4444,13 +4479,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="337" t="s">
-        <v>351</v>
-      </c>
-      <c r="C50" s="340"/>
-      <c r="D50" s="340"/>
-      <c r="E50" s="340"/>
-      <c r="F50" s="340"/>
+      <c r="B50" s="340" t="s">
+        <v>350</v>
+      </c>
+      <c r="C50" s="341"/>
+      <c r="D50" s="341"/>
+      <c r="E50" s="341"/>
+      <c r="F50" s="341"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4466,26 +4501,26 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="336" t="s">
-        <v>356</v>
-      </c>
-      <c r="C53" s="336"/>
-      <c r="D53" s="336"/>
-      <c r="E53" s="336"/>
-      <c r="F53" s="336"/>
+      <c r="B53" s="339" t="s">
+        <v>355</v>
+      </c>
+      <c r="C53" s="339"/>
+      <c r="D53" s="339"/>
+      <c r="E53" s="339"/>
+      <c r="F53" s="339"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="336" t="s">
-        <v>377</v>
-      </c>
-      <c r="C54" s="336"/>
-      <c r="D54" s="336"/>
-      <c r="E54" s="336"/>
-      <c r="F54" s="336"/>
+      <c r="B54" s="339" t="s">
+        <v>374</v>
+      </c>
+      <c r="C54" s="339"/>
+      <c r="D54" s="339"/>
+      <c r="E54" s="339"/>
+      <c r="F54" s="339"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
@@ -4511,25 +4546,25 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.5732763614444767E-2</v>
+        <v>3.573276361444476E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="254" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.972618247053226E-2</v>
+        <v>4.9726182470532274E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4542,22 +4577,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="336" t="s">
-        <v>378</v>
-      </c>
-      <c r="C63" s="336"/>
-      <c r="D63" s="336"/>
-      <c r="E63" s="336"/>
-      <c r="F63" s="336"/>
+      <c r="B63" s="339" t="s">
+        <v>375</v>
+      </c>
+      <c r="C63" s="339"/>
+      <c r="D63" s="339"/>
+      <c r="E63" s="339"/>
+      <c r="F63" s="339"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="338" t="s">
+      <c r="B64" s="342" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="338"/>
-      <c r="D64" s="338"/>
-      <c r="E64" s="338"/>
-      <c r="F64" s="338"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4566,7 +4601,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
@@ -4574,26 +4609,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4610,27 +4645,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="336" t="s">
-        <v>379</v>
-      </c>
-      <c r="C73" s="336"/>
-      <c r="D73" s="336"/>
-      <c r="E73" s="336"/>
-      <c r="F73" s="336"/>
+      <c r="B73" s="339" t="s">
+        <v>376</v>
+      </c>
+      <c r="C73" s="339"/>
+      <c r="D73" s="339"/>
+      <c r="E73" s="339"/>
+      <c r="F73" s="339"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="336" t="s">
-        <v>380</v>
-      </c>
-      <c r="C74" s="336"/>
-      <c r="D74" s="336"/>
-      <c r="E74" s="336"/>
-      <c r="F74" s="336"/>
+      <c r="B74" s="339" t="s">
+        <v>377</v>
+      </c>
+      <c r="C74" s="339"/>
+      <c r="D74" s="339"/>
+      <c r="E74" s="339"/>
+      <c r="F74" s="339"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4642,11 +4677,11 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B77" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.0273169539152871</v>
+        <v>1.0273169539152869</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4655,7 +4690,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4667,13 +4702,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="336" t="s">
-        <v>381</v>
-      </c>
-      <c r="C81" s="336"/>
-      <c r="D81" s="336"/>
-      <c r="E81" s="336"/>
-      <c r="F81" s="336"/>
+      <c r="B81" s="339" t="s">
+        <v>378</v>
+      </c>
+      <c r="C81" s="339"/>
+      <c r="D81" s="339"/>
+      <c r="E81" s="339"/>
+      <c r="F81" s="339"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4686,13 +4721,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="336" t="s">
-        <v>357</v>
-      </c>
-      <c r="C85" s="336"/>
-      <c r="D85" s="336"/>
-      <c r="E85" s="336"/>
-      <c r="F85" s="336"/>
+      <c r="B85" s="339" t="s">
+        <v>356</v>
+      </c>
+      <c r="C85" s="339"/>
+      <c r="D85" s="339"/>
+      <c r="E85" s="339"/>
+      <c r="F85" s="339"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4709,11 +4744,11 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>2.7200333441520827E-2</v>
+        <v>2.720033344152082E-2</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4727,7 +4762,7 @@
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C90" s="188">
         <f>BS!C66</f>
@@ -4740,7 +4775,7 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="47" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C91" s="188">
         <f>Valuation_Model!C8</f>
@@ -4753,11 +4788,11 @@
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B92" s="47" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.4997103404783552</v>
+        <v>1.4997103404783547</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4784,11 +4819,11 @@
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B96" s="47" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C96" s="248">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.18367973395900203</v>
+        <v>0.183679733959002</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4796,21 +4831,21 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="336" t="s">
-        <v>382</v>
-      </c>
-      <c r="C98" s="336"/>
-      <c r="D98" s="336"/>
-      <c r="E98" s="336"/>
-      <c r="F98" s="336"/>
+      <c r="B98" s="339" t="s">
+        <v>379</v>
+      </c>
+      <c r="C98" s="339"/>
+      <c r="D98" s="339"/>
+      <c r="E98" s="339"/>
+      <c r="F98" s="339"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
-        <v>2.6835066949111237</v>
+        <v>2.6835066949111233</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4819,7 +4854,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="247" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4828,13 +4863,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="337" t="s">
-        <v>383</v>
-      </c>
-      <c r="C104" s="337"/>
-      <c r="D104" s="337"/>
-      <c r="E104" s="337"/>
-      <c r="F104" s="337"/>
+      <c r="B104" s="340" t="s">
+        <v>380</v>
+      </c>
+      <c r="C104" s="340"/>
+      <c r="D104" s="340"/>
+      <c r="E104" s="340"/>
+      <c r="F104" s="340"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4969,7 +5004,7 @@
       </c>
       <c r="C113" s="241">
         <f>Scenarios!C60</f>
-        <v>2.6975644131821959</v>
+        <v>2.697564413182195</v>
       </c>
       <c r="D113" s="236" t="str">
         <f>Market_currency</f>
@@ -4977,17 +5012,17 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="341" t="s">
-        <v>386</v>
-      </c>
-      <c r="C115" s="341"/>
-      <c r="D115" s="341"/>
-      <c r="E115" s="341"/>
-      <c r="F115" s="341"/>
+      <c r="B115" s="343" t="s">
+        <v>383</v>
+      </c>
+      <c r="C115" s="343"/>
+      <c r="D115" s="343"/>
+      <c r="E115" s="343"/>
+      <c r="F115" s="343"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
-        <v>373</v>
+        <v>419</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -4996,22 +5031,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="339" t="s">
-        <v>384</v>
-      </c>
-      <c r="C119" s="339"/>
-      <c r="D119" s="339"/>
-      <c r="E119" s="339"/>
-      <c r="F119" s="339"/>
+      <c r="B119" s="344" t="s">
+        <v>381</v>
+      </c>
+      <c r="C119" s="344"/>
+      <c r="D119" s="344"/>
+      <c r="E119" s="344"/>
+      <c r="F119" s="344"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="336" t="s">
-        <v>385</v>
-      </c>
-      <c r="C120" s="336"/>
-      <c r="D120" s="336"/>
-      <c r="E120" s="336"/>
-      <c r="F120" s="336"/>
+      <c r="B120" s="339" t="s">
+        <v>382</v>
+      </c>
+      <c r="C120" s="339"/>
+      <c r="D120" s="339"/>
+      <c r="E120" s="339"/>
+      <c r="F120" s="339"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5020,7 +5055,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B122" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C122" s="251">
         <f>E20</f>
@@ -5029,7 +5064,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B123" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C123" s="250">
         <f>C19</f>
@@ -5042,7 +5077,7 @@
       </c>
       <c r="C124" s="237">
         <f>Scenarios!C77</f>
-        <v>0.11437021968222419</v>
+        <v>0.11437021968222422</v>
       </c>
       <c r="D124" s="236" t="str">
         <f>Market_currency</f>
@@ -5051,7 +5086,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B126" s="234" t="s">
-        <v>265</v>
+        <v>416</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
@@ -5061,7 +5096,7 @@
       </c>
       <c r="C127" s="240">
         <f>Scenarios!C81</f>
-        <v>0.22325066881970163</v>
+        <v>0.22325066881970168</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5071,7 +5106,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>1.3811529795492843</v>
+        <v>1.3811529795492838</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5080,7 +5115,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>1.6044036483689859</v>
+        <v>1.6044036483689856</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5093,127 +5128,163 @@
       </c>
       <c r="C130" s="92">
         <f>Scenarios!F83</f>
-        <v>0.40523991177792018</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A132" s="247" t="s">
+        <v>0.40523991177792007</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B132" s="234" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B133" s="236" t="str">
+        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C133" s="240">
+        <f>Scenarios!C91</f>
+        <v>0.32073012099393367</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B134" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C134" s="240">
+        <f>Scenarios!C92</f>
+        <v>2.4365781125120498</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B135" s="80" t="s">
+        <v>418</v>
+      </c>
+      <c r="C135" s="239">
+        <f>Scenarios!C93</f>
+        <v>2.7573082335059835</v>
+      </c>
+      <c r="D135" s="101" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B136" s="238" t="s">
+        <v>264</v>
+      </c>
+      <c r="C136" s="92">
+        <f>Scenarios!F93</f>
+        <v>-2.2147319275060973E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A138" s="247" t="s">
+        <v>387</v>
+      </c>
+      <c r="B138" s="36"/>
+      <c r="C138" s="36"/>
+      <c r="D138" s="36"/>
+      <c r="E138" s="36"/>
+      <c r="F138" s="36"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B140" s="338" t="s">
+        <v>389</v>
+      </c>
+      <c r="C140" s="339"/>
+      <c r="D140" s="339"/>
+      <c r="E140" s="339"/>
+      <c r="F140" s="339"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B142" s="234" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B143" s="341" t="s">
+        <v>393</v>
+      </c>
+      <c r="C143" s="341"/>
+      <c r="D143" s="341"/>
+      <c r="E143" s="341"/>
+      <c r="F143" s="341"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B144" s="238" t="s">
         <v>390</v>
       </c>
-      <c r="B132" s="36"/>
-      <c r="C132" s="36"/>
-      <c r="D132" s="36"/>
-      <c r="E132" s="36"/>
-      <c r="F132" s="36"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="343" t="s">
+    </row>
+    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B145" s="238" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B146" s="238" t="s">
         <v>392</v>
       </c>
-      <c r="C134" s="336"/>
-      <c r="D134" s="336"/>
-      <c r="E134" s="336"/>
-      <c r="F134" s="336"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B136" s="234" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B137" s="340" t="s">
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B148" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B149" s="340" t="s">
+        <v>394</v>
+      </c>
+      <c r="C149" s="340"/>
+      <c r="D149" s="340"/>
+      <c r="E149" s="340"/>
+      <c r="F149" s="340"/>
+    </row>
+    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B151" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B152" s="337" t="s">
+        <v>395</v>
+      </c>
+      <c r="C152" s="337"/>
+      <c r="D152" s="337"/>
+      <c r="E152" s="337"/>
+      <c r="F152" s="337"/>
+    </row>
+    <row r="153" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B153" s="337" t="s">
         <v>396</v>
       </c>
-      <c r="C137" s="340"/>
-      <c r="D137" s="340"/>
-      <c r="E137" s="340"/>
-      <c r="F137" s="340"/>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B138" s="238" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B139" s="238" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B140" s="238" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B142" s="1" t="s">
+      <c r="C153" s="337"/>
+      <c r="D153" s="337"/>
+      <c r="E153" s="337"/>
+      <c r="F153" s="337"/>
+    </row>
+    <row r="155" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B155" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B156" s="238" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="157" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B157" s="238" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="337" t="s">
-        <v>397</v>
-      </c>
-      <c r="C143" s="337"/>
-      <c r="D143" s="337"/>
-      <c r="E143" s="337"/>
-      <c r="F143" s="337"/>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B145" s="1" t="s">
+    <row r="158" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B158" s="238" t="s">
         <v>401</v>
-      </c>
-    </row>
-    <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="342" t="s">
-        <v>398</v>
-      </c>
-      <c r="C146" s="342"/>
-      <c r="D146" s="342"/>
-      <c r="E146" s="342"/>
-      <c r="F146" s="342"/>
-    </row>
-    <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="342" t="s">
-        <v>399</v>
-      </c>
-      <c r="C147" s="342"/>
-      <c r="D147" s="342"/>
-      <c r="E147" s="342"/>
-      <c r="F147" s="342"/>
-    </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B149" s="1" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B150" s="238" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B151" s="238" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B152" s="238" t="s">
-        <v>404</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5230,9 +5301,20 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B140:F140"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B143:F143"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5668,7 +5750,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C22" s="181"/>
       <c r="D22" s="181"/>
@@ -5684,7 +5766,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C23" s="181"/>
       <c r="D23" s="181"/>
@@ -5700,7 +5782,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C24" s="181"/>
       <c r="D24" s="181"/>
@@ -5721,15 +5803,15 @@
       </c>
       <c r="C25" s="39">
         <f>(0.0682+0.0538)/Exchange_Rate</f>
-        <v>0.11437021968222419</v>
+        <v>0.11437021968222422</v>
       </c>
       <c r="D25" s="39">
         <f>(0.064+0.041)/Exchange_Rate</f>
-        <v>9.8433385792078207E-2</v>
+        <v>9.8433385792078235E-2</v>
       </c>
       <c r="E25" s="39">
         <f>(0.022+0.0168)/Exchange_Rate</f>
-        <v>3.6373479702215564E-2</v>
+        <v>3.6373479702215571E-2</v>
       </c>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
@@ -5745,7 +5827,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -6968,7 +7050,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7021,15 +7103,15 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.11437021968222419</v>
+        <v>0.11437021968222422</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>9.8433385792078207E-2</v>
+        <v>9.8433385792078235E-2</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>3.6373479702215564E-2</v>
+        <v>3.6373479702215571E-2</v>
       </c>
       <c r="F65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8339,13 +8421,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C45" s="261" t="s">
         <v>138</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>60</v>
@@ -8353,7 +8435,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C46" s="188">
         <f>G29</f>
@@ -8372,11 +8454,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>2.528484562288805</v>
+        <v>2.5284845622888046</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.8653456492018885</v>
+        <v>1.8653456492018881</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8506,7 +8588,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="158" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C61" s="262" t="s">
         <v>139</v>
@@ -8529,7 +8611,7 @@
         <v>-5.2144077122608828E-4</v>
       </c>
       <c r="F62" s="283" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8551,7 +8633,7 @@
         <v>138</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F65" s="287" t="s">
         <v>60</v>
@@ -8618,7 +8700,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>97</v>
@@ -8630,7 +8712,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8641,12 +8723,12 @@
         <v>-138846.69846905672</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8657,12 +8739,12 @@
         <v>19.500931818003746</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8670,12 +8752,12 @@
         <v>833080.19081434025</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8683,7 +8765,7 @@
         <v>6</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8759,7 +8841,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="79" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8770,23 +8852,23 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>300</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="267" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-36267.115788750009</v>
+        <v>-36267.115788750001</v>
       </c>
       <c r="D86" s="248">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-2.7200333441520827E-2</v>
+        <v>-2.720033344152082E-2</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -8795,15 +8877,15 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="267" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>1999614.0372561971</v>
+        <v>1999614.0372561966</v>
       </c>
       <c r="D87" s="248">
         <f>C87*$H$1/Common_Shares</f>
-        <v>1.4997103404783552</v>
+        <v>1.4997103404783547</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -8816,11 +8898,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>244906.34255862504</v>
+        <v>244906.34255862498</v>
       </c>
       <c r="D88" s="248">
         <f>C88*$H$1/Common_Shares</f>
-        <v>0.18367973395900203</v>
+        <v>0.183679733959002</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -8829,7 +8911,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="80" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -8837,7 +8919,7 @@
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>1.6561897409958364</v>
+        <v>1.6561897409958359</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9700,7 +9782,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9725,7 +9807,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10053,7 +10135,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10113,7 +10195,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10237,7 +10319,7 @@
         <v>-192887</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10295,7 +10377,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10603,7 +10685,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10742,7 +10824,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -10797,7 +10879,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -10930,7 +11012,7 @@
         <v>3.0096689367862788E-2</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -10957,7 +11039,7 @@
         <v>5.5295743992470364E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11272,7 +11354,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11833,7 +11915,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12350,20 +12432,20 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.11437021968222419</v>
+        <v>0.11437021968222422</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.11437021968222419</v>
+        <v>0.11437021968222422</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>9.8433385792078207E-2</v>
+        <v>9.8433385792078235E-2</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>3.6373479702215564E-2</v>
+        <v>3.6373479702215571E-2</v>
       </c>
       <c r="J90" s="113" t="str">
         <f>Data!F65</f>
@@ -12406,20 +12488,20 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/$C$3</f>
-        <v>152493.64530466887</v>
+        <v>152493.6453046689</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
-        <v>152493.64530466887</v>
+        <v>152493.6453046689</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>131244.53079500192</v>
+        <v>131244.53079500195</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>48497.978998534039</v>
+        <v>48497.978998534047</v>
       </c>
       <c r="J91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12461,20 +12543,20 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>1.4844493651038801</v>
+        <v>1.4844493651038804</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>0.89815758208190444</v>
+        <v>0.89815758208190466</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>1.2733268524639332</v>
+        <v>1.2733268524639334</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>3.2832841377157314</v>
+        <v>3.2832841377157318</v>
       </c>
       <c r="J92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12512,20 +12594,20 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.972618247053226E-2</v>
+        <v>4.9726182470532274E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.972618247053226E-2</v>
+        <v>4.9726182470532274E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>4.2797124257425309E-2</v>
+        <v>4.2797124257425323E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -13206,7 +13288,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13258,7 +13340,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13658,22 +13740,22 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>8.2185356313222963E-2</v>
+        <v>8.2185356313222949E-2</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.13583362478242111</v>
+        <v>0.13583362478242109</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>8.2461152685833372E-2</v>
+        <v>8.2461152685833358E-2</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.1817435949053802E-2</v>
+        <v>1.18174359490538E-2</v>
       </c>
       <c r="J124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -13711,26 +13793,26 @@
     <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.5732763614444767E-2</v>
+        <v>3.573276361444476E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>5.9058097731487444E-2</v>
+        <v>5.905809773148743E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>3.585267508079712E-2</v>
+        <v>3.5852675080797113E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>5.1380156300233929E-3</v>
+        <v>5.1380156300233921E-3</v>
       </c>
       <c r="J125" s="77" t="str">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
@@ -13767,7 +13849,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14596,10 +14678,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="344" t="s">
+      <c r="E6" s="345" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="344"/>
+      <c r="F6" s="345"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14614,8 +14696,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="344"/>
-      <c r="F7" s="344"/>
+      <c r="E7" s="345"/>
+      <c r="F7" s="345"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14630,8 +14712,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="344"/>
-      <c r="F8" s="344"/>
+      <c r="E8" s="345"/>
+      <c r="F8" s="345"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14646,8 +14728,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="344"/>
-      <c r="F9" s="344"/>
+      <c r="E9" s="345"/>
+      <c r="F9" s="345"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -14670,7 +14752,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0667112500000002</v>
+        <v>1.06671125</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14684,7 +14766,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>2.6835066949111237</v>
+        <v>2.6835066949111233</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14737,7 +14819,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>2.7111861095082364</v>
+        <v>2.7111861095082355</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15673,23 +15755,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>2.6835066949111237</v>
+        <v>2.6835066949111233</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>2.6835066949111237</v>
+        <v>2.6835066949111233</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>2.6835066949111237</v>
+        <v>2.6835066949111233</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>2.6835066949111237</v>
+        <v>2.6835066949111233</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>2.6835066949111237</v>
+        <v>2.6835066949111233</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -15700,23 +15782,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.531231456486001</v>
+        <v>2.5312314564860006</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>2.5600221991096808</v>
+        <v>2.5600221991096803</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>2.7166533175731744</v>
+        <v>2.716653317573174</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>2.7507926671193488</v>
+        <v>2.7507926671193479</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>2.8222251519736057</v>
+        <v>2.8222251519736052</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15727,23 +15809,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>2.429011424107367</v>
+        <v>2.4290114241073666</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>2.4714513127748696</v>
+        <v>2.4714513127748692</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>2.7498304630367056</v>
+        <v>2.7498304630367052</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>2.8228016685131454</v>
+        <v>2.8228016685131445</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>2.9919575492408246</v>
+        <v>2.9919575492408241</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -15754,23 +15836,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>2.3319129593280263</v>
+        <v>2.3319129593280259</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>2.3840500108665932</v>
+        <v>2.3840500108665927</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>2.7908963797082422</v>
+        <v>2.7908963797082418</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>2.9166745336615816</v>
+        <v>2.9166745336615811</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>3.2387314856342102</v>
+        <v>3.2387314856342093</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -15781,23 +15863,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>2.2547659962957858</v>
+        <v>2.2547659962957853</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>2.3124005632031368</v>
+        <v>2.3124005632031364</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>2.83273596315636</v>
+        <v>2.8327359631563591</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>3.0177123442720619</v>
+        <v>3.0177123442720615</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>3.5379385990304821</v>
+        <v>3.5379385990304812</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -15808,23 +15890,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>2.1978149454839451</v>
+        <v>2.1978149454839446</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>2.2581801582223431</v>
+        <v>2.2581801582223426</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>2.8716490974419964</v>
+        <v>2.8716490974419959</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>3.1172380249571066</v>
+        <v>3.1172380249571061</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>3.8728308516620142</v>
+        <v>3.8728308516620134</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15834,23 +15916,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>2.1572682197018893</v>
+        <v>2.1572682197018889</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>2.2188308730935908</v>
+        <v>2.2188308730935904</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>2.9059758950171948</v>
+        <v>2.9059758950171939</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>3.210444706937595</v>
+        <v>3.2104447069375945</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>4.2320098104408759</v>
+        <v>4.232009810440875</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15885,7 +15967,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>3.2387314856342102</v>
+        <v>3.2387314856342093</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -15907,7 +15989,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>2.8228016685131454</v>
+        <v>2.8228016685131445</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -15930,7 +16012,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>2.7498304630367056</v>
+        <v>2.7498304630367052</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15953,7 +16035,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>2.4714513127748696</v>
+        <v>2.4714513127748692</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -15976,7 +16058,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.3319129593280263</v>
+        <v>2.3319129593280259</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -15992,7 +16074,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="156" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>107</v>
@@ -16044,7 +16126,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I92"/>
+  <dimension ref="B2:I98"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -16064,7 +16146,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I2" s="278"/>
     </row>
@@ -16097,7 +16179,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.11437021968222419</v>
+        <v>0.11437021968222422</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -16106,7 +16188,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.11437021968222419</v>
+        <v>0.11437021968222422</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
@@ -16118,7 +16200,7 @@
         <v>1000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="276">
@@ -16126,12 +16208,12 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>2.8119346328644199</v>
+        <v>2.811934632864419</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C7" s="115">
         <f>Normalized_FCF!G8</f>
@@ -16141,11 +16223,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="346" t="str">
+      <c r="E7" s="347" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 朝云集团(6601.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="346"/>
+      <c r="F7" s="347"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16166,8 +16248,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="346"/>
-      <c r="F8" s="346"/>
+      <c r="E8" s="347"/>
+      <c r="F8" s="347"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16188,8 +16270,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="346"/>
-      <c r="F9" s="346"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16199,8 +16281,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="346"/>
-      <c r="F10" s="346"/>
+      <c r="E10" s="347"/>
+      <c r="F10" s="347"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16211,10 +16293,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="160" t="s">
-        <v>282</v>
-      </c>
-      <c r="E11" s="346"/>
-      <c r="F11" s="346"/>
+        <v>281</v>
+      </c>
+      <c r="E11" s="347"/>
+      <c r="F11" s="347"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16232,8 +16314,8 @@
         <v>0.12167914390403989</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="346"/>
-      <c r="F12" s="346"/>
+      <c r="E12" s="347"/>
+      <c r="F12" s="347"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16250,8 +16332,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>7.4870016543118432</v>
       </c>
-      <c r="E13" s="346"/>
-      <c r="F13" s="346"/>
+      <c r="E13" s="347"/>
+      <c r="F13" s="347"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16268,8 +16350,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>2.3903303431197065</v>
       </c>
-      <c r="E14" s="346"/>
-      <c r="F14" s="346"/>
+      <c r="E14" s="347"/>
+      <c r="F14" s="347"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -16285,7 +16367,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16295,25 +16377,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="346" t="s">
-        <v>343</v>
-      </c>
-      <c r="F18" s="347"/>
+      <c r="E18" s="347" t="s">
+        <v>342</v>
+      </c>
+      <c r="F18" s="348"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="347"/>
-      <c r="F19" s="347"/>
+      <c r="E19" s="348"/>
+      <c r="F19" s="348"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="160" t="s">
-        <v>314</v>
-      </c>
-      <c r="E20" s="347"/>
-      <c r="F20" s="347"/>
+        <v>313</v>
+      </c>
+      <c r="E20" s="348"/>
+      <c r="F20" s="348"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="100" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16323,23 +16405,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="347"/>
-      <c r="F21" s="347"/>
+      <c r="E21" s="348"/>
+      <c r="F21" s="348"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>2.6835066949111237</v>
+        <v>2.6835066949111233</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="347"/>
-      <c r="F22" s="347"/>
+      <c r="E22" s="348"/>
+      <c r="F22" s="348"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="160" t="s">
@@ -16359,8 +16441,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="345"/>
-      <c r="F25" s="345"/>
+      <c r="E25" s="346"/>
+      <c r="F25" s="346"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="119" t="s">
@@ -16370,8 +16452,8 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="E26" s="346"/>
+      <c r="F26" s="346"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="100" t="s">
@@ -16379,14 +16461,14 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>2.7498304630367056</v>
+        <v>2.7498304630367052</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="345"/>
-      <c r="F27" s="345"/>
+      <c r="E27" s="346"/>
+      <c r="F27" s="346"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="100" t="s">
@@ -16396,8 +16478,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="345"/>
-      <c r="F28" s="345"/>
+      <c r="E28" s="346"/>
+      <c r="F28" s="346"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="160" t="s">
@@ -16417,8 +16499,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="E31" s="346"/>
+      <c r="F31" s="346"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="119" t="s">
@@ -16428,8 +16510,8 @@
         <v>-0.08</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="345"/>
-      <c r="F32" s="345"/>
+      <c r="E32" s="346"/>
+      <c r="F32" s="346"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="100" t="s">
@@ -16437,14 +16519,14 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>2.4714513127748696</v>
+        <v>2.4714513127748692</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="345"/>
-      <c r="F33" s="345"/>
+      <c r="E33" s="346"/>
+      <c r="F33" s="346"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="100" t="s">
@@ -16454,8 +16536,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="345"/>
-      <c r="F34" s="345"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="160" t="s">
@@ -16475,8 +16557,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="345"/>
-      <c r="F37" s="345"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="119" t="s">
@@ -16486,8 +16568,8 @@
         <v>0.04</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="345"/>
-      <c r="F38" s="345"/>
+      <c r="E38" s="346"/>
+      <c r="F38" s="346"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="100" t="s">
@@ -16495,14 +16577,14 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>2.8228016685131454</v>
+        <v>2.8228016685131445</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="345"/>
-      <c r="F39" s="345"/>
+      <c r="E39" s="346"/>
+      <c r="F39" s="346"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="100" t="s">
@@ -16513,8 +16595,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="345"/>
-      <c r="F40" s="345"/>
+      <c r="E40" s="346"/>
+      <c r="F40" s="346"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="100" t="s">
@@ -16522,7 +16604,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>2.7087488740796264</v>
+        <v>2.7087488740796259</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16576,8 +16658,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="345"/>
-      <c r="F49" s="345"/>
+      <c r="E49" s="346"/>
+      <c r="F49" s="346"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="119" t="s">
@@ -16587,8 +16669,8 @@
         <v>-0.1</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="345"/>
-      <c r="F50" s="345"/>
+      <c r="E50" s="346"/>
+      <c r="F50" s="346"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="100" t="s">
@@ -16596,14 +16678,14 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>2.3319129593280263</v>
+        <v>2.3319129593280259</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="345"/>
-      <c r="F51" s="345"/>
+      <c r="E51" s="346"/>
+      <c r="F51" s="346"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="100" t="s">
@@ -16613,12 +16695,12 @@
         <v>0.1</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="345"/>
-      <c r="F52" s="345"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>151</v>
@@ -16634,8 +16716,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="345"/>
-      <c r="F55" s="345"/>
+      <c r="E55" s="346"/>
+      <c r="F55" s="346"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="119" t="s">
@@ -16645,8 +16727,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="345"/>
-      <c r="F56" s="345"/>
+      <c r="E56" s="346"/>
+      <c r="F56" s="346"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="100" t="s">
@@ -16654,14 +16736,14 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>3.2387314856342102</v>
+        <v>3.2387314856342093</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="345"/>
-      <c r="F57" s="345"/>
+      <c r="E57" s="346"/>
+      <c r="F57" s="346"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="100" t="s">
@@ -16671,8 +16753,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="E58" s="346"/>
+      <c r="F58" s="346"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="100" t="s">
@@ -16680,14 +16762,14 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>2.6975644131821959</v>
+        <v>2.697564413182195</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
@@ -16696,7 +16778,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16705,10 +16787,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="109" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -16721,7 +16803,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16733,7 +16815,7 @@
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16742,27 +16824,27 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>2.7111861095082364</v>
+        <v>2.7111861095082355</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="100" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16772,19 +16854,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="100" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="100" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16794,14 +16876,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="100" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -16824,7 +16906,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="275" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -16838,7 +16920,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.11437021968222419</v>
+        <v>0.11437021968222422</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -16847,12 +16929,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="109" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="149" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!C123</f>
@@ -16865,7 +16947,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.22325066881970163</v>
+        <v>0.22325066881970168</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -16877,7 +16959,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>1.3811529795492843</v>
+        <v>1.3811529795492838</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -16887,7 +16969,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>1.6044036483689859</v>
+        <v>1.6044036483689856</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16898,7 +16980,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.40523991177792018</v>
+        <v>0.40523991177792007</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16906,12 +16988,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="109" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="149" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -16924,53 +17006,109 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="100" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10185445179346719</v>
+        <v>0.10185445179346697</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
-      <c r="E89" s="320" t="s">
+    <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B89" s="109" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B90" s="149" t="s">
+        <v>413</v>
+      </c>
+      <c r="C90" s="135">
+        <f>Thesis!E19</f>
+        <v>3.4500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B91" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C91" s="117">
+        <f>PV(C90, C76, -C77, 0)</f>
+        <v>0.32073012099393367</v>
+      </c>
+      <c r="D91" s="117"/>
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B92" s="100" t="s">
+        <v>124</v>
+      </c>
+      <c r="C92" s="117">
+        <f>C60/(1+C90)^C76</f>
+        <v>2.4365781125120498</v>
+      </c>
+      <c r="D92" s="117"/>
+    </row>
+    <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B93" s="111" t="s">
+        <v>414</v>
+      </c>
+      <c r="C93" s="112">
+        <f>C91+C92</f>
+        <v>2.7573082335059835</v>
+      </c>
+      <c r="D93" t="s">
+        <v>411</v>
+      </c>
+      <c r="E93" s="147" t="s">
+        <v>128</v>
+      </c>
+      <c r="F93" s="329">
+        <f>(1-C93/C60)</f>
+        <v>-2.2147319275060973E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B94" s="100"/>
+    </row>
+    <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
+      <c r="E95" s="320" t="s">
+        <v>336</v>
+      </c>
+      <c r="F95" s="317"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="316"/>
+    </row>
+    <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E96" s="313" t="s">
         <v>337</v>
       </c>
-      <c r="F89" s="317"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="316"/>
-    </row>
-    <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E90" s="313" t="s">
+      <c r="F96" s="318" t="s">
         <v>338</v>
       </c>
-      <c r="F90" s="318" t="s">
+      <c r="G96" s="2"/>
+      <c r="H96" s="316"/>
+    </row>
+    <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E97" s="314" t="s">
+        <v>337</v>
+      </c>
+      <c r="F97" s="318" t="s">
         <v>339</v>
       </c>
-      <c r="G90" s="2"/>
-      <c r="H90" s="316"/>
-    </row>
-    <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E91" s="314" t="s">
-        <v>338</v>
-      </c>
-      <c r="F91" s="318" t="s">
+      <c r="G97" s="2"/>
+      <c r="H97" s="316"/>
+    </row>
+    <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E98" s="315" t="s">
+        <v>337</v>
+      </c>
+      <c r="F98" s="319" t="s">
         <v>340</v>
       </c>
-      <c r="G91" s="2"/>
-      <c r="H91" s="316"/>
-    </row>
-    <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E92" s="315" t="s">
-        <v>338</v>
-      </c>
-      <c r="F92" s="319" t="s">
-        <v>341</v>
-      </c>
-      <c r="G92" s="2"/>
-      <c r="H92" s="316"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="316"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/6601.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6601.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3C6D29-D3C0-4C45-985E-BDE89851C05C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE05752-3E5D-46BB-9513-ABEE6890516D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="427">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1357,10 +1357,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Stress Test</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Rough Estimate only</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2321,31 +2317,47 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>@Cash Yield</t>
+    <t>Sell Above</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Implied Annual Return:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Buy)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Sell)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 5: Determining the Investment Decision</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>@Selling Yield</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
   <si>
-    <t>Sell Above</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Implied Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result (Buy)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result (Sell)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sell Above:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 5: Determining the Investment Decision</t>
+    <t>Liabilities to Equity Ratio =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Debt to Equity Ratio =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Est. Realizable Value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt to EBIT Ratio = </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3035,7 +3047,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="349">
+  <cellXfs count="352">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3731,6 +3743,11 @@
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4043,7 +4060,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J158"/>
+  <dimension ref="A1:J162"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4063,10 +4080,10 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -4095,13 +4112,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
      